--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E382D22D-3245-4DBD-B9CA-CC784B2230BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55D19DD-6D68-4182-A566-FD500A546B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -426,94 +426,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Nội dung giải đố gồm: Người chơi cần </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>tìm các mảnh giấy có chứa câu đố</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, sau khi giải xong sẽ </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>nhận được một dãy số dùng để nhập vào máy chủ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Khi thoả sẽ hoàn thành điều kiện.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Người chơi </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>cần tìm ra các đồ vật phù hợp với gợi ý được đưa ra bởi chính puzzle</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Sau khi thoả sẽ hoàn thành điều kiện.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Timlapse nhỏ chỉ hiển thị khi người chơi tiếp xúc đúng puzzle có chứa sự biến đổi trong khoảng thời gian 2.5 giây</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Khi timelapse nhỏ về 0, người chơi vẫn tính là thua. Mỗi puzzle sẽ có số thời gian timelapse khác nhau tuỳ vào độ khó.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <b/>
         <sz val="15"/>
@@ -1330,6 +1242,94 @@
         <family val="2"/>
       </rPr>
       <t>. Khi puzzle được kích hoạt, timelapse nhỏ sẽ xuất hiện trên đầu.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Timelapse nhỏ chỉ hiển thị khi người chơi tiếp xúc đúng puzzle có chứa sự biến đổi trong khoảng thời gian 2.5 giây</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Khi timelapse nhỏ về 0, người chơi vẫn tính là thua. Mỗi puzzle sẽ có số thời gian timelapse khác nhau tuỳ vào độ khó.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Người chơi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>cần tìm ra các đồ vật phù hợp với gợi ý được đưa ra bởi chính puzzle (số lượng là 2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Sau khi thoả sẽ hoàn thành điều kiện.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nội dung giải đố gồm: Người chơi cần </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>tìm các mảnh giấy có chứa câu đố (số lượng là 5)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, sau khi giải xong sẽ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>nhận được một dãy số dùng để nhập vào máy chủ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Khi thoả sẽ hoàn thành điều kiện.</t>
     </r>
   </si>
 </sst>
@@ -1455,7 +1455,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1495,11 +1495,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1507,20 +1510,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1531,19 +1522,22 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1552,23 +1546,32 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2323,29 +2326,29 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:26" ht="46.5" x14ac:dyDescent="0.7">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
     </row>
     <row r="3" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
@@ -2369,91 +2372,91 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="34"/>
-      <c r="S12" s="34"/>
-      <c r="T12" s="34"/>
-      <c r="U12" s="34"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="24"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="24"/>
     </row>
     <row r="13" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33"/>
-      <c r="S13" s="33"/>
-      <c r="T13" s="33"/>
-      <c r="U13" s="33"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="20"/>
     </row>
     <row r="14" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B14" s="5" t="s">
@@ -2469,28 +2472,28 @@
       <c r="J14" s="4"/>
     </row>
     <row r="15" spans="1:26" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
-      <c r="T15" s="31"/>
-      <c r="U15" s="31"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="21"/>
       <c r="V15" s="6"/>
       <c r="W15" s="6"/>
       <c r="X15" s="6"/>
@@ -2498,100 +2501,100 @@
       <c r="Z15" s="6"/>
     </row>
     <row r="16" spans="1:26" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="31"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="31"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="31"/>
-      <c r="T16" s="31"/>
-      <c r="U16" s="31"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="21"/>
     </row>
     <row r="17" spans="1:21" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
-      <c r="T17" s="33"/>
-      <c r="U17" s="33"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="20"/>
     </row>
     <row r="18" spans="1:21" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="22"/>
-      <c r="Q18" s="22"/>
-      <c r="R18" s="22"/>
-      <c r="S18" s="22"/>
-      <c r="T18" s="22"/>
-      <c r="U18" s="22"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="23"/>
+      <c r="U18" s="23"/>
     </row>
     <row r="19" spans="1:21" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="28"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="28"/>
-      <c r="U19" s="28"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="25"/>
+      <c r="P19" s="25"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="25"/>
+      <c r="U19" s="25"/>
     </row>
     <row r="21" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
@@ -2661,7 +2664,7 @@
     </row>
     <row r="29" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B29" s="14" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -2704,17 +2707,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B19:U19"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B15:U15"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="B17:U17"/>
     <mergeCell ref="B16:U16"/>
     <mergeCell ref="B18:U18"/>
     <mergeCell ref="B13:U13"/>
     <mergeCell ref="B12:U12"/>
-    <mergeCell ref="B19:U19"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B15:U15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2735,364 +2738,357 @@
       <c r="B4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35" t="s">
+      <c r="D4" s="36"/>
+      <c r="E4" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="35"/>
-      <c r="G4" s="39" t="s">
+      <c r="F4" s="36"/>
+      <c r="G4" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39" t="s">
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="39"/>
-      <c r="S4" s="39"/>
-      <c r="T4" s="39"/>
-      <c r="U4" s="39"/>
-      <c r="V4" s="39"/>
-      <c r="W4" s="39"/>
-      <c r="X4" s="39"/>
-      <c r="Y4" s="39"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="29"/>
+      <c r="Y4" s="29"/>
     </row>
     <row r="5" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11">
         <v>1</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="37" t="s">
+      <c r="D5" s="34"/>
+      <c r="E5" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="37"/>
-      <c r="G5" s="38" t="s">
+      <c r="F5" s="35"/>
+      <c r="G5" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="42" t="s">
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
-      <c r="P5" s="42"/>
-      <c r="Q5" s="42"/>
-      <c r="R5" s="42"/>
-      <c r="S5" s="42"/>
-      <c r="T5" s="42"/>
-      <c r="U5" s="42"/>
-      <c r="V5" s="42"/>
-      <c r="W5" s="42"/>
-      <c r="X5" s="42"/>
-      <c r="Y5" s="42"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
+      <c r="S5" s="30"/>
+      <c r="T5" s="30"/>
+      <c r="U5" s="30"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="30"/>
+      <c r="X5" s="30"/>
+      <c r="Y5" s="30"/>
     </row>
     <row r="6" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11">
         <v>2</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="37" t="s">
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="37"/>
-      <c r="G6" s="38" t="s">
+      <c r="F6" s="35"/>
+      <c r="G6" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="43" t="s">
-        <v>95</v>
-      </c>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="42"/>
-      <c r="U6" s="42"/>
-      <c r="V6" s="42"/>
-      <c r="W6" s="42"/>
-      <c r="X6" s="42"/>
-      <c r="Y6" s="42"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="30"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="30"/>
+      <c r="X6" s="30"/>
+      <c r="Y6" s="30"/>
     </row>
     <row r="7" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11">
         <v>3</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="37" t="s">
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="37"/>
-      <c r="G7" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="40" t="s">
+      <c r="F7" s="35"/>
+      <c r="G7" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="40"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="40"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="40"/>
-      <c r="W7" s="40"/>
-      <c r="X7" s="40"/>
-      <c r="Y7" s="40"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="28"/>
+      <c r="T7" s="28"/>
+      <c r="U7" s="28"/>
+      <c r="V7" s="28"/>
+      <c r="W7" s="28"/>
+      <c r="X7" s="28"/>
+      <c r="Y7" s="28"/>
     </row>
     <row r="8" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11">
         <v>4</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="37" t="s">
+      <c r="D8" s="34"/>
+      <c r="E8" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="37"/>
-      <c r="G8" s="38" t="s">
+      <c r="F8" s="35"/>
+      <c r="G8" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="40" t="s">
-        <v>48</v>
-      </c>
-      <c r="N8" s="40"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="40"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="40"/>
-      <c r="U8" s="40"/>
-      <c r="V8" s="40"/>
-      <c r="W8" s="40"/>
-      <c r="X8" s="40"/>
-      <c r="Y8" s="40"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="28"/>
+      <c r="S8" s="28"/>
+      <c r="T8" s="28"/>
+      <c r="U8" s="28"/>
+      <c r="V8" s="28"/>
+      <c r="W8" s="28"/>
+      <c r="X8" s="28"/>
+      <c r="Y8" s="28"/>
     </row>
     <row r="9" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11">
         <v>5</v>
       </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="37" t="s">
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="37"/>
-      <c r="G9" s="38" t="s">
+      <c r="F9" s="35"/>
+      <c r="G9" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="N9" s="40"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="40"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="40"/>
-      <c r="U9" s="40"/>
-      <c r="V9" s="40"/>
-      <c r="W9" s="40"/>
-      <c r="X9" s="40"/>
-      <c r="Y9" s="40"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="28"/>
     </row>
     <row r="10" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="11">
         <v>6</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="37" t="s">
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="37"/>
-      <c r="G10" s="38" t="s">
+      <c r="F10" s="35"/>
+      <c r="G10" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="40"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="40"/>
-      <c r="U10" s="40"/>
-      <c r="V10" s="40"/>
-      <c r="W10" s="40"/>
-      <c r="X10" s="40"/>
-      <c r="Y10" s="40"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="28"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="28"/>
+      <c r="W10" s="28"/>
+      <c r="X10" s="28"/>
+      <c r="Y10" s="28"/>
     </row>
     <row r="11" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="11">
         <v>7</v>
       </c>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="37" t="s">
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="37"/>
-      <c r="G11" s="38" t="s">
+      <c r="F11" s="35"/>
+      <c r="G11" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="40"/>
-      <c r="Q11" s="40"/>
-      <c r="R11" s="40"/>
-      <c r="S11" s="40"/>
-      <c r="T11" s="40"/>
-      <c r="U11" s="40"/>
-      <c r="V11" s="40"/>
-      <c r="W11" s="40"/>
-      <c r="X11" s="40"/>
-      <c r="Y11" s="40"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="28"/>
+      <c r="S11" s="28"/>
+      <c r="T11" s="28"/>
+      <c r="U11" s="28"/>
+      <c r="V11" s="28"/>
+      <c r="W11" s="28"/>
+      <c r="X11" s="28"/>
+      <c r="Y11" s="28"/>
     </row>
     <row r="12" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="11">
         <v>8</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="36"/>
-      <c r="E12" s="37" t="s">
+      <c r="D12" s="34"/>
+      <c r="E12" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="37"/>
-      <c r="G12" s="38" t="s">
+      <c r="F12" s="35"/>
+      <c r="G12" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="N12" s="40"/>
-      <c r="O12" s="40"/>
-      <c r="P12" s="40"/>
-      <c r="Q12" s="40"/>
-      <c r="R12" s="40"/>
-      <c r="S12" s="40"/>
-      <c r="T12" s="40"/>
-      <c r="U12" s="40"/>
-      <c r="V12" s="40"/>
-      <c r="W12" s="40"/>
-      <c r="X12" s="40"/>
-      <c r="Y12" s="40"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+      <c r="T12" s="28"/>
+      <c r="U12" s="28"/>
+      <c r="V12" s="28"/>
+      <c r="W12" s="28"/>
+      <c r="X12" s="28"/>
+      <c r="Y12" s="28"/>
     </row>
     <row r="46" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B56" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="C56" s="41"/>
-      <c r="D56" s="41"/>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="41"/>
-      <c r="H56" s="41"/>
-      <c r="I56" s="41"/>
-      <c r="J56" s="41"/>
-      <c r="K56" s="41"/>
-      <c r="L56" s="41"/>
-      <c r="M56" s="41"/>
-      <c r="N56" s="41"/>
-      <c r="O56" s="41"/>
-      <c r="P56" s="41"/>
-      <c r="Q56" s="41"/>
-      <c r="R56" s="41"/>
-      <c r="S56" s="41"/>
-      <c r="T56" s="41"/>
-      <c r="U56" s="41"/>
-      <c r="V56" s="41"/>
-      <c r="W56" s="41"/>
-      <c r="X56" s="41"/>
-      <c r="Y56" s="41"/>
+      <c r="B56" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="C56" s="33"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="33"/>
+      <c r="F56" s="33"/>
+      <c r="G56" s="33"/>
+      <c r="H56" s="33"/>
+      <c r="I56" s="33"/>
+      <c r="J56" s="33"/>
+      <c r="K56" s="33"/>
+      <c r="L56" s="33"/>
+      <c r="M56" s="33"/>
+      <c r="N56" s="33"/>
+      <c r="O56" s="33"/>
+      <c r="P56" s="33"/>
+      <c r="Q56" s="33"/>
+      <c r="R56" s="33"/>
+      <c r="S56" s="33"/>
+      <c r="T56" s="33"/>
+      <c r="U56" s="33"/>
+      <c r="V56" s="33"/>
+      <c r="W56" s="33"/>
+      <c r="X56" s="33"/>
+      <c r="Y56" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="M9:Y9"/>
-    <mergeCell ref="M4:Y4"/>
-    <mergeCell ref="M5:Y5"/>
-    <mergeCell ref="M6:Y6"/>
-    <mergeCell ref="M7:Y7"/>
-    <mergeCell ref="M8:Y8"/>
-    <mergeCell ref="M10:Y10"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="B56:Y56"/>
-    <mergeCell ref="M11:Y11"/>
-    <mergeCell ref="M12:Y12"/>
-    <mergeCell ref="G4:L4"/>
-    <mergeCell ref="G5:L5"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="G7:L7"/>
-    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
     <mergeCell ref="G9:L9"/>
     <mergeCell ref="G10:L10"/>
     <mergeCell ref="C12:D12"/>
@@ -3103,16 +3099,23 @@
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G4:L4"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="G7:L7"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="M10:Y10"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="B56:Y56"/>
+    <mergeCell ref="M11:Y11"/>
+    <mergeCell ref="M12:Y12"/>
+    <mergeCell ref="M9:Y9"/>
+    <mergeCell ref="M4:Y4"/>
+    <mergeCell ref="M5:Y5"/>
+    <mergeCell ref="M6:Y6"/>
+    <mergeCell ref="M7:Y7"/>
+    <mergeCell ref="M8:Y8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3131,24 +3134,24 @@
     </row>
     <row r="4" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="N6" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="O6" s="27"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="27"/>
-      <c r="S6" s="27"/>
-      <c r="T6" s="27"/>
-      <c r="U6" s="27"/>
-      <c r="V6" s="27"/>
-      <c r="W6" s="27"/>
-      <c r="X6" s="27"/>
-      <c r="Y6" s="27"/>
+      <c r="N6" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="O6" s="37"/>
+      <c r="P6" s="37"/>
+      <c r="Q6" s="37"/>
+      <c r="R6" s="37"/>
+      <c r="S6" s="37"/>
+      <c r="T6" s="37"/>
+      <c r="U6" s="37"/>
+      <c r="V6" s="37"/>
+      <c r="W6" s="37"/>
+      <c r="X6" s="37"/>
+      <c r="Y6" s="37"/>
     </row>
     <row r="7" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
       <c r="N7" s="7"/>
@@ -3165,25 +3168,25 @@
       <c r="Y7" s="7"/>
     </row>
     <row r="8" spans="1:30" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N8" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="O8" s="21"/>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="21"/>
-      <c r="S8" s="21"/>
-      <c r="T8" s="21"/>
-      <c r="U8" s="21"/>
-      <c r="V8" s="21"/>
-      <c r="W8" s="21"/>
-      <c r="X8" s="21"/>
-      <c r="Y8" s="21"/>
-      <c r="Z8" s="21"/>
-      <c r="AA8" s="21"/>
-      <c r="AB8" s="21"/>
-      <c r="AC8" s="21"/>
-      <c r="AD8" s="21"/>
+      <c r="N8" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="22"/>
+      <c r="V8" s="22"/>
+      <c r="W8" s="22"/>
+      <c r="X8" s="22"/>
+      <c r="Y8" s="22"/>
+      <c r="Z8" s="22"/>
+      <c r="AA8" s="22"/>
+      <c r="AB8" s="22"/>
+      <c r="AC8" s="22"/>
+      <c r="AD8" s="22"/>
     </row>
     <row r="9" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
       <c r="N9" s="7"/>
@@ -3200,67 +3203,67 @@
       <c r="Y9" s="7"/>
     </row>
     <row r="10" spans="1:30" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N10" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="22"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="22"/>
-      <c r="W10" s="22"/>
-      <c r="X10" s="22"/>
-      <c r="Y10" s="22"/>
-      <c r="Z10" s="22"/>
-      <c r="AA10" s="22"/>
-      <c r="AB10" s="22"/>
-      <c r="AC10" s="22"/>
-      <c r="AD10" s="22"/>
+      <c r="N10" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
+      <c r="S10" s="23"/>
+      <c r="T10" s="23"/>
+      <c r="U10" s="23"/>
+      <c r="V10" s="23"/>
+      <c r="W10" s="23"/>
+      <c r="X10" s="23"/>
+      <c r="Y10" s="23"/>
+      <c r="Z10" s="23"/>
+      <c r="AA10" s="23"/>
+      <c r="AB10" s="23"/>
+      <c r="AC10" s="23"/>
+      <c r="AD10" s="23"/>
     </row>
     <row r="13" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
       <c r="S13" s="12"/>
     </row>
     <row r="16" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B16" s="8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B17" s="8"/>
     </row>
     <row r="18" spans="2:33" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="24"/>
-      <c r="T18" s="24"/>
-      <c r="U18" s="24"/>
-      <c r="V18" s="24"/>
-      <c r="W18" s="24"/>
-      <c r="X18" s="24"/>
-      <c r="Y18" s="24"/>
-      <c r="Z18" s="24"/>
-      <c r="AA18" s="24"/>
-      <c r="AB18" s="24"/>
+      <c r="B18" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="42"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="42"/>
+      <c r="R18" s="42"/>
+      <c r="S18" s="42"/>
+      <c r="T18" s="42"/>
+      <c r="U18" s="42"/>
+      <c r="V18" s="42"/>
+      <c r="W18" s="42"/>
+      <c r="X18" s="42"/>
+      <c r="Y18" s="42"/>
+      <c r="Z18" s="42"/>
+      <c r="AA18" s="42"/>
+      <c r="AB18" s="42"/>
     </row>
     <row r="19" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="15"/>
@@ -3295,41 +3298,41 @@
       <c r="C21" s="10"/>
     </row>
     <row r="23" spans="2:33" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="T23" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="U23" s="23"/>
-      <c r="V23" s="23"/>
-      <c r="W23" s="23"/>
-      <c r="X23" s="23"/>
-      <c r="Y23" s="23"/>
-      <c r="Z23" s="23"/>
-      <c r="AA23" s="23"/>
-      <c r="AB23" s="23"/>
-      <c r="AC23" s="23"/>
-      <c r="AD23" s="23"/>
-      <c r="AE23" s="23"/>
-      <c r="AF23" s="23"/>
+      <c r="T23" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="U23" s="38"/>
+      <c r="V23" s="38"/>
+      <c r="W23" s="38"/>
+      <c r="X23" s="38"/>
+      <c r="Y23" s="38"/>
+      <c r="Z23" s="38"/>
+      <c r="AA23" s="38"/>
+      <c r="AB23" s="38"/>
+      <c r="AC23" s="38"/>
+      <c r="AD23" s="38"/>
+      <c r="AE23" s="38"/>
+      <c r="AF23" s="38"/>
     </row>
     <row r="24" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T24" s="12"/>
     </row>
     <row r="25" spans="2:33" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T25" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="U25" s="19"/>
-      <c r="V25" s="19"/>
-      <c r="W25" s="19"/>
-      <c r="X25" s="19"/>
-      <c r="Y25" s="19"/>
-      <c r="Z25" s="19"/>
-      <c r="AA25" s="19"/>
-      <c r="AB25" s="19"/>
-      <c r="AC25" s="19"/>
-      <c r="AD25" s="19"/>
-      <c r="AE25" s="19"/>
-      <c r="AF25" s="19"/>
+      <c r="T25" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="U25" s="39"/>
+      <c r="V25" s="39"/>
+      <c r="W25" s="39"/>
+      <c r="X25" s="39"/>
+      <c r="Y25" s="39"/>
+      <c r="Z25" s="39"/>
+      <c r="AA25" s="39"/>
+      <c r="AB25" s="39"/>
+      <c r="AC25" s="39"/>
+      <c r="AD25" s="39"/>
+      <c r="AE25" s="39"/>
+      <c r="AF25" s="39"/>
       <c r="AG25" s="17"/>
     </row>
     <row r="26" spans="2:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3349,33 +3352,33 @@
       <c r="AG26" s="17"/>
     </row>
     <row r="27" spans="2:33" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="T27" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="U27" s="23"/>
-      <c r="V27" s="23"/>
-      <c r="W27" s="23"/>
-      <c r="X27" s="23"/>
-      <c r="Y27" s="23"/>
-      <c r="Z27" s="23"/>
-      <c r="AA27" s="23"/>
-      <c r="AB27" s="23"/>
-      <c r="AC27" s="23"/>
-      <c r="AD27" s="23"/>
-      <c r="AE27" s="23"/>
-      <c r="AF27" s="23"/>
+      <c r="T27" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="U27" s="38"/>
+      <c r="V27" s="38"/>
+      <c r="W27" s="38"/>
+      <c r="X27" s="38"/>
+      <c r="Y27" s="38"/>
+      <c r="Z27" s="38"/>
+      <c r="AA27" s="38"/>
+      <c r="AB27" s="38"/>
+      <c r="AC27" s="38"/>
+      <c r="AD27" s="38"/>
+      <c r="AE27" s="38"/>
+      <c r="AF27" s="38"/>
     </row>
     <row r="28" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T28" s="12"/>
     </row>
     <row r="29" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T29" s="12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T30" s="12" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
@@ -3383,7 +3386,7 @@
     </row>
     <row r="32" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T32" s="8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
@@ -3393,7 +3396,7 @@
     </row>
     <row r="34" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T34" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="U34" s="12"/>
       <c r="V34" s="12"/>
@@ -3409,25 +3412,25 @@
       <c r="AF34" s="12"/>
     </row>
     <row r="35" spans="2:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T35" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="U35" s="21"/>
-      <c r="V35" s="21"/>
-      <c r="W35" s="21"/>
-      <c r="X35" s="21"/>
-      <c r="Y35" s="21"/>
-      <c r="Z35" s="21"/>
-      <c r="AA35" s="21"/>
-      <c r="AB35" s="21"/>
-      <c r="AC35" s="21"/>
-      <c r="AD35" s="21"/>
-      <c r="AE35" s="21"/>
-      <c r="AF35" s="21"/>
+      <c r="T35" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="U35" s="22"/>
+      <c r="V35" s="22"/>
+      <c r="W35" s="22"/>
+      <c r="X35" s="22"/>
+      <c r="Y35" s="22"/>
+      <c r="Z35" s="22"/>
+      <c r="AA35" s="22"/>
+      <c r="AB35" s="22"/>
+      <c r="AC35" s="22"/>
+      <c r="AD35" s="22"/>
+      <c r="AE35" s="22"/>
+      <c r="AF35" s="22"/>
     </row>
     <row r="37" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T37" s="8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="U37" s="12"/>
       <c r="V37" s="12"/>
@@ -3443,315 +3446,320 @@
       <c r="AF37" s="12"/>
     </row>
     <row r="38" spans="2:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T38" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="U38" s="21"/>
-      <c r="V38" s="21"/>
-      <c r="W38" s="21"/>
-      <c r="X38" s="21"/>
-      <c r="Y38" s="21"/>
-      <c r="Z38" s="21"/>
-      <c r="AA38" s="21"/>
-      <c r="AB38" s="21"/>
-      <c r="AC38" s="21"/>
-      <c r="AD38" s="21"/>
-      <c r="AE38" s="21"/>
-      <c r="AF38" s="21"/>
-      <c r="AG38" s="21"/>
-      <c r="AH38" s="21"/>
-      <c r="AI38" s="21"/>
-      <c r="AJ38" s="21"/>
-      <c r="AK38" s="21"/>
+      <c r="T38" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="U38" s="22"/>
+      <c r="V38" s="22"/>
+      <c r="W38" s="22"/>
+      <c r="X38" s="22"/>
+      <c r="Y38" s="22"/>
+      <c r="Z38" s="22"/>
+      <c r="AA38" s="22"/>
+      <c r="AB38" s="22"/>
+      <c r="AC38" s="22"/>
+      <c r="AD38" s="22"/>
+      <c r="AE38" s="22"/>
+      <c r="AF38" s="22"/>
+      <c r="AG38" s="22"/>
+      <c r="AH38" s="22"/>
+      <c r="AI38" s="22"/>
+      <c r="AJ38" s="22"/>
+      <c r="AK38" s="22"/>
     </row>
     <row r="39" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T39" s="12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T40" s="8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="2:37" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="T41" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="U41" s="23"/>
-      <c r="V41" s="23"/>
-      <c r="W41" s="23"/>
-      <c r="X41" s="23"/>
-      <c r="Y41" s="23"/>
-      <c r="Z41" s="23"/>
-      <c r="AA41" s="23"/>
-      <c r="AB41" s="23"/>
-      <c r="AC41" s="23"/>
-      <c r="AD41" s="23"/>
-      <c r="AE41" s="23"/>
-      <c r="AF41" s="23"/>
-      <c r="AG41" s="23"/>
+      <c r="T41" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="U41" s="38"/>
+      <c r="V41" s="38"/>
+      <c r="W41" s="38"/>
+      <c r="X41" s="38"/>
+      <c r="Y41" s="38"/>
+      <c r="Z41" s="38"/>
+      <c r="AA41" s="38"/>
+      <c r="AB41" s="38"/>
+      <c r="AC41" s="38"/>
+      <c r="AD41" s="38"/>
+      <c r="AE41" s="38"/>
+      <c r="AF41" s="38"/>
+      <c r="AG41" s="38"/>
     </row>
     <row r="42" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T42" s="12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T43" s="8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B44" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="C44" s="26"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="26"/>
-      <c r="G44" s="26"/>
-      <c r="H44" s="26"/>
-      <c r="I44" s="26"/>
-      <c r="J44" s="26"/>
-      <c r="K44" s="26"/>
-      <c r="L44" s="26"/>
-      <c r="M44" s="26"/>
-      <c r="N44" s="26"/>
-      <c r="O44" s="26"/>
-      <c r="P44" s="26"/>
-      <c r="Q44" s="26"/>
-      <c r="R44" s="26"/>
-      <c r="T44" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="U44" s="23"/>
-      <c r="V44" s="23"/>
-      <c r="W44" s="23"/>
-      <c r="X44" s="23"/>
-      <c r="Y44" s="23"/>
-      <c r="Z44" s="23"/>
-      <c r="AA44" s="23"/>
-      <c r="AB44" s="23"/>
-      <c r="AC44" s="23"/>
-      <c r="AD44" s="23"/>
-      <c r="AE44" s="23"/>
-      <c r="AF44" s="23"/>
-      <c r="AG44" s="23"/>
-      <c r="AH44" s="23"/>
-      <c r="AI44" s="23"/>
+      <c r="B44" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="41"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="41"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="41"/>
+      <c r="J44" s="41"/>
+      <c r="K44" s="41"/>
+      <c r="L44" s="41"/>
+      <c r="M44" s="41"/>
+      <c r="N44" s="41"/>
+      <c r="O44" s="41"/>
+      <c r="P44" s="41"/>
+      <c r="Q44" s="41"/>
+      <c r="R44" s="41"/>
+      <c r="T44" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="U44" s="38"/>
+      <c r="V44" s="38"/>
+      <c r="W44" s="38"/>
+      <c r="X44" s="38"/>
+      <c r="Y44" s="38"/>
+      <c r="Z44" s="38"/>
+      <c r="AA44" s="38"/>
+      <c r="AB44" s="38"/>
+      <c r="AC44" s="38"/>
+      <c r="AD44" s="38"/>
+      <c r="AE44" s="38"/>
+      <c r="AF44" s="38"/>
+      <c r="AG44" s="38"/>
+      <c r="AH44" s="38"/>
+      <c r="AI44" s="38"/>
     </row>
     <row r="45" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T45" s="12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T46" s="8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T47" s="12" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T48" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T49" s="8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T50" s="12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T51" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B54" s="8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="2:37" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T56" s="19" t="s">
+      <c r="T56" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="U56" s="39"/>
+      <c r="V56" s="39"/>
+      <c r="W56" s="39"/>
+      <c r="X56" s="39"/>
+      <c r="Y56" s="39"/>
+      <c r="Z56" s="39"/>
+      <c r="AA56" s="39"/>
+      <c r="AB56" s="39"/>
+      <c r="AC56" s="39"/>
+      <c r="AD56" s="39"/>
+      <c r="AE56" s="39"/>
+      <c r="AF56" s="39"/>
+      <c r="AG56" s="39"/>
+      <c r="AH56" s="39"/>
+      <c r="AI56" s="39"/>
+      <c r="AJ56" s="39"/>
+      <c r="AK56" s="39"/>
+    </row>
+    <row r="58" spans="2:37" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T58" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="U58" s="39"/>
+      <c r="V58" s="39"/>
+      <c r="W58" s="39"/>
+      <c r="X58" s="39"/>
+      <c r="Y58" s="39"/>
+      <c r="Z58" s="39"/>
+      <c r="AA58" s="39"/>
+      <c r="AB58" s="39"/>
+      <c r="AC58" s="39"/>
+      <c r="AD58" s="39"/>
+      <c r="AE58" s="39"/>
+      <c r="AF58" s="39"/>
+      <c r="AG58" s="39"/>
+      <c r="AH58" s="39"/>
+      <c r="AI58" s="39"/>
+      <c r="AJ58" s="39"/>
+      <c r="AK58" s="39"/>
+    </row>
+    <row r="59" spans="2:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T59" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="U56" s="19"/>
-      <c r="V56" s="19"/>
-      <c r="W56" s="19"/>
-      <c r="X56" s="19"/>
-      <c r="Y56" s="19"/>
-      <c r="Z56" s="19"/>
-      <c r="AA56" s="19"/>
-      <c r="AB56" s="19"/>
-      <c r="AC56" s="19"/>
-      <c r="AD56" s="19"/>
-      <c r="AE56" s="19"/>
-      <c r="AF56" s="19"/>
-      <c r="AG56" s="19"/>
-      <c r="AH56" s="19"/>
-      <c r="AI56" s="19"/>
-      <c r="AJ56" s="19"/>
-      <c r="AK56" s="19"/>
-    </row>
-    <row r="58" spans="2:37" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T58" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="U58" s="19"/>
-      <c r="V58" s="19"/>
-      <c r="W58" s="19"/>
-      <c r="X58" s="19"/>
-      <c r="Y58" s="19"/>
-      <c r="Z58" s="19"/>
-      <c r="AA58" s="19"/>
-      <c r="AB58" s="19"/>
-      <c r="AC58" s="19"/>
-      <c r="AD58" s="19"/>
-      <c r="AE58" s="19"/>
-      <c r="AF58" s="19"/>
-      <c r="AG58" s="19"/>
-      <c r="AH58" s="19"/>
-      <c r="AI58" s="19"/>
-      <c r="AJ58" s="19"/>
-      <c r="AK58" s="19"/>
-    </row>
-    <row r="59" spans="2:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T59" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="U59" s="19"/>
-      <c r="V59" s="19"/>
-      <c r="W59" s="19"/>
-      <c r="X59" s="19"/>
-      <c r="Y59" s="19"/>
-      <c r="Z59" s="19"/>
-      <c r="AA59" s="19"/>
-      <c r="AB59" s="19"/>
-      <c r="AC59" s="19"/>
-      <c r="AD59" s="19"/>
-      <c r="AE59" s="19"/>
-      <c r="AF59" s="19"/>
-      <c r="AG59" s="19"/>
-      <c r="AH59" s="19"/>
-      <c r="AI59" s="19"/>
-      <c r="AJ59" s="19"/>
-      <c r="AK59" s="19"/>
+      <c r="U59" s="39"/>
+      <c r="V59" s="39"/>
+      <c r="W59" s="39"/>
+      <c r="X59" s="39"/>
+      <c r="Y59" s="39"/>
+      <c r="Z59" s="39"/>
+      <c r="AA59" s="39"/>
+      <c r="AB59" s="39"/>
+      <c r="AC59" s="39"/>
+      <c r="AD59" s="39"/>
+      <c r="AE59" s="39"/>
+      <c r="AF59" s="39"/>
+      <c r="AG59" s="39"/>
+      <c r="AH59" s="39"/>
+      <c r="AI59" s="39"/>
+      <c r="AJ59" s="39"/>
+      <c r="AK59" s="39"/>
     </row>
     <row r="61" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T61" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="63" spans="2:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T63" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="U63" s="43"/>
+      <c r="V63" s="43"/>
+      <c r="W63" s="43"/>
+      <c r="X63" s="43"/>
+      <c r="Y63" s="43"/>
+      <c r="Z63" s="43"/>
+      <c r="AA63" s="43"/>
+      <c r="AB63" s="43"/>
+      <c r="AC63" s="43"/>
+      <c r="AD63" s="43"/>
+      <c r="AE63" s="43"/>
+      <c r="AF63" s="43"/>
+      <c r="AG63" s="43"/>
+      <c r="AH63" s="43"/>
+      <c r="AI63" s="43"/>
+      <c r="AJ63" s="43"/>
+      <c r="AK63" s="43"/>
+    </row>
+    <row r="64" spans="2:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T64" s="39" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="63" spans="2:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T63" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="U63" s="20"/>
-      <c r="V63" s="20"/>
-      <c r="W63" s="20"/>
-      <c r="X63" s="20"/>
-      <c r="Y63" s="20"/>
-      <c r="Z63" s="20"/>
-      <c r="AA63" s="20"/>
-      <c r="AB63" s="20"/>
-      <c r="AC63" s="20"/>
-      <c r="AD63" s="20"/>
-      <c r="AE63" s="20"/>
-      <c r="AF63" s="20"/>
-      <c r="AG63" s="20"/>
-      <c r="AH63" s="20"/>
-      <c r="AI63" s="20"/>
-      <c r="AJ63" s="20"/>
-      <c r="AK63" s="20"/>
-    </row>
-    <row r="64" spans="2:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T64" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="U64" s="19"/>
-      <c r="V64" s="19"/>
-      <c r="W64" s="19"/>
-      <c r="X64" s="19"/>
-      <c r="Y64" s="19"/>
-      <c r="Z64" s="19"/>
-      <c r="AA64" s="19"/>
-      <c r="AB64" s="19"/>
-      <c r="AC64" s="19"/>
-      <c r="AD64" s="19"/>
-      <c r="AE64" s="19"/>
-      <c r="AF64" s="19"/>
-      <c r="AG64" s="19"/>
-      <c r="AH64" s="19"/>
-      <c r="AI64" s="19"/>
-      <c r="AJ64" s="19"/>
-      <c r="AK64" s="19"/>
+      <c r="U64" s="39"/>
+      <c r="V64" s="39"/>
+      <c r="W64" s="39"/>
+      <c r="X64" s="39"/>
+      <c r="Y64" s="39"/>
+      <c r="Z64" s="39"/>
+      <c r="AA64" s="39"/>
+      <c r="AB64" s="39"/>
+      <c r="AC64" s="39"/>
+      <c r="AD64" s="39"/>
+      <c r="AE64" s="39"/>
+      <c r="AF64" s="39"/>
+      <c r="AG64" s="39"/>
+      <c r="AH64" s="39"/>
+      <c r="AI64" s="39"/>
+      <c r="AJ64" s="39"/>
+      <c r="AK64" s="39"/>
     </row>
     <row r="65" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T65" s="12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="66" spans="20:37" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="T66" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="U66" s="20"/>
-      <c r="V66" s="20"/>
-      <c r="W66" s="20"/>
-      <c r="X66" s="20"/>
-      <c r="Y66" s="20"/>
-      <c r="Z66" s="20"/>
-      <c r="AA66" s="20"/>
-      <c r="AB66" s="20"/>
-      <c r="AC66" s="20"/>
-      <c r="AD66" s="20"/>
-      <c r="AE66" s="20"/>
-      <c r="AF66" s="20"/>
-      <c r="AG66" s="20"/>
-      <c r="AH66" s="20"/>
-      <c r="AI66" s="20"/>
-      <c r="AJ66" s="20"/>
-      <c r="AK66" s="20"/>
+      <c r="T66" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="U66" s="43"/>
+      <c r="V66" s="43"/>
+      <c r="W66" s="43"/>
+      <c r="X66" s="43"/>
+      <c r="Y66" s="43"/>
+      <c r="Z66" s="43"/>
+      <c r="AA66" s="43"/>
+      <c r="AB66" s="43"/>
+      <c r="AC66" s="43"/>
+      <c r="AD66" s="43"/>
+      <c r="AE66" s="43"/>
+      <c r="AF66" s="43"/>
+      <c r="AG66" s="43"/>
+      <c r="AH66" s="43"/>
+      <c r="AI66" s="43"/>
+      <c r="AJ66" s="43"/>
+      <c r="AK66" s="43"/>
     </row>
     <row r="67" spans="20:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T67" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="U67" s="19"/>
-      <c r="V67" s="19"/>
-      <c r="W67" s="19"/>
-      <c r="X67" s="19"/>
-      <c r="Y67" s="19"/>
-      <c r="Z67" s="19"/>
-      <c r="AA67" s="19"/>
-      <c r="AB67" s="19"/>
-      <c r="AC67" s="19"/>
-      <c r="AD67" s="19"/>
-      <c r="AE67" s="19"/>
-      <c r="AF67" s="19"/>
-      <c r="AG67" s="19"/>
-      <c r="AH67" s="19"/>
-      <c r="AI67" s="19"/>
-      <c r="AJ67" s="19"/>
-      <c r="AK67" s="19"/>
+      <c r="T67" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="U67" s="39"/>
+      <c r="V67" s="39"/>
+      <c r="W67" s="39"/>
+      <c r="X67" s="39"/>
+      <c r="Y67" s="39"/>
+      <c r="Z67" s="39"/>
+      <c r="AA67" s="39"/>
+      <c r="AB67" s="39"/>
+      <c r="AC67" s="39"/>
+      <c r="AD67" s="39"/>
+      <c r="AE67" s="39"/>
+      <c r="AF67" s="39"/>
+      <c r="AG67" s="39"/>
+      <c r="AH67" s="39"/>
+      <c r="AI67" s="39"/>
+      <c r="AJ67" s="39"/>
+      <c r="AK67" s="39"/>
     </row>
     <row r="68" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T68" s="12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="T59:AK59"/>
+    <mergeCell ref="T63:AK63"/>
+    <mergeCell ref="T64:AK64"/>
+    <mergeCell ref="T66:AK66"/>
+    <mergeCell ref="T67:AK67"/>
     <mergeCell ref="N6:Y6"/>
     <mergeCell ref="T44:AI44"/>
     <mergeCell ref="T41:AG41"/>
@@ -3766,11 +3774,6 @@
     <mergeCell ref="T27:AF27"/>
     <mergeCell ref="B18:AB18"/>
     <mergeCell ref="T56:AK56"/>
-    <mergeCell ref="T59:AK59"/>
-    <mergeCell ref="T63:AK63"/>
-    <mergeCell ref="T64:AK64"/>
-    <mergeCell ref="T66:AK66"/>
-    <mergeCell ref="T67:AK67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55D19DD-6D68-4182-A566-FD500A546B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABF0D35-C151-4179-A07E-1CB3466B5639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
@@ -2322,6 +2322,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE8EA2C6-5D4C-4F72-BB1A-C66BB7164130}">
+  <sheetPr>
+    <tabColor rgb="FF0070C0"/>
+  </sheetPr>
   <dimension ref="A1:Z31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2725,6 +2728,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C18D58DC-C607-4C25-B716-A2FA80FEE53A}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
   <dimension ref="A2:Y56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3124,6 +3130,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65104074-029C-40D9-BBD1-23C9BE62AD60}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
   <dimension ref="A2:AK68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3782,6 +3791,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{987C42C5-2E1D-46D4-9447-A97F0394BB01}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -3791,6 +3803,9 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3239B50-CC89-47B5-B82D-EDCC53E377B4}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -3800,6 +3815,9 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9F41932-50C2-459B-97AA-8755C7255BDB}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABF0D35-C151-4179-A07E-1CB3466B5639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E25EE7-5C54-4AC6-9E28-FF8AA11E9B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -927,6 +927,175 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trong căn phòng to bao gồm:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
++ Các Object X: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>phục vụ cho nhu cầu trang trí, tăng tính thẩm mỹ.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
++ Các Object Y: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>phục vụ cho việc hoàn thành điều kiện của Puzzle.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
++ Puzzle: Với giao diện tương tự như các Object nhưng người chơi cần chú ý quan sát để tìm được nó và </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>hoàn thành yêu cầu điều kiện tổng (hoàn thành 2 loại puzzle)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Khi puzzle được kích hoạt, timelapse nhỏ sẽ xuất hiện trên đầu.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Timelapse nhỏ chỉ hiển thị khi người chơi tiếp xúc đúng puzzle có chứa sự biến đổi trong khoảng thời gian 2.5 giây</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Khi timelapse nhỏ về 0, người chơi vẫn tính là thua. Mỗi puzzle sẽ có số thời gian timelapse khác nhau tuỳ vào độ khó.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Người chơi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>cần tìm ra các đồ vật phù hợp với gợi ý được đưa ra bởi chính puzzle (số lượng là 2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Sau khi thoả sẽ hoàn thành điều kiện.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nội dung giải đố gồm: Người chơi cần </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>tìm các mảnh giấy có chứa câu đố (số lượng là 5)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, sau khi giải xong sẽ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>nhận được một dãy số dùng để nhập vào máy chủ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Khi thoả sẽ hoàn thành điều kiện.</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">- </t>
     </r>
     <r>
@@ -985,6 +1154,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> "Điều kiện tổng".
+- Cả 2 loại puzzle đều sẽ có sự biến đổi cứ khoảng 15-20 giây và chúng sẽ không xảy ra đồng thời với nhau. Ngoài ra sau khi biến đổi nó sẽ giữ nguyên trạng thái trong khoảng 7 giây rồi quay về trạng thái cũ.
 - </t>
     </r>
     <r>
@@ -1073,45 +1243,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">Timelapse nhỏ sẽ xuất hiện và bắt đầu tính thời gian.
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Cả 2 loại puzzle đều sẽ có sự biến đổi cứ khoảng </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>15-20 giây</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> và chúng sẽ không xảy ra đồng thời với nhau. Ngoài ra sau khi biến đổi nó sẽ giữ nguyên trạng thái trong khoảng 7 giây rồi quay về trạng thái cũ.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
 - Chỉ được kích hoạt 1 puzzle 1 lần. Khi puzzle đầu tiên hoàn thành thì có thể thực hiện puzzle thứ 2.
 ***Lưu ý: </t>
     </r>
@@ -1161,175 +1292,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> ngay lập tức.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trong căn phòng to bao gồm:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-+ Các Object X: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>phục vụ cho nhu cầu trang trí, tăng tính thẩm mỹ.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-+ Các Object Y: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>phục vụ cho việc hoàn thành điều kiện của Puzzle.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-+ Puzzle: Với giao diện tương tự như các Object nhưng người chơi cần chú ý quan sát để tìm được nó và </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>hoàn thành yêu cầu điều kiện tổng (hoàn thành 2 loại puzzle)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Khi puzzle được kích hoạt, timelapse nhỏ sẽ xuất hiện trên đầu.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Timelapse nhỏ chỉ hiển thị khi người chơi tiếp xúc đúng puzzle có chứa sự biến đổi trong khoảng thời gian 2.5 giây</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Khi timelapse nhỏ về 0, người chơi vẫn tính là thua. Mỗi puzzle sẽ có số thời gian timelapse khác nhau tuỳ vào độ khó.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Người chơi </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>cần tìm ra các đồ vật phù hợp với gợi ý được đưa ra bởi chính puzzle (số lượng là 2)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Sau khi thoả sẽ hoàn thành điều kiện.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Nội dung giải đố gồm: Người chơi cần </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>tìm các mảnh giấy có chứa câu đố (số lượng là 5)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, sau khi giải xong sẽ </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>nhận được một dãy số dùng để nhập vào máy chủ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Khi thoả sẽ hoàn thành điều kiện.</t>
     </r>
   </si>
 </sst>
@@ -1455,7 +1417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1572,6 +1534,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2901,7 +2866,7 @@
       <c r="K8" s="32"/>
       <c r="L8" s="32"/>
       <c r="M8" s="44" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N8" s="28"/>
       <c r="O8" s="28"/>
@@ -2935,7 +2900,7 @@
       <c r="K9" s="32"/>
       <c r="L9" s="32"/>
       <c r="M9" s="44" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N9" s="28"/>
       <c r="O9" s="28"/>
@@ -2969,7 +2934,7 @@
       <c r="K10" s="32"/>
       <c r="L10" s="32"/>
       <c r="M10" s="44" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N10" s="28"/>
       <c r="O10" s="28"/>
@@ -3213,7 +3178,7 @@
     </row>
     <row r="10" spans="1:30" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N10" s="22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O10" s="23"/>
       <c r="P10" s="23"/>
@@ -3244,8 +3209,8 @@
       <c r="B17" s="8"/>
     </row>
     <row r="18" spans="2:33" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="42" t="s">
-        <v>93</v>
+      <c r="B18" s="45" t="s">
+        <v>97</v>
       </c>
       <c r="C18" s="42"/>
       <c r="D18" s="42"/>

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E25EE7-5C54-4AC6-9E28-FF8AA11E9B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3596250-9C6E-4622-A625-3F7DFE9E697F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -1559,23 +1559,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>13607</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>53</xdr:row>
-      <xdr:rowOff>124891</xdr:rowOff>
+      <xdr:rowOff>180947</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9">
+        <xdr:cNvPr id="5" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BA5C7DC-54F9-54CC-98A7-C079AE6A70B9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB773E94-1695-0955-2238-B5E696F1EBE1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1597,8 +1597,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="590550" y="10239375"/>
-          <a:ext cx="14697075" cy="7754416"/>
+          <a:off x="625928" y="7633607"/>
+          <a:ext cx="14682108" cy="7746519"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3596250-9C6E-4622-A625-3F7DFE9E697F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA76C8D-09D3-455D-99F8-AD0954285B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -837,54 +837,7 @@
     </r>
   </si>
   <si>
-    <t>Puzzle tìm đồ vật cũng sẽ dựa vào câu đố nhưng lần này câu đố sẽ được cấp trực tiếp tại bức tranh, không phải đi tìm như giải đố. Bức tranh có thể giống theo mẫu bên trái.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Khi puzzle giải đố được kích hoạt: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Người chơi cần </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>tìm ra 2 đồ vật phù hợp nhất với câu đố.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Cầm trên tay mang lại bức tranh thì sẽ hoàn thành. </t>
-    </r>
-  </si>
-  <si>
     <t>CÂU ĐỐ ĐỂ TÌM ĐỒ VẬT PHÙ HỢP:</t>
-  </si>
-  <si>
-    <t>#Hướng dẫn: "This room once belonged to someone. They have departed but they did not take everything with them. They left behind two objects. Each one is hidden behind a message.
-Find the right one, and only then will you understand who they truly were."</t>
   </si>
   <si>
     <t>#1: "The One Who Never Strays"</t>
@@ -1292,6 +1245,64 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> ngay lập tức.</t>
+    </r>
+  </si>
+  <si>
+    <t>#Hướng dẫn: "This room once belonged to someone. They have departed but they did not take everything with them. They left behind two objects. Each one is hidden behind a message. Find the right one, and only then will you understand who they truly were."</t>
+  </si>
+  <si>
+    <r>
+      <t>Puzzle tìm đồ vật cũng sẽ dựa vào câu đố nhưng lần này câu đố sẽ được cấp trực tiếp tại bức tranh, không phải đi tìm như giải đố. Bức tranh có thể giống theo mẫu bên trái.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Có tổng cộng là 2 bức tranh.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Khi puzzle giải đố được kích hoạt: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Người chơi cần </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>tìm ra 2 đồ vật phù hợp nhất với câu đố. Mỗi lượt sẽ là câu đố cho 1 món đồ vật.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Cầm đồ vật chứa câu đố đầu tiên trên tay mang lại bức tranh thứ nhất thì câu đố thứ 2 sẽ mở ra ở bức tranh thứ 2. </t>
     </r>
   </si>
 </sst>
@@ -1417,7 +1428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1537,6 +1548,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1916,8 +1930,8 @@
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>47626</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2796,7 +2810,7 @@
       <c r="K6" s="32"/>
       <c r="L6" s="32"/>
       <c r="M6" s="31" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="N6" s="30"/>
       <c r="O6" s="30"/>
@@ -2866,7 +2880,7 @@
       <c r="K8" s="32"/>
       <c r="L8" s="32"/>
       <c r="M8" s="44" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="N8" s="28"/>
       <c r="O8" s="28"/>
@@ -2900,7 +2914,7 @@
       <c r="K9" s="32"/>
       <c r="L9" s="32"/>
       <c r="M9" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="N9" s="28"/>
       <c r="O9" s="28"/>
@@ -2934,7 +2948,7 @@
       <c r="K10" s="32"/>
       <c r="L10" s="32"/>
       <c r="M10" s="44" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="N10" s="28"/>
       <c r="O10" s="28"/>
@@ -3178,7 +3192,7 @@
     </row>
     <row r="10" spans="1:30" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N10" s="22" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O10" s="23"/>
       <c r="P10" s="23"/>
@@ -3210,7 +3224,7 @@
     </row>
     <row r="18" spans="2:33" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="45" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C18" s="42"/>
       <c r="D18" s="42"/>
@@ -3292,7 +3306,7 @@
       <c r="T24" s="12"/>
     </row>
     <row r="25" spans="2:33" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T25" s="39" t="s">
+      <c r="T25" s="46" t="s">
         <v>55</v>
       </c>
       <c r="U25" s="39"/>
@@ -3559,8 +3573,8 @@
       </c>
     </row>
     <row r="56" spans="2:37" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T56" s="39" t="s">
-        <v>82</v>
+      <c r="T56" s="46" t="s">
+        <v>96</v>
       </c>
       <c r="U56" s="39"/>
       <c r="V56" s="39"/>
@@ -3581,8 +3595,8 @@
       <c r="AK56" s="39"/>
     </row>
     <row r="58" spans="2:37" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T58" s="39" t="s">
-        <v>83</v>
+      <c r="T58" s="46" t="s">
+        <v>97</v>
       </c>
       <c r="U58" s="39"/>
       <c r="V58" s="39"/>
@@ -3602,9 +3616,9 @@
       <c r="AJ58" s="39"/>
       <c r="AK58" s="39"/>
     </row>
-    <row r="59" spans="2:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T59" s="39" t="s">
-        <v>85</v>
+    <row r="59" spans="2:37" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T59" s="46" t="s">
+        <v>95</v>
       </c>
       <c r="U59" s="39"/>
       <c r="V59" s="39"/>
@@ -3626,12 +3640,12 @@
     </row>
     <row r="61" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T61" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="63" spans="2:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T63" s="43" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="U63" s="43"/>
       <c r="V63" s="43"/>
@@ -3653,7 +3667,7 @@
     </row>
     <row r="64" spans="2:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T64" s="39" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="U64" s="39"/>
       <c r="V64" s="39"/>
@@ -3675,12 +3689,12 @@
     </row>
     <row r="65" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T65" s="12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="20:37" ht="19.5" x14ac:dyDescent="0.25">
       <c r="T66" s="43" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="U66" s="43"/>
       <c r="V66" s="43"/>
@@ -3702,7 +3716,7 @@
     </row>
     <row r="67" spans="20:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T67" s="39" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U67" s="39"/>
       <c r="V67" s="39"/>
@@ -3724,7 +3738,7 @@
     </row>
     <row r="68" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T68" s="12" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -3750,7 +3764,8 @@
     <mergeCell ref="T56:AK56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA76C8D-09D3-455D-99F8-AD0954285B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91DD172-953D-452E-A114-6CBB99C62268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="136">
   <si>
     <t>SIGNOMALY</t>
   </si>
@@ -131,25 +131,6 @@
         <family val="2"/>
       </rPr>
       <t>PC</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Gameplay:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Người chơi sẽ là người tham gia vào một trò chơi sinh tồn chết chóc. Người chơi sẽ bị nhốt trong một căn phòng tưởng chừng như bình thường, nhưng theo thời gian, căn phòng bắt đầu xuất hiện những "Tín hiệu (Signal)" bất thường (đồ vật biến đổi, âm thanh lạ, môi trường biến dạng). Nhiệm vụ người chơi là liên tục quan sát, thiết lập mức độ ưu tiên và phát hiện ra những tín hiệu trước khi chúng vào trạng thái báo động. Trò chơi yêu cầu cao về suy luận logic, tìm kiếm vật phẩm tương tác để khắc phục và đưa trạng thái của chúng về mức bình thường.</t>
     </r>
   </si>
   <si>
@@ -1248,9 +1229,6 @@
     </r>
   </si>
   <si>
-    <t>#Hướng dẫn: "This room once belonged to someone. They have departed but they did not take everything with them. They left behind two objects. Each one is hidden behind a message. Find the right one, and only then will you understand who they truly were."</t>
-  </si>
-  <si>
     <r>
       <t>Puzzle tìm đồ vật cũng sẽ dựa vào câu đố nhưng lần này câu đố sẽ được cấp trực tiếp tại bức tranh, không phải đi tìm như giải đố. Bức tranh có thể giống theo mẫu bên trái.</t>
     </r>
@@ -1304,15 +1282,175 @@
       </rPr>
       <t xml:space="preserve"> Cầm đồ vật chứa câu đố đầu tiên trên tay mang lại bức tranh thứ nhất thì câu đố thứ 2 sẽ mở ra ở bức tranh thứ 2. </t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#Tờ hướng dẫn:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> "This room once belonged to someone. They have departed but they did not take everything with them. They left behind two objects. Each one is hidden behind a message. Find the right one, and only then will you understand who they truly were."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Gameplay:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Người chơi sẽ là người tham gia vào một trò chơi sinh tồn giải đố. Người chơi sẽ bị nhốt trong một căn phòng tưởng chừng như bình thường, nhưng theo thời gian, căn phòng bắt đầu xuất hiện những "Tín hiệu (Signal)" bất thường (đồ vật biến đổi, âm thanh lạ, môi trường biến dạng). Nhiệm vụ người chơi là liên tục quan sát, thiết lập mức độ ưu tiên và phát hiện ra những tín hiệu trước khi chúng vào trạng thái báo động. Trò chơi yêu cầu cao về suy luận logic, tìm kiếm vật phẩm tương tác để khắc phục và đưa trạng thái của chúng về mức bình thường và hoàn thành trò chơi.</t>
+    </r>
+  </si>
+  <si>
+    <t>(Reference cơ chế đọc thư. Chỉ cần hiện nền đen và chữ. Có nút tắt)</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Tờ hướng dẫn</t>
+  </si>
+  <si>
+    <t>Dùng để hướng dẫn phương pháp giải đố, cách giải đố.</t>
+  </si>
+  <si>
+    <t>Loại</t>
+  </si>
+  <si>
+    <t>Tên Item</t>
+  </si>
+  <si>
+    <t>Compass</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Coins</t>
+  </si>
+  <si>
+    <t>Flower</t>
+  </si>
+  <si>
+    <t>Ball</t>
+  </si>
+  <si>
+    <t>Statue</t>
+  </si>
+  <si>
+    <t>Mirror</t>
+  </si>
+  <si>
+    <t>Lamp</t>
+  </si>
+  <si>
+    <t>Cup Champion</t>
+  </si>
+  <si>
+    <t>Cup of coffee</t>
+  </si>
+  <si>
+    <t>Table</t>
+  </si>
+  <si>
+    <t>Chair</t>
+  </si>
+  <si>
+    <t>Decoration</t>
+  </si>
+  <si>
+    <t>Giấy câu đố</t>
+  </si>
+  <si>
+    <t>Vật phẩm cho câu đố</t>
+  </si>
+  <si>
+    <t>Đồ trang trí</t>
+  </si>
+  <si>
+    <t>V. SCENES</t>
+  </si>
+  <si>
+    <t>VI. Item lists</t>
+  </si>
+  <si>
+    <t>VII. NPC</t>
+  </si>
+  <si>
+    <t>Key item No</t>
+  </si>
+  <si>
+    <t>Mico (NPC)</t>
+  </si>
+  <si>
+    <t>Instruction</t>
+  </si>
+  <si>
+    <t>Tranh Puzzle #1</t>
+  </si>
+  <si>
+    <t>Tranh Puzzle #2</t>
+  </si>
+  <si>
+    <t>Máy điền số</t>
+  </si>
+  <si>
+    <t>Dùng để điền mật mã tìm được</t>
+  </si>
+  <si>
+    <t>Dùng để giải đố</t>
+  </si>
+  <si>
+    <t>Interactable?</t>
+  </si>
+  <si>
+    <t>Chưa</t>
+  </si>
+  <si>
+    <t>Đã có Assets?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="15"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1386,8 +1524,20 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1400,8 +1550,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1424,133 +1580,227 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1924,14 +2174,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>47626</xdr:rowOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1963,6 +2213,128 @@
         <a:xfrm>
           <a:off x="609600" y="17497426"/>
           <a:ext cx="10363200" cy="5829300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>220133</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6" descr="A Better World, A New Friend - Red Dead Redemption 2 Guide - IGN">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF8834BF-F79C-54C7-DC3E-028237959FEE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609600" y="14582775"/>
+          <a:ext cx="5096933" cy="2867025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>138033</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8" descr="Video Games Don't Have To Be Fun - COGconnected">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97A42634-2C94-F454-E471-86E5E1030667}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5724525" y="14582775"/>
+          <a:ext cx="5095875" cy="2862183"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2308,29 +2680,29 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:26" ht="46.5" x14ac:dyDescent="0.7">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
     </row>
     <row r="3" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
@@ -2350,95 +2722,95 @@
     </row>
     <row r="7" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="24"/>
-      <c r="U12" s="24"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="37"/>
+      <c r="O12" s="37"/>
+      <c r="P12" s="37"/>
+      <c r="Q12" s="37"/>
+      <c r="R12" s="37"/>
+      <c r="S12" s="37"/>
+      <c r="T12" s="37"/>
+      <c r="U12" s="37"/>
     </row>
     <row r="13" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="20"/>
-      <c r="T13" s="20"/>
-      <c r="U13" s="20"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
+      <c r="S13" s="36"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="36"/>
     </row>
     <row r="14" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B14" s="5" t="s">
@@ -2454,28 +2826,28 @@
       <c r="J14" s="4"/>
     </row>
     <row r="15" spans="1:26" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
+      <c r="B15" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
+      <c r="T15" s="34"/>
+      <c r="U15" s="34"/>
       <c r="V15" s="6"/>
       <c r="W15" s="6"/>
       <c r="X15" s="6"/>
@@ -2483,114 +2855,114 @@
       <c r="Z15" s="6"/>
     </row>
     <row r="16" spans="1:26" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="34"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="34"/>
+      <c r="S16" s="34"/>
+      <c r="T16" s="34"/>
+      <c r="U16" s="34"/>
+    </row>
+    <row r="17" spans="1:21" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
+      <c r="S17" s="36"/>
+      <c r="T17" s="36"/>
+      <c r="U17" s="36"/>
+    </row>
+    <row r="18" spans="1:21" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="21"/>
-      <c r="Q16" s="21"/>
-      <c r="R16" s="21"/>
-      <c r="S16" s="21"/>
-      <c r="T16" s="21"/>
-      <c r="U16" s="21"/>
-    </row>
-    <row r="17" spans="1:21" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-      <c r="P17" s="20"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="20"/>
-      <c r="S17" s="20"/>
-      <c r="T17" s="20"/>
-      <c r="U17" s="20"/>
-    </row>
-    <row r="18" spans="1:21" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
-      <c r="S18" s="23"/>
-      <c r="T18" s="23"/>
-      <c r="U18" s="23"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="28"/>
+      <c r="R18" s="28"/>
+      <c r="S18" s="28"/>
+      <c r="T18" s="28"/>
+      <c r="U18" s="28"/>
     </row>
     <row r="19" spans="1:21" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B19" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
-      <c r="N19" s="25"/>
-      <c r="O19" s="25"/>
-      <c r="P19" s="25"/>
-      <c r="Q19" s="25"/>
-      <c r="R19" s="25"/>
-      <c r="S19" s="25"/>
-      <c r="T19" s="25"/>
-      <c r="U19" s="25"/>
+      <c r="B19" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="31"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="31"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="31"/>
+      <c r="Q19" s="31"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="31"/>
+      <c r="T19" s="31"/>
+      <c r="U19" s="31"/>
     </row>
     <row r="21" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -2618,7 +2990,7 @@
     </row>
     <row r="27" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B27" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
@@ -2646,7 +3018,7 @@
     </row>
     <row r="29" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B29" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -2661,7 +3033,7 @@
     </row>
     <row r="30" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B30" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -2689,17 +3061,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B19:U19"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B15:U15"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="B17:U17"/>
     <mergeCell ref="B16:U16"/>
     <mergeCell ref="B18:U18"/>
     <mergeCell ref="B13:U13"/>
     <mergeCell ref="B12:U12"/>
+    <mergeCell ref="B19:U19"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B15:U15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2715,366 +3087,367 @@
   <sheetData>
     <row r="2" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="8"/>
     </row>
     <row r="4" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="D4" s="40"/>
+      <c r="E4" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36" t="s">
+      <c r="F4" s="40"/>
+      <c r="G4" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="36"/>
-      <c r="G4" s="29" t="s">
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="29"/>
-      <c r="W4" s="29"/>
-      <c r="X4" s="29"/>
-      <c r="Y4" s="29"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="42"/>
+      <c r="R4" s="42"/>
+      <c r="S4" s="42"/>
+      <c r="T4" s="42"/>
+      <c r="U4" s="42"/>
+      <c r="V4" s="42"/>
+      <c r="W4" s="42"/>
+      <c r="X4" s="42"/>
+      <c r="Y4" s="42"/>
     </row>
     <row r="5" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11">
         <v>1</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="38"/>
+      <c r="E5" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="35"/>
-      <c r="G5" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="N5" s="30"/>
-      <c r="O5" s="30"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="30"/>
-      <c r="R5" s="30"/>
-      <c r="S5" s="30"/>
-      <c r="T5" s="30"/>
-      <c r="U5" s="30"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
-      <c r="X5" s="30"/>
-      <c r="Y5" s="30"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46"/>
+      <c r="R5" s="46"/>
+      <c r="S5" s="46"/>
+      <c r="T5" s="46"/>
+      <c r="U5" s="46"/>
+      <c r="V5" s="46"/>
+      <c r="W5" s="46"/>
+      <c r="X5" s="46"/>
+      <c r="Y5" s="46"/>
     </row>
     <row r="6" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11">
         <v>2</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="35"/>
-      <c r="G6" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="N6" s="30"/>
-      <c r="O6" s="30"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="30"/>
-      <c r="R6" s="30"/>
-      <c r="S6" s="30"/>
-      <c r="T6" s="30"/>
-      <c r="U6" s="30"/>
-      <c r="V6" s="30"/>
-      <c r="W6" s="30"/>
-      <c r="X6" s="30"/>
-      <c r="Y6" s="30"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="39"/>
+      <c r="G6" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
+      <c r="P6" s="46"/>
+      <c r="Q6" s="46"/>
+      <c r="R6" s="46"/>
+      <c r="S6" s="46"/>
+      <c r="T6" s="46"/>
+      <c r="U6" s="46"/>
+      <c r="V6" s="46"/>
+      <c r="W6" s="46"/>
+      <c r="X6" s="46"/>
+      <c r="Y6" s="46"/>
     </row>
     <row r="7" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11">
         <v>3</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="35"/>
-      <c r="G7" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="32"/>
-      <c r="M7" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28"/>
-      <c r="T7" s="28"/>
-      <c r="U7" s="28"/>
-      <c r="V7" s="28"/>
-      <c r="W7" s="28"/>
-      <c r="X7" s="28"/>
-      <c r="Y7" s="28"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="39"/>
+      <c r="G7" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" s="44"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="44"/>
+      <c r="Q7" s="44"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="44"/>
+      <c r="T7" s="44"/>
+      <c r="U7" s="44"/>
+      <c r="V7" s="44"/>
+      <c r="W7" s="44"/>
+      <c r="X7" s="44"/>
+      <c r="Y7" s="44"/>
     </row>
     <row r="8" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11">
         <v>4</v>
       </c>
-      <c r="C8" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="34"/>
-      <c r="E8" s="35" t="s">
+      <c r="C8" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="35"/>
-      <c r="G8" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="32"/>
-      <c r="M8" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="N8" s="28"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="28"/>
-      <c r="S8" s="28"/>
-      <c r="T8" s="28"/>
-      <c r="U8" s="28"/>
-      <c r="V8" s="28"/>
-      <c r="W8" s="28"/>
-      <c r="X8" s="28"/>
-      <c r="Y8" s="28"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="39"/>
+      <c r="G8" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="N8" s="44"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="44"/>
+      <c r="Q8" s="44"/>
+      <c r="R8" s="44"/>
+      <c r="S8" s="44"/>
+      <c r="T8" s="44"/>
+      <c r="U8" s="44"/>
+      <c r="V8" s="44"/>
+      <c r="W8" s="44"/>
+      <c r="X8" s="44"/>
+      <c r="Y8" s="44"/>
     </row>
     <row r="9" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11">
         <v>5</v>
       </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="35"/>
-      <c r="G9" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
-      <c r="L9" s="32"/>
-      <c r="M9" s="44" t="s">
-        <v>92</v>
-      </c>
-      <c r="N9" s="28"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="28"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="28"/>
-      <c r="S9" s="28"/>
-      <c r="T9" s="28"/>
-      <c r="U9" s="28"/>
-      <c r="V9" s="28"/>
-      <c r="W9" s="28"/>
-      <c r="X9" s="28"/>
-      <c r="Y9" s="28"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="39"/>
+      <c r="G9" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="N9" s="44"/>
+      <c r="O9" s="44"/>
+      <c r="P9" s="44"/>
+      <c r="Q9" s="44"/>
+      <c r="R9" s="44"/>
+      <c r="S9" s="44"/>
+      <c r="T9" s="44"/>
+      <c r="U9" s="44"/>
+      <c r="V9" s="44"/>
+      <c r="W9" s="44"/>
+      <c r="X9" s="44"/>
+      <c r="Y9" s="44"/>
     </row>
     <row r="10" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="11">
         <v>6</v>
       </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="35"/>
-      <c r="G10" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="N10" s="28"/>
-      <c r="O10" s="28"/>
-      <c r="P10" s="28"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="28"/>
-      <c r="S10" s="28"/>
-      <c r="T10" s="28"/>
-      <c r="U10" s="28"/>
-      <c r="V10" s="28"/>
-      <c r="W10" s="28"/>
-      <c r="X10" s="28"/>
-      <c r="Y10" s="28"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="39"/>
+      <c r="G10" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="N10" s="44"/>
+      <c r="O10" s="44"/>
+      <c r="P10" s="44"/>
+      <c r="Q10" s="44"/>
+      <c r="R10" s="44"/>
+      <c r="S10" s="44"/>
+      <c r="T10" s="44"/>
+      <c r="U10" s="44"/>
+      <c r="V10" s="44"/>
+      <c r="W10" s="44"/>
+      <c r="X10" s="44"/>
+      <c r="Y10" s="44"/>
     </row>
     <row r="11" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="11">
         <v>7</v>
       </c>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="35" t="s">
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="39"/>
+      <c r="G11" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="35"/>
-      <c r="G11" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32"/>
-      <c r="M11" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="N11" s="28"/>
-      <c r="O11" s="28"/>
-      <c r="P11" s="28"/>
-      <c r="Q11" s="28"/>
-      <c r="R11" s="28"/>
-      <c r="S11" s="28"/>
-      <c r="T11" s="28"/>
-      <c r="U11" s="28"/>
-      <c r="V11" s="28"/>
-      <c r="W11" s="28"/>
-      <c r="X11" s="28"/>
-      <c r="Y11" s="28"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="N11" s="44"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="44"/>
+      <c r="W11" s="44"/>
+      <c r="X11" s="44"/>
+      <c r="Y11" s="44"/>
     </row>
     <row r="12" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="11">
         <v>8</v>
       </c>
-      <c r="C12" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="34"/>
-      <c r="E12" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="35"/>
-      <c r="G12" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="N12" s="28"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="28"/>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="28"/>
-      <c r="S12" s="28"/>
-      <c r="T12" s="28"/>
-      <c r="U12" s="28"/>
-      <c r="V12" s="28"/>
-      <c r="W12" s="28"/>
-      <c r="X12" s="28"/>
-      <c r="Y12" s="28"/>
+      <c r="C12" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="38"/>
+      <c r="E12" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="39"/>
+      <c r="G12" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="41"/>
+      <c r="M12" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
+      <c r="T12" s="44"/>
+      <c r="U12" s="44"/>
+      <c r="V12" s="44"/>
+      <c r="W12" s="44"/>
+      <c r="X12" s="44"/>
+      <c r="Y12" s="44"/>
     </row>
     <row r="46" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B56" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="C56" s="33"/>
-      <c r="D56" s="33"/>
-      <c r="E56" s="33"/>
-      <c r="F56" s="33"/>
-      <c r="G56" s="33"/>
-      <c r="H56" s="33"/>
-      <c r="I56" s="33"/>
-      <c r="J56" s="33"/>
-      <c r="K56" s="33"/>
-      <c r="L56" s="33"/>
-      <c r="M56" s="33"/>
-      <c r="N56" s="33"/>
-      <c r="O56" s="33"/>
-      <c r="P56" s="33"/>
-      <c r="Q56" s="33"/>
-      <c r="R56" s="33"/>
-      <c r="S56" s="33"/>
-      <c r="T56" s="33"/>
-      <c r="U56" s="33"/>
-      <c r="V56" s="33"/>
-      <c r="W56" s="33"/>
-      <c r="X56" s="33"/>
-      <c r="Y56" s="33"/>
+      <c r="B56" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="C56" s="45"/>
+      <c r="D56" s="45"/>
+      <c r="E56" s="45"/>
+      <c r="F56" s="45"/>
+      <c r="G56" s="45"/>
+      <c r="H56" s="45"/>
+      <c r="I56" s="45"/>
+      <c r="J56" s="45"/>
+      <c r="K56" s="45"/>
+      <c r="L56" s="45"/>
+      <c r="M56" s="45"/>
+      <c r="N56" s="45"/>
+      <c r="O56" s="45"/>
+      <c r="P56" s="45"/>
+      <c r="Q56" s="45"/>
+      <c r="R56" s="45"/>
+      <c r="S56" s="45"/>
+      <c r="T56" s="45"/>
+      <c r="U56" s="45"/>
+      <c r="V56" s="45"/>
+      <c r="W56" s="45"/>
+      <c r="X56" s="45"/>
+      <c r="Y56" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G9:L9"/>
+    <mergeCell ref="M9:Y9"/>
+    <mergeCell ref="M4:Y4"/>
+    <mergeCell ref="M5:Y5"/>
+    <mergeCell ref="M6:Y6"/>
+    <mergeCell ref="M7:Y7"/>
+    <mergeCell ref="M8:Y8"/>
+    <mergeCell ref="M10:Y10"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="B56:Y56"/>
+    <mergeCell ref="M11:Y11"/>
+    <mergeCell ref="M12:Y12"/>
     <mergeCell ref="G10:L10"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="E12:F12"/>
@@ -3082,6 +3455,11 @@
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G9:L9"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="G4:L4"/>
@@ -3089,18 +3467,12 @@
     <mergeCell ref="G6:L6"/>
     <mergeCell ref="G7:L7"/>
     <mergeCell ref="G8:L8"/>
-    <mergeCell ref="M10:Y10"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="B56:Y56"/>
-    <mergeCell ref="M11:Y11"/>
-    <mergeCell ref="M12:Y12"/>
-    <mergeCell ref="M9:Y9"/>
-    <mergeCell ref="M4:Y4"/>
-    <mergeCell ref="M5:Y5"/>
-    <mergeCell ref="M6:Y6"/>
-    <mergeCell ref="M7:Y7"/>
-    <mergeCell ref="M8:Y8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3112,34 +3484,34 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A2:AK68"/>
+  <dimension ref="A2:AK77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:30" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="N6" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="37"/>
-      <c r="S6" s="37"/>
-      <c r="T6" s="37"/>
-      <c r="U6" s="37"/>
-      <c r="V6" s="37"/>
-      <c r="W6" s="37"/>
-      <c r="X6" s="37"/>
-      <c r="Y6" s="37"/>
+      <c r="N6" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="23"/>
+      <c r="T6" s="23"/>
+      <c r="U6" s="23"/>
+      <c r="V6" s="23"/>
+      <c r="W6" s="23"/>
+      <c r="X6" s="23"/>
+      <c r="Y6" s="23"/>
     </row>
     <row r="7" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
       <c r="N7" s="7"/>
@@ -3156,25 +3528,25 @@
       <c r="Y7" s="7"/>
     </row>
     <row r="8" spans="1:30" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N8" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
-      <c r="T8" s="22"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
-      <c r="W8" s="22"/>
-      <c r="X8" s="22"/>
-      <c r="Y8" s="22"/>
-      <c r="Z8" s="22"/>
-      <c r="AA8" s="22"/>
-      <c r="AB8" s="22"/>
-      <c r="AC8" s="22"/>
-      <c r="AD8" s="22"/>
+      <c r="N8" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="25"/>
+      <c r="W8" s="25"/>
+      <c r="X8" s="25"/>
+      <c r="Y8" s="25"/>
+      <c r="Z8" s="25"/>
+      <c r="AA8" s="25"/>
+      <c r="AB8" s="25"/>
+      <c r="AC8" s="25"/>
+      <c r="AD8" s="25"/>
     </row>
     <row r="9" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
       <c r="N9" s="7"/>
@@ -3191,67 +3563,67 @@
       <c r="Y9" s="7"/>
     </row>
     <row r="10" spans="1:30" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N10" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
-      <c r="T10" s="23"/>
-      <c r="U10" s="23"/>
-      <c r="V10" s="23"/>
-      <c r="W10" s="23"/>
-      <c r="X10" s="23"/>
-      <c r="Y10" s="23"/>
-      <c r="Z10" s="23"/>
-      <c r="AA10" s="23"/>
-      <c r="AB10" s="23"/>
-      <c r="AC10" s="23"/>
-      <c r="AD10" s="23"/>
+      <c r="N10" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="28"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="28"/>
+      <c r="W10" s="28"/>
+      <c r="X10" s="28"/>
+      <c r="Y10" s="28"/>
+      <c r="Z10" s="28"/>
+      <c r="AA10" s="28"/>
+      <c r="AB10" s="28"/>
+      <c r="AC10" s="28"/>
+      <c r="AD10" s="28"/>
     </row>
     <row r="13" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
       <c r="S13" s="12"/>
     </row>
     <row r="16" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B16" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B17" s="8"/>
     </row>
     <row r="18" spans="2:33" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="42"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="42"/>
-      <c r="R18" s="42"/>
-      <c r="S18" s="42"/>
-      <c r="T18" s="42"/>
-      <c r="U18" s="42"/>
-      <c r="V18" s="42"/>
-      <c r="W18" s="42"/>
-      <c r="X18" s="42"/>
-      <c r="Y18" s="42"/>
-      <c r="Z18" s="42"/>
-      <c r="AA18" s="42"/>
-      <c r="AB18" s="42"/>
+      <c r="B18" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="30"/>
+      <c r="Q18" s="30"/>
+      <c r="R18" s="30"/>
+      <c r="S18" s="30"/>
+      <c r="T18" s="30"/>
+      <c r="U18" s="30"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="30"/>
+      <c r="X18" s="30"/>
+      <c r="Y18" s="30"/>
+      <c r="Z18" s="30"/>
+      <c r="AA18" s="30"/>
+      <c r="AB18" s="30"/>
     </row>
     <row r="19" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="15"/>
@@ -3281,46 +3653,46 @@
     </row>
     <row r="21" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" s="10"/>
     </row>
     <row r="23" spans="2:33" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="T23" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="U23" s="38"/>
-      <c r="V23" s="38"/>
-      <c r="W23" s="38"/>
-      <c r="X23" s="38"/>
-      <c r="Y23" s="38"/>
-      <c r="Z23" s="38"/>
-      <c r="AA23" s="38"/>
-      <c r="AB23" s="38"/>
-      <c r="AC23" s="38"/>
-      <c r="AD23" s="38"/>
-      <c r="AE23" s="38"/>
-      <c r="AF23" s="38"/>
+      <c r="T23" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="U23" s="24"/>
+      <c r="V23" s="24"/>
+      <c r="W23" s="24"/>
+      <c r="X23" s="24"/>
+      <c r="Y23" s="24"/>
+      <c r="Z23" s="24"/>
+      <c r="AA23" s="24"/>
+      <c r="AB23" s="24"/>
+      <c r="AC23" s="24"/>
+      <c r="AD23" s="24"/>
+      <c r="AE23" s="24"/>
+      <c r="AF23" s="24"/>
     </row>
     <row r="24" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T24" s="12"/>
     </row>
     <row r="25" spans="2:33" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T25" s="46" t="s">
-        <v>55</v>
-      </c>
-      <c r="U25" s="39"/>
-      <c r="V25" s="39"/>
-      <c r="W25" s="39"/>
-      <c r="X25" s="39"/>
-      <c r="Y25" s="39"/>
-      <c r="Z25" s="39"/>
-      <c r="AA25" s="39"/>
-      <c r="AB25" s="39"/>
-      <c r="AC25" s="39"/>
-      <c r="AD25" s="39"/>
-      <c r="AE25" s="39"/>
-      <c r="AF25" s="39"/>
+      <c r="T25" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="U25" s="21"/>
+      <c r="V25" s="21"/>
+      <c r="W25" s="21"/>
+      <c r="X25" s="21"/>
+      <c r="Y25" s="21"/>
+      <c r="Z25" s="21"/>
+      <c r="AA25" s="21"/>
+      <c r="AB25" s="21"/>
+      <c r="AC25" s="21"/>
+      <c r="AD25" s="21"/>
+      <c r="AE25" s="21"/>
+      <c r="AF25" s="21"/>
       <c r="AG25" s="17"/>
     </row>
     <row r="26" spans="2:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3340,33 +3712,33 @@
       <c r="AG26" s="17"/>
     </row>
     <row r="27" spans="2:33" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="T27" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="U27" s="38"/>
-      <c r="V27" s="38"/>
-      <c r="W27" s="38"/>
-      <c r="X27" s="38"/>
-      <c r="Y27" s="38"/>
-      <c r="Z27" s="38"/>
-      <c r="AA27" s="38"/>
-      <c r="AB27" s="38"/>
-      <c r="AC27" s="38"/>
-      <c r="AD27" s="38"/>
-      <c r="AE27" s="38"/>
-      <c r="AF27" s="38"/>
+      <c r="T27" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="U27" s="24"/>
+      <c r="V27" s="24"/>
+      <c r="W27" s="24"/>
+      <c r="X27" s="24"/>
+      <c r="Y27" s="24"/>
+      <c r="Z27" s="24"/>
+      <c r="AA27" s="24"/>
+      <c r="AB27" s="24"/>
+      <c r="AC27" s="24"/>
+      <c r="AD27" s="24"/>
+      <c r="AE27" s="24"/>
+      <c r="AF27" s="24"/>
     </row>
     <row r="28" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T28" s="12"/>
     </row>
     <row r="29" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T29" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T30" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
@@ -3374,7 +3746,7 @@
     </row>
     <row r="32" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T32" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
@@ -3384,7 +3756,7 @@
     </row>
     <row r="34" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T34" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="U34" s="12"/>
       <c r="V34" s="12"/>
@@ -3400,25 +3772,25 @@
       <c r="AF34" s="12"/>
     </row>
     <row r="35" spans="2:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T35" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="U35" s="22"/>
-      <c r="V35" s="22"/>
-      <c r="W35" s="22"/>
-      <c r="X35" s="22"/>
-      <c r="Y35" s="22"/>
-      <c r="Z35" s="22"/>
-      <c r="AA35" s="22"/>
-      <c r="AB35" s="22"/>
-      <c r="AC35" s="22"/>
-      <c r="AD35" s="22"/>
-      <c r="AE35" s="22"/>
-      <c r="AF35" s="22"/>
+      <c r="T35" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="U35" s="25"/>
+      <c r="V35" s="25"/>
+      <c r="W35" s="25"/>
+      <c r="X35" s="25"/>
+      <c r="Y35" s="25"/>
+      <c r="Z35" s="25"/>
+      <c r="AA35" s="25"/>
+      <c r="AB35" s="25"/>
+      <c r="AC35" s="25"/>
+      <c r="AD35" s="25"/>
+      <c r="AE35" s="25"/>
+      <c r="AF35" s="25"/>
     </row>
     <row r="37" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T37" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="U37" s="12"/>
       <c r="V37" s="12"/>
@@ -3434,325 +3806,392 @@
       <c r="AF37" s="12"/>
     </row>
     <row r="38" spans="2:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T38" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="U38" s="22"/>
-      <c r="V38" s="22"/>
-      <c r="W38" s="22"/>
-      <c r="X38" s="22"/>
-      <c r="Y38" s="22"/>
-      <c r="Z38" s="22"/>
-      <c r="AA38" s="22"/>
-      <c r="AB38" s="22"/>
-      <c r="AC38" s="22"/>
-      <c r="AD38" s="22"/>
-      <c r="AE38" s="22"/>
-      <c r="AF38" s="22"/>
-      <c r="AG38" s="22"/>
-      <c r="AH38" s="22"/>
-      <c r="AI38" s="22"/>
-      <c r="AJ38" s="22"/>
-      <c r="AK38" s="22"/>
+      <c r="T38" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="U38" s="25"/>
+      <c r="V38" s="25"/>
+      <c r="W38" s="25"/>
+      <c r="X38" s="25"/>
+      <c r="Y38" s="25"/>
+      <c r="Z38" s="25"/>
+      <c r="AA38" s="25"/>
+      <c r="AB38" s="25"/>
+      <c r="AC38" s="25"/>
+      <c r="AD38" s="25"/>
+      <c r="AE38" s="25"/>
+      <c r="AF38" s="25"/>
+      <c r="AG38" s="25"/>
+      <c r="AH38" s="25"/>
+      <c r="AI38" s="25"/>
+      <c r="AJ38" s="25"/>
+      <c r="AK38" s="25"/>
     </row>
     <row r="39" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T39" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T40" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="2:37" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="T41" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="U41" s="38"/>
-      <c r="V41" s="38"/>
-      <c r="W41" s="38"/>
-      <c r="X41" s="38"/>
-      <c r="Y41" s="38"/>
-      <c r="Z41" s="38"/>
-      <c r="AA41" s="38"/>
-      <c r="AB41" s="38"/>
-      <c r="AC41" s="38"/>
-      <c r="AD41" s="38"/>
-      <c r="AE41" s="38"/>
-      <c r="AF41" s="38"/>
-      <c r="AG41" s="38"/>
+      <c r="T41" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="U41" s="24"/>
+      <c r="V41" s="24"/>
+      <c r="W41" s="24"/>
+      <c r="X41" s="24"/>
+      <c r="Y41" s="24"/>
+      <c r="Z41" s="24"/>
+      <c r="AA41" s="24"/>
+      <c r="AB41" s="24"/>
+      <c r="AC41" s="24"/>
+      <c r="AD41" s="24"/>
+      <c r="AE41" s="24"/>
+      <c r="AF41" s="24"/>
+      <c r="AG41" s="24"/>
     </row>
     <row r="42" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T42" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T43" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B44" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" s="27"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="27"/>
+      <c r="I44" s="27"/>
+      <c r="J44" s="27"/>
+      <c r="K44" s="27"/>
+      <c r="L44" s="27"/>
+      <c r="M44" s="27"/>
+      <c r="N44" s="27"/>
+      <c r="O44" s="27"/>
+      <c r="P44" s="27"/>
+      <c r="Q44" s="27"/>
+      <c r="R44" s="27"/>
+      <c r="T44" s="24" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="44" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B44" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="C44" s="41"/>
-      <c r="D44" s="41"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="41"/>
-      <c r="J44" s="41"/>
-      <c r="K44" s="41"/>
-      <c r="L44" s="41"/>
-      <c r="M44" s="41"/>
-      <c r="N44" s="41"/>
-      <c r="O44" s="41"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="41"/>
-      <c r="T44" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="U44" s="38"/>
-      <c r="V44" s="38"/>
-      <c r="W44" s="38"/>
-      <c r="X44" s="38"/>
-      <c r="Y44" s="38"/>
-      <c r="Z44" s="38"/>
-      <c r="AA44" s="38"/>
-      <c r="AB44" s="38"/>
-      <c r="AC44" s="38"/>
-      <c r="AD44" s="38"/>
-      <c r="AE44" s="38"/>
-      <c r="AF44" s="38"/>
-      <c r="AG44" s="38"/>
-      <c r="AH44" s="38"/>
-      <c r="AI44" s="38"/>
+      <c r="U44" s="24"/>
+      <c r="V44" s="24"/>
+      <c r="W44" s="24"/>
+      <c r="X44" s="24"/>
+      <c r="Y44" s="24"/>
+      <c r="Z44" s="24"/>
+      <c r="AA44" s="24"/>
+      <c r="AB44" s="24"/>
+      <c r="AC44" s="24"/>
+      <c r="AD44" s="24"/>
+      <c r="AE44" s="24"/>
+      <c r="AF44" s="24"/>
+      <c r="AG44" s="24"/>
+      <c r="AH44" s="24"/>
+      <c r="AI44" s="24"/>
     </row>
     <row r="45" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T45" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T46" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T47" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T48" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T49" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T50" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T51" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T52" s="12"/>
+    </row>
+    <row r="53" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T53" s="12"/>
+    </row>
+    <row r="54" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T54" s="12"/>
+    </row>
+    <row r="55" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T55" s="12"/>
+    </row>
+    <row r="56" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T56" s="12"/>
+    </row>
+    <row r="57" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T57" s="12"/>
+    </row>
+    <row r="58" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T58" s="12"/>
+    </row>
+    <row r="59" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B59" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="27"/>
+      <c r="I59" s="27"/>
+      <c r="J59" s="27"/>
+      <c r="K59" s="27"/>
+      <c r="L59" s="27"/>
+      <c r="M59" s="27"/>
+      <c r="N59" s="27"/>
+      <c r="O59" s="27"/>
+      <c r="P59" s="27"/>
+      <c r="Q59" s="27"/>
+      <c r="R59" s="27"/>
+      <c r="T59" s="12"/>
+    </row>
+    <row r="60" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T60" s="12"/>
+    </row>
+    <row r="61" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T61" s="12"/>
+    </row>
+    <row r="62" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B62" s="8" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="54" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B54" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="56" spans="2:37" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T56" s="46" t="s">
+    <row r="64" spans="2:37" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T64" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="U64" s="21"/>
+      <c r="V64" s="21"/>
+      <c r="W64" s="21"/>
+      <c r="X64" s="21"/>
+      <c r="Y64" s="21"/>
+      <c r="Z64" s="21"/>
+      <c r="AA64" s="21"/>
+      <c r="AB64" s="21"/>
+      <c r="AC64" s="21"/>
+      <c r="AD64" s="21"/>
+      <c r="AE64" s="21"/>
+      <c r="AF64" s="21"/>
+      <c r="AG64" s="21"/>
+      <c r="AH64" s="21"/>
+      <c r="AI64" s="21"/>
+      <c r="AJ64" s="21"/>
+      <c r="AK64" s="21"/>
+    </row>
+    <row r="66" spans="20:37" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T66" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="U66" s="21"/>
+      <c r="V66" s="21"/>
+      <c r="W66" s="21"/>
+      <c r="X66" s="21"/>
+      <c r="Y66" s="21"/>
+      <c r="Z66" s="21"/>
+      <c r="AA66" s="21"/>
+      <c r="AB66" s="21"/>
+      <c r="AC66" s="21"/>
+      <c r="AD66" s="21"/>
+      <c r="AE66" s="21"/>
+      <c r="AF66" s="21"/>
+      <c r="AG66" s="21"/>
+      <c r="AH66" s="21"/>
+      <c r="AI66" s="21"/>
+      <c r="AJ66" s="21"/>
+      <c r="AK66" s="21"/>
+    </row>
+    <row r="68" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T68" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="69" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T69" s="8"/>
+    </row>
+    <row r="70" spans="20:37" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T70" s="48" t="s">
         <v>96</v>
       </c>
-      <c r="U56" s="39"/>
-      <c r="V56" s="39"/>
-      <c r="W56" s="39"/>
-      <c r="X56" s="39"/>
-      <c r="Y56" s="39"/>
-      <c r="Z56" s="39"/>
-      <c r="AA56" s="39"/>
-      <c r="AB56" s="39"/>
-      <c r="AC56" s="39"/>
-      <c r="AD56" s="39"/>
-      <c r="AE56" s="39"/>
-      <c r="AF56" s="39"/>
-      <c r="AG56" s="39"/>
-      <c r="AH56" s="39"/>
-      <c r="AI56" s="39"/>
-      <c r="AJ56" s="39"/>
-      <c r="AK56" s="39"/>
-    </row>
-    <row r="58" spans="2:37" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T58" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="U58" s="39"/>
-      <c r="V58" s="39"/>
-      <c r="W58" s="39"/>
-      <c r="X58" s="39"/>
-      <c r="Y58" s="39"/>
-      <c r="Z58" s="39"/>
-      <c r="AA58" s="39"/>
-      <c r="AB58" s="39"/>
-      <c r="AC58" s="39"/>
-      <c r="AD58" s="39"/>
-      <c r="AE58" s="39"/>
-      <c r="AF58" s="39"/>
-      <c r="AG58" s="39"/>
-      <c r="AH58" s="39"/>
-      <c r="AI58" s="39"/>
-      <c r="AJ58" s="39"/>
-      <c r="AK58" s="39"/>
-    </row>
-    <row r="59" spans="2:37" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T59" s="46" t="s">
-        <v>95</v>
-      </c>
-      <c r="U59" s="39"/>
-      <c r="V59" s="39"/>
-      <c r="W59" s="39"/>
-      <c r="X59" s="39"/>
-      <c r="Y59" s="39"/>
-      <c r="Z59" s="39"/>
-      <c r="AA59" s="39"/>
-      <c r="AB59" s="39"/>
-      <c r="AC59" s="39"/>
-      <c r="AD59" s="39"/>
-      <c r="AE59" s="39"/>
-      <c r="AF59" s="39"/>
-      <c r="AG59" s="39"/>
-      <c r="AH59" s="39"/>
-      <c r="AI59" s="39"/>
-      <c r="AJ59" s="39"/>
-      <c r="AK59" s="39"/>
-    </row>
-    <row r="61" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T61" s="8" t="s">
+      <c r="U70" s="21"/>
+      <c r="V70" s="21"/>
+      <c r="W70" s="21"/>
+      <c r="X70" s="21"/>
+      <c r="Y70" s="21"/>
+      <c r="Z70" s="21"/>
+      <c r="AA70" s="21"/>
+      <c r="AB70" s="21"/>
+      <c r="AC70" s="21"/>
+      <c r="AD70" s="21"/>
+      <c r="AE70" s="21"/>
+      <c r="AF70" s="21"/>
+      <c r="AG70" s="21"/>
+      <c r="AH70" s="21"/>
+      <c r="AI70" s="21"/>
+      <c r="AJ70" s="21"/>
+      <c r="AK70" s="21"/>
+    </row>
+    <row r="71" spans="20:37" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="T71" s="19"/>
+      <c r="U71" s="18"/>
+      <c r="V71" s="18"/>
+      <c r="W71" s="18"/>
+      <c r="X71" s="18"/>
+      <c r="Y71" s="18"/>
+      <c r="Z71" s="18"/>
+      <c r="AA71" s="18"/>
+      <c r="AB71" s="18"/>
+      <c r="AC71" s="18"/>
+      <c r="AD71" s="18"/>
+      <c r="AE71" s="18"/>
+      <c r="AF71" s="18"/>
+      <c r="AG71" s="18"/>
+      <c r="AH71" s="18"/>
+      <c r="AI71" s="18"/>
+      <c r="AJ71" s="18"/>
+      <c r="AK71" s="18"/>
+    </row>
+    <row r="72" spans="20:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T72" s="22" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="63" spans="2:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T63" s="43" t="s">
+      <c r="U72" s="22"/>
+      <c r="V72" s="22"/>
+      <c r="W72" s="22"/>
+      <c r="X72" s="22"/>
+      <c r="Y72" s="22"/>
+      <c r="Z72" s="22"/>
+      <c r="AA72" s="22"/>
+      <c r="AB72" s="22"/>
+      <c r="AC72" s="22"/>
+      <c r="AD72" s="22"/>
+      <c r="AE72" s="22"/>
+      <c r="AF72" s="22"/>
+      <c r="AG72" s="22"/>
+      <c r="AH72" s="22"/>
+      <c r="AI72" s="22"/>
+      <c r="AJ72" s="22"/>
+      <c r="AK72" s="22"/>
+    </row>
+    <row r="73" spans="20:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T73" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="U63" s="43"/>
-      <c r="V63" s="43"/>
-      <c r="W63" s="43"/>
-      <c r="X63" s="43"/>
-      <c r="Y63" s="43"/>
-      <c r="Z63" s="43"/>
-      <c r="AA63" s="43"/>
-      <c r="AB63" s="43"/>
-      <c r="AC63" s="43"/>
-      <c r="AD63" s="43"/>
-      <c r="AE63" s="43"/>
-      <c r="AF63" s="43"/>
-      <c r="AG63" s="43"/>
-      <c r="AH63" s="43"/>
-      <c r="AI63" s="43"/>
-      <c r="AJ63" s="43"/>
-      <c r="AK63" s="43"/>
-    </row>
-    <row r="64" spans="2:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T64" s="39" t="s">
+      <c r="U73" s="21"/>
+      <c r="V73" s="21"/>
+      <c r="W73" s="21"/>
+      <c r="X73" s="21"/>
+      <c r="Y73" s="21"/>
+      <c r="Z73" s="21"/>
+      <c r="AA73" s="21"/>
+      <c r="AB73" s="21"/>
+      <c r="AC73" s="21"/>
+      <c r="AD73" s="21"/>
+      <c r="AE73" s="21"/>
+      <c r="AF73" s="21"/>
+      <c r="AG73" s="21"/>
+      <c r="AH73" s="21"/>
+      <c r="AI73" s="21"/>
+      <c r="AJ73" s="21"/>
+      <c r="AK73" s="21"/>
+    </row>
+    <row r="74" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T74" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="75" spans="20:37" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="T75" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="U64" s="39"/>
-      <c r="V64" s="39"/>
-      <c r="W64" s="39"/>
-      <c r="X64" s="39"/>
-      <c r="Y64" s="39"/>
-      <c r="Z64" s="39"/>
-      <c r="AA64" s="39"/>
-      <c r="AB64" s="39"/>
-      <c r="AC64" s="39"/>
-      <c r="AD64" s="39"/>
-      <c r="AE64" s="39"/>
-      <c r="AF64" s="39"/>
-      <c r="AG64" s="39"/>
-      <c r="AH64" s="39"/>
-      <c r="AI64" s="39"/>
-      <c r="AJ64" s="39"/>
-      <c r="AK64" s="39"/>
-    </row>
-    <row r="65" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T65" s="12" t="s">
+      <c r="U75" s="22"/>
+      <c r="V75" s="22"/>
+      <c r="W75" s="22"/>
+      <c r="X75" s="22"/>
+      <c r="Y75" s="22"/>
+      <c r="Z75" s="22"/>
+      <c r="AA75" s="22"/>
+      <c r="AB75" s="22"/>
+      <c r="AC75" s="22"/>
+      <c r="AD75" s="22"/>
+      <c r="AE75" s="22"/>
+      <c r="AF75" s="22"/>
+      <c r="AG75" s="22"/>
+      <c r="AH75" s="22"/>
+      <c r="AI75" s="22"/>
+      <c r="AJ75" s="22"/>
+      <c r="AK75" s="22"/>
+    </row>
+    <row r="76" spans="20:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T76" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="U76" s="21"/>
+      <c r="V76" s="21"/>
+      <c r="W76" s="21"/>
+      <c r="X76" s="21"/>
+      <c r="Y76" s="21"/>
+      <c r="Z76" s="21"/>
+      <c r="AA76" s="21"/>
+      <c r="AB76" s="21"/>
+      <c r="AC76" s="21"/>
+      <c r="AD76" s="21"/>
+      <c r="AE76" s="21"/>
+      <c r="AF76" s="21"/>
+      <c r="AG76" s="21"/>
+      <c r="AH76" s="21"/>
+      <c r="AI76" s="21"/>
+      <c r="AJ76" s="21"/>
+      <c r="AK76" s="21"/>
+    </row>
+    <row r="77" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T77" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="66" spans="20:37" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="T66" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="U66" s="43"/>
-      <c r="V66" s="43"/>
-      <c r="W66" s="43"/>
-      <c r="X66" s="43"/>
-      <c r="Y66" s="43"/>
-      <c r="Z66" s="43"/>
-      <c r="AA66" s="43"/>
-      <c r="AB66" s="43"/>
-      <c r="AC66" s="43"/>
-      <c r="AD66" s="43"/>
-      <c r="AE66" s="43"/>
-      <c r="AF66" s="43"/>
-      <c r="AG66" s="43"/>
-      <c r="AH66" s="43"/>
-      <c r="AI66" s="43"/>
-      <c r="AJ66" s="43"/>
-      <c r="AK66" s="43"/>
-    </row>
-    <row r="67" spans="20:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T67" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="U67" s="39"/>
-      <c r="V67" s="39"/>
-      <c r="W67" s="39"/>
-      <c r="X67" s="39"/>
-      <c r="Y67" s="39"/>
-      <c r="Z67" s="39"/>
-      <c r="AA67" s="39"/>
-      <c r="AB67" s="39"/>
-      <c r="AC67" s="39"/>
-      <c r="AD67" s="39"/>
-      <c r="AE67" s="39"/>
-      <c r="AF67" s="39"/>
-      <c r="AG67" s="39"/>
-      <c r="AH67" s="39"/>
-      <c r="AI67" s="39"/>
-      <c r="AJ67" s="39"/>
-      <c r="AK67" s="39"/>
-    </row>
-    <row r="68" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T68" s="12" t="s">
-        <v>88</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="T59:AK59"/>
-    <mergeCell ref="T63:AK63"/>
-    <mergeCell ref="T64:AK64"/>
-    <mergeCell ref="T66:AK66"/>
-    <mergeCell ref="T67:AK67"/>
+  <mergeCells count="20">
     <mergeCell ref="N6:Y6"/>
     <mergeCell ref="T44:AI44"/>
     <mergeCell ref="T41:AG41"/>
     <mergeCell ref="T38:AK38"/>
-    <mergeCell ref="T58:AK58"/>
+    <mergeCell ref="T66:AK66"/>
     <mergeCell ref="B44:R44"/>
     <mergeCell ref="T25:AF25"/>
     <mergeCell ref="T23:AF23"/>
@@ -3761,7 +4200,13 @@
     <mergeCell ref="N10:AD10"/>
     <mergeCell ref="T27:AF27"/>
     <mergeCell ref="B18:AB18"/>
-    <mergeCell ref="T56:AK56"/>
+    <mergeCell ref="T64:AK64"/>
+    <mergeCell ref="B59:R59"/>
+    <mergeCell ref="T70:AK70"/>
+    <mergeCell ref="T72:AK72"/>
+    <mergeCell ref="T73:AK73"/>
+    <mergeCell ref="T75:AK75"/>
+    <mergeCell ref="T76:AK76"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -3774,9 +4219,15 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="1:1" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3786,9 +4237,1084 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A2:X26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="1:24" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B4" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="40"/>
+      <c r="D4" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="53"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="40"/>
+      <c r="T4" s="40"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="40"/>
+      <c r="W4" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="X4" s="40"/>
+    </row>
+    <row r="5" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="50">
+        <v>1</v>
+      </c>
+      <c r="C5" s="50"/>
+      <c r="D5" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="56"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="H5" s="61"/>
+      <c r="I5" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="J5" s="51"/>
+      <c r="K5" s="64" t="s">
+        <v>127</v>
+      </c>
+      <c r="L5" s="64"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="O5" s="63"/>
+      <c r="P5" s="63"/>
+      <c r="Q5" s="63"/>
+      <c r="R5" s="63"/>
+      <c r="S5" s="63"/>
+      <c r="T5" s="63"/>
+      <c r="U5" s="63"/>
+      <c r="V5" s="63"/>
+      <c r="W5" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X5" s="64"/>
+    </row>
+    <row r="6" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B6" s="50">
+        <v>2</v>
+      </c>
+      <c r="C6" s="50"/>
+      <c r="D6" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="E6" s="56"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="H6" s="62"/>
+      <c r="I6" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="J6" s="51"/>
+      <c r="K6" s="64" t="s">
+        <v>127</v>
+      </c>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="O6" s="63"/>
+      <c r="P6" s="63"/>
+      <c r="Q6" s="63"/>
+      <c r="R6" s="63"/>
+      <c r="S6" s="63"/>
+      <c r="T6" s="63"/>
+      <c r="U6" s="63"/>
+      <c r="V6" s="63"/>
+      <c r="W6" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X6" s="64"/>
+    </row>
+    <row r="7" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="50">
+        <v>3</v>
+      </c>
+      <c r="C7" s="50"/>
+      <c r="D7" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="56"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="H7" s="61"/>
+      <c r="I7" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="J7" s="51"/>
+      <c r="K7" s="64" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="O7" s="63"/>
+      <c r="P7" s="63"/>
+      <c r="Q7" s="63"/>
+      <c r="R7" s="63"/>
+      <c r="S7" s="63"/>
+      <c r="T7" s="63"/>
+      <c r="U7" s="63"/>
+      <c r="V7" s="63"/>
+      <c r="W7" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X7" s="64"/>
+    </row>
+    <row r="8" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="50">
+        <v>4</v>
+      </c>
+      <c r="C8" s="50"/>
+      <c r="D8" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="56"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="H8" s="61"/>
+      <c r="I8" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="J8" s="51"/>
+      <c r="K8" s="64" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="64"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="O8" s="63"/>
+      <c r="P8" s="63"/>
+      <c r="Q8" s="63"/>
+      <c r="R8" s="63"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="63"/>
+      <c r="U8" s="63"/>
+      <c r="V8" s="63"/>
+      <c r="W8" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X8" s="64"/>
+    </row>
+    <row r="9" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="50">
+        <v>5</v>
+      </c>
+      <c r="C9" s="50"/>
+      <c r="D9" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="56"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="H9" s="61"/>
+      <c r="I9" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="J9" s="51"/>
+      <c r="K9" s="64" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="64"/>
+      <c r="M9" s="64"/>
+      <c r="N9" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="O9" s="63"/>
+      <c r="P9" s="63"/>
+      <c r="Q9" s="63"/>
+      <c r="R9" s="63"/>
+      <c r="S9" s="63"/>
+      <c r="T9" s="63"/>
+      <c r="U9" s="63"/>
+      <c r="V9" s="63"/>
+      <c r="W9" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X9" s="64"/>
+    </row>
+    <row r="10" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="50">
+        <v>6</v>
+      </c>
+      <c r="C10" s="50"/>
+      <c r="D10" s="55" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="56"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="H10" s="61"/>
+      <c r="I10" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="J10" s="51"/>
+      <c r="K10" s="64" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="64"/>
+      <c r="M10" s="64"/>
+      <c r="N10" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="O10" s="63"/>
+      <c r="P10" s="63"/>
+      <c r="Q10" s="63"/>
+      <c r="R10" s="63"/>
+      <c r="S10" s="63"/>
+      <c r="T10" s="63"/>
+      <c r="U10" s="63"/>
+      <c r="V10" s="63"/>
+      <c r="W10" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X10" s="64"/>
+    </row>
+    <row r="11" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="50">
+        <v>7</v>
+      </c>
+      <c r="C11" s="50"/>
+      <c r="D11" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="56"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="H11" s="61"/>
+      <c r="I11" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="J11" s="51"/>
+      <c r="K11" s="64" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="64"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="O11" s="63"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="63"/>
+      <c r="R11" s="63"/>
+      <c r="S11" s="63"/>
+      <c r="T11" s="63"/>
+      <c r="U11" s="63"/>
+      <c r="V11" s="63"/>
+      <c r="W11" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X11" s="64"/>
+    </row>
+    <row r="12" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="50">
+        <v>8</v>
+      </c>
+      <c r="C12" s="50"/>
+      <c r="D12" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" s="59"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="H12" s="61"/>
+      <c r="I12" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="J12" s="51"/>
+      <c r="K12" s="64" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="64"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="63" t="s">
+        <v>120</v>
+      </c>
+      <c r="O12" s="63"/>
+      <c r="P12" s="63"/>
+      <c r="Q12" s="63"/>
+      <c r="R12" s="63"/>
+      <c r="S12" s="63"/>
+      <c r="T12" s="63"/>
+      <c r="U12" s="63"/>
+      <c r="V12" s="63"/>
+      <c r="W12" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X12" s="64"/>
+    </row>
+    <row r="13" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="50">
+        <v>9</v>
+      </c>
+      <c r="C13" s="50"/>
+      <c r="D13" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="56"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="H13" s="61"/>
+      <c r="I13" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="J13" s="51"/>
+      <c r="K13" s="64" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="64"/>
+      <c r="M13" s="64"/>
+      <c r="N13" s="63" t="s">
+        <v>120</v>
+      </c>
+      <c r="O13" s="63"/>
+      <c r="P13" s="63"/>
+      <c r="Q13" s="63"/>
+      <c r="R13" s="63"/>
+      <c r="S13" s="63"/>
+      <c r="T13" s="63"/>
+      <c r="U13" s="63"/>
+      <c r="V13" s="63"/>
+      <c r="W13" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X13" s="64"/>
+    </row>
+    <row r="14" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="50">
+        <v>10</v>
+      </c>
+      <c r="C14" s="50"/>
+      <c r="D14" s="55" t="s">
+        <v>130</v>
+      </c>
+      <c r="E14" s="56"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="H14" s="62"/>
+      <c r="I14" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="J14" s="51"/>
+      <c r="K14" s="64" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="64"/>
+      <c r="M14" s="64"/>
+      <c r="N14" s="63" t="s">
+        <v>131</v>
+      </c>
+      <c r="O14" s="63"/>
+      <c r="P14" s="63"/>
+      <c r="Q14" s="63"/>
+      <c r="R14" s="63"/>
+      <c r="S14" s="63"/>
+      <c r="T14" s="63"/>
+      <c r="U14" s="63"/>
+      <c r="V14" s="63"/>
+      <c r="W14" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X14" s="64"/>
+    </row>
+    <row r="15" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="50">
+        <v>11</v>
+      </c>
+      <c r="C15" s="50"/>
+      <c r="D15" s="55" t="s">
+        <v>128</v>
+      </c>
+      <c r="E15" s="56"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="H15" s="62"/>
+      <c r="I15" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="J15" s="51"/>
+      <c r="K15" s="64" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="64"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="63" t="s">
+        <v>132</v>
+      </c>
+      <c r="O15" s="63"/>
+      <c r="P15" s="63"/>
+      <c r="Q15" s="63"/>
+      <c r="R15" s="63"/>
+      <c r="S15" s="63"/>
+      <c r="T15" s="63"/>
+      <c r="U15" s="63"/>
+      <c r="V15" s="63"/>
+      <c r="W15" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X15" s="64"/>
+    </row>
+    <row r="16" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="50">
+        <v>12</v>
+      </c>
+      <c r="C16" s="50"/>
+      <c r="D16" s="55" t="s">
+        <v>129</v>
+      </c>
+      <c r="E16" s="56"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="H16" s="62"/>
+      <c r="I16" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="J16" s="51"/>
+      <c r="K16" s="64" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="64"/>
+      <c r="M16" s="64"/>
+      <c r="N16" s="63" t="s">
+        <v>132</v>
+      </c>
+      <c r="O16" s="63"/>
+      <c r="P16" s="63"/>
+      <c r="Q16" s="63"/>
+      <c r="R16" s="63"/>
+      <c r="S16" s="63"/>
+      <c r="T16" s="63"/>
+      <c r="U16" s="63"/>
+      <c r="V16" s="63"/>
+      <c r="W16" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X16" s="64"/>
+    </row>
+    <row r="17" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B17" s="50">
+        <v>13</v>
+      </c>
+      <c r="C17" s="50"/>
+      <c r="D17" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" s="56"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="62"/>
+      <c r="I17" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="65"/>
+      <c r="K17" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="L17" s="64"/>
+      <c r="M17" s="64"/>
+      <c r="N17" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="O17" s="63"/>
+      <c r="P17" s="63"/>
+      <c r="Q17" s="63"/>
+      <c r="R17" s="63"/>
+      <c r="S17" s="63"/>
+      <c r="T17" s="63"/>
+      <c r="U17" s="63"/>
+      <c r="V17" s="63"/>
+      <c r="W17" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X17" s="64"/>
+    </row>
+    <row r="18" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B18" s="50">
+        <v>14</v>
+      </c>
+      <c r="C18" s="50"/>
+      <c r="D18" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="E18" s="56"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" s="62"/>
+      <c r="I18" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="65"/>
+      <c r="K18" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="L18" s="64"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="O18" s="63"/>
+      <c r="P18" s="63"/>
+      <c r="Q18" s="63"/>
+      <c r="R18" s="63"/>
+      <c r="S18" s="63"/>
+      <c r="T18" s="63"/>
+      <c r="U18" s="63"/>
+      <c r="V18" s="63"/>
+      <c r="W18" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X18" s="64"/>
+    </row>
+    <row r="19" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B19" s="50">
+        <v>15</v>
+      </c>
+      <c r="C19" s="50"/>
+      <c r="D19" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="E19" s="56"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="H19" s="62"/>
+      <c r="I19" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="65"/>
+      <c r="K19" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="L19" s="64"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="O19" s="63"/>
+      <c r="P19" s="63"/>
+      <c r="Q19" s="63"/>
+      <c r="R19" s="63"/>
+      <c r="S19" s="63"/>
+      <c r="T19" s="63"/>
+      <c r="U19" s="63"/>
+      <c r="V19" s="63"/>
+      <c r="W19" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X19" s="64"/>
+    </row>
+    <row r="20" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B20" s="50">
+        <v>16</v>
+      </c>
+      <c r="C20" s="50"/>
+      <c r="D20" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" s="56"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="62"/>
+      <c r="I20" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="65"/>
+      <c r="K20" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="L20" s="64"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="O20" s="63"/>
+      <c r="P20" s="63"/>
+      <c r="Q20" s="63"/>
+      <c r="R20" s="63"/>
+      <c r="S20" s="63"/>
+      <c r="T20" s="63"/>
+      <c r="U20" s="63"/>
+      <c r="V20" s="63"/>
+      <c r="W20" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X20" s="64"/>
+    </row>
+    <row r="21" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B21" s="50">
+        <v>17</v>
+      </c>
+      <c r="C21" s="50"/>
+      <c r="D21" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21" s="56"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="H21" s="62"/>
+      <c r="I21" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="65"/>
+      <c r="K21" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="L21" s="64"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="O21" s="63"/>
+      <c r="P21" s="63"/>
+      <c r="Q21" s="63"/>
+      <c r="R21" s="63"/>
+      <c r="S21" s="63"/>
+      <c r="T21" s="63"/>
+      <c r="U21" s="63"/>
+      <c r="V21" s="63"/>
+      <c r="W21" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X21" s="64"/>
+    </row>
+    <row r="22" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B22" s="50">
+        <v>18</v>
+      </c>
+      <c r="C22" s="50"/>
+      <c r="D22" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22" s="56"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="H22" s="62"/>
+      <c r="I22" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="65"/>
+      <c r="K22" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="L22" s="64"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="O22" s="63"/>
+      <c r="P22" s="63"/>
+      <c r="Q22" s="63"/>
+      <c r="R22" s="63"/>
+      <c r="S22" s="63"/>
+      <c r="T22" s="63"/>
+      <c r="U22" s="63"/>
+      <c r="V22" s="63"/>
+      <c r="W22" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X22" s="64"/>
+    </row>
+    <row r="23" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B23" s="50">
+        <v>19</v>
+      </c>
+      <c r="C23" s="50"/>
+      <c r="D23" s="55" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" s="56"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="H23" s="62"/>
+      <c r="I23" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="65"/>
+      <c r="K23" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="L23" s="64"/>
+      <c r="M23" s="64"/>
+      <c r="N23" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="O23" s="63"/>
+      <c r="P23" s="63"/>
+      <c r="Q23" s="63"/>
+      <c r="R23" s="63"/>
+      <c r="S23" s="63"/>
+      <c r="T23" s="63"/>
+      <c r="U23" s="63"/>
+      <c r="V23" s="63"/>
+      <c r="W23" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X23" s="64"/>
+    </row>
+    <row r="24" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B24" s="50">
+        <v>20</v>
+      </c>
+      <c r="C24" s="50"/>
+      <c r="D24" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" s="56"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="H24" s="62"/>
+      <c r="I24" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="65"/>
+      <c r="K24" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="L24" s="64"/>
+      <c r="M24" s="64"/>
+      <c r="N24" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="O24" s="63"/>
+      <c r="P24" s="63"/>
+      <c r="Q24" s="63"/>
+      <c r="R24" s="63"/>
+      <c r="S24" s="63"/>
+      <c r="T24" s="63"/>
+      <c r="U24" s="63"/>
+      <c r="V24" s="63"/>
+      <c r="W24" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X24" s="64"/>
+    </row>
+    <row r="25" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B25" s="50">
+        <v>21</v>
+      </c>
+      <c r="C25" s="50"/>
+      <c r="D25" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="E25" s="56"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="H25" s="62"/>
+      <c r="I25" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="65"/>
+      <c r="K25" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="L25" s="64"/>
+      <c r="M25" s="64"/>
+      <c r="N25" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="O25" s="63"/>
+      <c r="P25" s="63"/>
+      <c r="Q25" s="63"/>
+      <c r="R25" s="63"/>
+      <c r="S25" s="63"/>
+      <c r="T25" s="63"/>
+      <c r="U25" s="63"/>
+      <c r="V25" s="63"/>
+      <c r="W25" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X25" s="64"/>
+    </row>
+    <row r="26" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B26" s="50">
+        <v>22</v>
+      </c>
+      <c r="C26" s="50"/>
+      <c r="D26" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26" s="56"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="H26" s="62"/>
+      <c r="I26" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="65"/>
+      <c r="K26" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="L26" s="64"/>
+      <c r="M26" s="64"/>
+      <c r="N26" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="O26" s="63"/>
+      <c r="P26" s="63"/>
+      <c r="Q26" s="63"/>
+      <c r="R26" s="63"/>
+      <c r="S26" s="63"/>
+      <c r="T26" s="63"/>
+      <c r="U26" s="63"/>
+      <c r="V26" s="63"/>
+      <c r="W26" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="X26" s="64"/>
+    </row>
+  </sheetData>
+  <mergeCells count="161">
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="W26:X26"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="W20:X20"/>
+    <mergeCell ref="W21:X21"/>
+    <mergeCell ref="W22:X22"/>
+    <mergeCell ref="W23:X23"/>
+    <mergeCell ref="W24:X24"/>
+    <mergeCell ref="W10:X10"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="W7:X7"/>
+    <mergeCell ref="W8:X8"/>
+    <mergeCell ref="W9:X9"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="N16:V16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="N15:V15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="N14:V14"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="N6:V6"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="N26:V26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="N25:V25"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="N20:V20"/>
+    <mergeCell ref="N21:V21"/>
+    <mergeCell ref="N22:V22"/>
+    <mergeCell ref="N23:V23"/>
+    <mergeCell ref="N24:V24"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N4:V4"/>
+    <mergeCell ref="N5:V5"/>
+    <mergeCell ref="N7:V7"/>
+    <mergeCell ref="N8:V8"/>
+    <mergeCell ref="N9:V9"/>
+    <mergeCell ref="N10:V10"/>
+    <mergeCell ref="N11:V11"/>
+    <mergeCell ref="N12:V12"/>
+    <mergeCell ref="N13:V13"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="W18:X18"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="N17:V17"/>
+    <mergeCell ref="N18:V18"/>
+    <mergeCell ref="N19:V19"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="D4:F4"/>
+  </mergeCells>
+  <phoneticPr fontId="14" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:J26" xr:uid="{EBCDB7CB-9B76-4496-A9FD-E13B8548471C}">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W5:X26" xr:uid="{B5CE3419-EDB4-4E48-ADC1-5B4DD80F50CD}">
+      <formula1>"Đã có, Chưa, Bỏ, Cân nhắc"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3798,9 +5324,15 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="1:1" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91DD172-953D-452E-A114-6CBB99C62268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0699A0-8558-48E9-A533-A6E0D3122C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="184">
   <si>
     <t>SIGNOMALY</t>
   </si>
@@ -336,12 +336,6 @@
     <t>II. CORELOOP_WIN/LOSE CONDITIONS</t>
   </si>
   <si>
-    <t>III. TỔNG QUAN CÁC MODULE VÀ TÍNH NĂNG</t>
-  </si>
-  <si>
-    <t>IV. CHI TIẾT</t>
-  </si>
-  <si>
     <t>Độ phù hợp với theme:</t>
   </si>
   <si>
@@ -788,12 +782,6 @@
     </r>
   </si>
   <si>
-    <t>1. Map (For Blockout)</t>
-  </si>
-  <si>
-    <t>2. Puzzle (Main Mechanics)</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Puzzle giải đố sẽ </t>
     </r>
@@ -1399,12 +1387,6 @@
     <t>V. SCENES</t>
   </si>
   <si>
-    <t>VI. Item lists</t>
-  </si>
-  <si>
-    <t>VII. NPC</t>
-  </si>
-  <si>
     <t>Key item No</t>
   </si>
   <si>
@@ -1436,13 +1418,459 @@
   </si>
   <si>
     <t>Đã có Assets?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cần có Title game, các button như: New Game +, Options, Exit. Và được thiết kế layout tương tự như 2 hình mẫu. Với việc khung lựa chọn + Logo ở bên trái và illustration đại diện nằm bên phải. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Deep background: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#08090D</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">UI Surface: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#111118</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Secondary panels: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#2A2B3D</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inactive / borders: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#3D3E52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Primary text: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#D4D4E0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Secondary text: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#6B6B7A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Signal Active: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#24FF74</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Main accent / CRT glow</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Warnings / alerts: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#F5A623</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Danger / threat (Anomaly): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#E8263C</t>
+    </r>
+  </si>
+  <si>
+    <t>COLOR PALLETE</t>
+  </si>
+  <si>
+    <t>TYPOGRAPHY</t>
+  </si>
+  <si>
+    <t>Titles · UI headers · Terminal readouts · Game Over screen</t>
+  </si>
+  <si>
+    <t>USE FOR</t>
+  </si>
+  <si>
+    <t>VT323</t>
+  </si>
+  <si>
+    <t>Share Tech Mono</t>
+  </si>
+  <si>
+    <t>HUD labels · Subtitles · Button text · Status indicators</t>
+  </si>
+  <si>
+    <t>IBM Plex Mono</t>
+  </si>
+  <si>
+    <t>Log entries · Descriptions · Tooltips · Small text</t>
+  </si>
+  <si>
+    <t>(IN PREVIEW)</t>
+  </si>
+  <si>
+    <t>Option screen: cần có overall quality (với menu thả xuống để lựa chọn), Audio (on/off), nút back để quay về.</t>
+  </si>
+  <si>
+    <t>2. SCREEN</t>
+  </si>
+  <si>
+    <t>1. MAP (BLOCKOUT)</t>
+  </si>
+  <si>
+    <t>2. PUZZLE (MAIN MECHANICS)</t>
+  </si>
+  <si>
+    <t>1. DESIGN STYLE</t>
+  </si>
+  <si>
+    <t>2.3. IN-GAME</t>
+  </si>
+  <si>
+    <t>- Với mốc A: Tinh chỉnh hex màu tường (sàn, trần) từ màu của texture dần sang màu đỏ thẩm; Saturation: +7%</t>
+  </si>
+  <si>
+    <t>- Với mốc B: Tinh chỉnh hex màu tường (sàn, trần) từ màu của texture càng dần sang màu đỏ thẩm; Saturation: +12%</t>
+  </si>
+  <si>
+    <t>- Với mốc C: Tinh chỉnh hex màu tường (sàn, trần) từ màu của texture thành màu đỏ thẩm; Saturation: +17%</t>
+  </si>
+  <si>
+    <t>2.3.1. Biến đổi môi trường</t>
+  </si>
+  <si>
+    <t>2.3.2. Biến đổi Puzzle</t>
+  </si>
+  <si>
+    <t>Model Puzzle sẽ gồm 2 biến thể (A và B), trong đó: biến thể A là object ở trạng thái bình thường, biến thể B là object ở trạng thái Anomaly.</t>
+  </si>
+  <si>
+    <t>Thiết lập model Puzzle sẽ tự động chuyển A sang B với cooldown là 15-20 giây (random), và duration là 7 giây, sau đó sẽ quay trở lại biến thể A và lặp lại.</t>
+  </si>
+  <si>
+    <t>Khi puzzle giải đố được kích hoạt và người chơi nhấn giữ phím "E" thì sẽ luôn giữ ở dạng biến thể A. Sau khi hoàn thành nhấn giữ sẽ chuyển hoàn toàn sang biến thể B (Optional)</t>
+  </si>
+  <si>
+    <r>
+      <t>Mốc thời gian chính (Timelapse):</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 15 phút</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Chia ra 3 mốc thời gian như sau: A=B=C= 5 phút.</t>
+    </r>
+  </si>
+  <si>
+    <t>2.1. Menu Screen UI</t>
+  </si>
+  <si>
+    <t>2.2. Option Screen UI</t>
+  </si>
+  <si>
+    <t>III. MODULES AND FEATURES</t>
+  </si>
+  <si>
+    <t>IV. DETAILS</t>
+  </si>
+  <si>
+    <t>1. Game Movement</t>
+  </si>
+  <si>
+    <t>VI. GAME FEATURES</t>
+  </si>
+  <si>
+    <t>2. Game Interaction</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Người chơi có thể </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>nhấn giữ E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> khi phát hiện Puzzle để thực hiện câu đố.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Người chơi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>nhấn E để tương tác</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">; Người chơi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>nhấn Q để huỷ bỏ đồ vật đang cầm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> trên tay.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Người chơi sẽ tương tác với vật thể object như sau: Với</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> X là đồ vật trang trí sẽ có object tương tác được và không tương tác được</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Dựa vào Item List); </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Y: luôn cầm được</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (nó sẽ hiển thị icon chìa khoá ở top).</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Blink </t>
+  </si>
+  <si>
+    <t>Khi vừa vào game người chơi sẽ thấy màn hình đang chớp mắt (1-2 lần), từ mờ thành rõ ràng.</t>
+  </si>
+  <si>
+    <t>4. NPC</t>
+  </si>
+  <si>
+    <t>VII. Item lists</t>
+  </si>
+  <si>
+    <t>VIII. DIALOUGES</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Người chơi sẽ di chuyển bằng phím </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>"WASD"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Tốc độ khi di chuyển của người chơi sẽ nhanh vừa phải. Người chơi</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> không thể chạy, nhảy.</t>
+    </r>
+  </si>
+  <si>
+    <t>Dialogues!A1</t>
+  </si>
+  <si>
+    <t>Đối thoại với NPC để hiểu cơ chế chơi. Đoạn đối thoại có thể xem bên tab</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1536,6 +1964,38 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF3D3E52"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color theme="2" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="15"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1618,10 +2078,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1802,8 +2263,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2356,6 +2842,343 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>42625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>380999</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="RAIE HORROR GAME UI CONCEPT by Max Mezhuev on Dribbble">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AFAAF28-75C4-0E58-771D-F8CBDC1E6FB1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="619124" y="9910525"/>
+          <a:ext cx="7077075" cy="4777025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>134937</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>102753</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2" descr="Horror game menu (AAA) | 2D GUI | Unity Asset Store">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9B52FEB-ACE9-7D1D-BBD9-10FD89119284}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8059737" y="9867900"/>
+          <a:ext cx="8637588" cy="4865253"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>226817</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FED384E5-D203-7D0C-FA40-EE02FBEAF3EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="590550" y="1123950"/>
+          <a:ext cx="5734050" cy="6608567"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>60305</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>9954</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA05A0CB-CB0B-CD6B-9A09-AECDEFD8F07E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13268325" y="1266825"/>
+          <a:ext cx="8737580" cy="3181779"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>9526</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>133946</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5" descr="ArtStation - Horror Game UI">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79F76535-EC52-833D-472E-FE41EC62B728}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="638175" y="15763876"/>
+          <a:ext cx="8010525" cy="4505920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>131564</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6" descr="Horror Game UI Kit">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F70FF70F-0206-4E05-6FE3-0ED3E2707C9E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9144000" y="15754350"/>
+          <a:ext cx="7600950" cy="4513064"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2827,7 +3650,7 @@
     </row>
     <row r="15" spans="1:26" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C15" s="34"/>
       <c r="D15" s="34"/>
@@ -2928,7 +3751,7 @@
     </row>
     <row r="19" spans="1:21" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B19" s="31" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C19" s="31"/>
       <c r="D19" s="31"/>
@@ -3018,7 +3841,7 @@
     </row>
     <row r="29" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B29" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -3087,7 +3910,7 @@
   <sheetData>
     <row r="2" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>41</v>
+        <v>167</v>
       </c>
       <c r="B2" s="8"/>
     </row>
@@ -3148,7 +3971,7 @@
       <c r="K5" s="41"/>
       <c r="L5" s="41"/>
       <c r="M5" s="46" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N5" s="46"/>
       <c r="O5" s="46"/>
@@ -3182,7 +4005,7 @@
       <c r="K6" s="41"/>
       <c r="L6" s="41"/>
       <c r="M6" s="47" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="N6" s="46"/>
       <c r="O6" s="46"/>
@@ -3208,7 +4031,7 @@
       </c>
       <c r="F7" s="39"/>
       <c r="G7" s="41" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H7" s="41"/>
       <c r="I7" s="41"/>
@@ -3216,7 +4039,7 @@
       <c r="K7" s="41"/>
       <c r="L7" s="41"/>
       <c r="M7" s="44" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N7" s="44"/>
       <c r="O7" s="44"/>
@@ -3252,7 +4075,7 @@
       <c r="K8" s="41"/>
       <c r="L8" s="41"/>
       <c r="M8" s="43" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N8" s="44"/>
       <c r="O8" s="44"/>
@@ -3286,7 +4109,7 @@
       <c r="K9" s="41"/>
       <c r="L9" s="41"/>
       <c r="M9" s="43" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N9" s="44"/>
       <c r="O9" s="44"/>
@@ -3320,7 +4143,7 @@
       <c r="K10" s="41"/>
       <c r="L10" s="41"/>
       <c r="M10" s="43" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N10" s="44"/>
       <c r="O10" s="44"/>
@@ -3354,7 +4177,7 @@
       <c r="K11" s="41"/>
       <c r="L11" s="41"/>
       <c r="M11" s="44" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N11" s="44"/>
       <c r="O11" s="44"/>
@@ -3390,7 +4213,7 @@
       <c r="K12" s="41"/>
       <c r="L12" s="41"/>
       <c r="M12" s="44" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N12" s="44"/>
       <c r="O12" s="44"/>
@@ -3408,7 +4231,7 @@
     <row r="46" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B56" s="45" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C56" s="45"/>
       <c r="D56" s="45"/>
@@ -3489,17 +4312,17 @@
   <sheetData>
     <row r="2" spans="1:30" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>78</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="19.5" x14ac:dyDescent="0.25">
       <c r="N6" s="23" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="O6" s="23"/>
       <c r="P6" s="23"/>
@@ -3529,7 +4352,7 @@
     </row>
     <row r="8" spans="1:30" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N8" s="25" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="O8" s="25"/>
       <c r="P8" s="25"/>
@@ -3564,7 +4387,7 @@
     </row>
     <row r="10" spans="1:30" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N10" s="25" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="O10" s="28"/>
       <c r="P10" s="28"/>
@@ -3588,7 +4411,7 @@
     </row>
     <row r="16" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B16" s="8" t="s">
-        <v>79</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
@@ -3596,7 +4419,7 @@
     </row>
     <row r="18" spans="2:33" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="29" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C18" s="30"/>
       <c r="D18" s="30"/>
@@ -3653,13 +4476,13 @@
     </row>
     <row r="21" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C21" s="10"/>
     </row>
     <row r="23" spans="2:33" ht="19.5" x14ac:dyDescent="0.25">
       <c r="T23" s="24" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="U23" s="24"/>
       <c r="V23" s="24"/>
@@ -3679,7 +4502,7 @@
     </row>
     <row r="25" spans="2:33" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T25" s="20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="U25" s="21"/>
       <c r="V25" s="21"/>
@@ -3713,7 +4536,7 @@
     </row>
     <row r="27" spans="2:33" ht="19.5" x14ac:dyDescent="0.25">
       <c r="T27" s="24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="U27" s="24"/>
       <c r="V27" s="24"/>
@@ -3733,12 +4556,12 @@
     </row>
     <row r="29" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T29" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T30" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
@@ -3746,7 +4569,7 @@
     </row>
     <row r="32" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T32" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="U32" s="8"/>
       <c r="V32" s="8"/>
@@ -3756,7 +4579,7 @@
     </row>
     <row r="34" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T34" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U34" s="12"/>
       <c r="V34" s="12"/>
@@ -3773,7 +4596,7 @@
     </row>
     <row r="35" spans="2:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T35" s="25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="U35" s="25"/>
       <c r="V35" s="25"/>
@@ -3790,7 +4613,7 @@
     </row>
     <row r="37" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T37" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="U37" s="12"/>
       <c r="V37" s="12"/>
@@ -3807,7 +4630,7 @@
     </row>
     <row r="38" spans="2:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T38" s="25" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="U38" s="25"/>
       <c r="V38" s="25"/>
@@ -3829,17 +4652,17 @@
     </row>
     <row r="39" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T39" s="12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T40" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="2:37" ht="19.5" x14ac:dyDescent="0.25">
       <c r="T41" s="24" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="U41" s="24"/>
       <c r="V41" s="24"/>
@@ -3857,17 +4680,17 @@
     </row>
     <row r="42" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T42" s="12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T43" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B44" s="26" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C44" s="27"/>
       <c r="D44" s="27"/>
@@ -3886,7 +4709,7 @@
       <c r="Q44" s="27"/>
       <c r="R44" s="27"/>
       <c r="T44" s="24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="U44" s="24"/>
       <c r="V44" s="24"/>
@@ -3906,37 +4729,37 @@
     </row>
     <row r="45" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T45" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T46" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T47" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T48" s="12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T49" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="50" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T50" s="12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="51" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T51" s="12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
@@ -3962,7 +4785,7 @@
     </row>
     <row r="59" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B59" s="49" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C59" s="27"/>
       <c r="D59" s="27"/>
@@ -3990,12 +4813,12 @@
     </row>
     <row r="62" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B62" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="64" spans="2:37" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T64" s="20" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="U64" s="21"/>
       <c r="V64" s="21"/>
@@ -4017,7 +4840,7 @@
     </row>
     <row r="66" spans="20:37" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T66" s="20" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="U66" s="21"/>
       <c r="V66" s="21"/>
@@ -4039,7 +4862,7 @@
     </row>
     <row r="68" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T68" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
@@ -4047,7 +4870,7 @@
     </row>
     <row r="70" spans="20:37" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T70" s="48" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="U70" s="21"/>
       <c r="V70" s="21"/>
@@ -4089,7 +4912,7 @@
     </row>
     <row r="72" spans="20:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T72" s="22" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="U72" s="22"/>
       <c r="V72" s="22"/>
@@ -4111,7 +4934,7 @@
     </row>
     <row r="73" spans="20:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T73" s="21" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="U73" s="21"/>
       <c r="V73" s="21"/>
@@ -4133,12 +4956,12 @@
     </row>
     <row r="74" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T74" s="12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="75" spans="20:37" ht="19.5" x14ac:dyDescent="0.25">
       <c r="T75" s="22" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="U75" s="22"/>
       <c r="V75" s="22"/>
@@ -4160,7 +4983,7 @@
     </row>
     <row r="76" spans="20:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T76" s="21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="U76" s="21"/>
       <c r="V76" s="21"/>
@@ -4182,7 +5005,7 @@
     </row>
     <row r="77" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T77" s="12" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -4219,16 +5042,478 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A2"/>
+  <dimension ref="A2:AJ128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:1" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>122</v>
-      </c>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A3" s="1"/>
+    </row>
+    <row r="4" spans="1:36" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="1"/>
+      <c r="B4" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+    </row>
+    <row r="5" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1"/>
+      <c r="L5" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
+      <c r="P5" s="42"/>
+    </row>
+    <row r="6" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="1"/>
+      <c r="L6" s="69" t="s">
+        <v>131</v>
+      </c>
+      <c r="M6" s="69"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
+      <c r="P6" s="69"/>
+    </row>
+    <row r="7" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="1"/>
+      <c r="L7" s="63" t="s">
+        <v>132</v>
+      </c>
+      <c r="M7" s="63"/>
+      <c r="N7" s="63"/>
+      <c r="O7" s="63"/>
+      <c r="P7" s="63"/>
+    </row>
+    <row r="8" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1"/>
+      <c r="L8" s="69" t="s">
+        <v>133</v>
+      </c>
+      <c r="M8" s="69"/>
+      <c r="N8" s="69"/>
+      <c r="O8" s="69"/>
+      <c r="P8" s="69"/>
+    </row>
+    <row r="9" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1"/>
+      <c r="L9" s="69" t="s">
+        <v>134</v>
+      </c>
+      <c r="M9" s="69"/>
+      <c r="N9" s="69"/>
+      <c r="O9" s="69"/>
+      <c r="P9" s="69"/>
+      <c r="R9" s="70"/>
+      <c r="S9" s="70"/>
+      <c r="T9" s="70"/>
+      <c r="U9" s="70"/>
+      <c r="V9" s="70"/>
+      <c r="W9" s="70"/>
+      <c r="X9" s="70"/>
+      <c r="Y9" s="70"/>
+      <c r="Z9" s="70"/>
+    </row>
+    <row r="10" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="1"/>
+      <c r="L10" s="63" t="s">
+        <v>135</v>
+      </c>
+      <c r="M10" s="63"/>
+      <c r="N10" s="63"/>
+      <c r="O10" s="63"/>
+      <c r="P10" s="63"/>
+      <c r="R10" s="70"/>
+      <c r="S10" s="70"/>
+      <c r="T10" s="70"/>
+      <c r="U10" s="70"/>
+      <c r="V10" s="70"/>
+      <c r="W10" s="70"/>
+      <c r="X10" s="70"/>
+      <c r="Y10" s="70"/>
+      <c r="Z10" s="70"/>
+    </row>
+    <row r="11" spans="1:36" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="1"/>
+      <c r="L11" s="63" t="s">
+        <v>136</v>
+      </c>
+      <c r="M11" s="69"/>
+      <c r="N11" s="69"/>
+      <c r="O11" s="69"/>
+      <c r="P11" s="69"/>
+      <c r="R11" s="70"/>
+      <c r="S11" s="70"/>
+      <c r="T11" s="70"/>
+      <c r="U11" s="70"/>
+      <c r="V11" s="70"/>
+      <c r="W11" s="70"/>
+      <c r="X11" s="70"/>
+      <c r="Y11" s="70"/>
+      <c r="Z11" s="70"/>
+    </row>
+    <row r="12" spans="1:36" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="1"/>
+      <c r="L12" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="M12" s="63"/>
+      <c r="N12" s="63"/>
+      <c r="O12" s="63"/>
+      <c r="P12" s="63"/>
+      <c r="R12" s="70"/>
+      <c r="S12" s="70"/>
+      <c r="T12" s="70"/>
+      <c r="U12" s="70"/>
+      <c r="V12" s="70"/>
+    </row>
+    <row r="13" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="1"/>
+      <c r="L13" s="69" t="s">
+        <v>138</v>
+      </c>
+      <c r="M13" s="69"/>
+      <c r="N13" s="69"/>
+      <c r="O13" s="69"/>
+      <c r="P13" s="69"/>
+      <c r="R13" s="70"/>
+      <c r="S13" s="70"/>
+      <c r="T13" s="70"/>
+      <c r="U13" s="70"/>
+      <c r="W13" s="73" t="s">
+        <v>149</v>
+      </c>
+      <c r="X13" s="73"/>
+      <c r="Y13" s="73"/>
+      <c r="Z13" s="73"/>
+      <c r="AA13" s="73"/>
+      <c r="AB13" s="73"/>
+      <c r="AC13" s="73"/>
+      <c r="AD13" s="73"/>
+      <c r="AE13" s="73"/>
+      <c r="AF13" s="73"/>
+      <c r="AG13" s="73"/>
+      <c r="AH13" s="73"/>
+      <c r="AI13" s="73"/>
+      <c r="AJ13" s="73"/>
+    </row>
+    <row r="14" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A14" s="1"/>
+      <c r="L14" s="69" t="s">
+        <v>139</v>
+      </c>
+      <c r="M14" s="69"/>
+      <c r="N14" s="69"/>
+      <c r="O14" s="69"/>
+      <c r="P14" s="69"/>
+      <c r="R14" s="70"/>
+      <c r="S14" s="70"/>
+      <c r="T14" s="70"/>
+      <c r="U14" s="70"/>
+      <c r="V14" s="70"/>
+      <c r="W14" s="70"/>
+      <c r="X14" s="70"/>
+      <c r="Y14" s="70"/>
+      <c r="Z14" s="70"/>
+    </row>
+    <row r="15" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A15" s="1"/>
+      <c r="R15" s="71"/>
+    </row>
+    <row r="16" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A16" s="1"/>
+    </row>
+    <row r="17" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A17" s="1"/>
+      <c r="L17" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="42"/>
+      <c r="R17" s="42"/>
+      <c r="S17" s="42"/>
+      <c r="T17" s="42"/>
+    </row>
+    <row r="18" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A18" s="1"/>
+      <c r="L18" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M18" s="38"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="72" t="s">
+        <v>142</v>
+      </c>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="72"/>
+      <c r="T18" s="72"/>
+    </row>
+    <row r="19" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A19" s="1"/>
+      <c r="L19" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="72" t="s">
+        <v>146</v>
+      </c>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="72"/>
+      <c r="T19" s="72"/>
+    </row>
+    <row r="20" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A20" s="1"/>
+      <c r="L20" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="72" t="s">
+        <v>148</v>
+      </c>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="72"/>
+      <c r="T20" s="72"/>
+    </row>
+    <row r="21" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A21" s="1"/>
+    </row>
+    <row r="22" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A23" s="1"/>
+      <c r="L23" s="68"/>
+      <c r="M23" s="68"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="67"/>
+      <c r="P23" s="67"/>
+    </row>
+    <row r="25" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B25" s="8" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B26" s="8"/>
+    </row>
+    <row r="27" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B27" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B56" s="66" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B57" s="66"/>
+    </row>
+    <row r="58" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B58" s="8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B85" s="66" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B87" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B88" s="8"/>
+    </row>
+    <row r="89" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B89" s="8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B91" s="66" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B93" s="74" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B94" s="74" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B95" s="74" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="97" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B97" s="8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="99" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B99" s="66" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="101" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B101" s="66" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="103" spans="2:25" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B103" s="75" t="s">
+        <v>163</v>
+      </c>
+      <c r="C103" s="75"/>
+      <c r="D103" s="75"/>
+      <c r="E103" s="75"/>
+      <c r="F103" s="75"/>
+      <c r="G103" s="75"/>
+      <c r="H103" s="75"/>
+      <c r="I103" s="75"/>
+      <c r="J103" s="75"/>
+      <c r="K103" s="75"/>
+      <c r="L103" s="75"/>
+      <c r="M103" s="75"/>
+      <c r="N103" s="75"/>
+      <c r="O103" s="75"/>
+      <c r="P103" s="75"/>
+      <c r="Q103" s="75"/>
+      <c r="R103" s="75"/>
+      <c r="S103" s="75"/>
+      <c r="T103" s="75"/>
+      <c r="U103" s="75"/>
+      <c r="V103" s="75"/>
+      <c r="W103" s="75"/>
+      <c r="X103" s="75"/>
+      <c r="Y103" s="75"/>
+    </row>
+    <row r="106" spans="2:25" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="B106" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="108" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B108" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C108" s="8"/>
+      <c r="D108" s="76"/>
+    </row>
+    <row r="110" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B110" s="66" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="111" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B111" s="66"/>
+    </row>
+    <row r="112" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B112" s="66" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="114" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B114" s="8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="116" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B116" s="66" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="118" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B118" s="66" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="120" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B120" s="66" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="122" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B122" s="8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="124" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B124" s="66" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="126" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B126" s="8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="128" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B128" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="L128" s="77" t="s">
+        <v>182</v>
+      </c>
+      <c r="M128" s="66"/>
     </row>
   </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="B103:Y103"/>
+    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="W13:AJ13"/>
+    <mergeCell ref="O17:T17"/>
+    <mergeCell ref="O19:T19"/>
+    <mergeCell ref="O20:T20"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="L11:P11"/>
+    <mergeCell ref="L12:P12"/>
+    <mergeCell ref="L13:P13"/>
+    <mergeCell ref="L14:P14"/>
+    <mergeCell ref="L5:P5"/>
+    <mergeCell ref="L6:P6"/>
+    <mergeCell ref="L7:P7"/>
+    <mergeCell ref="L8:P8"/>
+    <mergeCell ref="L9:P9"/>
+    <mergeCell ref="L10:P10"/>
+    <mergeCell ref="B4:F4"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="L128" location="Dialogues!A1" display="Dialogues!A1" xr:uid="{5724AB96-1B0F-4DFD-A35F-382AC93CCD96}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4242,16 +5527,16 @@
   <sheetData>
     <row r="2" spans="1:24" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>123</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="40" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C4" s="40"/>
       <c r="D4" s="52" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E4" s="53"/>
       <c r="F4" s="54"/>
@@ -4260,11 +5545,11 @@
       </c>
       <c r="H4" s="40"/>
       <c r="I4" s="40" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J4" s="40"/>
       <c r="K4" s="40" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L4" s="40"/>
       <c r="M4" s="40"/>
@@ -4280,7 +5565,7 @@
       <c r="U4" s="40"/>
       <c r="V4" s="40"/>
       <c r="W4" s="40" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="X4" s="40"/>
     </row>
@@ -4290,25 +5575,25 @@
       </c>
       <c r="C5" s="50"/>
       <c r="D5" s="55" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E5" s="56"/>
       <c r="F5" s="57"/>
       <c r="G5" s="61" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H5" s="61"/>
       <c r="I5" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J5" s="51"/>
       <c r="K5" s="64" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="L5" s="64"/>
       <c r="M5" s="64"/>
       <c r="N5" s="63" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="O5" s="63"/>
       <c r="P5" s="63"/>
@@ -4319,7 +5604,7 @@
       <c r="U5" s="63"/>
       <c r="V5" s="63"/>
       <c r="W5" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X5" s="64"/>
     </row>
@@ -4329,25 +5614,25 @@
       </c>
       <c r="C6" s="50"/>
       <c r="D6" s="55" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E6" s="56"/>
       <c r="F6" s="57"/>
       <c r="G6" s="62" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H6" s="62"/>
       <c r="I6" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J6" s="51"/>
       <c r="K6" s="64" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="L6" s="64"/>
       <c r="M6" s="64"/>
       <c r="N6" s="63" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
@@ -4358,7 +5643,7 @@
       <c r="U6" s="63"/>
       <c r="V6" s="63"/>
       <c r="W6" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X6" s="64"/>
     </row>
@@ -4368,16 +5653,16 @@
       </c>
       <c r="C7" s="50"/>
       <c r="D7" s="55" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E7" s="56"/>
       <c r="F7" s="57"/>
       <c r="G7" s="61" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H7" s="61"/>
       <c r="I7" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J7" s="51"/>
       <c r="K7" s="64" t="s">
@@ -4386,7 +5671,7 @@
       <c r="L7" s="64"/>
       <c r="M7" s="64"/>
       <c r="N7" s="63" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="O7" s="63"/>
       <c r="P7" s="63"/>
@@ -4397,7 +5682,7 @@
       <c r="U7" s="63"/>
       <c r="V7" s="63"/>
       <c r="W7" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X7" s="64"/>
     </row>
@@ -4407,16 +5692,16 @@
       </c>
       <c r="C8" s="50"/>
       <c r="D8" s="55" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E8" s="56"/>
       <c r="F8" s="57"/>
       <c r="G8" s="61" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H8" s="61"/>
       <c r="I8" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J8" s="51"/>
       <c r="K8" s="64" t="s">
@@ -4425,7 +5710,7 @@
       <c r="L8" s="64"/>
       <c r="M8" s="64"/>
       <c r="N8" s="63" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="O8" s="63"/>
       <c r="P8" s="63"/>
@@ -4436,7 +5721,7 @@
       <c r="U8" s="63"/>
       <c r="V8" s="63"/>
       <c r="W8" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X8" s="64"/>
     </row>
@@ -4446,16 +5731,16 @@
       </c>
       <c r="C9" s="50"/>
       <c r="D9" s="55" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E9" s="56"/>
       <c r="F9" s="57"/>
       <c r="G9" s="61" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H9" s="61"/>
       <c r="I9" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J9" s="51"/>
       <c r="K9" s="64" t="s">
@@ -4464,7 +5749,7 @@
       <c r="L9" s="64"/>
       <c r="M9" s="64"/>
       <c r="N9" s="63" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="O9" s="63"/>
       <c r="P9" s="63"/>
@@ -4475,7 +5760,7 @@
       <c r="U9" s="63"/>
       <c r="V9" s="63"/>
       <c r="W9" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X9" s="64"/>
     </row>
@@ -4485,16 +5770,16 @@
       </c>
       <c r="C10" s="50"/>
       <c r="D10" s="55" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E10" s="56"/>
       <c r="F10" s="57"/>
       <c r="G10" s="61" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H10" s="61"/>
       <c r="I10" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J10" s="51"/>
       <c r="K10" s="64" t="s">
@@ -4503,7 +5788,7 @@
       <c r="L10" s="64"/>
       <c r="M10" s="64"/>
       <c r="N10" s="63" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="O10" s="63"/>
       <c r="P10" s="63"/>
@@ -4514,7 +5799,7 @@
       <c r="U10" s="63"/>
       <c r="V10" s="63"/>
       <c r="W10" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X10" s="64"/>
     </row>
@@ -4524,16 +5809,16 @@
       </c>
       <c r="C11" s="50"/>
       <c r="D11" s="55" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E11" s="56"/>
       <c r="F11" s="57"/>
       <c r="G11" s="61" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H11" s="61"/>
       <c r="I11" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J11" s="51"/>
       <c r="K11" s="64" t="s">
@@ -4542,7 +5827,7 @@
       <c r="L11" s="64"/>
       <c r="M11" s="64"/>
       <c r="N11" s="63" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="O11" s="63"/>
       <c r="P11" s="63"/>
@@ -4553,7 +5838,7 @@
       <c r="U11" s="63"/>
       <c r="V11" s="63"/>
       <c r="W11" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X11" s="64"/>
     </row>
@@ -4563,16 +5848,16 @@
       </c>
       <c r="C12" s="50"/>
       <c r="D12" s="58" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E12" s="59"/>
       <c r="F12" s="60"/>
       <c r="G12" s="61" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H12" s="61"/>
       <c r="I12" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J12" s="51"/>
       <c r="K12" s="64" t="s">
@@ -4581,7 +5866,7 @@
       <c r="L12" s="64"/>
       <c r="M12" s="64"/>
       <c r="N12" s="63" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="O12" s="63"/>
       <c r="P12" s="63"/>
@@ -4592,7 +5877,7 @@
       <c r="U12" s="63"/>
       <c r="V12" s="63"/>
       <c r="W12" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X12" s="64"/>
     </row>
@@ -4602,16 +5887,16 @@
       </c>
       <c r="C13" s="50"/>
       <c r="D13" s="55" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E13" s="56"/>
       <c r="F13" s="57"/>
       <c r="G13" s="61" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H13" s="61"/>
       <c r="I13" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J13" s="51"/>
       <c r="K13" s="64" t="s">
@@ -4620,7 +5905,7 @@
       <c r="L13" s="64"/>
       <c r="M13" s="64"/>
       <c r="N13" s="63" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="O13" s="63"/>
       <c r="P13" s="63"/>
@@ -4631,7 +5916,7 @@
       <c r="U13" s="63"/>
       <c r="V13" s="63"/>
       <c r="W13" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X13" s="64"/>
     </row>
@@ -4641,16 +5926,16 @@
       </c>
       <c r="C14" s="50"/>
       <c r="D14" s="55" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E14" s="56"/>
       <c r="F14" s="57"/>
       <c r="G14" s="62" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H14" s="62"/>
       <c r="I14" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J14" s="51"/>
       <c r="K14" s="64" t="s">
@@ -4659,7 +5944,7 @@
       <c r="L14" s="64"/>
       <c r="M14" s="64"/>
       <c r="N14" s="63" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="O14" s="63"/>
       <c r="P14" s="63"/>
@@ -4670,7 +5955,7 @@
       <c r="U14" s="63"/>
       <c r="V14" s="63"/>
       <c r="W14" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X14" s="64"/>
     </row>
@@ -4680,16 +5965,16 @@
       </c>
       <c r="C15" s="50"/>
       <c r="D15" s="55" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E15" s="56"/>
       <c r="F15" s="57"/>
       <c r="G15" s="62" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H15" s="62"/>
       <c r="I15" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J15" s="51"/>
       <c r="K15" s="64" t="s">
@@ -4698,7 +5983,7 @@
       <c r="L15" s="64"/>
       <c r="M15" s="64"/>
       <c r="N15" s="63" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="O15" s="63"/>
       <c r="P15" s="63"/>
@@ -4709,7 +5994,7 @@
       <c r="U15" s="63"/>
       <c r="V15" s="63"/>
       <c r="W15" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X15" s="64"/>
     </row>
@@ -4719,16 +6004,16 @@
       </c>
       <c r="C16" s="50"/>
       <c r="D16" s="55" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E16" s="56"/>
       <c r="F16" s="57"/>
       <c r="G16" s="62" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H16" s="62"/>
       <c r="I16" s="51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J16" s="51"/>
       <c r="K16" s="64" t="s">
@@ -4737,7 +6022,7 @@
       <c r="L16" s="64"/>
       <c r="M16" s="64"/>
       <c r="N16" s="63" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="O16" s="63"/>
       <c r="P16" s="63"/>
@@ -4748,7 +6033,7 @@
       <c r="U16" s="63"/>
       <c r="V16" s="63"/>
       <c r="W16" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X16" s="64"/>
     </row>
@@ -4758,12 +6043,12 @@
       </c>
       <c r="C17" s="50"/>
       <c r="D17" s="55" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E17" s="56"/>
       <c r="F17" s="57"/>
       <c r="G17" s="62" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H17" s="62"/>
       <c r="I17" s="65" t="s">
@@ -4771,12 +6056,12 @@
       </c>
       <c r="J17" s="65"/>
       <c r="K17" s="64" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L17" s="64"/>
       <c r="M17" s="64"/>
       <c r="N17" s="63" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="O17" s="63"/>
       <c r="P17" s="63"/>
@@ -4787,7 +6072,7 @@
       <c r="U17" s="63"/>
       <c r="V17" s="63"/>
       <c r="W17" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X17" s="64"/>
     </row>
@@ -4797,12 +6082,12 @@
       </c>
       <c r="C18" s="50"/>
       <c r="D18" s="55" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E18" s="56"/>
       <c r="F18" s="57"/>
       <c r="G18" s="62" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H18" s="62"/>
       <c r="I18" s="65" t="s">
@@ -4810,12 +6095,12 @@
       </c>
       <c r="J18" s="65"/>
       <c r="K18" s="64" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L18" s="64"/>
       <c r="M18" s="64"/>
       <c r="N18" s="63" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="O18" s="63"/>
       <c r="P18" s="63"/>
@@ -4826,7 +6111,7 @@
       <c r="U18" s="63"/>
       <c r="V18" s="63"/>
       <c r="W18" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X18" s="64"/>
     </row>
@@ -4836,12 +6121,12 @@
       </c>
       <c r="C19" s="50"/>
       <c r="D19" s="55" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E19" s="56"/>
       <c r="F19" s="57"/>
       <c r="G19" s="62" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H19" s="62"/>
       <c r="I19" s="65" t="s">
@@ -4849,12 +6134,12 @@
       </c>
       <c r="J19" s="65"/>
       <c r="K19" s="64" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L19" s="64"/>
       <c r="M19" s="64"/>
       <c r="N19" s="63" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="O19" s="63"/>
       <c r="P19" s="63"/>
@@ -4865,7 +6150,7 @@
       <c r="U19" s="63"/>
       <c r="V19" s="63"/>
       <c r="W19" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X19" s="64"/>
     </row>
@@ -4875,12 +6160,12 @@
       </c>
       <c r="C20" s="50"/>
       <c r="D20" s="55" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E20" s="56"/>
       <c r="F20" s="57"/>
       <c r="G20" s="62" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H20" s="62"/>
       <c r="I20" s="65" t="s">
@@ -4888,12 +6173,12 @@
       </c>
       <c r="J20" s="65"/>
       <c r="K20" s="64" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L20" s="64"/>
       <c r="M20" s="64"/>
       <c r="N20" s="63" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="O20" s="63"/>
       <c r="P20" s="63"/>
@@ -4904,7 +6189,7 @@
       <c r="U20" s="63"/>
       <c r="V20" s="63"/>
       <c r="W20" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X20" s="64"/>
     </row>
@@ -4914,12 +6199,12 @@
       </c>
       <c r="C21" s="50"/>
       <c r="D21" s="55" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E21" s="56"/>
       <c r="F21" s="57"/>
       <c r="G21" s="62" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H21" s="62"/>
       <c r="I21" s="65" t="s">
@@ -4927,12 +6212,12 @@
       </c>
       <c r="J21" s="65"/>
       <c r="K21" s="64" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L21" s="64"/>
       <c r="M21" s="64"/>
       <c r="N21" s="63" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="O21" s="63"/>
       <c r="P21" s="63"/>
@@ -4943,7 +6228,7 @@
       <c r="U21" s="63"/>
       <c r="V21" s="63"/>
       <c r="W21" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X21" s="64"/>
     </row>
@@ -4953,12 +6238,12 @@
       </c>
       <c r="C22" s="50"/>
       <c r="D22" s="55" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E22" s="56"/>
       <c r="F22" s="57"/>
       <c r="G22" s="62" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H22" s="62"/>
       <c r="I22" s="65" t="s">
@@ -4966,12 +6251,12 @@
       </c>
       <c r="J22" s="65"/>
       <c r="K22" s="64" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L22" s="64"/>
       <c r="M22" s="64"/>
       <c r="N22" s="63" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="O22" s="63"/>
       <c r="P22" s="63"/>
@@ -4982,7 +6267,7 @@
       <c r="U22" s="63"/>
       <c r="V22" s="63"/>
       <c r="W22" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X22" s="64"/>
     </row>
@@ -4992,12 +6277,12 @@
       </c>
       <c r="C23" s="50"/>
       <c r="D23" s="55" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E23" s="56"/>
       <c r="F23" s="57"/>
       <c r="G23" s="62" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H23" s="62"/>
       <c r="I23" s="65" t="s">
@@ -5005,12 +6290,12 @@
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="64" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L23" s="64"/>
       <c r="M23" s="64"/>
       <c r="N23" s="63" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="O23" s="63"/>
       <c r="P23" s="63"/>
@@ -5021,7 +6306,7 @@
       <c r="U23" s="63"/>
       <c r="V23" s="63"/>
       <c r="W23" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X23" s="64"/>
     </row>
@@ -5031,12 +6316,12 @@
       </c>
       <c r="C24" s="50"/>
       <c r="D24" s="55" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E24" s="56"/>
       <c r="F24" s="57"/>
       <c r="G24" s="62" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H24" s="62"/>
       <c r="I24" s="65" t="s">
@@ -5044,12 +6329,12 @@
       </c>
       <c r="J24" s="65"/>
       <c r="K24" s="64" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L24" s="64"/>
       <c r="M24" s="64"/>
       <c r="N24" s="63" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="O24" s="63"/>
       <c r="P24" s="63"/>
@@ -5060,7 +6345,7 @@
       <c r="U24" s="63"/>
       <c r="V24" s="63"/>
       <c r="W24" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X24" s="64"/>
     </row>
@@ -5070,12 +6355,12 @@
       </c>
       <c r="C25" s="50"/>
       <c r="D25" s="55" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E25" s="56"/>
       <c r="F25" s="57"/>
       <c r="G25" s="62" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H25" s="62"/>
       <c r="I25" s="65" t="s">
@@ -5083,12 +6368,12 @@
       </c>
       <c r="J25" s="65"/>
       <c r="K25" s="64" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L25" s="64"/>
       <c r="M25" s="64"/>
       <c r="N25" s="63" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="O25" s="63"/>
       <c r="P25" s="63"/>
@@ -5099,7 +6384,7 @@
       <c r="U25" s="63"/>
       <c r="V25" s="63"/>
       <c r="W25" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X25" s="64"/>
     </row>
@@ -5109,12 +6394,12 @@
       </c>
       <c r="C26" s="50"/>
       <c r="D26" s="55" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E26" s="56"/>
       <c r="F26" s="57"/>
       <c r="G26" s="62" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H26" s="62"/>
       <c r="I26" s="65" t="s">
@@ -5122,12 +6407,12 @@
       </c>
       <c r="J26" s="65"/>
       <c r="K26" s="64" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="L26" s="64"/>
       <c r="M26" s="64"/>
       <c r="N26" s="63" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="O26" s="63"/>
       <c r="P26" s="63"/>
@@ -5138,7 +6423,7 @@
       <c r="U26" s="63"/>
       <c r="V26" s="63"/>
       <c r="W26" s="64" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="X26" s="64"/>
     </row>
@@ -5322,14 +6607,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9F41932-50C2-459B-97AA-8755C7255BDB}">
   <sheetPr>
-    <tabColor rgb="FF92D050"/>
+    <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>124</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0699A0-8558-48E9-A533-A6E0D3122C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3699EFF-376E-4449-BE39-EAD8FB27DDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
@@ -6051,10 +6051,10 @@
         <v>95</v>
       </c>
       <c r="H17" s="62"/>
-      <c r="I17" s="65" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="65"/>
+      <c r="I17" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="J17" s="51"/>
       <c r="K17" s="64" t="s">
         <v>114</v>
       </c>
@@ -6090,10 +6090,10 @@
         <v>95</v>
       </c>
       <c r="H18" s="62"/>
-      <c r="I18" s="65" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="65"/>
+      <c r="I18" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="J18" s="51"/>
       <c r="K18" s="64" t="s">
         <v>114</v>
       </c>
@@ -6168,10 +6168,10 @@
         <v>95</v>
       </c>
       <c r="H20" s="62"/>
-      <c r="I20" s="65" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" s="65"/>
+      <c r="I20" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="J20" s="51"/>
       <c r="K20" s="64" t="s">
         <v>114</v>
       </c>

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3699EFF-376E-4449-BE39-EAD8FB27DDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11753A6-397B-44F0-ACEF-79874D8F19E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
@@ -5930,10 +5930,10 @@
       </c>
       <c r="E14" s="56"/>
       <c r="F14" s="57"/>
-      <c r="G14" s="62" t="s">
-        <v>95</v>
-      </c>
-      <c r="H14" s="62"/>
+      <c r="G14" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="H14" s="61"/>
       <c r="I14" s="51" t="s">
         <v>97</v>
       </c>
@@ -5969,10 +5969,10 @@
       </c>
       <c r="E15" s="56"/>
       <c r="F15" s="57"/>
-      <c r="G15" s="62" t="s">
-        <v>95</v>
-      </c>
-      <c r="H15" s="62"/>
+      <c r="G15" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" s="61"/>
       <c r="I15" s="51" t="s">
         <v>97</v>
       </c>
@@ -6008,10 +6008,10 @@
       </c>
       <c r="E16" s="56"/>
       <c r="F16" s="57"/>
-      <c r="G16" s="62" t="s">
-        <v>95</v>
-      </c>
-      <c r="H16" s="62"/>
+      <c r="G16" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="H16" s="61"/>
       <c r="I16" s="51" t="s">
         <v>97</v>
       </c>

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11753A6-397B-44F0-ACEF-79874D8F19E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0829FB2-6645-47B5-868F-01D02F4FBAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="183">
   <si>
     <t>SIGNOMALY</t>
   </si>
@@ -1703,30 +1703,6 @@
   </si>
   <si>
     <t>2. Game Interaction</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Người chơi có thể </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>nhấn giữ E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> khi phát hiện Puzzle để thực hiện câu đố.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -5042,7 +5018,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A2:AJ128"/>
+  <dimension ref="A2:AJ126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
@@ -5430,7 +5406,7 @@
     </row>
     <row r="110" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B110" s="66" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="111" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
@@ -5438,7 +5414,7 @@
     </row>
     <row r="112" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B112" s="66" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="114" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
@@ -5448,42 +5424,37 @@
     </row>
     <row r="116" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B116" s="66" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="118" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B118" s="66" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="120" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B120" s="66" t="s">
-        <v>172</v>
+      <c r="B120" s="8" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="122" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B122" s="8" t="s">
+      <c r="B122" s="66" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="124" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B124" s="66" t="s">
+      <c r="B124" s="8" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="126" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B126" s="8" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="128" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B128" s="66" t="s">
-        <v>183</v>
-      </c>
-      <c r="L128" s="77" t="s">
+      <c r="B126" s="66" t="s">
         <v>182</v>
       </c>
-      <c r="M128" s="66"/>
+      <c r="L126" s="77" t="s">
+        <v>181</v>
+      </c>
+      <c r="M126" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -5510,7 +5481,7 @@
     <mergeCell ref="B4:F4"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="L128" location="Dialogues!A1" display="Dialogues!A1" xr:uid="{5724AB96-1B0F-4DFD-A35F-382AC93CCD96}"/>
+    <hyperlink ref="L126" location="Dialogues!A1" display="Dialogues!A1" xr:uid="{5724AB96-1B0F-4DFD-A35F-382AC93CCD96}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5527,7 +5498,7 @@
   <sheetData>
     <row r="2" spans="1:24" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
@@ -6121,7 +6092,7 @@
       </c>
       <c r="C19" s="50"/>
       <c r="D19" s="55" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E19" s="56"/>
       <c r="F19" s="57"/>
@@ -6129,10 +6100,10 @@
         <v>95</v>
       </c>
       <c r="H19" s="62"/>
-      <c r="I19" s="65" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="65"/>
+      <c r="I19" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="J19" s="51"/>
       <c r="K19" s="64" t="s">
         <v>114</v>
       </c>
@@ -6160,7 +6131,7 @@
       </c>
       <c r="C20" s="50"/>
       <c r="D20" s="55" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E20" s="56"/>
       <c r="F20" s="57"/>
@@ -6168,10 +6139,10 @@
         <v>95</v>
       </c>
       <c r="H20" s="62"/>
-      <c r="I20" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="J20" s="51"/>
+      <c r="I20" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="65"/>
       <c r="K20" s="64" t="s">
         <v>114</v>
       </c>
@@ -6199,7 +6170,7 @@
       </c>
       <c r="C21" s="50"/>
       <c r="D21" s="55" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E21" s="56"/>
       <c r="F21" s="57"/>
@@ -6238,7 +6209,7 @@
       </c>
       <c r="C22" s="50"/>
       <c r="D22" s="55" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E22" s="56"/>
       <c r="F22" s="57"/>
@@ -6277,7 +6248,7 @@
       </c>
       <c r="C23" s="50"/>
       <c r="D23" s="55" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E23" s="56"/>
       <c r="F23" s="57"/>
@@ -6316,7 +6287,7 @@
       </c>
       <c r="C24" s="50"/>
       <c r="D24" s="55" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E24" s="56"/>
       <c r="F24" s="57"/>
@@ -6355,7 +6326,7 @@
       </c>
       <c r="C25" s="50"/>
       <c r="D25" s="55" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E25" s="56"/>
       <c r="F25" s="57"/>
@@ -6394,7 +6365,7 @@
       </c>
       <c r="C26" s="50"/>
       <c r="D26" s="55" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E26" s="56"/>
       <c r="F26" s="57"/>
@@ -6429,6 +6400,7 @@
     </row>
   </sheetData>
   <mergeCells count="161">
+    <mergeCell ref="W24:X24"/>
     <mergeCell ref="W25:X25"/>
     <mergeCell ref="W26:X26"/>
     <mergeCell ref="W19:X19"/>
@@ -6436,7 +6408,6 @@
     <mergeCell ref="W21:X21"/>
     <mergeCell ref="W22:X22"/>
     <mergeCell ref="W23:X23"/>
-    <mergeCell ref="W24:X24"/>
     <mergeCell ref="W10:X10"/>
     <mergeCell ref="W11:X11"/>
     <mergeCell ref="W12:X12"/>
@@ -6473,29 +6444,29 @@
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="N6:V6"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="N26:V26"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="I25:J25"/>
     <mergeCell ref="K25:M25"/>
     <mergeCell ref="N25:V25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="N24:V24"/>
     <mergeCell ref="K18:M18"/>
+    <mergeCell ref="K26:M26"/>
     <mergeCell ref="K19:M19"/>
     <mergeCell ref="K20:M20"/>
     <mergeCell ref="K21:M21"/>
     <mergeCell ref="K22:M22"/>
-    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="N19:V19"/>
     <mergeCell ref="N20:V20"/>
     <mergeCell ref="N21:V21"/>
     <mergeCell ref="N22:V22"/>
     <mergeCell ref="N23:V23"/>
-    <mergeCell ref="N24:V24"/>
     <mergeCell ref="K4:M4"/>
     <mergeCell ref="K5:M5"/>
     <mergeCell ref="K7:M7"/>
@@ -6510,7 +6481,7 @@
     <mergeCell ref="N11:V11"/>
     <mergeCell ref="N12:V12"/>
     <mergeCell ref="N13:V13"/>
-    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="K23:M23"/>
     <mergeCell ref="W16:X16"/>
     <mergeCell ref="W17:X17"/>
     <mergeCell ref="W18:X18"/>
@@ -6520,42 +6491,42 @@
     <mergeCell ref="K13:M13"/>
     <mergeCell ref="N17:V17"/>
     <mergeCell ref="N18:V18"/>
-    <mergeCell ref="N19:V19"/>
+    <mergeCell ref="N26:V26"/>
     <mergeCell ref="K17:M17"/>
+    <mergeCell ref="D20:F20"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="D22:F22"/>
     <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D26:F26"/>
     <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D11:F11"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="G23:H23"/>
     <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="I21:J21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
@@ -6614,7 +6585,7 @@
   <sheetData>
     <row r="2" spans="1:1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0829FB2-6645-47B5-868F-01D02F4FBAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD0BA7F-5BA2-4A4D-A24F-D5401773BDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="185">
   <si>
     <t>SIGNOMALY</t>
   </si>
@@ -578,65 +578,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Khi puzzle giải đố được kích hoạt: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Người chơi cần </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>tìm ra các mảnh bằng chứng</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (vật phẩm, giấy) có chứa các đoạn văn và </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>cần giải mã để ra một dãy số (không có văn bản)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Dãy số này sẽ là lời giải cho câu đố và thoả mãn "Điều kiện tổng".</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Số lượng ô cần điền đáp án cho mỗi dãy số là </t>
     </r>
     <r>
@@ -1276,27 +1217,6 @@
       <rPr>
         <b/>
         <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>#Tờ hướng dẫn:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> "This room once belonged to someone. They have departed but they did not take everything with them. They left behind two objects. Each one is hidden behind a message. Find the right one, and only then will you understand who they truly were."</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
@@ -1840,6 +1760,101 @@
   </si>
   <si>
     <t>Đối thoại với NPC để hiểu cơ chế chơi. Đoạn đối thoại có thể xem bên tab</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Khi puzzle giải đố được kích hoạt: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Người chơi cần </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>tìm ra các mảnh bằng chứng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (vật phẩm, giấy) có chứa các đoạn văn và </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>cần giải mã để ra một dãy số (không có văn bản)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Dãy số này sẽ là lời giải cho câu đố và thoả mãn "Điều kiện tổng".</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Ngoài ra sẽ hiện luôn cả #Tờ hướng dẫn, kế bên.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#Hướng dẫn:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> "This room once belonged to someone. They have departed but they did not take everything with them. They left behind two objects. Each one is hidden behind a message. Find the right one, and only then will you understand who they truly were."</t>
+    </r>
+  </si>
+  <si>
+    <t>Phần Puzzle UI này sẽ nhìn trực diện vào máy bảo mật, và có nút back ra. Khi bấm sai thì nó sẽ hiển thị: "This is incorrect".</t>
+  </si>
+  <si>
+    <t>Phần Puzzle UI này sẽ không cần nhìn vào #tờ hướng dẫn. Mà sẽ hiển thị #hướng dẫn trực tiếp trên màn hình, và có nút back về. Nếu đưa đồ vật không phù hợp, thì sẽ không thể vào Puzzle UI mà sẽ hiển thị chữ: "This item is not correct!".</t>
   </si>
 </sst>
 </file>
@@ -2058,7 +2073,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2240,6 +2255,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2398,8 +2416,8 @@
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>607798</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2459,8 +2477,8 @@
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>147043</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>127993</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2514,13 +2532,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>34528</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>183952</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2575,13 +2593,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>57151</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>190501</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2636,14 +2654,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>82</xdr:row>
-      <xdr:rowOff>76201</xdr:rowOff>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2697,13 +2715,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>220133</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2758,13 +2776,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>138033</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3626,7 +3644,7 @@
     </row>
     <row r="15" spans="1:26" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="34" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C15" s="34"/>
       <c r="D15" s="34"/>
@@ -3886,7 +3904,7 @@
   <sheetData>
     <row r="2" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B2" s="8"/>
     </row>
@@ -3981,7 +3999,7 @@
       <c r="K6" s="41"/>
       <c r="L6" s="41"/>
       <c r="M6" s="47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N6" s="46"/>
       <c r="O6" s="46"/>
@@ -4051,7 +4069,7 @@
       <c r="K8" s="41"/>
       <c r="L8" s="41"/>
       <c r="M8" s="43" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N8" s="44"/>
       <c r="O8" s="44"/>
@@ -4085,7 +4103,7 @@
       <c r="K9" s="41"/>
       <c r="L9" s="41"/>
       <c r="M9" s="43" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N9" s="44"/>
       <c r="O9" s="44"/>
@@ -4119,7 +4137,7 @@
       <c r="K10" s="41"/>
       <c r="L10" s="41"/>
       <c r="M10" s="43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N10" s="44"/>
       <c r="O10" s="44"/>
@@ -4283,17 +4301,17 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A2:AK77"/>
+  <dimension ref="A2:AK81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:30" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="19.5" x14ac:dyDescent="0.25">
@@ -4328,7 +4346,7 @@
     </row>
     <row r="8" spans="1:30" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N8" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O8" s="25"/>
       <c r="P8" s="25"/>
@@ -4363,7 +4381,7 @@
     </row>
     <row r="10" spans="1:30" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N10" s="25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O10" s="28"/>
       <c r="P10" s="28"/>
@@ -4387,7 +4405,7 @@
     </row>
     <row r="16" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B16" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
@@ -4395,7 +4413,7 @@
     </row>
     <row r="18" spans="2:33" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C18" s="30"/>
       <c r="D18" s="30"/>
@@ -4458,7 +4476,7 @@
     </row>
     <row r="23" spans="2:33" ht="19.5" x14ac:dyDescent="0.25">
       <c r="T23" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="U23" s="24"/>
       <c r="V23" s="24"/>
@@ -4477,8 +4495,8 @@
       <c r="T24" s="12"/>
     </row>
     <row r="25" spans="2:33" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T25" s="20" t="s">
-        <v>52</v>
+      <c r="T25" s="48" t="s">
+        <v>181</v>
       </c>
       <c r="U25" s="21"/>
       <c r="V25" s="21"/>
@@ -4495,7 +4513,7 @@
       <c r="AG25" s="17"/>
     </row>
     <row r="26" spans="2:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T26" s="18"/>
+      <c r="T26" s="67"/>
       <c r="U26" s="18"/>
       <c r="V26" s="18"/>
       <c r="W26" s="18"/>
@@ -4510,313 +4528,325 @@
       <c r="AF26" s="18"/>
       <c r="AG26" s="17"/>
     </row>
-    <row r="27" spans="2:33" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="T27" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="U27" s="24"/>
-      <c r="V27" s="24"/>
-      <c r="W27" s="24"/>
-      <c r="X27" s="24"/>
-      <c r="Y27" s="24"/>
-      <c r="Z27" s="24"/>
-      <c r="AA27" s="24"/>
-      <c r="AB27" s="24"/>
-      <c r="AC27" s="24"/>
-      <c r="AD27" s="24"/>
-      <c r="AE27" s="24"/>
-      <c r="AF27" s="24"/>
-    </row>
-    <row r="28" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T28" s="12"/>
-    </row>
-    <row r="29" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T29" s="12" t="s">
+    <row r="27" spans="2:33" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T27" s="48" t="s">
+        <v>183</v>
+      </c>
+      <c r="U27" s="48"/>
+      <c r="V27" s="48"/>
+      <c r="W27" s="48"/>
+      <c r="X27" s="48"/>
+      <c r="Y27" s="48"/>
+      <c r="Z27" s="48"/>
+      <c r="AA27" s="48"/>
+      <c r="AB27" s="48"/>
+      <c r="AC27" s="48"/>
+      <c r="AD27" s="48"/>
+      <c r="AE27" s="48"/>
+      <c r="AF27" s="48"/>
+      <c r="AG27" s="17"/>
+    </row>
+    <row r="28" spans="2:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T28" s="18"/>
+      <c r="U28" s="18"/>
+      <c r="V28" s="18"/>
+      <c r="W28" s="18"/>
+      <c r="X28" s="18"/>
+      <c r="Y28" s="18"/>
+      <c r="Z28" s="18"/>
+      <c r="AA28" s="18"/>
+      <c r="AB28" s="18"/>
+      <c r="AC28" s="18"/>
+      <c r="AD28" s="18"/>
+      <c r="AE28" s="18"/>
+      <c r="AF28" s="18"/>
+      <c r="AG28" s="17"/>
+    </row>
+    <row r="29" spans="2:33" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="T29" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="U29" s="24"/>
+      <c r="V29" s="24"/>
+      <c r="W29" s="24"/>
+      <c r="X29" s="24"/>
+      <c r="Y29" s="24"/>
+      <c r="Z29" s="24"/>
+      <c r="AA29" s="24"/>
+      <c r="AB29" s="24"/>
+      <c r="AC29" s="24"/>
+      <c r="AD29" s="24"/>
+      <c r="AE29" s="24"/>
+      <c r="AF29" s="24"/>
+    </row>
+    <row r="30" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T30" s="12"/>
+    </row>
+    <row r="31" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T31" s="12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T32" s="12" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T30" s="12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T31" s="12"/>
-    </row>
-    <row r="32" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T32" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="U32" s="8"/>
-      <c r="V32" s="8"/>
-      <c r="W32" s="8"/>
-      <c r="X32" s="8"/>
-      <c r="Y32" s="8"/>
+    <row r="33" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T33" s="12"/>
     </row>
     <row r="34" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T34" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="U34" s="8"/>
+      <c r="V34" s="8"/>
+      <c r="W34" s="8"/>
+      <c r="X34" s="8"/>
+      <c r="Y34" s="8"/>
+    </row>
+    <row r="36" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T36" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="U36" s="12"/>
+      <c r="V36" s="12"/>
+      <c r="W36" s="12"/>
+      <c r="X36" s="12"/>
+      <c r="Y36" s="12"/>
+      <c r="Z36" s="12"/>
+      <c r="AA36" s="12"/>
+      <c r="AB36" s="12"/>
+      <c r="AC36" s="12"/>
+      <c r="AD36" s="12"/>
+      <c r="AE36" s="12"/>
+      <c r="AF36" s="12"/>
+    </row>
+    <row r="37" spans="2:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T37" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="U37" s="25"/>
+      <c r="V37" s="25"/>
+      <c r="W37" s="25"/>
+      <c r="X37" s="25"/>
+      <c r="Y37" s="25"/>
+      <c r="Z37" s="25"/>
+      <c r="AA37" s="25"/>
+      <c r="AB37" s="25"/>
+      <c r="AC37" s="25"/>
+      <c r="AD37" s="25"/>
+      <c r="AE37" s="25"/>
+      <c r="AF37" s="25"/>
+    </row>
+    <row r="39" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T39" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="U39" s="12"/>
+      <c r="V39" s="12"/>
+      <c r="W39" s="12"/>
+      <c r="X39" s="12"/>
+      <c r="Y39" s="12"/>
+      <c r="Z39" s="12"/>
+      <c r="AA39" s="12"/>
+      <c r="AB39" s="12"/>
+      <c r="AC39" s="12"/>
+      <c r="AD39" s="12"/>
+      <c r="AE39" s="12"/>
+      <c r="AF39" s="12"/>
+    </row>
+    <row r="40" spans="2:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T40" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="U40" s="25"/>
+      <c r="V40" s="25"/>
+      <c r="W40" s="25"/>
+      <c r="X40" s="25"/>
+      <c r="Y40" s="25"/>
+      <c r="Z40" s="25"/>
+      <c r="AA40" s="25"/>
+      <c r="AB40" s="25"/>
+      <c r="AC40" s="25"/>
+      <c r="AD40" s="25"/>
+      <c r="AE40" s="25"/>
+      <c r="AF40" s="25"/>
+      <c r="AG40" s="25"/>
+      <c r="AH40" s="25"/>
+      <c r="AI40" s="25"/>
+      <c r="AJ40" s="25"/>
+      <c r="AK40" s="25"/>
+    </row>
+    <row r="41" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T41" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T42" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="2:37" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="T43" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="U34" s="12"/>
-      <c r="V34" s="12"/>
-      <c r="W34" s="12"/>
-      <c r="X34" s="12"/>
-      <c r="Y34" s="12"/>
-      <c r="Z34" s="12"/>
-      <c r="AA34" s="12"/>
-      <c r="AB34" s="12"/>
-      <c r="AC34" s="12"/>
-      <c r="AD34" s="12"/>
-      <c r="AE34" s="12"/>
-      <c r="AF34" s="12"/>
-    </row>
-    <row r="35" spans="2:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T35" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="U35" s="25"/>
-      <c r="V35" s="25"/>
-      <c r="W35" s="25"/>
-      <c r="X35" s="25"/>
-      <c r="Y35" s="25"/>
-      <c r="Z35" s="25"/>
-      <c r="AA35" s="25"/>
-      <c r="AB35" s="25"/>
-      <c r="AC35" s="25"/>
-      <c r="AD35" s="25"/>
-      <c r="AE35" s="25"/>
-      <c r="AF35" s="25"/>
-    </row>
-    <row r="37" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T37" s="8" t="s">
+      <c r="U43" s="24"/>
+      <c r="V43" s="24"/>
+      <c r="W43" s="24"/>
+      <c r="X43" s="24"/>
+      <c r="Y43" s="24"/>
+      <c r="Z43" s="24"/>
+      <c r="AA43" s="24"/>
+      <c r="AB43" s="24"/>
+      <c r="AC43" s="24"/>
+      <c r="AD43" s="24"/>
+      <c r="AE43" s="24"/>
+      <c r="AF43" s="24"/>
+      <c r="AG43" s="24"/>
+    </row>
+    <row r="44" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T44" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T45" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="U37" s="12"/>
-      <c r="V37" s="12"/>
-      <c r="W37" s="12"/>
-      <c r="X37" s="12"/>
-      <c r="Y37" s="12"/>
-      <c r="Z37" s="12"/>
-      <c r="AA37" s="12"/>
-      <c r="AB37" s="12"/>
-      <c r="AC37" s="12"/>
-      <c r="AD37" s="12"/>
-      <c r="AE37" s="12"/>
-      <c r="AF37" s="12"/>
-    </row>
-    <row r="38" spans="2:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T38" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="U38" s="25"/>
-      <c r="V38" s="25"/>
-      <c r="W38" s="25"/>
-      <c r="X38" s="25"/>
-      <c r="Y38" s="25"/>
-      <c r="Z38" s="25"/>
-      <c r="AA38" s="25"/>
-      <c r="AB38" s="25"/>
-      <c r="AC38" s="25"/>
-      <c r="AD38" s="25"/>
-      <c r="AE38" s="25"/>
-      <c r="AF38" s="25"/>
-      <c r="AG38" s="25"/>
-      <c r="AH38" s="25"/>
-      <c r="AI38" s="25"/>
-      <c r="AJ38" s="25"/>
-      <c r="AK38" s="25"/>
-    </row>
-    <row r="39" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T39" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="40" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T40" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="41" spans="2:37" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="T41" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="U41" s="24"/>
-      <c r="V41" s="24"/>
-      <c r="W41" s="24"/>
-      <c r="X41" s="24"/>
-      <c r="Y41" s="24"/>
-      <c r="Z41" s="24"/>
-      <c r="AA41" s="24"/>
-      <c r="AB41" s="24"/>
-      <c r="AC41" s="24"/>
-      <c r="AD41" s="24"/>
-      <c r="AE41" s="24"/>
-      <c r="AF41" s="24"/>
-      <c r="AG41" s="24"/>
-    </row>
-    <row r="42" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T42" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="43" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T43" s="8" t="s">
+    </row>
+    <row r="46" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B46" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" s="27"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
+      <c r="I46" s="27"/>
+      <c r="J46" s="27"/>
+      <c r="K46" s="27"/>
+      <c r="L46" s="27"/>
+      <c r="M46" s="27"/>
+      <c r="N46" s="27"/>
+      <c r="O46" s="27"/>
+      <c r="P46" s="27"/>
+      <c r="Q46" s="27"/>
+      <c r="R46" s="27"/>
+      <c r="T46" s="24" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="44" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B44" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="27"/>
-      <c r="J44" s="27"/>
-      <c r="K44" s="27"/>
-      <c r="L44" s="27"/>
-      <c r="M44" s="27"/>
-      <c r="N44" s="27"/>
-      <c r="O44" s="27"/>
-      <c r="P44" s="27"/>
-      <c r="Q44" s="27"/>
-      <c r="R44" s="27"/>
-      <c r="T44" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="U44" s="24"/>
-      <c r="V44" s="24"/>
-      <c r="W44" s="24"/>
-      <c r="X44" s="24"/>
-      <c r="Y44" s="24"/>
-      <c r="Z44" s="24"/>
-      <c r="AA44" s="24"/>
-      <c r="AB44" s="24"/>
-      <c r="AC44" s="24"/>
-      <c r="AD44" s="24"/>
-      <c r="AE44" s="24"/>
-      <c r="AF44" s="24"/>
-      <c r="AG44" s="24"/>
-      <c r="AH44" s="24"/>
-      <c r="AI44" s="24"/>
-    </row>
-    <row r="45" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T45" s="12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="46" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T46" s="8" t="s">
-        <v>63</v>
-      </c>
+      <c r="U46" s="24"/>
+      <c r="V46" s="24"/>
+      <c r="W46" s="24"/>
+      <c r="X46" s="24"/>
+      <c r="Y46" s="24"/>
+      <c r="Z46" s="24"/>
+      <c r="AA46" s="24"/>
+      <c r="AB46" s="24"/>
+      <c r="AC46" s="24"/>
+      <c r="AD46" s="24"/>
+      <c r="AE46" s="24"/>
+      <c r="AF46" s="24"/>
+      <c r="AG46" s="24"/>
+      <c r="AH46" s="24"/>
+      <c r="AI46" s="24"/>
     </row>
     <row r="47" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T47" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T48" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="49" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T49" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T50" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T51" s="8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="48" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T48" s="12" t="s">
+    <row r="52" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T52" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="53" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T53" s="12" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="49" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T49" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="50" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T50" s="12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="51" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T51" s="12" t="s">
+    <row r="54" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T54" s="12"/>
+    </row>
+    <row r="55" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T55" s="12"/>
+    </row>
+    <row r="56" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T56" s="12"/>
+    </row>
+    <row r="57" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T57" s="12"/>
+    </row>
+    <row r="58" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T58" s="12"/>
+    </row>
+    <row r="59" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T59" s="12"/>
+    </row>
+    <row r="60" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T60" s="12"/>
+    </row>
+    <row r="61" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B61" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="C61" s="27"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="27"/>
+      <c r="I61" s="27"/>
+      <c r="J61" s="27"/>
+      <c r="K61" s="27"/>
+      <c r="L61" s="27"/>
+      <c r="M61" s="27"/>
+      <c r="N61" s="27"/>
+      <c r="O61" s="27"/>
+      <c r="P61" s="27"/>
+      <c r="Q61" s="27"/>
+      <c r="R61" s="27"/>
+      <c r="T61" s="12"/>
+    </row>
+    <row r="62" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T62" s="12"/>
+    </row>
+    <row r="63" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T63" s="12"/>
+    </row>
+    <row r="64" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B64" s="8" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="52" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T52" s="12"/>
-    </row>
-    <row r="53" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T53" s="12"/>
-    </row>
-    <row r="54" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T54" s="12"/>
-    </row>
-    <row r="55" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T55" s="12"/>
-    </row>
-    <row r="56" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T56" s="12"/>
-    </row>
-    <row r="57" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T57" s="12"/>
-    </row>
-    <row r="58" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T58" s="12"/>
-    </row>
-    <row r="59" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B59" s="49" t="s">
-        <v>94</v>
-      </c>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
-      <c r="E59" s="27"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="27"/>
-      <c r="I59" s="27"/>
-      <c r="J59" s="27"/>
-      <c r="K59" s="27"/>
-      <c r="L59" s="27"/>
-      <c r="M59" s="27"/>
-      <c r="N59" s="27"/>
-      <c r="O59" s="27"/>
-      <c r="P59" s="27"/>
-      <c r="Q59" s="27"/>
-      <c r="R59" s="27"/>
-      <c r="T59" s="12"/>
-    </row>
-    <row r="60" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T60" s="12"/>
-    </row>
-    <row r="61" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T61" s="12"/>
-    </row>
-    <row r="62" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B62" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="64" spans="2:37" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T64" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="U64" s="21"/>
-      <c r="V64" s="21"/>
-      <c r="W64" s="21"/>
-      <c r="X64" s="21"/>
-      <c r="Y64" s="21"/>
-      <c r="Z64" s="21"/>
-      <c r="AA64" s="21"/>
-      <c r="AB64" s="21"/>
-      <c r="AC64" s="21"/>
-      <c r="AD64" s="21"/>
-      <c r="AE64" s="21"/>
-      <c r="AF64" s="21"/>
-      <c r="AG64" s="21"/>
-      <c r="AH64" s="21"/>
-      <c r="AI64" s="21"/>
-      <c r="AJ64" s="21"/>
-      <c r="AK64" s="21"/>
-    </row>
-    <row r="66" spans="20:37" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="20:37" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T66" s="20" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="U66" s="21"/>
       <c r="V66" s="21"/>
@@ -4836,176 +4866,242 @@
       <c r="AJ66" s="21"/>
       <c r="AK66" s="21"/>
     </row>
-    <row r="68" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T68" s="8" t="s">
+    <row r="68" spans="20:37" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T68" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="U68" s="21"/>
+      <c r="V68" s="21"/>
+      <c r="W68" s="21"/>
+      <c r="X68" s="21"/>
+      <c r="Y68" s="21"/>
+      <c r="Z68" s="21"/>
+      <c r="AA68" s="21"/>
+      <c r="AB68" s="21"/>
+      <c r="AC68" s="21"/>
+      <c r="AD68" s="21"/>
+      <c r="AE68" s="21"/>
+      <c r="AF68" s="21"/>
+      <c r="AG68" s="21"/>
+      <c r="AH68" s="21"/>
+      <c r="AI68" s="21"/>
+      <c r="AJ68" s="21"/>
+      <c r="AK68" s="21"/>
+    </row>
+    <row r="69" spans="20:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T69" s="19"/>
+      <c r="U69" s="18"/>
+      <c r="V69" s="18"/>
+      <c r="W69" s="18"/>
+      <c r="X69" s="18"/>
+      <c r="Y69" s="18"/>
+      <c r="Z69" s="18"/>
+      <c r="AA69" s="18"/>
+      <c r="AB69" s="18"/>
+      <c r="AC69" s="18"/>
+      <c r="AD69" s="18"/>
+      <c r="AE69" s="18"/>
+      <c r="AF69" s="18"/>
+      <c r="AG69" s="18"/>
+      <c r="AH69" s="18"/>
+      <c r="AI69" s="18"/>
+      <c r="AJ69" s="18"/>
+      <c r="AK69" s="18"/>
+    </row>
+    <row r="70" spans="20:37" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T70" s="48" t="s">
+        <v>184</v>
+      </c>
+      <c r="U70" s="48"/>
+      <c r="V70" s="48"/>
+      <c r="W70" s="48"/>
+      <c r="X70" s="48"/>
+      <c r="Y70" s="48"/>
+      <c r="Z70" s="48"/>
+      <c r="AA70" s="48"/>
+      <c r="AB70" s="48"/>
+      <c r="AC70" s="48"/>
+      <c r="AD70" s="48"/>
+      <c r="AE70" s="48"/>
+      <c r="AF70" s="48"/>
+      <c r="AG70" s="48"/>
+      <c r="AH70" s="48"/>
+      <c r="AI70" s="48"/>
+      <c r="AJ70" s="48"/>
+      <c r="AK70" s="48"/>
+    </row>
+    <row r="72" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T72" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="73" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T73" s="8"/>
+    </row>
+    <row r="74" spans="20:37" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T74" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="U74" s="21"/>
+      <c r="V74" s="21"/>
+      <c r="W74" s="21"/>
+      <c r="X74" s="21"/>
+      <c r="Y74" s="21"/>
+      <c r="Z74" s="21"/>
+      <c r="AA74" s="21"/>
+      <c r="AB74" s="21"/>
+      <c r="AC74" s="21"/>
+      <c r="AD74" s="21"/>
+      <c r="AE74" s="21"/>
+      <c r="AF74" s="21"/>
+      <c r="AG74" s="21"/>
+      <c r="AH74" s="21"/>
+      <c r="AI74" s="21"/>
+      <c r="AJ74" s="21"/>
+      <c r="AK74" s="21"/>
+    </row>
+    <row r="75" spans="20:37" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="T75" s="19"/>
+      <c r="U75" s="18"/>
+      <c r="V75" s="18"/>
+      <c r="W75" s="18"/>
+      <c r="X75" s="18"/>
+      <c r="Y75" s="18"/>
+      <c r="Z75" s="18"/>
+      <c r="AA75" s="18"/>
+      <c r="AB75" s="18"/>
+      <c r="AC75" s="18"/>
+      <c r="AD75" s="18"/>
+      <c r="AE75" s="18"/>
+      <c r="AF75" s="18"/>
+      <c r="AG75" s="18"/>
+      <c r="AH75" s="18"/>
+      <c r="AI75" s="18"/>
+      <c r="AJ75" s="18"/>
+      <c r="AK75" s="18"/>
+    </row>
+    <row r="76" spans="20:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T76" s="22" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="69" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T69" s="8"/>
-    </row>
-    <row r="70" spans="20:37" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T70" s="48" t="s">
-        <v>92</v>
-      </c>
-      <c r="U70" s="21"/>
-      <c r="V70" s="21"/>
-      <c r="W70" s="21"/>
-      <c r="X70" s="21"/>
-      <c r="Y70" s="21"/>
-      <c r="Z70" s="21"/>
-      <c r="AA70" s="21"/>
-      <c r="AB70" s="21"/>
-      <c r="AC70" s="21"/>
-      <c r="AD70" s="21"/>
-      <c r="AE70" s="21"/>
-      <c r="AF70" s="21"/>
-      <c r="AG70" s="21"/>
-      <c r="AH70" s="21"/>
-      <c r="AI70" s="21"/>
-      <c r="AJ70" s="21"/>
-      <c r="AK70" s="21"/>
-    </row>
-    <row r="71" spans="20:37" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="T71" s="19"/>
-      <c r="U71" s="18"/>
-      <c r="V71" s="18"/>
-      <c r="W71" s="18"/>
-      <c r="X71" s="18"/>
-      <c r="Y71" s="18"/>
-      <c r="Z71" s="18"/>
-      <c r="AA71" s="18"/>
-      <c r="AB71" s="18"/>
-      <c r="AC71" s="18"/>
-      <c r="AD71" s="18"/>
-      <c r="AE71" s="18"/>
-      <c r="AF71" s="18"/>
-      <c r="AG71" s="18"/>
-      <c r="AH71" s="18"/>
-      <c r="AI71" s="18"/>
-      <c r="AJ71" s="18"/>
-      <c r="AK71" s="18"/>
-    </row>
-    <row r="72" spans="20:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T72" s="22" t="s">
+      <c r="U76" s="22"/>
+      <c r="V76" s="22"/>
+      <c r="W76" s="22"/>
+      <c r="X76" s="22"/>
+      <c r="Y76" s="22"/>
+      <c r="Z76" s="22"/>
+      <c r="AA76" s="22"/>
+      <c r="AB76" s="22"/>
+      <c r="AC76" s="22"/>
+      <c r="AD76" s="22"/>
+      <c r="AE76" s="22"/>
+      <c r="AF76" s="22"/>
+      <c r="AG76" s="22"/>
+      <c r="AH76" s="22"/>
+      <c r="AI76" s="22"/>
+      <c r="AJ76" s="22"/>
+      <c r="AK76" s="22"/>
+    </row>
+    <row r="77" spans="20:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T77" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="U72" s="22"/>
-      <c r="V72" s="22"/>
-      <c r="W72" s="22"/>
-      <c r="X72" s="22"/>
-      <c r="Y72" s="22"/>
-      <c r="Z72" s="22"/>
-      <c r="AA72" s="22"/>
-      <c r="AB72" s="22"/>
-      <c r="AC72" s="22"/>
-      <c r="AD72" s="22"/>
-      <c r="AE72" s="22"/>
-      <c r="AF72" s="22"/>
-      <c r="AG72" s="22"/>
-      <c r="AH72" s="22"/>
-      <c r="AI72" s="22"/>
-      <c r="AJ72" s="22"/>
-      <c r="AK72" s="22"/>
-    </row>
-    <row r="73" spans="20:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T73" s="21" t="s">
+      <c r="U77" s="21"/>
+      <c r="V77" s="21"/>
+      <c r="W77" s="21"/>
+      <c r="X77" s="21"/>
+      <c r="Y77" s="21"/>
+      <c r="Z77" s="21"/>
+      <c r="AA77" s="21"/>
+      <c r="AB77" s="21"/>
+      <c r="AC77" s="21"/>
+      <c r="AD77" s="21"/>
+      <c r="AE77" s="21"/>
+      <c r="AF77" s="21"/>
+      <c r="AG77" s="21"/>
+      <c r="AH77" s="21"/>
+      <c r="AI77" s="21"/>
+      <c r="AJ77" s="21"/>
+      <c r="AK77" s="21"/>
+    </row>
+    <row r="78" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T78" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="79" spans="20:37" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="T79" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="U73" s="21"/>
-      <c r="V73" s="21"/>
-      <c r="W73" s="21"/>
-      <c r="X73" s="21"/>
-      <c r="Y73" s="21"/>
-      <c r="Z73" s="21"/>
-      <c r="AA73" s="21"/>
-      <c r="AB73" s="21"/>
-      <c r="AC73" s="21"/>
-      <c r="AD73" s="21"/>
-      <c r="AE73" s="21"/>
-      <c r="AF73" s="21"/>
-      <c r="AG73" s="21"/>
-      <c r="AH73" s="21"/>
-      <c r="AI73" s="21"/>
-      <c r="AJ73" s="21"/>
-      <c r="AK73" s="21"/>
-    </row>
-    <row r="74" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T74" s="12" t="s">
+      <c r="U79" s="22"/>
+      <c r="V79" s="22"/>
+      <c r="W79" s="22"/>
+      <c r="X79" s="22"/>
+      <c r="Y79" s="22"/>
+      <c r="Z79" s="22"/>
+      <c r="AA79" s="22"/>
+      <c r="AB79" s="22"/>
+      <c r="AC79" s="22"/>
+      <c r="AD79" s="22"/>
+      <c r="AE79" s="22"/>
+      <c r="AF79" s="22"/>
+      <c r="AG79" s="22"/>
+      <c r="AH79" s="22"/>
+      <c r="AI79" s="22"/>
+      <c r="AJ79" s="22"/>
+      <c r="AK79" s="22"/>
+    </row>
+    <row r="80" spans="20:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T80" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="U80" s="21"/>
+      <c r="V80" s="21"/>
+      <c r="W80" s="21"/>
+      <c r="X80" s="21"/>
+      <c r="Y80" s="21"/>
+      <c r="Z80" s="21"/>
+      <c r="AA80" s="21"/>
+      <c r="AB80" s="21"/>
+      <c r="AC80" s="21"/>
+      <c r="AD80" s="21"/>
+      <c r="AE80" s="21"/>
+      <c r="AF80" s="21"/>
+      <c r="AG80" s="21"/>
+      <c r="AH80" s="21"/>
+      <c r="AI80" s="21"/>
+      <c r="AJ80" s="21"/>
+      <c r="AK80" s="21"/>
+    </row>
+    <row r="81" spans="20:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T81" s="12" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="75" spans="20:37" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="T75" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="U75" s="22"/>
-      <c r="V75" s="22"/>
-      <c r="W75" s="22"/>
-      <c r="X75" s="22"/>
-      <c r="Y75" s="22"/>
-      <c r="Z75" s="22"/>
-      <c r="AA75" s="22"/>
-      <c r="AB75" s="22"/>
-      <c r="AC75" s="22"/>
-      <c r="AD75" s="22"/>
-      <c r="AE75" s="22"/>
-      <c r="AF75" s="22"/>
-      <c r="AG75" s="22"/>
-      <c r="AH75" s="22"/>
-      <c r="AI75" s="22"/>
-      <c r="AJ75" s="22"/>
-      <c r="AK75" s="22"/>
-    </row>
-    <row r="76" spans="20:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T76" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="U76" s="21"/>
-      <c r="V76" s="21"/>
-      <c r="W76" s="21"/>
-      <c r="X76" s="21"/>
-      <c r="Y76" s="21"/>
-      <c r="Z76" s="21"/>
-      <c r="AA76" s="21"/>
-      <c r="AB76" s="21"/>
-      <c r="AC76" s="21"/>
-      <c r="AD76" s="21"/>
-      <c r="AE76" s="21"/>
-      <c r="AF76" s="21"/>
-      <c r="AG76" s="21"/>
-      <c r="AH76" s="21"/>
-      <c r="AI76" s="21"/>
-      <c r="AJ76" s="21"/>
-      <c r="AK76" s="21"/>
-    </row>
-    <row r="77" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T77" s="12" t="s">
-        <v>83</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="22">
+    <mergeCell ref="T70:AK70"/>
     <mergeCell ref="N6:Y6"/>
-    <mergeCell ref="T44:AI44"/>
-    <mergeCell ref="T41:AG41"/>
-    <mergeCell ref="T38:AK38"/>
-    <mergeCell ref="T66:AK66"/>
-    <mergeCell ref="B44:R44"/>
+    <mergeCell ref="T46:AI46"/>
+    <mergeCell ref="T43:AG43"/>
+    <mergeCell ref="T40:AK40"/>
+    <mergeCell ref="T68:AK68"/>
+    <mergeCell ref="B46:R46"/>
     <mergeCell ref="T25:AF25"/>
     <mergeCell ref="T23:AF23"/>
-    <mergeCell ref="T35:AF35"/>
+    <mergeCell ref="T37:AF37"/>
     <mergeCell ref="N8:AD8"/>
     <mergeCell ref="N10:AD10"/>
+    <mergeCell ref="T29:AF29"/>
+    <mergeCell ref="B18:AB18"/>
+    <mergeCell ref="T66:AK66"/>
+    <mergeCell ref="B61:R61"/>
     <mergeCell ref="T27:AF27"/>
-    <mergeCell ref="B18:AB18"/>
-    <mergeCell ref="T64:AK64"/>
-    <mergeCell ref="B59:R59"/>
-    <mergeCell ref="T70:AK70"/>
-    <mergeCell ref="T72:AK72"/>
-    <mergeCell ref="T73:AK73"/>
-    <mergeCell ref="T75:AK75"/>
+    <mergeCell ref="T74:AK74"/>
     <mergeCell ref="T76:AK76"/>
+    <mergeCell ref="T77:AK77"/>
+    <mergeCell ref="T79:AK79"/>
+    <mergeCell ref="T80:AK80"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -5023,7 +5119,7 @@
   <sheetData>
     <row r="2" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
@@ -5032,7 +5128,7 @@
     <row r="4" spans="1:36" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="B4" s="31" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C4" s="31"/>
       <c r="D4" s="31"/>
@@ -5042,7 +5138,7 @@
     <row r="5" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="L5" s="42" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M5" s="42"/>
       <c r="N5" s="42"/>
@@ -5051,18 +5147,18 @@
     </row>
     <row r="6" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
-      <c r="L6" s="69" t="s">
-        <v>131</v>
-      </c>
-      <c r="M6" s="69"/>
-      <c r="N6" s="69"/>
-      <c r="O6" s="69"/>
-      <c r="P6" s="69"/>
+      <c r="L6" s="70" t="s">
+        <v>129</v>
+      </c>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="70"/>
     </row>
     <row r="7" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="L7" s="63" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M7" s="63"/>
       <c r="N7" s="63"/>
@@ -5071,138 +5167,138 @@
     </row>
     <row r="8" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
-      <c r="L8" s="69" t="s">
-        <v>133</v>
-      </c>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="69"/>
-      <c r="P8" s="69"/>
+      <c r="L8" s="70" t="s">
+        <v>131</v>
+      </c>
+      <c r="M8" s="70"/>
+      <c r="N8" s="70"/>
+      <c r="O8" s="70"/>
+      <c r="P8" s="70"/>
     </row>
     <row r="9" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1"/>
-      <c r="L9" s="69" t="s">
-        <v>134</v>
-      </c>
-      <c r="M9" s="69"/>
-      <c r="N9" s="69"/>
-      <c r="O9" s="69"/>
-      <c r="P9" s="69"/>
-      <c r="R9" s="70"/>
-      <c r="S9" s="70"/>
-      <c r="T9" s="70"/>
-      <c r="U9" s="70"/>
-      <c r="V9" s="70"/>
-      <c r="W9" s="70"/>
-      <c r="X9" s="70"/>
-      <c r="Y9" s="70"/>
-      <c r="Z9" s="70"/>
+      <c r="L9" s="70" t="s">
+        <v>132</v>
+      </c>
+      <c r="M9" s="70"/>
+      <c r="N9" s="70"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="70"/>
+      <c r="R9" s="71"/>
+      <c r="S9" s="71"/>
+      <c r="T9" s="71"/>
+      <c r="U9" s="71"/>
+      <c r="V9" s="71"/>
+      <c r="W9" s="71"/>
+      <c r="X9" s="71"/>
+      <c r="Y9" s="71"/>
+      <c r="Z9" s="71"/>
     </row>
     <row r="10" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
       <c r="L10" s="63" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M10" s="63"/>
       <c r="N10" s="63"/>
       <c r="O10" s="63"/>
       <c r="P10" s="63"/>
-      <c r="R10" s="70"/>
-      <c r="S10" s="70"/>
-      <c r="T10" s="70"/>
-      <c r="U10" s="70"/>
-      <c r="V10" s="70"/>
-      <c r="W10" s="70"/>
-      <c r="X10" s="70"/>
-      <c r="Y10" s="70"/>
-      <c r="Z10" s="70"/>
+      <c r="R10" s="71"/>
+      <c r="S10" s="71"/>
+      <c r="T10" s="71"/>
+      <c r="U10" s="71"/>
+      <c r="V10" s="71"/>
+      <c r="W10" s="71"/>
+      <c r="X10" s="71"/>
+      <c r="Y10" s="71"/>
+      <c r="Z10" s="71"/>
     </row>
     <row r="11" spans="1:36" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
       <c r="L11" s="63" t="s">
-        <v>136</v>
-      </c>
-      <c r="M11" s="69"/>
-      <c r="N11" s="69"/>
-      <c r="O11" s="69"/>
-      <c r="P11" s="69"/>
-      <c r="R11" s="70"/>
-      <c r="S11" s="70"/>
-      <c r="T11" s="70"/>
-      <c r="U11" s="70"/>
-      <c r="V11" s="70"/>
-      <c r="W11" s="70"/>
-      <c r="X11" s="70"/>
-      <c r="Y11" s="70"/>
-      <c r="Z11" s="70"/>
+        <v>134</v>
+      </c>
+      <c r="M11" s="70"/>
+      <c r="N11" s="70"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="70"/>
+      <c r="R11" s="71"/>
+      <c r="S11" s="71"/>
+      <c r="T11" s="71"/>
+      <c r="U11" s="71"/>
+      <c r="V11" s="71"/>
+      <c r="W11" s="71"/>
+      <c r="X11" s="71"/>
+      <c r="Y11" s="71"/>
+      <c r="Z11" s="71"/>
     </row>
     <row r="12" spans="1:36" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1"/>
       <c r="L12" s="63" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M12" s="63"/>
       <c r="N12" s="63"/>
       <c r="O12" s="63"/>
       <c r="P12" s="63"/>
-      <c r="R12" s="70"/>
-      <c r="S12" s="70"/>
-      <c r="T12" s="70"/>
-      <c r="U12" s="70"/>
-      <c r="V12" s="70"/>
+      <c r="R12" s="71"/>
+      <c r="S12" s="71"/>
+      <c r="T12" s="71"/>
+      <c r="U12" s="71"/>
+      <c r="V12" s="71"/>
     </row>
     <row r="13" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
-      <c r="L13" s="69" t="s">
-        <v>138</v>
-      </c>
-      <c r="M13" s="69"/>
-      <c r="N13" s="69"/>
-      <c r="O13" s="69"/>
-      <c r="P13" s="69"/>
-      <c r="R13" s="70"/>
-      <c r="S13" s="70"/>
-      <c r="T13" s="70"/>
-      <c r="U13" s="70"/>
-      <c r="W13" s="73" t="s">
-        <v>149</v>
-      </c>
-      <c r="X13" s="73"/>
-      <c r="Y13" s="73"/>
-      <c r="Z13" s="73"/>
-      <c r="AA13" s="73"/>
-      <c r="AB13" s="73"/>
-      <c r="AC13" s="73"/>
-      <c r="AD13" s="73"/>
-      <c r="AE13" s="73"/>
-      <c r="AF13" s="73"/>
-      <c r="AG13" s="73"/>
-      <c r="AH13" s="73"/>
-      <c r="AI13" s="73"/>
-      <c r="AJ13" s="73"/>
+      <c r="L13" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="M13" s="70"/>
+      <c r="N13" s="70"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="70"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="71"/>
+      <c r="T13" s="71"/>
+      <c r="U13" s="71"/>
+      <c r="W13" s="74" t="s">
+        <v>147</v>
+      </c>
+      <c r="X13" s="74"/>
+      <c r="Y13" s="74"/>
+      <c r="Z13" s="74"/>
+      <c r="AA13" s="74"/>
+      <c r="AB13" s="74"/>
+      <c r="AC13" s="74"/>
+      <c r="AD13" s="74"/>
+      <c r="AE13" s="74"/>
+      <c r="AF13" s="74"/>
+      <c r="AG13" s="74"/>
+      <c r="AH13" s="74"/>
+      <c r="AI13" s="74"/>
+      <c r="AJ13" s="74"/>
     </row>
     <row r="14" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A14" s="1"/>
-      <c r="L14" s="69" t="s">
-        <v>139</v>
-      </c>
-      <c r="M14" s="69"/>
-      <c r="N14" s="69"/>
-      <c r="O14" s="69"/>
-      <c r="P14" s="69"/>
-      <c r="R14" s="70"/>
-      <c r="S14" s="70"/>
-      <c r="T14" s="70"/>
-      <c r="U14" s="70"/>
-      <c r="V14" s="70"/>
-      <c r="W14" s="70"/>
-      <c r="X14" s="70"/>
-      <c r="Y14" s="70"/>
-      <c r="Z14" s="70"/>
+      <c r="L14" s="70" t="s">
+        <v>137</v>
+      </c>
+      <c r="M14" s="70"/>
+      <c r="N14" s="70"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="70"/>
+      <c r="R14" s="71"/>
+      <c r="S14" s="71"/>
+      <c r="T14" s="71"/>
+      <c r="U14" s="71"/>
+      <c r="V14" s="71"/>
+      <c r="W14" s="71"/>
+      <c r="X14" s="71"/>
+      <c r="Y14" s="71"/>
+      <c r="Z14" s="71"/>
     </row>
     <row r="15" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
-      <c r="R15" s="71"/>
+      <c r="R15" s="72"/>
     </row>
     <row r="16" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
@@ -5210,12 +5306,12 @@
     <row r="17" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A17" s="1"/>
       <c r="L17" s="42" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M17" s="42"/>
       <c r="N17" s="42"/>
       <c r="O17" s="42" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P17" s="42"/>
       <c r="Q17" s="42"/>
@@ -5226,50 +5322,50 @@
     <row r="18" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
       <c r="L18" s="38" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="M18" s="38"/>
       <c r="N18" s="38"/>
-      <c r="O18" s="72" t="s">
-        <v>142</v>
-      </c>
-      <c r="P18" s="72"/>
-      <c r="Q18" s="72"/>
-      <c r="R18" s="72"/>
-      <c r="S18" s="72"/>
-      <c r="T18" s="72"/>
+      <c r="O18" s="73" t="s">
+        <v>140</v>
+      </c>
+      <c r="P18" s="73"/>
+      <c r="Q18" s="73"/>
+      <c r="R18" s="73"/>
+      <c r="S18" s="73"/>
+      <c r="T18" s="73"/>
     </row>
     <row r="19" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="L19" s="38" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="M19" s="38"/>
       <c r="N19" s="38"/>
-      <c r="O19" s="72" t="s">
-        <v>146</v>
-      </c>
-      <c r="P19" s="72"/>
-      <c r="Q19" s="72"/>
-      <c r="R19" s="72"/>
-      <c r="S19" s="72"/>
-      <c r="T19" s="72"/>
+      <c r="O19" s="73" t="s">
+        <v>144</v>
+      </c>
+      <c r="P19" s="73"/>
+      <c r="Q19" s="73"/>
+      <c r="R19" s="73"/>
+      <c r="S19" s="73"/>
+      <c r="T19" s="73"/>
     </row>
     <row r="20" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
       <c r="L20" s="38" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="M20" s="38"/>
       <c r="N20" s="38"/>
-      <c r="O20" s="72" t="s">
-        <v>148</v>
-      </c>
-      <c r="P20" s="72"/>
-      <c r="Q20" s="72"/>
-      <c r="R20" s="72"/>
-      <c r="S20" s="72"/>
-      <c r="T20" s="72"/>
+      <c r="O20" s="73" t="s">
+        <v>146</v>
+      </c>
+      <c r="P20" s="73"/>
+      <c r="Q20" s="73"/>
+      <c r="R20" s="73"/>
+      <c r="S20" s="73"/>
+      <c r="T20" s="73"/>
     </row>
     <row r="21" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A21" s="1"/>
@@ -5279,15 +5375,15 @@
     </row>
     <row r="23" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A23" s="1"/>
-      <c r="L23" s="68"/>
-      <c r="M23" s="68"/>
-      <c r="N23" s="68"/>
-      <c r="O23" s="67"/>
-      <c r="P23" s="67"/>
+      <c r="L23" s="69"/>
+      <c r="M23" s="69"/>
+      <c r="N23" s="69"/>
+      <c r="O23" s="68"/>
+      <c r="P23" s="68"/>
     </row>
     <row r="25" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B25" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
@@ -5295,12 +5391,12 @@
     </row>
     <row r="27" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B27" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B56" s="66" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
@@ -5308,17 +5404,17 @@
     </row>
     <row r="58" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="85" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B85" s="66" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="87" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B87" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="88" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
@@ -5326,87 +5422,87 @@
     </row>
     <row r="89" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B89" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="91" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B91" s="66" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="93" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B93" s="74" t="s">
+      <c r="B93" s="75" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B94" s="75" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B95" s="75" t="s">
         <v>156</v>
-      </c>
-    </row>
-    <row r="94" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B94" s="74" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="95" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B95" s="74" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="97" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B97" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="99" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B99" s="66" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="101" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B101" s="66" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="103" spans="2:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B103" s="75" t="s">
-        <v>163</v>
-      </c>
-      <c r="C103" s="75"/>
-      <c r="D103" s="75"/>
-      <c r="E103" s="75"/>
-      <c r="F103" s="75"/>
-      <c r="G103" s="75"/>
-      <c r="H103" s="75"/>
-      <c r="I103" s="75"/>
-      <c r="J103" s="75"/>
-      <c r="K103" s="75"/>
-      <c r="L103" s="75"/>
-      <c r="M103" s="75"/>
-      <c r="N103" s="75"/>
-      <c r="O103" s="75"/>
-      <c r="P103" s="75"/>
-      <c r="Q103" s="75"/>
-      <c r="R103" s="75"/>
-      <c r="S103" s="75"/>
-      <c r="T103" s="75"/>
-      <c r="U103" s="75"/>
-      <c r="V103" s="75"/>
-      <c r="W103" s="75"/>
-      <c r="X103" s="75"/>
-      <c r="Y103" s="75"/>
+      <c r="B103" s="76" t="s">
+        <v>161</v>
+      </c>
+      <c r="C103" s="76"/>
+      <c r="D103" s="76"/>
+      <c r="E103" s="76"/>
+      <c r="F103" s="76"/>
+      <c r="G103" s="76"/>
+      <c r="H103" s="76"/>
+      <c r="I103" s="76"/>
+      <c r="J103" s="76"/>
+      <c r="K103" s="76"/>
+      <c r="L103" s="76"/>
+      <c r="M103" s="76"/>
+      <c r="N103" s="76"/>
+      <c r="O103" s="76"/>
+      <c r="P103" s="76"/>
+      <c r="Q103" s="76"/>
+      <c r="R103" s="76"/>
+      <c r="S103" s="76"/>
+      <c r="T103" s="76"/>
+      <c r="U103" s="76"/>
+      <c r="V103" s="76"/>
+      <c r="W103" s="76"/>
+      <c r="X103" s="76"/>
+      <c r="Y103" s="76"/>
     </row>
     <row r="106" spans="2:25" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B106" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="108" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B108" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C108" s="8"/>
-      <c r="D108" s="76"/>
+      <c r="D108" s="77"/>
     </row>
     <row r="110" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B110" s="66" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="111" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
@@ -5414,45 +5510,45 @@
     </row>
     <row r="112" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B112" s="66" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="114" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B114" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="116" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B116" s="66" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="118" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B118" s="66" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="120" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B120" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="122" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B122" s="66" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="124" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B124" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="126" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B126" s="66" t="s">
-        <v>182</v>
-      </c>
-      <c r="L126" s="77" t="s">
-        <v>181</v>
+        <v>180</v>
+      </c>
+      <c r="L126" s="78" t="s">
+        <v>179</v>
       </c>
       <c r="M126" s="66"/>
     </row>
@@ -5498,16 +5594,16 @@
   <sheetData>
     <row r="2" spans="1:24" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="40" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C4" s="40"/>
       <c r="D4" s="52" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E4" s="53"/>
       <c r="F4" s="54"/>
@@ -5516,11 +5612,11 @@
       </c>
       <c r="H4" s="40"/>
       <c r="I4" s="40" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J4" s="40"/>
       <c r="K4" s="40" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L4" s="40"/>
       <c r="M4" s="40"/>
@@ -5536,7 +5632,7 @@
       <c r="U4" s="40"/>
       <c r="V4" s="40"/>
       <c r="W4" s="40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X4" s="40"/>
     </row>
@@ -5546,25 +5642,25 @@
       </c>
       <c r="C5" s="50"/>
       <c r="D5" s="55" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E5" s="56"/>
       <c r="F5" s="57"/>
       <c r="G5" s="61" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H5" s="61"/>
       <c r="I5" s="51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J5" s="51"/>
       <c r="K5" s="64" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L5" s="64"/>
       <c r="M5" s="64"/>
       <c r="N5" s="63" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="O5" s="63"/>
       <c r="P5" s="63"/>
@@ -5575,7 +5671,7 @@
       <c r="U5" s="63"/>
       <c r="V5" s="63"/>
       <c r="W5" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X5" s="64"/>
     </row>
@@ -5585,25 +5681,25 @@
       </c>
       <c r="C6" s="50"/>
       <c r="D6" s="55" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E6" s="56"/>
       <c r="F6" s="57"/>
       <c r="G6" s="62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H6" s="62"/>
       <c r="I6" s="51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J6" s="51"/>
       <c r="K6" s="64" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L6" s="64"/>
       <c r="M6" s="64"/>
       <c r="N6" s="63" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
@@ -5614,7 +5710,7 @@
       <c r="U6" s="63"/>
       <c r="V6" s="63"/>
       <c r="W6" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X6" s="64"/>
     </row>
@@ -5624,16 +5720,16 @@
       </c>
       <c r="C7" s="50"/>
       <c r="D7" s="55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" s="56"/>
       <c r="F7" s="57"/>
       <c r="G7" s="61" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H7" s="61"/>
       <c r="I7" s="51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J7" s="51"/>
       <c r="K7" s="64" t="s">
@@ -5642,7 +5738,7 @@
       <c r="L7" s="64"/>
       <c r="M7" s="64"/>
       <c r="N7" s="63" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="O7" s="63"/>
       <c r="P7" s="63"/>
@@ -5653,7 +5749,7 @@
       <c r="U7" s="63"/>
       <c r="V7" s="63"/>
       <c r="W7" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X7" s="64"/>
     </row>
@@ -5663,16 +5759,16 @@
       </c>
       <c r="C8" s="50"/>
       <c r="D8" s="55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" s="56"/>
       <c r="F8" s="57"/>
       <c r="G8" s="61" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H8" s="61"/>
       <c r="I8" s="51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J8" s="51"/>
       <c r="K8" s="64" t="s">
@@ -5681,7 +5777,7 @@
       <c r="L8" s="64"/>
       <c r="M8" s="64"/>
       <c r="N8" s="63" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="O8" s="63"/>
       <c r="P8" s="63"/>
@@ -5692,7 +5788,7 @@
       <c r="U8" s="63"/>
       <c r="V8" s="63"/>
       <c r="W8" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X8" s="64"/>
     </row>
@@ -5702,16 +5798,16 @@
       </c>
       <c r="C9" s="50"/>
       <c r="D9" s="55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" s="56"/>
       <c r="F9" s="57"/>
       <c r="G9" s="61" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H9" s="61"/>
       <c r="I9" s="51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J9" s="51"/>
       <c r="K9" s="64" t="s">
@@ -5720,7 +5816,7 @@
       <c r="L9" s="64"/>
       <c r="M9" s="64"/>
       <c r="N9" s="63" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="O9" s="63"/>
       <c r="P9" s="63"/>
@@ -5731,7 +5827,7 @@
       <c r="U9" s="63"/>
       <c r="V9" s="63"/>
       <c r="W9" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X9" s="64"/>
     </row>
@@ -5741,16 +5837,16 @@
       </c>
       <c r="C10" s="50"/>
       <c r="D10" s="55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E10" s="56"/>
       <c r="F10" s="57"/>
       <c r="G10" s="61" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H10" s="61"/>
       <c r="I10" s="51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J10" s="51"/>
       <c r="K10" s="64" t="s">
@@ -5759,7 +5855,7 @@
       <c r="L10" s="64"/>
       <c r="M10" s="64"/>
       <c r="N10" s="63" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="O10" s="63"/>
       <c r="P10" s="63"/>
@@ -5770,7 +5866,7 @@
       <c r="U10" s="63"/>
       <c r="V10" s="63"/>
       <c r="W10" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X10" s="64"/>
     </row>
@@ -5780,16 +5876,16 @@
       </c>
       <c r="C11" s="50"/>
       <c r="D11" s="55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" s="56"/>
       <c r="F11" s="57"/>
       <c r="G11" s="61" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H11" s="61"/>
       <c r="I11" s="51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J11" s="51"/>
       <c r="K11" s="64" t="s">
@@ -5798,7 +5894,7 @@
       <c r="L11" s="64"/>
       <c r="M11" s="64"/>
       <c r="N11" s="63" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="O11" s="63"/>
       <c r="P11" s="63"/>
@@ -5809,7 +5905,7 @@
       <c r="U11" s="63"/>
       <c r="V11" s="63"/>
       <c r="W11" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X11" s="64"/>
     </row>
@@ -5819,16 +5915,16 @@
       </c>
       <c r="C12" s="50"/>
       <c r="D12" s="58" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E12" s="59"/>
       <c r="F12" s="60"/>
       <c r="G12" s="61" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H12" s="61"/>
       <c r="I12" s="51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J12" s="51"/>
       <c r="K12" s="64" t="s">
@@ -5837,7 +5933,7 @@
       <c r="L12" s="64"/>
       <c r="M12" s="64"/>
       <c r="N12" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="O12" s="63"/>
       <c r="P12" s="63"/>
@@ -5848,7 +5944,7 @@
       <c r="U12" s="63"/>
       <c r="V12" s="63"/>
       <c r="W12" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X12" s="64"/>
     </row>
@@ -5858,16 +5954,16 @@
       </c>
       <c r="C13" s="50"/>
       <c r="D13" s="55" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E13" s="56"/>
       <c r="F13" s="57"/>
       <c r="G13" s="61" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H13" s="61"/>
       <c r="I13" s="51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J13" s="51"/>
       <c r="K13" s="64" t="s">
@@ -5876,7 +5972,7 @@
       <c r="L13" s="64"/>
       <c r="M13" s="64"/>
       <c r="N13" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="O13" s="63"/>
       <c r="P13" s="63"/>
@@ -5887,7 +5983,7 @@
       <c r="U13" s="63"/>
       <c r="V13" s="63"/>
       <c r="W13" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X13" s="64"/>
     </row>
@@ -5897,16 +5993,16 @@
       </c>
       <c r="C14" s="50"/>
       <c r="D14" s="55" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E14" s="56"/>
       <c r="F14" s="57"/>
       <c r="G14" s="61" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H14" s="61"/>
       <c r="I14" s="51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J14" s="51"/>
       <c r="K14" s="64" t="s">
@@ -5915,7 +6011,7 @@
       <c r="L14" s="64"/>
       <c r="M14" s="64"/>
       <c r="N14" s="63" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="O14" s="63"/>
       <c r="P14" s="63"/>
@@ -5926,7 +6022,7 @@
       <c r="U14" s="63"/>
       <c r="V14" s="63"/>
       <c r="W14" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X14" s="64"/>
     </row>
@@ -5936,16 +6032,16 @@
       </c>
       <c r="C15" s="50"/>
       <c r="D15" s="55" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E15" s="56"/>
       <c r="F15" s="57"/>
       <c r="G15" s="61" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H15" s="61"/>
       <c r="I15" s="51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J15" s="51"/>
       <c r="K15" s="64" t="s">
@@ -5954,7 +6050,7 @@
       <c r="L15" s="64"/>
       <c r="M15" s="64"/>
       <c r="N15" s="63" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="O15" s="63"/>
       <c r="P15" s="63"/>
@@ -5965,7 +6061,7 @@
       <c r="U15" s="63"/>
       <c r="V15" s="63"/>
       <c r="W15" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X15" s="64"/>
     </row>
@@ -5975,16 +6071,16 @@
       </c>
       <c r="C16" s="50"/>
       <c r="D16" s="55" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E16" s="56"/>
       <c r="F16" s="57"/>
       <c r="G16" s="61" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H16" s="61"/>
       <c r="I16" s="51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J16" s="51"/>
       <c r="K16" s="64" t="s">
@@ -5993,7 +6089,7 @@
       <c r="L16" s="64"/>
       <c r="M16" s="64"/>
       <c r="N16" s="63" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="O16" s="63"/>
       <c r="P16" s="63"/>
@@ -6004,7 +6100,7 @@
       <c r="U16" s="63"/>
       <c r="V16" s="63"/>
       <c r="W16" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X16" s="64"/>
     </row>
@@ -6014,25 +6110,25 @@
       </c>
       <c r="C17" s="50"/>
       <c r="D17" s="55" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E17" s="56"/>
       <c r="F17" s="57"/>
       <c r="G17" s="62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H17" s="62"/>
       <c r="I17" s="51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J17" s="51"/>
       <c r="K17" s="64" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L17" s="64"/>
       <c r="M17" s="64"/>
       <c r="N17" s="63" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O17" s="63"/>
       <c r="P17" s="63"/>
@@ -6043,7 +6139,7 @@
       <c r="U17" s="63"/>
       <c r="V17" s="63"/>
       <c r="W17" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X17" s="64"/>
     </row>
@@ -6053,25 +6149,25 @@
       </c>
       <c r="C18" s="50"/>
       <c r="D18" s="55" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E18" s="56"/>
       <c r="F18" s="57"/>
       <c r="G18" s="62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H18" s="62"/>
       <c r="I18" s="51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J18" s="51"/>
       <c r="K18" s="64" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L18" s="64"/>
       <c r="M18" s="64"/>
       <c r="N18" s="63" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O18" s="63"/>
       <c r="P18" s="63"/>
@@ -6082,7 +6178,7 @@
       <c r="U18" s="63"/>
       <c r="V18" s="63"/>
       <c r="W18" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X18" s="64"/>
     </row>
@@ -6092,25 +6188,25 @@
       </c>
       <c r="C19" s="50"/>
       <c r="D19" s="55" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E19" s="56"/>
       <c r="F19" s="57"/>
       <c r="G19" s="62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H19" s="62"/>
       <c r="I19" s="51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J19" s="51"/>
       <c r="K19" s="64" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L19" s="64"/>
       <c r="M19" s="64"/>
       <c r="N19" s="63" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O19" s="63"/>
       <c r="P19" s="63"/>
@@ -6121,7 +6217,7 @@
       <c r="U19" s="63"/>
       <c r="V19" s="63"/>
       <c r="W19" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X19" s="64"/>
     </row>
@@ -6131,12 +6227,12 @@
       </c>
       <c r="C20" s="50"/>
       <c r="D20" s="55" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E20" s="56"/>
       <c r="F20" s="57"/>
       <c r="G20" s="62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H20" s="62"/>
       <c r="I20" s="65" t="s">
@@ -6144,12 +6240,12 @@
       </c>
       <c r="J20" s="65"/>
       <c r="K20" s="64" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L20" s="64"/>
       <c r="M20" s="64"/>
       <c r="N20" s="63" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O20" s="63"/>
       <c r="P20" s="63"/>
@@ -6160,7 +6256,7 @@
       <c r="U20" s="63"/>
       <c r="V20" s="63"/>
       <c r="W20" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X20" s="64"/>
     </row>
@@ -6170,12 +6266,12 @@
       </c>
       <c r="C21" s="50"/>
       <c r="D21" s="55" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E21" s="56"/>
       <c r="F21" s="57"/>
       <c r="G21" s="62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H21" s="62"/>
       <c r="I21" s="65" t="s">
@@ -6183,12 +6279,12 @@
       </c>
       <c r="J21" s="65"/>
       <c r="K21" s="64" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L21" s="64"/>
       <c r="M21" s="64"/>
       <c r="N21" s="63" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O21" s="63"/>
       <c r="P21" s="63"/>
@@ -6199,7 +6295,7 @@
       <c r="U21" s="63"/>
       <c r="V21" s="63"/>
       <c r="W21" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X21" s="64"/>
     </row>
@@ -6209,12 +6305,12 @@
       </c>
       <c r="C22" s="50"/>
       <c r="D22" s="55" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E22" s="56"/>
       <c r="F22" s="57"/>
       <c r="G22" s="62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H22" s="62"/>
       <c r="I22" s="65" t="s">
@@ -6222,12 +6318,12 @@
       </c>
       <c r="J22" s="65"/>
       <c r="K22" s="64" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L22" s="64"/>
       <c r="M22" s="64"/>
       <c r="N22" s="63" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O22" s="63"/>
       <c r="P22" s="63"/>
@@ -6238,7 +6334,7 @@
       <c r="U22" s="63"/>
       <c r="V22" s="63"/>
       <c r="W22" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X22" s="64"/>
     </row>
@@ -6248,12 +6344,12 @@
       </c>
       <c r="C23" s="50"/>
       <c r="D23" s="55" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E23" s="56"/>
       <c r="F23" s="57"/>
       <c r="G23" s="62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H23" s="62"/>
       <c r="I23" s="65" t="s">
@@ -6261,12 +6357,12 @@
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="64" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L23" s="64"/>
       <c r="M23" s="64"/>
       <c r="N23" s="63" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O23" s="63"/>
       <c r="P23" s="63"/>
@@ -6277,7 +6373,7 @@
       <c r="U23" s="63"/>
       <c r="V23" s="63"/>
       <c r="W23" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X23" s="64"/>
     </row>
@@ -6287,12 +6383,12 @@
       </c>
       <c r="C24" s="50"/>
       <c r="D24" s="55" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E24" s="56"/>
       <c r="F24" s="57"/>
       <c r="G24" s="62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H24" s="62"/>
       <c r="I24" s="65" t="s">
@@ -6300,12 +6396,12 @@
       </c>
       <c r="J24" s="65"/>
       <c r="K24" s="64" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L24" s="64"/>
       <c r="M24" s="64"/>
       <c r="N24" s="63" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O24" s="63"/>
       <c r="P24" s="63"/>
@@ -6316,7 +6412,7 @@
       <c r="U24" s="63"/>
       <c r="V24" s="63"/>
       <c r="W24" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X24" s="64"/>
     </row>
@@ -6326,12 +6422,12 @@
       </c>
       <c r="C25" s="50"/>
       <c r="D25" s="55" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E25" s="56"/>
       <c r="F25" s="57"/>
       <c r="G25" s="62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H25" s="62"/>
       <c r="I25" s="65" t="s">
@@ -6339,12 +6435,12 @@
       </c>
       <c r="J25" s="65"/>
       <c r="K25" s="64" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L25" s="64"/>
       <c r="M25" s="64"/>
       <c r="N25" s="63" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O25" s="63"/>
       <c r="P25" s="63"/>
@@ -6355,7 +6451,7 @@
       <c r="U25" s="63"/>
       <c r="V25" s="63"/>
       <c r="W25" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X25" s="64"/>
     </row>
@@ -6365,12 +6461,12 @@
       </c>
       <c r="C26" s="50"/>
       <c r="D26" s="55" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E26" s="56"/>
       <c r="F26" s="57"/>
       <c r="G26" s="62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H26" s="62"/>
       <c r="I26" s="65" t="s">
@@ -6378,12 +6474,12 @@
       </c>
       <c r="J26" s="65"/>
       <c r="K26" s="64" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L26" s="64"/>
       <c r="M26" s="64"/>
       <c r="N26" s="63" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O26" s="63"/>
       <c r="P26" s="63"/>
@@ -6394,7 +6490,7 @@
       <c r="U26" s="63"/>
       <c r="V26" s="63"/>
       <c r="W26" s="64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="X26" s="64"/>
     </row>
@@ -6585,7 +6681,7 @@
   <sheetData>
     <row r="2" spans="1:1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD0BA7F-5BA2-4A4D-A24F-D5401773BDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0E0BFC-31B1-496E-9817-B390EFBE13EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="187">
   <si>
     <t>SIGNOMALY</t>
   </si>
@@ -336,9 +336,6 @@
     <t>II. CORELOOP_WIN/LOSE CONDITIONS</t>
   </si>
   <si>
-    <t>Độ phù hợp với theme:</t>
-  </si>
-  <si>
     <t>2.1. Puzzle giải đố</t>
   </si>
   <si>
@@ -1855,6 +1852,36 @@
   </si>
   <si>
     <t>Phần Puzzle UI này sẽ không cần nhìn vào #tờ hướng dẫn. Mà sẽ hiển thị #hướng dẫn trực tiếp trên màn hình, và có nút back về. Nếu đưa đồ vật không phù hợp, thì sẽ không thể vào Puzzle UI mà sẽ hiển thị chữ: "This item is not correct!".</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Style: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Low-Poly</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Độ phù hợp với theme: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Các sự kiện bất thường trong phòng chính là tín hiệu mà người chơi phải nhận ra. Gameplay xoay quanh việc giải mã và xử lý tín hiệu để sinh tồn. Yếu tố thời gian và sự thay đổi liên tục khiến tín hiệu trở thành cơ chế trung tâm, không chỉ là chi tiết phụ.</t>
+    </r>
+  </si>
+  <si>
+    <t>Item List'!A1</t>
   </si>
 </sst>
 </file>
@@ -1981,6 +2008,7 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
       <u/>
       <sz val="15"/>
       <color theme="10"/>
@@ -2073,7 +2101,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2280,6 +2308,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -3493,7 +3525,7 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:Z31"/>
+  <dimension ref="A1:Z32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:26" ht="46.5" x14ac:dyDescent="0.7">
@@ -3581,99 +3613,83 @@
       <c r="I11" s="33"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="37" t="s">
+    <row r="12" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="78" t="s">
+        <v>184</v>
+      </c>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="78"/>
+    </row>
+    <row r="13" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37"/>
-      <c r="K12" s="37"/>
-      <c r="L12" s="37"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
-      <c r="S12" s="37"/>
-      <c r="T12" s="37"/>
-      <c r="U12" s="37"/>
-    </row>
-    <row r="13" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="36" t="s">
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="37"/>
+      <c r="O13" s="37"/>
+      <c r="P13" s="37"/>
+      <c r="Q13" s="37"/>
+      <c r="R13" s="37"/>
+      <c r="S13" s="37"/>
+      <c r="T13" s="37"/>
+      <c r="U13" s="37"/>
+    </row>
+    <row r="14" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
-      <c r="S13" s="36"/>
-      <c r="T13" s="36"/>
-      <c r="U13" s="36"/>
-    </row>
-    <row r="14" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="36"/>
+      <c r="L14" s="36"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
+      <c r="S14" s="36"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="36"/>
+    </row>
+    <row r="15" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:26" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
-      <c r="T15" s="34"/>
-      <c r="U15" s="34"/>
-      <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
-      <c r="X15" s="6"/>
-      <c r="Y15" s="6"/>
-      <c r="Z15" s="6"/>
-    </row>
-    <row r="16" spans="1:26" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:26" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="C16" s="34"/>
       <c r="D16" s="34"/>
@@ -3694,106 +3710,122 @@
       <c r="S16" s="34"/>
       <c r="T16" s="34"/>
       <c r="U16" s="34"/>
-    </row>
-    <row r="17" spans="1:21" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="36" t="s">
+      <c r="V16" s="6"/>
+      <c r="W16" s="6"/>
+      <c r="X16" s="6"/>
+      <c r="Y16" s="6"/>
+      <c r="Z16" s="6"/>
+    </row>
+    <row r="17" spans="1:21" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="34"/>
+      <c r="S17" s="34"/>
+      <c r="T17" s="34"/>
+      <c r="U17" s="34"/>
+    </row>
+    <row r="18" spans="1:21" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="36"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36"/>
-      <c r="T17" s="36"/>
-      <c r="U17" s="36"/>
-    </row>
-    <row r="18" spans="1:21" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="25" t="s">
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
+      <c r="S18" s="36"/>
+      <c r="T18" s="36"/>
+      <c r="U18" s="36"/>
+    </row>
+    <row r="19" spans="1:21" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="28"/>
-      <c r="M18" s="28"/>
-      <c r="N18" s="28"/>
-      <c r="O18" s="28"/>
-      <c r="P18" s="28"/>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="28"/>
-      <c r="U18" s="28"/>
-    </row>
-    <row r="19" spans="1:21" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B19" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="31"/>
-      <c r="O19" s="31"/>
-      <c r="P19" s="31"/>
-      <c r="Q19" s="31"/>
-      <c r="R19" s="31"/>
-      <c r="S19" s="31"/>
-      <c r="T19" s="31"/>
-      <c r="U19" s="31"/>
-    </row>
-    <row r="21" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A21" s="1" t="s">
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="28"/>
+    </row>
+    <row r="20" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="22"/>
+      <c r="S20" s="22"/>
+      <c r="T20" s="22"/>
+      <c r="U20" s="22"/>
+    </row>
+    <row r="22" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A22" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B23" s="8" t="s">
+    <row r="24" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B24" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B25" s="7" t="s">
+    <row r="26" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B26" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-    </row>
-    <row r="26" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
@@ -3806,9 +3838,7 @@
       <c r="L26" s="7"/>
     </row>
     <row r="27" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B27" s="8" t="s">
-        <v>38</v>
-      </c>
+      <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
@@ -3821,7 +3851,9 @@
       <c r="L27" s="7"/>
     </row>
     <row r="28" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B28" s="7"/>
+      <c r="B28" s="8" t="s">
+        <v>38</v>
+      </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
@@ -3834,9 +3866,7 @@
       <c r="L28" s="7"/>
     </row>
     <row r="29" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B29" s="14" t="s">
-        <v>51</v>
-      </c>
+      <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
@@ -3849,8 +3879,8 @@
       <c r="L29" s="7"/>
     </row>
     <row r="30" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B30" s="9" t="s">
-        <v>39</v>
+      <c r="B30" s="14" t="s">
+        <v>50</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -3864,7 +3894,9 @@
       <c r="L30" s="7"/>
     </row>
     <row r="31" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B31" s="9"/>
+      <c r="B31" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
@@ -3876,19 +3908,33 @@
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
     </row>
+    <row r="32" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B32" s="9"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A1:U1"/>
+    <mergeCell ref="B18:U18"/>
     <mergeCell ref="B17:U17"/>
-    <mergeCell ref="B16:U16"/>
-    <mergeCell ref="B18:U18"/>
+    <mergeCell ref="B19:U19"/>
+    <mergeCell ref="B14:U14"/>
     <mergeCell ref="B13:U13"/>
-    <mergeCell ref="B12:U12"/>
-    <mergeCell ref="B19:U19"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B20:U20"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B15:U15"/>
+    <mergeCell ref="B16:U16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3904,7 +3950,7 @@
   <sheetData>
     <row r="2" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B2" s="8"/>
     </row>
@@ -3965,7 +4011,7 @@
       <c r="K5" s="41"/>
       <c r="L5" s="41"/>
       <c r="M5" s="46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N5" s="46"/>
       <c r="O5" s="46"/>
@@ -3999,7 +4045,7 @@
       <c r="K6" s="41"/>
       <c r="L6" s="41"/>
       <c r="M6" s="47" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N6" s="46"/>
       <c r="O6" s="46"/>
@@ -4025,7 +4071,7 @@
       </c>
       <c r="F7" s="39"/>
       <c r="G7" s="41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H7" s="41"/>
       <c r="I7" s="41"/>
@@ -4033,7 +4079,7 @@
       <c r="K7" s="41"/>
       <c r="L7" s="41"/>
       <c r="M7" s="44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N7" s="44"/>
       <c r="O7" s="44"/>
@@ -4069,7 +4115,7 @@
       <c r="K8" s="41"/>
       <c r="L8" s="41"/>
       <c r="M8" s="43" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N8" s="44"/>
       <c r="O8" s="44"/>
@@ -4103,7 +4149,7 @@
       <c r="K9" s="41"/>
       <c r="L9" s="41"/>
       <c r="M9" s="43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N9" s="44"/>
       <c r="O9" s="44"/>
@@ -4137,7 +4183,7 @@
       <c r="K10" s="41"/>
       <c r="L10" s="41"/>
       <c r="M10" s="43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N10" s="44"/>
       <c r="O10" s="44"/>
@@ -4171,7 +4217,7 @@
       <c r="K11" s="41"/>
       <c r="L11" s="41"/>
       <c r="M11" s="44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N11" s="44"/>
       <c r="O11" s="44"/>
@@ -4207,7 +4253,7 @@
       <c r="K12" s="41"/>
       <c r="L12" s="41"/>
       <c r="M12" s="44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N12" s="44"/>
       <c r="O12" s="44"/>
@@ -4225,7 +4271,7 @@
     <row r="46" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B56" s="45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C56" s="45"/>
       <c r="D56" s="45"/>
@@ -4306,17 +4352,17 @@
   <sheetData>
     <row r="2" spans="1:30" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="19.5" x14ac:dyDescent="0.25">
       <c r="N6" s="23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O6" s="23"/>
       <c r="P6" s="23"/>
@@ -4346,7 +4392,7 @@
     </row>
     <row r="8" spans="1:30" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N8" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O8" s="25"/>
       <c r="P8" s="25"/>
@@ -4381,7 +4427,7 @@
     </row>
     <row r="10" spans="1:30" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N10" s="25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O10" s="28"/>
       <c r="P10" s="28"/>
@@ -4405,7 +4451,7 @@
     </row>
     <row r="16" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B16" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
@@ -4413,7 +4459,7 @@
     </row>
     <row r="18" spans="2:33" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C18" s="30"/>
       <c r="D18" s="30"/>
@@ -4470,13 +4516,13 @@
     </row>
     <row r="21" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="10"/>
     </row>
     <row r="23" spans="2:33" ht="19.5" x14ac:dyDescent="0.25">
       <c r="T23" s="24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U23" s="24"/>
       <c r="V23" s="24"/>
@@ -4496,7 +4542,7 @@
     </row>
     <row r="25" spans="2:33" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T25" s="48" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="U25" s="21"/>
       <c r="V25" s="21"/>
@@ -4530,7 +4576,7 @@
     </row>
     <row r="27" spans="2:33" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T27" s="48" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="U27" s="48"/>
       <c r="V27" s="48"/>
@@ -4564,7 +4610,7 @@
     </row>
     <row r="29" spans="2:33" ht="19.5" x14ac:dyDescent="0.25">
       <c r="T29" s="24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="U29" s="24"/>
       <c r="V29" s="24"/>
@@ -4584,12 +4630,12 @@
     </row>
     <row r="31" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T31" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T32" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
@@ -4597,7 +4643,7 @@
     </row>
     <row r="34" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T34" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="U34" s="8"/>
       <c r="V34" s="8"/>
@@ -4607,7 +4653,7 @@
     </row>
     <row r="36" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T36" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U36" s="12"/>
       <c r="V36" s="12"/>
@@ -4624,7 +4670,7 @@
     </row>
     <row r="37" spans="2:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T37" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="U37" s="25"/>
       <c r="V37" s="25"/>
@@ -4641,7 +4687,7 @@
     </row>
     <row r="39" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T39" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="U39" s="12"/>
       <c r="V39" s="12"/>
@@ -4658,7 +4704,7 @@
     </row>
     <row r="40" spans="2:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T40" s="25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="U40" s="25"/>
       <c r="V40" s="25"/>
@@ -4680,17 +4726,17 @@
     </row>
     <row r="41" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T41" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T42" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="2:37" ht="19.5" x14ac:dyDescent="0.25">
       <c r="T43" s="24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U43" s="24"/>
       <c r="V43" s="24"/>
@@ -4708,17 +4754,17 @@
     </row>
     <row r="44" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T44" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T45" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B46" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46" s="27"/>
       <c r="D46" s="27"/>
@@ -4737,7 +4783,7 @@
       <c r="Q46" s="27"/>
       <c r="R46" s="27"/>
       <c r="T46" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="U46" s="24"/>
       <c r="V46" s="24"/>
@@ -4757,37 +4803,37 @@
     </row>
     <row r="47" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T47" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T48" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T49" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T50" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T51" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T52" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T53" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="54" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
@@ -4813,7 +4859,7 @@
     </row>
     <row r="61" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B61" s="49" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C61" s="27"/>
       <c r="D61" s="27"/>
@@ -4841,12 +4887,12 @@
     </row>
     <row r="64" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B64" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="20:37" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T66" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U66" s="21"/>
       <c r="V66" s="21"/>
@@ -4868,7 +4914,7 @@
     </row>
     <row r="68" spans="20:37" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T68" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="U68" s="21"/>
       <c r="V68" s="21"/>
@@ -4910,7 +4956,7 @@
     </row>
     <row r="70" spans="20:37" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T70" s="48" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="U70" s="48"/>
       <c r="V70" s="48"/>
@@ -4932,7 +4978,7 @@
     </row>
     <row r="72" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T72" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
@@ -4940,7 +4986,7 @@
     </row>
     <row r="74" spans="20:37" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T74" s="48" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="U74" s="21"/>
       <c r="V74" s="21"/>
@@ -4982,7 +5028,7 @@
     </row>
     <row r="76" spans="20:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T76" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U76" s="22"/>
       <c r="V76" s="22"/>
@@ -5004,7 +5050,7 @@
     </row>
     <row r="77" spans="20:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T77" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="U77" s="21"/>
       <c r="V77" s="21"/>
@@ -5026,12 +5072,12 @@
     </row>
     <row r="78" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T78" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" spans="20:37" ht="19.5" x14ac:dyDescent="0.25">
       <c r="T79" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="U79" s="22"/>
       <c r="V79" s="22"/>
@@ -5053,7 +5099,7 @@
     </row>
     <row r="80" spans="20:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T80" s="21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U80" s="21"/>
       <c r="V80" s="21"/>
@@ -5075,7 +5121,7 @@
     </row>
     <row r="81" spans="20:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T81" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -5119,7 +5165,7 @@
   <sheetData>
     <row r="2" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
@@ -5128,7 +5174,7 @@
     <row r="4" spans="1:36" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="B4" s="31" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="31"/>
       <c r="D4" s="31"/>
@@ -5138,7 +5184,7 @@
     <row r="5" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="L5" s="42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M5" s="42"/>
       <c r="N5" s="42"/>
@@ -5148,7 +5194,7 @@
     <row r="6" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
       <c r="L6" s="70" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M6" s="70"/>
       <c r="N6" s="70"/>
@@ -5158,7 +5204,7 @@
     <row r="7" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="L7" s="63" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M7" s="63"/>
       <c r="N7" s="63"/>
@@ -5168,7 +5214,7 @@
     <row r="8" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
       <c r="L8" s="70" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M8" s="70"/>
       <c r="N8" s="70"/>
@@ -5178,7 +5224,7 @@
     <row r="9" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1"/>
       <c r="L9" s="70" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M9" s="70"/>
       <c r="N9" s="70"/>
@@ -5197,7 +5243,7 @@
     <row r="10" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
       <c r="L10" s="63" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M10" s="63"/>
       <c r="N10" s="63"/>
@@ -5216,7 +5262,7 @@
     <row r="11" spans="1:36" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
       <c r="L11" s="63" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="M11" s="70"/>
       <c r="N11" s="70"/>
@@ -5235,7 +5281,7 @@
     <row r="12" spans="1:36" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1"/>
       <c r="L12" s="63" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M12" s="63"/>
       <c r="N12" s="63"/>
@@ -5250,7 +5296,7 @@
     <row r="13" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="L13" s="70" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M13" s="70"/>
       <c r="N13" s="70"/>
@@ -5261,7 +5307,7 @@
       <c r="T13" s="71"/>
       <c r="U13" s="71"/>
       <c r="W13" s="74" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="X13" s="74"/>
       <c r="Y13" s="74"/>
@@ -5280,7 +5326,7 @@
     <row r="14" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A14" s="1"/>
       <c r="L14" s="70" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M14" s="70"/>
       <c r="N14" s="70"/>
@@ -5306,12 +5352,12 @@
     <row r="17" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A17" s="1"/>
       <c r="L17" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M17" s="42"/>
       <c r="N17" s="42"/>
       <c r="O17" s="42" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P17" s="42"/>
       <c r="Q17" s="42"/>
@@ -5322,12 +5368,12 @@
     <row r="18" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
       <c r="L18" s="38" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M18" s="38"/>
       <c r="N18" s="38"/>
       <c r="O18" s="73" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P18" s="73"/>
       <c r="Q18" s="73"/>
@@ -5338,12 +5384,12 @@
     <row r="19" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="L19" s="38" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="M19" s="38"/>
       <c r="N19" s="38"/>
       <c r="O19" s="73" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P19" s="73"/>
       <c r="Q19" s="73"/>
@@ -5354,12 +5400,12 @@
     <row r="20" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
       <c r="L20" s="38" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M20" s="38"/>
       <c r="N20" s="38"/>
       <c r="O20" s="73" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P20" s="73"/>
       <c r="Q20" s="73"/>
@@ -5383,7 +5429,7 @@
     </row>
     <row r="25" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B25" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
@@ -5391,12 +5437,12 @@
     </row>
     <row r="27" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B27" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="56" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B56" s="66" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
@@ -5404,17 +5450,17 @@
     </row>
     <row r="58" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="85" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B85" s="66" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="87" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B87" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="88" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
@@ -5422,47 +5468,47 @@
     </row>
     <row r="89" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B89" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="91" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B91" s="66" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="93" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B93" s="75" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="94" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B94" s="75" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="95" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B95" s="75" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="97" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B97" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="99" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B99" s="66" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="101" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B101" s="66" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="103" spans="2:25" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B103" s="76" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C103" s="76"/>
       <c r="D103" s="76"/>
@@ -5490,19 +5536,19 @@
     </row>
     <row r="106" spans="2:25" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B106" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="108" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B108" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C108" s="8"/>
       <c r="D108" s="77"/>
     </row>
     <row r="110" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B110" s="66" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="111" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
@@ -5510,45 +5556,48 @@
     </row>
     <row r="112" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B112" s="66" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="114" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B114" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="116" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B116" s="66" t="s">
+        <v>170</v>
+      </c>
+      <c r="AC116" s="79" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="118" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B118" s="66" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="120" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B120" s="8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="122" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B122" s="66" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="124" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B124" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="126" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B126" s="66" t="s">
+        <v>179</v>
+      </c>
+      <c r="L126" s="80" t="s">
         <v>178</v>
-      </c>
-    </row>
-    <row r="114" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B114" s="8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="116" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B116" s="66" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="118" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B118" s="66" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="120" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B120" s="8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="122" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B122" s="66" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="124" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B124" s="8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="126" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B126" s="66" t="s">
-        <v>180</v>
-      </c>
-      <c r="L126" s="78" t="s">
-        <v>179</v>
       </c>
       <c r="M126" s="66"/>
     </row>
@@ -5578,6 +5627,7 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L126" location="Dialogues!A1" display="Dialogues!A1" xr:uid="{5724AB96-1B0F-4DFD-A35F-382AC93CCD96}"/>
+    <hyperlink ref="AC116" location="'Item List'!A1" display="'Item List'!A1" xr:uid="{961E795F-F85E-4E2A-BAED-F63C80C609A5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5594,16 +5644,16 @@
   <sheetData>
     <row r="2" spans="1:24" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C4" s="40"/>
       <c r="D4" s="52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E4" s="53"/>
       <c r="F4" s="54"/>
@@ -5612,11 +5662,11 @@
       </c>
       <c r="H4" s="40"/>
       <c r="I4" s="40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J4" s="40"/>
       <c r="K4" s="40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L4" s="40"/>
       <c r="M4" s="40"/>
@@ -5632,7 +5682,7 @@
       <c r="U4" s="40"/>
       <c r="V4" s="40"/>
       <c r="W4" s="40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X4" s="40"/>
     </row>
@@ -5642,25 +5692,25 @@
       </c>
       <c r="C5" s="50"/>
       <c r="D5" s="55" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E5" s="56"/>
       <c r="F5" s="57"/>
       <c r="G5" s="61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H5" s="61"/>
       <c r="I5" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J5" s="51"/>
       <c r="K5" s="64" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L5" s="64"/>
       <c r="M5" s="64"/>
       <c r="N5" s="63" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O5" s="63"/>
       <c r="P5" s="63"/>
@@ -5671,7 +5721,7 @@
       <c r="U5" s="63"/>
       <c r="V5" s="63"/>
       <c r="W5" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X5" s="64"/>
     </row>
@@ -5681,25 +5731,25 @@
       </c>
       <c r="C6" s="50"/>
       <c r="D6" s="55" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E6" s="56"/>
       <c r="F6" s="57"/>
       <c r="G6" s="62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H6" s="62"/>
       <c r="I6" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J6" s="51"/>
       <c r="K6" s="64" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L6" s="64"/>
       <c r="M6" s="64"/>
       <c r="N6" s="63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
@@ -5710,7 +5760,7 @@
       <c r="U6" s="63"/>
       <c r="V6" s="63"/>
       <c r="W6" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X6" s="64"/>
     </row>
@@ -5720,16 +5770,16 @@
       </c>
       <c r="C7" s="50"/>
       <c r="D7" s="55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" s="56"/>
       <c r="F7" s="57"/>
       <c r="G7" s="61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H7" s="61"/>
       <c r="I7" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J7" s="51"/>
       <c r="K7" s="64" t="s">
@@ -5738,7 +5788,7 @@
       <c r="L7" s="64"/>
       <c r="M7" s="64"/>
       <c r="N7" s="63" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O7" s="63"/>
       <c r="P7" s="63"/>
@@ -5749,7 +5799,7 @@
       <c r="U7" s="63"/>
       <c r="V7" s="63"/>
       <c r="W7" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X7" s="64"/>
     </row>
@@ -5759,16 +5809,16 @@
       </c>
       <c r="C8" s="50"/>
       <c r="D8" s="55" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" s="56"/>
       <c r="F8" s="57"/>
       <c r="G8" s="61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H8" s="61"/>
       <c r="I8" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J8" s="51"/>
       <c r="K8" s="64" t="s">
@@ -5777,7 +5827,7 @@
       <c r="L8" s="64"/>
       <c r="M8" s="64"/>
       <c r="N8" s="63" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O8" s="63"/>
       <c r="P8" s="63"/>
@@ -5788,7 +5838,7 @@
       <c r="U8" s="63"/>
       <c r="V8" s="63"/>
       <c r="W8" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X8" s="64"/>
     </row>
@@ -5798,16 +5848,16 @@
       </c>
       <c r="C9" s="50"/>
       <c r="D9" s="55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" s="56"/>
       <c r="F9" s="57"/>
       <c r="G9" s="61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H9" s="61"/>
       <c r="I9" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J9" s="51"/>
       <c r="K9" s="64" t="s">
@@ -5816,7 +5866,7 @@
       <c r="L9" s="64"/>
       <c r="M9" s="64"/>
       <c r="N9" s="63" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O9" s="63"/>
       <c r="P9" s="63"/>
@@ -5827,7 +5877,7 @@
       <c r="U9" s="63"/>
       <c r="V9" s="63"/>
       <c r="W9" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X9" s="64"/>
     </row>
@@ -5837,16 +5887,16 @@
       </c>
       <c r="C10" s="50"/>
       <c r="D10" s="55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E10" s="56"/>
       <c r="F10" s="57"/>
       <c r="G10" s="61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H10" s="61"/>
       <c r="I10" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J10" s="51"/>
       <c r="K10" s="64" t="s">
@@ -5855,7 +5905,7 @@
       <c r="L10" s="64"/>
       <c r="M10" s="64"/>
       <c r="N10" s="63" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O10" s="63"/>
       <c r="P10" s="63"/>
@@ -5866,7 +5916,7 @@
       <c r="U10" s="63"/>
       <c r="V10" s="63"/>
       <c r="W10" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X10" s="64"/>
     </row>
@@ -5876,16 +5926,16 @@
       </c>
       <c r="C11" s="50"/>
       <c r="D11" s="55" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E11" s="56"/>
       <c r="F11" s="57"/>
       <c r="G11" s="61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H11" s="61"/>
       <c r="I11" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J11" s="51"/>
       <c r="K11" s="64" t="s">
@@ -5894,7 +5944,7 @@
       <c r="L11" s="64"/>
       <c r="M11" s="64"/>
       <c r="N11" s="63" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O11" s="63"/>
       <c r="P11" s="63"/>
@@ -5905,7 +5955,7 @@
       <c r="U11" s="63"/>
       <c r="V11" s="63"/>
       <c r="W11" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X11" s="64"/>
     </row>
@@ -5915,16 +5965,16 @@
       </c>
       <c r="C12" s="50"/>
       <c r="D12" s="58" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E12" s="59"/>
       <c r="F12" s="60"/>
       <c r="G12" s="61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H12" s="61"/>
       <c r="I12" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J12" s="51"/>
       <c r="K12" s="64" t="s">
@@ -5933,7 +5983,7 @@
       <c r="L12" s="64"/>
       <c r="M12" s="64"/>
       <c r="N12" s="63" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O12" s="63"/>
       <c r="P12" s="63"/>
@@ -5944,7 +5994,7 @@
       <c r="U12" s="63"/>
       <c r="V12" s="63"/>
       <c r="W12" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X12" s="64"/>
     </row>
@@ -5954,16 +6004,16 @@
       </c>
       <c r="C13" s="50"/>
       <c r="D13" s="55" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E13" s="56"/>
       <c r="F13" s="57"/>
       <c r="G13" s="61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H13" s="61"/>
       <c r="I13" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J13" s="51"/>
       <c r="K13" s="64" t="s">
@@ -5972,7 +6022,7 @@
       <c r="L13" s="64"/>
       <c r="M13" s="64"/>
       <c r="N13" s="63" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O13" s="63"/>
       <c r="P13" s="63"/>
@@ -5983,7 +6033,7 @@
       <c r="U13" s="63"/>
       <c r="V13" s="63"/>
       <c r="W13" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X13" s="64"/>
     </row>
@@ -5993,16 +6043,16 @@
       </c>
       <c r="C14" s="50"/>
       <c r="D14" s="55" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E14" s="56"/>
       <c r="F14" s="57"/>
       <c r="G14" s="61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H14" s="61"/>
       <c r="I14" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J14" s="51"/>
       <c r="K14" s="64" t="s">
@@ -6011,7 +6061,7 @@
       <c r="L14" s="64"/>
       <c r="M14" s="64"/>
       <c r="N14" s="63" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O14" s="63"/>
       <c r="P14" s="63"/>
@@ -6022,7 +6072,7 @@
       <c r="U14" s="63"/>
       <c r="V14" s="63"/>
       <c r="W14" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X14" s="64"/>
     </row>
@@ -6032,16 +6082,16 @@
       </c>
       <c r="C15" s="50"/>
       <c r="D15" s="55" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E15" s="56"/>
       <c r="F15" s="57"/>
       <c r="G15" s="61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H15" s="61"/>
       <c r="I15" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J15" s="51"/>
       <c r="K15" s="64" t="s">
@@ -6050,7 +6100,7 @@
       <c r="L15" s="64"/>
       <c r="M15" s="64"/>
       <c r="N15" s="63" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O15" s="63"/>
       <c r="P15" s="63"/>
@@ -6061,7 +6111,7 @@
       <c r="U15" s="63"/>
       <c r="V15" s="63"/>
       <c r="W15" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X15" s="64"/>
     </row>
@@ -6071,16 +6121,16 @@
       </c>
       <c r="C16" s="50"/>
       <c r="D16" s="55" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E16" s="56"/>
       <c r="F16" s="57"/>
       <c r="G16" s="61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H16" s="61"/>
       <c r="I16" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J16" s="51"/>
       <c r="K16" s="64" t="s">
@@ -6089,7 +6139,7 @@
       <c r="L16" s="64"/>
       <c r="M16" s="64"/>
       <c r="N16" s="63" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O16" s="63"/>
       <c r="P16" s="63"/>
@@ -6100,7 +6150,7 @@
       <c r="U16" s="63"/>
       <c r="V16" s="63"/>
       <c r="W16" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X16" s="64"/>
     </row>
@@ -6110,25 +6160,25 @@
       </c>
       <c r="C17" s="50"/>
       <c r="D17" s="55" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E17" s="56"/>
       <c r="F17" s="57"/>
       <c r="G17" s="62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H17" s="62"/>
       <c r="I17" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J17" s="51"/>
       <c r="K17" s="64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L17" s="64"/>
       <c r="M17" s="64"/>
       <c r="N17" s="63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O17" s="63"/>
       <c r="P17" s="63"/>
@@ -6139,7 +6189,7 @@
       <c r="U17" s="63"/>
       <c r="V17" s="63"/>
       <c r="W17" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X17" s="64"/>
     </row>
@@ -6149,25 +6199,25 @@
       </c>
       <c r="C18" s="50"/>
       <c r="D18" s="55" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E18" s="56"/>
       <c r="F18" s="57"/>
       <c r="G18" s="62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H18" s="62"/>
       <c r="I18" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J18" s="51"/>
       <c r="K18" s="64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L18" s="64"/>
       <c r="M18" s="64"/>
       <c r="N18" s="63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O18" s="63"/>
       <c r="P18" s="63"/>
@@ -6178,7 +6228,7 @@
       <c r="U18" s="63"/>
       <c r="V18" s="63"/>
       <c r="W18" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X18" s="64"/>
     </row>
@@ -6188,25 +6238,25 @@
       </c>
       <c r="C19" s="50"/>
       <c r="D19" s="55" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E19" s="56"/>
       <c r="F19" s="57"/>
       <c r="G19" s="62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H19" s="62"/>
       <c r="I19" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J19" s="51"/>
       <c r="K19" s="64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L19" s="64"/>
       <c r="M19" s="64"/>
       <c r="N19" s="63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O19" s="63"/>
       <c r="P19" s="63"/>
@@ -6217,7 +6267,7 @@
       <c r="U19" s="63"/>
       <c r="V19" s="63"/>
       <c r="W19" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X19" s="64"/>
     </row>
@@ -6227,12 +6277,12 @@
       </c>
       <c r="C20" s="50"/>
       <c r="D20" s="55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E20" s="56"/>
       <c r="F20" s="57"/>
       <c r="G20" s="62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H20" s="62"/>
       <c r="I20" s="65" t="s">
@@ -6240,12 +6290,12 @@
       </c>
       <c r="J20" s="65"/>
       <c r="K20" s="64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L20" s="64"/>
       <c r="M20" s="64"/>
       <c r="N20" s="63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O20" s="63"/>
       <c r="P20" s="63"/>
@@ -6256,7 +6306,7 @@
       <c r="U20" s="63"/>
       <c r="V20" s="63"/>
       <c r="W20" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X20" s="64"/>
     </row>
@@ -6266,12 +6316,12 @@
       </c>
       <c r="C21" s="50"/>
       <c r="D21" s="55" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E21" s="56"/>
       <c r="F21" s="57"/>
       <c r="G21" s="62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H21" s="62"/>
       <c r="I21" s="65" t="s">
@@ -6279,12 +6329,12 @@
       </c>
       <c r="J21" s="65"/>
       <c r="K21" s="64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L21" s="64"/>
       <c r="M21" s="64"/>
       <c r="N21" s="63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O21" s="63"/>
       <c r="P21" s="63"/>
@@ -6295,7 +6345,7 @@
       <c r="U21" s="63"/>
       <c r="V21" s="63"/>
       <c r="W21" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X21" s="64"/>
     </row>
@@ -6305,12 +6355,12 @@
       </c>
       <c r="C22" s="50"/>
       <c r="D22" s="55" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E22" s="56"/>
       <c r="F22" s="57"/>
       <c r="G22" s="62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H22" s="62"/>
       <c r="I22" s="65" t="s">
@@ -6318,12 +6368,12 @@
       </c>
       <c r="J22" s="65"/>
       <c r="K22" s="64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L22" s="64"/>
       <c r="M22" s="64"/>
       <c r="N22" s="63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O22" s="63"/>
       <c r="P22" s="63"/>
@@ -6334,7 +6384,7 @@
       <c r="U22" s="63"/>
       <c r="V22" s="63"/>
       <c r="W22" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X22" s="64"/>
     </row>
@@ -6344,12 +6394,12 @@
       </c>
       <c r="C23" s="50"/>
       <c r="D23" s="55" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E23" s="56"/>
       <c r="F23" s="57"/>
       <c r="G23" s="62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H23" s="62"/>
       <c r="I23" s="65" t="s">
@@ -6357,12 +6407,12 @@
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L23" s="64"/>
       <c r="M23" s="64"/>
       <c r="N23" s="63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O23" s="63"/>
       <c r="P23" s="63"/>
@@ -6373,7 +6423,7 @@
       <c r="U23" s="63"/>
       <c r="V23" s="63"/>
       <c r="W23" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X23" s="64"/>
     </row>
@@ -6383,12 +6433,12 @@
       </c>
       <c r="C24" s="50"/>
       <c r="D24" s="55" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E24" s="56"/>
       <c r="F24" s="57"/>
       <c r="G24" s="62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H24" s="62"/>
       <c r="I24" s="65" t="s">
@@ -6396,12 +6446,12 @@
       </c>
       <c r="J24" s="65"/>
       <c r="K24" s="64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L24" s="64"/>
       <c r="M24" s="64"/>
       <c r="N24" s="63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O24" s="63"/>
       <c r="P24" s="63"/>
@@ -6412,7 +6462,7 @@
       <c r="U24" s="63"/>
       <c r="V24" s="63"/>
       <c r="W24" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X24" s="64"/>
     </row>
@@ -6422,12 +6472,12 @@
       </c>
       <c r="C25" s="50"/>
       <c r="D25" s="55" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E25" s="56"/>
       <c r="F25" s="57"/>
       <c r="G25" s="62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H25" s="62"/>
       <c r="I25" s="65" t="s">
@@ -6435,12 +6485,12 @@
       </c>
       <c r="J25" s="65"/>
       <c r="K25" s="64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L25" s="64"/>
       <c r="M25" s="64"/>
       <c r="N25" s="63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O25" s="63"/>
       <c r="P25" s="63"/>
@@ -6451,7 +6501,7 @@
       <c r="U25" s="63"/>
       <c r="V25" s="63"/>
       <c r="W25" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X25" s="64"/>
     </row>
@@ -6461,12 +6511,12 @@
       </c>
       <c r="C26" s="50"/>
       <c r="D26" s="55" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E26" s="56"/>
       <c r="F26" s="57"/>
       <c r="G26" s="62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H26" s="62"/>
       <c r="I26" s="65" t="s">
@@ -6474,12 +6524,12 @@
       </c>
       <c r="J26" s="65"/>
       <c r="K26" s="64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L26" s="64"/>
       <c r="M26" s="64"/>
       <c r="N26" s="63" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O26" s="63"/>
       <c r="P26" s="63"/>
@@ -6490,7 +6540,7 @@
       <c r="U26" s="63"/>
       <c r="V26" s="63"/>
       <c r="W26" s="64" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X26" s="64"/>
     </row>
@@ -6681,7 +6731,7 @@
   <sheetData>
     <row r="2" spans="1:1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0E0BFC-31B1-496E-9817-B390EFBE13EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9892E8-3062-4453-83EE-54D9FA49B30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="189">
   <si>
     <t>SIGNOMALY</t>
   </si>
@@ -1720,9 +1720,6 @@
     <t>VII. Item lists</t>
   </si>
   <si>
-    <t>VIII. DIALOUGES</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Người chơi sẽ di chuyển bằng phím </t>
     </r>
@@ -1882,6 +1879,15 @@
   </si>
   <si>
     <t>Item List'!A1</t>
+  </si>
+  <si>
+    <t>Người hướng dẫn</t>
+  </si>
+  <si>
+    <t>VIII. DIALOGUES</t>
+  </si>
+  <si>
+    <t>Sau khi hiển thị Timelapse, nó sẽ luôn ở biến thể B. Và sau khi ông hoàn thành điều kiện, nó sẽ quay trở lại biến thể A.</t>
   </si>
 </sst>
 </file>
@@ -2171,9 +2177,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2313,6 +2316,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3529,29 +3535,29 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:26" ht="46.5" x14ac:dyDescent="0.7">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
     </row>
     <row r="3" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
@@ -3575,104 +3581,104 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="78" t="s">
-        <v>184</v>
-      </c>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
+      <c r="B12" s="77" t="s">
+        <v>183</v>
+      </c>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="77"/>
     </row>
     <row r="13" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="37"/>
-      <c r="L13" s="37"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
-      <c r="S13" s="37"/>
-      <c r="T13" s="37"/>
-      <c r="U13" s="37"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
+      <c r="S13" s="36"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="36"/>
     </row>
     <row r="14" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="36"/>
-      <c r="L14" s="36"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
-      <c r="S14" s="36"/>
-      <c r="T14" s="36"/>
-      <c r="U14" s="36"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="35"/>
+      <c r="U14" s="35"/>
     </row>
     <row r="15" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
@@ -3688,28 +3694,28 @@
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:26" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="34"/>
-      <c r="Q16" s="34"/>
-      <c r="R16" s="34"/>
-      <c r="S16" s="34"/>
-      <c r="T16" s="34"/>
-      <c r="U16" s="34"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="33"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="33"/>
       <c r="V16" s="6"/>
       <c r="W16" s="6"/>
       <c r="X16" s="6"/>
@@ -3717,52 +3723,52 @@
       <c r="Z16" s="6"/>
     </row>
     <row r="17" spans="1:21" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="34"/>
-      <c r="S17" s="34"/>
-      <c r="T17" s="34"/>
-      <c r="U17" s="34"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="33"/>
+      <c r="S17" s="33"/>
+      <c r="T17" s="33"/>
+      <c r="U17" s="33"/>
     </row>
     <row r="18" spans="1:21" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="36"/>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
-      <c r="S18" s="36"/>
-      <c r="T18" s="36"/>
-      <c r="U18" s="36"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="35"/>
+      <c r="T18" s="35"/>
+      <c r="U18" s="35"/>
     </row>
     <row r="19" spans="1:21" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="25" t="s">
@@ -3790,7 +3796,7 @@
     </row>
     <row r="20" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="22" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C20" s="22"/>
       <c r="D20" s="22"/>
@@ -3958,344 +3964,344 @@
       <c r="B4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40" t="s">
+      <c r="D4" s="39"/>
+      <c r="E4" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="40"/>
-      <c r="G4" s="42" t="s">
+      <c r="F4" s="39"/>
+      <c r="G4" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42" t="s">
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
-      <c r="P4" s="42"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="42"/>
-      <c r="S4" s="42"/>
-      <c r="T4" s="42"/>
-      <c r="U4" s="42"/>
-      <c r="V4" s="42"/>
-      <c r="W4" s="42"/>
-      <c r="X4" s="42"/>
-      <c r="Y4" s="42"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="41"/>
     </row>
     <row r="5" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11">
         <v>1</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="38"/>
-      <c r="E5" s="39" t="s">
+      <c r="D5" s="37"/>
+      <c r="E5" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="39"/>
-      <c r="G5" s="41" t="s">
+      <c r="F5" s="38"/>
+      <c r="G5" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="46" t="s">
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="N5" s="46"/>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46"/>
-      <c r="Q5" s="46"/>
-      <c r="R5" s="46"/>
-      <c r="S5" s="46"/>
-      <c r="T5" s="46"/>
-      <c r="U5" s="46"/>
-      <c r="V5" s="46"/>
-      <c r="W5" s="46"/>
-      <c r="X5" s="46"/>
-      <c r="Y5" s="46"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
+      <c r="P5" s="45"/>
+      <c r="Q5" s="45"/>
+      <c r="R5" s="45"/>
+      <c r="S5" s="45"/>
+      <c r="T5" s="45"/>
+      <c r="U5" s="45"/>
+      <c r="V5" s="45"/>
+      <c r="W5" s="45"/>
+      <c r="X5" s="45"/>
+      <c r="Y5" s="45"/>
     </row>
     <row r="6" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11">
         <v>2</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="39" t="s">
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="39"/>
-      <c r="G6" s="41" t="s">
+      <c r="F6" s="38"/>
+      <c r="G6" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="47" t="s">
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="N6" s="46"/>
-      <c r="O6" s="46"/>
-      <c r="P6" s="46"/>
-      <c r="Q6" s="46"/>
-      <c r="R6" s="46"/>
-      <c r="S6" s="46"/>
-      <c r="T6" s="46"/>
-      <c r="U6" s="46"/>
-      <c r="V6" s="46"/>
-      <c r="W6" s="46"/>
-      <c r="X6" s="46"/>
-      <c r="Y6" s="46"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
+      <c r="P6" s="45"/>
+      <c r="Q6" s="45"/>
+      <c r="R6" s="45"/>
+      <c r="S6" s="45"/>
+      <c r="T6" s="45"/>
+      <c r="U6" s="45"/>
+      <c r="V6" s="45"/>
+      <c r="W6" s="45"/>
+      <c r="X6" s="45"/>
+      <c r="Y6" s="45"/>
     </row>
     <row r="7" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11">
         <v>3</v>
       </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="39" t="s">
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="39"/>
-      <c r="G7" s="41" t="s">
+      <c r="F7" s="38"/>
+      <c r="G7" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="44" t="s">
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
-      <c r="T7" s="44"/>
-      <c r="U7" s="44"/>
-      <c r="V7" s="44"/>
-      <c r="W7" s="44"/>
-      <c r="X7" s="44"/>
-      <c r="Y7" s="44"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="43"/>
+      <c r="U7" s="43"/>
+      <c r="V7" s="43"/>
+      <c r="W7" s="43"/>
+      <c r="X7" s="43"/>
+      <c r="Y7" s="43"/>
     </row>
     <row r="8" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11">
         <v>4</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="38"/>
-      <c r="E8" s="39" t="s">
+      <c r="D8" s="37"/>
+      <c r="E8" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="39"/>
-      <c r="G8" s="41" t="s">
+      <c r="F8" s="38"/>
+      <c r="G8" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="43" t="s">
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="N8" s="44"/>
-      <c r="O8" s="44"/>
-      <c r="P8" s="44"/>
-      <c r="Q8" s="44"/>
-      <c r="R8" s="44"/>
-      <c r="S8" s="44"/>
-      <c r="T8" s="44"/>
-      <c r="U8" s="44"/>
-      <c r="V8" s="44"/>
-      <c r="W8" s="44"/>
-      <c r="X8" s="44"/>
-      <c r="Y8" s="44"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
+      <c r="V8" s="43"/>
+      <c r="W8" s="43"/>
+      <c r="X8" s="43"/>
+      <c r="Y8" s="43"/>
     </row>
     <row r="9" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11">
         <v>5</v>
       </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="39" t="s">
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="39"/>
-      <c r="G9" s="41" t="s">
+      <c r="F9" s="38"/>
+      <c r="G9" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="43" t="s">
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="N9" s="44"/>
-      <c r="O9" s="44"/>
-      <c r="P9" s="44"/>
-      <c r="Q9" s="44"/>
-      <c r="R9" s="44"/>
-      <c r="S9" s="44"/>
-      <c r="T9" s="44"/>
-      <c r="U9" s="44"/>
-      <c r="V9" s="44"/>
-      <c r="W9" s="44"/>
-      <c r="X9" s="44"/>
-      <c r="Y9" s="44"/>
+      <c r="N9" s="43"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
+      <c r="V9" s="43"/>
+      <c r="W9" s="43"/>
+      <c r="X9" s="43"/>
+      <c r="Y9" s="43"/>
     </row>
     <row r="10" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="11">
         <v>6</v>
       </c>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="39" t="s">
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="39"/>
-      <c r="G10" s="41" t="s">
+      <c r="F10" s="38"/>
+      <c r="G10" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="43" t="s">
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="N10" s="44"/>
-      <c r="O10" s="44"/>
-      <c r="P10" s="44"/>
-      <c r="Q10" s="44"/>
-      <c r="R10" s="44"/>
-      <c r="S10" s="44"/>
-      <c r="T10" s="44"/>
-      <c r="U10" s="44"/>
-      <c r="V10" s="44"/>
-      <c r="W10" s="44"/>
-      <c r="X10" s="44"/>
-      <c r="Y10" s="44"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="43"/>
+      <c r="X10" s="43"/>
+      <c r="Y10" s="43"/>
     </row>
     <row r="11" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="11">
         <v>7</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="39" t="s">
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="39"/>
-      <c r="G11" s="41" t="s">
+      <c r="F11" s="38"/>
+      <c r="G11" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="44" t="s">
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="44"/>
-      <c r="O11" s="44"/>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="44"/>
-      <c r="S11" s="44"/>
-      <c r="T11" s="44"/>
-      <c r="U11" s="44"/>
-      <c r="V11" s="44"/>
-      <c r="W11" s="44"/>
-      <c r="X11" s="44"/>
-      <c r="Y11" s="44"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
+      <c r="V11" s="43"/>
+      <c r="W11" s="43"/>
+      <c r="X11" s="43"/>
+      <c r="Y11" s="43"/>
     </row>
     <row r="12" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="11">
         <v>8</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="39" t="s">
+      <c r="D12" s="37"/>
+      <c r="E12" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="41" t="s">
+      <c r="F12" s="38"/>
+      <c r="G12" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="41"/>
-      <c r="L12" s="41"/>
-      <c r="M12" s="44" t="s">
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="N12" s="44"/>
-      <c r="O12" s="44"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="44"/>
-      <c r="R12" s="44"/>
-      <c r="S12" s="44"/>
-      <c r="T12" s="44"/>
-      <c r="U12" s="44"/>
-      <c r="V12" s="44"/>
-      <c r="W12" s="44"/>
-      <c r="X12" s="44"/>
-      <c r="Y12" s="44"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="43"/>
+      <c r="W12" s="43"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="43"/>
     </row>
     <row r="46" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B56" s="45" t="s">
+      <c r="B56" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="C56" s="45"/>
-      <c r="D56" s="45"/>
-      <c r="E56" s="45"/>
-      <c r="F56" s="45"/>
-      <c r="G56" s="45"/>
-      <c r="H56" s="45"/>
-      <c r="I56" s="45"/>
-      <c r="J56" s="45"/>
-      <c r="K56" s="45"/>
-      <c r="L56" s="45"/>
-      <c r="M56" s="45"/>
-      <c r="N56" s="45"/>
-      <c r="O56" s="45"/>
-      <c r="P56" s="45"/>
-      <c r="Q56" s="45"/>
-      <c r="R56" s="45"/>
-      <c r="S56" s="45"/>
-      <c r="T56" s="45"/>
-      <c r="U56" s="45"/>
-      <c r="V56" s="45"/>
-      <c r="W56" s="45"/>
-      <c r="X56" s="45"/>
-      <c r="Y56" s="45"/>
+      <c r="C56" s="44"/>
+      <c r="D56" s="44"/>
+      <c r="E56" s="44"/>
+      <c r="F56" s="44"/>
+      <c r="G56" s="44"/>
+      <c r="H56" s="44"/>
+      <c r="I56" s="44"/>
+      <c r="J56" s="44"/>
+      <c r="K56" s="44"/>
+      <c r="L56" s="44"/>
+      <c r="M56" s="44"/>
+      <c r="N56" s="44"/>
+      <c r="O56" s="44"/>
+      <c r="P56" s="44"/>
+      <c r="Q56" s="44"/>
+      <c r="R56" s="44"/>
+      <c r="S56" s="44"/>
+      <c r="T56" s="44"/>
+      <c r="U56" s="44"/>
+      <c r="V56" s="44"/>
+      <c r="W56" s="44"/>
+      <c r="X56" s="44"/>
+      <c r="Y56" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="37">
@@ -4458,35 +4464,35 @@
       <c r="B17" s="8"/>
     </row>
     <row r="18" spans="2:33" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="80" t="s">
         <v>87</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="30"/>
-      <c r="P18" s="30"/>
-      <c r="Q18" s="30"/>
-      <c r="R18" s="30"/>
-      <c r="S18" s="30"/>
-      <c r="T18" s="30"/>
-      <c r="U18" s="30"/>
-      <c r="V18" s="30"/>
-      <c r="W18" s="30"/>
-      <c r="X18" s="30"/>
-      <c r="Y18" s="30"/>
-      <c r="Z18" s="30"/>
-      <c r="AA18" s="30"/>
-      <c r="AB18" s="30"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="29"/>
+      <c r="T18" s="29"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="29"/>
+      <c r="W18" s="29"/>
+      <c r="X18" s="29"/>
+      <c r="Y18" s="29"/>
+      <c r="Z18" s="29"/>
+      <c r="AA18" s="29"/>
+      <c r="AB18" s="29"/>
     </row>
     <row r="19" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="15"/>
@@ -4541,8 +4547,8 @@
       <c r="T24" s="12"/>
     </row>
     <row r="25" spans="2:33" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T25" s="48" t="s">
-        <v>180</v>
+      <c r="T25" s="47" t="s">
+        <v>179</v>
       </c>
       <c r="U25" s="21"/>
       <c r="V25" s="21"/>
@@ -4559,7 +4565,7 @@
       <c r="AG25" s="17"/>
     </row>
     <row r="26" spans="2:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T26" s="67"/>
+      <c r="T26" s="66"/>
       <c r="U26" s="18"/>
       <c r="V26" s="18"/>
       <c r="W26" s="18"/>
@@ -4575,21 +4581,21 @@
       <c r="AG26" s="17"/>
     </row>
     <row r="27" spans="2:33" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T27" s="48" t="s">
-        <v>182</v>
-      </c>
-      <c r="U27" s="48"/>
-      <c r="V27" s="48"/>
-      <c r="W27" s="48"/>
-      <c r="X27" s="48"/>
-      <c r="Y27" s="48"/>
-      <c r="Z27" s="48"/>
-      <c r="AA27" s="48"/>
-      <c r="AB27" s="48"/>
-      <c r="AC27" s="48"/>
-      <c r="AD27" s="48"/>
-      <c r="AE27" s="48"/>
-      <c r="AF27" s="48"/>
+      <c r="T27" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="U27" s="47"/>
+      <c r="V27" s="47"/>
+      <c r="W27" s="47"/>
+      <c r="X27" s="47"/>
+      <c r="Y27" s="47"/>
+      <c r="Z27" s="47"/>
+      <c r="AA27" s="47"/>
+      <c r="AB27" s="47"/>
+      <c r="AC27" s="47"/>
+      <c r="AD27" s="47"/>
+      <c r="AE27" s="47"/>
+      <c r="AF27" s="47"/>
       <c r="AG27" s="17"/>
     </row>
     <row r="28" spans="2:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4858,7 +4864,7 @@
       <c r="T60" s="12"/>
     </row>
     <row r="61" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B61" s="49" t="s">
+      <c r="B61" s="48" t="s">
         <v>91</v>
       </c>
       <c r="C61" s="27"/>
@@ -4955,26 +4961,26 @@
       <c r="AK69" s="18"/>
     </row>
     <row r="70" spans="20:37" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T70" s="48" t="s">
-        <v>183</v>
-      </c>
-      <c r="U70" s="48"/>
-      <c r="V70" s="48"/>
-      <c r="W70" s="48"/>
-      <c r="X70" s="48"/>
-      <c r="Y70" s="48"/>
-      <c r="Z70" s="48"/>
-      <c r="AA70" s="48"/>
-      <c r="AB70" s="48"/>
-      <c r="AC70" s="48"/>
-      <c r="AD70" s="48"/>
-      <c r="AE70" s="48"/>
-      <c r="AF70" s="48"/>
-      <c r="AG70" s="48"/>
-      <c r="AH70" s="48"/>
-      <c r="AI70" s="48"/>
-      <c r="AJ70" s="48"/>
-      <c r="AK70" s="48"/>
+      <c r="T70" s="47" t="s">
+        <v>182</v>
+      </c>
+      <c r="U70" s="47"/>
+      <c r="V70" s="47"/>
+      <c r="W70" s="47"/>
+      <c r="X70" s="47"/>
+      <c r="Y70" s="47"/>
+      <c r="Z70" s="47"/>
+      <c r="AA70" s="47"/>
+      <c r="AB70" s="47"/>
+      <c r="AC70" s="47"/>
+      <c r="AD70" s="47"/>
+      <c r="AE70" s="47"/>
+      <c r="AF70" s="47"/>
+      <c r="AG70" s="47"/>
+      <c r="AH70" s="47"/>
+      <c r="AI70" s="47"/>
+      <c r="AJ70" s="47"/>
+      <c r="AK70" s="47"/>
     </row>
     <row r="72" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
       <c r="T72" s="8" t="s">
@@ -4985,8 +4991,8 @@
       <c r="T73" s="8"/>
     </row>
     <row r="74" spans="20:37" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T74" s="48" t="s">
-        <v>181</v>
+      <c r="T74" s="47" t="s">
+        <v>180</v>
       </c>
       <c r="U74" s="21"/>
       <c r="V74" s="21"/>
@@ -5160,7 +5166,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A2:AJ126"/>
+  <dimension ref="A2:AJ128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
@@ -5173,245 +5179,245 @@
     </row>
     <row r="4" spans="1:36" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
     </row>
     <row r="5" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="L5" s="42" t="s">
+      <c r="L5" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="M5" s="42"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
-      <c r="P5" s="42"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
     </row>
     <row r="6" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
-      <c r="L6" s="70" t="s">
+      <c r="L6" s="69" t="s">
         <v>128</v>
       </c>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
+      <c r="P6" s="69"/>
     </row>
     <row r="7" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
-      <c r="L7" s="63" t="s">
+      <c r="L7" s="62" t="s">
         <v>129</v>
       </c>
-      <c r="M7" s="63"/>
-      <c r="N7" s="63"/>
-      <c r="O7" s="63"/>
-      <c r="P7" s="63"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="62"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="62"/>
     </row>
     <row r="8" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
-      <c r="L8" s="70" t="s">
+      <c r="L8" s="69" t="s">
         <v>130</v>
       </c>
-      <c r="M8" s="70"/>
-      <c r="N8" s="70"/>
-      <c r="O8" s="70"/>
-      <c r="P8" s="70"/>
+      <c r="M8" s="69"/>
+      <c r="N8" s="69"/>
+      <c r="O8" s="69"/>
+      <c r="P8" s="69"/>
     </row>
     <row r="9" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1"/>
-      <c r="L9" s="70" t="s">
+      <c r="L9" s="69" t="s">
         <v>131</v>
       </c>
-      <c r="M9" s="70"/>
-      <c r="N9" s="70"/>
-      <c r="O9" s="70"/>
-      <c r="P9" s="70"/>
-      <c r="R9" s="71"/>
-      <c r="S9" s="71"/>
-      <c r="T9" s="71"/>
-      <c r="U9" s="71"/>
-      <c r="V9" s="71"/>
-      <c r="W9" s="71"/>
-      <c r="X9" s="71"/>
-      <c r="Y9" s="71"/>
-      <c r="Z9" s="71"/>
+      <c r="M9" s="69"/>
+      <c r="N9" s="69"/>
+      <c r="O9" s="69"/>
+      <c r="P9" s="69"/>
+      <c r="R9" s="70"/>
+      <c r="S9" s="70"/>
+      <c r="T9" s="70"/>
+      <c r="U9" s="70"/>
+      <c r="V9" s="70"/>
+      <c r="W9" s="70"/>
+      <c r="X9" s="70"/>
+      <c r="Y9" s="70"/>
+      <c r="Z9" s="70"/>
     </row>
     <row r="10" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
-      <c r="L10" s="63" t="s">
+      <c r="L10" s="62" t="s">
         <v>132</v>
       </c>
-      <c r="M10" s="63"/>
-      <c r="N10" s="63"/>
-      <c r="O10" s="63"/>
-      <c r="P10" s="63"/>
-      <c r="R10" s="71"/>
-      <c r="S10" s="71"/>
-      <c r="T10" s="71"/>
-      <c r="U10" s="71"/>
-      <c r="V10" s="71"/>
-      <c r="W10" s="71"/>
-      <c r="X10" s="71"/>
-      <c r="Y10" s="71"/>
-      <c r="Z10" s="71"/>
+      <c r="M10" s="62"/>
+      <c r="N10" s="62"/>
+      <c r="O10" s="62"/>
+      <c r="P10" s="62"/>
+      <c r="R10" s="70"/>
+      <c r="S10" s="70"/>
+      <c r="T10" s="70"/>
+      <c r="U10" s="70"/>
+      <c r="V10" s="70"/>
+      <c r="W10" s="70"/>
+      <c r="X10" s="70"/>
+      <c r="Y10" s="70"/>
+      <c r="Z10" s="70"/>
     </row>
     <row r="11" spans="1:36" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
-      <c r="L11" s="63" t="s">
+      <c r="L11" s="62" t="s">
         <v>133</v>
       </c>
-      <c r="M11" s="70"/>
-      <c r="N11" s="70"/>
-      <c r="O11" s="70"/>
-      <c r="P11" s="70"/>
-      <c r="R11" s="71"/>
-      <c r="S11" s="71"/>
-      <c r="T11" s="71"/>
-      <c r="U11" s="71"/>
-      <c r="V11" s="71"/>
-      <c r="W11" s="71"/>
-      <c r="X11" s="71"/>
-      <c r="Y11" s="71"/>
-      <c r="Z11" s="71"/>
+      <c r="M11" s="69"/>
+      <c r="N11" s="69"/>
+      <c r="O11" s="69"/>
+      <c r="P11" s="69"/>
+      <c r="R11" s="70"/>
+      <c r="S11" s="70"/>
+      <c r="T11" s="70"/>
+      <c r="U11" s="70"/>
+      <c r="V11" s="70"/>
+      <c r="W11" s="70"/>
+      <c r="X11" s="70"/>
+      <c r="Y11" s="70"/>
+      <c r="Z11" s="70"/>
     </row>
     <row r="12" spans="1:36" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1"/>
-      <c r="L12" s="63" t="s">
+      <c r="L12" s="62" t="s">
         <v>134</v>
       </c>
-      <c r="M12" s="63"/>
-      <c r="N12" s="63"/>
-      <c r="O12" s="63"/>
-      <c r="P12" s="63"/>
-      <c r="R12" s="71"/>
-      <c r="S12" s="71"/>
-      <c r="T12" s="71"/>
-      <c r="U12" s="71"/>
-      <c r="V12" s="71"/>
+      <c r="M12" s="62"/>
+      <c r="N12" s="62"/>
+      <c r="O12" s="62"/>
+      <c r="P12" s="62"/>
+      <c r="R12" s="70"/>
+      <c r="S12" s="70"/>
+      <c r="T12" s="70"/>
+      <c r="U12" s="70"/>
+      <c r="V12" s="70"/>
     </row>
     <row r="13" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
-      <c r="L13" s="70" t="s">
+      <c r="L13" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="M13" s="70"/>
-      <c r="N13" s="70"/>
-      <c r="O13" s="70"/>
-      <c r="P13" s="70"/>
-      <c r="R13" s="71"/>
-      <c r="S13" s="71"/>
-      <c r="T13" s="71"/>
-      <c r="U13" s="71"/>
-      <c r="W13" s="74" t="s">
+      <c r="M13" s="69"/>
+      <c r="N13" s="69"/>
+      <c r="O13" s="69"/>
+      <c r="P13" s="69"/>
+      <c r="R13" s="70"/>
+      <c r="S13" s="70"/>
+      <c r="T13" s="70"/>
+      <c r="U13" s="70"/>
+      <c r="W13" s="73" t="s">
         <v>146</v>
       </c>
-      <c r="X13" s="74"/>
-      <c r="Y13" s="74"/>
-      <c r="Z13" s="74"/>
-      <c r="AA13" s="74"/>
-      <c r="AB13" s="74"/>
-      <c r="AC13" s="74"/>
-      <c r="AD13" s="74"/>
-      <c r="AE13" s="74"/>
-      <c r="AF13" s="74"/>
-      <c r="AG13" s="74"/>
-      <c r="AH13" s="74"/>
-      <c r="AI13" s="74"/>
-      <c r="AJ13" s="74"/>
+      <c r="X13" s="73"/>
+      <c r="Y13" s="73"/>
+      <c r="Z13" s="73"/>
+      <c r="AA13" s="73"/>
+      <c r="AB13" s="73"/>
+      <c r="AC13" s="73"/>
+      <c r="AD13" s="73"/>
+      <c r="AE13" s="73"/>
+      <c r="AF13" s="73"/>
+      <c r="AG13" s="73"/>
+      <c r="AH13" s="73"/>
+      <c r="AI13" s="73"/>
+      <c r="AJ13" s="73"/>
     </row>
     <row r="14" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A14" s="1"/>
-      <c r="L14" s="70" t="s">
+      <c r="L14" s="69" t="s">
         <v>136</v>
       </c>
-      <c r="M14" s="70"/>
-      <c r="N14" s="70"/>
-      <c r="O14" s="70"/>
-      <c r="P14" s="70"/>
-      <c r="R14" s="71"/>
-      <c r="S14" s="71"/>
-      <c r="T14" s="71"/>
-      <c r="U14" s="71"/>
-      <c r="V14" s="71"/>
-      <c r="W14" s="71"/>
-      <c r="X14" s="71"/>
-      <c r="Y14" s="71"/>
-      <c r="Z14" s="71"/>
+      <c r="M14" s="69"/>
+      <c r="N14" s="69"/>
+      <c r="O14" s="69"/>
+      <c r="P14" s="69"/>
+      <c r="R14" s="70"/>
+      <c r="S14" s="70"/>
+      <c r="T14" s="70"/>
+      <c r="U14" s="70"/>
+      <c r="V14" s="70"/>
+      <c r="W14" s="70"/>
+      <c r="X14" s="70"/>
+      <c r="Y14" s="70"/>
+      <c r="Z14" s="70"/>
     </row>
     <row r="15" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
-      <c r="R15" s="72"/>
+      <c r="R15" s="71"/>
     </row>
     <row r="16" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
     </row>
     <row r="17" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A17" s="1"/>
-      <c r="L17" s="42" t="s">
+      <c r="L17" s="41" t="s">
         <v>138</v>
       </c>
-      <c r="M17" s="42"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="42" t="s">
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="42"/>
+      <c r="P17" s="41"/>
+      <c r="Q17" s="41"/>
+      <c r="R17" s="41"/>
+      <c r="S17" s="41"/>
+      <c r="T17" s="41"/>
     </row>
     <row r="18" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
-      <c r="L18" s="38" t="s">
+      <c r="L18" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="73" t="s">
+      <c r="M18" s="37"/>
+      <c r="N18" s="37"/>
+      <c r="O18" s="72" t="s">
         <v>139</v>
       </c>
-      <c r="P18" s="73"/>
-      <c r="Q18" s="73"/>
-      <c r="R18" s="73"/>
-      <c r="S18" s="73"/>
-      <c r="T18" s="73"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="72"/>
+      <c r="T18" s="72"/>
     </row>
     <row r="19" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
-      <c r="L19" s="38" t="s">
+      <c r="L19" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="M19" s="38"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="73" t="s">
+      <c r="M19" s="37"/>
+      <c r="N19" s="37"/>
+      <c r="O19" s="72" t="s">
         <v>143</v>
       </c>
-      <c r="P19" s="73"/>
-      <c r="Q19" s="73"/>
-      <c r="R19" s="73"/>
-      <c r="S19" s="73"/>
-      <c r="T19" s="73"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="72"/>
+      <c r="T19" s="72"/>
     </row>
     <row r="20" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
-      <c r="L20" s="38" t="s">
+      <c r="L20" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="73" t="s">
+      <c r="M20" s="37"/>
+      <c r="N20" s="37"/>
+      <c r="O20" s="72" t="s">
         <v>145</v>
       </c>
-      <c r="P20" s="73"/>
-      <c r="Q20" s="73"/>
-      <c r="R20" s="73"/>
-      <c r="S20" s="73"/>
-      <c r="T20" s="73"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="72"/>
+      <c r="T20" s="72"/>
     </row>
     <row r="21" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A21" s="1"/>
@@ -5421,11 +5427,11 @@
     </row>
     <row r="23" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A23" s="1"/>
-      <c r="L23" s="69"/>
-      <c r="M23" s="69"/>
-      <c r="N23" s="69"/>
-      <c r="O23" s="68"/>
-      <c r="P23" s="68"/>
+      <c r="L23" s="68"/>
+      <c r="M23" s="68"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="67"/>
+      <c r="P23" s="67"/>
     </row>
     <row r="25" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B25" s="8" t="s">
@@ -5441,12 +5447,12 @@
       </c>
     </row>
     <row r="56" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B56" s="66" t="s">
+      <c r="B56" s="65" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="57" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B57" s="66"/>
+      <c r="B57" s="65"/>
     </row>
     <row r="58" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
@@ -5454,7 +5460,7 @@
       </c>
     </row>
     <row r="85" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B85" s="66" t="s">
+      <c r="B85" s="65" t="s">
         <v>147</v>
       </c>
     </row>
@@ -5472,138 +5478,146 @@
       </c>
     </row>
     <row r="91" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B91" s="66" t="s">
+      <c r="B91" s="65" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="93" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B93" s="75" t="s">
+      <c r="B93" s="74" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="94" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B94" s="75" t="s">
+      <c r="B94" s="74" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="95" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B95" s="75" t="s">
+      <c r="B95" s="74" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="97" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B97" s="8" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="99" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B99" s="66" t="s">
+    <row r="99" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B99" s="65" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="101" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B101" s="66" t="s">
+    <row r="101" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B101" s="65" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="103" spans="2:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B103" s="76" t="s">
+    <row r="102" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B102" s="65"/>
+    </row>
+    <row r="103" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B103" s="65" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B105" s="75" t="s">
         <v>160</v>
       </c>
-      <c r="C103" s="76"/>
-      <c r="D103" s="76"/>
-      <c r="E103" s="76"/>
-      <c r="F103" s="76"/>
-      <c r="G103" s="76"/>
-      <c r="H103" s="76"/>
-      <c r="I103" s="76"/>
-      <c r="J103" s="76"/>
-      <c r="K103" s="76"/>
-      <c r="L103" s="76"/>
-      <c r="M103" s="76"/>
-      <c r="N103" s="76"/>
-      <c r="O103" s="76"/>
-      <c r="P103" s="76"/>
-      <c r="Q103" s="76"/>
-      <c r="R103" s="76"/>
-      <c r="S103" s="76"/>
-      <c r="T103" s="76"/>
-      <c r="U103" s="76"/>
-      <c r="V103" s="76"/>
-      <c r="W103" s="76"/>
-      <c r="X103" s="76"/>
-      <c r="Y103" s="76"/>
-    </row>
-    <row r="106" spans="2:25" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="B106" s="1" t="s">
+      <c r="C105" s="75"/>
+      <c r="D105" s="75"/>
+      <c r="E105" s="75"/>
+      <c r="F105" s="75"/>
+      <c r="G105" s="75"/>
+      <c r="H105" s="75"/>
+      <c r="I105" s="75"/>
+      <c r="J105" s="75"/>
+      <c r="K105" s="75"/>
+      <c r="L105" s="75"/>
+      <c r="M105" s="75"/>
+      <c r="N105" s="75"/>
+      <c r="O105" s="75"/>
+      <c r="P105" s="75"/>
+      <c r="Q105" s="75"/>
+      <c r="R105" s="75"/>
+      <c r="S105" s="75"/>
+      <c r="T105" s="75"/>
+      <c r="U105" s="75"/>
+      <c r="V105" s="75"/>
+      <c r="W105" s="75"/>
+      <c r="X105" s="75"/>
+      <c r="Y105" s="75"/>
+    </row>
+    <row r="108" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A108" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="108" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B108" s="8" t="s">
+    <row r="110" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B110" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="C108" s="8"/>
-      <c r="D108" s="77"/>
-    </row>
-    <row r="110" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B110" s="66" t="s">
+      <c r="C110" s="8"/>
+      <c r="D110" s="76"/>
+    </row>
+    <row r="112" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B112" s="65" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="113" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B113" s="65"/>
+    </row>
+    <row r="114" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B114" s="65" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="111" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B111" s="66"/>
-    </row>
-    <row r="112" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B112" s="66" t="s">
+    <row r="116" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B116" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="118" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B118" s="65" t="s">
+        <v>170</v>
+      </c>
+      <c r="AC118" s="78" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="120" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B120" s="65" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="122" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B122" s="8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="124" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B124" s="65" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="126" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B126" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="128" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B128" s="65" t="s">
+        <v>178</v>
+      </c>
+      <c r="L128" s="79" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="114" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B114" s="8" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="116" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B116" s="66" t="s">
-        <v>170</v>
-      </c>
-      <c r="AC116" s="79" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="118" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B118" s="66" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="120" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B120" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="122" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B122" s="66" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="124" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B124" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="126" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B126" s="66" t="s">
-        <v>179</v>
-      </c>
-      <c r="L126" s="80" t="s">
-        <v>178</v>
-      </c>
-      <c r="M126" s="66"/>
+      <c r="M128" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B103:Y103"/>
+    <mergeCell ref="B105:Y105"/>
     <mergeCell ref="O18:T18"/>
     <mergeCell ref="W13:AJ13"/>
     <mergeCell ref="O17:T17"/>
@@ -5626,8 +5640,8 @@
     <mergeCell ref="B4:F4"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="L126" location="Dialogues!A1" display="Dialogues!A1" xr:uid="{5724AB96-1B0F-4DFD-A35F-382AC93CCD96}"/>
-    <hyperlink ref="AC116" location="'Item List'!A1" display="'Item List'!A1" xr:uid="{961E795F-F85E-4E2A-BAED-F63C80C609A5}"/>
+    <hyperlink ref="L128" location="Dialogues!A1" display="Dialogues!A1" xr:uid="{5724AB96-1B0F-4DFD-A35F-382AC93CCD96}"/>
+    <hyperlink ref="AC118" location="'Item List'!A1" display="'Item List'!A1" xr:uid="{961E795F-F85E-4E2A-BAED-F63C80C609A5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5648,901 +5662,901 @@
       </c>
     </row>
     <row r="4" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="C4" s="40"/>
-      <c r="D4" s="52" t="s">
+      <c r="C4" s="39"/>
+      <c r="D4" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="40" t="s">
+      <c r="E4" s="52"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40" t="s">
+      <c r="H4" s="39"/>
+      <c r="I4" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40" t="s">
+      <c r="J4" s="39"/>
+      <c r="K4" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40" t="s">
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="40"/>
-      <c r="S4" s="40"/>
-      <c r="T4" s="40"/>
-      <c r="U4" s="40"/>
-      <c r="V4" s="40"/>
-      <c r="W4" s="40" t="s">
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="39"/>
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="39"/>
+      <c r="W4" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="X4" s="40"/>
+      <c r="X4" s="39"/>
     </row>
     <row r="5" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="50">
+      <c r="B5" s="49">
         <v>1</v>
       </c>
-      <c r="C5" s="50"/>
-      <c r="D5" s="55" t="s">
+      <c r="C5" s="49"/>
+      <c r="D5" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="E5" s="56"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="61" t="s">
+      <c r="E5" s="55"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="60" t="s">
         <v>93</v>
       </c>
-      <c r="H5" s="61"/>
-      <c r="I5" s="51" t="s">
+      <c r="H5" s="60"/>
+      <c r="I5" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="J5" s="51"/>
-      <c r="K5" s="64" t="s">
+      <c r="J5" s="50"/>
+      <c r="K5" s="63" t="s">
         <v>118</v>
       </c>
-      <c r="L5" s="64"/>
-      <c r="M5" s="64"/>
-      <c r="N5" s="63" t="s">
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
+      <c r="N5" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="O5" s="63"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="64" t="s">
+      <c r="O5" s="62"/>
+      <c r="P5" s="62"/>
+      <c r="Q5" s="62"/>
+      <c r="R5" s="62"/>
+      <c r="S5" s="62"/>
+      <c r="T5" s="62"/>
+      <c r="U5" s="62"/>
+      <c r="V5" s="62"/>
+      <c r="W5" s="63" t="s">
         <v>125</v>
       </c>
-      <c r="X5" s="64"/>
+      <c r="X5" s="63"/>
     </row>
     <row r="6" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B6" s="50">
+      <c r="B6" s="49">
         <v>2</v>
       </c>
-      <c r="C6" s="50"/>
-      <c r="D6" s="55" t="s">
+      <c r="C6" s="49"/>
+      <c r="D6" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="E6" s="56"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="62" t="s">
+      <c r="E6" s="55"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="H6" s="62"/>
-      <c r="I6" s="51" t="s">
+      <c r="H6" s="61"/>
+      <c r="I6" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="J6" s="51"/>
-      <c r="K6" s="64" t="s">
+      <c r="J6" s="50"/>
+      <c r="K6" s="63" t="s">
         <v>118</v>
       </c>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="63" t="s">
+      <c r="L6" s="63"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="62" t="s">
+        <v>186</v>
+      </c>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="62"/>
+      <c r="T6" s="62"/>
+      <c r="U6" s="62"/>
+      <c r="V6" s="62"/>
+      <c r="W6" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="X6" s="63"/>
+    </row>
+    <row r="7" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="49">
+        <v>3</v>
+      </c>
+      <c r="C7" s="49"/>
+      <c r="D7" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="55"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="H7" s="60"/>
+      <c r="I7" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J7" s="50"/>
+      <c r="K7" s="63" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="63"/>
+      <c r="M7" s="63"/>
+      <c r="N7" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="O7" s="62"/>
+      <c r="P7" s="62"/>
+      <c r="Q7" s="62"/>
+      <c r="R7" s="62"/>
+      <c r="S7" s="62"/>
+      <c r="T7" s="62"/>
+      <c r="U7" s="62"/>
+      <c r="V7" s="62"/>
+      <c r="W7" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="X7" s="63"/>
+    </row>
+    <row r="8" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="49">
+        <v>4</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="55"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="H8" s="60"/>
+      <c r="I8" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J8" s="50"/>
+      <c r="K8" s="63" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="63"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="O8" s="62"/>
+      <c r="P8" s="62"/>
+      <c r="Q8" s="62"/>
+      <c r="R8" s="62"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="62"/>
+      <c r="U8" s="62"/>
+      <c r="V8" s="62"/>
+      <c r="W8" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="X8" s="63"/>
+    </row>
+    <row r="9" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="49">
+        <v>5</v>
+      </c>
+      <c r="C9" s="49"/>
+      <c r="D9" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="55"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="H9" s="60"/>
+      <c r="I9" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J9" s="50"/>
+      <c r="K9" s="63" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="63"/>
+      <c r="M9" s="63"/>
+      <c r="N9" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="O9" s="62"/>
+      <c r="P9" s="62"/>
+      <c r="Q9" s="62"/>
+      <c r="R9" s="62"/>
+      <c r="S9" s="62"/>
+      <c r="T9" s="62"/>
+      <c r="U9" s="62"/>
+      <c r="V9" s="62"/>
+      <c r="W9" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="X9" s="63"/>
+    </row>
+    <row r="10" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="49">
+        <v>6</v>
+      </c>
+      <c r="C10" s="49"/>
+      <c r="D10" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="55"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="H10" s="60"/>
+      <c r="I10" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J10" s="50"/>
+      <c r="K10" s="63" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="63"/>
+      <c r="M10" s="63"/>
+      <c r="N10" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="O10" s="62"/>
+      <c r="P10" s="62"/>
+      <c r="Q10" s="62"/>
+      <c r="R10" s="62"/>
+      <c r="S10" s="62"/>
+      <c r="T10" s="62"/>
+      <c r="U10" s="62"/>
+      <c r="V10" s="62"/>
+      <c r="W10" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="X10" s="63"/>
+    </row>
+    <row r="11" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="49">
+        <v>7</v>
+      </c>
+      <c r="C11" s="49"/>
+      <c r="D11" s="54" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="55"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="H11" s="60"/>
+      <c r="I11" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J11" s="50"/>
+      <c r="K11" s="63" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="63"/>
+      <c r="M11" s="63"/>
+      <c r="N11" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="O11" s="62"/>
+      <c r="P11" s="62"/>
+      <c r="Q11" s="62"/>
+      <c r="R11" s="62"/>
+      <c r="S11" s="62"/>
+      <c r="T11" s="62"/>
+      <c r="U11" s="62"/>
+      <c r="V11" s="62"/>
+      <c r="W11" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="X11" s="63"/>
+    </row>
+    <row r="12" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="49">
+        <v>8</v>
+      </c>
+      <c r="C12" s="49"/>
+      <c r="D12" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" s="58"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="H12" s="60"/>
+      <c r="I12" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J12" s="50"/>
+      <c r="K12" s="63" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="63"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="62" t="s">
+        <v>113</v>
+      </c>
+      <c r="O12" s="62"/>
+      <c r="P12" s="62"/>
+      <c r="Q12" s="62"/>
+      <c r="R12" s="62"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="62"/>
+      <c r="U12" s="62"/>
+      <c r="V12" s="62"/>
+      <c r="W12" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="X12" s="63"/>
+    </row>
+    <row r="13" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="49">
+        <v>9</v>
+      </c>
+      <c r="C13" s="49"/>
+      <c r="D13" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" s="55"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="H13" s="60"/>
+      <c r="I13" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J13" s="50"/>
+      <c r="K13" s="63" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="62" t="s">
+        <v>113</v>
+      </c>
+      <c r="O13" s="62"/>
+      <c r="P13" s="62"/>
+      <c r="Q13" s="62"/>
+      <c r="R13" s="62"/>
+      <c r="S13" s="62"/>
+      <c r="T13" s="62"/>
+      <c r="U13" s="62"/>
+      <c r="V13" s="62"/>
+      <c r="W13" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="X13" s="63"/>
+    </row>
+    <row r="14" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="49">
+        <v>10</v>
+      </c>
+      <c r="C14" s="49"/>
+      <c r="D14" s="54" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="55"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="H14" s="60"/>
+      <c r="I14" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J14" s="50"/>
+      <c r="K14" s="63" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="63"/>
+      <c r="M14" s="63"/>
+      <c r="N14" s="62" t="s">
+        <v>122</v>
+      </c>
+      <c r="O14" s="62"/>
+      <c r="P14" s="62"/>
+      <c r="Q14" s="62"/>
+      <c r="R14" s="62"/>
+      <c r="S14" s="62"/>
+      <c r="T14" s="62"/>
+      <c r="U14" s="62"/>
+      <c r="V14" s="62"/>
+      <c r="W14" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="X14" s="63"/>
+    </row>
+    <row r="15" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="49">
+        <v>11</v>
+      </c>
+      <c r="C15" s="49"/>
+      <c r="D15" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="55"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="H15" s="60"/>
+      <c r="I15" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J15" s="50"/>
+      <c r="K15" s="63" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="63"/>
+      <c r="M15" s="63"/>
+      <c r="N15" s="62" t="s">
+        <v>123</v>
+      </c>
+      <c r="O15" s="62"/>
+      <c r="P15" s="62"/>
+      <c r="Q15" s="62"/>
+      <c r="R15" s="62"/>
+      <c r="S15" s="62"/>
+      <c r="T15" s="62"/>
+      <c r="U15" s="62"/>
+      <c r="V15" s="62"/>
+      <c r="W15" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="X15" s="63"/>
+    </row>
+    <row r="16" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="49">
+        <v>12</v>
+      </c>
+      <c r="C16" s="49"/>
+      <c r="D16" s="54" t="s">
+        <v>120</v>
+      </c>
+      <c r="E16" s="55"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="60"/>
+      <c r="I16" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J16" s="50"/>
+      <c r="K16" s="63" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="63"/>
+      <c r="M16" s="63"/>
+      <c r="N16" s="62" t="s">
+        <v>123</v>
+      </c>
+      <c r="O16" s="62"/>
+      <c r="P16" s="62"/>
+      <c r="Q16" s="62"/>
+      <c r="R16" s="62"/>
+      <c r="S16" s="62"/>
+      <c r="T16" s="62"/>
+      <c r="U16" s="62"/>
+      <c r="V16" s="62"/>
+      <c r="W16" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="X16" s="63"/>
+    </row>
+    <row r="17" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B17" s="49">
+        <v>13</v>
+      </c>
+      <c r="C17" s="49"/>
+      <c r="D17" s="54" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="55"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" s="61"/>
+      <c r="I17" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J17" s="50"/>
+      <c r="K17" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="L17" s="63"/>
+      <c r="M17" s="63"/>
+      <c r="N17" s="62" t="s">
         <v>114</v>
       </c>
-      <c r="O6" s="63"/>
-      <c r="P6" s="63"/>
-      <c r="Q6" s="63"/>
-      <c r="R6" s="63"/>
-      <c r="S6" s="63"/>
-      <c r="T6" s="63"/>
-      <c r="U6" s="63"/>
-      <c r="V6" s="63"/>
-      <c r="W6" s="64" t="s">
+      <c r="O17" s="62"/>
+      <c r="P17" s="62"/>
+      <c r="Q17" s="62"/>
+      <c r="R17" s="62"/>
+      <c r="S17" s="62"/>
+      <c r="T17" s="62"/>
+      <c r="U17" s="62"/>
+      <c r="V17" s="62"/>
+      <c r="W17" s="63" t="s">
         <v>125</v>
       </c>
-      <c r="X6" s="64"/>
-    </row>
-    <row r="7" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="50">
-        <v>3</v>
-      </c>
-      <c r="C7" s="50"/>
-      <c r="D7" s="55" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="56"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="61" t="s">
-        <v>93</v>
-      </c>
-      <c r="H7" s="61"/>
-      <c r="I7" s="51" t="s">
+      <c r="X17" s="63"/>
+    </row>
+    <row r="18" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B18" s="49">
+        <v>14</v>
+      </c>
+      <c r="C18" s="49"/>
+      <c r="D18" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="55"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" s="61"/>
+      <c r="I18" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="J7" s="51"/>
-      <c r="K7" s="64" t="s">
+      <c r="J18" s="50"/>
+      <c r="K18" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="L18" s="63"/>
+      <c r="M18" s="63"/>
+      <c r="N18" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="O18" s="62"/>
+      <c r="P18" s="62"/>
+      <c r="Q18" s="62"/>
+      <c r="R18" s="62"/>
+      <c r="S18" s="62"/>
+      <c r="T18" s="62"/>
+      <c r="U18" s="62"/>
+      <c r="V18" s="62"/>
+      <c r="W18" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="X18" s="63"/>
+    </row>
+    <row r="19" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B19" s="49">
+        <v>15</v>
+      </c>
+      <c r="C19" s="49"/>
+      <c r="D19" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" s="55"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="H19" s="61"/>
+      <c r="I19" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J19" s="50"/>
+      <c r="K19" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="L19" s="63"/>
+      <c r="M19" s="63"/>
+      <c r="N19" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="O19" s="62"/>
+      <c r="P19" s="62"/>
+      <c r="Q19" s="62"/>
+      <c r="R19" s="62"/>
+      <c r="S19" s="62"/>
+      <c r="T19" s="62"/>
+      <c r="U19" s="62"/>
+      <c r="V19" s="62"/>
+      <c r="W19" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="X19" s="63"/>
+    </row>
+    <row r="20" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B20" s="49">
+        <v>16</v>
+      </c>
+      <c r="C20" s="49"/>
+      <c r="D20" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="E20" s="55"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" s="61"/>
+      <c r="I20" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="64"/>
+      <c r="K20" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="L20" s="63"/>
+      <c r="M20" s="63"/>
+      <c r="N20" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="O20" s="62"/>
+      <c r="P20" s="62"/>
+      <c r="Q20" s="62"/>
+      <c r="R20" s="62"/>
+      <c r="S20" s="62"/>
+      <c r="T20" s="62"/>
+      <c r="U20" s="62"/>
+      <c r="V20" s="62"/>
+      <c r="W20" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="X20" s="63"/>
+    </row>
+    <row r="21" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B21" s="49">
+        <v>17</v>
+      </c>
+      <c r="C21" s="49"/>
+      <c r="D21" s="54" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" s="55"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="61"/>
+      <c r="I21" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="64"/>
+      <c r="K21" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="L21" s="63"/>
+      <c r="M21" s="63"/>
+      <c r="N21" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="O21" s="62"/>
+      <c r="P21" s="62"/>
+      <c r="Q21" s="62"/>
+      <c r="R21" s="62"/>
+      <c r="S21" s="62"/>
+      <c r="T21" s="62"/>
+      <c r="U21" s="62"/>
+      <c r="V21" s="62"/>
+      <c r="W21" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="X21" s="63"/>
+    </row>
+    <row r="22" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B22" s="49">
+        <v>18</v>
+      </c>
+      <c r="C22" s="49"/>
+      <c r="D22" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" s="55"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" s="61"/>
+      <c r="I22" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="64"/>
+      <c r="K22" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="L22" s="63"/>
+      <c r="M22" s="63"/>
+      <c r="N22" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="O22" s="62"/>
+      <c r="P22" s="62"/>
+      <c r="Q22" s="62"/>
+      <c r="R22" s="62"/>
+      <c r="S22" s="62"/>
+      <c r="T22" s="62"/>
+      <c r="U22" s="62"/>
+      <c r="V22" s="62"/>
+      <c r="W22" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="X22" s="63"/>
+    </row>
+    <row r="23" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B23" s="49">
+        <v>19</v>
+      </c>
+      <c r="C23" s="49"/>
+      <c r="D23" s="54" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23" s="55"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="H23" s="61"/>
+      <c r="I23" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="64"/>
+      <c r="K23" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="L23" s="63"/>
+      <c r="M23" s="63"/>
+      <c r="N23" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="O23" s="62"/>
+      <c r="P23" s="62"/>
+      <c r="Q23" s="62"/>
+      <c r="R23" s="62"/>
+      <c r="S23" s="62"/>
+      <c r="T23" s="62"/>
+      <c r="U23" s="62"/>
+      <c r="V23" s="62"/>
+      <c r="W23" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="X23" s="63"/>
+    </row>
+    <row r="24" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B24" s="49">
+        <v>20</v>
+      </c>
+      <c r="C24" s="49"/>
+      <c r="D24" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="55"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="H24" s="61"/>
+      <c r="I24" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="64"/>
+      <c r="K24" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="L24" s="63"/>
+      <c r="M24" s="63"/>
+      <c r="N24" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="O24" s="62"/>
+      <c r="P24" s="62"/>
+      <c r="Q24" s="62"/>
+      <c r="R24" s="62"/>
+      <c r="S24" s="62"/>
+      <c r="T24" s="62"/>
+      <c r="U24" s="62"/>
+      <c r="V24" s="62"/>
+      <c r="W24" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="X24" s="63"/>
+    </row>
+    <row r="25" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B25" s="49">
         <v>21</v>
       </c>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="63" t="s">
-        <v>112</v>
-      </c>
-      <c r="O7" s="63"/>
-      <c r="P7" s="63"/>
-      <c r="Q7" s="63"/>
-      <c r="R7" s="63"/>
-      <c r="S7" s="63"/>
-      <c r="T7" s="63"/>
-      <c r="U7" s="63"/>
-      <c r="V7" s="63"/>
-      <c r="W7" s="64" t="s">
+      <c r="C25" s="49"/>
+      <c r="D25" s="54" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="55"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" s="61"/>
+      <c r="I25" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="64"/>
+      <c r="K25" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="L25" s="63"/>
+      <c r="M25" s="63"/>
+      <c r="N25" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="O25" s="62"/>
+      <c r="P25" s="62"/>
+      <c r="Q25" s="62"/>
+      <c r="R25" s="62"/>
+      <c r="S25" s="62"/>
+      <c r="T25" s="62"/>
+      <c r="U25" s="62"/>
+      <c r="V25" s="62"/>
+      <c r="W25" s="63" t="s">
         <v>125</v>
       </c>
-      <c r="X7" s="64"/>
-    </row>
-    <row r="8" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="50">
-        <v>4</v>
-      </c>
-      <c r="C8" s="50"/>
-      <c r="D8" s="55" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="56"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="61" t="s">
-        <v>93</v>
-      </c>
-      <c r="H8" s="61"/>
-      <c r="I8" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="J8" s="51"/>
-      <c r="K8" s="64" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
-      <c r="N8" s="63" t="s">
-        <v>112</v>
-      </c>
-      <c r="O8" s="63"/>
-      <c r="P8" s="63"/>
-      <c r="Q8" s="63"/>
-      <c r="R8" s="63"/>
-      <c r="S8" s="63"/>
-      <c r="T8" s="63"/>
-      <c r="U8" s="63"/>
-      <c r="V8" s="63"/>
-      <c r="W8" s="64" t="s">
+      <c r="X25" s="63"/>
+    </row>
+    <row r="26" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B26" s="49">
+        <v>22</v>
+      </c>
+      <c r="C26" s="49"/>
+      <c r="D26" s="54" t="s">
+        <v>104</v>
+      </c>
+      <c r="E26" s="55"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="H26" s="61"/>
+      <c r="I26" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="64"/>
+      <c r="K26" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="L26" s="63"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="O26" s="62"/>
+      <c r="P26" s="62"/>
+      <c r="Q26" s="62"/>
+      <c r="R26" s="62"/>
+      <c r="S26" s="62"/>
+      <c r="T26" s="62"/>
+      <c r="U26" s="62"/>
+      <c r="V26" s="62"/>
+      <c r="W26" s="63" t="s">
         <v>125</v>
       </c>
-      <c r="X8" s="64"/>
-    </row>
-    <row r="9" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="50">
-        <v>5</v>
-      </c>
-      <c r="C9" s="50"/>
-      <c r="D9" s="55" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="56"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="61" t="s">
-        <v>93</v>
-      </c>
-      <c r="H9" s="61"/>
-      <c r="I9" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="J9" s="51"/>
-      <c r="K9" s="64" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="64"/>
-      <c r="M9" s="64"/>
-      <c r="N9" s="63" t="s">
-        <v>112</v>
-      </c>
-      <c r="O9" s="63"/>
-      <c r="P9" s="63"/>
-      <c r="Q9" s="63"/>
-      <c r="R9" s="63"/>
-      <c r="S9" s="63"/>
-      <c r="T9" s="63"/>
-      <c r="U9" s="63"/>
-      <c r="V9" s="63"/>
-      <c r="W9" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="X9" s="64"/>
-    </row>
-    <row r="10" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="50">
-        <v>6</v>
-      </c>
-      <c r="C10" s="50"/>
-      <c r="D10" s="55" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="56"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="61" t="s">
-        <v>93</v>
-      </c>
-      <c r="H10" s="61"/>
-      <c r="I10" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="J10" s="51"/>
-      <c r="K10" s="64" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" s="64"/>
-      <c r="M10" s="64"/>
-      <c r="N10" s="63" t="s">
-        <v>112</v>
-      </c>
-      <c r="O10" s="63"/>
-      <c r="P10" s="63"/>
-      <c r="Q10" s="63"/>
-      <c r="R10" s="63"/>
-      <c r="S10" s="63"/>
-      <c r="T10" s="63"/>
-      <c r="U10" s="63"/>
-      <c r="V10" s="63"/>
-      <c r="W10" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="X10" s="64"/>
-    </row>
-    <row r="11" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="50">
-        <v>7</v>
-      </c>
-      <c r="C11" s="50"/>
-      <c r="D11" s="55" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" s="56"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="61" t="s">
-        <v>93</v>
-      </c>
-      <c r="H11" s="61"/>
-      <c r="I11" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="J11" s="51"/>
-      <c r="K11" s="64" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="64"/>
-      <c r="M11" s="64"/>
-      <c r="N11" s="63" t="s">
-        <v>112</v>
-      </c>
-      <c r="O11" s="63"/>
-      <c r="P11" s="63"/>
-      <c r="Q11" s="63"/>
-      <c r="R11" s="63"/>
-      <c r="S11" s="63"/>
-      <c r="T11" s="63"/>
-      <c r="U11" s="63"/>
-      <c r="V11" s="63"/>
-      <c r="W11" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="X11" s="64"/>
-    </row>
-    <row r="12" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="50">
-        <v>8</v>
-      </c>
-      <c r="C12" s="50"/>
-      <c r="D12" s="58" t="s">
-        <v>99</v>
-      </c>
-      <c r="E12" s="59"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="61" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="61"/>
-      <c r="I12" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="J12" s="51"/>
-      <c r="K12" s="64" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" s="64"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="63" t="s">
-        <v>113</v>
-      </c>
-      <c r="O12" s="63"/>
-      <c r="P12" s="63"/>
-      <c r="Q12" s="63"/>
-      <c r="R12" s="63"/>
-      <c r="S12" s="63"/>
-      <c r="T12" s="63"/>
-      <c r="U12" s="63"/>
-      <c r="V12" s="63"/>
-      <c r="W12" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="X12" s="64"/>
-    </row>
-    <row r="13" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B13" s="50">
-        <v>9</v>
-      </c>
-      <c r="C13" s="50"/>
-      <c r="D13" s="55" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" s="56"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="61" t="s">
-        <v>93</v>
-      </c>
-      <c r="H13" s="61"/>
-      <c r="I13" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="J13" s="51"/>
-      <c r="K13" s="64" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" s="64"/>
-      <c r="M13" s="64"/>
-      <c r="N13" s="63" t="s">
-        <v>113</v>
-      </c>
-      <c r="O13" s="63"/>
-      <c r="P13" s="63"/>
-      <c r="Q13" s="63"/>
-      <c r="R13" s="63"/>
-      <c r="S13" s="63"/>
-      <c r="T13" s="63"/>
-      <c r="U13" s="63"/>
-      <c r="V13" s="63"/>
-      <c r="W13" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="X13" s="64"/>
-    </row>
-    <row r="14" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="50">
-        <v>10</v>
-      </c>
-      <c r="C14" s="50"/>
-      <c r="D14" s="55" t="s">
-        <v>121</v>
-      </c>
-      <c r="E14" s="56"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="61" t="s">
-        <v>93</v>
-      </c>
-      <c r="H14" s="61"/>
-      <c r="I14" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="J14" s="51"/>
-      <c r="K14" s="64" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="64"/>
-      <c r="M14" s="64"/>
-      <c r="N14" s="63" t="s">
-        <v>122</v>
-      </c>
-      <c r="O14" s="63"/>
-      <c r="P14" s="63"/>
-      <c r="Q14" s="63"/>
-      <c r="R14" s="63"/>
-      <c r="S14" s="63"/>
-      <c r="T14" s="63"/>
-      <c r="U14" s="63"/>
-      <c r="V14" s="63"/>
-      <c r="W14" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="X14" s="64"/>
-    </row>
-    <row r="15" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="50">
-        <v>11</v>
-      </c>
-      <c r="C15" s="50"/>
-      <c r="D15" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="E15" s="56"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="61" t="s">
-        <v>93</v>
-      </c>
-      <c r="H15" s="61"/>
-      <c r="I15" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="J15" s="51"/>
-      <c r="K15" s="64" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="64"/>
-      <c r="M15" s="64"/>
-      <c r="N15" s="63" t="s">
-        <v>123</v>
-      </c>
-      <c r="O15" s="63"/>
-      <c r="P15" s="63"/>
-      <c r="Q15" s="63"/>
-      <c r="R15" s="63"/>
-      <c r="S15" s="63"/>
-      <c r="T15" s="63"/>
-      <c r="U15" s="63"/>
-      <c r="V15" s="63"/>
-      <c r="W15" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="X15" s="64"/>
-    </row>
-    <row r="16" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="50">
-        <v>12</v>
-      </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="55" t="s">
-        <v>120</v>
-      </c>
-      <c r="E16" s="56"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="61" t="s">
-        <v>93</v>
-      </c>
-      <c r="H16" s="61"/>
-      <c r="I16" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="J16" s="51"/>
-      <c r="K16" s="64" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" s="64"/>
-      <c r="M16" s="64"/>
-      <c r="N16" s="63" t="s">
-        <v>123</v>
-      </c>
-      <c r="O16" s="63"/>
-      <c r="P16" s="63"/>
-      <c r="Q16" s="63"/>
-      <c r="R16" s="63"/>
-      <c r="S16" s="63"/>
-      <c r="T16" s="63"/>
-      <c r="U16" s="63"/>
-      <c r="V16" s="63"/>
-      <c r="W16" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="X16" s="64"/>
-    </row>
-    <row r="17" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B17" s="50">
-        <v>13</v>
-      </c>
-      <c r="C17" s="50"/>
-      <c r="D17" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="E17" s="56"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="62" t="s">
-        <v>92</v>
-      </c>
-      <c r="H17" s="62"/>
-      <c r="I17" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="J17" s="51"/>
-      <c r="K17" s="64" t="s">
-        <v>111</v>
-      </c>
-      <c r="L17" s="64"/>
-      <c r="M17" s="64"/>
-      <c r="N17" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="O17" s="63"/>
-      <c r="P17" s="63"/>
-      <c r="Q17" s="63"/>
-      <c r="R17" s="63"/>
-      <c r="S17" s="63"/>
-      <c r="T17" s="63"/>
-      <c r="U17" s="63"/>
-      <c r="V17" s="63"/>
-      <c r="W17" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="X17" s="64"/>
-    </row>
-    <row r="18" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B18" s="50">
-        <v>14</v>
-      </c>
-      <c r="C18" s="50"/>
-      <c r="D18" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" s="56"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="62" t="s">
-        <v>92</v>
-      </c>
-      <c r="H18" s="62"/>
-      <c r="I18" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="J18" s="51"/>
-      <c r="K18" s="64" t="s">
-        <v>111</v>
-      </c>
-      <c r="L18" s="64"/>
-      <c r="M18" s="64"/>
-      <c r="N18" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="O18" s="63"/>
-      <c r="P18" s="63"/>
-      <c r="Q18" s="63"/>
-      <c r="R18" s="63"/>
-      <c r="S18" s="63"/>
-      <c r="T18" s="63"/>
-      <c r="U18" s="63"/>
-      <c r="V18" s="63"/>
-      <c r="W18" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="X18" s="64"/>
-    </row>
-    <row r="19" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B19" s="50">
-        <v>15</v>
-      </c>
-      <c r="C19" s="50"/>
-      <c r="D19" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="E19" s="56"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="62" t="s">
-        <v>92</v>
-      </c>
-      <c r="H19" s="62"/>
-      <c r="I19" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="J19" s="51"/>
-      <c r="K19" s="64" t="s">
-        <v>111</v>
-      </c>
-      <c r="L19" s="64"/>
-      <c r="M19" s="64"/>
-      <c r="N19" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="O19" s="63"/>
-      <c r="P19" s="63"/>
-      <c r="Q19" s="63"/>
-      <c r="R19" s="63"/>
-      <c r="S19" s="63"/>
-      <c r="T19" s="63"/>
-      <c r="U19" s="63"/>
-      <c r="V19" s="63"/>
-      <c r="W19" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="X19" s="64"/>
-    </row>
-    <row r="20" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B20" s="50">
-        <v>16</v>
-      </c>
-      <c r="C20" s="50"/>
-      <c r="D20" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="E20" s="56"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="62" t="s">
-        <v>92</v>
-      </c>
-      <c r="H20" s="62"/>
-      <c r="I20" s="65" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" s="65"/>
-      <c r="K20" s="64" t="s">
-        <v>111</v>
-      </c>
-      <c r="L20" s="64"/>
-      <c r="M20" s="64"/>
-      <c r="N20" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="O20" s="63"/>
-      <c r="P20" s="63"/>
-      <c r="Q20" s="63"/>
-      <c r="R20" s="63"/>
-      <c r="S20" s="63"/>
-      <c r="T20" s="63"/>
-      <c r="U20" s="63"/>
-      <c r="V20" s="63"/>
-      <c r="W20" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="X20" s="64"/>
-    </row>
-    <row r="21" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B21" s="50">
-        <v>17</v>
-      </c>
-      <c r="C21" s="50"/>
-      <c r="D21" s="55" t="s">
-        <v>106</v>
-      </c>
-      <c r="E21" s="56"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="62" t="s">
-        <v>92</v>
-      </c>
-      <c r="H21" s="62"/>
-      <c r="I21" s="65" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="65"/>
-      <c r="K21" s="64" t="s">
-        <v>111</v>
-      </c>
-      <c r="L21" s="64"/>
-      <c r="M21" s="64"/>
-      <c r="N21" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="O21" s="63"/>
-      <c r="P21" s="63"/>
-      <c r="Q21" s="63"/>
-      <c r="R21" s="63"/>
-      <c r="S21" s="63"/>
-      <c r="T21" s="63"/>
-      <c r="U21" s="63"/>
-      <c r="V21" s="63"/>
-      <c r="W21" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="X21" s="64"/>
-    </row>
-    <row r="22" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B22" s="50">
-        <v>18</v>
-      </c>
-      <c r="C22" s="50"/>
-      <c r="D22" s="55" t="s">
-        <v>107</v>
-      </c>
-      <c r="E22" s="56"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="62" t="s">
-        <v>92</v>
-      </c>
-      <c r="H22" s="62"/>
-      <c r="I22" s="65" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="65"/>
-      <c r="K22" s="64" t="s">
-        <v>111</v>
-      </c>
-      <c r="L22" s="64"/>
-      <c r="M22" s="64"/>
-      <c r="N22" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="O22" s="63"/>
-      <c r="P22" s="63"/>
-      <c r="Q22" s="63"/>
-      <c r="R22" s="63"/>
-      <c r="S22" s="63"/>
-      <c r="T22" s="63"/>
-      <c r="U22" s="63"/>
-      <c r="V22" s="63"/>
-      <c r="W22" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="X22" s="64"/>
-    </row>
-    <row r="23" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B23" s="50">
-        <v>19</v>
-      </c>
-      <c r="C23" s="50"/>
-      <c r="D23" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="E23" s="56"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="62" t="s">
-        <v>92</v>
-      </c>
-      <c r="H23" s="62"/>
-      <c r="I23" s="65" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="65"/>
-      <c r="K23" s="64" t="s">
-        <v>111</v>
-      </c>
-      <c r="L23" s="64"/>
-      <c r="M23" s="64"/>
-      <c r="N23" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="O23" s="63"/>
-      <c r="P23" s="63"/>
-      <c r="Q23" s="63"/>
-      <c r="R23" s="63"/>
-      <c r="S23" s="63"/>
-      <c r="T23" s="63"/>
-      <c r="U23" s="63"/>
-      <c r="V23" s="63"/>
-      <c r="W23" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="X23" s="64"/>
-    </row>
-    <row r="24" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B24" s="50">
-        <v>20</v>
-      </c>
-      <c r="C24" s="50"/>
-      <c r="D24" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="E24" s="56"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="62" t="s">
-        <v>92</v>
-      </c>
-      <c r="H24" s="62"/>
-      <c r="I24" s="65" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="65"/>
-      <c r="K24" s="64" t="s">
-        <v>111</v>
-      </c>
-      <c r="L24" s="64"/>
-      <c r="M24" s="64"/>
-      <c r="N24" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="O24" s="63"/>
-      <c r="P24" s="63"/>
-      <c r="Q24" s="63"/>
-      <c r="R24" s="63"/>
-      <c r="S24" s="63"/>
-      <c r="T24" s="63"/>
-      <c r="U24" s="63"/>
-      <c r="V24" s="63"/>
-      <c r="W24" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="X24" s="64"/>
-    </row>
-    <row r="25" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B25" s="50">
-        <v>21</v>
-      </c>
-      <c r="C25" s="50"/>
-      <c r="D25" s="55" t="s">
-        <v>110</v>
-      </c>
-      <c r="E25" s="56"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="62" t="s">
-        <v>92</v>
-      </c>
-      <c r="H25" s="62"/>
-      <c r="I25" s="65" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="65"/>
-      <c r="K25" s="64" t="s">
-        <v>111</v>
-      </c>
-      <c r="L25" s="64"/>
-      <c r="M25" s="64"/>
-      <c r="N25" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="O25" s="63"/>
-      <c r="P25" s="63"/>
-      <c r="Q25" s="63"/>
-      <c r="R25" s="63"/>
-      <c r="S25" s="63"/>
-      <c r="T25" s="63"/>
-      <c r="U25" s="63"/>
-      <c r="V25" s="63"/>
-      <c r="W25" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="X25" s="64"/>
-    </row>
-    <row r="26" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B26" s="50">
-        <v>22</v>
-      </c>
-      <c r="C26" s="50"/>
-      <c r="D26" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="E26" s="56"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="62" t="s">
-        <v>92</v>
-      </c>
-      <c r="H26" s="62"/>
-      <c r="I26" s="65" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="65"/>
-      <c r="K26" s="64" t="s">
-        <v>111</v>
-      </c>
-      <c r="L26" s="64"/>
-      <c r="M26" s="64"/>
-      <c r="N26" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="O26" s="63"/>
-      <c r="P26" s="63"/>
-      <c r="Q26" s="63"/>
-      <c r="R26" s="63"/>
-      <c r="S26" s="63"/>
-      <c r="T26" s="63"/>
-      <c r="U26" s="63"/>
-      <c r="V26" s="63"/>
-      <c r="W26" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="X26" s="64"/>
+      <c r="X26" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="161">
@@ -6731,7 +6745,7 @@
   <sheetData>
     <row r="2" spans="1:1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9892E8-3062-4453-83EE-54D9FA49B30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48BE0603-83CB-42B4-A0B8-CF70F4D1F79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="209">
   <si>
     <t>SIGNOMALY</t>
   </si>
@@ -1247,9 +1247,6 @@
     <t>Dùng để hướng dẫn phương pháp giải đố, cách giải đố.</t>
   </si>
   <si>
-    <t>Loại</t>
-  </si>
-  <si>
     <t>Tên Item</t>
   </si>
   <si>
@@ -1289,9 +1286,6 @@
     <t>Chair</t>
   </si>
   <si>
-    <t>Decoration</t>
-  </si>
-  <si>
     <t>Giấy câu đố</t>
   </si>
   <si>
@@ -1304,13 +1298,7 @@
     <t>V. SCENES</t>
   </si>
   <si>
-    <t>Key item No</t>
-  </si>
-  <si>
     <t>Mico (NPC)</t>
-  </si>
-  <si>
-    <t>Instruction</t>
   </si>
   <si>
     <t>Tranh Puzzle #1</t>
@@ -1887,7 +1875,79 @@
     <t>VIII. DIALOGUES</t>
   </si>
   <si>
-    <t>Sau khi hiển thị Timelapse, nó sẽ luôn ở biến thể B. Và sau khi ông hoàn thành điều kiện, nó sẽ quay trở lại biến thể A.</t>
+    <t>Sau khi hiển thị Timelapse, nó sẽ luôn ở biến thể B. Và sau khi hoàn thành điều kiện, nó sẽ quay trở lại biến thể A.</t>
+  </si>
+  <si>
+    <t>Nút UI của E sẽ hiển thị ở vị trí của object.</t>
+  </si>
+  <si>
+    <t>Key item ID</t>
+  </si>
+  <si>
+    <t>INS_GUIDE</t>
+  </si>
+  <si>
+    <t>INS_MICRO</t>
+  </si>
+  <si>
+    <t>PZS_MERCURY</t>
+  </si>
+  <si>
+    <t>PZS_VENUS</t>
+  </si>
+  <si>
+    <t>PZS_EARTH</t>
+  </si>
+  <si>
+    <t>PZS_MARS</t>
+  </si>
+  <si>
+    <t>PZS_JUPITER</t>
+  </si>
+  <si>
+    <t>PZ_COMPASS</t>
+  </si>
+  <si>
+    <t>PZ_KEY</t>
+  </si>
+  <si>
+    <t>PZ_MACHINE</t>
+  </si>
+  <si>
+    <t>PZ_PICTURE1</t>
+  </si>
+  <si>
+    <t>PZ_PICTURE2</t>
+  </si>
+  <si>
+    <t>DEC_FLOWER</t>
+  </si>
+  <si>
+    <t>DEC_BALL</t>
+  </si>
+  <si>
+    <t>DEC_COINS</t>
+  </si>
+  <si>
+    <t>DEC_MIRROR</t>
+  </si>
+  <si>
+    <t>DEC_LAMP</t>
+  </si>
+  <si>
+    <t>DEC_CHAMP</t>
+  </si>
+  <si>
+    <t>DEC_COFFEE</t>
+  </si>
+  <si>
+    <t>DEC_TABLE</t>
+  </si>
+  <si>
+    <t>DEC_CHAIR</t>
+  </si>
+  <si>
+    <t>DEC_STATUE</t>
   </si>
 </sst>
 </file>
@@ -2881,11 +2941,11 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>9524</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>42625</xdr:rowOff>
+      <xdr:rowOff>10477</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>380999</xdr:colOff>
+      <xdr:colOff>428625</xdr:colOff>
       <xdr:row>54</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
@@ -2917,8 +2977,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="619124" y="9910525"/>
-          <a:ext cx="7077075" cy="4777025"/>
+          <a:off x="619124" y="9497377"/>
+          <a:ext cx="7124701" cy="4809173"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3001,15 +3061,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
+      <xdr:colOff>590549</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>226817</xdr:rowOff>
+      <xdr:colOff>321056</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3032,8 +3092,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="590550" y="1123950"/>
-          <a:ext cx="5734050" cy="6608567"/>
+          <a:off x="590549" y="1123950"/>
+          <a:ext cx="5826507" cy="6715125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3621,7 +3681,7 @@
     </row>
     <row r="12" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B12" s="77" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C12" s="77"/>
       <c r="D12" s="77"/>
@@ -3796,7 +3856,7 @@
     </row>
     <row r="20" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="22" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C20" s="22"/>
       <c r="D20" s="22"/>
@@ -3956,7 +4016,7 @@
   <sheetData>
     <row r="2" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B2" s="8"/>
     </row>
@@ -4358,12 +4418,12 @@
   <sheetData>
     <row r="2" spans="1:30" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="19.5" x14ac:dyDescent="0.25">
@@ -4457,7 +4517,7 @@
     </row>
     <row r="16" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B16" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
@@ -4548,7 +4608,7 @@
     </row>
     <row r="25" spans="2:33" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T25" s="47" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="U25" s="21"/>
       <c r="V25" s="21"/>
@@ -4582,7 +4642,7 @@
     </row>
     <row r="27" spans="2:33" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T27" s="47" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="U27" s="47"/>
       <c r="V27" s="47"/>
@@ -4962,7 +5022,7 @@
     </row>
     <row r="70" spans="20:37" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T70" s="47" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="U70" s="47"/>
       <c r="V70" s="47"/>
@@ -4992,7 +5052,7 @@
     </row>
     <row r="74" spans="20:37" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="T74" s="47" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="U74" s="21"/>
       <c r="V74" s="21"/>
@@ -5166,12 +5226,12 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A2:AJ128"/>
+  <dimension ref="A2:AJ130"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
@@ -5180,7 +5240,7 @@
     <row r="4" spans="1:36" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="B4" s="30" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C4" s="30"/>
       <c r="D4" s="30"/>
@@ -5190,7 +5250,7 @@
     <row r="5" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="L5" s="41" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M5" s="41"/>
       <c r="N5" s="41"/>
@@ -5200,7 +5260,7 @@
     <row r="6" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
       <c r="L6" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="M6" s="69"/>
       <c r="N6" s="69"/>
@@ -5210,7 +5270,7 @@
     <row r="7" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="L7" s="62" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="M7" s="62"/>
       <c r="N7" s="62"/>
@@ -5220,7 +5280,7 @@
     <row r="8" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
       <c r="L8" s="69" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="M8" s="69"/>
       <c r="N8" s="69"/>
@@ -5230,7 +5290,7 @@
     <row r="9" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1"/>
       <c r="L9" s="69" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M9" s="69"/>
       <c r="N9" s="69"/>
@@ -5249,7 +5309,7 @@
     <row r="10" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
       <c r="L10" s="62" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="M10" s="62"/>
       <c r="N10" s="62"/>
@@ -5268,7 +5328,7 @@
     <row r="11" spans="1:36" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
       <c r="L11" s="62" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="M11" s="69"/>
       <c r="N11" s="69"/>
@@ -5287,7 +5347,7 @@
     <row r="12" spans="1:36" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1"/>
       <c r="L12" s="62" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="M12" s="62"/>
       <c r="N12" s="62"/>
@@ -5302,7 +5362,7 @@
     <row r="13" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="L13" s="69" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="M13" s="69"/>
       <c r="N13" s="69"/>
@@ -5313,7 +5373,7 @@
       <c r="T13" s="70"/>
       <c r="U13" s="70"/>
       <c r="W13" s="73" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="X13" s="73"/>
       <c r="Y13" s="73"/>
@@ -5332,7 +5392,7 @@
     <row r="14" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A14" s="1"/>
       <c r="L14" s="69" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="M14" s="69"/>
       <c r="N14" s="69"/>
@@ -5358,12 +5418,12 @@
     <row r="17" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A17" s="1"/>
       <c r="L17" s="41" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M17" s="41"/>
       <c r="N17" s="41"/>
       <c r="O17" s="41" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P17" s="41"/>
       <c r="Q17" s="41"/>
@@ -5374,12 +5434,12 @@
     <row r="18" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
       <c r="L18" s="37" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="M18" s="37"/>
       <c r="N18" s="37"/>
       <c r="O18" s="72" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="P18" s="72"/>
       <c r="Q18" s="72"/>
@@ -5390,12 +5450,12 @@
     <row r="19" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="L19" s="37" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="M19" s="37"/>
       <c r="N19" s="37"/>
       <c r="O19" s="72" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="P19" s="72"/>
       <c r="Q19" s="72"/>
@@ -5406,12 +5466,12 @@
     <row r="20" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
       <c r="L20" s="37" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M20" s="37"/>
       <c r="N20" s="37"/>
       <c r="O20" s="72" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="P20" s="72"/>
       <c r="Q20" s="72"/>
@@ -5435,7 +5495,7 @@
     </row>
     <row r="25" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B25" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
@@ -5443,12 +5503,12 @@
     </row>
     <row r="27" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B27" s="8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="56" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B56" s="65" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
@@ -5456,17 +5516,17 @@
     </row>
     <row r="58" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="85" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B85" s="65" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="87" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B87" s="8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="88" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
@@ -5474,42 +5534,42 @@
     </row>
     <row r="89" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B89" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="91" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B91" s="65" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="93" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B93" s="74" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="94" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B94" s="74" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="95" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B95" s="74" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="97" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B97" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="99" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B99" s="65" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="101" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B101" s="65" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="102" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
@@ -5517,12 +5577,12 @@
     </row>
     <row r="103" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B103" s="65" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B105" s="75" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C105" s="75"/>
       <c r="D105" s="75"/>
@@ -5550,19 +5610,19 @@
     </row>
     <row r="108" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A108" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="110" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B110" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C110" s="8"/>
       <c r="D110" s="76"/>
     </row>
     <row r="112" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B112" s="65" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="113" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
@@ -5570,50 +5630,58 @@
     </row>
     <row r="114" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B114" s="65" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="116" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B116" s="8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="118" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B118" s="65" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AC118" s="78" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="120" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B120" s="65" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="121" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B121" s="65"/>
+    </row>
+    <row r="122" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B122" s="65" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="124" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B124" s="8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="126" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B126" s="65" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="128" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B128" s="8" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="122" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B122" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="124" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B124" s="65" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="126" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B126" s="8" t="s">
+    <row r="130" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B130" s="65" t="s">
+        <v>174</v>
+      </c>
+      <c r="L130" s="79" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="128" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B128" s="65" t="s">
-        <v>178</v>
-      </c>
-      <c r="L128" s="79" t="s">
-        <v>177</v>
-      </c>
-      <c r="M128" s="65"/>
+      <c r="M130" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -5640,7 +5708,7 @@
     <mergeCell ref="B4:F4"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="L128" location="Dialogues!A1" display="Dialogues!A1" xr:uid="{5724AB96-1B0F-4DFD-A35F-382AC93CCD96}"/>
+    <hyperlink ref="L130" location="Dialogues!A1" display="Dialogues!A1" xr:uid="{5724AB96-1B0F-4DFD-A35F-382AC93CCD96}"/>
     <hyperlink ref="AC118" location="'Item List'!A1" display="'Item List'!A1" xr:uid="{961E795F-F85E-4E2A-BAED-F63C80C609A5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5653,21 +5721,21 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A2:X26"/>
+  <dimension ref="A2:U26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:24" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="39" t="s">
-        <v>116</v>
+        <v>186</v>
       </c>
       <c r="C4" s="39"/>
       <c r="D4" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E4" s="52"/>
       <c r="F4" s="53"/>
@@ -5676,33 +5744,28 @@
       </c>
       <c r="H4" s="39"/>
       <c r="I4" s="39" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="J4" s="39"/>
       <c r="K4" s="39" t="s">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="L4" s="39"/>
       <c r="M4" s="39"/>
-      <c r="N4" s="39" t="s">
-        <v>19</v>
-      </c>
+      <c r="N4" s="39"/>
       <c r="O4" s="39"/>
       <c r="P4" s="39"/>
       <c r="Q4" s="39"/>
       <c r="R4" s="39"/>
       <c r="S4" s="39"/>
-      <c r="T4" s="39"/>
+      <c r="T4" s="39" t="s">
+        <v>122</v>
+      </c>
       <c r="U4" s="39"/>
-      <c r="V4" s="39"/>
-      <c r="W4" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="X4" s="39"/>
-    </row>
-    <row r="5" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="49">
-        <v>1</v>
+    </row>
+    <row r="5" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="49" t="s">
+        <v>187</v>
       </c>
       <c r="C5" s="49"/>
       <c r="D5" s="54" t="s">
@@ -5718,34 +5781,29 @@
         <v>94</v>
       </c>
       <c r="J5" s="50"/>
-      <c r="K5" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="L5" s="63"/>
-      <c r="M5" s="63"/>
-      <c r="N5" s="62" t="s">
+      <c r="K5" s="62" t="s">
         <v>96</v>
       </c>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="62"/>
       <c r="O5" s="62"/>
       <c r="P5" s="62"/>
       <c r="Q5" s="62"/>
       <c r="R5" s="62"/>
       <c r="S5" s="62"/>
-      <c r="T5" s="62"/>
-      <c r="U5" s="62"/>
-      <c r="V5" s="62"/>
-      <c r="W5" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X5" s="63"/>
-    </row>
-    <row r="6" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B6" s="49">
-        <v>2</v>
+      <c r="T5" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U5" s="63"/>
+    </row>
+    <row r="6" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B6" s="49" t="s">
+        <v>188</v>
       </c>
       <c r="C6" s="49"/>
       <c r="D6" s="54" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E6" s="55"/>
       <c r="F6" s="56"/>
@@ -5757,30 +5815,25 @@
         <v>94</v>
       </c>
       <c r="J6" s="50"/>
-      <c r="K6" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="L6" s="63"/>
-      <c r="M6" s="63"/>
-      <c r="N6" s="62" t="s">
-        <v>186</v>
-      </c>
+      <c r="K6" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
       <c r="O6" s="62"/>
       <c r="P6" s="62"/>
       <c r="Q6" s="62"/>
       <c r="R6" s="62"/>
       <c r="S6" s="62"/>
-      <c r="T6" s="62"/>
-      <c r="U6" s="62"/>
-      <c r="V6" s="62"/>
-      <c r="W6" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X6" s="63"/>
-    </row>
-    <row r="7" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="49">
-        <v>3</v>
+      <c r="T6" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U6" s="63"/>
+    </row>
+    <row r="7" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="49" t="s">
+        <v>189</v>
       </c>
       <c r="C7" s="49"/>
       <c r="D7" s="54" t="s">
@@ -5796,30 +5849,25 @@
         <v>94</v>
       </c>
       <c r="J7" s="50"/>
-      <c r="K7" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="63"/>
-      <c r="M7" s="63"/>
-      <c r="N7" s="62" t="s">
-        <v>112</v>
-      </c>
+      <c r="K7" s="62" t="s">
+        <v>110</v>
+      </c>
+      <c r="L7" s="62"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="62"/>
       <c r="O7" s="62"/>
       <c r="P7" s="62"/>
       <c r="Q7" s="62"/>
       <c r="R7" s="62"/>
       <c r="S7" s="62"/>
-      <c r="T7" s="62"/>
-      <c r="U7" s="62"/>
-      <c r="V7" s="62"/>
-      <c r="W7" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X7" s="63"/>
-    </row>
-    <row r="8" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="49">
-        <v>4</v>
+      <c r="T7" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U7" s="63"/>
+    </row>
+    <row r="8" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="49" t="s">
+        <v>190</v>
       </c>
       <c r="C8" s="49"/>
       <c r="D8" s="54" t="s">
@@ -5835,30 +5883,25 @@
         <v>94</v>
       </c>
       <c r="J8" s="50"/>
-      <c r="K8" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="63"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="62" t="s">
-        <v>112</v>
-      </c>
+      <c r="K8" s="62" t="s">
+        <v>110</v>
+      </c>
+      <c r="L8" s="62"/>
+      <c r="M8" s="62"/>
+      <c r="N8" s="62"/>
       <c r="O8" s="62"/>
       <c r="P8" s="62"/>
       <c r="Q8" s="62"/>
       <c r="R8" s="62"/>
       <c r="S8" s="62"/>
-      <c r="T8" s="62"/>
-      <c r="U8" s="62"/>
-      <c r="V8" s="62"/>
-      <c r="W8" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X8" s="63"/>
-    </row>
-    <row r="9" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="49">
-        <v>5</v>
+      <c r="T8" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U8" s="63"/>
+    </row>
+    <row r="9" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="49" t="s">
+        <v>191</v>
       </c>
       <c r="C9" s="49"/>
       <c r="D9" s="54" t="s">
@@ -5874,30 +5917,25 @@
         <v>94</v>
       </c>
       <c r="J9" s="50"/>
-      <c r="K9" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="63"/>
-      <c r="M9" s="63"/>
-      <c r="N9" s="62" t="s">
-        <v>112</v>
-      </c>
+      <c r="K9" s="62" t="s">
+        <v>110</v>
+      </c>
+      <c r="L9" s="62"/>
+      <c r="M9" s="62"/>
+      <c r="N9" s="62"/>
       <c r="O9" s="62"/>
       <c r="P9" s="62"/>
       <c r="Q9" s="62"/>
       <c r="R9" s="62"/>
       <c r="S9" s="62"/>
-      <c r="T9" s="62"/>
-      <c r="U9" s="62"/>
-      <c r="V9" s="62"/>
-      <c r="W9" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X9" s="63"/>
-    </row>
-    <row r="10" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="49">
-        <v>6</v>
+      <c r="T9" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U9" s="63"/>
+    </row>
+    <row r="10" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="49" t="s">
+        <v>192</v>
       </c>
       <c r="C10" s="49"/>
       <c r="D10" s="54" t="s">
@@ -5913,30 +5951,25 @@
         <v>94</v>
       </c>
       <c r="J10" s="50"/>
-      <c r="K10" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" s="63"/>
-      <c r="M10" s="63"/>
-      <c r="N10" s="62" t="s">
-        <v>112</v>
-      </c>
+      <c r="K10" s="62" t="s">
+        <v>110</v>
+      </c>
+      <c r="L10" s="62"/>
+      <c r="M10" s="62"/>
+      <c r="N10" s="62"/>
       <c r="O10" s="62"/>
       <c r="P10" s="62"/>
       <c r="Q10" s="62"/>
       <c r="R10" s="62"/>
       <c r="S10" s="62"/>
-      <c r="T10" s="62"/>
-      <c r="U10" s="62"/>
-      <c r="V10" s="62"/>
-      <c r="W10" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X10" s="63"/>
-    </row>
-    <row r="11" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="49">
-        <v>7</v>
+      <c r="T10" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U10" s="63"/>
+    </row>
+    <row r="11" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="49" t="s">
+        <v>193</v>
       </c>
       <c r="C11" s="49"/>
       <c r="D11" s="54" t="s">
@@ -5952,34 +5985,29 @@
         <v>94</v>
       </c>
       <c r="J11" s="50"/>
-      <c r="K11" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="63"/>
-      <c r="M11" s="63"/>
-      <c r="N11" s="62" t="s">
-        <v>112</v>
-      </c>
+      <c r="K11" s="62" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11" s="62"/>
+      <c r="M11" s="62"/>
+      <c r="N11" s="62"/>
       <c r="O11" s="62"/>
       <c r="P11" s="62"/>
       <c r="Q11" s="62"/>
       <c r="R11" s="62"/>
       <c r="S11" s="62"/>
-      <c r="T11" s="62"/>
-      <c r="U11" s="62"/>
-      <c r="V11" s="62"/>
-      <c r="W11" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X11" s="63"/>
-    </row>
-    <row r="12" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="49">
-        <v>8</v>
+      <c r="T11" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U11" s="63"/>
+    </row>
+    <row r="12" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="49" t="s">
+        <v>194</v>
       </c>
       <c r="C12" s="49"/>
       <c r="D12" s="57" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E12" s="58"/>
       <c r="F12" s="59"/>
@@ -5991,34 +6019,29 @@
         <v>94</v>
       </c>
       <c r="J12" s="50"/>
-      <c r="K12" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" s="63"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="62" t="s">
-        <v>113</v>
-      </c>
+      <c r="K12" s="62" t="s">
+        <v>111</v>
+      </c>
+      <c r="L12" s="62"/>
+      <c r="M12" s="62"/>
+      <c r="N12" s="62"/>
       <c r="O12" s="62"/>
       <c r="P12" s="62"/>
       <c r="Q12" s="62"/>
       <c r="R12" s="62"/>
       <c r="S12" s="62"/>
-      <c r="T12" s="62"/>
-      <c r="U12" s="62"/>
-      <c r="V12" s="62"/>
-      <c r="W12" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X12" s="63"/>
-    </row>
-    <row r="13" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B13" s="49">
-        <v>9</v>
+      <c r="T12" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U12" s="63"/>
+    </row>
+    <row r="13" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="49" t="s">
+        <v>195</v>
       </c>
       <c r="C13" s="49"/>
       <c r="D13" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E13" s="55"/>
       <c r="F13" s="56"/>
@@ -6030,34 +6053,29 @@
         <v>94</v>
       </c>
       <c r="J13" s="50"/>
-      <c r="K13" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" s="63"/>
-      <c r="M13" s="63"/>
-      <c r="N13" s="62" t="s">
-        <v>113</v>
-      </c>
+      <c r="K13" s="62" t="s">
+        <v>111</v>
+      </c>
+      <c r="L13" s="62"/>
+      <c r="M13" s="62"/>
+      <c r="N13" s="62"/>
       <c r="O13" s="62"/>
       <c r="P13" s="62"/>
       <c r="Q13" s="62"/>
       <c r="R13" s="62"/>
       <c r="S13" s="62"/>
-      <c r="T13" s="62"/>
-      <c r="U13" s="62"/>
-      <c r="V13" s="62"/>
-      <c r="W13" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X13" s="63"/>
-    </row>
-    <row r="14" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="49">
-        <v>10</v>
+      <c r="T13" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U13" s="63"/>
+    </row>
+    <row r="14" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="49" t="s">
+        <v>196</v>
       </c>
       <c r="C14" s="49"/>
       <c r="D14" s="54" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E14" s="55"/>
       <c r="F14" s="56"/>
@@ -6069,34 +6087,29 @@
         <v>94</v>
       </c>
       <c r="J14" s="50"/>
-      <c r="K14" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="63"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="62" t="s">
-        <v>122</v>
-      </c>
+      <c r="K14" s="62" t="s">
+        <v>118</v>
+      </c>
+      <c r="L14" s="62"/>
+      <c r="M14" s="62"/>
+      <c r="N14" s="62"/>
       <c r="O14" s="62"/>
       <c r="P14" s="62"/>
       <c r="Q14" s="62"/>
       <c r="R14" s="62"/>
       <c r="S14" s="62"/>
-      <c r="T14" s="62"/>
-      <c r="U14" s="62"/>
-      <c r="V14" s="62"/>
-      <c r="W14" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X14" s="63"/>
-    </row>
-    <row r="15" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="49">
-        <v>11</v>
+      <c r="T14" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U14" s="63"/>
+    </row>
+    <row r="15" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="49" t="s">
+        <v>197</v>
       </c>
       <c r="C15" s="49"/>
       <c r="D15" s="54" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E15" s="55"/>
       <c r="F15" s="56"/>
@@ -6108,34 +6121,29 @@
         <v>94</v>
       </c>
       <c r="J15" s="50"/>
-      <c r="K15" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="63"/>
-      <c r="M15" s="63"/>
-      <c r="N15" s="62" t="s">
-        <v>123</v>
-      </c>
+      <c r="K15" s="62" t="s">
+        <v>119</v>
+      </c>
+      <c r="L15" s="62"/>
+      <c r="M15" s="62"/>
+      <c r="N15" s="62"/>
       <c r="O15" s="62"/>
       <c r="P15" s="62"/>
       <c r="Q15" s="62"/>
       <c r="R15" s="62"/>
       <c r="S15" s="62"/>
-      <c r="T15" s="62"/>
-      <c r="U15" s="62"/>
-      <c r="V15" s="62"/>
-      <c r="W15" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X15" s="63"/>
-    </row>
-    <row r="16" spans="1:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="49">
-        <v>12</v>
+      <c r="T15" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U15" s="63"/>
+    </row>
+    <row r="16" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="49" t="s">
+        <v>198</v>
       </c>
       <c r="C16" s="49"/>
       <c r="D16" s="54" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E16" s="55"/>
       <c r="F16" s="56"/>
@@ -6147,34 +6155,29 @@
         <v>94</v>
       </c>
       <c r="J16" s="50"/>
-      <c r="K16" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" s="63"/>
-      <c r="M16" s="63"/>
-      <c r="N16" s="62" t="s">
-        <v>123</v>
-      </c>
+      <c r="K16" s="62" t="s">
+        <v>119</v>
+      </c>
+      <c r="L16" s="62"/>
+      <c r="M16" s="62"/>
+      <c r="N16" s="62"/>
       <c r="O16" s="62"/>
       <c r="P16" s="62"/>
       <c r="Q16" s="62"/>
       <c r="R16" s="62"/>
       <c r="S16" s="62"/>
-      <c r="T16" s="62"/>
-      <c r="U16" s="62"/>
-      <c r="V16" s="62"/>
-      <c r="W16" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X16" s="63"/>
-    </row>
-    <row r="17" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B17" s="49">
-        <v>13</v>
+      <c r="T16" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U16" s="63"/>
+    </row>
+    <row r="17" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B17" s="49" t="s">
+        <v>199</v>
       </c>
       <c r="C17" s="49"/>
       <c r="D17" s="54" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E17" s="55"/>
       <c r="F17" s="56"/>
@@ -6186,34 +6189,29 @@
         <v>94</v>
       </c>
       <c r="J17" s="50"/>
-      <c r="K17" s="63" t="s">
-        <v>111</v>
-      </c>
-      <c r="L17" s="63"/>
-      <c r="M17" s="63"/>
-      <c r="N17" s="62" t="s">
-        <v>114</v>
-      </c>
+      <c r="K17" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="L17" s="62"/>
+      <c r="M17" s="62"/>
+      <c r="N17" s="62"/>
       <c r="O17" s="62"/>
       <c r="P17" s="62"/>
       <c r="Q17" s="62"/>
       <c r="R17" s="62"/>
       <c r="S17" s="62"/>
-      <c r="T17" s="62"/>
-      <c r="U17" s="62"/>
-      <c r="V17" s="62"/>
-      <c r="W17" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X17" s="63"/>
-    </row>
-    <row r="18" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B18" s="49">
-        <v>14</v>
+      <c r="T17" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U17" s="63"/>
+    </row>
+    <row r="18" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B18" s="49" t="s">
+        <v>200</v>
       </c>
       <c r="C18" s="49"/>
       <c r="D18" s="54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E18" s="55"/>
       <c r="F18" s="56"/>
@@ -6225,34 +6223,29 @@
         <v>94</v>
       </c>
       <c r="J18" s="50"/>
-      <c r="K18" s="63" t="s">
-        <v>111</v>
-      </c>
-      <c r="L18" s="63"/>
-      <c r="M18" s="63"/>
-      <c r="N18" s="62" t="s">
-        <v>114</v>
-      </c>
+      <c r="K18" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="L18" s="62"/>
+      <c r="M18" s="62"/>
+      <c r="N18" s="62"/>
       <c r="O18" s="62"/>
       <c r="P18" s="62"/>
       <c r="Q18" s="62"/>
       <c r="R18" s="62"/>
       <c r="S18" s="62"/>
-      <c r="T18" s="62"/>
-      <c r="U18" s="62"/>
-      <c r="V18" s="62"/>
-      <c r="W18" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X18" s="63"/>
-    </row>
-    <row r="19" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B19" s="49">
-        <v>15</v>
+      <c r="T18" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U18" s="63"/>
+    </row>
+    <row r="19" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B19" s="49" t="s">
+        <v>201</v>
       </c>
       <c r="C19" s="49"/>
       <c r="D19" s="54" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E19" s="55"/>
       <c r="F19" s="56"/>
@@ -6264,34 +6257,29 @@
         <v>94</v>
       </c>
       <c r="J19" s="50"/>
-      <c r="K19" s="63" t="s">
-        <v>111</v>
-      </c>
-      <c r="L19" s="63"/>
-      <c r="M19" s="63"/>
-      <c r="N19" s="62" t="s">
-        <v>114</v>
-      </c>
+      <c r="K19" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="L19" s="62"/>
+      <c r="M19" s="62"/>
+      <c r="N19" s="62"/>
       <c r="O19" s="62"/>
       <c r="P19" s="62"/>
       <c r="Q19" s="62"/>
       <c r="R19" s="62"/>
       <c r="S19" s="62"/>
-      <c r="T19" s="62"/>
-      <c r="U19" s="62"/>
-      <c r="V19" s="62"/>
-      <c r="W19" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X19" s="63"/>
-    </row>
-    <row r="20" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B20" s="49">
-        <v>16</v>
+      <c r="T19" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U19" s="63"/>
+    </row>
+    <row r="20" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B20" s="49" t="s">
+        <v>202</v>
       </c>
       <c r="C20" s="49"/>
       <c r="D20" s="54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E20" s="55"/>
       <c r="F20" s="56"/>
@@ -6303,34 +6291,29 @@
         <v>15</v>
       </c>
       <c r="J20" s="64"/>
-      <c r="K20" s="63" t="s">
-        <v>111</v>
-      </c>
-      <c r="L20" s="63"/>
-      <c r="M20" s="63"/>
-      <c r="N20" s="62" t="s">
-        <v>114</v>
-      </c>
+      <c r="K20" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="L20" s="62"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="62"/>
       <c r="O20" s="62"/>
       <c r="P20" s="62"/>
       <c r="Q20" s="62"/>
       <c r="R20" s="62"/>
       <c r="S20" s="62"/>
-      <c r="T20" s="62"/>
-      <c r="U20" s="62"/>
-      <c r="V20" s="62"/>
-      <c r="W20" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X20" s="63"/>
-    </row>
-    <row r="21" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B21" s="49">
-        <v>17</v>
+      <c r="T20" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U20" s="63"/>
+    </row>
+    <row r="21" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B21" s="49" t="s">
+        <v>203</v>
       </c>
       <c r="C21" s="49"/>
       <c r="D21" s="54" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E21" s="55"/>
       <c r="F21" s="56"/>
@@ -6342,34 +6325,29 @@
         <v>15</v>
       </c>
       <c r="J21" s="64"/>
-      <c r="K21" s="63" t="s">
-        <v>111</v>
-      </c>
-      <c r="L21" s="63"/>
-      <c r="M21" s="63"/>
-      <c r="N21" s="62" t="s">
-        <v>114</v>
-      </c>
+      <c r="K21" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="L21" s="62"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="62"/>
       <c r="O21" s="62"/>
       <c r="P21" s="62"/>
       <c r="Q21" s="62"/>
       <c r="R21" s="62"/>
       <c r="S21" s="62"/>
-      <c r="T21" s="62"/>
-      <c r="U21" s="62"/>
-      <c r="V21" s="62"/>
-      <c r="W21" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X21" s="63"/>
-    </row>
-    <row r="22" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B22" s="49">
-        <v>18</v>
+      <c r="T21" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U21" s="63"/>
+    </row>
+    <row r="22" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B22" s="49" t="s">
+        <v>204</v>
       </c>
       <c r="C22" s="49"/>
       <c r="D22" s="54" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E22" s="55"/>
       <c r="F22" s="56"/>
@@ -6381,34 +6359,29 @@
         <v>15</v>
       </c>
       <c r="J22" s="64"/>
-      <c r="K22" s="63" t="s">
-        <v>111</v>
-      </c>
-      <c r="L22" s="63"/>
-      <c r="M22" s="63"/>
-      <c r="N22" s="62" t="s">
-        <v>114</v>
-      </c>
+      <c r="K22" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="L22" s="62"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="62"/>
       <c r="O22" s="62"/>
       <c r="P22" s="62"/>
       <c r="Q22" s="62"/>
       <c r="R22" s="62"/>
       <c r="S22" s="62"/>
-      <c r="T22" s="62"/>
-      <c r="U22" s="62"/>
-      <c r="V22" s="62"/>
-      <c r="W22" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X22" s="63"/>
-    </row>
-    <row r="23" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B23" s="49">
-        <v>19</v>
+      <c r="T22" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U22" s="63"/>
+    </row>
+    <row r="23" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B23" s="49" t="s">
+        <v>205</v>
       </c>
       <c r="C23" s="49"/>
       <c r="D23" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E23" s="55"/>
       <c r="F23" s="56"/>
@@ -6420,34 +6393,29 @@
         <v>15</v>
       </c>
       <c r="J23" s="64"/>
-      <c r="K23" s="63" t="s">
-        <v>111</v>
-      </c>
-      <c r="L23" s="63"/>
-      <c r="M23" s="63"/>
-      <c r="N23" s="62" t="s">
-        <v>114</v>
-      </c>
+      <c r="K23" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="L23" s="62"/>
+      <c r="M23" s="62"/>
+      <c r="N23" s="62"/>
       <c r="O23" s="62"/>
       <c r="P23" s="62"/>
       <c r="Q23" s="62"/>
       <c r="R23" s="62"/>
       <c r="S23" s="62"/>
-      <c r="T23" s="62"/>
-      <c r="U23" s="62"/>
-      <c r="V23" s="62"/>
-      <c r="W23" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X23" s="63"/>
-    </row>
-    <row r="24" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B24" s="49">
-        <v>20</v>
+      <c r="T23" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U23" s="63"/>
+    </row>
+    <row r="24" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B24" s="49" t="s">
+        <v>206</v>
       </c>
       <c r="C24" s="49"/>
       <c r="D24" s="54" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E24" s="55"/>
       <c r="F24" s="56"/>
@@ -6459,34 +6427,29 @@
         <v>15</v>
       </c>
       <c r="J24" s="64"/>
-      <c r="K24" s="63" t="s">
-        <v>111</v>
-      </c>
-      <c r="L24" s="63"/>
-      <c r="M24" s="63"/>
-      <c r="N24" s="62" t="s">
-        <v>114</v>
-      </c>
+      <c r="K24" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="L24" s="62"/>
+      <c r="M24" s="62"/>
+      <c r="N24" s="62"/>
       <c r="O24" s="62"/>
       <c r="P24" s="62"/>
       <c r="Q24" s="62"/>
       <c r="R24" s="62"/>
       <c r="S24" s="62"/>
-      <c r="T24" s="62"/>
-      <c r="U24" s="62"/>
-      <c r="V24" s="62"/>
-      <c r="W24" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X24" s="63"/>
-    </row>
-    <row r="25" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B25" s="49">
-        <v>21</v>
+      <c r="T24" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U24" s="63"/>
+    </row>
+    <row r="25" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B25" s="49" t="s">
+        <v>207</v>
       </c>
       <c r="C25" s="49"/>
       <c r="D25" s="54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E25" s="55"/>
       <c r="F25" s="56"/>
@@ -6498,34 +6461,29 @@
         <v>15</v>
       </c>
       <c r="J25" s="64"/>
-      <c r="K25" s="63" t="s">
-        <v>111</v>
-      </c>
-      <c r="L25" s="63"/>
-      <c r="M25" s="63"/>
-      <c r="N25" s="62" t="s">
-        <v>114</v>
-      </c>
+      <c r="K25" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="L25" s="62"/>
+      <c r="M25" s="62"/>
+      <c r="N25" s="62"/>
       <c r="O25" s="62"/>
       <c r="P25" s="62"/>
       <c r="Q25" s="62"/>
       <c r="R25" s="62"/>
       <c r="S25" s="62"/>
-      <c r="T25" s="62"/>
-      <c r="U25" s="62"/>
-      <c r="V25" s="62"/>
-      <c r="W25" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X25" s="63"/>
-    </row>
-    <row r="26" spans="2:24" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B26" s="49">
-        <v>22</v>
+      <c r="T25" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U25" s="63"/>
+    </row>
+    <row r="26" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B26" s="49" t="s">
+        <v>208</v>
       </c>
       <c r="C26" s="49"/>
       <c r="D26" s="54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E26" s="55"/>
       <c r="F26" s="56"/>
@@ -6537,122 +6495,94 @@
         <v>15</v>
       </c>
       <c r="J26" s="64"/>
-      <c r="K26" s="63" t="s">
-        <v>111</v>
-      </c>
-      <c r="L26" s="63"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="62" t="s">
-        <v>114</v>
-      </c>
+      <c r="K26" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="L26" s="62"/>
+      <c r="M26" s="62"/>
+      <c r="N26" s="62"/>
       <c r="O26" s="62"/>
       <c r="P26" s="62"/>
       <c r="Q26" s="62"/>
       <c r="R26" s="62"/>
       <c r="S26" s="62"/>
-      <c r="T26" s="62"/>
-      <c r="U26" s="62"/>
-      <c r="V26" s="62"/>
-      <c r="W26" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="X26" s="63"/>
+      <c r="T26" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="U26" s="63"/>
     </row>
   </sheetData>
-  <mergeCells count="161">
-    <mergeCell ref="W24:X24"/>
-    <mergeCell ref="W25:X25"/>
-    <mergeCell ref="W26:X26"/>
-    <mergeCell ref="W19:X19"/>
-    <mergeCell ref="W20:X20"/>
-    <mergeCell ref="W21:X21"/>
-    <mergeCell ref="W22:X22"/>
-    <mergeCell ref="W23:X23"/>
-    <mergeCell ref="W10:X10"/>
-    <mergeCell ref="W11:X11"/>
-    <mergeCell ref="W12:X12"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="W14:X14"/>
-    <mergeCell ref="W15:X15"/>
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="W6:X6"/>
-    <mergeCell ref="W7:X7"/>
-    <mergeCell ref="W8:X8"/>
-    <mergeCell ref="W9:X9"/>
+  <mergeCells count="138">
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="T26:U26"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="T9:U9"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="N16:V16"/>
+    <mergeCell ref="K16:S16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="N15:V15"/>
+    <mergeCell ref="K15:S15"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="N14:V14"/>
+    <mergeCell ref="K14:S14"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="N6:V6"/>
+    <mergeCell ref="K6:S6"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="N25:V25"/>
+    <mergeCell ref="K25:S25"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="N24:V24"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="N19:V19"/>
-    <mergeCell ref="N20:V20"/>
-    <mergeCell ref="N21:V21"/>
-    <mergeCell ref="N22:V22"/>
-    <mergeCell ref="N23:V23"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N4:V4"/>
-    <mergeCell ref="N5:V5"/>
-    <mergeCell ref="N7:V7"/>
-    <mergeCell ref="N8:V8"/>
-    <mergeCell ref="N9:V9"/>
-    <mergeCell ref="N10:V10"/>
-    <mergeCell ref="N11:V11"/>
-    <mergeCell ref="N12:V12"/>
-    <mergeCell ref="N13:V13"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="W16:X16"/>
-    <mergeCell ref="W17:X17"/>
-    <mergeCell ref="W18:X18"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="N17:V17"/>
-    <mergeCell ref="N18:V18"/>
-    <mergeCell ref="N26:V26"/>
-    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="K24:S24"/>
+    <mergeCell ref="K19:S19"/>
+    <mergeCell ref="K20:S20"/>
+    <mergeCell ref="K21:S21"/>
+    <mergeCell ref="K22:S22"/>
+    <mergeCell ref="K23:S23"/>
+    <mergeCell ref="K4:S4"/>
+    <mergeCell ref="K5:S5"/>
+    <mergeCell ref="K7:S7"/>
+    <mergeCell ref="K8:S8"/>
+    <mergeCell ref="K9:S9"/>
+    <mergeCell ref="K10:S10"/>
+    <mergeCell ref="K11:S11"/>
+    <mergeCell ref="K12:S12"/>
+    <mergeCell ref="K13:S13"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="K17:S17"/>
+    <mergeCell ref="K18:S18"/>
+    <mergeCell ref="K26:S26"/>
     <mergeCell ref="D20:F20"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="D22:F22"/>
@@ -6727,7 +6657,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:J26" xr:uid="{EBCDB7CB-9B76-4496-A9FD-E13B8548471C}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W5:X26" xr:uid="{B5CE3419-EDB4-4E48-ADC1-5B4DD80F50CD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T5:U26" xr:uid="{B5CE3419-EDB4-4E48-ADC1-5B4DD80F50CD}">
       <formula1>"Đã có, Chưa, Bỏ, Cân nhắc"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6745,7 +6675,7 @@
   <sheetData>
     <row r="2" spans="1:1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48BE0603-83CB-42B4-A0B8-CF70F4D1F79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67037082-824D-49EB-921E-2EE533CAB740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="241">
   <si>
     <t>SIGNOMALY</t>
   </si>
@@ -613,9 +613,6 @@
     <t>"He created masterpieces in total deafness. His life’s work consists of exactly that many symphonies."</t>
   </si>
   <si>
-    <t>"An alphabet of twenty-six. But strip away the silent consonants. How many letters hold the true voice of the language? Count the vowels."</t>
-  </si>
-  <si>
     <t>#VENUS</t>
   </si>
   <si>
@@ -1881,30 +1878,9 @@
     <t>Nút UI của E sẽ hiển thị ở vị trí của object.</t>
   </si>
   <si>
-    <t>Key item ID</t>
-  </si>
-  <si>
     <t>INS_GUIDE</t>
   </si>
   <si>
-    <t>INS_MICRO</t>
-  </si>
-  <si>
-    <t>PZS_MERCURY</t>
-  </si>
-  <si>
-    <t>PZS_VENUS</t>
-  </si>
-  <si>
-    <t>PZS_EARTH</t>
-  </si>
-  <si>
-    <t>PZS_MARS</t>
-  </si>
-  <si>
-    <t>PZS_JUPITER</t>
-  </si>
-  <si>
     <t>PZ_COMPASS</t>
   </si>
   <si>
@@ -1920,43 +1896,795 @@
     <t>PZ_PICTURE2</t>
   </si>
   <si>
-    <t>DEC_FLOWER</t>
-  </si>
-  <si>
-    <t>DEC_BALL</t>
-  </si>
-  <si>
-    <t>DEC_COINS</t>
-  </si>
-  <si>
-    <t>DEC_MIRROR</t>
-  </si>
-  <si>
-    <t>DEC_LAMP</t>
-  </si>
-  <si>
-    <t>DEC_CHAMP</t>
-  </si>
-  <si>
-    <t>DEC_COFFEE</t>
-  </si>
-  <si>
-    <t>DEC_TABLE</t>
-  </si>
-  <si>
-    <t>DEC_CHAIR</t>
-  </si>
-  <si>
-    <t>DEC_STATUE</t>
+    <t>Y_MERCURY</t>
+  </si>
+  <si>
+    <t>Y_VENUS</t>
+  </si>
+  <si>
+    <t>Y_EARTH</t>
+  </si>
+  <si>
+    <t>Y_MARS</t>
+  </si>
+  <si>
+    <t>Y_JUPITER</t>
+  </si>
+  <si>
+    <t>X_BALL</t>
+  </si>
+  <si>
+    <t>X_FLOWER</t>
+  </si>
+  <si>
+    <t>X_COINS</t>
+  </si>
+  <si>
+    <t>X_MIRROR</t>
+  </si>
+  <si>
+    <t>X_LAMP</t>
+  </si>
+  <si>
+    <t>X_CHAMP</t>
+  </si>
+  <si>
+    <t>X_COFFEE</t>
+  </si>
+  <si>
+    <t>X_TABLE</t>
+  </si>
+  <si>
+    <t>X_CHAIR</t>
+  </si>
+  <si>
+    <t>X_STATUE</t>
+  </si>
+  <si>
+    <t>INS_MICO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Điều kiện để tương tác với vật thể: Vật thể phải luôn trong tầm nhìn của người chơi; Phạm vi của vật thể phát hiện người chơi. Trong trường hợp </t>
+  </si>
+  <si>
+    <t>"An alphabet of twenty-six. But strip away the silent consonants. How many letters hold the true voice of the language?
+Count the vowels."</t>
+  </si>
+  <si>
+    <t>1. Các loại hộp Dialouges (tham khảo)</t>
+  </si>
+  <si>
+    <t>2 loại hộp dialouges phổ biến trong game 3D.</t>
+  </si>
+  <si>
+    <t>Cần hiển thị hộp dialouges như mẫu kế bên.</t>
+  </si>
+  <si>
+    <t>Tinh chỉnh góc quay phù hợp khi bắt đầu cuộc đối thoại với NPC (Optional)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Về phương thức tương tác:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  Ở </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>lần tương tác đầu tiên</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>, người chơi</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> không thể skip, double click</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> chạy hết chữ, hay </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>thoát ra ngoài</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> vào gameplay, mà phải xem hết một đoạn đối thoại, sau đó mới được click để sang đoạn tiếp theo. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Để tiếp tục đoạn đối thoại</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>, người chơi</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> sẽ nhấn chuột trái</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Ở</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> lần tương tác thứ 2,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> người chơi sẽ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">được phép double click </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">để chạy full đoạn đối thoại và nhảy sang đoạn đối thoại tiếp theo, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>được phép thoát ra ngoài</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> khi đang đối thoại. Nút để thoát ra ngoài là </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>"ESCAPE"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Yêu cầu:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Khung đối thoại có </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>màu đen constrast cao</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, độ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>opacity cần là 60%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> để đảm bảo vẫn nhìn rõ môi trường đằng sau. Cần có tên người nói hiển thị ở góc trên đoạn đối thoại (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>tên người nói màu Trắng, brightness thấp hơn đối thoại và viết hoa chữ cái đầu)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Đoạn đối thoại </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>cần viết thường, và chỉ viết hoa chữ cái đầu sau dấu chấm (đoạn đối thoại màu trắng, với brightness cao hơn tên)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Lời đối thoại</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Well, everything comes at a price.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Heh… another one, huh? Are you really that greedy for money?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Win, and you might walk away with that massive fortune. But lose… and we take no responsibility. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> If you want the treasure, you’ll have to play the game just like the contract says.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> You’ll become nothing more than entertainment for Them. Hahahaha…</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  So… ready to step into hell?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  Good. Here are the rules of our little game. See that door beside you, ahh the one with the… unusual requirement? That’s your way out. But to unlock it, you’ll need to fulfill two conditions.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  First, look at the door in front of you. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  See the timer? Fifteen minutes.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  That’s all the time you have left to finish the game. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  Meet the other condition before it hits zero, and the door will open. If not… hahaha.</t>
+    </r>
+  </si>
+  <si>
+    <t>***Lưu ý: Mỗi đoạn được viết dưới đây thì đều là từng đoạn sẽ hiển thị ra khi người chơi click chuột sang đoạn kế.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  Second, beyond this room lies a space filled with all sorts of objects. Your task is to find the anomalies among them.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  If you suspect something’s off, stand your ground and face it directly, don’t look away. It will present you with a puzzle. Solve it, and you’ll set it free.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  Each of them has its own timer hovering overhead… and if their time runs out, it’s game over for you too. So keep your eyes sharp.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  But don’t get too corky. These anomalies aren’t as forgiving as I am. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  Free them all within the fifteen minutes I’ve given you, and the door will open. Walk through it, and that million-dollar prize is yours.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  …assuming you can pull it off. Plenty have tried. Plenty have died. Turns out, if you want something valuable, you have to pay a matching price.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  Good luck? I guess… and perhaps we’ll meet again or not, hahaha…</t>
+    </r>
+  </si>
+  <si>
+    <t>2.2. Tương tác lần 2: chỉ hiển thị chỉ dẫn cần thiết</t>
+  </si>
+  <si>
+    <t>2.1. Tương tác lần đầu: hiển thị toàn bộ cuộc trò chuyện</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  See that door beside you, ahh the one with the… unusual requirement? That’s your way out. But to unlock it, you’ll need to fulfill two conditions.</t>
+    </r>
+  </si>
+  <si>
+    <t>***Lưu ý: không thể skip, double click chạy hết chữ, hay thoát ra ngoài vào gameplay.</t>
+  </si>
+  <si>
+    <t>***Lưu ý: lần tương tác thứ 2, người chơi sẽ được phép double click để chạy full đoạn đối thoại và nhảy sang đoạn đối thoại tiếp theo, được phép thoát ra ngoài.</t>
+  </si>
+  <si>
+    <t>Item ID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="15"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2165,44 +2893,44 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2210,175 +2938,202 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2401,16 +3156,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>13607</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>54428</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>594632</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>187779</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>180947</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>56937</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2439,8 +3194,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="625928" y="7633607"/>
-          <a:ext cx="14682108" cy="7746519"/>
+          <a:off x="594632" y="7550604"/>
+          <a:ext cx="12873505" cy="6822622"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2465,7 +3220,7 @@
       <xdr:col>10</xdr:col>
       <xdr:colOff>125960</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>35719</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2506,16 +3261,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>609599</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2380</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>607798</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>54949</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>102967</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2545,8 +3300,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="609599" y="23641050"/>
-          <a:ext cx="4874999" cy="3095625"/>
+          <a:off x="609599" y="8096251"/>
+          <a:ext cx="3695881" cy="2365154"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2567,16 +3322,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>54769</xdr:colOff>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>4763</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>127993</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>12580</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>129024</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2606,8 +3361,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5467350" y="23645813"/>
-          <a:ext cx="5553075" cy="3123605"/>
+          <a:off x="4305300" y="8101013"/>
+          <a:ext cx="4208343" cy="2386449"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2630,14 +3385,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>34528</xdr:rowOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>105966</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>183952</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>57208</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>31622</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2667,8 +3422,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="590550" y="11950303"/>
-          <a:ext cx="4905375" cy="2759274"/>
+          <a:off x="590550" y="10464404"/>
+          <a:ext cx="3717189" cy="2116406"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2689,16 +3444,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>57151</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>100807</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>190501</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>603251</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>33998</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2728,8 +3483,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5486400" y="11972926"/>
-          <a:ext cx="5543550" cy="2743200"/>
+          <a:off x="4296834" y="10398390"/>
+          <a:ext cx="4286250" cy="2071025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2752,14 +3507,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>238126</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>604610</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>238125</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2789,8 +3544,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="609600" y="17497426"/>
-          <a:ext cx="10363200" cy="5829300"/>
+          <a:off x="609600" y="18154651"/>
+          <a:ext cx="7310210" cy="4105274"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2811,16 +3566,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>573881</xdr:colOff>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>220133</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>290539</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2850,8 +3605,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="609600" y="14582775"/>
-          <a:ext cx="5096933" cy="2867025"/>
+          <a:off x="573881" y="12944475"/>
+          <a:ext cx="3983858" cy="2247900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2872,16 +3627,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>273415</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>247649</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>138033</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>607218</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2911,8 +3666,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5724525" y="14582775"/>
-          <a:ext cx="5095875" cy="2862183"/>
+          <a:off x="4540615" y="12944474"/>
+          <a:ext cx="3991403" cy="2238375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3104,16 +3859,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>466725</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>60305</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>9954</xdr:rowOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>8731</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3136,8 +3891,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13268325" y="1266825"/>
-          <a:ext cx="8737580" cy="3181779"/>
+          <a:off x="10363199" y="1104900"/>
+          <a:ext cx="7323932" cy="2667000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3250,6 +4005,194 @@
         <a:xfrm>
           <a:off x="9144000" y="15754350"/>
           <a:ext cx="7600950" cy="4513064"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>141227</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Group Project – Dialogue System – Planning – Games Design work">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D3DAED7-3C6F-7B2B-941E-0D57E1F91815}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="609601" y="1171575"/>
+          <a:ext cx="4000499" cy="2084327"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>401107</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>148233</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3" descr="Unity Progress #24: First NPC Dialogue &amp; Add Item PopUp UI">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06B45D1A-4D72-FA38-61FF-F4F29552A9E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4668307" y="1152525"/>
+          <a:ext cx="3751793" cy="2110383"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>6457</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4" descr="Always make sure to check NPC dialogue for gems like this :  r/XenobladeChroniclesX">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{425DFB54-B837-FCB1-2373-DC0523E817DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2800350" y="3686175"/>
+          <a:ext cx="5629275" cy="3816457"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3595,29 +4538,29 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:26" ht="46.5" x14ac:dyDescent="0.7">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
     </row>
     <row r="3" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
@@ -3641,104 +4584,104 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="77" t="s">
-        <v>179</v>
-      </c>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="77"/>
+      <c r="B12" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
     </row>
     <row r="13" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
-      <c r="S13" s="36"/>
-      <c r="T13" s="36"/>
-      <c r="U13" s="36"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="50"/>
+      <c r="M13" s="50"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="50"/>
+      <c r="Q13" s="50"/>
+      <c r="R13" s="50"/>
+      <c r="S13" s="50"/>
+      <c r="T13" s="50"/>
+      <c r="U13" s="50"/>
     </row>
     <row r="14" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
-      <c r="R14" s="35"/>
-      <c r="S14" s="35"/>
-      <c r="T14" s="35"/>
-      <c r="U14" s="35"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="46"/>
+      <c r="O14" s="46"/>
+      <c r="P14" s="46"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="46"/>
+      <c r="S14" s="46"/>
+      <c r="T14" s="46"/>
+      <c r="U14" s="46"/>
     </row>
     <row r="15" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
@@ -3754,28 +4697,28 @@
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:26" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="33"/>
+      <c r="B16" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="47"/>
+      <c r="L16" s="47"/>
+      <c r="M16" s="47"/>
+      <c r="N16" s="47"/>
+      <c r="O16" s="47"/>
+      <c r="P16" s="47"/>
+      <c r="Q16" s="47"/>
+      <c r="R16" s="47"/>
+      <c r="S16" s="47"/>
+      <c r="T16" s="47"/>
+      <c r="U16" s="47"/>
       <c r="V16" s="6"/>
       <c r="W16" s="6"/>
       <c r="X16" s="6"/>
@@ -3783,100 +4726,100 @@
       <c r="Z16" s="6"/>
     </row>
     <row r="17" spans="1:21" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
-      <c r="T17" s="33"/>
-      <c r="U17" s="33"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="47"/>
+      <c r="L17" s="47"/>
+      <c r="M17" s="47"/>
+      <c r="N17" s="47"/>
+      <c r="O17" s="47"/>
+      <c r="P17" s="47"/>
+      <c r="Q17" s="47"/>
+      <c r="R17" s="47"/>
+      <c r="S17" s="47"/>
+      <c r="T17" s="47"/>
+      <c r="U17" s="47"/>
     </row>
     <row r="18" spans="1:21" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="35"/>
-      <c r="T18" s="35"/>
-      <c r="U18" s="35"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="46"/>
+      <c r="K18" s="46"/>
+      <c r="L18" s="46"/>
+      <c r="M18" s="46"/>
+      <c r="N18" s="46"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="46"/>
+      <c r="Q18" s="46"/>
+      <c r="R18" s="46"/>
+      <c r="S18" s="46"/>
+      <c r="T18" s="46"/>
+      <c r="U18" s="46"/>
     </row>
     <row r="19" spans="1:21" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="28"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="28"/>
-      <c r="U19" s="28"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="49"/>
+      <c r="K19" s="49"/>
+      <c r="L19" s="49"/>
+      <c r="M19" s="49"/>
+      <c r="N19" s="49"/>
+      <c r="O19" s="49"/>
+      <c r="P19" s="49"/>
+      <c r="Q19" s="49"/>
+      <c r="R19" s="49"/>
+      <c r="S19" s="49"/>
+      <c r="T19" s="49"/>
+      <c r="U19" s="49"/>
     </row>
     <row r="20" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="22" t="s">
-        <v>180</v>
-      </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="22"/>
-      <c r="O20" s="22"/>
-      <c r="P20" s="22"/>
-      <c r="Q20" s="22"/>
-      <c r="R20" s="22"/>
-      <c r="S20" s="22"/>
-      <c r="T20" s="22"/>
-      <c r="U20" s="22"/>
+      <c r="B20" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="52"/>
+      <c r="K20" s="52"/>
+      <c r="L20" s="52"/>
+      <c r="M20" s="52"/>
+      <c r="N20" s="52"/>
+      <c r="O20" s="52"/>
+      <c r="P20" s="52"/>
+      <c r="Q20" s="52"/>
+      <c r="R20" s="52"/>
+      <c r="S20" s="52"/>
+      <c r="T20" s="52"/>
+      <c r="U20" s="52"/>
     </row>
     <row r="22" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
@@ -3989,6 +4932,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B20:U20"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B16:U16"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="B18:U18"/>
     <mergeCell ref="B17:U17"/>
@@ -3996,11 +4944,6 @@
     <mergeCell ref="B14:U14"/>
     <mergeCell ref="B13:U13"/>
     <mergeCell ref="B12:J12"/>
-    <mergeCell ref="B20:U20"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B16:U16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4011,12 +4954,12 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A2:Y56"/>
+  <dimension ref="A2:Y50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B2" s="8"/>
     </row>
@@ -4024,366 +4967,373 @@
       <c r="B4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39" t="s">
+      <c r="D4" s="29"/>
+      <c r="E4" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="39"/>
-      <c r="G4" s="41" t="s">
+      <c r="F4" s="29"/>
+      <c r="G4" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41" t="s">
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
-      <c r="V4" s="41"/>
-      <c r="W4" s="41"/>
-      <c r="X4" s="41"/>
-      <c r="Y4" s="41"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
+      <c r="Q4" s="57"/>
+      <c r="R4" s="57"/>
+      <c r="S4" s="57"/>
+      <c r="T4" s="57"/>
+      <c r="U4" s="57"/>
+      <c r="V4" s="57"/>
+      <c r="W4" s="57"/>
+      <c r="X4" s="57"/>
+      <c r="Y4" s="57"/>
     </row>
     <row r="5" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11">
         <v>1</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="37"/>
-      <c r="E5" s="38" t="s">
+      <c r="D5" s="62"/>
+      <c r="E5" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="38"/>
-      <c r="G5" s="40" t="s">
+      <c r="F5" s="63"/>
+      <c r="G5" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="45" t="s">
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="60"/>
+      <c r="L5" s="60"/>
+      <c r="M5" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="45"/>
-      <c r="U5" s="45"/>
-      <c r="V5" s="45"/>
-      <c r="W5" s="45"/>
-      <c r="X5" s="45"/>
-      <c r="Y5" s="45"/>
+      <c r="N5" s="58"/>
+      <c r="O5" s="58"/>
+      <c r="P5" s="58"/>
+      <c r="Q5" s="58"/>
+      <c r="R5" s="58"/>
+      <c r="S5" s="58"/>
+      <c r="T5" s="58"/>
+      <c r="U5" s="58"/>
+      <c r="V5" s="58"/>
+      <c r="W5" s="58"/>
+      <c r="X5" s="58"/>
+      <c r="Y5" s="58"/>
     </row>
     <row r="6" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11">
         <v>2</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="38" t="s">
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="38"/>
-      <c r="G6" s="40" t="s">
+      <c r="F6" s="63"/>
+      <c r="G6" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="46" t="s">
-        <v>82</v>
-      </c>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="45"/>
-      <c r="S6" s="45"/>
-      <c r="T6" s="45"/>
-      <c r="U6" s="45"/>
-      <c r="V6" s="45"/>
-      <c r="W6" s="45"/>
-      <c r="X6" s="45"/>
-      <c r="Y6" s="45"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="60"/>
+      <c r="K6" s="60"/>
+      <c r="L6" s="60"/>
+      <c r="M6" s="59" t="s">
+        <v>81</v>
+      </c>
+      <c r="N6" s="58"/>
+      <c r="O6" s="58"/>
+      <c r="P6" s="58"/>
+      <c r="Q6" s="58"/>
+      <c r="R6" s="58"/>
+      <c r="S6" s="58"/>
+      <c r="T6" s="58"/>
+      <c r="U6" s="58"/>
+      <c r="V6" s="58"/>
+      <c r="W6" s="58"/>
+      <c r="X6" s="58"/>
+      <c r="Y6" s="58"/>
     </row>
     <row r="7" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11">
         <v>3</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="38" t="s">
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="38"/>
-      <c r="G7" s="40" t="s">
+      <c r="F7" s="63"/>
+      <c r="G7" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="40"/>
-      <c r="M7" s="43" t="s">
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="60"/>
+      <c r="L7" s="60"/>
+      <c r="M7" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="43"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="43"/>
-      <c r="R7" s="43"/>
-      <c r="S7" s="43"/>
-      <c r="T7" s="43"/>
-      <c r="U7" s="43"/>
-      <c r="V7" s="43"/>
-      <c r="W7" s="43"/>
-      <c r="X7" s="43"/>
-      <c r="Y7" s="43"/>
+      <c r="N7" s="56"/>
+      <c r="O7" s="56"/>
+      <c r="P7" s="56"/>
+      <c r="Q7" s="56"/>
+      <c r="R7" s="56"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="56"/>
+      <c r="U7" s="56"/>
+      <c r="V7" s="56"/>
+      <c r="W7" s="56"/>
+      <c r="X7" s="56"/>
+      <c r="Y7" s="56"/>
     </row>
     <row r="8" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11">
         <v>4</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="38" t="s">
+      <c r="D8" s="62"/>
+      <c r="E8" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="38"/>
-      <c r="G8" s="40" t="s">
+      <c r="F8" s="63"/>
+      <c r="G8" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="40"/>
-      <c r="M8" s="42" t="s">
-        <v>86</v>
-      </c>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="43"/>
-      <c r="R8" s="43"/>
-      <c r="S8" s="43"/>
-      <c r="T8" s="43"/>
-      <c r="U8" s="43"/>
-      <c r="V8" s="43"/>
-      <c r="W8" s="43"/>
-      <c r="X8" s="43"/>
-      <c r="Y8" s="43"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="60"/>
+      <c r="L8" s="60"/>
+      <c r="M8" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="N8" s="56"/>
+      <c r="O8" s="56"/>
+      <c r="P8" s="56"/>
+      <c r="Q8" s="56"/>
+      <c r="R8" s="56"/>
+      <c r="S8" s="56"/>
+      <c r="T8" s="56"/>
+      <c r="U8" s="56"/>
+      <c r="V8" s="56"/>
+      <c r="W8" s="56"/>
+      <c r="X8" s="56"/>
+      <c r="Y8" s="56"/>
     </row>
     <row r="9" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11">
         <v>5</v>
       </c>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="38" t="s">
+      <c r="C9" s="62"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="38"/>
-      <c r="G9" s="40" t="s">
+      <c r="F9" s="63"/>
+      <c r="G9" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="40"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="40"/>
-      <c r="M9" s="42" t="s">
-        <v>85</v>
-      </c>
-      <c r="N9" s="43"/>
-      <c r="O9" s="43"/>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="43"/>
-      <c r="S9" s="43"/>
-      <c r="T9" s="43"/>
-      <c r="U9" s="43"/>
-      <c r="V9" s="43"/>
-      <c r="W9" s="43"/>
-      <c r="X9" s="43"/>
-      <c r="Y9" s="43"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="60"/>
+      <c r="M9" s="55" t="s">
+        <v>84</v>
+      </c>
+      <c r="N9" s="56"/>
+      <c r="O9" s="56"/>
+      <c r="P9" s="56"/>
+      <c r="Q9" s="56"/>
+      <c r="R9" s="56"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="56"/>
+      <c r="U9" s="56"/>
+      <c r="V9" s="56"/>
+      <c r="W9" s="56"/>
+      <c r="X9" s="56"/>
+      <c r="Y9" s="56"/>
     </row>
     <row r="10" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="11">
         <v>6</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="38" t="s">
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="38"/>
-      <c r="G10" s="40" t="s">
+      <c r="F10" s="63"/>
+      <c r="G10" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="N10" s="43"/>
-      <c r="O10" s="43"/>
-      <c r="P10" s="43"/>
-      <c r="Q10" s="43"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="43"/>
-      <c r="V10" s="43"/>
-      <c r="W10" s="43"/>
-      <c r="X10" s="43"/>
-      <c r="Y10" s="43"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="55" t="s">
+        <v>83</v>
+      </c>
+      <c r="N10" s="56"/>
+      <c r="O10" s="56"/>
+      <c r="P10" s="56"/>
+      <c r="Q10" s="56"/>
+      <c r="R10" s="56"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="56"/>
+      <c r="U10" s="56"/>
+      <c r="V10" s="56"/>
+      <c r="W10" s="56"/>
+      <c r="X10" s="56"/>
+      <c r="Y10" s="56"/>
     </row>
     <row r="11" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="11">
         <v>7</v>
       </c>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="38" t="s">
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="38"/>
-      <c r="G11" s="40" t="s">
+      <c r="F11" s="63"/>
+      <c r="G11" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="43" t="s">
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="60"/>
+      <c r="L11" s="60"/>
+      <c r="M11" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="43"/>
-      <c r="O11" s="43"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="43"/>
-      <c r="W11" s="43"/>
-      <c r="X11" s="43"/>
-      <c r="Y11" s="43"/>
+      <c r="N11" s="56"/>
+      <c r="O11" s="56"/>
+      <c r="P11" s="56"/>
+      <c r="Q11" s="56"/>
+      <c r="R11" s="56"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="56"/>
+      <c r="U11" s="56"/>
+      <c r="V11" s="56"/>
+      <c r="W11" s="56"/>
+      <c r="X11" s="56"/>
+      <c r="Y11" s="56"/>
     </row>
     <row r="12" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="11">
         <v>8</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="38" t="s">
+      <c r="D12" s="62"/>
+      <c r="E12" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="38"/>
-      <c r="G12" s="40" t="s">
+      <c r="F12" s="63"/>
+      <c r="G12" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="40"/>
-      <c r="M12" s="43" t="s">
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="60"/>
+      <c r="L12" s="60"/>
+      <c r="M12" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="43"/>
-      <c r="W12" s="43"/>
-      <c r="X12" s="43"/>
-      <c r="Y12" s="43"/>
+      <c r="N12" s="56"/>
+      <c r="O12" s="56"/>
+      <c r="P12" s="56"/>
+      <c r="Q12" s="56"/>
+      <c r="R12" s="56"/>
+      <c r="S12" s="56"/>
+      <c r="T12" s="56"/>
+      <c r="U12" s="56"/>
+      <c r="V12" s="56"/>
+      <c r="W12" s="56"/>
+      <c r="X12" s="56"/>
+      <c r="Y12" s="56"/>
     </row>
     <row r="46" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B56" s="44" t="s">
+    <row r="49" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B49" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="C56" s="44"/>
-      <c r="D56" s="44"/>
-      <c r="E56" s="44"/>
-      <c r="F56" s="44"/>
-      <c r="G56" s="44"/>
-      <c r="H56" s="44"/>
-      <c r="I56" s="44"/>
-      <c r="J56" s="44"/>
-      <c r="K56" s="44"/>
-      <c r="L56" s="44"/>
-      <c r="M56" s="44"/>
-      <c r="N56" s="44"/>
-      <c r="O56" s="44"/>
-      <c r="P56" s="44"/>
-      <c r="Q56" s="44"/>
-      <c r="R56" s="44"/>
-      <c r="S56" s="44"/>
-      <c r="T56" s="44"/>
-      <c r="U56" s="44"/>
-      <c r="V56" s="44"/>
-      <c r="W56" s="44"/>
-      <c r="X56" s="44"/>
-      <c r="Y56" s="44"/>
+      <c r="C49" s="61"/>
+      <c r="D49" s="61"/>
+      <c r="E49" s="61"/>
+      <c r="F49" s="61"/>
+      <c r="G49" s="61"/>
+      <c r="H49" s="61"/>
+      <c r="I49" s="61"/>
+      <c r="J49" s="61"/>
+      <c r="K49" s="61"/>
+      <c r="L49" s="61"/>
+      <c r="M49" s="61"/>
+      <c r="N49" s="61"/>
+      <c r="O49" s="61"/>
+      <c r="P49" s="61"/>
+      <c r="Q49" s="61"/>
+      <c r="R49" s="61"/>
+      <c r="S49" s="61"/>
+      <c r="T49" s="61"/>
+      <c r="U49" s="61"/>
+      <c r="V49" s="61"/>
+    </row>
+    <row r="50" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B50" s="61"/>
+      <c r="C50" s="61"/>
+      <c r="D50" s="61"/>
+      <c r="E50" s="61"/>
+      <c r="F50" s="61"/>
+      <c r="G50" s="61"/>
+      <c r="H50" s="61"/>
+      <c r="I50" s="61"/>
+      <c r="J50" s="61"/>
+      <c r="K50" s="61"/>
+      <c r="L50" s="61"/>
+      <c r="M50" s="61"/>
+      <c r="N50" s="61"/>
+      <c r="O50" s="61"/>
+      <c r="P50" s="61"/>
+      <c r="Q50" s="61"/>
+      <c r="R50" s="61"/>
+      <c r="S50" s="61"/>
+      <c r="T50" s="61"/>
+      <c r="U50" s="61"/>
+      <c r="V50" s="61"/>
+      <c r="W50" s="90"/>
+      <c r="X50" s="90"/>
+      <c r="Y50" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="M9:Y9"/>
-    <mergeCell ref="M4:Y4"/>
-    <mergeCell ref="M5:Y5"/>
-    <mergeCell ref="M6:Y6"/>
-    <mergeCell ref="M7:Y7"/>
-    <mergeCell ref="M8:Y8"/>
-    <mergeCell ref="M10:Y10"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="B56:Y56"/>
-    <mergeCell ref="M11:Y11"/>
-    <mergeCell ref="M12:Y12"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="B49:V50"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="C5:D5"/>
@@ -4400,8 +5350,24 @@
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="M10:Y10"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="M11:Y11"/>
+    <mergeCell ref="M12:Y12"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="M9:Y9"/>
+    <mergeCell ref="M4:Y4"/>
+    <mergeCell ref="M5:Y5"/>
+    <mergeCell ref="M6:Y6"/>
+    <mergeCell ref="M7:Y7"/>
+    <mergeCell ref="M8:Y8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4413,71 +5379,38 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A2:AK81"/>
+  <dimension ref="A2:AC78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:30" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:28" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="N6" s="23" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L8" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="23"/>
-      <c r="T6" s="23"/>
-      <c r="U6" s="23"/>
-      <c r="V6" s="23"/>
-      <c r="W6" s="23"/>
-      <c r="X6" s="23"/>
-      <c r="Y6" s="23"/>
-    </row>
-    <row r="7" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-    </row>
-    <row r="8" spans="1:30" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N8" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="O8" s="25"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="25"/>
-      <c r="S8" s="25"/>
-      <c r="T8" s="25"/>
-      <c r="U8" s="25"/>
-      <c r="V8" s="25"/>
-      <c r="W8" s="25"/>
-      <c r="X8" s="25"/>
-      <c r="Y8" s="25"/>
-      <c r="Z8" s="25"/>
-      <c r="AA8" s="25"/>
-      <c r="AB8" s="25"/>
-      <c r="AC8" s="25"/>
-      <c r="AD8" s="25"/>
-    </row>
-    <row r="9" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="M8" s="65"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="65"/>
+      <c r="Q8" s="65"/>
+      <c r="R8" s="65"/>
+      <c r="S8" s="65"/>
+      <c r="T8" s="65"/>
+      <c r="U8" s="65"/>
+      <c r="V8" s="65"/>
+      <c r="W8" s="65"/>
+    </row>
+    <row r="9" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
@@ -4488,732 +5421,727 @@
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
       <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-    </row>
-    <row r="10" spans="1:30" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N10" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="O10" s="28"/>
-      <c r="P10" s="28"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="28"/>
-      <c r="S10" s="28"/>
-      <c r="T10" s="28"/>
-      <c r="U10" s="28"/>
-      <c r="V10" s="28"/>
-      <c r="W10" s="28"/>
-      <c r="X10" s="28"/>
-      <c r="Y10" s="28"/>
-      <c r="Z10" s="28"/>
-      <c r="AA10" s="28"/>
-      <c r="AB10" s="28"/>
-      <c r="AC10" s="28"/>
-      <c r="AD10" s="28"/>
-    </row>
-    <row r="13" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:28" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L10" s="77" t="s">
+        <v>63</v>
+      </c>
+      <c r="M10" s="48"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="48"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="48"/>
+      <c r="R10" s="48"/>
+      <c r="S10" s="48"/>
+      <c r="T10" s="48"/>
+      <c r="U10" s="48"/>
+      <c r="V10" s="48"/>
+      <c r="W10" s="48"/>
+      <c r="X10" s="48"/>
+      <c r="Y10" s="48"/>
+      <c r="Z10" s="48"/>
+      <c r="AA10" s="48"/>
+      <c r="AB10" s="48"/>
+    </row>
+    <row r="11" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+    </row>
+    <row r="12" spans="1:28" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L12" s="77" t="s">
+        <v>82</v>
+      </c>
+      <c r="M12" s="49"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="49"/>
+      <c r="P12" s="49"/>
+      <c r="Q12" s="49"/>
+      <c r="R12" s="49"/>
+      <c r="S12" s="49"/>
+      <c r="T12" s="49"/>
+      <c r="U12" s="49"/>
+      <c r="V12" s="49"/>
+      <c r="W12" s="49"/>
+      <c r="X12" s="49"/>
+      <c r="Y12" s="49"/>
+      <c r="Z12" s="49"/>
+      <c r="AA12" s="49"/>
+      <c r="AB12" s="49"/>
+    </row>
+    <row r="13" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="S13" s="12"/>
     </row>
-    <row r="16" spans="1:30" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="17" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B17" s="8"/>
-    </row>
-    <row r="18" spans="2:33" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="80" t="s">
+    <row r="15" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="8"/>
+    </row>
+    <row r="17" spans="2:28" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="69" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="70"/>
+      <c r="M17" s="70"/>
+      <c r="N17" s="70"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="70"/>
+      <c r="Q17" s="70"/>
+      <c r="R17" s="70"/>
+      <c r="S17" s="70"/>
+      <c r="T17" s="70"/>
+      <c r="U17" s="70"/>
+      <c r="V17" s="70"/>
+      <c r="W17" s="70"/>
+      <c r="X17" s="70"/>
+      <c r="Y17" s="70"/>
+      <c r="Z17" s="70"/>
+      <c r="AA17" s="70"/>
+      <c r="AB17" s="70"/>
+    </row>
+    <row r="18" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="15"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="16"/>
+      <c r="T18" s="16"/>
+      <c r="U18" s="16"/>
+      <c r="V18" s="16"/>
+      <c r="W18" s="16"/>
+      <c r="X18" s="16"/>
+      <c r="Y18" s="16"/>
+    </row>
+    <row r="20" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B20" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="10"/>
+    </row>
+    <row r="22" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="P22" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q22" s="66"/>
+      <c r="R22" s="66"/>
+      <c r="S22" s="66"/>
+      <c r="T22" s="66"/>
+      <c r="U22" s="66"/>
+      <c r="V22" s="66"/>
+      <c r="W22" s="66"/>
+      <c r="X22" s="66"/>
+      <c r="Y22" s="66"/>
+      <c r="Z22" s="66"/>
+      <c r="AA22" s="66"/>
+      <c r="AB22" s="66"/>
+    </row>
+    <row r="23" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P23" s="12"/>
+    </row>
+    <row r="24" spans="2:28" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P24" s="64" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="67"/>
+      <c r="S24" s="67"/>
+      <c r="T24" s="67"/>
+      <c r="U24" s="67"/>
+      <c r="V24" s="67"/>
+      <c r="W24" s="67"/>
+      <c r="X24" s="67"/>
+      <c r="Y24" s="67"/>
+      <c r="Z24" s="67"/>
+      <c r="AA24" s="67"/>
+      <c r="AB24" s="67"/>
+    </row>
+    <row r="25" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P25" s="19"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="17"/>
+      <c r="U25" s="17"/>
+      <c r="V25" s="17"/>
+      <c r="W25" s="17"/>
+      <c r="X25" s="17"/>
+      <c r="Y25" s="17"/>
+      <c r="Z25" s="17"/>
+      <c r="AA25" s="17"/>
+      <c r="AB25" s="17"/>
+    </row>
+    <row r="26" spans="2:28" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P26" s="64" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q26" s="64"/>
+      <c r="R26" s="64"/>
+      <c r="S26" s="64"/>
+      <c r="T26" s="64"/>
+      <c r="U26" s="64"/>
+      <c r="V26" s="64"/>
+      <c r="W26" s="64"/>
+      <c r="X26" s="64"/>
+      <c r="Y26" s="64"/>
+      <c r="Z26" s="64"/>
+      <c r="AA26" s="64"/>
+      <c r="AB26" s="64"/>
+    </row>
+    <row r="27" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17"/>
+      <c r="T27" s="17"/>
+      <c r="U27" s="17"/>
+      <c r="V27" s="17"/>
+      <c r="W27" s="17"/>
+      <c r="X27" s="17"/>
+      <c r="Y27" s="17"/>
+      <c r="Z27" s="17"/>
+      <c r="AA27" s="17"/>
+      <c r="AB27" s="17"/>
+    </row>
+    <row r="28" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="P28" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q28" s="66"/>
+      <c r="R28" s="66"/>
+      <c r="S28" s="66"/>
+      <c r="T28" s="66"/>
+      <c r="U28" s="66"/>
+      <c r="V28" s="66"/>
+      <c r="W28" s="66"/>
+      <c r="X28" s="66"/>
+      <c r="Y28" s="66"/>
+      <c r="Z28" s="66"/>
+      <c r="AA28" s="66"/>
+      <c r="AB28" s="66"/>
+    </row>
+    <row r="29" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P29" s="12"/>
+    </row>
+    <row r="30" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P30" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P31" s="12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P32" s="12"/>
+    </row>
+    <row r="33" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P33" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q33" s="8"/>
+      <c r="R33" s="8"/>
+      <c r="S33" s="8"/>
+      <c r="T33" s="8"/>
+      <c r="U33" s="8"/>
+    </row>
+    <row r="35" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P35" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q35" s="12"/>
+      <c r="R35" s="12"/>
+      <c r="S35" s="12"/>
+      <c r="T35" s="12"/>
+      <c r="U35" s="12"/>
+      <c r="V35" s="12"/>
+      <c r="W35" s="12"/>
+      <c r="X35" s="12"/>
+      <c r="Y35" s="12"/>
+      <c r="Z35" s="12"/>
+      <c r="AA35" s="12"/>
+      <c r="AB35" s="12"/>
+    </row>
+    <row r="36" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P36" s="48" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q36" s="48"/>
+      <c r="R36" s="48"/>
+      <c r="S36" s="48"/>
+      <c r="T36" s="48"/>
+      <c r="U36" s="48"/>
+      <c r="V36" s="48"/>
+      <c r="W36" s="48"/>
+      <c r="X36" s="48"/>
+      <c r="Y36" s="48"/>
+      <c r="Z36" s="48"/>
+      <c r="AA36" s="48"/>
+      <c r="AB36" s="48"/>
+    </row>
+    <row r="38" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B38" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="68"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="68"/>
+      <c r="H38" s="68"/>
+      <c r="I38" s="68"/>
+      <c r="J38" s="68"/>
+      <c r="K38" s="68"/>
+      <c r="L38" s="68"/>
+      <c r="M38" s="68"/>
+      <c r="N38" s="68"/>
+      <c r="O38" s="80"/>
+      <c r="P38" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q38" s="12"/>
+      <c r="R38" s="12"/>
+      <c r="S38" s="12"/>
+      <c r="T38" s="12"/>
+      <c r="U38" s="12"/>
+      <c r="V38" s="12"/>
+      <c r="W38" s="12"/>
+      <c r="X38" s="12"/>
+      <c r="Y38" s="12"/>
+      <c r="Z38" s="12"/>
+      <c r="AA38" s="12"/>
+      <c r="AB38" s="12"/>
+    </row>
+    <row r="39" spans="2:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P39" s="77" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q39" s="77"/>
+      <c r="R39" s="77"/>
+      <c r="S39" s="77"/>
+      <c r="T39" s="77"/>
+      <c r="U39" s="77"/>
+      <c r="V39" s="77"/>
+      <c r="W39" s="77"/>
+      <c r="X39" s="77"/>
+      <c r="Y39" s="77"/>
+      <c r="Z39" s="77"/>
+      <c r="AA39" s="77"/>
+      <c r="AB39" s="77"/>
+      <c r="AC39" s="87"/>
+    </row>
+    <row r="40" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P40" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P41" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="P42" s="66" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q42" s="66"/>
+      <c r="R42" s="66"/>
+      <c r="S42" s="66"/>
+      <c r="T42" s="66"/>
+      <c r="U42" s="66"/>
+      <c r="V42" s="66"/>
+      <c r="W42" s="66"/>
+      <c r="X42" s="66"/>
+      <c r="Y42" s="66"/>
+      <c r="Z42" s="66"/>
+      <c r="AA42" s="66"/>
+      <c r="AB42" s="66"/>
+      <c r="AC42" s="66"/>
+    </row>
+    <row r="43" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P43" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P44" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P45" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q45" s="48"/>
+      <c r="R45" s="48"/>
+      <c r="S45" s="48"/>
+      <c r="T45" s="48"/>
+      <c r="U45" s="48"/>
+      <c r="V45" s="48"/>
+      <c r="W45" s="48"/>
+      <c r="X45" s="48"/>
+      <c r="Y45" s="48"/>
+      <c r="Z45" s="48"/>
+      <c r="AA45" s="48"/>
+      <c r="AB45" s="48"/>
+      <c r="AC45" s="88"/>
+    </row>
+    <row r="46" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P46" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B47" s="81" t="s">
+        <v>90</v>
+      </c>
+      <c r="C47" s="81"/>
+      <c r="D47" s="81"/>
+      <c r="E47" s="81"/>
+      <c r="F47" s="81"/>
+      <c r="G47" s="81"/>
+      <c r="H47" s="81"/>
+      <c r="I47" s="81"/>
+      <c r="J47" s="81"/>
+      <c r="K47" s="81"/>
+      <c r="L47" s="81"/>
+      <c r="M47" s="81"/>
+      <c r="P47" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P48" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q48" s="77"/>
+      <c r="R48" s="77"/>
+      <c r="S48" s="77"/>
+      <c r="T48" s="77"/>
+      <c r="U48" s="77"/>
+      <c r="V48" s="77"/>
+      <c r="W48" s="77"/>
+      <c r="X48" s="77"/>
+      <c r="Y48" s="77"/>
+      <c r="Z48" s="77"/>
+      <c r="AA48" s="77"/>
+      <c r="AB48" s="77"/>
+      <c r="AC48" s="82"/>
+    </row>
+    <row r="49" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="N49" s="80"/>
+      <c r="O49" s="80"/>
+      <c r="P49" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P50" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="51" spans="2:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P51" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q51" s="48"/>
+      <c r="R51" s="48"/>
+      <c r="S51" s="48"/>
+      <c r="T51" s="48"/>
+      <c r="U51" s="48"/>
+      <c r="V51" s="48"/>
+      <c r="W51" s="48"/>
+      <c r="X51" s="48"/>
+      <c r="Y51" s="48"/>
+      <c r="Z51" s="48"/>
+      <c r="AA51" s="48"/>
+      <c r="AB51" s="48"/>
+    </row>
+    <row r="52" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P52" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T53" s="12"/>
+    </row>
+    <row r="54" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B54" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="T54" s="12"/>
+    </row>
+    <row r="55" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="T55" s="12"/>
+    </row>
+    <row r="56" spans="2:29" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O56" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="29"/>
-      <c r="O18" s="29"/>
-      <c r="P18" s="29"/>
-      <c r="Q18" s="29"/>
-      <c r="R18" s="29"/>
-      <c r="S18" s="29"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="29"/>
-      <c r="V18" s="29"/>
-      <c r="W18" s="29"/>
-      <c r="X18" s="29"/>
-      <c r="Y18" s="29"/>
-      <c r="Z18" s="29"/>
-      <c r="AA18" s="29"/>
-      <c r="AB18" s="29"/>
-    </row>
-    <row r="19" spans="2:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="15"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="16"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="16"/>
-      <c r="Y19" s="16"/>
-    </row>
-    <row r="21" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B21" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="10"/>
-    </row>
-    <row r="23" spans="2:33" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="T23" s="24" t="s">
+      <c r="P56" s="77"/>
+      <c r="Q56" s="77"/>
+      <c r="R56" s="77"/>
+      <c r="S56" s="77"/>
+      <c r="T56" s="77"/>
+      <c r="U56" s="77"/>
+      <c r="V56" s="77"/>
+      <c r="W56" s="77"/>
+      <c r="X56" s="77"/>
+      <c r="Y56" s="77"/>
+      <c r="Z56" s="77"/>
+      <c r="AA56" s="77"/>
+      <c r="AB56" s="77"/>
+      <c r="AC56" s="77"/>
+    </row>
+    <row r="58" spans="2:29" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O58" s="83" t="s">
+        <v>88</v>
+      </c>
+      <c r="P58" s="83"/>
+      <c r="Q58" s="83"/>
+      <c r="R58" s="83"/>
+      <c r="S58" s="83"/>
+      <c r="T58" s="83"/>
+      <c r="U58" s="83"/>
+      <c r="V58" s="83"/>
+      <c r="W58" s="83"/>
+      <c r="X58" s="83"/>
+      <c r="Y58" s="83"/>
+      <c r="Z58" s="83"/>
+      <c r="AA58" s="83"/>
+      <c r="AB58" s="83"/>
+      <c r="AC58" s="83"/>
+    </row>
+    <row r="59" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="O59" s="18"/>
+      <c r="P59" s="17"/>
+      <c r="Q59" s="17"/>
+      <c r="R59" s="17"/>
+      <c r="S59" s="17"/>
+      <c r="T59" s="17"/>
+      <c r="U59" s="17"/>
+      <c r="V59" s="17"/>
+      <c r="W59" s="17"/>
+      <c r="X59" s="17"/>
+      <c r="Y59" s="17"/>
+      <c r="Z59" s="17"/>
+      <c r="AA59" s="17"/>
+      <c r="AB59" s="17"/>
+      <c r="AC59" s="17"/>
+    </row>
+    <row r="60" spans="2:29" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O60" s="84" t="s">
+        <v>177</v>
+      </c>
+      <c r="P60" s="84"/>
+      <c r="Q60" s="84"/>
+      <c r="R60" s="84"/>
+      <c r="S60" s="84"/>
+      <c r="T60" s="84"/>
+      <c r="U60" s="84"/>
+      <c r="V60" s="84"/>
+      <c r="W60" s="84"/>
+      <c r="X60" s="84"/>
+      <c r="Y60" s="84"/>
+      <c r="Z60" s="84"/>
+      <c r="AA60" s="84"/>
+      <c r="AB60" s="84"/>
+      <c r="AC60" s="84"/>
+    </row>
+    <row r="62" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="O62" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="U23" s="24"/>
-      <c r="V23" s="24"/>
-      <c r="W23" s="24"/>
-      <c r="X23" s="24"/>
-      <c r="Y23" s="24"/>
-      <c r="Z23" s="24"/>
-      <c r="AA23" s="24"/>
-      <c r="AB23" s="24"/>
-      <c r="AC23" s="24"/>
-      <c r="AD23" s="24"/>
-      <c r="AE23" s="24"/>
-      <c r="AF23" s="24"/>
-    </row>
-    <row r="24" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T24" s="12"/>
-    </row>
-    <row r="25" spans="2:33" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T25" s="47" t="s">
+    </row>
+    <row r="63" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="O63" s="8"/>
+    </row>
+    <row r="64" spans="2:29" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O64" s="78" t="s">
         <v>175</v>
       </c>
-      <c r="U25" s="21"/>
-      <c r="V25" s="21"/>
-      <c r="W25" s="21"/>
-      <c r="X25" s="21"/>
-      <c r="Y25" s="21"/>
-      <c r="Z25" s="21"/>
-      <c r="AA25" s="21"/>
-      <c r="AB25" s="21"/>
-      <c r="AC25" s="21"/>
-      <c r="AD25" s="21"/>
-      <c r="AE25" s="21"/>
-      <c r="AF25" s="21"/>
-      <c r="AG25" s="17"/>
-    </row>
-    <row r="26" spans="2:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T26" s="66"/>
-      <c r="U26" s="18"/>
-      <c r="V26" s="18"/>
-      <c r="W26" s="18"/>
-      <c r="X26" s="18"/>
-      <c r="Y26" s="18"/>
-      <c r="Z26" s="18"/>
-      <c r="AA26" s="18"/>
-      <c r="AB26" s="18"/>
-      <c r="AC26" s="18"/>
-      <c r="AD26" s="18"/>
-      <c r="AE26" s="18"/>
-      <c r="AF26" s="18"/>
-      <c r="AG26" s="17"/>
-    </row>
-    <row r="27" spans="2:33" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T27" s="47" t="s">
-        <v>177</v>
-      </c>
-      <c r="U27" s="47"/>
-      <c r="V27" s="47"/>
-      <c r="W27" s="47"/>
-      <c r="X27" s="47"/>
-      <c r="Y27" s="47"/>
-      <c r="Z27" s="47"/>
-      <c r="AA27" s="47"/>
-      <c r="AB27" s="47"/>
-      <c r="AC27" s="47"/>
-      <c r="AD27" s="47"/>
-      <c r="AE27" s="47"/>
-      <c r="AF27" s="47"/>
-      <c r="AG27" s="17"/>
-    </row>
-    <row r="28" spans="2:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T28" s="18"/>
-      <c r="U28" s="18"/>
-      <c r="V28" s="18"/>
-      <c r="W28" s="18"/>
-      <c r="X28" s="18"/>
-      <c r="Y28" s="18"/>
-      <c r="Z28" s="18"/>
-      <c r="AA28" s="18"/>
-      <c r="AB28" s="18"/>
-      <c r="AC28" s="18"/>
-      <c r="AD28" s="18"/>
-      <c r="AE28" s="18"/>
-      <c r="AF28" s="18"/>
-      <c r="AG28" s="17"/>
-    </row>
-    <row r="29" spans="2:33" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="T29" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="U29" s="24"/>
-      <c r="V29" s="24"/>
-      <c r="W29" s="24"/>
-      <c r="X29" s="24"/>
-      <c r="Y29" s="24"/>
-      <c r="Z29" s="24"/>
-      <c r="AA29" s="24"/>
-      <c r="AB29" s="24"/>
-      <c r="AC29" s="24"/>
-      <c r="AD29" s="24"/>
-      <c r="AE29" s="24"/>
-      <c r="AF29" s="24"/>
-    </row>
-    <row r="30" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T30" s="12"/>
-    </row>
-    <row r="31" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T31" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" spans="2:33" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T32" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T33" s="12"/>
-    </row>
-    <row r="34" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T34" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="U34" s="8"/>
-      <c r="V34" s="8"/>
-      <c r="W34" s="8"/>
-      <c r="X34" s="8"/>
-      <c r="Y34" s="8"/>
-    </row>
-    <row r="36" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T36" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="U36" s="12"/>
-      <c r="V36" s="12"/>
-      <c r="W36" s="12"/>
-      <c r="X36" s="12"/>
-      <c r="Y36" s="12"/>
-      <c r="Z36" s="12"/>
-      <c r="AA36" s="12"/>
-      <c r="AB36" s="12"/>
-      <c r="AC36" s="12"/>
-      <c r="AD36" s="12"/>
-      <c r="AE36" s="12"/>
-      <c r="AF36" s="12"/>
-    </row>
-    <row r="37" spans="2:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T37" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="U37" s="25"/>
-      <c r="V37" s="25"/>
-      <c r="W37" s="25"/>
-      <c r="X37" s="25"/>
-      <c r="Y37" s="25"/>
-      <c r="Z37" s="25"/>
-      <c r="AA37" s="25"/>
-      <c r="AB37" s="25"/>
-      <c r="AC37" s="25"/>
-      <c r="AD37" s="25"/>
-      <c r="AE37" s="25"/>
-      <c r="AF37" s="25"/>
-    </row>
-    <row r="39" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T39" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="U39" s="12"/>
-      <c r="V39" s="12"/>
-      <c r="W39" s="12"/>
-      <c r="X39" s="12"/>
-      <c r="Y39" s="12"/>
-      <c r="Z39" s="12"/>
-      <c r="AA39" s="12"/>
-      <c r="AB39" s="12"/>
-      <c r="AC39" s="12"/>
-      <c r="AD39" s="12"/>
-      <c r="AE39" s="12"/>
-      <c r="AF39" s="12"/>
-    </row>
-    <row r="40" spans="2:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T40" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="U40" s="25"/>
-      <c r="V40" s="25"/>
-      <c r="W40" s="25"/>
-      <c r="X40" s="25"/>
-      <c r="Y40" s="25"/>
-      <c r="Z40" s="25"/>
-      <c r="AA40" s="25"/>
-      <c r="AB40" s="25"/>
-      <c r="AC40" s="25"/>
-      <c r="AD40" s="25"/>
-      <c r="AE40" s="25"/>
-      <c r="AF40" s="25"/>
-      <c r="AG40" s="25"/>
-      <c r="AH40" s="25"/>
-      <c r="AI40" s="25"/>
-      <c r="AJ40" s="25"/>
-      <c r="AK40" s="25"/>
-    </row>
-    <row r="41" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T41" s="12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="42" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T42" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="2:37" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="T43" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="U43" s="24"/>
-      <c r="V43" s="24"/>
-      <c r="W43" s="24"/>
-      <c r="X43" s="24"/>
-      <c r="Y43" s="24"/>
-      <c r="Z43" s="24"/>
-      <c r="AA43" s="24"/>
-      <c r="AB43" s="24"/>
-      <c r="AC43" s="24"/>
-      <c r="AD43" s="24"/>
-      <c r="AE43" s="24"/>
-      <c r="AF43" s="24"/>
-      <c r="AG43" s="24"/>
-    </row>
-    <row r="44" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T44" s="12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="45" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T45" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="46" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B46" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="27"/>
-      <c r="M46" s="27"/>
-      <c r="N46" s="27"/>
-      <c r="O46" s="27"/>
-      <c r="P46" s="27"/>
-      <c r="Q46" s="27"/>
-      <c r="R46" s="27"/>
-      <c r="T46" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="U46" s="24"/>
-      <c r="V46" s="24"/>
-      <c r="W46" s="24"/>
-      <c r="X46" s="24"/>
-      <c r="Y46" s="24"/>
-      <c r="Z46" s="24"/>
-      <c r="AA46" s="24"/>
-      <c r="AB46" s="24"/>
-      <c r="AC46" s="24"/>
-      <c r="AD46" s="24"/>
-      <c r="AE46" s="24"/>
-      <c r="AF46" s="24"/>
-      <c r="AG46" s="24"/>
-      <c r="AH46" s="24"/>
-      <c r="AI46" s="24"/>
-    </row>
-    <row r="47" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T47" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="48" spans="2:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T48" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="49" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T49" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="50" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T50" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="51" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T51" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="52" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T52" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="53" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T53" s="12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="54" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T54" s="12"/>
-    </row>
-    <row r="55" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T55" s="12"/>
-    </row>
-    <row r="56" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T56" s="12"/>
-    </row>
-    <row r="57" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T57" s="12"/>
-    </row>
-    <row r="58" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T58" s="12"/>
-    </row>
-    <row r="59" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T59" s="12"/>
-    </row>
-    <row r="60" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T60" s="12"/>
-    </row>
-    <row r="61" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B61" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="27"/>
-      <c r="I61" s="27"/>
-      <c r="J61" s="27"/>
-      <c r="K61" s="27"/>
-      <c r="L61" s="27"/>
-      <c r="M61" s="27"/>
-      <c r="N61" s="27"/>
-      <c r="O61" s="27"/>
-      <c r="P61" s="27"/>
-      <c r="Q61" s="27"/>
-      <c r="R61" s="27"/>
-      <c r="T61" s="12"/>
-    </row>
-    <row r="62" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T62" s="12"/>
-    </row>
-    <row r="63" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T63" s="12"/>
-    </row>
-    <row r="64" spans="2:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B64" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="66" spans="20:37" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T66" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="U66" s="21"/>
-      <c r="V66" s="21"/>
-      <c r="W66" s="21"/>
-      <c r="X66" s="21"/>
-      <c r="Y66" s="21"/>
-      <c r="Z66" s="21"/>
-      <c r="AA66" s="21"/>
-      <c r="AB66" s="21"/>
-      <c r="AC66" s="21"/>
-      <c r="AD66" s="21"/>
-      <c r="AE66" s="21"/>
-      <c r="AF66" s="21"/>
-      <c r="AG66" s="21"/>
-      <c r="AH66" s="21"/>
-      <c r="AI66" s="21"/>
-      <c r="AJ66" s="21"/>
-      <c r="AK66" s="21"/>
-    </row>
-    <row r="68" spans="20:37" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T68" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="U68" s="21"/>
-      <c r="V68" s="21"/>
-      <c r="W68" s="21"/>
-      <c r="X68" s="21"/>
-      <c r="Y68" s="21"/>
-      <c r="Z68" s="21"/>
-      <c r="AA68" s="21"/>
-      <c r="AB68" s="21"/>
-      <c r="AC68" s="21"/>
-      <c r="AD68" s="21"/>
-      <c r="AE68" s="21"/>
-      <c r="AF68" s="21"/>
-      <c r="AG68" s="21"/>
-      <c r="AH68" s="21"/>
-      <c r="AI68" s="21"/>
-      <c r="AJ68" s="21"/>
-      <c r="AK68" s="21"/>
-    </row>
-    <row r="69" spans="20:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T69" s="19"/>
-      <c r="U69" s="18"/>
-      <c r="V69" s="18"/>
-      <c r="W69" s="18"/>
-      <c r="X69" s="18"/>
-      <c r="Y69" s="18"/>
-      <c r="Z69" s="18"/>
-      <c r="AA69" s="18"/>
-      <c r="AB69" s="18"/>
-      <c r="AC69" s="18"/>
-      <c r="AD69" s="18"/>
-      <c r="AE69" s="18"/>
-      <c r="AF69" s="18"/>
-      <c r="AG69" s="18"/>
-      <c r="AH69" s="18"/>
-      <c r="AI69" s="18"/>
-      <c r="AJ69" s="18"/>
-      <c r="AK69" s="18"/>
-    </row>
-    <row r="70" spans="20:37" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T70" s="47" t="s">
-        <v>178</v>
-      </c>
-      <c r="U70" s="47"/>
-      <c r="V70" s="47"/>
-      <c r="W70" s="47"/>
-      <c r="X70" s="47"/>
-      <c r="Y70" s="47"/>
-      <c r="Z70" s="47"/>
-      <c r="AA70" s="47"/>
-      <c r="AB70" s="47"/>
-      <c r="AC70" s="47"/>
-      <c r="AD70" s="47"/>
-      <c r="AE70" s="47"/>
-      <c r="AF70" s="47"/>
-      <c r="AG70" s="47"/>
-      <c r="AH70" s="47"/>
-      <c r="AI70" s="47"/>
-      <c r="AJ70" s="47"/>
-      <c r="AK70" s="47"/>
-    </row>
-    <row r="72" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T72" s="8" t="s">
+      <c r="P64" s="64"/>
+      <c r="Q64" s="64"/>
+      <c r="R64" s="64"/>
+      <c r="S64" s="64"/>
+      <c r="T64" s="64"/>
+      <c r="U64" s="64"/>
+      <c r="V64" s="64"/>
+      <c r="W64" s="64"/>
+      <c r="X64" s="64"/>
+      <c r="Y64" s="64"/>
+      <c r="Z64" s="64"/>
+      <c r="AA64" s="64"/>
+      <c r="AB64" s="64"/>
+      <c r="AC64" s="64"/>
+    </row>
+    <row r="65" spans="15:29" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="O65" s="18"/>
+      <c r="P65" s="17"/>
+      <c r="Q65" s="17"/>
+      <c r="R65" s="17"/>
+      <c r="S65" s="17"/>
+      <c r="T65" s="17"/>
+      <c r="U65" s="17"/>
+      <c r="V65" s="17"/>
+      <c r="W65" s="17"/>
+      <c r="X65" s="17"/>
+      <c r="Y65" s="17"/>
+      <c r="Z65" s="17"/>
+      <c r="AA65" s="17"/>
+      <c r="AB65" s="17"/>
+      <c r="AC65" s="17"/>
+    </row>
+    <row r="66" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O66" s="86" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="73" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T73" s="8"/>
-    </row>
-    <row r="74" spans="20:37" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T74" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="U74" s="21"/>
-      <c r="V74" s="21"/>
-      <c r="W74" s="21"/>
-      <c r="X74" s="21"/>
-      <c r="Y74" s="21"/>
-      <c r="Z74" s="21"/>
-      <c r="AA74" s="21"/>
-      <c r="AB74" s="21"/>
-      <c r="AC74" s="21"/>
-      <c r="AD74" s="21"/>
-      <c r="AE74" s="21"/>
-      <c r="AF74" s="21"/>
-      <c r="AG74" s="21"/>
-      <c r="AH74" s="21"/>
-      <c r="AI74" s="21"/>
-      <c r="AJ74" s="21"/>
-      <c r="AK74" s="21"/>
-    </row>
-    <row r="75" spans="20:37" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="T75" s="19"/>
-      <c r="U75" s="18"/>
-      <c r="V75" s="18"/>
-      <c r="W75" s="18"/>
-      <c r="X75" s="18"/>
-      <c r="Y75" s="18"/>
-      <c r="Z75" s="18"/>
-      <c r="AA75" s="18"/>
-      <c r="AB75" s="18"/>
-      <c r="AC75" s="18"/>
-      <c r="AD75" s="18"/>
-      <c r="AE75" s="18"/>
-      <c r="AF75" s="18"/>
-      <c r="AG75" s="18"/>
-      <c r="AH75" s="18"/>
-      <c r="AI75" s="18"/>
-      <c r="AJ75" s="18"/>
-      <c r="AK75" s="18"/>
-    </row>
-    <row r="76" spans="20:37" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T76" s="22" t="s">
+      <c r="P66" s="86"/>
+      <c r="Q66" s="86"/>
+      <c r="R66" s="86"/>
+      <c r="S66" s="86"/>
+      <c r="T66" s="85"/>
+      <c r="U66" s="85"/>
+      <c r="V66" s="85"/>
+      <c r="W66" s="85"/>
+      <c r="X66" s="85"/>
+      <c r="Y66" s="85"/>
+      <c r="Z66" s="85"/>
+      <c r="AA66" s="85"/>
+      <c r="AB66" s="85"/>
+      <c r="AC66" s="85"/>
+    </row>
+    <row r="67" spans="15:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O67" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="U76" s="22"/>
-      <c r="V76" s="22"/>
-      <c r="W76" s="22"/>
-      <c r="X76" s="22"/>
-      <c r="Y76" s="22"/>
-      <c r="Z76" s="22"/>
-      <c r="AA76" s="22"/>
-      <c r="AB76" s="22"/>
-      <c r="AC76" s="22"/>
-      <c r="AD76" s="22"/>
-      <c r="AE76" s="22"/>
-      <c r="AF76" s="22"/>
-      <c r="AG76" s="22"/>
-      <c r="AH76" s="22"/>
-      <c r="AI76" s="22"/>
-      <c r="AJ76" s="22"/>
-      <c r="AK76" s="22"/>
-    </row>
-    <row r="77" spans="20:37" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T77" s="21" t="s">
+      <c r="P67" s="48"/>
+      <c r="Q67" s="48"/>
+      <c r="R67" s="48"/>
+      <c r="S67" s="48"/>
+      <c r="T67" s="48"/>
+      <c r="U67" s="48"/>
+      <c r="V67" s="48"/>
+      <c r="W67" s="48"/>
+      <c r="X67" s="48"/>
+      <c r="Y67" s="48"/>
+      <c r="Z67" s="48"/>
+      <c r="AA67" s="48"/>
+      <c r="AB67" s="48"/>
+      <c r="AC67" s="48"/>
+    </row>
+    <row r="68" spans="15:29" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O68" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="69" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O69" s="86" t="s">
         <v>77</v>
       </c>
-      <c r="U77" s="21"/>
-      <c r="V77" s="21"/>
-      <c r="W77" s="21"/>
-      <c r="X77" s="21"/>
-      <c r="Y77" s="21"/>
-      <c r="Z77" s="21"/>
-      <c r="AA77" s="21"/>
-      <c r="AB77" s="21"/>
-      <c r="AC77" s="21"/>
-      <c r="AD77" s="21"/>
-      <c r="AE77" s="21"/>
-      <c r="AF77" s="21"/>
-      <c r="AG77" s="21"/>
-      <c r="AH77" s="21"/>
-      <c r="AI77" s="21"/>
-      <c r="AJ77" s="21"/>
-      <c r="AK77" s="21"/>
-    </row>
-    <row r="78" spans="20:37" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T78" s="12" t="s">
+      <c r="P69" s="86"/>
+      <c r="Q69" s="86"/>
+      <c r="R69" s="86"/>
+      <c r="S69" s="86"/>
+      <c r="T69" s="85"/>
+      <c r="U69" s="85"/>
+      <c r="V69" s="85"/>
+      <c r="W69" s="85"/>
+      <c r="X69" s="85"/>
+      <c r="Y69" s="85"/>
+      <c r="Z69" s="85"/>
+      <c r="AA69" s="85"/>
+      <c r="AB69" s="85"/>
+      <c r="AC69" s="85"/>
+    </row>
+    <row r="70" spans="15:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O70" s="77" t="s">
+        <v>78</v>
+      </c>
+      <c r="P70" s="77"/>
+      <c r="Q70" s="77"/>
+      <c r="R70" s="77"/>
+      <c r="S70" s="77"/>
+      <c r="T70" s="77"/>
+      <c r="U70" s="77"/>
+      <c r="V70" s="77"/>
+      <c r="W70" s="77"/>
+      <c r="X70" s="77"/>
+      <c r="Y70" s="77"/>
+      <c r="Z70" s="77"/>
+      <c r="AA70" s="77"/>
+      <c r="AB70" s="77"/>
+      <c r="AC70" s="77"/>
+    </row>
+    <row r="71" spans="15:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="O71" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="79" spans="20:37" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="T79" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="U79" s="22"/>
-      <c r="V79" s="22"/>
-      <c r="W79" s="22"/>
-      <c r="X79" s="22"/>
-      <c r="Y79" s="22"/>
-      <c r="Z79" s="22"/>
-      <c r="AA79" s="22"/>
-      <c r="AB79" s="22"/>
-      <c r="AC79" s="22"/>
-      <c r="AD79" s="22"/>
-      <c r="AE79" s="22"/>
-      <c r="AF79" s="22"/>
-      <c r="AG79" s="22"/>
-      <c r="AH79" s="22"/>
-      <c r="AI79" s="22"/>
-      <c r="AJ79" s="22"/>
-      <c r="AK79" s="22"/>
-    </row>
-    <row r="80" spans="20:37" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T80" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="U80" s="21"/>
-      <c r="V80" s="21"/>
-      <c r="W80" s="21"/>
-      <c r="X80" s="21"/>
-      <c r="Y80" s="21"/>
-      <c r="Z80" s="21"/>
-      <c r="AA80" s="21"/>
-      <c r="AB80" s="21"/>
-      <c r="AC80" s="21"/>
-      <c r="AD80" s="21"/>
-      <c r="AE80" s="21"/>
-      <c r="AF80" s="21"/>
-      <c r="AG80" s="21"/>
-      <c r="AH80" s="21"/>
-      <c r="AI80" s="21"/>
-      <c r="AJ80" s="21"/>
-      <c r="AK80" s="21"/>
-    </row>
-    <row r="81" spans="20:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="T81" s="12" t="s">
-        <v>81</v>
-      </c>
-    </row>
+    <row r="72" spans="15:29" ht="42" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="15:29" ht="40.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="15:29" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="T70:AK70"/>
-    <mergeCell ref="N6:Y6"/>
-    <mergeCell ref="T46:AI46"/>
-    <mergeCell ref="T43:AG43"/>
-    <mergeCell ref="T40:AK40"/>
-    <mergeCell ref="T68:AK68"/>
-    <mergeCell ref="B46:R46"/>
-    <mergeCell ref="T25:AF25"/>
-    <mergeCell ref="T23:AF23"/>
-    <mergeCell ref="T37:AF37"/>
-    <mergeCell ref="N8:AD8"/>
-    <mergeCell ref="N10:AD10"/>
-    <mergeCell ref="T29:AF29"/>
-    <mergeCell ref="B18:AB18"/>
-    <mergeCell ref="T66:AK66"/>
-    <mergeCell ref="B61:R61"/>
-    <mergeCell ref="T27:AF27"/>
-    <mergeCell ref="T74:AK74"/>
-    <mergeCell ref="T76:AK76"/>
-    <mergeCell ref="T77:AK77"/>
-    <mergeCell ref="T79:AK79"/>
-    <mergeCell ref="T80:AK80"/>
+  <mergeCells count="24">
+    <mergeCell ref="B38:N38"/>
+    <mergeCell ref="B47:M47"/>
+    <mergeCell ref="O58:AC58"/>
+    <mergeCell ref="O56:AC56"/>
+    <mergeCell ref="O60:AC60"/>
+    <mergeCell ref="O64:AC64"/>
+    <mergeCell ref="O66:S66"/>
+    <mergeCell ref="O67:AC67"/>
+    <mergeCell ref="O69:S69"/>
+    <mergeCell ref="O70:AC70"/>
+    <mergeCell ref="P39:AB39"/>
+    <mergeCell ref="P45:AB45"/>
+    <mergeCell ref="P48:AB48"/>
+    <mergeCell ref="P26:AB26"/>
+    <mergeCell ref="P51:AB51"/>
+    <mergeCell ref="L8:W8"/>
+    <mergeCell ref="P42:AC42"/>
+    <mergeCell ref="P24:AB24"/>
+    <mergeCell ref="P22:AB22"/>
+    <mergeCell ref="P36:AB36"/>
+    <mergeCell ref="L10:AB10"/>
+    <mergeCell ref="L12:AB12"/>
+    <mergeCell ref="P28:AB28"/>
+    <mergeCell ref="B17:AB17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -5226,220 +6154,175 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A2:AJ130"/>
+  <dimension ref="A2:AE133"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
     </row>
-    <row r="4" spans="1:36" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-    </row>
-    <row r="5" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="75" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+    </row>
+    <row r="5" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="L5" s="41" t="s">
-        <v>133</v>
-      </c>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41"/>
-      <c r="O5" s="41"/>
-      <c r="P5" s="41"/>
-    </row>
-    <row r="6" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L5" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="57"/>
+    </row>
+    <row r="6" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
-      <c r="L6" s="69" t="s">
+      <c r="L6" s="74" t="s">
+        <v>123</v>
+      </c>
+      <c r="M6" s="74"/>
+      <c r="N6" s="74"/>
+      <c r="O6" s="74"/>
+      <c r="P6" s="74"/>
+    </row>
+    <row r="7" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="1"/>
+      <c r="L7" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="M6" s="69"/>
-      <c r="N6" s="69"/>
-      <c r="O6" s="69"/>
-      <c r="P6" s="69"/>
-    </row>
-    <row r="7" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="1"/>
-      <c r="L7" s="62" t="s">
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+    </row>
+    <row r="8" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1"/>
+      <c r="L8" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="M7" s="62"/>
-      <c r="N7" s="62"/>
-      <c r="O7" s="62"/>
-      <c r="P7" s="62"/>
-    </row>
-    <row r="8" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="1"/>
-      <c r="L8" s="69" t="s">
+      <c r="M8" s="74"/>
+      <c r="N8" s="74"/>
+      <c r="O8" s="74"/>
+      <c r="P8" s="74"/>
+    </row>
+    <row r="9" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="1"/>
+      <c r="L9" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="69"/>
-      <c r="P8" s="69"/>
-    </row>
-    <row r="9" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="1"/>
-      <c r="L9" s="69" t="s">
+      <c r="M9" s="74"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="74"/>
+      <c r="P9" s="74"/>
+    </row>
+    <row r="10" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="1"/>
+      <c r="L10" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="M9" s="69"/>
-      <c r="N9" s="69"/>
-      <c r="O9" s="69"/>
-      <c r="P9" s="69"/>
-      <c r="R9" s="70"/>
-      <c r="S9" s="70"/>
-      <c r="T9" s="70"/>
-      <c r="U9" s="70"/>
-      <c r="V9" s="70"/>
-      <c r="W9" s="70"/>
-      <c r="X9" s="70"/>
-      <c r="Y9" s="70"/>
-      <c r="Z9" s="70"/>
-    </row>
-    <row r="10" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="1"/>
-      <c r="L10" s="62" t="s">
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+    </row>
+    <row r="11" spans="1:31" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="1"/>
+      <c r="L11" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="M10" s="62"/>
-      <c r="N10" s="62"/>
-      <c r="O10" s="62"/>
-      <c r="P10" s="62"/>
-      <c r="R10" s="70"/>
-      <c r="S10" s="70"/>
-      <c r="T10" s="70"/>
-      <c r="U10" s="70"/>
-      <c r="V10" s="70"/>
-      <c r="W10" s="70"/>
-      <c r="X10" s="70"/>
-      <c r="Y10" s="70"/>
-      <c r="Z10" s="70"/>
-    </row>
-    <row r="11" spans="1:36" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="1"/>
-      <c r="L11" s="62" t="s">
+      <c r="M11" s="74"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="74"/>
+      <c r="P11" s="74"/>
+    </row>
+    <row r="12" spans="1:31" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="1"/>
+      <c r="L12" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="M11" s="69"/>
-      <c r="N11" s="69"/>
-      <c r="O11" s="69"/>
-      <c r="P11" s="69"/>
-      <c r="R11" s="70"/>
-      <c r="S11" s="70"/>
-      <c r="T11" s="70"/>
-      <c r="U11" s="70"/>
-      <c r="V11" s="70"/>
-      <c r="W11" s="70"/>
-      <c r="X11" s="70"/>
-      <c r="Y11" s="70"/>
-      <c r="Z11" s="70"/>
-    </row>
-    <row r="12" spans="1:36" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="1"/>
-      <c r="L12" s="62" t="s">
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="R12" s="73" t="s">
+        <v>141</v>
+      </c>
+      <c r="S12" s="73"/>
+      <c r="T12" s="73"/>
+      <c r="U12" s="73"/>
+      <c r="V12" s="73"/>
+      <c r="W12" s="73"/>
+      <c r="X12" s="73"/>
+      <c r="Y12" s="73"/>
+      <c r="Z12" s="73"/>
+      <c r="AA12" s="73"/>
+      <c r="AB12" s="73"/>
+      <c r="AC12" s="73"/>
+      <c r="AD12" s="89"/>
+      <c r="AE12" s="89"/>
+    </row>
+    <row r="13" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="1"/>
+      <c r="L13" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="M12" s="62"/>
-      <c r="N12" s="62"/>
-      <c r="O12" s="62"/>
-      <c r="P12" s="62"/>
-      <c r="R12" s="70"/>
-      <c r="S12" s="70"/>
-      <c r="T12" s="70"/>
-      <c r="U12" s="70"/>
-      <c r="V12" s="70"/>
-    </row>
-    <row r="13" spans="1:36" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="1"/>
-      <c r="L13" s="69" t="s">
+      <c r="M13" s="74"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="74"/>
+      <c r="P13" s="74"/>
+    </row>
+    <row r="14" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A14" s="1"/>
+      <c r="L14" s="74" t="s">
         <v>131</v>
       </c>
-      <c r="M13" s="69"/>
-      <c r="N13" s="69"/>
-      <c r="O13" s="69"/>
-      <c r="P13" s="69"/>
-      <c r="R13" s="70"/>
-      <c r="S13" s="70"/>
-      <c r="T13" s="70"/>
-      <c r="U13" s="70"/>
-      <c r="W13" s="73" t="s">
-        <v>142</v>
-      </c>
-      <c r="X13" s="73"/>
-      <c r="Y13" s="73"/>
-      <c r="Z13" s="73"/>
-      <c r="AA13" s="73"/>
-      <c r="AB13" s="73"/>
-      <c r="AC13" s="73"/>
-      <c r="AD13" s="73"/>
-      <c r="AE13" s="73"/>
-      <c r="AF13" s="73"/>
-      <c r="AG13" s="73"/>
-      <c r="AH13" s="73"/>
-      <c r="AI13" s="73"/>
-      <c r="AJ13" s="73"/>
-    </row>
-    <row r="14" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A14" s="1"/>
-      <c r="L14" s="69" t="s">
-        <v>132</v>
-      </c>
-      <c r="M14" s="69"/>
-      <c r="N14" s="69"/>
-      <c r="O14" s="69"/>
-      <c r="P14" s="69"/>
-      <c r="R14" s="70"/>
-      <c r="S14" s="70"/>
-      <c r="T14" s="70"/>
-      <c r="U14" s="70"/>
-      <c r="V14" s="70"/>
-      <c r="W14" s="70"/>
-      <c r="X14" s="70"/>
-      <c r="Y14" s="70"/>
-      <c r="Z14" s="70"/>
-    </row>
-    <row r="15" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="M14" s="74"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="74"/>
+      <c r="P14" s="74"/>
+    </row>
+    <row r="15" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
-      <c r="R15" s="71"/>
-    </row>
-    <row r="16" spans="1:36" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="R15" s="23"/>
+    </row>
+    <row r="16" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
     </row>
     <row r="17" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A17" s="1"/>
-      <c r="L17" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="M17" s="41"/>
-      <c r="N17" s="41"/>
-      <c r="O17" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="P17" s="41"/>
-      <c r="Q17" s="41"/>
-      <c r="R17" s="41"/>
-      <c r="S17" s="41"/>
-      <c r="T17" s="41"/>
+      <c r="L17" s="57" t="s">
+        <v>133</v>
+      </c>
+      <c r="M17" s="57"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="57" t="s">
+        <v>135</v>
+      </c>
+      <c r="P17" s="57"/>
+      <c r="Q17" s="57"/>
+      <c r="R17" s="57"/>
+      <c r="S17" s="57"/>
+      <c r="T17" s="57"/>
     </row>
     <row r="18" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
-      <c r="L18" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
+      <c r="L18" s="62" t="s">
+        <v>136</v>
+      </c>
+      <c r="M18" s="62"/>
+      <c r="N18" s="62"/>
       <c r="O18" s="72" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P18" s="72"/>
       <c r="Q18" s="72"/>
@@ -5449,13 +6332,13 @@
     </row>
     <row r="19" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
-      <c r="L19" s="37" t="s">
+      <c r="L19" s="62" t="s">
+        <v>137</v>
+      </c>
+      <c r="M19" s="62"/>
+      <c r="N19" s="62"/>
+      <c r="O19" s="72" t="s">
         <v>138</v>
-      </c>
-      <c r="M19" s="37"/>
-      <c r="N19" s="37"/>
-      <c r="O19" s="72" t="s">
-        <v>139</v>
       </c>
       <c r="P19" s="72"/>
       <c r="Q19" s="72"/>
@@ -5465,13 +6348,13 @@
     </row>
     <row r="20" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
-      <c r="L20" s="37" t="s">
+      <c r="L20" s="62" t="s">
+        <v>139</v>
+      </c>
+      <c r="M20" s="62"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="72" t="s">
         <v>140</v>
-      </c>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="72" t="s">
-        <v>141</v>
       </c>
       <c r="P20" s="72"/>
       <c r="Q20" s="72"/>
@@ -5487,15 +6370,15 @@
     </row>
     <row r="23" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A23" s="1"/>
-      <c r="L23" s="68"/>
-      <c r="M23" s="68"/>
-      <c r="N23" s="68"/>
-      <c r="O23" s="67"/>
-      <c r="P23" s="67"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="21"/>
     </row>
     <row r="25" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B25" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
@@ -5503,30 +6386,30 @@
     </row>
     <row r="27" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B27" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="56" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B56" s="65" t="s">
-        <v>123</v>
+      <c r="B56" s="20" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B57" s="65"/>
+      <c r="B57" s="20"/>
     </row>
     <row r="58" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="85" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B85" s="65" t="s">
-        <v>143</v>
+      <c r="B85" s="20" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="87" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B87" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="88" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
@@ -5534,167 +6417,200 @@
     </row>
     <row r="89" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B89" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="91" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B91" s="65" t="s">
-        <v>157</v>
+      <c r="B91" s="20" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="93" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B93" s="74" t="s">
+      <c r="B93" s="24" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B94" s="24" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="94" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B94" s="74" t="s">
+    <row r="95" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B95" s="24" t="s">
         <v>150</v>
-      </c>
-    </row>
-    <row r="95" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B95" s="74" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="97" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B97" s="8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B99" s="20" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B99" s="65" t="s">
+    <row r="101" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B101" s="20" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B101" s="65" t="s">
+    <row r="102" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B102" s="20"/>
+    </row>
+    <row r="103" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B103" s="20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B105" s="71" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="102" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B102" s="65"/>
-    </row>
-    <row r="103" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B103" s="65" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="105" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B105" s="75" t="s">
-        <v>156</v>
-      </c>
-      <c r="C105" s="75"/>
-      <c r="D105" s="75"/>
-      <c r="E105" s="75"/>
-      <c r="F105" s="75"/>
-      <c r="G105" s="75"/>
-      <c r="H105" s="75"/>
-      <c r="I105" s="75"/>
-      <c r="J105" s="75"/>
-      <c r="K105" s="75"/>
-      <c r="L105" s="75"/>
-      <c r="M105" s="75"/>
-      <c r="N105" s="75"/>
-      <c r="O105" s="75"/>
-      <c r="P105" s="75"/>
-      <c r="Q105" s="75"/>
-      <c r="R105" s="75"/>
-      <c r="S105" s="75"/>
-      <c r="T105" s="75"/>
-      <c r="U105" s="75"/>
-      <c r="V105" s="75"/>
-      <c r="W105" s="75"/>
-      <c r="X105" s="75"/>
-      <c r="Y105" s="75"/>
+      <c r="C105" s="71"/>
+      <c r="D105" s="71"/>
+      <c r="E105" s="71"/>
+      <c r="F105" s="71"/>
+      <c r="G105" s="71"/>
+      <c r="H105" s="71"/>
+      <c r="I105" s="71"/>
+      <c r="J105" s="71"/>
+      <c r="K105" s="71"/>
+      <c r="L105" s="71"/>
+      <c r="M105" s="71"/>
+      <c r="N105" s="71"/>
+      <c r="O105" s="71"/>
+      <c r="P105" s="71"/>
+      <c r="Q105" s="71"/>
+      <c r="R105" s="71"/>
+      <c r="S105" s="71"/>
+      <c r="T105" s="71"/>
+      <c r="U105" s="71"/>
+      <c r="V105" s="71"/>
+      <c r="W105" s="71"/>
+      <c r="X105" s="71"/>
+      <c r="Y105" s="71"/>
     </row>
     <row r="108" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A108" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="110" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B110" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C110" s="8"/>
-      <c r="D110" s="76"/>
+      <c r="D110" s="25"/>
     </row>
     <row r="112" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B112" s="65" t="s">
+      <c r="B112" s="20" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="113" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B113" s="20"/>
+    </row>
+    <row r="114" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B114" s="20" t="s">
         <v>171</v>
-      </c>
-    </row>
-    <row r="113" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B113" s="65"/>
-    </row>
-    <row r="114" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B114" s="65" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="116" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B116" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="118" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B118" s="77" t="s">
+        <v>165</v>
+      </c>
+      <c r="C118" s="77"/>
+      <c r="D118" s="77"/>
+      <c r="E118" s="77"/>
+      <c r="F118" s="77"/>
+      <c r="G118" s="77"/>
+      <c r="H118" s="77"/>
+      <c r="I118" s="77"/>
+      <c r="J118" s="77"/>
+      <c r="K118" s="77"/>
+      <c r="L118" s="77"/>
+      <c r="M118" s="77"/>
+      <c r="N118" s="77"/>
+      <c r="O118" s="77"/>
+      <c r="P118" s="77"/>
+      <c r="Q118" s="77"/>
+      <c r="R118" s="77"/>
+      <c r="S118" s="77"/>
+      <c r="T118" s="77"/>
+      <c r="U118" s="77"/>
+      <c r="V118" s="77"/>
+      <c r="W118" s="77"/>
+      <c r="X118" s="77"/>
+      <c r="Y118" s="77"/>
+      <c r="Z118" s="77"/>
+      <c r="AA118" s="77"/>
+      <c r="AB118" s="77"/>
+      <c r="AC118" s="77"/>
+    </row>
+    <row r="119" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B119" s="26" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="120" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B120" s="26"/>
+    </row>
+    <row r="121" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B121" s="20" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="118" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B118" s="65" t="s">
+    <row r="122" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B122" s="20"/>
+    </row>
+    <row r="123" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B123" s="76" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="124" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B124" s="20"/>
+    </row>
+    <row r="125" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B125" s="20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="127" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B127" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="AC118" s="78" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="120" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B120" s="65" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="121" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B121" s="65"/>
-    </row>
-    <row r="122" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B122" s="65" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="124" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B124" s="8" t="s">
+    </row>
+    <row r="129" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B129" s="20" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="126" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B126" s="65" t="s">
+    <row r="131" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B131" s="8" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="128" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B128" s="8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="130" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B130" s="65" t="s">
-        <v>174</v>
-      </c>
-      <c r="L130" s="79" t="s">
+    <row r="133" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B133" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="M130" s="65"/>
+      <c r="L133" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="M133" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="B105:Y105"/>
-    <mergeCell ref="O18:T18"/>
-    <mergeCell ref="W13:AJ13"/>
-    <mergeCell ref="O17:T17"/>
-    <mergeCell ref="O19:T19"/>
-    <mergeCell ref="O20:T20"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L20:N20"/>
+  <mergeCells count="22">
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="R12:AC12"/>
+    <mergeCell ref="B118:AC118"/>
     <mergeCell ref="L11:P11"/>
     <mergeCell ref="L12:P12"/>
     <mergeCell ref="L13:P13"/>
@@ -5705,11 +6621,19 @@
     <mergeCell ref="L8:P8"/>
     <mergeCell ref="L9:P9"/>
     <mergeCell ref="L10:P10"/>
-    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B105:Y105"/>
+    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="O17:T17"/>
+    <mergeCell ref="O19:T19"/>
+    <mergeCell ref="O20:T20"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L20:N20"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="L130" location="Dialogues!A1" display="Dialogues!A1" xr:uid="{5724AB96-1B0F-4DFD-A35F-382AC93CCD96}"/>
-    <hyperlink ref="AC118" location="'Item List'!A1" display="'Item List'!A1" xr:uid="{961E795F-F85E-4E2A-BAED-F63C80C609A5}"/>
+    <hyperlink ref="L133" location="Dialogues!A1" display="Dialogues!A1" xr:uid="{5724AB96-1B0F-4DFD-A35F-382AC93CCD96}"/>
+    <hyperlink ref="B119" location="'Item List'!A1" display="'Item List'!A1" xr:uid="{961E795F-F85E-4E2A-BAED-F63C80C609A5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5726,807 +6650,890 @@
   <sheetData>
     <row r="2" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="29" t="s">
+        <v>240</v>
+      </c>
+      <c r="C4" s="29"/>
+      <c r="D4" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="43"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="U4" s="29"/>
+    </row>
+    <row r="5" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="32"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" s="34"/>
+      <c r="I5" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="J5" s="35"/>
+      <c r="K5" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U5" s="28"/>
+    </row>
+    <row r="6" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B6" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C6" s="30"/>
+      <c r="D6" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="32"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" s="37"/>
+      <c r="I6" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="J6" s="35"/>
+      <c r="K6" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U6" s="28"/>
+    </row>
+    <row r="7" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="30"/>
+      <c r="D7" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="32"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="34"/>
+      <c r="I7" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="J7" s="35"/>
+      <c r="K7" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
+      <c r="S7" s="36"/>
+      <c r="T7" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U7" s="28"/>
+    </row>
+    <row r="8" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="C8" s="30"/>
+      <c r="D8" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="32"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8" s="34"/>
+      <c r="I8" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="J8" s="35"/>
+      <c r="K8" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="L8" s="36"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
+      <c r="S8" s="36"/>
+      <c r="T8" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U8" s="28"/>
+    </row>
+    <row r="9" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" s="30"/>
+      <c r="D9" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="32"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="34"/>
+      <c r="I9" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" s="35"/>
+      <c r="K9" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
+      <c r="S9" s="36"/>
+      <c r="T9" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U9" s="28"/>
+    </row>
+    <row r="10" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="C10" s="30"/>
+      <c r="D10" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="32"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="34"/>
+      <c r="I10" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="J10" s="35"/>
+      <c r="K10" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="36"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
+      <c r="S10" s="36"/>
+      <c r="T10" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U10" s="28"/>
+    </row>
+    <row r="11" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="30"/>
+      <c r="D11" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="32"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="34"/>
+      <c r="I11" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="J11" s="35"/>
+      <c r="K11" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="L11" s="36"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
+      <c r="S11" s="36"/>
+      <c r="T11" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U11" s="28"/>
+    </row>
+    <row r="12" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="C4" s="39"/>
-      <c r="D4" s="51" t="s">
+      <c r="C12" s="30"/>
+      <c r="D12" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39" t="s">
+      <c r="E12" s="40"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="34"/>
+      <c r="I12" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="J12" s="35"/>
+      <c r="K12" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
+      <c r="S12" s="36"/>
+      <c r="T12" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="39"/>
-      <c r="S4" s="39"/>
-      <c r="T4" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="U4" s="39"/>
-    </row>
-    <row r="5" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="49" t="s">
+      <c r="U12" s="28"/>
+    </row>
+    <row r="13" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="30" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="49"/>
-      <c r="D5" s="54" t="s">
-        <v>95</v>
-      </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="60" t="s">
+      <c r="C13" s="30"/>
+      <c r="D13" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="32"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H13" s="34"/>
+      <c r="I13" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="H5" s="60"/>
-      <c r="I5" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="J5" s="50"/>
-      <c r="K5" s="62" t="s">
-        <v>96</v>
-      </c>
-      <c r="L5" s="62"/>
-      <c r="M5" s="62"/>
-      <c r="N5" s="62"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="62"/>
-      <c r="Q5" s="62"/>
-      <c r="R5" s="62"/>
-      <c r="S5" s="62"/>
-      <c r="T5" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U5" s="63"/>
-    </row>
-    <row r="6" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B6" s="49" t="s">
+      <c r="J13" s="35"/>
+      <c r="K13" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
+      <c r="S13" s="36"/>
+      <c r="T13" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U13" s="28"/>
+    </row>
+    <row r="14" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="30" t="s">
         <v>188</v>
       </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="54" t="s">
+      <c r="C14" s="30"/>
+      <c r="D14" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" s="32"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="34"/>
+      <c r="I14" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="J14" s="35"/>
+      <c r="K14" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="L14" s="36"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
+      <c r="S14" s="36"/>
+      <c r="T14" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U14" s="28"/>
+    </row>
+    <row r="15" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="C15" s="30"/>
+      <c r="D15" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="E6" s="55"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="61" t="s">
+      <c r="E15" s="32"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="H6" s="61"/>
-      <c r="I6" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="J6" s="50"/>
-      <c r="K6" s="62" t="s">
-        <v>182</v>
-      </c>
-      <c r="L6" s="62"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="62"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="62"/>
-      <c r="T6" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U6" s="63"/>
-    </row>
-    <row r="7" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="55"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="60" t="s">
+      <c r="H15" s="34"/>
+      <c r="I15" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="H7" s="60"/>
-      <c r="I7" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="J7" s="50"/>
-      <c r="K7" s="62" t="s">
-        <v>110</v>
-      </c>
-      <c r="L7" s="62"/>
-      <c r="M7" s="62"/>
-      <c r="N7" s="62"/>
-      <c r="O7" s="62"/>
-      <c r="P7" s="62"/>
-      <c r="Q7" s="62"/>
-      <c r="R7" s="62"/>
-      <c r="S7" s="62"/>
-      <c r="T7" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U7" s="63"/>
-    </row>
-    <row r="8" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="49" t="s">
+      <c r="J15" s="35"/>
+      <c r="K15" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="L15" s="36"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
+      <c r="S15" s="36"/>
+      <c r="T15" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U15" s="28"/>
+    </row>
+    <row r="16" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="30" t="s">
         <v>190</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="55"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="60" t="s">
+      <c r="C16" s="30"/>
+      <c r="D16" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="32"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="34"/>
+      <c r="I16" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="H8" s="60"/>
-      <c r="I8" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="J8" s="50"/>
-      <c r="K8" s="62" t="s">
-        <v>110</v>
-      </c>
-      <c r="L8" s="62"/>
-      <c r="M8" s="62"/>
-      <c r="N8" s="62"/>
-      <c r="O8" s="62"/>
-      <c r="P8" s="62"/>
-      <c r="Q8" s="62"/>
-      <c r="R8" s="62"/>
-      <c r="S8" s="62"/>
-      <c r="T8" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U8" s="63"/>
-    </row>
-    <row r="9" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="C9" s="49"/>
-      <c r="D9" s="54" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="55"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="60" t="s">
+      <c r="J16" s="35"/>
+      <c r="K16" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="L16" s="36"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
+      <c r="S16" s="36"/>
+      <c r="T16" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U16" s="28"/>
+    </row>
+    <row r="17" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B17" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="C17" s="30"/>
+      <c r="D17" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="32"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="37"/>
+      <c r="I17" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="H9" s="60"/>
-      <c r="I9" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="J9" s="50"/>
-      <c r="K9" s="62" t="s">
-        <v>110</v>
-      </c>
-      <c r="L9" s="62"/>
-      <c r="M9" s="62"/>
-      <c r="N9" s="62"/>
-      <c r="O9" s="62"/>
-      <c r="P9" s="62"/>
-      <c r="Q9" s="62"/>
-      <c r="R9" s="62"/>
-      <c r="S9" s="62"/>
-      <c r="T9" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U9" s="63"/>
-    </row>
-    <row r="10" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="49" t="s">
-        <v>192</v>
-      </c>
-      <c r="C10" s="49"/>
-      <c r="D10" s="54" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="55"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="60" t="s">
+      <c r="J17" s="35"/>
+      <c r="K17" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
+      <c r="S17" s="36"/>
+      <c r="T17" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U17" s="28"/>
+    </row>
+    <row r="18" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B18" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="C18" s="30"/>
+      <c r="D18" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="32"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="37"/>
+      <c r="I18" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="H10" s="60"/>
-      <c r="I10" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="J10" s="50"/>
-      <c r="K10" s="62" t="s">
-        <v>110</v>
-      </c>
-      <c r="L10" s="62"/>
-      <c r="M10" s="62"/>
-      <c r="N10" s="62"/>
-      <c r="O10" s="62"/>
-      <c r="P10" s="62"/>
-      <c r="Q10" s="62"/>
-      <c r="R10" s="62"/>
-      <c r="S10" s="62"/>
-      <c r="T10" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U10" s="63"/>
-    </row>
-    <row r="11" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="C11" s="49"/>
-      <c r="D11" s="54" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" s="55"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="60" t="s">
+      <c r="J18" s="35"/>
+      <c r="K18" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
+      <c r="S18" s="36"/>
+      <c r="T18" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U18" s="28"/>
+    </row>
+    <row r="19" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B19" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="C19" s="30"/>
+      <c r="D19" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" s="32"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="37"/>
+      <c r="I19" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="H11" s="60"/>
-      <c r="I11" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="J11" s="50"/>
-      <c r="K11" s="62" t="s">
-        <v>110</v>
-      </c>
-      <c r="L11" s="62"/>
-      <c r="M11" s="62"/>
-      <c r="N11" s="62"/>
-      <c r="O11" s="62"/>
-      <c r="P11" s="62"/>
-      <c r="Q11" s="62"/>
-      <c r="R11" s="62"/>
-      <c r="S11" s="62"/>
-      <c r="T11" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U11" s="63"/>
-    </row>
-    <row r="12" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="C12" s="49"/>
-      <c r="D12" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" s="58"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="60" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="60"/>
-      <c r="I12" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="J12" s="50"/>
-      <c r="K12" s="62" t="s">
+      <c r="J19" s="35"/>
+      <c r="K19" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="L12" s="62"/>
-      <c r="M12" s="62"/>
-      <c r="N12" s="62"/>
-      <c r="O12" s="62"/>
-      <c r="P12" s="62"/>
-      <c r="Q12" s="62"/>
-      <c r="R12" s="62"/>
-      <c r="S12" s="62"/>
-      <c r="T12" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U12" s="63"/>
-    </row>
-    <row r="13" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B13" s="49" t="s">
-        <v>195</v>
-      </c>
-      <c r="C13" s="49"/>
-      <c r="D13" s="54" t="s">
-        <v>99</v>
-      </c>
-      <c r="E13" s="55"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="60" t="s">
-        <v>93</v>
-      </c>
-      <c r="H13" s="60"/>
-      <c r="I13" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="J13" s="50"/>
-      <c r="K13" s="62" t="s">
+      <c r="L19" s="36"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
+      <c r="S19" s="36"/>
+      <c r="T19" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U19" s="28"/>
+    </row>
+    <row r="20" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B20" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="C20" s="30"/>
+      <c r="D20" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="32"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="37"/>
+      <c r="I20" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="38"/>
+      <c r="K20" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="L13" s="62"/>
-      <c r="M13" s="62"/>
-      <c r="N13" s="62"/>
-      <c r="O13" s="62"/>
-      <c r="P13" s="62"/>
-      <c r="Q13" s="62"/>
-      <c r="R13" s="62"/>
-      <c r="S13" s="62"/>
-      <c r="T13" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U13" s="63"/>
-    </row>
-    <row r="14" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="49" t="s">
-        <v>196</v>
-      </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="54" t="s">
-        <v>117</v>
-      </c>
-      <c r="E14" s="55"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="60" t="s">
-        <v>93</v>
-      </c>
-      <c r="H14" s="60"/>
-      <c r="I14" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="J14" s="50"/>
-      <c r="K14" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="L14" s="62"/>
-      <c r="M14" s="62"/>
-      <c r="N14" s="62"/>
-      <c r="O14" s="62"/>
-      <c r="P14" s="62"/>
-      <c r="Q14" s="62"/>
-      <c r="R14" s="62"/>
-      <c r="S14" s="62"/>
-      <c r="T14" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U14" s="63"/>
-    </row>
-    <row r="15" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="54" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" s="55"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="60" t="s">
-        <v>93</v>
-      </c>
-      <c r="H15" s="60"/>
-      <c r="I15" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="J15" s="50"/>
-      <c r="K15" s="62" t="s">
-        <v>119</v>
-      </c>
-      <c r="L15" s="62"/>
-      <c r="M15" s="62"/>
-      <c r="N15" s="62"/>
-      <c r="O15" s="62"/>
-      <c r="P15" s="62"/>
-      <c r="Q15" s="62"/>
-      <c r="R15" s="62"/>
-      <c r="S15" s="62"/>
-      <c r="T15" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U15" s="63"/>
-    </row>
-    <row r="16" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="C16" s="49"/>
-      <c r="D16" s="54" t="s">
-        <v>116</v>
-      </c>
-      <c r="E16" s="55"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="60" t="s">
-        <v>93</v>
-      </c>
-      <c r="H16" s="60"/>
-      <c r="I16" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="J16" s="50"/>
-      <c r="K16" s="62" t="s">
-        <v>119</v>
-      </c>
-      <c r="L16" s="62"/>
-      <c r="M16" s="62"/>
-      <c r="N16" s="62"/>
-      <c r="O16" s="62"/>
-      <c r="P16" s="62"/>
-      <c r="Q16" s="62"/>
-      <c r="R16" s="62"/>
-      <c r="S16" s="62"/>
-      <c r="T16" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U16" s="63"/>
-    </row>
-    <row r="17" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B17" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="C17" s="49"/>
-      <c r="D17" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="E17" s="55"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="61" t="s">
-        <v>92</v>
-      </c>
-      <c r="H17" s="61"/>
-      <c r="I17" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="J17" s="50"/>
-      <c r="K17" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="L17" s="62"/>
-      <c r="M17" s="62"/>
-      <c r="N17" s="62"/>
-      <c r="O17" s="62"/>
-      <c r="P17" s="62"/>
-      <c r="Q17" s="62"/>
-      <c r="R17" s="62"/>
-      <c r="S17" s="62"/>
-      <c r="T17" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U17" s="63"/>
-    </row>
-    <row r="18" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B18" s="49" t="s">
+      <c r="L20" s="36"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
+      <c r="S20" s="36"/>
+      <c r="T20" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U20" s="28"/>
+    </row>
+    <row r="21" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B21" s="30" t="s">
         <v>200</v>
       </c>
-      <c r="C18" s="49"/>
-      <c r="D18" s="54" t="s">
+      <c r="C21" s="30"/>
+      <c r="D21" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="32"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" s="37"/>
+      <c r="I21" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="38"/>
+      <c r="K21" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="L21" s="36"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
+      <c r="S21" s="36"/>
+      <c r="T21" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U21" s="28"/>
+    </row>
+    <row r="22" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B22" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="C22" s="30"/>
+      <c r="D22" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="32"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="37"/>
+      <c r="I22" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="38"/>
+      <c r="K22" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
+      <c r="S22" s="36"/>
+      <c r="T22" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U22" s="28"/>
+    </row>
+    <row r="23" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B23" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="C23" s="30"/>
+      <c r="D23" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="32"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="H23" s="37"/>
+      <c r="I23" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="38"/>
+      <c r="K23" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="L23" s="36"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="36"/>
+      <c r="O23" s="36"/>
+      <c r="P23" s="36"/>
+      <c r="Q23" s="36"/>
+      <c r="R23" s="36"/>
+      <c r="S23" s="36"/>
+      <c r="T23" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U23" s="28"/>
+    </row>
+    <row r="24" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B24" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="C24" s="30"/>
+      <c r="D24" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" s="32"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="H24" s="37"/>
+      <c r="I24" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="38"/>
+      <c r="K24" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="L24" s="36"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="36"/>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="36"/>
+      <c r="R24" s="36"/>
+      <c r="S24" s="36"/>
+      <c r="T24" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U24" s="28"/>
+    </row>
+    <row r="25" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B25" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="C25" s="30"/>
+      <c r="D25" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="E25" s="32"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25" s="37"/>
+      <c r="I25" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="38"/>
+      <c r="K25" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="L25" s="36"/>
+      <c r="M25" s="36"/>
+      <c r="N25" s="36"/>
+      <c r="O25" s="36"/>
+      <c r="P25" s="36"/>
+      <c r="Q25" s="36"/>
+      <c r="R25" s="36"/>
+      <c r="S25" s="36"/>
+      <c r="T25" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U25" s="28"/>
+    </row>
+    <row r="26" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B26" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C26" s="30"/>
+      <c r="D26" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="E18" s="55"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="61" t="s">
-        <v>92</v>
-      </c>
-      <c r="H18" s="61"/>
-      <c r="I18" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="J18" s="50"/>
-      <c r="K18" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="L18" s="62"/>
-      <c r="M18" s="62"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="62"/>
-      <c r="P18" s="62"/>
-      <c r="Q18" s="62"/>
-      <c r="R18" s="62"/>
-      <c r="S18" s="62"/>
-      <c r="T18" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U18" s="63"/>
-    </row>
-    <row r="19" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B19" s="49" t="s">
-        <v>201</v>
-      </c>
-      <c r="C19" s="49"/>
-      <c r="D19" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" s="55"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="61" t="s">
-        <v>92</v>
-      </c>
-      <c r="H19" s="61"/>
-      <c r="I19" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="J19" s="50"/>
-      <c r="K19" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="L19" s="62"/>
-      <c r="M19" s="62"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="62"/>
-      <c r="P19" s="62"/>
-      <c r="Q19" s="62"/>
-      <c r="R19" s="62"/>
-      <c r="S19" s="62"/>
-      <c r="T19" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U19" s="63"/>
-    </row>
-    <row r="20" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B20" s="49" t="s">
-        <v>202</v>
-      </c>
-      <c r="C20" s="49"/>
-      <c r="D20" s="54" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" s="55"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="61" t="s">
-        <v>92</v>
-      </c>
-      <c r="H20" s="61"/>
-      <c r="I20" s="64" t="s">
+      <c r="E26" s="32"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="H26" s="37"/>
+      <c r="I26" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="J20" s="64"/>
-      <c r="K20" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="L20" s="62"/>
-      <c r="M20" s="62"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="62"/>
-      <c r="P20" s="62"/>
-      <c r="Q20" s="62"/>
-      <c r="R20" s="62"/>
-      <c r="S20" s="62"/>
-      <c r="T20" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U20" s="63"/>
-    </row>
-    <row r="21" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B21" s="49" t="s">
-        <v>203</v>
-      </c>
-      <c r="C21" s="49"/>
-      <c r="D21" s="54" t="s">
-        <v>105</v>
-      </c>
-      <c r="E21" s="55"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="61" t="s">
-        <v>92</v>
-      </c>
-      <c r="H21" s="61"/>
-      <c r="I21" s="64" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="64"/>
-      <c r="K21" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="L21" s="62"/>
-      <c r="M21" s="62"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="62"/>
-      <c r="P21" s="62"/>
-      <c r="Q21" s="62"/>
-      <c r="R21" s="62"/>
-      <c r="S21" s="62"/>
-      <c r="T21" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U21" s="63"/>
-    </row>
-    <row r="22" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B22" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="C22" s="49"/>
-      <c r="D22" s="54" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" s="55"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="61" t="s">
-        <v>92</v>
-      </c>
-      <c r="H22" s="61"/>
-      <c r="I22" s="64" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="64"/>
-      <c r="K22" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="L22" s="62"/>
-      <c r="M22" s="62"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="62"/>
-      <c r="P22" s="62"/>
-      <c r="Q22" s="62"/>
-      <c r="R22" s="62"/>
-      <c r="S22" s="62"/>
-      <c r="T22" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U22" s="63"/>
-    </row>
-    <row r="23" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B23" s="49" t="s">
-        <v>205</v>
-      </c>
-      <c r="C23" s="49"/>
-      <c r="D23" s="54" t="s">
-        <v>107</v>
-      </c>
-      <c r="E23" s="55"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="61" t="s">
-        <v>92</v>
-      </c>
-      <c r="H23" s="61"/>
-      <c r="I23" s="64" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="64"/>
-      <c r="K23" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="L23" s="62"/>
-      <c r="M23" s="62"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="62"/>
-      <c r="P23" s="62"/>
-      <c r="Q23" s="62"/>
-      <c r="R23" s="62"/>
-      <c r="S23" s="62"/>
-      <c r="T23" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U23" s="63"/>
-    </row>
-    <row r="24" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B24" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="C24" s="49"/>
-      <c r="D24" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="E24" s="55"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="61" t="s">
-        <v>92</v>
-      </c>
-      <c r="H24" s="61"/>
-      <c r="I24" s="64" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="64"/>
-      <c r="K24" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="L24" s="62"/>
-      <c r="M24" s="62"/>
-      <c r="N24" s="62"/>
-      <c r="O24" s="62"/>
-      <c r="P24" s="62"/>
-      <c r="Q24" s="62"/>
-      <c r="R24" s="62"/>
-      <c r="S24" s="62"/>
-      <c r="T24" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U24" s="63"/>
-    </row>
-    <row r="25" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B25" s="49" t="s">
-        <v>207</v>
-      </c>
-      <c r="C25" s="49"/>
-      <c r="D25" s="54" t="s">
-        <v>109</v>
-      </c>
-      <c r="E25" s="55"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="61" t="s">
-        <v>92</v>
-      </c>
-      <c r="H25" s="61"/>
-      <c r="I25" s="64" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="64"/>
-      <c r="K25" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="L25" s="62"/>
-      <c r="M25" s="62"/>
-      <c r="N25" s="62"/>
-      <c r="O25" s="62"/>
-      <c r="P25" s="62"/>
-      <c r="Q25" s="62"/>
-      <c r="R25" s="62"/>
-      <c r="S25" s="62"/>
-      <c r="T25" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U25" s="63"/>
-    </row>
-    <row r="26" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B26" s="49" t="s">
-        <v>208</v>
-      </c>
-      <c r="C26" s="49"/>
-      <c r="D26" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="E26" s="55"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="61" t="s">
-        <v>92</v>
-      </c>
-      <c r="H26" s="61"/>
-      <c r="I26" s="64" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="64"/>
-      <c r="K26" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="L26" s="62"/>
-      <c r="M26" s="62"/>
-      <c r="N26" s="62"/>
-      <c r="O26" s="62"/>
-      <c r="P26" s="62"/>
-      <c r="Q26" s="62"/>
-      <c r="R26" s="62"/>
-      <c r="S26" s="62"/>
-      <c r="T26" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="U26" s="63"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="L26" s="36"/>
+      <c r="M26" s="36"/>
+      <c r="N26" s="36"/>
+      <c r="O26" s="36"/>
+      <c r="P26" s="36"/>
+      <c r="Q26" s="36"/>
+      <c r="R26" s="36"/>
+      <c r="S26" s="36"/>
+      <c r="T26" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="U26" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="138">
-    <mergeCell ref="T24:U24"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="T26:U26"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K26:S26"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K4:S4"/>
+    <mergeCell ref="K5:S5"/>
+    <mergeCell ref="K7:S7"/>
+    <mergeCell ref="K8:S8"/>
+    <mergeCell ref="K9:S9"/>
+    <mergeCell ref="K10:S10"/>
+    <mergeCell ref="K11:S11"/>
+    <mergeCell ref="K12:S12"/>
+    <mergeCell ref="K13:S13"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:S6"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:S25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K24:S24"/>
+    <mergeCell ref="K19:S19"/>
+    <mergeCell ref="K20:S20"/>
+    <mergeCell ref="K21:S21"/>
+    <mergeCell ref="K22:S22"/>
+    <mergeCell ref="K23:S23"/>
+    <mergeCell ref="K17:S17"/>
+    <mergeCell ref="K18:S18"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="T4:U4"/>
     <mergeCell ref="T5:U5"/>
     <mergeCell ref="T6:U6"/>
@@ -6551,108 +7558,25 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:S6"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:S25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:S24"/>
-    <mergeCell ref="K19:S19"/>
-    <mergeCell ref="K20:S20"/>
-    <mergeCell ref="K21:S21"/>
-    <mergeCell ref="K22:S22"/>
-    <mergeCell ref="K23:S23"/>
-    <mergeCell ref="K4:S4"/>
-    <mergeCell ref="K5:S5"/>
-    <mergeCell ref="K7:S7"/>
-    <mergeCell ref="K8:S8"/>
-    <mergeCell ref="K9:S9"/>
-    <mergeCell ref="K10:S10"/>
-    <mergeCell ref="K11:S11"/>
-    <mergeCell ref="K12:S12"/>
-    <mergeCell ref="K13:S13"/>
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="T26:U26"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="T15:U15"/>
     <mergeCell ref="T16:U16"/>
     <mergeCell ref="T17:U17"/>
     <mergeCell ref="T18:U18"/>
-    <mergeCell ref="K17:S17"/>
-    <mergeCell ref="K18:S18"/>
-    <mergeCell ref="K26:S26"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="D4:F4"/>
   </mergeCells>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:J26" xr:uid="{EBCDB7CB-9B76-4496-A9FD-E13B8548471C}">
       <formula1>"Yes,No"</formula1>
@@ -6670,15 +7594,1007 @@
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A2"/>
+  <dimension ref="A2:AB67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:1" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>183</v>
-      </c>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B4" s="8" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P10" s="76" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="21" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P21" s="76" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="22" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P22" s="91" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="24" spans="2:28" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P24" s="77" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q24" s="77"/>
+      <c r="R24" s="77"/>
+      <c r="S24" s="77"/>
+      <c r="T24" s="77"/>
+      <c r="U24" s="77"/>
+      <c r="V24" s="77"/>
+      <c r="W24" s="77"/>
+      <c r="X24" s="77"/>
+      <c r="Y24" s="77"/>
+      <c r="Z24" s="77"/>
+      <c r="AA24" s="77"/>
+      <c r="AB24" s="77"/>
+    </row>
+    <row r="26" spans="2:28" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P26" s="77" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q26" s="77"/>
+      <c r="R26" s="77"/>
+      <c r="S26" s="77"/>
+      <c r="T26" s="77"/>
+      <c r="U26" s="77"/>
+      <c r="V26" s="77"/>
+      <c r="W26" s="77"/>
+      <c r="X26" s="77"/>
+      <c r="Y26" s="77"/>
+      <c r="Z26" s="77"/>
+      <c r="AA26" s="77"/>
+      <c r="AB26" s="77"/>
+    </row>
+    <row r="27" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="30" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="8"/>
+    </row>
+    <row r="31" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B31" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="32" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B32" s="8" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B33" s="8" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="77" t="s">
+        <v>217</v>
+      </c>
+      <c r="C35" s="77"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
+      <c r="I35" s="77"/>
+      <c r="J35" s="77"/>
+      <c r="K35" s="77"/>
+      <c r="L35" s="77"/>
+      <c r="M35" s="77"/>
+      <c r="N35" s="77"/>
+      <c r="O35" s="77"/>
+      <c r="P35" s="77"/>
+      <c r="Q35" s="77"/>
+      <c r="R35" s="77"/>
+      <c r="S35" s="77"/>
+      <c r="T35" s="77"/>
+      <c r="U35" s="77"/>
+      <c r="V35" s="77"/>
+      <c r="W35" s="77"/>
+      <c r="X35" s="77"/>
+      <c r="Y35" s="77"/>
+      <c r="Z35" s="77"/>
+      <c r="AA35" s="77"/>
+      <c r="AB35" s="77"/>
+    </row>
+    <row r="36" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="77" t="s">
+        <v>216</v>
+      </c>
+      <c r="C36" s="77"/>
+      <c r="D36" s="77"/>
+      <c r="E36" s="77"/>
+      <c r="F36" s="77"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
+      <c r="I36" s="77"/>
+      <c r="J36" s="77"/>
+      <c r="K36" s="77"/>
+      <c r="L36" s="77"/>
+      <c r="M36" s="77"/>
+      <c r="N36" s="77"/>
+      <c r="O36" s="77"/>
+      <c r="P36" s="77"/>
+      <c r="Q36" s="77"/>
+      <c r="R36" s="77"/>
+      <c r="S36" s="77"/>
+      <c r="T36" s="77"/>
+      <c r="U36" s="77"/>
+      <c r="V36" s="77"/>
+      <c r="W36" s="77"/>
+      <c r="X36" s="77"/>
+      <c r="Y36" s="77"/>
+      <c r="Z36" s="77"/>
+      <c r="AA36" s="77"/>
+      <c r="AB36" s="77"/>
+    </row>
+    <row r="37" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="77" t="s">
+        <v>219</v>
+      </c>
+      <c r="C37" s="77"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
+      <c r="I37" s="77"/>
+      <c r="J37" s="77"/>
+      <c r="K37" s="77"/>
+      <c r="L37" s="77"/>
+      <c r="M37" s="77"/>
+      <c r="N37" s="77"/>
+      <c r="O37" s="77"/>
+      <c r="P37" s="77"/>
+      <c r="Q37" s="77"/>
+      <c r="R37" s="77"/>
+      <c r="S37" s="77"/>
+      <c r="T37" s="77"/>
+      <c r="U37" s="77"/>
+      <c r="V37" s="77"/>
+      <c r="W37" s="77"/>
+      <c r="X37" s="77"/>
+      <c r="Y37" s="77"/>
+      <c r="Z37" s="77"/>
+      <c r="AA37" s="77"/>
+      <c r="AB37" s="77"/>
+    </row>
+    <row r="38" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="77" t="s">
+        <v>218</v>
+      </c>
+      <c r="C38" s="77"/>
+      <c r="D38" s="77"/>
+      <c r="E38" s="77"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
+      <c r="I38" s="77"/>
+      <c r="J38" s="77"/>
+      <c r="K38" s="77"/>
+      <c r="L38" s="77"/>
+      <c r="M38" s="77"/>
+      <c r="N38" s="77"/>
+      <c r="O38" s="77"/>
+      <c r="P38" s="77"/>
+      <c r="Q38" s="77"/>
+      <c r="R38" s="77"/>
+      <c r="S38" s="77"/>
+      <c r="T38" s="77"/>
+      <c r="U38" s="77"/>
+      <c r="V38" s="77"/>
+      <c r="W38" s="77"/>
+      <c r="X38" s="77"/>
+      <c r="Y38" s="77"/>
+      <c r="Z38" s="77"/>
+      <c r="AA38" s="77"/>
+      <c r="AB38" s="77"/>
+    </row>
+    <row r="39" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="77" t="s">
+        <v>220</v>
+      </c>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
+      <c r="I39" s="77"/>
+      <c r="J39" s="77"/>
+      <c r="K39" s="77"/>
+      <c r="L39" s="77"/>
+      <c r="M39" s="77"/>
+      <c r="N39" s="77"/>
+      <c r="O39" s="77"/>
+      <c r="P39" s="77"/>
+      <c r="Q39" s="77"/>
+      <c r="R39" s="77"/>
+      <c r="S39" s="77"/>
+      <c r="T39" s="77"/>
+      <c r="U39" s="77"/>
+      <c r="V39" s="77"/>
+      <c r="W39" s="77"/>
+      <c r="X39" s="77"/>
+      <c r="Y39" s="77"/>
+      <c r="Z39" s="77"/>
+      <c r="AA39" s="77"/>
+      <c r="AB39" s="77"/>
+    </row>
+    <row r="41" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="77" t="s">
+        <v>221</v>
+      </c>
+      <c r="C41" s="77"/>
+      <c r="D41" s="77"/>
+      <c r="E41" s="77"/>
+      <c r="F41" s="77"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="77"/>
+      <c r="I41" s="77"/>
+      <c r="J41" s="77"/>
+      <c r="K41" s="77"/>
+      <c r="L41" s="77"/>
+      <c r="M41" s="77"/>
+      <c r="N41" s="77"/>
+      <c r="O41" s="77"/>
+      <c r="P41" s="77"/>
+      <c r="Q41" s="77"/>
+      <c r="R41" s="77"/>
+      <c r="S41" s="77"/>
+      <c r="T41" s="77"/>
+      <c r="U41" s="77"/>
+      <c r="V41" s="77"/>
+      <c r="W41" s="77"/>
+      <c r="X41" s="77"/>
+      <c r="Y41" s="77"/>
+      <c r="Z41" s="77"/>
+      <c r="AA41" s="77"/>
+      <c r="AB41" s="77"/>
+    </row>
+    <row r="42" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B42" s="77" t="s">
+        <v>222</v>
+      </c>
+      <c r="C42" s="77"/>
+      <c r="D42" s="77"/>
+      <c r="E42" s="77"/>
+      <c r="F42" s="77"/>
+      <c r="G42" s="77"/>
+      <c r="H42" s="77"/>
+      <c r="I42" s="77"/>
+      <c r="J42" s="77"/>
+      <c r="K42" s="77"/>
+      <c r="L42" s="77"/>
+      <c r="M42" s="77"/>
+      <c r="N42" s="77"/>
+      <c r="O42" s="77"/>
+      <c r="P42" s="77"/>
+      <c r="Q42" s="77"/>
+      <c r="R42" s="77"/>
+      <c r="S42" s="77"/>
+      <c r="T42" s="77"/>
+      <c r="U42" s="77"/>
+      <c r="V42" s="77"/>
+      <c r="W42" s="77"/>
+      <c r="X42" s="77"/>
+      <c r="Y42" s="77"/>
+      <c r="Z42" s="77"/>
+      <c r="AA42" s="77"/>
+      <c r="AB42" s="77"/>
+    </row>
+    <row r="43" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B43" s="77" t="s">
+        <v>223</v>
+      </c>
+      <c r="C43" s="77"/>
+      <c r="D43" s="77"/>
+      <c r="E43" s="77"/>
+      <c r="F43" s="77"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="77"/>
+      <c r="I43" s="77"/>
+      <c r="J43" s="77"/>
+      <c r="K43" s="77"/>
+      <c r="L43" s="77"/>
+      <c r="M43" s="77"/>
+      <c r="N43" s="77"/>
+      <c r="O43" s="77"/>
+      <c r="P43" s="77"/>
+      <c r="Q43" s="77"/>
+      <c r="R43" s="77"/>
+      <c r="S43" s="77"/>
+      <c r="T43" s="77"/>
+      <c r="U43" s="77"/>
+      <c r="V43" s="77"/>
+      <c r="W43" s="77"/>
+      <c r="X43" s="77"/>
+      <c r="Y43" s="77"/>
+      <c r="Z43" s="77"/>
+      <c r="AA43" s="77"/>
+      <c r="AB43" s="77"/>
+    </row>
+    <row r="44" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B44" s="77" t="s">
+        <v>224</v>
+      </c>
+      <c r="C44" s="77"/>
+      <c r="D44" s="77"/>
+      <c r="E44" s="77"/>
+      <c r="F44" s="77"/>
+      <c r="G44" s="77"/>
+      <c r="H44" s="77"/>
+      <c r="I44" s="77"/>
+      <c r="J44" s="77"/>
+      <c r="K44" s="77"/>
+      <c r="L44" s="77"/>
+      <c r="M44" s="77"/>
+      <c r="N44" s="77"/>
+      <c r="O44" s="77"/>
+      <c r="P44" s="77"/>
+      <c r="Q44" s="77"/>
+      <c r="R44" s="77"/>
+      <c r="S44" s="77"/>
+      <c r="T44" s="77"/>
+      <c r="U44" s="77"/>
+      <c r="V44" s="77"/>
+      <c r="W44" s="77"/>
+      <c r="X44" s="77"/>
+      <c r="Y44" s="77"/>
+      <c r="Z44" s="77"/>
+      <c r="AA44" s="77"/>
+      <c r="AB44" s="77"/>
+    </row>
+    <row r="45" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B45" s="77" t="s">
+        <v>225</v>
+      </c>
+      <c r="C45" s="77"/>
+      <c r="D45" s="77"/>
+      <c r="E45" s="77"/>
+      <c r="F45" s="77"/>
+      <c r="G45" s="77"/>
+      <c r="H45" s="77"/>
+      <c r="I45" s="77"/>
+      <c r="J45" s="77"/>
+      <c r="K45" s="77"/>
+      <c r="L45" s="77"/>
+      <c r="M45" s="77"/>
+      <c r="N45" s="77"/>
+      <c r="O45" s="77"/>
+      <c r="P45" s="77"/>
+      <c r="Q45" s="77"/>
+      <c r="R45" s="77"/>
+      <c r="S45" s="77"/>
+      <c r="T45" s="77"/>
+      <c r="U45" s="77"/>
+      <c r="V45" s="77"/>
+      <c r="W45" s="77"/>
+      <c r="X45" s="77"/>
+      <c r="Y45" s="77"/>
+      <c r="Z45" s="77"/>
+      <c r="AA45" s="77"/>
+      <c r="AB45" s="77"/>
+    </row>
+    <row r="46" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B46" s="77" t="s">
+        <v>226</v>
+      </c>
+      <c r="C46" s="77"/>
+      <c r="D46" s="77"/>
+      <c r="E46" s="77"/>
+      <c r="F46" s="77"/>
+      <c r="G46" s="77"/>
+      <c r="H46" s="77"/>
+      <c r="I46" s="77"/>
+      <c r="J46" s="77"/>
+      <c r="K46" s="77"/>
+      <c r="L46" s="77"/>
+      <c r="M46" s="77"/>
+      <c r="N46" s="77"/>
+      <c r="O46" s="77"/>
+      <c r="P46" s="77"/>
+      <c r="Q46" s="77"/>
+      <c r="R46" s="77"/>
+      <c r="S46" s="77"/>
+      <c r="T46" s="77"/>
+      <c r="U46" s="77"/>
+      <c r="V46" s="77"/>
+      <c r="W46" s="77"/>
+      <c r="X46" s="77"/>
+      <c r="Y46" s="77"/>
+      <c r="Z46" s="77"/>
+      <c r="AA46" s="77"/>
+      <c r="AB46" s="77"/>
+    </row>
+    <row r="47" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B47" s="77" t="s">
+        <v>228</v>
+      </c>
+      <c r="C47" s="77"/>
+      <c r="D47" s="77"/>
+      <c r="E47" s="77"/>
+      <c r="F47" s="77"/>
+      <c r="G47" s="77"/>
+      <c r="H47" s="77"/>
+      <c r="I47" s="77"/>
+      <c r="J47" s="77"/>
+      <c r="K47" s="77"/>
+      <c r="L47" s="77"/>
+      <c r="M47" s="77"/>
+      <c r="N47" s="77"/>
+      <c r="O47" s="77"/>
+      <c r="P47" s="77"/>
+      <c r="Q47" s="77"/>
+      <c r="R47" s="77"/>
+      <c r="S47" s="77"/>
+      <c r="T47" s="77"/>
+      <c r="U47" s="77"/>
+      <c r="V47" s="77"/>
+      <c r="W47" s="77"/>
+      <c r="X47" s="77"/>
+      <c r="Y47" s="77"/>
+      <c r="Z47" s="77"/>
+      <c r="AA47" s="77"/>
+      <c r="AB47" s="77"/>
+    </row>
+    <row r="48" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B48" s="77" t="s">
+        <v>229</v>
+      </c>
+      <c r="C48" s="77"/>
+      <c r="D48" s="77"/>
+      <c r="E48" s="77"/>
+      <c r="F48" s="77"/>
+      <c r="G48" s="77"/>
+      <c r="H48" s="77"/>
+      <c r="I48" s="77"/>
+      <c r="J48" s="77"/>
+      <c r="K48" s="77"/>
+      <c r="L48" s="77"/>
+      <c r="M48" s="77"/>
+      <c r="N48" s="77"/>
+      <c r="O48" s="77"/>
+      <c r="P48" s="77"/>
+      <c r="Q48" s="77"/>
+      <c r="R48" s="77"/>
+      <c r="S48" s="77"/>
+      <c r="T48" s="77"/>
+      <c r="U48" s="77"/>
+      <c r="V48" s="77"/>
+      <c r="W48" s="77"/>
+      <c r="X48" s="77"/>
+      <c r="Y48" s="77"/>
+      <c r="Z48" s="77"/>
+      <c r="AA48" s="77"/>
+      <c r="AB48" s="77"/>
+    </row>
+    <row r="49" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B49" s="77" t="s">
+        <v>231</v>
+      </c>
+      <c r="C49" s="77"/>
+      <c r="D49" s="77"/>
+      <c r="E49" s="77"/>
+      <c r="F49" s="77"/>
+      <c r="G49" s="77"/>
+      <c r="H49" s="77"/>
+      <c r="I49" s="77"/>
+      <c r="J49" s="77"/>
+      <c r="K49" s="77"/>
+      <c r="L49" s="77"/>
+      <c r="M49" s="77"/>
+      <c r="N49" s="77"/>
+      <c r="O49" s="77"/>
+      <c r="P49" s="77"/>
+      <c r="Q49" s="77"/>
+      <c r="R49" s="77"/>
+      <c r="S49" s="77"/>
+      <c r="T49" s="77"/>
+      <c r="U49" s="77"/>
+      <c r="V49" s="77"/>
+      <c r="W49" s="77"/>
+      <c r="X49" s="77"/>
+      <c r="Y49" s="77"/>
+      <c r="Z49" s="77"/>
+      <c r="AA49" s="77"/>
+      <c r="AB49" s="77"/>
+    </row>
+    <row r="50" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B50" s="77" t="s">
+        <v>230</v>
+      </c>
+      <c r="C50" s="77"/>
+      <c r="D50" s="77"/>
+      <c r="E50" s="77"/>
+      <c r="F50" s="77"/>
+      <c r="G50" s="77"/>
+      <c r="H50" s="77"/>
+      <c r="I50" s="77"/>
+      <c r="J50" s="77"/>
+      <c r="K50" s="77"/>
+      <c r="L50" s="77"/>
+      <c r="M50" s="77"/>
+      <c r="N50" s="77"/>
+      <c r="O50" s="77"/>
+      <c r="P50" s="77"/>
+      <c r="Q50" s="77"/>
+      <c r="R50" s="77"/>
+      <c r="S50" s="77"/>
+      <c r="T50" s="77"/>
+      <c r="U50" s="77"/>
+      <c r="V50" s="77"/>
+      <c r="W50" s="77"/>
+      <c r="X50" s="77"/>
+      <c r="Y50" s="77"/>
+      <c r="Z50" s="77"/>
+      <c r="AA50" s="77"/>
+      <c r="AB50" s="77"/>
+    </row>
+    <row r="51" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B51" s="77" t="s">
+        <v>232</v>
+      </c>
+      <c r="C51" s="77"/>
+      <c r="D51" s="77"/>
+      <c r="E51" s="77"/>
+      <c r="F51" s="77"/>
+      <c r="G51" s="77"/>
+      <c r="H51" s="77"/>
+      <c r="I51" s="77"/>
+      <c r="J51" s="77"/>
+      <c r="K51" s="77"/>
+      <c r="L51" s="77"/>
+      <c r="M51" s="77"/>
+      <c r="N51" s="77"/>
+      <c r="O51" s="77"/>
+      <c r="P51" s="77"/>
+      <c r="Q51" s="77"/>
+      <c r="R51" s="77"/>
+      <c r="S51" s="77"/>
+      <c r="T51" s="77"/>
+      <c r="U51" s="77"/>
+      <c r="V51" s="77"/>
+      <c r="W51" s="77"/>
+      <c r="X51" s="77"/>
+      <c r="Y51" s="77"/>
+      <c r="Z51" s="77"/>
+      <c r="AA51" s="77"/>
+      <c r="AB51" s="77"/>
+    </row>
+    <row r="52" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B52" s="77" t="s">
+        <v>233</v>
+      </c>
+      <c r="C52" s="77"/>
+      <c r="D52" s="77"/>
+      <c r="E52" s="77"/>
+      <c r="F52" s="77"/>
+      <c r="G52" s="77"/>
+      <c r="H52" s="77"/>
+      <c r="I52" s="77"/>
+      <c r="J52" s="77"/>
+      <c r="K52" s="77"/>
+      <c r="L52" s="77"/>
+      <c r="M52" s="77"/>
+      <c r="N52" s="77"/>
+      <c r="O52" s="77"/>
+      <c r="P52" s="77"/>
+      <c r="Q52" s="77"/>
+      <c r="R52" s="77"/>
+      <c r="S52" s="77"/>
+      <c r="T52" s="77"/>
+      <c r="U52" s="77"/>
+      <c r="V52" s="77"/>
+      <c r="W52" s="77"/>
+      <c r="X52" s="77"/>
+      <c r="Y52" s="77"/>
+      <c r="Z52" s="77"/>
+      <c r="AA52" s="77"/>
+      <c r="AB52" s="77"/>
+    </row>
+    <row r="53" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B53" s="77" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="77"/>
+      <c r="D53" s="77"/>
+      <c r="E53" s="77"/>
+      <c r="F53" s="77"/>
+      <c r="G53" s="77"/>
+      <c r="H53" s="77"/>
+      <c r="I53" s="77"/>
+      <c r="J53" s="77"/>
+      <c r="K53" s="77"/>
+      <c r="L53" s="77"/>
+      <c r="M53" s="77"/>
+      <c r="N53" s="77"/>
+      <c r="O53" s="77"/>
+      <c r="P53" s="77"/>
+      <c r="Q53" s="77"/>
+      <c r="R53" s="77"/>
+      <c r="S53" s="77"/>
+      <c r="T53" s="77"/>
+      <c r="U53" s="77"/>
+      <c r="V53" s="77"/>
+      <c r="W53" s="77"/>
+      <c r="X53" s="77"/>
+      <c r="Y53" s="77"/>
+      <c r="Z53" s="77"/>
+      <c r="AA53" s="77"/>
+      <c r="AB53" s="77"/>
+    </row>
+    <row r="55" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B55" s="8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="56" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B56" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="57" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B57" s="8"/>
+    </row>
+    <row r="58" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B58" s="77" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="77"/>
+      <c r="D58" s="77"/>
+      <c r="E58" s="77"/>
+      <c r="F58" s="77"/>
+      <c r="G58" s="77"/>
+      <c r="H58" s="77"/>
+      <c r="I58" s="77"/>
+      <c r="J58" s="77"/>
+      <c r="K58" s="77"/>
+      <c r="L58" s="77"/>
+      <c r="M58" s="77"/>
+      <c r="N58" s="77"/>
+      <c r="O58" s="77"/>
+      <c r="P58" s="77"/>
+      <c r="Q58" s="77"/>
+      <c r="R58" s="77"/>
+      <c r="S58" s="77"/>
+      <c r="T58" s="77"/>
+      <c r="U58" s="77"/>
+      <c r="V58" s="77"/>
+      <c r="W58" s="77"/>
+      <c r="X58" s="77"/>
+      <c r="Y58" s="77"/>
+      <c r="Z58" s="77"/>
+      <c r="AA58" s="77"/>
+      <c r="AB58" s="77"/>
+    </row>
+    <row r="59" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B59" s="77" t="s">
+        <v>223</v>
+      </c>
+      <c r="C59" s="77"/>
+      <c r="D59" s="77"/>
+      <c r="E59" s="77"/>
+      <c r="F59" s="77"/>
+      <c r="G59" s="77"/>
+      <c r="H59" s="77"/>
+      <c r="I59" s="77"/>
+      <c r="J59" s="77"/>
+      <c r="K59" s="77"/>
+      <c r="L59" s="77"/>
+      <c r="M59" s="77"/>
+      <c r="N59" s="77"/>
+      <c r="O59" s="77"/>
+      <c r="P59" s="77"/>
+      <c r="Q59" s="77"/>
+      <c r="R59" s="77"/>
+      <c r="S59" s="77"/>
+      <c r="T59" s="77"/>
+      <c r="U59" s="77"/>
+      <c r="V59" s="77"/>
+      <c r="W59" s="77"/>
+      <c r="X59" s="77"/>
+      <c r="Y59" s="77"/>
+      <c r="Z59" s="77"/>
+      <c r="AA59" s="77"/>
+      <c r="AB59" s="77"/>
+    </row>
+    <row r="60" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B60" s="77" t="s">
+        <v>224</v>
+      </c>
+      <c r="C60" s="77"/>
+      <c r="D60" s="77"/>
+      <c r="E60" s="77"/>
+      <c r="F60" s="77"/>
+      <c r="G60" s="77"/>
+      <c r="H60" s="77"/>
+      <c r="I60" s="77"/>
+      <c r="J60" s="77"/>
+      <c r="K60" s="77"/>
+      <c r="L60" s="77"/>
+      <c r="M60" s="77"/>
+      <c r="N60" s="77"/>
+      <c r="O60" s="77"/>
+      <c r="P60" s="77"/>
+      <c r="Q60" s="77"/>
+      <c r="R60" s="77"/>
+      <c r="S60" s="77"/>
+      <c r="T60" s="77"/>
+      <c r="U60" s="77"/>
+      <c r="V60" s="77"/>
+      <c r="W60" s="77"/>
+      <c r="X60" s="77"/>
+      <c r="Y60" s="77"/>
+      <c r="Z60" s="77"/>
+      <c r="AA60" s="77"/>
+      <c r="AB60" s="77"/>
+    </row>
+    <row r="61" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B61" s="77" t="s">
+        <v>225</v>
+      </c>
+      <c r="C61" s="77"/>
+      <c r="D61" s="77"/>
+      <c r="E61" s="77"/>
+      <c r="F61" s="77"/>
+      <c r="G61" s="77"/>
+      <c r="H61" s="77"/>
+      <c r="I61" s="77"/>
+      <c r="J61" s="77"/>
+      <c r="K61" s="77"/>
+      <c r="L61" s="77"/>
+      <c r="M61" s="77"/>
+      <c r="N61" s="77"/>
+      <c r="O61" s="77"/>
+      <c r="P61" s="77"/>
+      <c r="Q61" s="77"/>
+      <c r="R61" s="77"/>
+      <c r="S61" s="77"/>
+      <c r="T61" s="77"/>
+      <c r="U61" s="77"/>
+      <c r="V61" s="77"/>
+      <c r="W61" s="77"/>
+      <c r="X61" s="77"/>
+      <c r="Y61" s="77"/>
+      <c r="Z61" s="77"/>
+      <c r="AA61" s="77"/>
+      <c r="AB61" s="77"/>
+    </row>
+    <row r="62" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B62" s="77" t="s">
+        <v>226</v>
+      </c>
+      <c r="C62" s="77"/>
+      <c r="D62" s="77"/>
+      <c r="E62" s="77"/>
+      <c r="F62" s="77"/>
+      <c r="G62" s="77"/>
+      <c r="H62" s="77"/>
+      <c r="I62" s="77"/>
+      <c r="J62" s="77"/>
+      <c r="K62" s="77"/>
+      <c r="L62" s="77"/>
+      <c r="M62" s="77"/>
+      <c r="N62" s="77"/>
+      <c r="O62" s="77"/>
+      <c r="P62" s="77"/>
+      <c r="Q62" s="77"/>
+      <c r="R62" s="77"/>
+      <c r="S62" s="77"/>
+      <c r="T62" s="77"/>
+      <c r="U62" s="77"/>
+      <c r="V62" s="77"/>
+      <c r="W62" s="77"/>
+      <c r="X62" s="77"/>
+      <c r="Y62" s="77"/>
+      <c r="Z62" s="77"/>
+      <c r="AA62" s="77"/>
+      <c r="AB62" s="77"/>
+    </row>
+    <row r="63" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B63" s="77" t="s">
+        <v>228</v>
+      </c>
+      <c r="C63" s="77"/>
+      <c r="D63" s="77"/>
+      <c r="E63" s="77"/>
+      <c r="F63" s="77"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="77"/>
+      <c r="I63" s="77"/>
+      <c r="J63" s="77"/>
+      <c r="K63" s="77"/>
+      <c r="L63" s="77"/>
+      <c r="M63" s="77"/>
+      <c r="N63" s="77"/>
+      <c r="O63" s="77"/>
+      <c r="P63" s="77"/>
+      <c r="Q63" s="77"/>
+      <c r="R63" s="77"/>
+      <c r="S63" s="77"/>
+      <c r="T63" s="77"/>
+      <c r="U63" s="77"/>
+      <c r="V63" s="77"/>
+      <c r="W63" s="77"/>
+      <c r="X63" s="77"/>
+      <c r="Y63" s="77"/>
+      <c r="Z63" s="77"/>
+      <c r="AA63" s="77"/>
+      <c r="AB63" s="77"/>
+    </row>
+    <row r="64" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B64" s="77" t="s">
+        <v>229</v>
+      </c>
+      <c r="C64" s="77"/>
+      <c r="D64" s="77"/>
+      <c r="E64" s="77"/>
+      <c r="F64" s="77"/>
+      <c r="G64" s="77"/>
+      <c r="H64" s="77"/>
+      <c r="I64" s="77"/>
+      <c r="J64" s="77"/>
+      <c r="K64" s="77"/>
+      <c r="L64" s="77"/>
+      <c r="M64" s="77"/>
+      <c r="N64" s="77"/>
+      <c r="O64" s="77"/>
+      <c r="P64" s="77"/>
+      <c r="Q64" s="77"/>
+      <c r="R64" s="77"/>
+      <c r="S64" s="77"/>
+      <c r="T64" s="77"/>
+      <c r="U64" s="77"/>
+      <c r="V64" s="77"/>
+      <c r="W64" s="77"/>
+      <c r="X64" s="77"/>
+      <c r="Y64" s="77"/>
+      <c r="Z64" s="77"/>
+      <c r="AA64" s="77"/>
+      <c r="AB64" s="77"/>
+    </row>
+    <row r="65" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B65" s="77" t="s">
+        <v>231</v>
+      </c>
+      <c r="C65" s="77"/>
+      <c r="D65" s="77"/>
+      <c r="E65" s="77"/>
+      <c r="F65" s="77"/>
+      <c r="G65" s="77"/>
+      <c r="H65" s="77"/>
+      <c r="I65" s="77"/>
+      <c r="J65" s="77"/>
+      <c r="K65" s="77"/>
+      <c r="L65" s="77"/>
+      <c r="M65" s="77"/>
+      <c r="N65" s="77"/>
+      <c r="O65" s="77"/>
+      <c r="P65" s="77"/>
+      <c r="Q65" s="77"/>
+      <c r="R65" s="77"/>
+      <c r="S65" s="77"/>
+      <c r="T65" s="77"/>
+      <c r="U65" s="77"/>
+      <c r="V65" s="77"/>
+      <c r="W65" s="77"/>
+      <c r="X65" s="77"/>
+      <c r="Y65" s="77"/>
+      <c r="Z65" s="77"/>
+      <c r="AA65" s="77"/>
+      <c r="AB65" s="77"/>
+    </row>
+    <row r="66" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B66" s="77" t="s">
+        <v>230</v>
+      </c>
+      <c r="C66" s="77"/>
+      <c r="D66" s="77"/>
+      <c r="E66" s="77"/>
+      <c r="F66" s="77"/>
+      <c r="G66" s="77"/>
+      <c r="H66" s="77"/>
+      <c r="I66" s="77"/>
+      <c r="J66" s="77"/>
+      <c r="K66" s="77"/>
+      <c r="L66" s="77"/>
+      <c r="M66" s="77"/>
+      <c r="N66" s="77"/>
+      <c r="O66" s="77"/>
+      <c r="P66" s="77"/>
+      <c r="Q66" s="77"/>
+      <c r="R66" s="77"/>
+      <c r="S66" s="77"/>
+      <c r="T66" s="77"/>
+      <c r="U66" s="77"/>
+      <c r="V66" s="77"/>
+      <c r="W66" s="77"/>
+      <c r="X66" s="77"/>
+      <c r="Y66" s="77"/>
+      <c r="Z66" s="77"/>
+      <c r="AA66" s="77"/>
+      <c r="AB66" s="77"/>
+    </row>
+    <row r="67" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B67" s="77" t="s">
+        <v>232</v>
+      </c>
+      <c r="C67" s="77"/>
+      <c r="D67" s="77"/>
+      <c r="E67" s="77"/>
+      <c r="F67" s="77"/>
+      <c r="G67" s="77"/>
+      <c r="H67" s="77"/>
+      <c r="I67" s="77"/>
+      <c r="J67" s="77"/>
+      <c r="K67" s="77"/>
+      <c r="L67" s="77"/>
+      <c r="M67" s="77"/>
+      <c r="N67" s="77"/>
+      <c r="O67" s="77"/>
+      <c r="P67" s="77"/>
+      <c r="Q67" s="77"/>
+      <c r="R67" s="77"/>
+      <c r="S67" s="77"/>
+      <c r="T67" s="77"/>
+      <c r="U67" s="77"/>
+      <c r="V67" s="77"/>
+      <c r="W67" s="77"/>
+      <c r="X67" s="77"/>
+      <c r="Y67" s="77"/>
+      <c r="Z67" s="77"/>
+      <c r="AA67" s="77"/>
+      <c r="AB67" s="77"/>
     </row>
   </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="B62:AB62"/>
+    <mergeCell ref="B63:AB63"/>
+    <mergeCell ref="B64:AB64"/>
+    <mergeCell ref="B65:AB65"/>
+    <mergeCell ref="B66:AB66"/>
+    <mergeCell ref="B67:AB67"/>
+    <mergeCell ref="B52:AB52"/>
+    <mergeCell ref="B53:AB53"/>
+    <mergeCell ref="B58:AB58"/>
+    <mergeCell ref="B59:AB59"/>
+    <mergeCell ref="B60:AB60"/>
+    <mergeCell ref="B61:AB61"/>
+    <mergeCell ref="B46:AB46"/>
+    <mergeCell ref="B47:AB47"/>
+    <mergeCell ref="B48:AB48"/>
+    <mergeCell ref="B49:AB49"/>
+    <mergeCell ref="B50:AB50"/>
+    <mergeCell ref="B51:AB51"/>
+    <mergeCell ref="B39:AB39"/>
+    <mergeCell ref="B41:AB41"/>
+    <mergeCell ref="B42:AB42"/>
+    <mergeCell ref="B43:AB43"/>
+    <mergeCell ref="B44:AB44"/>
+    <mergeCell ref="B45:AB45"/>
+    <mergeCell ref="P24:AB24"/>
+    <mergeCell ref="P26:AB26"/>
+    <mergeCell ref="B35:AB35"/>
+    <mergeCell ref="B36:AB36"/>
+    <mergeCell ref="B37:AB37"/>
+    <mergeCell ref="B38:AB38"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67037082-824D-49EB-921E-2EE533CAB740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0750AEF-1FBF-4DCE-A5C3-9C9A0D3FE52E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -1944,9 +1944,6 @@
     <t>INS_MICO</t>
   </si>
   <si>
-    <t xml:space="preserve">Điều kiện để tương tác với vật thể: Vật thể phải luôn trong tầm nhìn của người chơi; Phạm vi của vật thể phát hiện người chơi. Trong trường hợp </t>
-  </si>
-  <si>
     <t>"An alphabet of twenty-six. But strip away the silent consonants. How many letters hold the true voice of the language?
 Count the vowels."</t>
   </si>
@@ -2670,6 +2667,9 @@
   </si>
   <si>
     <t>Item ID</t>
+  </si>
+  <si>
+    <t>Điều kiện để tương tác với vật thể: Vật thể phải luôn trong tầm nhìn của người chơi; Phạm vi của vật thể phát hiện người chơi. Trong trường hợp có 2 vật thể thì chỉ cho người chơi tương tác với vật thể gần nhất.</t>
   </si>
 </sst>
 </file>
@@ -5748,7 +5748,7 @@
     </row>
     <row r="39" spans="2:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P39" s="77" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q39" s="77"/>
       <c r="R39" s="77"/>
@@ -6571,7 +6571,7 @@
     </row>
     <row r="123" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B123" s="76" t="s">
-        <v>207</v>
+        <v>240</v>
       </c>
     </row>
     <row r="124" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
@@ -6655,7 +6655,7 @@
     </row>
     <row r="4" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="29" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C4" s="29"/>
       <c r="D4" s="42" t="s">
@@ -7604,27 +7604,27 @@
     </row>
     <row r="4" spans="1:16" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P10" s="76" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P21" s="76" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P22" s="91" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="24" spans="2:28" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P24" s="77" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q24" s="77"/>
       <c r="R24" s="77"/>
@@ -7641,7 +7641,7 @@
     </row>
     <row r="26" spans="2:28" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P26" s="77" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q26" s="77"/>
       <c r="R26" s="77"/>
@@ -7659,7 +7659,7 @@
     <row r="27" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7667,22 +7667,22 @@
     </row>
     <row r="31" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B33" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="35" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="77" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C35" s="77"/>
       <c r="D35" s="77"/>
@@ -7713,7 +7713,7 @@
     </row>
     <row r="36" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="77" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C36" s="77"/>
       <c r="D36" s="77"/>
@@ -7744,7 +7744,7 @@
     </row>
     <row r="37" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="77" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C37" s="77"/>
       <c r="D37" s="77"/>
@@ -7775,7 +7775,7 @@
     </row>
     <row r="38" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="77" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C38" s="77"/>
       <c r="D38" s="77"/>
@@ -7806,7 +7806,7 @@
     </row>
     <row r="39" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="77" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C39" s="77"/>
       <c r="D39" s="77"/>
@@ -7837,7 +7837,7 @@
     </row>
     <row r="41" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="77" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C41" s="77"/>
       <c r="D41" s="77"/>
@@ -7868,7 +7868,7 @@
     </row>
     <row r="42" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B42" s="77" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C42" s="77"/>
       <c r="D42" s="77"/>
@@ -7899,7 +7899,7 @@
     </row>
     <row r="43" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B43" s="77" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C43" s="77"/>
       <c r="D43" s="77"/>
@@ -7930,7 +7930,7 @@
     </row>
     <row r="44" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B44" s="77" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C44" s="77"/>
       <c r="D44" s="77"/>
@@ -7961,7 +7961,7 @@
     </row>
     <row r="45" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B45" s="77" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C45" s="77"/>
       <c r="D45" s="77"/>
@@ -7992,7 +7992,7 @@
     </row>
     <row r="46" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B46" s="77" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C46" s="77"/>
       <c r="D46" s="77"/>
@@ -8023,7 +8023,7 @@
     </row>
     <row r="47" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B47" s="77" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C47" s="77"/>
       <c r="D47" s="77"/>
@@ -8054,7 +8054,7 @@
     </row>
     <row r="48" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B48" s="77" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C48" s="77"/>
       <c r="D48" s="77"/>
@@ -8085,7 +8085,7 @@
     </row>
     <row r="49" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B49" s="77" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C49" s="77"/>
       <c r="D49" s="77"/>
@@ -8116,7 +8116,7 @@
     </row>
     <row r="50" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B50" s="77" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C50" s="77"/>
       <c r="D50" s="77"/>
@@ -8147,7 +8147,7 @@
     </row>
     <row r="51" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B51" s="77" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C51" s="77"/>
       <c r="D51" s="77"/>
@@ -8178,7 +8178,7 @@
     </row>
     <row r="52" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B52" s="77" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C52" s="77"/>
       <c r="D52" s="77"/>
@@ -8209,7 +8209,7 @@
     </row>
     <row r="53" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B53" s="77" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C53" s="77"/>
       <c r="D53" s="77"/>
@@ -8240,12 +8240,12 @@
     </row>
     <row r="55" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B55" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B56" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="57" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
@@ -8253,7 +8253,7 @@
     </row>
     <row r="58" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B58" s="77" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C58" s="77"/>
       <c r="D58" s="77"/>
@@ -8284,7 +8284,7 @@
     </row>
     <row r="59" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B59" s="77" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C59" s="77"/>
       <c r="D59" s="77"/>
@@ -8315,7 +8315,7 @@
     </row>
     <row r="60" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B60" s="77" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C60" s="77"/>
       <c r="D60" s="77"/>
@@ -8346,7 +8346,7 @@
     </row>
     <row r="61" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B61" s="77" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C61" s="77"/>
       <c r="D61" s="77"/>
@@ -8377,7 +8377,7 @@
     </row>
     <row r="62" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B62" s="77" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C62" s="77"/>
       <c r="D62" s="77"/>
@@ -8408,7 +8408,7 @@
     </row>
     <row r="63" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B63" s="77" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C63" s="77"/>
       <c r="D63" s="77"/>
@@ -8439,7 +8439,7 @@
     </row>
     <row r="64" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B64" s="77" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C64" s="77"/>
       <c r="D64" s="77"/>
@@ -8470,7 +8470,7 @@
     </row>
     <row r="65" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B65" s="77" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C65" s="77"/>
       <c r="D65" s="77"/>
@@ -8501,7 +8501,7 @@
     </row>
     <row r="66" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B66" s="77" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C66" s="77"/>
       <c r="D66" s="77"/>
@@ -8532,7 +8532,7 @@
     </row>
     <row r="67" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B67" s="77" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C67" s="77"/>
       <c r="D67" s="77"/>

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0750AEF-1FBF-4DCE-A5C3-9C9A0D3FE52E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432EA86E-CEFA-47E3-A94F-7640DAEB79C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -1316,12 +1316,6 @@
     <t>Interactable?</t>
   </si>
   <si>
-    <t>Chưa</t>
-  </si>
-  <si>
-    <t>Đã có Assets?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cần có Title game, các button như: New Game +, Options, Exit. Và được thiết kế layout tương tự như 2 hình mẫu. Với việc khung lựa chọn + Logo ở bên trái và illustration đại diện nằm bên phải. </t>
   </si>
   <si>
@@ -2633,9 +2627,6 @@
     </r>
   </si>
   <si>
-    <t>2.2. Tương tác lần 2: chỉ hiển thị chỉ dẫn cần thiết</t>
-  </si>
-  <si>
     <t>2.1. Tương tác lần đầu: hiển thị toàn bộ cuộc trò chuyện</t>
   </si>
   <si>
@@ -2670,6 +2661,15 @@
   </si>
   <si>
     <t>Điều kiện để tương tác với vật thể: Vật thể phải luôn trong tầm nhìn của người chơi; Phạm vi của vật thể phát hiện người chơi. Trong trường hợp có 2 vật thể thì chỉ cho người chơi tương tác với vật thể gần nhất.</t>
+  </si>
+  <si>
+    <t>2.2. Tương tác lần 2 trở đi: chỉ hiển thị chỉ dẫn cần thiết</t>
+  </si>
+  <si>
+    <t>FBX?</t>
+  </si>
+  <si>
+    <t>Chưa có</t>
   </si>
 </sst>
 </file>
@@ -2895,7 +2895,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2950,9 +2950,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3134,6 +3131,10 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4538,29 +4539,29 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:26" ht="46.5" x14ac:dyDescent="0.7">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
     </row>
     <row r="3" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
@@ -4584,104 +4585,104 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="54" t="s">
+      <c r="B11" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="51" t="s">
-        <v>178</v>
-      </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
+      <c r="B12" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
     </row>
     <row r="13" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="50" t="s">
+      <c r="B13" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="50"/>
-      <c r="M13" s="50"/>
-      <c r="N13" s="50"/>
-      <c r="O13" s="50"/>
-      <c r="P13" s="50"/>
-      <c r="Q13" s="50"/>
-      <c r="R13" s="50"/>
-      <c r="S13" s="50"/>
-      <c r="T13" s="50"/>
-      <c r="U13" s="50"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="49"/>
+      <c r="N13" s="49"/>
+      <c r="O13" s="49"/>
+      <c r="P13" s="49"/>
+      <c r="Q13" s="49"/>
+      <c r="R13" s="49"/>
+      <c r="S13" s="49"/>
+      <c r="T13" s="49"/>
+      <c r="U13" s="49"/>
     </row>
     <row r="14" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
-      <c r="N14" s="46"/>
-      <c r="O14" s="46"/>
-      <c r="P14" s="46"/>
-      <c r="Q14" s="46"/>
-      <c r="R14" s="46"/>
-      <c r="S14" s="46"/>
-      <c r="T14" s="46"/>
-      <c r="U14" s="46"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="45"/>
+      <c r="M14" s="45"/>
+      <c r="N14" s="45"/>
+      <c r="O14" s="45"/>
+      <c r="P14" s="45"/>
+      <c r="Q14" s="45"/>
+      <c r="R14" s="45"/>
+      <c r="S14" s="45"/>
+      <c r="T14" s="45"/>
+      <c r="U14" s="45"/>
     </row>
     <row r="15" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
@@ -4697,28 +4698,28 @@
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:26" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="47"/>
-      <c r="K16" s="47"/>
-      <c r="L16" s="47"/>
-      <c r="M16" s="47"/>
-      <c r="N16" s="47"/>
-      <c r="O16" s="47"/>
-      <c r="P16" s="47"/>
-      <c r="Q16" s="47"/>
-      <c r="R16" s="47"/>
-      <c r="S16" s="47"/>
-      <c r="T16" s="47"/>
-      <c r="U16" s="47"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="46"/>
+      <c r="K16" s="46"/>
+      <c r="L16" s="46"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="46"/>
+      <c r="O16" s="46"/>
+      <c r="P16" s="46"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="46"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="46"/>
+      <c r="U16" s="46"/>
       <c r="V16" s="6"/>
       <c r="W16" s="6"/>
       <c r="X16" s="6"/>
@@ -4726,100 +4727,100 @@
       <c r="Z16" s="6"/>
     </row>
     <row r="17" spans="1:21" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="47" t="s">
+      <c r="B17" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="47"/>
-      <c r="J17" s="47"/>
-      <c r="K17" s="47"/>
-      <c r="L17" s="47"/>
-      <c r="M17" s="47"/>
-      <c r="N17" s="47"/>
-      <c r="O17" s="47"/>
-      <c r="P17" s="47"/>
-      <c r="Q17" s="47"/>
-      <c r="R17" s="47"/>
-      <c r="S17" s="47"/>
-      <c r="T17" s="47"/>
-      <c r="U17" s="47"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="46"/>
+      <c r="L17" s="46"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="46"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="46"/>
+      <c r="U17" s="46"/>
     </row>
     <row r="18" spans="1:21" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="46"/>
-      <c r="M18" s="46"/>
-      <c r="N18" s="46"/>
-      <c r="O18" s="46"/>
-      <c r="P18" s="46"/>
-      <c r="Q18" s="46"/>
-      <c r="R18" s="46"/>
-      <c r="S18" s="46"/>
-      <c r="T18" s="46"/>
-      <c r="U18" s="46"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="45"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="45"/>
+      <c r="P18" s="45"/>
+      <c r="Q18" s="45"/>
+      <c r="R18" s="45"/>
+      <c r="S18" s="45"/>
+      <c r="T18" s="45"/>
+      <c r="U18" s="45"/>
     </row>
     <row r="19" spans="1:21" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="48" t="s">
+      <c r="B19" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="49"/>
-      <c r="M19" s="49"/>
-      <c r="N19" s="49"/>
-      <c r="O19" s="49"/>
-      <c r="P19" s="49"/>
-      <c r="Q19" s="49"/>
-      <c r="R19" s="49"/>
-      <c r="S19" s="49"/>
-      <c r="T19" s="49"/>
-      <c r="U19" s="49"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
     </row>
     <row r="20" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="52" t="s">
-        <v>179</v>
-      </c>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="52"/>
-      <c r="K20" s="52"/>
-      <c r="L20" s="52"/>
-      <c r="M20" s="52"/>
-      <c r="N20" s="52"/>
-      <c r="O20" s="52"/>
-      <c r="P20" s="52"/>
-      <c r="Q20" s="52"/>
-      <c r="R20" s="52"/>
-      <c r="S20" s="52"/>
-      <c r="T20" s="52"/>
-      <c r="U20" s="52"/>
+      <c r="B20" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
+      <c r="L20" s="51"/>
+      <c r="M20" s="51"/>
+      <c r="N20" s="51"/>
+      <c r="O20" s="51"/>
+      <c r="P20" s="51"/>
+      <c r="Q20" s="51"/>
+      <c r="R20" s="51"/>
+      <c r="S20" s="51"/>
+      <c r="T20" s="51"/>
+      <c r="U20" s="51"/>
     </row>
     <row r="22" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
@@ -4959,7 +4960,7 @@
   <sheetData>
     <row r="2" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B2" s="8"/>
     </row>
@@ -4967,367 +4968,367 @@
       <c r="B4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29" t="s">
+      <c r="D4" s="28"/>
+      <c r="E4" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="57" t="s">
+      <c r="F4" s="28"/>
+      <c r="G4" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57" t="s">
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="57"/>
-      <c r="O4" s="57"/>
-      <c r="P4" s="57"/>
-      <c r="Q4" s="57"/>
-      <c r="R4" s="57"/>
-      <c r="S4" s="57"/>
-      <c r="T4" s="57"/>
-      <c r="U4" s="57"/>
-      <c r="V4" s="57"/>
-      <c r="W4" s="57"/>
-      <c r="X4" s="57"/>
-      <c r="Y4" s="57"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="56"/>
+      <c r="Q4" s="56"/>
+      <c r="R4" s="56"/>
+      <c r="S4" s="56"/>
+      <c r="T4" s="56"/>
+      <c r="U4" s="56"/>
+      <c r="V4" s="56"/>
+      <c r="W4" s="56"/>
+      <c r="X4" s="56"/>
+      <c r="Y4" s="56"/>
     </row>
     <row r="5" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11">
         <v>1</v>
       </c>
-      <c r="C5" s="62" t="s">
+      <c r="C5" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="62"/>
-      <c r="E5" s="63" t="s">
+      <c r="D5" s="61"/>
+      <c r="E5" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="63"/>
-      <c r="G5" s="60" t="s">
+      <c r="F5" s="62"/>
+      <c r="G5" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="58" t="s">
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
+      <c r="L5" s="59"/>
+      <c r="M5" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="N5" s="58"/>
-      <c r="O5" s="58"/>
-      <c r="P5" s="58"/>
-      <c r="Q5" s="58"/>
-      <c r="R5" s="58"/>
-      <c r="S5" s="58"/>
-      <c r="T5" s="58"/>
-      <c r="U5" s="58"/>
-      <c r="V5" s="58"/>
-      <c r="W5" s="58"/>
-      <c r="X5" s="58"/>
-      <c r="Y5" s="58"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="57"/>
+      <c r="Q5" s="57"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="57"/>
+      <c r="U5" s="57"/>
+      <c r="V5" s="57"/>
+      <c r="W5" s="57"/>
+      <c r="X5" s="57"/>
+      <c r="Y5" s="57"/>
     </row>
     <row r="6" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11">
         <v>2</v>
       </c>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="63" t="s">
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="63"/>
-      <c r="G6" s="60" t="s">
+      <c r="F6" s="62"/>
+      <c r="G6" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="59" t="s">
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="N6" s="58"/>
-      <c r="O6" s="58"/>
-      <c r="P6" s="58"/>
-      <c r="Q6" s="58"/>
-      <c r="R6" s="58"/>
-      <c r="S6" s="58"/>
-      <c r="T6" s="58"/>
-      <c r="U6" s="58"/>
-      <c r="V6" s="58"/>
-      <c r="W6" s="58"/>
-      <c r="X6" s="58"/>
-      <c r="Y6" s="58"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="57"/>
+      <c r="P6" s="57"/>
+      <c r="Q6" s="57"/>
+      <c r="R6" s="57"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="57"/>
+      <c r="U6" s="57"/>
+      <c r="V6" s="57"/>
+      <c r="W6" s="57"/>
+      <c r="X6" s="57"/>
+      <c r="Y6" s="57"/>
     </row>
     <row r="7" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11">
         <v>3</v>
       </c>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="63" t="s">
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="63"/>
-      <c r="G7" s="60" t="s">
+      <c r="F7" s="62"/>
+      <c r="G7" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="56" t="s">
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="56"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="56"/>
-      <c r="Q7" s="56"/>
-      <c r="R7" s="56"/>
-      <c r="S7" s="56"/>
-      <c r="T7" s="56"/>
-      <c r="U7" s="56"/>
-      <c r="V7" s="56"/>
-      <c r="W7" s="56"/>
-      <c r="X7" s="56"/>
-      <c r="Y7" s="56"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="55"/>
+      <c r="P7" s="55"/>
+      <c r="Q7" s="55"/>
+      <c r="R7" s="55"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="55"/>
+      <c r="U7" s="55"/>
+      <c r="V7" s="55"/>
+      <c r="W7" s="55"/>
+      <c r="X7" s="55"/>
+      <c r="Y7" s="55"/>
     </row>
     <row r="8" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11">
         <v>4</v>
       </c>
-      <c r="C8" s="62" t="s">
+      <c r="C8" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="62"/>
-      <c r="E8" s="63" t="s">
+      <c r="D8" s="61"/>
+      <c r="E8" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="63"/>
-      <c r="G8" s="60" t="s">
+      <c r="F8" s="62"/>
+      <c r="G8" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="60"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="55" t="s">
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="59"/>
+      <c r="K8" s="59"/>
+      <c r="L8" s="59"/>
+      <c r="M8" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="N8" s="56"/>
-      <c r="O8" s="56"/>
-      <c r="P8" s="56"/>
-      <c r="Q8" s="56"/>
-      <c r="R8" s="56"/>
-      <c r="S8" s="56"/>
-      <c r="T8" s="56"/>
-      <c r="U8" s="56"/>
-      <c r="V8" s="56"/>
-      <c r="W8" s="56"/>
-      <c r="X8" s="56"/>
-      <c r="Y8" s="56"/>
+      <c r="N8" s="55"/>
+      <c r="O8" s="55"/>
+      <c r="P8" s="55"/>
+      <c r="Q8" s="55"/>
+      <c r="R8" s="55"/>
+      <c r="S8" s="55"/>
+      <c r="T8" s="55"/>
+      <c r="U8" s="55"/>
+      <c r="V8" s="55"/>
+      <c r="W8" s="55"/>
+      <c r="X8" s="55"/>
+      <c r="Y8" s="55"/>
     </row>
     <row r="9" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11">
         <v>5</v>
       </c>
-      <c r="C9" s="62"/>
-      <c r="D9" s="62"/>
-      <c r="E9" s="63" t="s">
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="63"/>
-      <c r="G9" s="60" t="s">
+      <c r="F9" s="62"/>
+      <c r="G9" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="55" t="s">
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="59"/>
+      <c r="K9" s="59"/>
+      <c r="L9" s="59"/>
+      <c r="M9" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="56"/>
-      <c r="O9" s="56"/>
-      <c r="P9" s="56"/>
-      <c r="Q9" s="56"/>
-      <c r="R9" s="56"/>
-      <c r="S9" s="56"/>
-      <c r="T9" s="56"/>
-      <c r="U9" s="56"/>
-      <c r="V9" s="56"/>
-      <c r="W9" s="56"/>
-      <c r="X9" s="56"/>
-      <c r="Y9" s="56"/>
+      <c r="N9" s="55"/>
+      <c r="O9" s="55"/>
+      <c r="P9" s="55"/>
+      <c r="Q9" s="55"/>
+      <c r="R9" s="55"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="55"/>
+      <c r="U9" s="55"/>
+      <c r="V9" s="55"/>
+      <c r="W9" s="55"/>
+      <c r="X9" s="55"/>
+      <c r="Y9" s="55"/>
     </row>
     <row r="10" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="11">
         <v>6</v>
       </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="63" t="s">
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="63"/>
-      <c r="G10" s="60" t="s">
+      <c r="F10" s="62"/>
+      <c r="G10" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="60"/>
-      <c r="K10" s="60"/>
-      <c r="L10" s="60"/>
-      <c r="M10" s="55" t="s">
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="59"/>
+      <c r="L10" s="59"/>
+      <c r="M10" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="N10" s="56"/>
-      <c r="O10" s="56"/>
-      <c r="P10" s="56"/>
-      <c r="Q10" s="56"/>
-      <c r="R10" s="56"/>
-      <c r="S10" s="56"/>
-      <c r="T10" s="56"/>
-      <c r="U10" s="56"/>
-      <c r="V10" s="56"/>
-      <c r="W10" s="56"/>
-      <c r="X10" s="56"/>
-      <c r="Y10" s="56"/>
+      <c r="N10" s="55"/>
+      <c r="O10" s="55"/>
+      <c r="P10" s="55"/>
+      <c r="Q10" s="55"/>
+      <c r="R10" s="55"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="55"/>
+      <c r="U10" s="55"/>
+      <c r="V10" s="55"/>
+      <c r="W10" s="55"/>
+      <c r="X10" s="55"/>
+      <c r="Y10" s="55"/>
     </row>
     <row r="11" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="11">
         <v>7</v>
       </c>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="63" t="s">
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="63"/>
-      <c r="G11" s="60" t="s">
+      <c r="F11" s="62"/>
+      <c r="G11" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="60"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="60"/>
-      <c r="K11" s="60"/>
-      <c r="L11" s="60"/>
-      <c r="M11" s="56" t="s">
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="59"/>
+      <c r="L11" s="59"/>
+      <c r="M11" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="56"/>
-      <c r="O11" s="56"/>
-      <c r="P11" s="56"/>
-      <c r="Q11" s="56"/>
-      <c r="R11" s="56"/>
-      <c r="S11" s="56"/>
-      <c r="T11" s="56"/>
-      <c r="U11" s="56"/>
-      <c r="V11" s="56"/>
-      <c r="W11" s="56"/>
-      <c r="X11" s="56"/>
-      <c r="Y11" s="56"/>
+      <c r="N11" s="55"/>
+      <c r="O11" s="55"/>
+      <c r="P11" s="55"/>
+      <c r="Q11" s="55"/>
+      <c r="R11" s="55"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="55"/>
+      <c r="U11" s="55"/>
+      <c r="V11" s="55"/>
+      <c r="W11" s="55"/>
+      <c r="X11" s="55"/>
+      <c r="Y11" s="55"/>
     </row>
     <row r="12" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="11">
         <v>8</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="62"/>
-      <c r="E12" s="63" t="s">
+      <c r="D12" s="61"/>
+      <c r="E12" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="63"/>
-      <c r="G12" s="60" t="s">
+      <c r="F12" s="62"/>
+      <c r="G12" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="60"/>
-      <c r="K12" s="60"/>
-      <c r="L12" s="60"/>
-      <c r="M12" s="56" t="s">
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="59"/>
+      <c r="K12" s="59"/>
+      <c r="L12" s="59"/>
+      <c r="M12" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="N12" s="56"/>
-      <c r="O12" s="56"/>
-      <c r="P12" s="56"/>
-      <c r="Q12" s="56"/>
-      <c r="R12" s="56"/>
-      <c r="S12" s="56"/>
-      <c r="T12" s="56"/>
-      <c r="U12" s="56"/>
-      <c r="V12" s="56"/>
-      <c r="W12" s="56"/>
-      <c r="X12" s="56"/>
-      <c r="Y12" s="56"/>
+      <c r="N12" s="55"/>
+      <c r="O12" s="55"/>
+      <c r="P12" s="55"/>
+      <c r="Q12" s="55"/>
+      <c r="R12" s="55"/>
+      <c r="S12" s="55"/>
+      <c r="T12" s="55"/>
+      <c r="U12" s="55"/>
+      <c r="V12" s="55"/>
+      <c r="W12" s="55"/>
+      <c r="X12" s="55"/>
+      <c r="Y12" s="55"/>
     </row>
     <row r="46" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B49" s="61" t="s">
+      <c r="B49" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="61"/>
-      <c r="D49" s="61"/>
-      <c r="E49" s="61"/>
-      <c r="F49" s="61"/>
-      <c r="G49" s="61"/>
-      <c r="H49" s="61"/>
-      <c r="I49" s="61"/>
-      <c r="J49" s="61"/>
-      <c r="K49" s="61"/>
-      <c r="L49" s="61"/>
-      <c r="M49" s="61"/>
-      <c r="N49" s="61"/>
-      <c r="O49" s="61"/>
-      <c r="P49" s="61"/>
-      <c r="Q49" s="61"/>
-      <c r="R49" s="61"/>
-      <c r="S49" s="61"/>
-      <c r="T49" s="61"/>
-      <c r="U49" s="61"/>
-      <c r="V49" s="61"/>
+      <c r="C49" s="60"/>
+      <c r="D49" s="60"/>
+      <c r="E49" s="60"/>
+      <c r="F49" s="60"/>
+      <c r="G49" s="60"/>
+      <c r="H49" s="60"/>
+      <c r="I49" s="60"/>
+      <c r="J49" s="60"/>
+      <c r="K49" s="60"/>
+      <c r="L49" s="60"/>
+      <c r="M49" s="60"/>
+      <c r="N49" s="60"/>
+      <c r="O49" s="60"/>
+      <c r="P49" s="60"/>
+      <c r="Q49" s="60"/>
+      <c r="R49" s="60"/>
+      <c r="S49" s="60"/>
+      <c r="T49" s="60"/>
+      <c r="U49" s="60"/>
+      <c r="V49" s="60"/>
     </row>
     <row r="50" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B50" s="61"/>
-      <c r="C50" s="61"/>
-      <c r="D50" s="61"/>
-      <c r="E50" s="61"/>
-      <c r="F50" s="61"/>
-      <c r="G50" s="61"/>
-      <c r="H50" s="61"/>
-      <c r="I50" s="61"/>
-      <c r="J50" s="61"/>
-      <c r="K50" s="61"/>
-      <c r="L50" s="61"/>
-      <c r="M50" s="61"/>
-      <c r="N50" s="61"/>
-      <c r="O50" s="61"/>
-      <c r="P50" s="61"/>
-      <c r="Q50" s="61"/>
-      <c r="R50" s="61"/>
-      <c r="S50" s="61"/>
-      <c r="T50" s="61"/>
-      <c r="U50" s="61"/>
-      <c r="V50" s="61"/>
-      <c r="W50" s="90"/>
-      <c r="X50" s="90"/>
-      <c r="Y50" s="90"/>
+      <c r="B50" s="60"/>
+      <c r="C50" s="60"/>
+      <c r="D50" s="60"/>
+      <c r="E50" s="60"/>
+      <c r="F50" s="60"/>
+      <c r="G50" s="60"/>
+      <c r="H50" s="60"/>
+      <c r="I50" s="60"/>
+      <c r="J50" s="60"/>
+      <c r="K50" s="60"/>
+      <c r="L50" s="60"/>
+      <c r="M50" s="60"/>
+      <c r="N50" s="60"/>
+      <c r="O50" s="60"/>
+      <c r="P50" s="60"/>
+      <c r="Q50" s="60"/>
+      <c r="R50" s="60"/>
+      <c r="S50" s="60"/>
+      <c r="T50" s="60"/>
+      <c r="U50" s="60"/>
+      <c r="V50" s="60"/>
+      <c r="W50" s="89"/>
+      <c r="X50" s="89"/>
+      <c r="Y50" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="37">
@@ -5384,29 +5385,29 @@
   <sheetData>
     <row r="2" spans="1:28" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L8" s="79" t="s">
+      <c r="L8" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="M8" s="65"/>
-      <c r="N8" s="65"/>
-      <c r="O8" s="65"/>
-      <c r="P8" s="65"/>
-      <c r="Q8" s="65"/>
-      <c r="R8" s="65"/>
-      <c r="S8" s="65"/>
-      <c r="T8" s="65"/>
-      <c r="U8" s="65"/>
-      <c r="V8" s="65"/>
-      <c r="W8" s="65"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="64"/>
+      <c r="P8" s="64"/>
+      <c r="Q8" s="64"/>
+      <c r="R8" s="64"/>
+      <c r="S8" s="64"/>
+      <c r="T8" s="64"/>
+      <c r="U8" s="64"/>
+      <c r="V8" s="64"/>
+      <c r="W8" s="64"/>
     </row>
     <row r="9" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="L9" s="7"/>
@@ -5423,25 +5424,25 @@
       <c r="W9" s="7"/>
     </row>
     <row r="10" spans="1:28" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L10" s="77" t="s">
+      <c r="L10" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="M10" s="48"/>
-      <c r="N10" s="48"/>
-      <c r="O10" s="48"/>
-      <c r="P10" s="48"/>
-      <c r="Q10" s="48"/>
-      <c r="R10" s="48"/>
-      <c r="S10" s="48"/>
-      <c r="T10" s="48"/>
-      <c r="U10" s="48"/>
-      <c r="V10" s="48"/>
-      <c r="W10" s="48"/>
-      <c r="X10" s="48"/>
-      <c r="Y10" s="48"/>
-      <c r="Z10" s="48"/>
-      <c r="AA10" s="48"/>
-      <c r="AB10" s="48"/>
+      <c r="M10" s="47"/>
+      <c r="N10" s="47"/>
+      <c r="O10" s="47"/>
+      <c r="P10" s="47"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="47"/>
+      <c r="S10" s="47"/>
+      <c r="T10" s="47"/>
+      <c r="U10" s="47"/>
+      <c r="V10" s="47"/>
+      <c r="W10" s="47"/>
+      <c r="X10" s="47"/>
+      <c r="Y10" s="47"/>
+      <c r="Z10" s="47"/>
+      <c r="AA10" s="47"/>
+      <c r="AB10" s="47"/>
     </row>
     <row r="11" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="L11" s="7"/>
@@ -5458,67 +5459,67 @@
       <c r="W11" s="7"/>
     </row>
     <row r="12" spans="1:28" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L12" s="77" t="s">
+      <c r="L12" s="76" t="s">
         <v>82</v>
       </c>
-      <c r="M12" s="49"/>
-      <c r="N12" s="49"/>
-      <c r="O12" s="49"/>
-      <c r="P12" s="49"/>
-      <c r="Q12" s="49"/>
-      <c r="R12" s="49"/>
-      <c r="S12" s="49"/>
-      <c r="T12" s="49"/>
-      <c r="U12" s="49"/>
-      <c r="V12" s="49"/>
-      <c r="W12" s="49"/>
-      <c r="X12" s="49"/>
-      <c r="Y12" s="49"/>
-      <c r="Z12" s="49"/>
-      <c r="AA12" s="49"/>
-      <c r="AB12" s="49"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="48"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48"/>
+      <c r="R12" s="48"/>
+      <c r="S12" s="48"/>
+      <c r="T12" s="48"/>
+      <c r="U12" s="48"/>
+      <c r="V12" s="48"/>
+      <c r="W12" s="48"/>
+      <c r="X12" s="48"/>
+      <c r="Y12" s="48"/>
+      <c r="Z12" s="48"/>
+      <c r="AA12" s="48"/>
+      <c r="AB12" s="48"/>
     </row>
     <row r="13" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="S13" s="12"/>
     </row>
     <row r="15" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B15" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B16" s="8"/>
     </row>
     <row r="17" spans="2:28" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="69" t="s">
+      <c r="B17" s="68" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="70"/>
-      <c r="J17" s="70"/>
-      <c r="K17" s="70"/>
-      <c r="L17" s="70"/>
-      <c r="M17" s="70"/>
-      <c r="N17" s="70"/>
-      <c r="O17" s="70"/>
-      <c r="P17" s="70"/>
-      <c r="Q17" s="70"/>
-      <c r="R17" s="70"/>
-      <c r="S17" s="70"/>
-      <c r="T17" s="70"/>
-      <c r="U17" s="70"/>
-      <c r="V17" s="70"/>
-      <c r="W17" s="70"/>
-      <c r="X17" s="70"/>
-      <c r="Y17" s="70"/>
-      <c r="Z17" s="70"/>
-      <c r="AA17" s="70"/>
-      <c r="AB17" s="70"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
+      <c r="L17" s="69"/>
+      <c r="M17" s="69"/>
+      <c r="N17" s="69"/>
+      <c r="O17" s="69"/>
+      <c r="P17" s="69"/>
+      <c r="Q17" s="69"/>
+      <c r="R17" s="69"/>
+      <c r="S17" s="69"/>
+      <c r="T17" s="69"/>
+      <c r="U17" s="69"/>
+      <c r="V17" s="69"/>
+      <c r="W17" s="69"/>
+      <c r="X17" s="69"/>
+      <c r="Y17" s="69"/>
+      <c r="Z17" s="69"/>
+      <c r="AA17" s="69"/>
+      <c r="AB17" s="69"/>
     </row>
     <row r="18" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="15"/>
@@ -5553,41 +5554,41 @@
       <c r="C20" s="10"/>
     </row>
     <row r="22" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="P22" s="66" t="s">
+      <c r="P22" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="Q22" s="66"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="66"/>
-      <c r="U22" s="66"/>
-      <c r="V22" s="66"/>
-      <c r="W22" s="66"/>
-      <c r="X22" s="66"/>
-      <c r="Y22" s="66"/>
-      <c r="Z22" s="66"/>
-      <c r="AA22" s="66"/>
-      <c r="AB22" s="66"/>
+      <c r="Q22" s="65"/>
+      <c r="R22" s="65"/>
+      <c r="S22" s="65"/>
+      <c r="T22" s="65"/>
+      <c r="U22" s="65"/>
+      <c r="V22" s="65"/>
+      <c r="W22" s="65"/>
+      <c r="X22" s="65"/>
+      <c r="Y22" s="65"/>
+      <c r="Z22" s="65"/>
+      <c r="AA22" s="65"/>
+      <c r="AB22" s="65"/>
     </row>
     <row r="23" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P23" s="12"/>
     </row>
     <row r="24" spans="2:28" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P24" s="64" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q24" s="67"/>
-      <c r="R24" s="67"/>
-      <c r="S24" s="67"/>
-      <c r="T24" s="67"/>
-      <c r="U24" s="67"/>
-      <c r="V24" s="67"/>
-      <c r="W24" s="67"/>
-      <c r="X24" s="67"/>
-      <c r="Y24" s="67"/>
-      <c r="Z24" s="67"/>
-      <c r="AA24" s="67"/>
-      <c r="AB24" s="67"/>
+      <c r="P24" s="63" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q24" s="66"/>
+      <c r="R24" s="66"/>
+      <c r="S24" s="66"/>
+      <c r="T24" s="66"/>
+      <c r="U24" s="66"/>
+      <c r="V24" s="66"/>
+      <c r="W24" s="66"/>
+      <c r="X24" s="66"/>
+      <c r="Y24" s="66"/>
+      <c r="Z24" s="66"/>
+      <c r="AA24" s="66"/>
+      <c r="AB24" s="66"/>
     </row>
     <row r="25" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P25" s="19"/>
@@ -5605,21 +5606,21 @@
       <c r="AB25" s="17"/>
     </row>
     <row r="26" spans="2:28" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P26" s="64" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q26" s="64"/>
-      <c r="R26" s="64"/>
-      <c r="S26" s="64"/>
-      <c r="T26" s="64"/>
-      <c r="U26" s="64"/>
-      <c r="V26" s="64"/>
-      <c r="W26" s="64"/>
-      <c r="X26" s="64"/>
-      <c r="Y26" s="64"/>
-      <c r="Z26" s="64"/>
-      <c r="AA26" s="64"/>
-      <c r="AB26" s="64"/>
+      <c r="P26" s="63" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q26" s="63"/>
+      <c r="R26" s="63"/>
+      <c r="S26" s="63"/>
+      <c r="T26" s="63"/>
+      <c r="U26" s="63"/>
+      <c r="V26" s="63"/>
+      <c r="W26" s="63"/>
+      <c r="X26" s="63"/>
+      <c r="Y26" s="63"/>
+      <c r="Z26" s="63"/>
+      <c r="AA26" s="63"/>
+      <c r="AB26" s="63"/>
     </row>
     <row r="27" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P27" s="17"/>
@@ -5637,21 +5638,21 @@
       <c r="AB27" s="17"/>
     </row>
     <row r="28" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="P28" s="66" t="s">
+      <c r="P28" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="Q28" s="66"/>
-      <c r="R28" s="66"/>
-      <c r="S28" s="66"/>
-      <c r="T28" s="66"/>
-      <c r="U28" s="66"/>
-      <c r="V28" s="66"/>
-      <c r="W28" s="66"/>
-      <c r="X28" s="66"/>
-      <c r="Y28" s="66"/>
-      <c r="Z28" s="66"/>
-      <c r="AA28" s="66"/>
-      <c r="AB28" s="66"/>
+      <c r="Q28" s="65"/>
+      <c r="R28" s="65"/>
+      <c r="S28" s="65"/>
+      <c r="T28" s="65"/>
+      <c r="U28" s="65"/>
+      <c r="V28" s="65"/>
+      <c r="W28" s="65"/>
+      <c r="X28" s="65"/>
+      <c r="Y28" s="65"/>
+      <c r="Z28" s="65"/>
+      <c r="AA28" s="65"/>
+      <c r="AB28" s="65"/>
     </row>
     <row r="29" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P29" s="12"/>
@@ -5697,39 +5698,39 @@
       <c r="AB35" s="12"/>
     </row>
     <row r="36" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P36" s="48" t="s">
+      <c r="P36" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="Q36" s="48"/>
-      <c r="R36" s="48"/>
-      <c r="S36" s="48"/>
-      <c r="T36" s="48"/>
-      <c r="U36" s="48"/>
-      <c r="V36" s="48"/>
-      <c r="W36" s="48"/>
-      <c r="X36" s="48"/>
-      <c r="Y36" s="48"/>
-      <c r="Z36" s="48"/>
-      <c r="AA36" s="48"/>
-      <c r="AB36" s="48"/>
+      <c r="Q36" s="47"/>
+      <c r="R36" s="47"/>
+      <c r="S36" s="47"/>
+      <c r="T36" s="47"/>
+      <c r="U36" s="47"/>
+      <c r="V36" s="47"/>
+      <c r="W36" s="47"/>
+      <c r="X36" s="47"/>
+      <c r="Y36" s="47"/>
+      <c r="Z36" s="47"/>
+      <c r="AA36" s="47"/>
+      <c r="AB36" s="47"/>
     </row>
     <row r="38" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B38" s="68" t="s">
+      <c r="B38" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="68"/>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="68"/>
-      <c r="H38" s="68"/>
-      <c r="I38" s="68"/>
-      <c r="J38" s="68"/>
-      <c r="K38" s="68"/>
-      <c r="L38" s="68"/>
-      <c r="M38" s="68"/>
-      <c r="N38" s="68"/>
-      <c r="O38" s="80"/>
+      <c r="C38" s="67"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="67"/>
+      <c r="H38" s="67"/>
+      <c r="I38" s="67"/>
+      <c r="J38" s="67"/>
+      <c r="K38" s="67"/>
+      <c r="L38" s="67"/>
+      <c r="M38" s="67"/>
+      <c r="N38" s="67"/>
+      <c r="O38" s="79"/>
       <c r="P38" s="8" t="s">
         <v>57</v>
       </c>
@@ -5747,22 +5748,22 @@
       <c r="AB38" s="12"/>
     </row>
     <row r="39" spans="2:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P39" s="77" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q39" s="77"/>
-      <c r="R39" s="77"/>
-      <c r="S39" s="77"/>
-      <c r="T39" s="77"/>
-      <c r="U39" s="77"/>
-      <c r="V39" s="77"/>
-      <c r="W39" s="77"/>
-      <c r="X39" s="77"/>
-      <c r="Y39" s="77"/>
-      <c r="Z39" s="77"/>
-      <c r="AA39" s="77"/>
-      <c r="AB39" s="77"/>
-      <c r="AC39" s="87"/>
+      <c r="P39" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q39" s="76"/>
+      <c r="R39" s="76"/>
+      <c r="S39" s="76"/>
+      <c r="T39" s="76"/>
+      <c r="U39" s="76"/>
+      <c r="V39" s="76"/>
+      <c r="W39" s="76"/>
+      <c r="X39" s="76"/>
+      <c r="Y39" s="76"/>
+      <c r="Z39" s="76"/>
+      <c r="AA39" s="76"/>
+      <c r="AB39" s="76"/>
+      <c r="AC39" s="86"/>
     </row>
     <row r="40" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P40" s="12" t="s">
@@ -5775,22 +5776,22 @@
       </c>
     </row>
     <row r="42" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="P42" s="66" t="s">
+      <c r="P42" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="Q42" s="66"/>
-      <c r="R42" s="66"/>
-      <c r="S42" s="66"/>
-      <c r="T42" s="66"/>
-      <c r="U42" s="66"/>
-      <c r="V42" s="66"/>
-      <c r="W42" s="66"/>
-      <c r="X42" s="66"/>
-      <c r="Y42" s="66"/>
-      <c r="Z42" s="66"/>
-      <c r="AA42" s="66"/>
-      <c r="AB42" s="66"/>
-      <c r="AC42" s="66"/>
+      <c r="Q42" s="65"/>
+      <c r="R42" s="65"/>
+      <c r="S42" s="65"/>
+      <c r="T42" s="65"/>
+      <c r="U42" s="65"/>
+      <c r="V42" s="65"/>
+      <c r="W42" s="65"/>
+      <c r="X42" s="65"/>
+      <c r="Y42" s="65"/>
+      <c r="Z42" s="65"/>
+      <c r="AA42" s="65"/>
+      <c r="AB42" s="65"/>
+      <c r="AC42" s="65"/>
     </row>
     <row r="43" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P43" s="12" t="s">
@@ -5803,22 +5804,22 @@
       </c>
     </row>
     <row r="45" spans="2:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P45" s="48" t="s">
+      <c r="P45" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="Q45" s="48"/>
-      <c r="R45" s="48"/>
-      <c r="S45" s="48"/>
-      <c r="T45" s="48"/>
-      <c r="U45" s="48"/>
-      <c r="V45" s="48"/>
-      <c r="W45" s="48"/>
-      <c r="X45" s="48"/>
-      <c r="Y45" s="48"/>
-      <c r="Z45" s="48"/>
-      <c r="AA45" s="48"/>
-      <c r="AB45" s="48"/>
-      <c r="AC45" s="88"/>
+      <c r="Q45" s="47"/>
+      <c r="R45" s="47"/>
+      <c r="S45" s="47"/>
+      <c r="T45" s="47"/>
+      <c r="U45" s="47"/>
+      <c r="V45" s="47"/>
+      <c r="W45" s="47"/>
+      <c r="X45" s="47"/>
+      <c r="Y45" s="47"/>
+      <c r="Z45" s="47"/>
+      <c r="AA45" s="47"/>
+      <c r="AB45" s="47"/>
+      <c r="AC45" s="87"/>
     </row>
     <row r="46" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P46" s="12" t="s">
@@ -5826,45 +5827,45 @@
       </c>
     </row>
     <row r="47" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B47" s="81" t="s">
+      <c r="B47" s="80" t="s">
         <v>90</v>
       </c>
-      <c r="C47" s="81"/>
-      <c r="D47" s="81"/>
-      <c r="E47" s="81"/>
-      <c r="F47" s="81"/>
-      <c r="G47" s="81"/>
-      <c r="H47" s="81"/>
-      <c r="I47" s="81"/>
-      <c r="J47" s="81"/>
-      <c r="K47" s="81"/>
-      <c r="L47" s="81"/>
-      <c r="M47" s="81"/>
+      <c r="C47" s="80"/>
+      <c r="D47" s="80"/>
+      <c r="E47" s="80"/>
+      <c r="F47" s="80"/>
+      <c r="G47" s="80"/>
+      <c r="H47" s="80"/>
+      <c r="I47" s="80"/>
+      <c r="J47" s="80"/>
+      <c r="K47" s="80"/>
+      <c r="L47" s="80"/>
+      <c r="M47" s="80"/>
       <c r="P47" s="8" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="48" spans="2:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P48" s="77" t="s">
+      <c r="P48" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="Q48" s="77"/>
-      <c r="R48" s="77"/>
-      <c r="S48" s="77"/>
-      <c r="T48" s="77"/>
-      <c r="U48" s="77"/>
-      <c r="V48" s="77"/>
-      <c r="W48" s="77"/>
-      <c r="X48" s="77"/>
-      <c r="Y48" s="77"/>
-      <c r="Z48" s="77"/>
-      <c r="AA48" s="77"/>
-      <c r="AB48" s="77"/>
-      <c r="AC48" s="82"/>
+      <c r="Q48" s="76"/>
+      <c r="R48" s="76"/>
+      <c r="S48" s="76"/>
+      <c r="T48" s="76"/>
+      <c r="U48" s="76"/>
+      <c r="V48" s="76"/>
+      <c r="W48" s="76"/>
+      <c r="X48" s="76"/>
+      <c r="Y48" s="76"/>
+      <c r="Z48" s="76"/>
+      <c r="AA48" s="76"/>
+      <c r="AB48" s="76"/>
+      <c r="AC48" s="81"/>
     </row>
     <row r="49" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="N49" s="80"/>
-      <c r="O49" s="80"/>
+      <c r="N49" s="79"/>
+      <c r="O49" s="79"/>
       <c r="P49" s="12" t="s">
         <v>69</v>
       </c>
@@ -5875,21 +5876,21 @@
       </c>
     </row>
     <row r="51" spans="2:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P51" s="48" t="s">
+      <c r="P51" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="Q51" s="48"/>
-      <c r="R51" s="48"/>
-      <c r="S51" s="48"/>
-      <c r="T51" s="48"/>
-      <c r="U51" s="48"/>
-      <c r="V51" s="48"/>
-      <c r="W51" s="48"/>
-      <c r="X51" s="48"/>
-      <c r="Y51" s="48"/>
-      <c r="Z51" s="48"/>
-      <c r="AA51" s="48"/>
-      <c r="AB51" s="48"/>
+      <c r="Q51" s="47"/>
+      <c r="R51" s="47"/>
+      <c r="S51" s="47"/>
+      <c r="T51" s="47"/>
+      <c r="U51" s="47"/>
+      <c r="V51" s="47"/>
+      <c r="W51" s="47"/>
+      <c r="X51" s="47"/>
+      <c r="Y51" s="47"/>
+      <c r="Z51" s="47"/>
+      <c r="AA51" s="47"/>
+      <c r="AB51" s="47"/>
     </row>
     <row r="52" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P52" s="12" t="s">
@@ -5909,42 +5910,42 @@
       <c r="T55" s="12"/>
     </row>
     <row r="56" spans="2:29" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O56" s="77" t="s">
+      <c r="O56" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="P56" s="77"/>
-      <c r="Q56" s="77"/>
-      <c r="R56" s="77"/>
-      <c r="S56" s="77"/>
-      <c r="T56" s="77"/>
-      <c r="U56" s="77"/>
-      <c r="V56" s="77"/>
-      <c r="W56" s="77"/>
-      <c r="X56" s="77"/>
-      <c r="Y56" s="77"/>
-      <c r="Z56" s="77"/>
-      <c r="AA56" s="77"/>
-      <c r="AB56" s="77"/>
-      <c r="AC56" s="77"/>
+      <c r="P56" s="76"/>
+      <c r="Q56" s="76"/>
+      <c r="R56" s="76"/>
+      <c r="S56" s="76"/>
+      <c r="T56" s="76"/>
+      <c r="U56" s="76"/>
+      <c r="V56" s="76"/>
+      <c r="W56" s="76"/>
+      <c r="X56" s="76"/>
+      <c r="Y56" s="76"/>
+      <c r="Z56" s="76"/>
+      <c r="AA56" s="76"/>
+      <c r="AB56" s="76"/>
+      <c r="AC56" s="76"/>
     </row>
     <row r="58" spans="2:29" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O58" s="83" t="s">
+      <c r="O58" s="82" t="s">
         <v>88</v>
       </c>
-      <c r="P58" s="83"/>
-      <c r="Q58" s="83"/>
-      <c r="R58" s="83"/>
-      <c r="S58" s="83"/>
-      <c r="T58" s="83"/>
-      <c r="U58" s="83"/>
-      <c r="V58" s="83"/>
-      <c r="W58" s="83"/>
-      <c r="X58" s="83"/>
-      <c r="Y58" s="83"/>
-      <c r="Z58" s="83"/>
-      <c r="AA58" s="83"/>
-      <c r="AB58" s="83"/>
-      <c r="AC58" s="83"/>
+      <c r="P58" s="82"/>
+      <c r="Q58" s="82"/>
+      <c r="R58" s="82"/>
+      <c r="S58" s="82"/>
+      <c r="T58" s="82"/>
+      <c r="U58" s="82"/>
+      <c r="V58" s="82"/>
+      <c r="W58" s="82"/>
+      <c r="X58" s="82"/>
+      <c r="Y58" s="82"/>
+      <c r="Z58" s="82"/>
+      <c r="AA58" s="82"/>
+      <c r="AB58" s="82"/>
+      <c r="AC58" s="82"/>
     </row>
     <row r="59" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
       <c r="O59" s="18"/>
@@ -5964,23 +5965,23 @@
       <c r="AC59" s="17"/>
     </row>
     <row r="60" spans="2:29" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O60" s="84" t="s">
-        <v>177</v>
-      </c>
-      <c r="P60" s="84"/>
-      <c r="Q60" s="84"/>
-      <c r="R60" s="84"/>
-      <c r="S60" s="84"/>
-      <c r="T60" s="84"/>
-      <c r="U60" s="84"/>
-      <c r="V60" s="84"/>
-      <c r="W60" s="84"/>
-      <c r="X60" s="84"/>
-      <c r="Y60" s="84"/>
-      <c r="Z60" s="84"/>
-      <c r="AA60" s="84"/>
-      <c r="AB60" s="84"/>
-      <c r="AC60" s="84"/>
+      <c r="O60" s="83" t="s">
+        <v>175</v>
+      </c>
+      <c r="P60" s="83"/>
+      <c r="Q60" s="83"/>
+      <c r="R60" s="83"/>
+      <c r="S60" s="83"/>
+      <c r="T60" s="83"/>
+      <c r="U60" s="83"/>
+      <c r="V60" s="83"/>
+      <c r="W60" s="83"/>
+      <c r="X60" s="83"/>
+      <c r="Y60" s="83"/>
+      <c r="Z60" s="83"/>
+      <c r="AA60" s="83"/>
+      <c r="AB60" s="83"/>
+      <c r="AC60" s="83"/>
     </row>
     <row r="62" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="O62" s="8" t="s">
@@ -5991,23 +5992,23 @@
       <c r="O63" s="8"/>
     </row>
     <row r="64" spans="2:29" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O64" s="78" t="s">
-        <v>175</v>
-      </c>
-      <c r="P64" s="64"/>
-      <c r="Q64" s="64"/>
-      <c r="R64" s="64"/>
-      <c r="S64" s="64"/>
-      <c r="T64" s="64"/>
-      <c r="U64" s="64"/>
-      <c r="V64" s="64"/>
-      <c r="W64" s="64"/>
-      <c r="X64" s="64"/>
-      <c r="Y64" s="64"/>
-      <c r="Z64" s="64"/>
-      <c r="AA64" s="64"/>
-      <c r="AB64" s="64"/>
-      <c r="AC64" s="64"/>
+      <c r="O64" s="77" t="s">
+        <v>173</v>
+      </c>
+      <c r="P64" s="63"/>
+      <c r="Q64" s="63"/>
+      <c r="R64" s="63"/>
+      <c r="S64" s="63"/>
+      <c r="T64" s="63"/>
+      <c r="U64" s="63"/>
+      <c r="V64" s="63"/>
+      <c r="W64" s="63"/>
+      <c r="X64" s="63"/>
+      <c r="Y64" s="63"/>
+      <c r="Z64" s="63"/>
+      <c r="AA64" s="63"/>
+      <c r="AB64" s="63"/>
+      <c r="AC64" s="63"/>
     </row>
     <row r="65" spans="15:29" ht="19.5" x14ac:dyDescent="0.25">
       <c r="O65" s="18"/>
@@ -6027,42 +6028,42 @@
       <c r="AC65" s="17"/>
     </row>
     <row r="66" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O66" s="86" t="s">
+      <c r="O66" s="85" t="s">
         <v>75</v>
       </c>
-      <c r="P66" s="86"/>
-      <c r="Q66" s="86"/>
-      <c r="R66" s="86"/>
-      <c r="S66" s="86"/>
-      <c r="T66" s="85"/>
-      <c r="U66" s="85"/>
-      <c r="V66" s="85"/>
-      <c r="W66" s="85"/>
-      <c r="X66" s="85"/>
-      <c r="Y66" s="85"/>
-      <c r="Z66" s="85"/>
-      <c r="AA66" s="85"/>
-      <c r="AB66" s="85"/>
-      <c r="AC66" s="85"/>
+      <c r="P66" s="85"/>
+      <c r="Q66" s="85"/>
+      <c r="R66" s="85"/>
+      <c r="S66" s="85"/>
+      <c r="T66" s="84"/>
+      <c r="U66" s="84"/>
+      <c r="V66" s="84"/>
+      <c r="W66" s="84"/>
+      <c r="X66" s="84"/>
+      <c r="Y66" s="84"/>
+      <c r="Z66" s="84"/>
+      <c r="AA66" s="84"/>
+      <c r="AB66" s="84"/>
+      <c r="AC66" s="84"/>
     </row>
     <row r="67" spans="15:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O67" s="77" t="s">
+      <c r="O67" s="76" t="s">
         <v>76</v>
       </c>
-      <c r="P67" s="48"/>
-      <c r="Q67" s="48"/>
-      <c r="R67" s="48"/>
-      <c r="S67" s="48"/>
-      <c r="T67" s="48"/>
-      <c r="U67" s="48"/>
-      <c r="V67" s="48"/>
-      <c r="W67" s="48"/>
-      <c r="X67" s="48"/>
-      <c r="Y67" s="48"/>
-      <c r="Z67" s="48"/>
-      <c r="AA67" s="48"/>
-      <c r="AB67" s="48"/>
-      <c r="AC67" s="48"/>
+      <c r="P67" s="47"/>
+      <c r="Q67" s="47"/>
+      <c r="R67" s="47"/>
+      <c r="S67" s="47"/>
+      <c r="T67" s="47"/>
+      <c r="U67" s="47"/>
+      <c r="V67" s="47"/>
+      <c r="W67" s="47"/>
+      <c r="X67" s="47"/>
+      <c r="Y67" s="47"/>
+      <c r="Z67" s="47"/>
+      <c r="AA67" s="47"/>
+      <c r="AB67" s="47"/>
+      <c r="AC67" s="47"/>
     </row>
     <row r="68" spans="15:29" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="O68" s="12" t="s">
@@ -6070,42 +6071,42 @@
       </c>
     </row>
     <row r="69" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O69" s="86" t="s">
+      <c r="O69" s="85" t="s">
         <v>77</v>
       </c>
-      <c r="P69" s="86"/>
-      <c r="Q69" s="86"/>
-      <c r="R69" s="86"/>
-      <c r="S69" s="86"/>
-      <c r="T69" s="85"/>
-      <c r="U69" s="85"/>
-      <c r="V69" s="85"/>
-      <c r="W69" s="85"/>
-      <c r="X69" s="85"/>
-      <c r="Y69" s="85"/>
-      <c r="Z69" s="85"/>
-      <c r="AA69" s="85"/>
-      <c r="AB69" s="85"/>
-      <c r="AC69" s="85"/>
+      <c r="P69" s="85"/>
+      <c r="Q69" s="85"/>
+      <c r="R69" s="85"/>
+      <c r="S69" s="85"/>
+      <c r="T69" s="84"/>
+      <c r="U69" s="84"/>
+      <c r="V69" s="84"/>
+      <c r="W69" s="84"/>
+      <c r="X69" s="84"/>
+      <c r="Y69" s="84"/>
+      <c r="Z69" s="84"/>
+      <c r="AA69" s="84"/>
+      <c r="AB69" s="84"/>
+      <c r="AC69" s="84"/>
     </row>
     <row r="70" spans="15:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O70" s="77" t="s">
+      <c r="O70" s="76" t="s">
         <v>78</v>
       </c>
-      <c r="P70" s="77"/>
-      <c r="Q70" s="77"/>
-      <c r="R70" s="77"/>
-      <c r="S70" s="77"/>
-      <c r="T70" s="77"/>
-      <c r="U70" s="77"/>
-      <c r="V70" s="77"/>
-      <c r="W70" s="77"/>
-      <c r="X70" s="77"/>
-      <c r="Y70" s="77"/>
-      <c r="Z70" s="77"/>
-      <c r="AA70" s="77"/>
-      <c r="AB70" s="77"/>
-      <c r="AC70" s="77"/>
+      <c r="P70" s="76"/>
+      <c r="Q70" s="76"/>
+      <c r="R70" s="76"/>
+      <c r="S70" s="76"/>
+      <c r="T70" s="76"/>
+      <c r="U70" s="76"/>
+      <c r="V70" s="76"/>
+      <c r="W70" s="76"/>
+      <c r="X70" s="76"/>
+      <c r="Y70" s="76"/>
+      <c r="Z70" s="76"/>
+      <c r="AA70" s="76"/>
+      <c r="AB70" s="76"/>
+      <c r="AC70" s="76"/>
     </row>
     <row r="71" spans="15:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="O71" s="12" t="s">
@@ -6167,129 +6168,129 @@
     </row>
     <row r="4" spans="1:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75" t="s">
-        <v>146</v>
-      </c>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
+      <c r="B4" s="74" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
     </row>
     <row r="5" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="L5" s="57" t="s">
-        <v>132</v>
-      </c>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="57"/>
-      <c r="P5" s="57"/>
+      <c r="L5" s="56" t="s">
+        <v>130</v>
+      </c>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="56"/>
     </row>
     <row r="6" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
-      <c r="L6" s="74" t="s">
-        <v>123</v>
-      </c>
-      <c r="M6" s="74"/>
-      <c r="N6" s="74"/>
-      <c r="O6" s="74"/>
-      <c r="P6" s="74"/>
+      <c r="L6" s="73" t="s">
+        <v>121</v>
+      </c>
+      <c r="M6" s="73"/>
+      <c r="N6" s="73"/>
+      <c r="O6" s="73"/>
+      <c r="P6" s="73"/>
     </row>
     <row r="7" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
-      <c r="L7" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
+      <c r="L7" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="35"/>
     </row>
     <row r="8" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
-      <c r="L8" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="M8" s="74"/>
-      <c r="N8" s="74"/>
-      <c r="O8" s="74"/>
-      <c r="P8" s="74"/>
+      <c r="L8" s="73" t="s">
+        <v>123</v>
+      </c>
+      <c r="M8" s="73"/>
+      <c r="N8" s="73"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="73"/>
     </row>
     <row r="9" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1"/>
-      <c r="L9" s="74" t="s">
-        <v>126</v>
-      </c>
-      <c r="M9" s="74"/>
-      <c r="N9" s="74"/>
-      <c r="O9" s="74"/>
-      <c r="P9" s="74"/>
+      <c r="L9" s="73" t="s">
+        <v>124</v>
+      </c>
+      <c r="M9" s="73"/>
+      <c r="N9" s="73"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="73"/>
     </row>
     <row r="10" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
-      <c r="L10" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
+      <c r="L10" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="M10" s="35"/>
+      <c r="N10" s="35"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="35"/>
     </row>
     <row r="11" spans="1:31" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
-      <c r="L11" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="M11" s="74"/>
-      <c r="N11" s="74"/>
-      <c r="O11" s="74"/>
-      <c r="P11" s="74"/>
+      <c r="L11" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="M11" s="73"/>
+      <c r="N11" s="73"/>
+      <c r="O11" s="73"/>
+      <c r="P11" s="73"/>
     </row>
     <row r="12" spans="1:31" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1"/>
-      <c r="L12" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="R12" s="73" t="s">
-        <v>141</v>
-      </c>
-      <c r="S12" s="73"/>
-      <c r="T12" s="73"/>
-      <c r="U12" s="73"/>
-      <c r="V12" s="73"/>
-      <c r="W12" s="73"/>
-      <c r="X12" s="73"/>
-      <c r="Y12" s="73"/>
-      <c r="Z12" s="73"/>
-      <c r="AA12" s="73"/>
-      <c r="AB12" s="73"/>
-      <c r="AC12" s="73"/>
-      <c r="AD12" s="89"/>
-      <c r="AE12" s="89"/>
+      <c r="L12" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35"/>
+      <c r="R12" s="72" t="s">
+        <v>139</v>
+      </c>
+      <c r="S12" s="72"/>
+      <c r="T12" s="72"/>
+      <c r="U12" s="72"/>
+      <c r="V12" s="72"/>
+      <c r="W12" s="72"/>
+      <c r="X12" s="72"/>
+      <c r="Y12" s="72"/>
+      <c r="Z12" s="72"/>
+      <c r="AA12" s="72"/>
+      <c r="AB12" s="72"/>
+      <c r="AC12" s="72"/>
+      <c r="AD12" s="88"/>
+      <c r="AE12" s="88"/>
     </row>
     <row r="13" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
-      <c r="L13" s="74" t="s">
-        <v>130</v>
-      </c>
-      <c r="M13" s="74"/>
-      <c r="N13" s="74"/>
-      <c r="O13" s="74"/>
-      <c r="P13" s="74"/>
+      <c r="L13" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="M13" s="73"/>
+      <c r="N13" s="73"/>
+      <c r="O13" s="73"/>
+      <c r="P13" s="73"/>
     </row>
     <row r="14" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A14" s="1"/>
-      <c r="L14" s="74" t="s">
-        <v>131</v>
-      </c>
-      <c r="M14" s="74"/>
-      <c r="N14" s="74"/>
-      <c r="O14" s="74"/>
-      <c r="P14" s="74"/>
+      <c r="L14" s="73" t="s">
+        <v>129</v>
+      </c>
+      <c r="M14" s="73"/>
+      <c r="N14" s="73"/>
+      <c r="O14" s="73"/>
+      <c r="P14" s="73"/>
     </row>
     <row r="15" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
@@ -6300,67 +6301,67 @@
     </row>
     <row r="17" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A17" s="1"/>
-      <c r="L17" s="57" t="s">
+      <c r="L17" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="M17" s="56"/>
+      <c r="N17" s="56"/>
+      <c r="O17" s="56" t="s">
         <v>133</v>
       </c>
-      <c r="M17" s="57"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="57" t="s">
-        <v>135</v>
-      </c>
-      <c r="P17" s="57"/>
-      <c r="Q17" s="57"/>
-      <c r="R17" s="57"/>
-      <c r="S17" s="57"/>
-      <c r="T17" s="57"/>
+      <c r="P17" s="56"/>
+      <c r="Q17" s="56"/>
+      <c r="R17" s="56"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="56"/>
     </row>
     <row r="18" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
-      <c r="L18" s="62" t="s">
-        <v>136</v>
-      </c>
-      <c r="M18" s="62"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="72" t="s">
+      <c r="L18" s="61" t="s">
         <v>134</v>
       </c>
-      <c r="P18" s="72"/>
-      <c r="Q18" s="72"/>
-      <c r="R18" s="72"/>
-      <c r="S18" s="72"/>
-      <c r="T18" s="72"/>
+      <c r="M18" s="61"/>
+      <c r="N18" s="61"/>
+      <c r="O18" s="71" t="s">
+        <v>132</v>
+      </c>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="71"/>
+      <c r="S18" s="71"/>
+      <c r="T18" s="71"/>
     </row>
     <row r="19" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
-      <c r="L19" s="62" t="s">
-        <v>137</v>
-      </c>
-      <c r="M19" s="62"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="72" t="s">
-        <v>138</v>
-      </c>
-      <c r="P19" s="72"/>
-      <c r="Q19" s="72"/>
-      <c r="R19" s="72"/>
-      <c r="S19" s="72"/>
-      <c r="T19" s="72"/>
+      <c r="L19" s="61" t="s">
+        <v>135</v>
+      </c>
+      <c r="M19" s="61"/>
+      <c r="N19" s="61"/>
+      <c r="O19" s="71" t="s">
+        <v>136</v>
+      </c>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="71"/>
+      <c r="S19" s="71"/>
+      <c r="T19" s="71"/>
     </row>
     <row r="20" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
-      <c r="L20" s="62" t="s">
-        <v>139</v>
-      </c>
-      <c r="M20" s="62"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="72" t="s">
-        <v>140</v>
-      </c>
-      <c r="P20" s="72"/>
-      <c r="Q20" s="72"/>
-      <c r="R20" s="72"/>
-      <c r="S20" s="72"/>
-      <c r="T20" s="72"/>
+      <c r="L20" s="61" t="s">
+        <v>137</v>
+      </c>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="71" t="s">
+        <v>138</v>
+      </c>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="71"/>
+      <c r="S20" s="71"/>
+      <c r="T20" s="71"/>
     </row>
     <row r="21" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A21" s="1"/>
@@ -6378,7 +6379,7 @@
     </row>
     <row r="25" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B25" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
@@ -6386,12 +6387,12 @@
     </row>
     <row r="27" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B27" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="56" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B56" s="20" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
@@ -6399,17 +6400,17 @@
     </row>
     <row r="58" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="85" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B85" s="20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="87" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B87" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="88" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
@@ -6417,42 +6418,42 @@
     </row>
     <row r="89" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B89" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="91" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B91" s="20" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="93" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B93" s="24" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="94" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B94" s="24" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="95" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B95" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="97" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B97" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="99" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B99" s="20" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="101" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B101" s="20" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="102" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
@@ -6460,52 +6461,52 @@
     </row>
     <row r="103" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B103" s="20" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="105" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B105" s="71" t="s">
-        <v>155</v>
-      </c>
-      <c r="C105" s="71"/>
-      <c r="D105" s="71"/>
-      <c r="E105" s="71"/>
-      <c r="F105" s="71"/>
-      <c r="G105" s="71"/>
-      <c r="H105" s="71"/>
-      <c r="I105" s="71"/>
-      <c r="J105" s="71"/>
-      <c r="K105" s="71"/>
-      <c r="L105" s="71"/>
-      <c r="M105" s="71"/>
-      <c r="N105" s="71"/>
-      <c r="O105" s="71"/>
-      <c r="P105" s="71"/>
-      <c r="Q105" s="71"/>
-      <c r="R105" s="71"/>
-      <c r="S105" s="71"/>
-      <c r="T105" s="71"/>
-      <c r="U105" s="71"/>
-      <c r="V105" s="71"/>
-      <c r="W105" s="71"/>
-      <c r="X105" s="71"/>
-      <c r="Y105" s="71"/>
+      <c r="B105" s="70" t="s">
+        <v>153</v>
+      </c>
+      <c r="C105" s="70"/>
+      <c r="D105" s="70"/>
+      <c r="E105" s="70"/>
+      <c r="F105" s="70"/>
+      <c r="G105" s="70"/>
+      <c r="H105" s="70"/>
+      <c r="I105" s="70"/>
+      <c r="J105" s="70"/>
+      <c r="K105" s="70"/>
+      <c r="L105" s="70"/>
+      <c r="M105" s="70"/>
+      <c r="N105" s="70"/>
+      <c r="O105" s="70"/>
+      <c r="P105" s="70"/>
+      <c r="Q105" s="70"/>
+      <c r="R105" s="70"/>
+      <c r="S105" s="70"/>
+      <c r="T105" s="70"/>
+      <c r="U105" s="70"/>
+      <c r="V105" s="70"/>
+      <c r="W105" s="70"/>
+      <c r="X105" s="70"/>
+      <c r="Y105" s="70"/>
     </row>
     <row r="108" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A108" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="110" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B110" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C110" s="8"/>
       <c r="D110" s="25"/>
     </row>
     <row r="112" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B112" s="20" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="113" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
@@ -6513,49 +6514,49 @@
     </row>
     <row r="114" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B114" s="20" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="116" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B116" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="118" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B118" s="76" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="118" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="77" t="s">
-        <v>165</v>
-      </c>
-      <c r="C118" s="77"/>
-      <c r="D118" s="77"/>
-      <c r="E118" s="77"/>
-      <c r="F118" s="77"/>
-      <c r="G118" s="77"/>
-      <c r="H118" s="77"/>
-      <c r="I118" s="77"/>
-      <c r="J118" s="77"/>
-      <c r="K118" s="77"/>
-      <c r="L118" s="77"/>
-      <c r="M118" s="77"/>
-      <c r="N118" s="77"/>
-      <c r="O118" s="77"/>
-      <c r="P118" s="77"/>
-      <c r="Q118" s="77"/>
-      <c r="R118" s="77"/>
-      <c r="S118" s="77"/>
-      <c r="T118" s="77"/>
-      <c r="U118" s="77"/>
-      <c r="V118" s="77"/>
-      <c r="W118" s="77"/>
-      <c r="X118" s="77"/>
-      <c r="Y118" s="77"/>
-      <c r="Z118" s="77"/>
-      <c r="AA118" s="77"/>
-      <c r="AB118" s="77"/>
-      <c r="AC118" s="77"/>
+      <c r="C118" s="76"/>
+      <c r="D118" s="76"/>
+      <c r="E118" s="76"/>
+      <c r="F118" s="76"/>
+      <c r="G118" s="76"/>
+      <c r="H118" s="76"/>
+      <c r="I118" s="76"/>
+      <c r="J118" s="76"/>
+      <c r="K118" s="76"/>
+      <c r="L118" s="76"/>
+      <c r="M118" s="76"/>
+      <c r="N118" s="76"/>
+      <c r="O118" s="76"/>
+      <c r="P118" s="76"/>
+      <c r="Q118" s="76"/>
+      <c r="R118" s="76"/>
+      <c r="S118" s="76"/>
+      <c r="T118" s="76"/>
+      <c r="U118" s="76"/>
+      <c r="V118" s="76"/>
+      <c r="W118" s="76"/>
+      <c r="X118" s="76"/>
+      <c r="Y118" s="76"/>
+      <c r="Z118" s="76"/>
+      <c r="AA118" s="76"/>
+      <c r="AB118" s="76"/>
+      <c r="AC118" s="76"/>
     </row>
     <row r="119" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B119" s="26" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="120" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
@@ -6563,15 +6564,15 @@
     </row>
     <row r="121" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B121" s="20" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="122" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B122" s="20"/>
     </row>
     <row r="123" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B123" s="76" t="s">
-        <v>240</v>
+      <c r="B123" s="75" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="124" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
@@ -6579,30 +6580,30 @@
     </row>
     <row r="125" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B125" s="20" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="127" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B127" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="129" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B129" s="20" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="131" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B131" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="133" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B133" s="20" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L133" s="27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M133" s="20"/>
     </row>
@@ -6645,802 +6646,829 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A2:U26"/>
+  <dimension ref="A2:W27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="C4" s="28"/>
+      <c r="D4" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="42"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28" t="s">
         <v>239</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" s="43"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="U4" s="29"/>
+      <c r="U4" s="28"/>
     </row>
     <row r="5" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="C5" s="29"/>
+      <c r="D5" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="31"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" s="33"/>
+      <c r="I5" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="J5" s="34"/>
+      <c r="K5" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
+      <c r="P5" s="35"/>
+      <c r="Q5" s="35"/>
+      <c r="R5" s="35"/>
+      <c r="S5" s="35"/>
+      <c r="T5" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U5" s="92"/>
+    </row>
+    <row r="6" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B6" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="29"/>
+      <c r="D6" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="31"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" s="36"/>
+      <c r="I6" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="J6" s="34"/>
+      <c r="K6" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="35"/>
+      <c r="S6" s="35"/>
+      <c r="T6" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U6" s="92"/>
+    </row>
+    <row r="7" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="C7" s="29"/>
+      <c r="D7" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="31"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="33"/>
+      <c r="I7" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="J7" s="34"/>
+      <c r="K7" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="35"/>
+      <c r="S7" s="35"/>
+      <c r="T7" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U7" s="92"/>
+    </row>
+    <row r="8" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="29"/>
+      <c r="D8" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8" s="33"/>
+      <c r="I8" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="J8" s="34"/>
+      <c r="K8" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U8" s="92"/>
+    </row>
+    <row r="9" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="29" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" s="29"/>
+      <c r="D9" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="33"/>
+      <c r="I9" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" s="34"/>
+      <c r="K9" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="35"/>
+      <c r="S9" s="35"/>
+      <c r="T9" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U9" s="92"/>
+    </row>
+    <row r="10" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="29"/>
+      <c r="D10" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="31"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="33"/>
+      <c r="I10" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="J10" s="34"/>
+      <c r="K10" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="35"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="35"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="35"/>
+      <c r="Q10" s="35"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="35"/>
+      <c r="T10" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U10" s="92"/>
+    </row>
+    <row r="11" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="29"/>
+      <c r="D11" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="31"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="33"/>
+      <c r="I11" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="J11" s="34"/>
+      <c r="K11" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="35"/>
+      <c r="S11" s="35"/>
+      <c r="T11" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U11" s="92"/>
+    </row>
+    <row r="12" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="C12" s="29"/>
+      <c r="D12" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="39"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="33"/>
+      <c r="I12" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="J12" s="34"/>
+      <c r="K12" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="35"/>
+      <c r="S12" s="35"/>
+      <c r="T12" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U12" s="92"/>
+    </row>
+    <row r="13" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" s="32"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="34" t="s">
+      <c r="C13" s="29"/>
+      <c r="D13" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="31"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="H5" s="34"/>
-      <c r="I5" s="35" t="s">
+      <c r="H13" s="33"/>
+      <c r="I13" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="J5" s="35"/>
-      <c r="K5" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U5" s="28"/>
-    </row>
-    <row r="6" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B6" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="E6" s="32"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="37" t="s">
+      <c r="J13" s="34"/>
+      <c r="K13" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="35"/>
+      <c r="S13" s="35"/>
+      <c r="T13" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U13" s="92"/>
+    </row>
+    <row r="14" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" s="31"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="33"/>
+      <c r="I14" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="J14" s="34"/>
+      <c r="K14" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U14" s="92"/>
+    </row>
+    <row r="15" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" s="29"/>
+      <c r="D15" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="31"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="33"/>
+      <c r="I15" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="J15" s="34"/>
+      <c r="K15" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="35"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U15" s="92"/>
+    </row>
+    <row r="16" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C16" s="29"/>
+      <c r="D16" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="31"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="33"/>
+      <c r="I16" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="J16" s="34"/>
+      <c r="K16" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U16" s="92"/>
+    </row>
+    <row r="17" spans="2:23" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B17" s="29" t="s">
+        <v>195</v>
+      </c>
+      <c r="C17" s="29"/>
+      <c r="D17" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="31"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="H6" s="37"/>
-      <c r="I6" s="35" t="s">
+      <c r="H17" s="36"/>
+      <c r="I17" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="J6" s="35"/>
-      <c r="K6" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U6" s="28"/>
-    </row>
-    <row r="7" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="30" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="32"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="H7" s="34"/>
-      <c r="I7" s="35" t="s">
+      <c r="J17" s="34"/>
+      <c r="K17" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="35"/>
+      <c r="T17" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U17" s="92"/>
+    </row>
+    <row r="18" spans="2:23" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B18" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="C18" s="29"/>
+      <c r="D18" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="31"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="36"/>
+      <c r="I18" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="J7" s="35"/>
-      <c r="K7" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
-      <c r="S7" s="36"/>
-      <c r="T7" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U7" s="28"/>
-    </row>
-    <row r="8" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="H8" s="34"/>
-      <c r="I8" s="35" t="s">
+      <c r="J18" s="34"/>
+      <c r="K18" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="35"/>
+      <c r="T18" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U18" s="92"/>
+    </row>
+    <row r="19" spans="2:23" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B19" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" s="29"/>
+      <c r="D19" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" s="31"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="36"/>
+      <c r="I19" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="J8" s="35"/>
-      <c r="K8" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
-      <c r="S8" s="36"/>
-      <c r="T8" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U8" s="28"/>
-    </row>
-    <row r="9" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="32"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="34"/>
-      <c r="I9" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="J9" s="35"/>
-      <c r="K9" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
-      <c r="S9" s="36"/>
-      <c r="T9" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U9" s="28"/>
-    </row>
-    <row r="10" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="H10" s="34"/>
-      <c r="I10" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="J10" s="35"/>
-      <c r="K10" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="L10" s="36"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
-      <c r="S10" s="36"/>
-      <c r="T10" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U10" s="28"/>
-    </row>
-    <row r="11" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="H11" s="34"/>
-      <c r="I11" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="J11" s="35"/>
-      <c r="K11" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
-      <c r="S11" s="36"/>
-      <c r="T11" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U11" s="28"/>
-    </row>
-    <row r="12" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="39" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12" s="40"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="H12" s="34"/>
-      <c r="I12" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="J12" s="35"/>
-      <c r="K12" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
-      <c r="S12" s="36"/>
-      <c r="T12" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U12" s="28"/>
-    </row>
-    <row r="13" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B13" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="E13" s="32"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" s="34"/>
-      <c r="I13" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="J13" s="35"/>
-      <c r="K13" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
-      <c r="S13" s="36"/>
-      <c r="T13" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U13" s="28"/>
-    </row>
-    <row r="14" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="30" t="s">
-        <v>188</v>
-      </c>
-      <c r="C14" s="30"/>
-      <c r="D14" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="H14" s="34"/>
-      <c r="I14" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="J14" s="35"/>
-      <c r="K14" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="L14" s="36"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
-      <c r="S14" s="36"/>
-      <c r="T14" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U14" s="28"/>
-    </row>
-    <row r="15" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" s="32"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="H15" s="34"/>
-      <c r="I15" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="J15" s="35"/>
-      <c r="K15" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="L15" s="36"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
-      <c r="S15" s="36"/>
-      <c r="T15" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U15" s="28"/>
-    </row>
-    <row r="16" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="31" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="H16" s="34"/>
-      <c r="I16" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="J16" s="35"/>
-      <c r="K16" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="L16" s="36"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
-      <c r="S16" s="36"/>
-      <c r="T16" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U16" s="28"/>
-    </row>
-    <row r="17" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B17" s="30" t="s">
+      <c r="J19" s="34"/>
+      <c r="K19" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="35"/>
+      <c r="T19" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U19" s="92"/>
+    </row>
+    <row r="20" spans="2:23" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B20" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="C17" s="30"/>
-      <c r="D17" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="E17" s="32"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="37" t="s">
+      <c r="C20" s="29"/>
+      <c r="D20" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="31"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="H17" s="37"/>
-      <c r="I17" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="J17" s="35"/>
-      <c r="K17" s="36" t="s">
+      <c r="H20" s="36"/>
+      <c r="I20" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="37"/>
+      <c r="K20" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="L17" s="36"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36"/>
-      <c r="T17" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U17" s="28"/>
-    </row>
-    <row r="18" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B18" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="E18" s="32"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="37" t="s">
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="35"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="35"/>
+      <c r="T20" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U20" s="92"/>
+    </row>
+    <row r="21" spans="2:23" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B21" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="C21" s="29"/>
+      <c r="D21" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="31"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="H18" s="37"/>
-      <c r="I18" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="J18" s="35"/>
-      <c r="K18" s="36" t="s">
+      <c r="H21" s="36"/>
+      <c r="I21" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="37"/>
+      <c r="K21" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="L18" s="36"/>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
-      <c r="S18" s="36"/>
-      <c r="T18" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U18" s="28"/>
-    </row>
-    <row r="19" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B19" s="30" t="s">
-        <v>198</v>
-      </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="E19" s="32"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="37" t="s">
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="35"/>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="35"/>
+      <c r="S21" s="35"/>
+      <c r="T21" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U21" s="92"/>
+    </row>
+    <row r="22" spans="2:23" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B22" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="C22" s="29"/>
+      <c r="D22" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="31"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="H19" s="37"/>
-      <c r="I19" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="J19" s="35"/>
-      <c r="K19" s="36" t="s">
+      <c r="H22" s="36"/>
+      <c r="I22" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="37"/>
+      <c r="K22" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="L19" s="36"/>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
-      <c r="S19" s="36"/>
-      <c r="T19" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U19" s="28"/>
-    </row>
-    <row r="20" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B20" s="30" t="s">
-        <v>199</v>
-      </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="E20" s="32"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="37" t="s">
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="35"/>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="35"/>
+      <c r="S22" s="35"/>
+      <c r="T22" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U22" s="92"/>
+    </row>
+    <row r="23" spans="2:23" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B23" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="C23" s="29"/>
+      <c r="D23" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="31"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="H20" s="37"/>
-      <c r="I20" s="38" t="s">
+      <c r="H23" s="36"/>
+      <c r="I23" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="J20" s="38"/>
-      <c r="K20" s="36" t="s">
+      <c r="J23" s="37"/>
+      <c r="K23" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="L20" s="36"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
-      <c r="S20" s="36"/>
-      <c r="T20" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U20" s="28"/>
-    </row>
-    <row r="21" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B21" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" s="32"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="37" t="s">
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="35"/>
+      <c r="S23" s="35"/>
+      <c r="T23" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U23" s="92"/>
+    </row>
+    <row r="24" spans="2:23" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B24" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="C24" s="29"/>
+      <c r="D24" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" s="31"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="H21" s="37"/>
-      <c r="I21" s="38" t="s">
+      <c r="H24" s="36"/>
+      <c r="I24" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="J21" s="38"/>
-      <c r="K21" s="36" t="s">
+      <c r="J24" s="37"/>
+      <c r="K24" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
-      <c r="S21" s="36"/>
-      <c r="T21" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U21" s="28"/>
-    </row>
-    <row r="22" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B22" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="C22" s="30"/>
-      <c r="D22" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="E22" s="32"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="37" t="s">
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="35"/>
+      <c r="Q24" s="35"/>
+      <c r="R24" s="35"/>
+      <c r="S24" s="35"/>
+      <c r="T24" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U24" s="92"/>
+    </row>
+    <row r="25" spans="2:23" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B25" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="C25" s="29"/>
+      <c r="D25" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="E25" s="31"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="H22" s="37"/>
-      <c r="I22" s="38" t="s">
+      <c r="H25" s="36"/>
+      <c r="I25" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="J22" s="38"/>
-      <c r="K22" s="36" t="s">
+      <c r="J25" s="37"/>
+      <c r="K25" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="L22" s="36"/>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
-      <c r="S22" s="36"/>
-      <c r="T22" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U22" s="28"/>
-    </row>
-    <row r="23" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B23" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="C23" s="30"/>
-      <c r="D23" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="E23" s="32"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="37" t="s">
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="35"/>
+      <c r="Q25" s="35"/>
+      <c r="R25" s="35"/>
+      <c r="S25" s="35"/>
+      <c r="T25" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U25" s="92"/>
+    </row>
+    <row r="26" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="C26" s="29"/>
+      <c r="D26" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26" s="31"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="H23" s="37"/>
-      <c r="I23" s="38" t="s">
+      <c r="H26" s="36"/>
+      <c r="I26" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="J23" s="38"/>
-      <c r="K23" s="36" t="s">
+      <c r="J26" s="37"/>
+      <c r="K26" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="L23" s="36"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
-      <c r="O23" s="36"/>
-      <c r="P23" s="36"/>
-      <c r="Q23" s="36"/>
-      <c r="R23" s="36"/>
-      <c r="S23" s="36"/>
-      <c r="T23" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U23" s="28"/>
-    </row>
-    <row r="24" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B24" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="C24" s="30"/>
-      <c r="D24" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" s="32"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="H24" s="37"/>
-      <c r="I24" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="38"/>
-      <c r="K24" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="L24" s="36"/>
-      <c r="M24" s="36"/>
-      <c r="N24" s="36"/>
-      <c r="O24" s="36"/>
-      <c r="P24" s="36"/>
-      <c r="Q24" s="36"/>
-      <c r="R24" s="36"/>
-      <c r="S24" s="36"/>
-      <c r="T24" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U24" s="28"/>
-    </row>
-    <row r="25" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B25" s="30" t="s">
-        <v>204</v>
-      </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="E25" s="32"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="H25" s="37"/>
-      <c r="I25" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="38"/>
-      <c r="K25" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="L25" s="36"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="36"/>
-      <c r="O25" s="36"/>
-      <c r="P25" s="36"/>
-      <c r="Q25" s="36"/>
-      <c r="R25" s="36"/>
-      <c r="S25" s="36"/>
-      <c r="T25" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U25" s="28"/>
-    </row>
-    <row r="26" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B26" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="C26" s="30"/>
-      <c r="D26" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="E26" s="32"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="H26" s="37"/>
-      <c r="I26" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="38"/>
-      <c r="K26" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="L26" s="36"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="36"/>
-      <c r="O26" s="36"/>
-      <c r="P26" s="36"/>
-      <c r="Q26" s="36"/>
-      <c r="R26" s="36"/>
-      <c r="S26" s="36"/>
-      <c r="T26" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="U26" s="28"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="35"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="35"/>
+      <c r="Q26" s="35"/>
+      <c r="R26" s="35"/>
+      <c r="S26" s="35"/>
+      <c r="T26" s="92" t="s">
+        <v>240</v>
+      </c>
+      <c r="U26" s="92"/>
+    </row>
+    <row r="27" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="V27" s="91"/>
+      <c r="W27" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="138">
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="T26:U26"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="T17:U17"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="D4:F4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="T8:U8"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="B9:C9"/>
@@ -7534,12 +7562,6 @@
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="T9:U9"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="G16:H16"/>
@@ -7558,31 +7580,26 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="G6:H6"/>
-    <mergeCell ref="T24:U24"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="T26:U26"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="T18:U18"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
+  <conditionalFormatting sqref="T5:U5">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:J26" xr:uid="{EBCDB7CB-9B76-4496-A9FD-E13B8548471C}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T5:U26" xr:uid="{B5CE3419-EDB4-4E48-ADC1-5B4DD80F50CD}">
-      <formula1>"Đã có, Chưa, Bỏ, Cân nhắc"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T5:U26" xr:uid="{1261FD57-5C4E-4608-A621-9535D2C1ADDD}">
+      <formula1>"Sẵn sàng, Đang Render, Chưa có"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7599,67 +7616,67 @@
   <sheetData>
     <row r="2" spans="1:16" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P10" s="75" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="21" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P21" s="75" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="P10" s="76" t="s">
+    <row r="22" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P22" s="90" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="21" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="P21" s="76" t="s">
+    <row r="24" spans="2:28" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P24" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q24" s="76"/>
+      <c r="R24" s="76"/>
+      <c r="S24" s="76"/>
+      <c r="T24" s="76"/>
+      <c r="U24" s="76"/>
+      <c r="V24" s="76"/>
+      <c r="W24" s="76"/>
+      <c r="X24" s="76"/>
+      <c r="Y24" s="76"/>
+      <c r="Z24" s="76"/>
+      <c r="AA24" s="76"/>
+      <c r="AB24" s="76"/>
+    </row>
+    <row r="26" spans="2:28" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P26" s="76" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="22" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="P22" s="91" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="24" spans="2:28" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P24" s="77" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q24" s="77"/>
-      <c r="R24" s="77"/>
-      <c r="S24" s="77"/>
-      <c r="T24" s="77"/>
-      <c r="U24" s="77"/>
-      <c r="V24" s="77"/>
-      <c r="W24" s="77"/>
-      <c r="X24" s="77"/>
-      <c r="Y24" s="77"/>
-      <c r="Z24" s="77"/>
-      <c r="AA24" s="77"/>
-      <c r="AB24" s="77"/>
-    </row>
-    <row r="26" spans="2:28" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P26" s="77" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q26" s="77"/>
-      <c r="R26" s="77"/>
-      <c r="S26" s="77"/>
-      <c r="T26" s="77"/>
-      <c r="U26" s="77"/>
-      <c r="V26" s="77"/>
-      <c r="W26" s="77"/>
-      <c r="X26" s="77"/>
-      <c r="Y26" s="77"/>
-      <c r="Z26" s="77"/>
-      <c r="AA26" s="77"/>
-      <c r="AB26" s="77"/>
+      <c r="Q26" s="76"/>
+      <c r="R26" s="76"/>
+      <c r="S26" s="76"/>
+      <c r="T26" s="76"/>
+      <c r="U26" s="76"/>
+      <c r="V26" s="76"/>
+      <c r="W26" s="76"/>
+      <c r="X26" s="76"/>
+      <c r="Y26" s="76"/>
+      <c r="Z26" s="76"/>
+      <c r="AA26" s="76"/>
+      <c r="AB26" s="76"/>
     </row>
     <row r="27" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7667,899 +7684,899 @@
     </row>
     <row r="31" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B33" s="8" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="77" t="s">
+      <c r="B35" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="C35" s="76"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+      <c r="I35" s="76"/>
+      <c r="J35" s="76"/>
+      <c r="K35" s="76"/>
+      <c r="L35" s="76"/>
+      <c r="M35" s="76"/>
+      <c r="N35" s="76"/>
+      <c r="O35" s="76"/>
+      <c r="P35" s="76"/>
+      <c r="Q35" s="76"/>
+      <c r="R35" s="76"/>
+      <c r="S35" s="76"/>
+      <c r="T35" s="76"/>
+      <c r="U35" s="76"/>
+      <c r="V35" s="76"/>
+      <c r="W35" s="76"/>
+      <c r="X35" s="76"/>
+      <c r="Y35" s="76"/>
+      <c r="Z35" s="76"/>
+      <c r="AA35" s="76"/>
+      <c r="AB35" s="76"/>
+    </row>
+    <row r="36" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="C36" s="76"/>
+      <c r="D36" s="76"/>
+      <c r="E36" s="76"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
+      <c r="I36" s="76"/>
+      <c r="J36" s="76"/>
+      <c r="K36" s="76"/>
+      <c r="L36" s="76"/>
+      <c r="M36" s="76"/>
+      <c r="N36" s="76"/>
+      <c r="O36" s="76"/>
+      <c r="P36" s="76"/>
+      <c r="Q36" s="76"/>
+      <c r="R36" s="76"/>
+      <c r="S36" s="76"/>
+      <c r="T36" s="76"/>
+      <c r="U36" s="76"/>
+      <c r="V36" s="76"/>
+      <c r="W36" s="76"/>
+      <c r="X36" s="76"/>
+      <c r="Y36" s="76"/>
+      <c r="Z36" s="76"/>
+      <c r="AA36" s="76"/>
+      <c r="AB36" s="76"/>
+    </row>
+    <row r="37" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="76" t="s">
         <v>216</v>
       </c>
-      <c r="C35" s="77"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
-      <c r="I35" s="77"/>
-      <c r="J35" s="77"/>
-      <c r="K35" s="77"/>
-      <c r="L35" s="77"/>
-      <c r="M35" s="77"/>
-      <c r="N35" s="77"/>
-      <c r="O35" s="77"/>
-      <c r="P35" s="77"/>
-      <c r="Q35" s="77"/>
-      <c r="R35" s="77"/>
-      <c r="S35" s="77"/>
-      <c r="T35" s="77"/>
-      <c r="U35" s="77"/>
-      <c r="V35" s="77"/>
-      <c r="W35" s="77"/>
-      <c r="X35" s="77"/>
-      <c r="Y35" s="77"/>
-      <c r="Z35" s="77"/>
-      <c r="AA35" s="77"/>
-      <c r="AB35" s="77"/>
-    </row>
-    <row r="36" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="77" t="s">
+      <c r="C37" s="76"/>
+      <c r="D37" s="76"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="76"/>
+      <c r="J37" s="76"/>
+      <c r="K37" s="76"/>
+      <c r="L37" s="76"/>
+      <c r="M37" s="76"/>
+      <c r="N37" s="76"/>
+      <c r="O37" s="76"/>
+      <c r="P37" s="76"/>
+      <c r="Q37" s="76"/>
+      <c r="R37" s="76"/>
+      <c r="S37" s="76"/>
+      <c r="T37" s="76"/>
+      <c r="U37" s="76"/>
+      <c r="V37" s="76"/>
+      <c r="W37" s="76"/>
+      <c r="X37" s="76"/>
+      <c r="Y37" s="76"/>
+      <c r="Z37" s="76"/>
+      <c r="AA37" s="76"/>
+      <c r="AB37" s="76"/>
+    </row>
+    <row r="38" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="76" t="s">
         <v>215</v>
       </c>
-      <c r="C36" s="77"/>
-      <c r="D36" s="77"/>
-      <c r="E36" s="77"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
-      <c r="I36" s="77"/>
-      <c r="J36" s="77"/>
-      <c r="K36" s="77"/>
-      <c r="L36" s="77"/>
-      <c r="M36" s="77"/>
-      <c r="N36" s="77"/>
-      <c r="O36" s="77"/>
-      <c r="P36" s="77"/>
-      <c r="Q36" s="77"/>
-      <c r="R36" s="77"/>
-      <c r="S36" s="77"/>
-      <c r="T36" s="77"/>
-      <c r="U36" s="77"/>
-      <c r="V36" s="77"/>
-      <c r="W36" s="77"/>
-      <c r="X36" s="77"/>
-      <c r="Y36" s="77"/>
-      <c r="Z36" s="77"/>
-      <c r="AA36" s="77"/>
-      <c r="AB36" s="77"/>
-    </row>
-    <row r="37" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="77" t="s">
+      <c r="C38" s="76"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="76"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="76"/>
+      <c r="H38" s="76"/>
+      <c r="I38" s="76"/>
+      <c r="J38" s="76"/>
+      <c r="K38" s="76"/>
+      <c r="L38" s="76"/>
+      <c r="M38" s="76"/>
+      <c r="N38" s="76"/>
+      <c r="O38" s="76"/>
+      <c r="P38" s="76"/>
+      <c r="Q38" s="76"/>
+      <c r="R38" s="76"/>
+      <c r="S38" s="76"/>
+      <c r="T38" s="76"/>
+      <c r="U38" s="76"/>
+      <c r="V38" s="76"/>
+      <c r="W38" s="76"/>
+      <c r="X38" s="76"/>
+      <c r="Y38" s="76"/>
+      <c r="Z38" s="76"/>
+      <c r="AA38" s="76"/>
+      <c r="AB38" s="76"/>
+    </row>
+    <row r="39" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="C39" s="76"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="76"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="76"/>
+      <c r="I39" s="76"/>
+      <c r="J39" s="76"/>
+      <c r="K39" s="76"/>
+      <c r="L39" s="76"/>
+      <c r="M39" s="76"/>
+      <c r="N39" s="76"/>
+      <c r="O39" s="76"/>
+      <c r="P39" s="76"/>
+      <c r="Q39" s="76"/>
+      <c r="R39" s="76"/>
+      <c r="S39" s="76"/>
+      <c r="T39" s="76"/>
+      <c r="U39" s="76"/>
+      <c r="V39" s="76"/>
+      <c r="W39" s="76"/>
+      <c r="X39" s="76"/>
+      <c r="Y39" s="76"/>
+      <c r="Z39" s="76"/>
+      <c r="AA39" s="76"/>
+      <c r="AB39" s="76"/>
+    </row>
+    <row r="41" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="76" t="s">
         <v>218</v>
       </c>
-      <c r="C37" s="77"/>
-      <c r="D37" s="77"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
-      <c r="I37" s="77"/>
-      <c r="J37" s="77"/>
-      <c r="K37" s="77"/>
-      <c r="L37" s="77"/>
-      <c r="M37" s="77"/>
-      <c r="N37" s="77"/>
-      <c r="O37" s="77"/>
-      <c r="P37" s="77"/>
-      <c r="Q37" s="77"/>
-      <c r="R37" s="77"/>
-      <c r="S37" s="77"/>
-      <c r="T37" s="77"/>
-      <c r="U37" s="77"/>
-      <c r="V37" s="77"/>
-      <c r="W37" s="77"/>
-      <c r="X37" s="77"/>
-      <c r="Y37" s="77"/>
-      <c r="Z37" s="77"/>
-      <c r="AA37" s="77"/>
-      <c r="AB37" s="77"/>
-    </row>
-    <row r="38" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="77" t="s">
-        <v>217</v>
-      </c>
-      <c r="C38" s="77"/>
-      <c r="D38" s="77"/>
-      <c r="E38" s="77"/>
-      <c r="F38" s="77"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="77"/>
-      <c r="I38" s="77"/>
-      <c r="J38" s="77"/>
-      <c r="K38" s="77"/>
-      <c r="L38" s="77"/>
-      <c r="M38" s="77"/>
-      <c r="N38" s="77"/>
-      <c r="O38" s="77"/>
-      <c r="P38" s="77"/>
-      <c r="Q38" s="77"/>
-      <c r="R38" s="77"/>
-      <c r="S38" s="77"/>
-      <c r="T38" s="77"/>
-      <c r="U38" s="77"/>
-      <c r="V38" s="77"/>
-      <c r="W38" s="77"/>
-      <c r="X38" s="77"/>
-      <c r="Y38" s="77"/>
-      <c r="Z38" s="77"/>
-      <c r="AA38" s="77"/>
-      <c r="AB38" s="77"/>
-    </row>
-    <row r="39" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="77" t="s">
+      <c r="C41" s="76"/>
+      <c r="D41" s="76"/>
+      <c r="E41" s="76"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="76"/>
+      <c r="I41" s="76"/>
+      <c r="J41" s="76"/>
+      <c r="K41" s="76"/>
+      <c r="L41" s="76"/>
+      <c r="M41" s="76"/>
+      <c r="N41" s="76"/>
+      <c r="O41" s="76"/>
+      <c r="P41" s="76"/>
+      <c r="Q41" s="76"/>
+      <c r="R41" s="76"/>
+      <c r="S41" s="76"/>
+      <c r="T41" s="76"/>
+      <c r="U41" s="76"/>
+      <c r="V41" s="76"/>
+      <c r="W41" s="76"/>
+      <c r="X41" s="76"/>
+      <c r="Y41" s="76"/>
+      <c r="Z41" s="76"/>
+      <c r="AA41" s="76"/>
+      <c r="AB41" s="76"/>
+    </row>
+    <row r="42" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B42" s="76" t="s">
         <v>219</v>
       </c>
-      <c r="C39" s="77"/>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
-      <c r="I39" s="77"/>
-      <c r="J39" s="77"/>
-      <c r="K39" s="77"/>
-      <c r="L39" s="77"/>
-      <c r="M39" s="77"/>
-      <c r="N39" s="77"/>
-      <c r="O39" s="77"/>
-      <c r="P39" s="77"/>
-      <c r="Q39" s="77"/>
-      <c r="R39" s="77"/>
-      <c r="S39" s="77"/>
-      <c r="T39" s="77"/>
-      <c r="U39" s="77"/>
-      <c r="V39" s="77"/>
-      <c r="W39" s="77"/>
-      <c r="X39" s="77"/>
-      <c r="Y39" s="77"/>
-      <c r="Z39" s="77"/>
-      <c r="AA39" s="77"/>
-      <c r="AB39" s="77"/>
-    </row>
-    <row r="41" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="77" t="s">
+      <c r="C42" s="76"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="76"/>
+      <c r="H42" s="76"/>
+      <c r="I42" s="76"/>
+      <c r="J42" s="76"/>
+      <c r="K42" s="76"/>
+      <c r="L42" s="76"/>
+      <c r="M42" s="76"/>
+      <c r="N42" s="76"/>
+      <c r="O42" s="76"/>
+      <c r="P42" s="76"/>
+      <c r="Q42" s="76"/>
+      <c r="R42" s="76"/>
+      <c r="S42" s="76"/>
+      <c r="T42" s="76"/>
+      <c r="U42" s="76"/>
+      <c r="V42" s="76"/>
+      <c r="W42" s="76"/>
+      <c r="X42" s="76"/>
+      <c r="Y42" s="76"/>
+      <c r="Z42" s="76"/>
+      <c r="AA42" s="76"/>
+      <c r="AB42" s="76"/>
+    </row>
+    <row r="43" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B43" s="76" t="s">
         <v>220</v>
       </c>
-      <c r="C41" s="77"/>
-      <c r="D41" s="77"/>
-      <c r="E41" s="77"/>
-      <c r="F41" s="77"/>
-      <c r="G41" s="77"/>
-      <c r="H41" s="77"/>
-      <c r="I41" s="77"/>
-      <c r="J41" s="77"/>
-      <c r="K41" s="77"/>
-      <c r="L41" s="77"/>
-      <c r="M41" s="77"/>
-      <c r="N41" s="77"/>
-      <c r="O41" s="77"/>
-      <c r="P41" s="77"/>
-      <c r="Q41" s="77"/>
-      <c r="R41" s="77"/>
-      <c r="S41" s="77"/>
-      <c r="T41" s="77"/>
-      <c r="U41" s="77"/>
-      <c r="V41" s="77"/>
-      <c r="W41" s="77"/>
-      <c r="X41" s="77"/>
-      <c r="Y41" s="77"/>
-      <c r="Z41" s="77"/>
-      <c r="AA41" s="77"/>
-      <c r="AB41" s="77"/>
-    </row>
-    <row r="42" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B42" s="77" t="s">
+      <c r="C43" s="76"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="76"/>
+      <c r="I43" s="76"/>
+      <c r="J43" s="76"/>
+      <c r="K43" s="76"/>
+      <c r="L43" s="76"/>
+      <c r="M43" s="76"/>
+      <c r="N43" s="76"/>
+      <c r="O43" s="76"/>
+      <c r="P43" s="76"/>
+      <c r="Q43" s="76"/>
+      <c r="R43" s="76"/>
+      <c r="S43" s="76"/>
+      <c r="T43" s="76"/>
+      <c r="U43" s="76"/>
+      <c r="V43" s="76"/>
+      <c r="W43" s="76"/>
+      <c r="X43" s="76"/>
+      <c r="Y43" s="76"/>
+      <c r="Z43" s="76"/>
+      <c r="AA43" s="76"/>
+      <c r="AB43" s="76"/>
+    </row>
+    <row r="44" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B44" s="76" t="s">
         <v>221</v>
       </c>
-      <c r="C42" s="77"/>
-      <c r="D42" s="77"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="77"/>
-      <c r="G42" s="77"/>
-      <c r="H42" s="77"/>
-      <c r="I42" s="77"/>
-      <c r="J42" s="77"/>
-      <c r="K42" s="77"/>
-      <c r="L42" s="77"/>
-      <c r="M42" s="77"/>
-      <c r="N42" s="77"/>
-      <c r="O42" s="77"/>
-      <c r="P42" s="77"/>
-      <c r="Q42" s="77"/>
-      <c r="R42" s="77"/>
-      <c r="S42" s="77"/>
-      <c r="T42" s="77"/>
-      <c r="U42" s="77"/>
-      <c r="V42" s="77"/>
-      <c r="W42" s="77"/>
-      <c r="X42" s="77"/>
-      <c r="Y42" s="77"/>
-      <c r="Z42" s="77"/>
-      <c r="AA42" s="77"/>
-      <c r="AB42" s="77"/>
-    </row>
-    <row r="43" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B43" s="77" t="s">
+      <c r="C44" s="76"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="76"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="76"/>
+      <c r="H44" s="76"/>
+      <c r="I44" s="76"/>
+      <c r="J44" s="76"/>
+      <c r="K44" s="76"/>
+      <c r="L44" s="76"/>
+      <c r="M44" s="76"/>
+      <c r="N44" s="76"/>
+      <c r="O44" s="76"/>
+      <c r="P44" s="76"/>
+      <c r="Q44" s="76"/>
+      <c r="R44" s="76"/>
+      <c r="S44" s="76"/>
+      <c r="T44" s="76"/>
+      <c r="U44" s="76"/>
+      <c r="V44" s="76"/>
+      <c r="W44" s="76"/>
+      <c r="X44" s="76"/>
+      <c r="Y44" s="76"/>
+      <c r="Z44" s="76"/>
+      <c r="AA44" s="76"/>
+      <c r="AB44" s="76"/>
+    </row>
+    <row r="45" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B45" s="76" t="s">
         <v>222</v>
       </c>
-      <c r="C43" s="77"/>
-      <c r="D43" s="77"/>
-      <c r="E43" s="77"/>
-      <c r="F43" s="77"/>
-      <c r="G43" s="77"/>
-      <c r="H43" s="77"/>
-      <c r="I43" s="77"/>
-      <c r="J43" s="77"/>
-      <c r="K43" s="77"/>
-      <c r="L43" s="77"/>
-      <c r="M43" s="77"/>
-      <c r="N43" s="77"/>
-      <c r="O43" s="77"/>
-      <c r="P43" s="77"/>
-      <c r="Q43" s="77"/>
-      <c r="R43" s="77"/>
-      <c r="S43" s="77"/>
-      <c r="T43" s="77"/>
-      <c r="U43" s="77"/>
-      <c r="V43" s="77"/>
-      <c r="W43" s="77"/>
-      <c r="X43" s="77"/>
-      <c r="Y43" s="77"/>
-      <c r="Z43" s="77"/>
-      <c r="AA43" s="77"/>
-      <c r="AB43" s="77"/>
-    </row>
-    <row r="44" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B44" s="77" t="s">
+      <c r="C45" s="76"/>
+      <c r="D45" s="76"/>
+      <c r="E45" s="76"/>
+      <c r="F45" s="76"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="76"/>
+      <c r="I45" s="76"/>
+      <c r="J45" s="76"/>
+      <c r="K45" s="76"/>
+      <c r="L45" s="76"/>
+      <c r="M45" s="76"/>
+      <c r="N45" s="76"/>
+      <c r="O45" s="76"/>
+      <c r="P45" s="76"/>
+      <c r="Q45" s="76"/>
+      <c r="R45" s="76"/>
+      <c r="S45" s="76"/>
+      <c r="T45" s="76"/>
+      <c r="U45" s="76"/>
+      <c r="V45" s="76"/>
+      <c r="W45" s="76"/>
+      <c r="X45" s="76"/>
+      <c r="Y45" s="76"/>
+      <c r="Z45" s="76"/>
+      <c r="AA45" s="76"/>
+      <c r="AB45" s="76"/>
+    </row>
+    <row r="46" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B46" s="76" t="s">
         <v>223</v>
       </c>
-      <c r="C44" s="77"/>
-      <c r="D44" s="77"/>
-      <c r="E44" s="77"/>
-      <c r="F44" s="77"/>
-      <c r="G44" s="77"/>
-      <c r="H44" s="77"/>
-      <c r="I44" s="77"/>
-      <c r="J44" s="77"/>
-      <c r="K44" s="77"/>
-      <c r="L44" s="77"/>
-      <c r="M44" s="77"/>
-      <c r="N44" s="77"/>
-      <c r="O44" s="77"/>
-      <c r="P44" s="77"/>
-      <c r="Q44" s="77"/>
-      <c r="R44" s="77"/>
-      <c r="S44" s="77"/>
-      <c r="T44" s="77"/>
-      <c r="U44" s="77"/>
-      <c r="V44" s="77"/>
-      <c r="W44" s="77"/>
-      <c r="X44" s="77"/>
-      <c r="Y44" s="77"/>
-      <c r="Z44" s="77"/>
-      <c r="AA44" s="77"/>
-      <c r="AB44" s="77"/>
-    </row>
-    <row r="45" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B45" s="77" t="s">
-        <v>224</v>
-      </c>
-      <c r="C45" s="77"/>
-      <c r="D45" s="77"/>
-      <c r="E45" s="77"/>
-      <c r="F45" s="77"/>
-      <c r="G45" s="77"/>
-      <c r="H45" s="77"/>
-      <c r="I45" s="77"/>
-      <c r="J45" s="77"/>
-      <c r="K45" s="77"/>
-      <c r="L45" s="77"/>
-      <c r="M45" s="77"/>
-      <c r="N45" s="77"/>
-      <c r="O45" s="77"/>
-      <c r="P45" s="77"/>
-      <c r="Q45" s="77"/>
-      <c r="R45" s="77"/>
-      <c r="S45" s="77"/>
-      <c r="T45" s="77"/>
-      <c r="U45" s="77"/>
-      <c r="V45" s="77"/>
-      <c r="W45" s="77"/>
-      <c r="X45" s="77"/>
-      <c r="Y45" s="77"/>
-      <c r="Z45" s="77"/>
-      <c r="AA45" s="77"/>
-      <c r="AB45" s="77"/>
-    </row>
-    <row r="46" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B46" s="77" t="s">
+      <c r="C46" s="76"/>
+      <c r="D46" s="76"/>
+      <c r="E46" s="76"/>
+      <c r="F46" s="76"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="76"/>
+      <c r="I46" s="76"/>
+      <c r="J46" s="76"/>
+      <c r="K46" s="76"/>
+      <c r="L46" s="76"/>
+      <c r="M46" s="76"/>
+      <c r="N46" s="76"/>
+      <c r="O46" s="76"/>
+      <c r="P46" s="76"/>
+      <c r="Q46" s="76"/>
+      <c r="R46" s="76"/>
+      <c r="S46" s="76"/>
+      <c r="T46" s="76"/>
+      <c r="U46" s="76"/>
+      <c r="V46" s="76"/>
+      <c r="W46" s="76"/>
+      <c r="X46" s="76"/>
+      <c r="Y46" s="76"/>
+      <c r="Z46" s="76"/>
+      <c r="AA46" s="76"/>
+      <c r="AB46" s="76"/>
+    </row>
+    <row r="47" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B47" s="76" t="s">
         <v>225</v>
       </c>
-      <c r="C46" s="77"/>
-      <c r="D46" s="77"/>
-      <c r="E46" s="77"/>
-      <c r="F46" s="77"/>
-      <c r="G46" s="77"/>
-      <c r="H46" s="77"/>
-      <c r="I46" s="77"/>
-      <c r="J46" s="77"/>
-      <c r="K46" s="77"/>
-      <c r="L46" s="77"/>
-      <c r="M46" s="77"/>
-      <c r="N46" s="77"/>
-      <c r="O46" s="77"/>
-      <c r="P46" s="77"/>
-      <c r="Q46" s="77"/>
-      <c r="R46" s="77"/>
-      <c r="S46" s="77"/>
-      <c r="T46" s="77"/>
-      <c r="U46" s="77"/>
-      <c r="V46" s="77"/>
-      <c r="W46" s="77"/>
-      <c r="X46" s="77"/>
-      <c r="Y46" s="77"/>
-      <c r="Z46" s="77"/>
-      <c r="AA46" s="77"/>
-      <c r="AB46" s="77"/>
-    </row>
-    <row r="47" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B47" s="77" t="s">
+      <c r="C47" s="76"/>
+      <c r="D47" s="76"/>
+      <c r="E47" s="76"/>
+      <c r="F47" s="76"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="76"/>
+      <c r="I47" s="76"/>
+      <c r="J47" s="76"/>
+      <c r="K47" s="76"/>
+      <c r="L47" s="76"/>
+      <c r="M47" s="76"/>
+      <c r="N47" s="76"/>
+      <c r="O47" s="76"/>
+      <c r="P47" s="76"/>
+      <c r="Q47" s="76"/>
+      <c r="R47" s="76"/>
+      <c r="S47" s="76"/>
+      <c r="T47" s="76"/>
+      <c r="U47" s="76"/>
+      <c r="V47" s="76"/>
+      <c r="W47" s="76"/>
+      <c r="X47" s="76"/>
+      <c r="Y47" s="76"/>
+      <c r="Z47" s="76"/>
+      <c r="AA47" s="76"/>
+      <c r="AB47" s="76"/>
+    </row>
+    <row r="48" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B48" s="76" t="s">
+        <v>226</v>
+      </c>
+      <c r="C48" s="76"/>
+      <c r="D48" s="76"/>
+      <c r="E48" s="76"/>
+      <c r="F48" s="76"/>
+      <c r="G48" s="76"/>
+      <c r="H48" s="76"/>
+      <c r="I48" s="76"/>
+      <c r="J48" s="76"/>
+      <c r="K48" s="76"/>
+      <c r="L48" s="76"/>
+      <c r="M48" s="76"/>
+      <c r="N48" s="76"/>
+      <c r="O48" s="76"/>
+      <c r="P48" s="76"/>
+      <c r="Q48" s="76"/>
+      <c r="R48" s="76"/>
+      <c r="S48" s="76"/>
+      <c r="T48" s="76"/>
+      <c r="U48" s="76"/>
+      <c r="V48" s="76"/>
+      <c r="W48" s="76"/>
+      <c r="X48" s="76"/>
+      <c r="Y48" s="76"/>
+      <c r="Z48" s="76"/>
+      <c r="AA48" s="76"/>
+      <c r="AB48" s="76"/>
+    </row>
+    <row r="49" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B49" s="76" t="s">
+        <v>228</v>
+      </c>
+      <c r="C49" s="76"/>
+      <c r="D49" s="76"/>
+      <c r="E49" s="76"/>
+      <c r="F49" s="76"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="76"/>
+      <c r="I49" s="76"/>
+      <c r="J49" s="76"/>
+      <c r="K49" s="76"/>
+      <c r="L49" s="76"/>
+      <c r="M49" s="76"/>
+      <c r="N49" s="76"/>
+      <c r="O49" s="76"/>
+      <c r="P49" s="76"/>
+      <c r="Q49" s="76"/>
+      <c r="R49" s="76"/>
+      <c r="S49" s="76"/>
+      <c r="T49" s="76"/>
+      <c r="U49" s="76"/>
+      <c r="V49" s="76"/>
+      <c r="W49" s="76"/>
+      <c r="X49" s="76"/>
+      <c r="Y49" s="76"/>
+      <c r="Z49" s="76"/>
+      <c r="AA49" s="76"/>
+      <c r="AB49" s="76"/>
+    </row>
+    <row r="50" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B50" s="76" t="s">
         <v>227</v>
       </c>
-      <c r="C47" s="77"/>
-      <c r="D47" s="77"/>
-      <c r="E47" s="77"/>
-      <c r="F47" s="77"/>
-      <c r="G47" s="77"/>
-      <c r="H47" s="77"/>
-      <c r="I47" s="77"/>
-      <c r="J47" s="77"/>
-      <c r="K47" s="77"/>
-      <c r="L47" s="77"/>
-      <c r="M47" s="77"/>
-      <c r="N47" s="77"/>
-      <c r="O47" s="77"/>
-      <c r="P47" s="77"/>
-      <c r="Q47" s="77"/>
-      <c r="R47" s="77"/>
-      <c r="S47" s="77"/>
-      <c r="T47" s="77"/>
-      <c r="U47" s="77"/>
-      <c r="V47" s="77"/>
-      <c r="W47" s="77"/>
-      <c r="X47" s="77"/>
-      <c r="Y47" s="77"/>
-      <c r="Z47" s="77"/>
-      <c r="AA47" s="77"/>
-      <c r="AB47" s="77"/>
-    </row>
-    <row r="48" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B48" s="77" t="s">
-        <v>228</v>
-      </c>
-      <c r="C48" s="77"/>
-      <c r="D48" s="77"/>
-      <c r="E48" s="77"/>
-      <c r="F48" s="77"/>
-      <c r="G48" s="77"/>
-      <c r="H48" s="77"/>
-      <c r="I48" s="77"/>
-      <c r="J48" s="77"/>
-      <c r="K48" s="77"/>
-      <c r="L48" s="77"/>
-      <c r="M48" s="77"/>
-      <c r="N48" s="77"/>
-      <c r="O48" s="77"/>
-      <c r="P48" s="77"/>
-      <c r="Q48" s="77"/>
-      <c r="R48" s="77"/>
-      <c r="S48" s="77"/>
-      <c r="T48" s="77"/>
-      <c r="U48" s="77"/>
-      <c r="V48" s="77"/>
-      <c r="W48" s="77"/>
-      <c r="X48" s="77"/>
-      <c r="Y48" s="77"/>
-      <c r="Z48" s="77"/>
-      <c r="AA48" s="77"/>
-      <c r="AB48" s="77"/>
-    </row>
-    <row r="49" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B49" s="77" t="s">
+      <c r="C50" s="76"/>
+      <c r="D50" s="76"/>
+      <c r="E50" s="76"/>
+      <c r="F50" s="76"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="76"/>
+      <c r="I50" s="76"/>
+      <c r="J50" s="76"/>
+      <c r="K50" s="76"/>
+      <c r="L50" s="76"/>
+      <c r="M50" s="76"/>
+      <c r="N50" s="76"/>
+      <c r="O50" s="76"/>
+      <c r="P50" s="76"/>
+      <c r="Q50" s="76"/>
+      <c r="R50" s="76"/>
+      <c r="S50" s="76"/>
+      <c r="T50" s="76"/>
+      <c r="U50" s="76"/>
+      <c r="V50" s="76"/>
+      <c r="W50" s="76"/>
+      <c r="X50" s="76"/>
+      <c r="Y50" s="76"/>
+      <c r="Z50" s="76"/>
+      <c r="AA50" s="76"/>
+      <c r="AB50" s="76"/>
+    </row>
+    <row r="51" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B51" s="76" t="s">
+        <v>229</v>
+      </c>
+      <c r="C51" s="76"/>
+      <c r="D51" s="76"/>
+      <c r="E51" s="76"/>
+      <c r="F51" s="76"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="76"/>
+      <c r="I51" s="76"/>
+      <c r="J51" s="76"/>
+      <c r="K51" s="76"/>
+      <c r="L51" s="76"/>
+      <c r="M51" s="76"/>
+      <c r="N51" s="76"/>
+      <c r="O51" s="76"/>
+      <c r="P51" s="76"/>
+      <c r="Q51" s="76"/>
+      <c r="R51" s="76"/>
+      <c r="S51" s="76"/>
+      <c r="T51" s="76"/>
+      <c r="U51" s="76"/>
+      <c r="V51" s="76"/>
+      <c r="W51" s="76"/>
+      <c r="X51" s="76"/>
+      <c r="Y51" s="76"/>
+      <c r="Z51" s="76"/>
+      <c r="AA51" s="76"/>
+      <c r="AB51" s="76"/>
+    </row>
+    <row r="52" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B52" s="76" t="s">
         <v>230</v>
       </c>
-      <c r="C49" s="77"/>
-      <c r="D49" s="77"/>
-      <c r="E49" s="77"/>
-      <c r="F49" s="77"/>
-      <c r="G49" s="77"/>
-      <c r="H49" s="77"/>
-      <c r="I49" s="77"/>
-      <c r="J49" s="77"/>
-      <c r="K49" s="77"/>
-      <c r="L49" s="77"/>
-      <c r="M49" s="77"/>
-      <c r="N49" s="77"/>
-      <c r="O49" s="77"/>
-      <c r="P49" s="77"/>
-      <c r="Q49" s="77"/>
-      <c r="R49" s="77"/>
-      <c r="S49" s="77"/>
-      <c r="T49" s="77"/>
-      <c r="U49" s="77"/>
-      <c r="V49" s="77"/>
-      <c r="W49" s="77"/>
-      <c r="X49" s="77"/>
-      <c r="Y49" s="77"/>
-      <c r="Z49" s="77"/>
-      <c r="AA49" s="77"/>
-      <c r="AB49" s="77"/>
-    </row>
-    <row r="50" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B50" s="77" t="s">
-        <v>229</v>
-      </c>
-      <c r="C50" s="77"/>
-      <c r="D50" s="77"/>
-      <c r="E50" s="77"/>
-      <c r="F50" s="77"/>
-      <c r="G50" s="77"/>
-      <c r="H50" s="77"/>
-      <c r="I50" s="77"/>
-      <c r="J50" s="77"/>
-      <c r="K50" s="77"/>
-      <c r="L50" s="77"/>
-      <c r="M50" s="77"/>
-      <c r="N50" s="77"/>
-      <c r="O50" s="77"/>
-      <c r="P50" s="77"/>
-      <c r="Q50" s="77"/>
-      <c r="R50" s="77"/>
-      <c r="S50" s="77"/>
-      <c r="T50" s="77"/>
-      <c r="U50" s="77"/>
-      <c r="V50" s="77"/>
-      <c r="W50" s="77"/>
-      <c r="X50" s="77"/>
-      <c r="Y50" s="77"/>
-      <c r="Z50" s="77"/>
-      <c r="AA50" s="77"/>
-      <c r="AB50" s="77"/>
-    </row>
-    <row r="51" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B51" s="77" t="s">
+      <c r="C52" s="76"/>
+      <c r="D52" s="76"/>
+      <c r="E52" s="76"/>
+      <c r="F52" s="76"/>
+      <c r="G52" s="76"/>
+      <c r="H52" s="76"/>
+      <c r="I52" s="76"/>
+      <c r="J52" s="76"/>
+      <c r="K52" s="76"/>
+      <c r="L52" s="76"/>
+      <c r="M52" s="76"/>
+      <c r="N52" s="76"/>
+      <c r="O52" s="76"/>
+      <c r="P52" s="76"/>
+      <c r="Q52" s="76"/>
+      <c r="R52" s="76"/>
+      <c r="S52" s="76"/>
+      <c r="T52" s="76"/>
+      <c r="U52" s="76"/>
+      <c r="V52" s="76"/>
+      <c r="W52" s="76"/>
+      <c r="X52" s="76"/>
+      <c r="Y52" s="76"/>
+      <c r="Z52" s="76"/>
+      <c r="AA52" s="76"/>
+      <c r="AB52" s="76"/>
+    </row>
+    <row r="53" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B53" s="76" t="s">
         <v>231</v>
       </c>
-      <c r="C51" s="77"/>
-      <c r="D51" s="77"/>
-      <c r="E51" s="77"/>
-      <c r="F51" s="77"/>
-      <c r="G51" s="77"/>
-      <c r="H51" s="77"/>
-      <c r="I51" s="77"/>
-      <c r="J51" s="77"/>
-      <c r="K51" s="77"/>
-      <c r="L51" s="77"/>
-      <c r="M51" s="77"/>
-      <c r="N51" s="77"/>
-      <c r="O51" s="77"/>
-      <c r="P51" s="77"/>
-      <c r="Q51" s="77"/>
-      <c r="R51" s="77"/>
-      <c r="S51" s="77"/>
-      <c r="T51" s="77"/>
-      <c r="U51" s="77"/>
-      <c r="V51" s="77"/>
-      <c r="W51" s="77"/>
-      <c r="X51" s="77"/>
-      <c r="Y51" s="77"/>
-      <c r="Z51" s="77"/>
-      <c r="AA51" s="77"/>
-      <c r="AB51" s="77"/>
-    </row>
-    <row r="52" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B52" s="77" t="s">
-        <v>232</v>
-      </c>
-      <c r="C52" s="77"/>
-      <c r="D52" s="77"/>
-      <c r="E52" s="77"/>
-      <c r="F52" s="77"/>
-      <c r="G52" s="77"/>
-      <c r="H52" s="77"/>
-      <c r="I52" s="77"/>
-      <c r="J52" s="77"/>
-      <c r="K52" s="77"/>
-      <c r="L52" s="77"/>
-      <c r="M52" s="77"/>
-      <c r="N52" s="77"/>
-      <c r="O52" s="77"/>
-      <c r="P52" s="77"/>
-      <c r="Q52" s="77"/>
-      <c r="R52" s="77"/>
-      <c r="S52" s="77"/>
-      <c r="T52" s="77"/>
-      <c r="U52" s="77"/>
-      <c r="V52" s="77"/>
-      <c r="W52" s="77"/>
-      <c r="X52" s="77"/>
-      <c r="Y52" s="77"/>
-      <c r="Z52" s="77"/>
-      <c r="AA52" s="77"/>
-      <c r="AB52" s="77"/>
-    </row>
-    <row r="53" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B53" s="77" t="s">
-        <v>233</v>
-      </c>
-      <c r="C53" s="77"/>
-      <c r="D53" s="77"/>
-      <c r="E53" s="77"/>
-      <c r="F53" s="77"/>
-      <c r="G53" s="77"/>
-      <c r="H53" s="77"/>
-      <c r="I53" s="77"/>
-      <c r="J53" s="77"/>
-      <c r="K53" s="77"/>
-      <c r="L53" s="77"/>
-      <c r="M53" s="77"/>
-      <c r="N53" s="77"/>
-      <c r="O53" s="77"/>
-      <c r="P53" s="77"/>
-      <c r="Q53" s="77"/>
-      <c r="R53" s="77"/>
-      <c r="S53" s="77"/>
-      <c r="T53" s="77"/>
-      <c r="U53" s="77"/>
-      <c r="V53" s="77"/>
-      <c r="W53" s="77"/>
-      <c r="X53" s="77"/>
-      <c r="Y53" s="77"/>
-      <c r="Z53" s="77"/>
-      <c r="AA53" s="77"/>
-      <c r="AB53" s="77"/>
+      <c r="C53" s="76"/>
+      <c r="D53" s="76"/>
+      <c r="E53" s="76"/>
+      <c r="F53" s="76"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="76"/>
+      <c r="I53" s="76"/>
+      <c r="J53" s="76"/>
+      <c r="K53" s="76"/>
+      <c r="L53" s="76"/>
+      <c r="M53" s="76"/>
+      <c r="N53" s="76"/>
+      <c r="O53" s="76"/>
+      <c r="P53" s="76"/>
+      <c r="Q53" s="76"/>
+      <c r="R53" s="76"/>
+      <c r="S53" s="76"/>
+      <c r="T53" s="76"/>
+      <c r="U53" s="76"/>
+      <c r="V53" s="76"/>
+      <c r="W53" s="76"/>
+      <c r="X53" s="76"/>
+      <c r="Y53" s="76"/>
+      <c r="Z53" s="76"/>
+      <c r="AA53" s="76"/>
+      <c r="AB53" s="76"/>
     </row>
     <row r="55" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B55" s="8" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="56" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B56" s="8" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="57" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B57" s="8"/>
     </row>
     <row r="58" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B58" s="77" t="s">
-        <v>236</v>
-      </c>
-      <c r="C58" s="77"/>
-      <c r="D58" s="77"/>
-      <c r="E58" s="77"/>
-      <c r="F58" s="77"/>
-      <c r="G58" s="77"/>
-      <c r="H58" s="77"/>
-      <c r="I58" s="77"/>
-      <c r="J58" s="77"/>
-      <c r="K58" s="77"/>
-      <c r="L58" s="77"/>
-      <c r="M58" s="77"/>
-      <c r="N58" s="77"/>
-      <c r="O58" s="77"/>
-      <c r="P58" s="77"/>
-      <c r="Q58" s="77"/>
-      <c r="R58" s="77"/>
-      <c r="S58" s="77"/>
-      <c r="T58" s="77"/>
-      <c r="U58" s="77"/>
-      <c r="V58" s="77"/>
-      <c r="W58" s="77"/>
-      <c r="X58" s="77"/>
-      <c r="Y58" s="77"/>
-      <c r="Z58" s="77"/>
-      <c r="AA58" s="77"/>
-      <c r="AB58" s="77"/>
+      <c r="B58" s="76" t="s">
+        <v>233</v>
+      </c>
+      <c r="C58" s="76"/>
+      <c r="D58" s="76"/>
+      <c r="E58" s="76"/>
+      <c r="F58" s="76"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="76"/>
+      <c r="I58" s="76"/>
+      <c r="J58" s="76"/>
+      <c r="K58" s="76"/>
+      <c r="L58" s="76"/>
+      <c r="M58" s="76"/>
+      <c r="N58" s="76"/>
+      <c r="O58" s="76"/>
+      <c r="P58" s="76"/>
+      <c r="Q58" s="76"/>
+      <c r="R58" s="76"/>
+      <c r="S58" s="76"/>
+      <c r="T58" s="76"/>
+      <c r="U58" s="76"/>
+      <c r="V58" s="76"/>
+      <c r="W58" s="76"/>
+      <c r="X58" s="76"/>
+      <c r="Y58" s="76"/>
+      <c r="Z58" s="76"/>
+      <c r="AA58" s="76"/>
+      <c r="AB58" s="76"/>
     </row>
     <row r="59" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B59" s="77" t="s">
+      <c r="B59" s="76" t="s">
+        <v>220</v>
+      </c>
+      <c r="C59" s="76"/>
+      <c r="D59" s="76"/>
+      <c r="E59" s="76"/>
+      <c r="F59" s="76"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="76"/>
+      <c r="I59" s="76"/>
+      <c r="J59" s="76"/>
+      <c r="K59" s="76"/>
+      <c r="L59" s="76"/>
+      <c r="M59" s="76"/>
+      <c r="N59" s="76"/>
+      <c r="O59" s="76"/>
+      <c r="P59" s="76"/>
+      <c r="Q59" s="76"/>
+      <c r="R59" s="76"/>
+      <c r="S59" s="76"/>
+      <c r="T59" s="76"/>
+      <c r="U59" s="76"/>
+      <c r="V59" s="76"/>
+      <c r="W59" s="76"/>
+      <c r="X59" s="76"/>
+      <c r="Y59" s="76"/>
+      <c r="Z59" s="76"/>
+      <c r="AA59" s="76"/>
+      <c r="AB59" s="76"/>
+    </row>
+    <row r="60" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B60" s="76" t="s">
+        <v>221</v>
+      </c>
+      <c r="C60" s="76"/>
+      <c r="D60" s="76"/>
+      <c r="E60" s="76"/>
+      <c r="F60" s="76"/>
+      <c r="G60" s="76"/>
+      <c r="H60" s="76"/>
+      <c r="I60" s="76"/>
+      <c r="J60" s="76"/>
+      <c r="K60" s="76"/>
+      <c r="L60" s="76"/>
+      <c r="M60" s="76"/>
+      <c r="N60" s="76"/>
+      <c r="O60" s="76"/>
+      <c r="P60" s="76"/>
+      <c r="Q60" s="76"/>
+      <c r="R60" s="76"/>
+      <c r="S60" s="76"/>
+      <c r="T60" s="76"/>
+      <c r="U60" s="76"/>
+      <c r="V60" s="76"/>
+      <c r="W60" s="76"/>
+      <c r="X60" s="76"/>
+      <c r="Y60" s="76"/>
+      <c r="Z60" s="76"/>
+      <c r="AA60" s="76"/>
+      <c r="AB60" s="76"/>
+    </row>
+    <row r="61" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B61" s="76" t="s">
         <v>222</v>
       </c>
-      <c r="C59" s="77"/>
-      <c r="D59" s="77"/>
-      <c r="E59" s="77"/>
-      <c r="F59" s="77"/>
-      <c r="G59" s="77"/>
-      <c r="H59" s="77"/>
-      <c r="I59" s="77"/>
-      <c r="J59" s="77"/>
-      <c r="K59" s="77"/>
-      <c r="L59" s="77"/>
-      <c r="M59" s="77"/>
-      <c r="N59" s="77"/>
-      <c r="O59" s="77"/>
-      <c r="P59" s="77"/>
-      <c r="Q59" s="77"/>
-      <c r="R59" s="77"/>
-      <c r="S59" s="77"/>
-      <c r="T59" s="77"/>
-      <c r="U59" s="77"/>
-      <c r="V59" s="77"/>
-      <c r="W59" s="77"/>
-      <c r="X59" s="77"/>
-      <c r="Y59" s="77"/>
-      <c r="Z59" s="77"/>
-      <c r="AA59" s="77"/>
-      <c r="AB59" s="77"/>
-    </row>
-    <row r="60" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B60" s="77" t="s">
+      <c r="C61" s="76"/>
+      <c r="D61" s="76"/>
+      <c r="E61" s="76"/>
+      <c r="F61" s="76"/>
+      <c r="G61" s="76"/>
+      <c r="H61" s="76"/>
+      <c r="I61" s="76"/>
+      <c r="J61" s="76"/>
+      <c r="K61" s="76"/>
+      <c r="L61" s="76"/>
+      <c r="M61" s="76"/>
+      <c r="N61" s="76"/>
+      <c r="O61" s="76"/>
+      <c r="P61" s="76"/>
+      <c r="Q61" s="76"/>
+      <c r="R61" s="76"/>
+      <c r="S61" s="76"/>
+      <c r="T61" s="76"/>
+      <c r="U61" s="76"/>
+      <c r="V61" s="76"/>
+      <c r="W61" s="76"/>
+      <c r="X61" s="76"/>
+      <c r="Y61" s="76"/>
+      <c r="Z61" s="76"/>
+      <c r="AA61" s="76"/>
+      <c r="AB61" s="76"/>
+    </row>
+    <row r="62" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B62" s="76" t="s">
         <v>223</v>
       </c>
-      <c r="C60" s="77"/>
-      <c r="D60" s="77"/>
-      <c r="E60" s="77"/>
-      <c r="F60" s="77"/>
-      <c r="G60" s="77"/>
-      <c r="H60" s="77"/>
-      <c r="I60" s="77"/>
-      <c r="J60" s="77"/>
-      <c r="K60" s="77"/>
-      <c r="L60" s="77"/>
-      <c r="M60" s="77"/>
-      <c r="N60" s="77"/>
-      <c r="O60" s="77"/>
-      <c r="P60" s="77"/>
-      <c r="Q60" s="77"/>
-      <c r="R60" s="77"/>
-      <c r="S60" s="77"/>
-      <c r="T60" s="77"/>
-      <c r="U60" s="77"/>
-      <c r="V60" s="77"/>
-      <c r="W60" s="77"/>
-      <c r="X60" s="77"/>
-      <c r="Y60" s="77"/>
-      <c r="Z60" s="77"/>
-      <c r="AA60" s="77"/>
-      <c r="AB60" s="77"/>
-    </row>
-    <row r="61" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B61" s="77" t="s">
-        <v>224</v>
-      </c>
-      <c r="C61" s="77"/>
-      <c r="D61" s="77"/>
-      <c r="E61" s="77"/>
-      <c r="F61" s="77"/>
-      <c r="G61" s="77"/>
-      <c r="H61" s="77"/>
-      <c r="I61" s="77"/>
-      <c r="J61" s="77"/>
-      <c r="K61" s="77"/>
-      <c r="L61" s="77"/>
-      <c r="M61" s="77"/>
-      <c r="N61" s="77"/>
-      <c r="O61" s="77"/>
-      <c r="P61" s="77"/>
-      <c r="Q61" s="77"/>
-      <c r="R61" s="77"/>
-      <c r="S61" s="77"/>
-      <c r="T61" s="77"/>
-      <c r="U61" s="77"/>
-      <c r="V61" s="77"/>
-      <c r="W61" s="77"/>
-      <c r="X61" s="77"/>
-      <c r="Y61" s="77"/>
-      <c r="Z61" s="77"/>
-      <c r="AA61" s="77"/>
-      <c r="AB61" s="77"/>
-    </row>
-    <row r="62" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B62" s="77" t="s">
+      <c r="C62" s="76"/>
+      <c r="D62" s="76"/>
+      <c r="E62" s="76"/>
+      <c r="F62" s="76"/>
+      <c r="G62" s="76"/>
+      <c r="H62" s="76"/>
+      <c r="I62" s="76"/>
+      <c r="J62" s="76"/>
+      <c r="K62" s="76"/>
+      <c r="L62" s="76"/>
+      <c r="M62" s="76"/>
+      <c r="N62" s="76"/>
+      <c r="O62" s="76"/>
+      <c r="P62" s="76"/>
+      <c r="Q62" s="76"/>
+      <c r="R62" s="76"/>
+      <c r="S62" s="76"/>
+      <c r="T62" s="76"/>
+      <c r="U62" s="76"/>
+      <c r="V62" s="76"/>
+      <c r="W62" s="76"/>
+      <c r="X62" s="76"/>
+      <c r="Y62" s="76"/>
+      <c r="Z62" s="76"/>
+      <c r="AA62" s="76"/>
+      <c r="AB62" s="76"/>
+    </row>
+    <row r="63" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B63" s="76" t="s">
         <v>225</v>
       </c>
-      <c r="C62" s="77"/>
-      <c r="D62" s="77"/>
-      <c r="E62" s="77"/>
-      <c r="F62" s="77"/>
-      <c r="G62" s="77"/>
-      <c r="H62" s="77"/>
-      <c r="I62" s="77"/>
-      <c r="J62" s="77"/>
-      <c r="K62" s="77"/>
-      <c r="L62" s="77"/>
-      <c r="M62" s="77"/>
-      <c r="N62" s="77"/>
-      <c r="O62" s="77"/>
-      <c r="P62" s="77"/>
-      <c r="Q62" s="77"/>
-      <c r="R62" s="77"/>
-      <c r="S62" s="77"/>
-      <c r="T62" s="77"/>
-      <c r="U62" s="77"/>
-      <c r="V62" s="77"/>
-      <c r="W62" s="77"/>
-      <c r="X62" s="77"/>
-      <c r="Y62" s="77"/>
-      <c r="Z62" s="77"/>
-      <c r="AA62" s="77"/>
-      <c r="AB62" s="77"/>
-    </row>
-    <row r="63" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B63" s="77" t="s">
+      <c r="C63" s="76"/>
+      <c r="D63" s="76"/>
+      <c r="E63" s="76"/>
+      <c r="F63" s="76"/>
+      <c r="G63" s="76"/>
+      <c r="H63" s="76"/>
+      <c r="I63" s="76"/>
+      <c r="J63" s="76"/>
+      <c r="K63" s="76"/>
+      <c r="L63" s="76"/>
+      <c r="M63" s="76"/>
+      <c r="N63" s="76"/>
+      <c r="O63" s="76"/>
+      <c r="P63" s="76"/>
+      <c r="Q63" s="76"/>
+      <c r="R63" s="76"/>
+      <c r="S63" s="76"/>
+      <c r="T63" s="76"/>
+      <c r="U63" s="76"/>
+      <c r="V63" s="76"/>
+      <c r="W63" s="76"/>
+      <c r="X63" s="76"/>
+      <c r="Y63" s="76"/>
+      <c r="Z63" s="76"/>
+      <c r="AA63" s="76"/>
+      <c r="AB63" s="76"/>
+    </row>
+    <row r="64" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B64" s="76" t="s">
+        <v>226</v>
+      </c>
+      <c r="C64" s="76"/>
+      <c r="D64" s="76"/>
+      <c r="E64" s="76"/>
+      <c r="F64" s="76"/>
+      <c r="G64" s="76"/>
+      <c r="H64" s="76"/>
+      <c r="I64" s="76"/>
+      <c r="J64" s="76"/>
+      <c r="K64" s="76"/>
+      <c r="L64" s="76"/>
+      <c r="M64" s="76"/>
+      <c r="N64" s="76"/>
+      <c r="O64" s="76"/>
+      <c r="P64" s="76"/>
+      <c r="Q64" s="76"/>
+      <c r="R64" s="76"/>
+      <c r="S64" s="76"/>
+      <c r="T64" s="76"/>
+      <c r="U64" s="76"/>
+      <c r="V64" s="76"/>
+      <c r="W64" s="76"/>
+      <c r="X64" s="76"/>
+      <c r="Y64" s="76"/>
+      <c r="Z64" s="76"/>
+      <c r="AA64" s="76"/>
+      <c r="AB64" s="76"/>
+    </row>
+    <row r="65" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B65" s="76" t="s">
+        <v>228</v>
+      </c>
+      <c r="C65" s="76"/>
+      <c r="D65" s="76"/>
+      <c r="E65" s="76"/>
+      <c r="F65" s="76"/>
+      <c r="G65" s="76"/>
+      <c r="H65" s="76"/>
+      <c r="I65" s="76"/>
+      <c r="J65" s="76"/>
+      <c r="K65" s="76"/>
+      <c r="L65" s="76"/>
+      <c r="M65" s="76"/>
+      <c r="N65" s="76"/>
+      <c r="O65" s="76"/>
+      <c r="P65" s="76"/>
+      <c r="Q65" s="76"/>
+      <c r="R65" s="76"/>
+      <c r="S65" s="76"/>
+      <c r="T65" s="76"/>
+      <c r="U65" s="76"/>
+      <c r="V65" s="76"/>
+      <c r="W65" s="76"/>
+      <c r="X65" s="76"/>
+      <c r="Y65" s="76"/>
+      <c r="Z65" s="76"/>
+      <c r="AA65" s="76"/>
+      <c r="AB65" s="76"/>
+    </row>
+    <row r="66" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B66" s="76" t="s">
         <v>227</v>
       </c>
-      <c r="C63" s="77"/>
-      <c r="D63" s="77"/>
-      <c r="E63" s="77"/>
-      <c r="F63" s="77"/>
-      <c r="G63" s="77"/>
-      <c r="H63" s="77"/>
-      <c r="I63" s="77"/>
-      <c r="J63" s="77"/>
-      <c r="K63" s="77"/>
-      <c r="L63" s="77"/>
-      <c r="M63" s="77"/>
-      <c r="N63" s="77"/>
-      <c r="O63" s="77"/>
-      <c r="P63" s="77"/>
-      <c r="Q63" s="77"/>
-      <c r="R63" s="77"/>
-      <c r="S63" s="77"/>
-      <c r="T63" s="77"/>
-      <c r="U63" s="77"/>
-      <c r="V63" s="77"/>
-      <c r="W63" s="77"/>
-      <c r="X63" s="77"/>
-      <c r="Y63" s="77"/>
-      <c r="Z63" s="77"/>
-      <c r="AA63" s="77"/>
-      <c r="AB63" s="77"/>
-    </row>
-    <row r="64" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B64" s="77" t="s">
-        <v>228</v>
-      </c>
-      <c r="C64" s="77"/>
-      <c r="D64" s="77"/>
-      <c r="E64" s="77"/>
-      <c r="F64" s="77"/>
-      <c r="G64" s="77"/>
-      <c r="H64" s="77"/>
-      <c r="I64" s="77"/>
-      <c r="J64" s="77"/>
-      <c r="K64" s="77"/>
-      <c r="L64" s="77"/>
-      <c r="M64" s="77"/>
-      <c r="N64" s="77"/>
-      <c r="O64" s="77"/>
-      <c r="P64" s="77"/>
-      <c r="Q64" s="77"/>
-      <c r="R64" s="77"/>
-      <c r="S64" s="77"/>
-      <c r="T64" s="77"/>
-      <c r="U64" s="77"/>
-      <c r="V64" s="77"/>
-      <c r="W64" s="77"/>
-      <c r="X64" s="77"/>
-      <c r="Y64" s="77"/>
-      <c r="Z64" s="77"/>
-      <c r="AA64" s="77"/>
-      <c r="AB64" s="77"/>
-    </row>
-    <row r="65" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B65" s="77" t="s">
-        <v>230</v>
-      </c>
-      <c r="C65" s="77"/>
-      <c r="D65" s="77"/>
-      <c r="E65" s="77"/>
-      <c r="F65" s="77"/>
-      <c r="G65" s="77"/>
-      <c r="H65" s="77"/>
-      <c r="I65" s="77"/>
-      <c r="J65" s="77"/>
-      <c r="K65" s="77"/>
-      <c r="L65" s="77"/>
-      <c r="M65" s="77"/>
-      <c r="N65" s="77"/>
-      <c r="O65" s="77"/>
-      <c r="P65" s="77"/>
-      <c r="Q65" s="77"/>
-      <c r="R65" s="77"/>
-      <c r="S65" s="77"/>
-      <c r="T65" s="77"/>
-      <c r="U65" s="77"/>
-      <c r="V65" s="77"/>
-      <c r="W65" s="77"/>
-      <c r="X65" s="77"/>
-      <c r="Y65" s="77"/>
-      <c r="Z65" s="77"/>
-      <c r="AA65" s="77"/>
-      <c r="AB65" s="77"/>
-    </row>
-    <row r="66" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B66" s="77" t="s">
+      <c r="C66" s="76"/>
+      <c r="D66" s="76"/>
+      <c r="E66" s="76"/>
+      <c r="F66" s="76"/>
+      <c r="G66" s="76"/>
+      <c r="H66" s="76"/>
+      <c r="I66" s="76"/>
+      <c r="J66" s="76"/>
+      <c r="K66" s="76"/>
+      <c r="L66" s="76"/>
+      <c r="M66" s="76"/>
+      <c r="N66" s="76"/>
+      <c r="O66" s="76"/>
+      <c r="P66" s="76"/>
+      <c r="Q66" s="76"/>
+      <c r="R66" s="76"/>
+      <c r="S66" s="76"/>
+      <c r="T66" s="76"/>
+      <c r="U66" s="76"/>
+      <c r="V66" s="76"/>
+      <c r="W66" s="76"/>
+      <c r="X66" s="76"/>
+      <c r="Y66" s="76"/>
+      <c r="Z66" s="76"/>
+      <c r="AA66" s="76"/>
+      <c r="AB66" s="76"/>
+    </row>
+    <row r="67" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B67" s="76" t="s">
         <v>229</v>
       </c>
-      <c r="C66" s="77"/>
-      <c r="D66" s="77"/>
-      <c r="E66" s="77"/>
-      <c r="F66" s="77"/>
-      <c r="G66" s="77"/>
-      <c r="H66" s="77"/>
-      <c r="I66" s="77"/>
-      <c r="J66" s="77"/>
-      <c r="K66" s="77"/>
-      <c r="L66" s="77"/>
-      <c r="M66" s="77"/>
-      <c r="N66" s="77"/>
-      <c r="O66" s="77"/>
-      <c r="P66" s="77"/>
-      <c r="Q66" s="77"/>
-      <c r="R66" s="77"/>
-      <c r="S66" s="77"/>
-      <c r="T66" s="77"/>
-      <c r="U66" s="77"/>
-      <c r="V66" s="77"/>
-      <c r="W66" s="77"/>
-      <c r="X66" s="77"/>
-      <c r="Y66" s="77"/>
-      <c r="Z66" s="77"/>
-      <c r="AA66" s="77"/>
-      <c r="AB66" s="77"/>
-    </row>
-    <row r="67" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B67" s="77" t="s">
-        <v>231</v>
-      </c>
-      <c r="C67" s="77"/>
-      <c r="D67" s="77"/>
-      <c r="E67" s="77"/>
-      <c r="F67" s="77"/>
-      <c r="G67" s="77"/>
-      <c r="H67" s="77"/>
-      <c r="I67" s="77"/>
-      <c r="J67" s="77"/>
-      <c r="K67" s="77"/>
-      <c r="L67" s="77"/>
-      <c r="M67" s="77"/>
-      <c r="N67" s="77"/>
-      <c r="O67" s="77"/>
-      <c r="P67" s="77"/>
-      <c r="Q67" s="77"/>
-      <c r="R67" s="77"/>
-      <c r="S67" s="77"/>
-      <c r="T67" s="77"/>
-      <c r="U67" s="77"/>
-      <c r="V67" s="77"/>
-      <c r="W67" s="77"/>
-      <c r="X67" s="77"/>
-      <c r="Y67" s="77"/>
-      <c r="Z67" s="77"/>
-      <c r="AA67" s="77"/>
-      <c r="AB67" s="77"/>
+      <c r="C67" s="76"/>
+      <c r="D67" s="76"/>
+      <c r="E67" s="76"/>
+      <c r="F67" s="76"/>
+      <c r="G67" s="76"/>
+      <c r="H67" s="76"/>
+      <c r="I67" s="76"/>
+      <c r="J67" s="76"/>
+      <c r="K67" s="76"/>
+      <c r="L67" s="76"/>
+      <c r="M67" s="76"/>
+      <c r="N67" s="76"/>
+      <c r="O67" s="76"/>
+      <c r="P67" s="76"/>
+      <c r="Q67" s="76"/>
+      <c r="R67" s="76"/>
+      <c r="S67" s="76"/>
+      <c r="T67" s="76"/>
+      <c r="U67" s="76"/>
+      <c r="V67" s="76"/>
+      <c r="W67" s="76"/>
+      <c r="X67" s="76"/>
+      <c r="Y67" s="76"/>
+      <c r="Z67" s="76"/>
+      <c r="AA67" s="76"/>
+      <c r="AB67" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="30">

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432EA86E-CEFA-47E3-A94F-7640DAEB79C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236A9A78-398C-4A35-9A08-78AB3E66D440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="243">
   <si>
     <t>SIGNOMALY</t>
   </si>
@@ -2246,411 +2246,15 @@
     <t>2. Lời đối thoại</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Well, everything comes at a price.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Heh… another one, huh? Are you really that greedy for money?</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Win, and you might walk away with that massive fortune. But lose… and we take no responsibility. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> If you want the treasure, you’ll have to play the game just like the contract says.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> You’ll become nothing more than entertainment for Them. Hahahaha…</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  So… ready to step into hell?</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  Good. Here are the rules of our little game. See that door beside you, ahh the one with the… unusual requirement? That’s your way out. But to unlock it, you’ll need to fulfill two conditions.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  First, look at the door in front of you. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  See the timer? Fifteen minutes.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  That’s all the time you have left to finish the game. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  Meet the other condition before it hits zero, and the door will open. If not… hahaha.</t>
-    </r>
+    <t>You’ll become nothing more than entertainment for Them. Hahahaha…</t>
   </si>
   <si>
     <t>***Lưu ý: Mỗi đoạn được viết dưới đây thì đều là từng đoạn sẽ hiển thị ra khi người chơi click chuột sang đoạn kế.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  Second, beyond this room lies a space filled with all sorts of objects. Your task is to find the anomalies among them.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  If you suspect something’s off, stand your ground and face it directly, don’t look away. It will present you with a puzzle. Solve it, and you’ll set it free.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  Each of them has its own timer hovering overhead… and if their time runs out, it’s game over for you too. So keep your eyes sharp.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  But don’t get too corky. These anomalies aren’t as forgiving as I am. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  Free them all within the fifteen minutes I’ve given you, and the door will open. Walk through it, and that million-dollar prize is yours.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  …assuming you can pull it off. Plenty have tried. Plenty have died. Turns out, if you want something valuable, you have to pay a matching price.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  Good luck? I guess… and perhaps we’ll meet again or not, hahaha…</t>
-    </r>
-  </si>
-  <si>
     <t>2.1. Tương tác lần đầu: hiển thị toàn bộ cuộc trò chuyện</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>NPC:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  See that door beside you, ahh the one with the… unusual requirement? That’s your way out. But to unlock it, you’ll need to fulfill two conditions.</t>
-    </r>
-  </si>
-  <si>
     <t>***Lưu ý: không thể skip, double click chạy hết chữ, hay thoát ra ngoài vào gameplay.</t>
   </si>
   <si>
@@ -2670,6 +2274,66 @@
   </si>
   <si>
     <t>Chưa có</t>
+  </si>
+  <si>
+    <t>Đang Render</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPC: </t>
+  </si>
+  <si>
+    <t>Heh… another one, huh? Are you really that greedy for money?</t>
+  </si>
+  <si>
+    <t>Well, everything comes at a price.</t>
+  </si>
+  <si>
+    <t>If you want the treasure, you’ll have to play the game just like the contract says.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Win, and you might walk away with that massive fortune. But lose… and we take no responsibility. </t>
+  </si>
+  <si>
+    <t>So… ready to step into hell?</t>
+  </si>
+  <si>
+    <t>Good. Here are the rules of our little game. See that door beside you, ahh the one with the… unusual requirement? That’s your way out. But to unlock it, you’ll need to fulfill two conditions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First, look at the door in front of you. </t>
+  </si>
+  <si>
+    <t>See the timer? Fifteen minutes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That’s all the time you have left to finish the game. </t>
+  </si>
+  <si>
+    <t>Meet the other condition before it hits zero, and the door will open. If not… hahaha.</t>
+  </si>
+  <si>
+    <t>Second, beyond this room lies a space filled with all sorts of objects. Your task is to find the anomalies among them.</t>
+  </si>
+  <si>
+    <t>If you suspect something’s off, stand your ground and face it directly, don’t look away. It will present you with a puzzle. Solve it, and you’ll set it free.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">But don’t get too corky. These anomalies aren’t as forgiving as I am. </t>
+  </si>
+  <si>
+    <t>Each of them has its own timer hovering overhead… and if their time runs out, it’s game over for you too. So keep your eyes sharp.</t>
+  </si>
+  <si>
+    <t>Free them all within the fifteen minutes I’ve given you, and the door will open. Walk through it, and that million-dollar prize is yours.</t>
+  </si>
+  <si>
+    <t>…assuming you can pull it off. Plenty have tried. Plenty have died. Turns out, if you want something valuable, you have to pay a matching price.</t>
+  </si>
+  <si>
+    <t>Good luck? I guess… and perhaps we’ll meet again or not, hahaha…</t>
+  </si>
+  <si>
+    <t>See that door beside you, ahh the one with the… unusual requirement? That’s your way out. But to unlock it, you’ll need to fulfill two conditions.</t>
   </si>
 </sst>
 </file>
@@ -6572,7 +6236,7 @@
     </row>
     <row r="123" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B123" s="75" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
     </row>
     <row r="124" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
@@ -6656,7 +6320,7 @@
     </row>
     <row r="4" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="28" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="C4" s="28"/>
       <c r="D4" s="41" t="s">
@@ -6684,7 +6348,7 @@
       <c r="R4" s="28"/>
       <c r="S4" s="28"/>
       <c r="T4" s="28" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="U4" s="28"/>
     </row>
@@ -6718,7 +6382,7 @@
       <c r="R5" s="35"/>
       <c r="S5" s="35"/>
       <c r="T5" s="92" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="U5" s="92"/>
     </row>
@@ -6752,7 +6416,7 @@
       <c r="R6" s="35"/>
       <c r="S6" s="35"/>
       <c r="T6" s="92" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="U6" s="92"/>
     </row>
@@ -6786,7 +6450,7 @@
       <c r="R7" s="35"/>
       <c r="S7" s="35"/>
       <c r="T7" s="92" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="U7" s="92"/>
     </row>
@@ -6820,7 +6484,7 @@
       <c r="R8" s="35"/>
       <c r="S8" s="35"/>
       <c r="T8" s="92" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="U8" s="92"/>
     </row>
@@ -6854,7 +6518,7 @@
       <c r="R9" s="35"/>
       <c r="S9" s="35"/>
       <c r="T9" s="92" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="U9" s="92"/>
     </row>
@@ -6888,7 +6552,7 @@
       <c r="R10" s="35"/>
       <c r="S10" s="35"/>
       <c r="T10" s="92" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="U10" s="92"/>
     </row>
@@ -6922,7 +6586,7 @@
       <c r="R11" s="35"/>
       <c r="S11" s="35"/>
       <c r="T11" s="92" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="U11" s="92"/>
     </row>
@@ -6956,7 +6620,7 @@
       <c r="R12" s="35"/>
       <c r="S12" s="35"/>
       <c r="T12" s="92" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="U12" s="92"/>
     </row>
@@ -6990,7 +6654,7 @@
       <c r="R13" s="35"/>
       <c r="S13" s="35"/>
       <c r="T13" s="92" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="U13" s="92"/>
     </row>
@@ -7024,7 +6688,7 @@
       <c r="R14" s="35"/>
       <c r="S14" s="35"/>
       <c r="T14" s="92" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="U14" s="92"/>
     </row>
@@ -7058,7 +6722,7 @@
       <c r="R15" s="35"/>
       <c r="S15" s="35"/>
       <c r="T15" s="92" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="U15" s="92"/>
     </row>
@@ -7092,7 +6756,7 @@
       <c r="R16" s="35"/>
       <c r="S16" s="35"/>
       <c r="T16" s="92" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="U16" s="92"/>
     </row>
@@ -7126,7 +6790,7 @@
       <c r="R17" s="35"/>
       <c r="S17" s="35"/>
       <c r="T17" s="92" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="U17" s="92"/>
     </row>
@@ -7160,7 +6824,7 @@
       <c r="R18" s="35"/>
       <c r="S18" s="35"/>
       <c r="T18" s="92" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="U18" s="92"/>
     </row>
@@ -7194,7 +6858,7 @@
       <c r="R19" s="35"/>
       <c r="S19" s="35"/>
       <c r="T19" s="92" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="U19" s="92"/>
     </row>
@@ -7228,7 +6892,7 @@
       <c r="R20" s="35"/>
       <c r="S20" s="35"/>
       <c r="T20" s="92" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="U20" s="92"/>
     </row>
@@ -7262,7 +6926,7 @@
       <c r="R21" s="35"/>
       <c r="S21" s="35"/>
       <c r="T21" s="92" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="U21" s="92"/>
     </row>
@@ -7296,7 +6960,7 @@
       <c r="R22" s="35"/>
       <c r="S22" s="35"/>
       <c r="T22" s="92" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="U22" s="92"/>
     </row>
@@ -7330,7 +6994,7 @@
       <c r="R23" s="35"/>
       <c r="S23" s="35"/>
       <c r="T23" s="92" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="U23" s="92"/>
     </row>
@@ -7364,7 +7028,7 @@
       <c r="R24" s="35"/>
       <c r="S24" s="35"/>
       <c r="T24" s="92" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="U24" s="92"/>
     </row>
@@ -7398,7 +7062,7 @@
       <c r="R25" s="35"/>
       <c r="S25" s="35"/>
       <c r="T25" s="92" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="U25" s="92"/>
     </row>
@@ -7432,7 +7096,7 @@
       <c r="R26" s="35"/>
       <c r="S26" s="35"/>
       <c r="T26" s="92" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="U26" s="92"/>
     </row>
@@ -7684,22 +7348,25 @@
     </row>
     <row r="31" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
     </row>
     <row r="32" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B33" s="8" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="75" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B33" s="8" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="35" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="76" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="C35" s="76"/>
       <c r="D35" s="76"/>
@@ -7728,9 +7395,9 @@
       <c r="AA35" s="76"/>
       <c r="AB35" s="76"/>
     </row>
-    <row r="36" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="76" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C36" s="76"/>
       <c r="D36" s="76"/>
@@ -7759,9 +7426,9 @@
       <c r="AA36" s="76"/>
       <c r="AB36" s="76"/>
     </row>
-    <row r="37" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="76" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="C37" s="76"/>
       <c r="D37" s="76"/>
@@ -7790,9 +7457,9 @@
       <c r="AA37" s="76"/>
       <c r="AB37" s="76"/>
     </row>
-    <row r="38" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="76" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="C38" s="76"/>
       <c r="D38" s="76"/>
@@ -7821,9 +7488,9 @@
       <c r="AA38" s="76"/>
       <c r="AB38" s="76"/>
     </row>
-    <row r="39" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="76" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C39" s="76"/>
       <c r="D39" s="76"/>
@@ -7852,9 +7519,9 @@
       <c r="AA39" s="76"/>
       <c r="AB39" s="76"/>
     </row>
-    <row r="41" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="76" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="C41" s="76"/>
       <c r="D41" s="76"/>
@@ -7883,9 +7550,9 @@
       <c r="AA41" s="76"/>
       <c r="AB41" s="76"/>
     </row>
-    <row r="42" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B42" s="76" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="C42" s="76"/>
       <c r="D42" s="76"/>
@@ -7914,9 +7581,9 @@
       <c r="AA42" s="76"/>
       <c r="AB42" s="76"/>
     </row>
-    <row r="43" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B43" s="76" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C43" s="76"/>
       <c r="D43" s="76"/>
@@ -7945,9 +7612,9 @@
       <c r="AA43" s="76"/>
       <c r="AB43" s="76"/>
     </row>
-    <row r="44" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B44" s="76" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C44" s="76"/>
       <c r="D44" s="76"/>
@@ -7976,9 +7643,9 @@
       <c r="AA44" s="76"/>
       <c r="AB44" s="76"/>
     </row>
-    <row r="45" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="C45" s="76"/>
       <c r="D45" s="76"/>
@@ -8007,9 +7674,9 @@
       <c r="AA45" s="76"/>
       <c r="AB45" s="76"/>
     </row>
-    <row r="46" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B46" s="76" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="C46" s="76"/>
       <c r="D46" s="76"/>
@@ -8038,9 +7705,9 @@
       <c r="AA46" s="76"/>
       <c r="AB46" s="76"/>
     </row>
-    <row r="47" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B47" s="76" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="C47" s="76"/>
       <c r="D47" s="76"/>
@@ -8069,9 +7736,9 @@
       <c r="AA47" s="76"/>
       <c r="AB47" s="76"/>
     </row>
-    <row r="48" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B48" s="76" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C48" s="76"/>
       <c r="D48" s="76"/>
@@ -8100,9 +7767,9 @@
       <c r="AA48" s="76"/>
       <c r="AB48" s="76"/>
     </row>
-    <row r="49" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B49" s="76" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C49" s="76"/>
       <c r="D49" s="76"/>
@@ -8131,9 +7798,9 @@
       <c r="AA49" s="76"/>
       <c r="AB49" s="76"/>
     </row>
-    <row r="50" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B50" s="76" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="C50" s="76"/>
       <c r="D50" s="76"/>
@@ -8162,9 +7829,9 @@
       <c r="AA50" s="76"/>
       <c r="AB50" s="76"/>
     </row>
-    <row r="51" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B51" s="76" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C51" s="76"/>
       <c r="D51" s="76"/>
@@ -8193,9 +7860,9 @@
       <c r="AA51" s="76"/>
       <c r="AB51" s="76"/>
     </row>
-    <row r="52" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B52" s="76" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C52" s="76"/>
       <c r="D52" s="76"/>
@@ -8224,9 +7891,9 @@
       <c r="AA52" s="76"/>
       <c r="AB52" s="76"/>
     </row>
-    <row r="53" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B53" s="76" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="C53" s="76"/>
       <c r="D53" s="76"/>
@@ -8255,22 +7922,25 @@
       <c r="AA53" s="76"/>
       <c r="AB53" s="76"/>
     </row>
-    <row r="55" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B55" s="8" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="56" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B56" s="8" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="57" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B57" s="8"/>
     </row>
-    <row r="58" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A58" s="75" t="s">
+        <v>224</v>
+      </c>
       <c r="B58" s="76" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="C58" s="76"/>
       <c r="D58" s="76"/>
@@ -8299,9 +7969,9 @@
       <c r="AA58" s="76"/>
       <c r="AB58" s="76"/>
     </row>
-    <row r="59" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B59" s="76" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C59" s="76"/>
       <c r="D59" s="76"/>
@@ -8330,9 +8000,9 @@
       <c r="AA59" s="76"/>
       <c r="AB59" s="76"/>
     </row>
-    <row r="60" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B60" s="76" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C60" s="76"/>
       <c r="D60" s="76"/>
@@ -8361,9 +8031,9 @@
       <c r="AA60" s="76"/>
       <c r="AB60" s="76"/>
     </row>
-    <row r="61" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B61" s="76" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="C61" s="76"/>
       <c r="D61" s="76"/>
@@ -8392,9 +8062,9 @@
       <c r="AA61" s="76"/>
       <c r="AB61" s="76"/>
     </row>
-    <row r="62" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B62" s="76" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="C62" s="76"/>
       <c r="D62" s="76"/>
@@ -8423,9 +8093,9 @@
       <c r="AA62" s="76"/>
       <c r="AB62" s="76"/>
     </row>
-    <row r="63" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B63" s="76" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="C63" s="76"/>
       <c r="D63" s="76"/>
@@ -8454,9 +8124,9 @@
       <c r="AA63" s="76"/>
       <c r="AB63" s="76"/>
     </row>
-    <row r="64" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B64" s="76" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C64" s="76"/>
       <c r="D64" s="76"/>
@@ -8487,7 +8157,7 @@
     </row>
     <row r="65" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B65" s="76" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C65" s="76"/>
       <c r="D65" s="76"/>
@@ -8518,7 +8188,7 @@
     </row>
     <row r="66" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B66" s="76" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="C66" s="76"/>
       <c r="D66" s="76"/>
@@ -8549,7 +8219,7 @@
     </row>
     <row r="67" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B67" s="76" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C67" s="76"/>
       <c r="D67" s="76"/>

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236A9A78-398C-4A35-9A08-78AB3E66D440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226ED0FD-6AFE-4068-A0C8-4116B067C007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -2340,9 +2340,21 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="15"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2557,86 +2569,214 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2644,160 +2784,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4203,29 +4215,29 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:26" ht="46.5" x14ac:dyDescent="0.7">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
     </row>
     <row r="3" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
@@ -4249,104 +4261,104 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="53" t="s">
+      <c r="B10" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="45"/>
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="53" t="s">
+      <c r="B11" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
     </row>
     <row r="13" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="49" t="s">
+      <c r="B13" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="49"/>
-      <c r="L13" s="49"/>
-      <c r="M13" s="49"/>
-      <c r="N13" s="49"/>
-      <c r="O13" s="49"/>
-      <c r="P13" s="49"/>
-      <c r="Q13" s="49"/>
-      <c r="R13" s="49"/>
-      <c r="S13" s="49"/>
-      <c r="T13" s="49"/>
-      <c r="U13" s="49"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="41"/>
+      <c r="P13" s="41"/>
+      <c r="Q13" s="41"/>
+      <c r="R13" s="41"/>
+      <c r="S13" s="41"/>
+      <c r="T13" s="41"/>
+      <c r="U13" s="41"/>
     </row>
     <row r="14" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="45"/>
-      <c r="L14" s="45"/>
-      <c r="M14" s="45"/>
-      <c r="N14" s="45"/>
-      <c r="O14" s="45"/>
-      <c r="P14" s="45"/>
-      <c r="Q14" s="45"/>
-      <c r="R14" s="45"/>
-      <c r="S14" s="45"/>
-      <c r="T14" s="45"/>
-      <c r="U14" s="45"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37"/>
+      <c r="K14" s="37"/>
+      <c r="L14" s="37"/>
+      <c r="M14" s="37"/>
+      <c r="N14" s="37"/>
+      <c r="O14" s="37"/>
+      <c r="P14" s="37"/>
+      <c r="Q14" s="37"/>
+      <c r="R14" s="37"/>
+      <c r="S14" s="37"/>
+      <c r="T14" s="37"/>
+      <c r="U14" s="37"/>
     </row>
     <row r="15" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
@@ -4362,28 +4374,28 @@
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:26" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="46"/>
-      <c r="M16" s="46"/>
-      <c r="N16" s="46"/>
-      <c r="O16" s="46"/>
-      <c r="P16" s="46"/>
-      <c r="Q16" s="46"/>
-      <c r="R16" s="46"/>
-      <c r="S16" s="46"/>
-      <c r="T16" s="46"/>
-      <c r="U16" s="46"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="38"/>
+      <c r="T16" s="38"/>
+      <c r="U16" s="38"/>
       <c r="V16" s="6"/>
       <c r="W16" s="6"/>
       <c r="X16" s="6"/>
@@ -4391,100 +4403,100 @@
       <c r="Z16" s="6"/>
     </row>
     <row r="17" spans="1:21" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="46"/>
-      <c r="N17" s="46"/>
-      <c r="O17" s="46"/>
-      <c r="P17" s="46"/>
-      <c r="Q17" s="46"/>
-      <c r="R17" s="46"/>
-      <c r="S17" s="46"/>
-      <c r="T17" s="46"/>
-      <c r="U17" s="46"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="38"/>
+      <c r="P17" s="38"/>
+      <c r="Q17" s="38"/>
+      <c r="R17" s="38"/>
+      <c r="S17" s="38"/>
+      <c r="T17" s="38"/>
+      <c r="U17" s="38"/>
     </row>
     <row r="18" spans="1:21" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="45"/>
-      <c r="P18" s="45"/>
-      <c r="Q18" s="45"/>
-      <c r="R18" s="45"/>
-      <c r="S18" s="45"/>
-      <c r="T18" s="45"/>
-      <c r="U18" s="45"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="37"/>
+      <c r="M18" s="37"/>
+      <c r="N18" s="37"/>
+      <c r="O18" s="37"/>
+      <c r="P18" s="37"/>
+      <c r="Q18" s="37"/>
+      <c r="R18" s="37"/>
+      <c r="S18" s="37"/>
+      <c r="T18" s="37"/>
+      <c r="U18" s="37"/>
     </row>
     <row r="19" spans="1:21" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="48"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="40"/>
+      <c r="P19" s="40"/>
+      <c r="Q19" s="40"/>
+      <c r="R19" s="40"/>
+      <c r="S19" s="40"/>
+      <c r="T19" s="40"/>
+      <c r="U19" s="40"/>
     </row>
     <row r="20" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="51" t="s">
+      <c r="B20" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51"/>
-      <c r="K20" s="51"/>
-      <c r="L20" s="51"/>
-      <c r="M20" s="51"/>
-      <c r="N20" s="51"/>
-      <c r="O20" s="51"/>
-      <c r="P20" s="51"/>
-      <c r="Q20" s="51"/>
-      <c r="R20" s="51"/>
-      <c r="S20" s="51"/>
-      <c r="T20" s="51"/>
-      <c r="U20" s="51"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="43"/>
+      <c r="R20" s="43"/>
+      <c r="S20" s="43"/>
+      <c r="T20" s="43"/>
+      <c r="U20" s="43"/>
     </row>
     <row r="22" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
@@ -4632,372 +4644,370 @@
       <c r="B4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28" t="s">
+      <c r="D4" s="55"/>
+      <c r="E4" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="28"/>
-      <c r="G4" s="56" t="s">
+      <c r="F4" s="55"/>
+      <c r="G4" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56" t="s">
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="56"/>
-      <c r="R4" s="56"/>
-      <c r="S4" s="56"/>
-      <c r="T4" s="56"/>
-      <c r="U4" s="56"/>
-      <c r="V4" s="56"/>
-      <c r="W4" s="56"/>
-      <c r="X4" s="56"/>
-      <c r="Y4" s="56"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46"/>
+      <c r="S4" s="46"/>
+      <c r="T4" s="46"/>
+      <c r="U4" s="46"/>
+      <c r="V4" s="46"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="46"/>
+      <c r="Y4" s="46"/>
     </row>
     <row r="5" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11">
         <v>1</v>
       </c>
-      <c r="C5" s="61" t="s">
+      <c r="C5" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="61"/>
-      <c r="E5" s="62" t="s">
+      <c r="D5" s="52"/>
+      <c r="E5" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="62"/>
-      <c r="G5" s="59" t="s">
+      <c r="F5" s="53"/>
+      <c r="G5" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="59"/>
-      <c r="L5" s="59"/>
-      <c r="M5" s="57" t="s">
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="N5" s="57"/>
-      <c r="O5" s="57"/>
-      <c r="P5" s="57"/>
-      <c r="Q5" s="57"/>
-      <c r="R5" s="57"/>
-      <c r="S5" s="57"/>
-      <c r="T5" s="57"/>
-      <c r="U5" s="57"/>
-      <c r="V5" s="57"/>
-      <c r="W5" s="57"/>
-      <c r="X5" s="57"/>
-      <c r="Y5" s="57"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
+      <c r="Q5" s="47"/>
+      <c r="R5" s="47"/>
+      <c r="S5" s="47"/>
+      <c r="T5" s="47"/>
+      <c r="U5" s="47"/>
+      <c r="V5" s="47"/>
+      <c r="W5" s="47"/>
+      <c r="X5" s="47"/>
+      <c r="Y5" s="47"/>
     </row>
     <row r="6" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11">
         <v>2</v>
       </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="62" t="s">
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="62"/>
-      <c r="G6" s="59" t="s">
+      <c r="F6" s="53"/>
+      <c r="G6" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="58" t="s">
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="N6" s="57"/>
-      <c r="O6" s="57"/>
-      <c r="P6" s="57"/>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="57"/>
-      <c r="S6" s="57"/>
-      <c r="T6" s="57"/>
-      <c r="U6" s="57"/>
-      <c r="V6" s="57"/>
-      <c r="W6" s="57"/>
-      <c r="X6" s="57"/>
-      <c r="Y6" s="57"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="47"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="47"/>
+      <c r="U6" s="47"/>
+      <c r="V6" s="47"/>
+      <c r="W6" s="47"/>
+      <c r="X6" s="47"/>
+      <c r="Y6" s="47"/>
     </row>
     <row r="7" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11">
         <v>3</v>
       </c>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="62" t="s">
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="62"/>
-      <c r="G7" s="59" t="s">
+      <c r="F7" s="53"/>
+      <c r="G7" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="59"/>
-      <c r="L7" s="59"/>
-      <c r="M7" s="55" t="s">
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="51"/>
+      <c r="M7" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="55"/>
-      <c r="O7" s="55"/>
-      <c r="P7" s="55"/>
-      <c r="Q7" s="55"/>
-      <c r="R7" s="55"/>
-      <c r="S7" s="55"/>
-      <c r="T7" s="55"/>
-      <c r="U7" s="55"/>
-      <c r="V7" s="55"/>
-      <c r="W7" s="55"/>
-      <c r="X7" s="55"/>
-      <c r="Y7" s="55"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="49"/>
+      <c r="R7" s="49"/>
+      <c r="S7" s="49"/>
+      <c r="T7" s="49"/>
+      <c r="U7" s="49"/>
+      <c r="V7" s="49"/>
+      <c r="W7" s="49"/>
+      <c r="X7" s="49"/>
+      <c r="Y7" s="49"/>
     </row>
     <row r="8" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11">
         <v>4</v>
       </c>
-      <c r="C8" s="61" t="s">
+      <c r="C8" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="61"/>
-      <c r="E8" s="62" t="s">
+      <c r="D8" s="52"/>
+      <c r="E8" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="62"/>
-      <c r="G8" s="59" t="s">
+      <c r="F8" s="53"/>
+      <c r="G8" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="59"/>
-      <c r="K8" s="59"/>
-      <c r="L8" s="59"/>
-      <c r="M8" s="54" t="s">
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="N8" s="55"/>
-      <c r="O8" s="55"/>
-      <c r="P8" s="55"/>
-      <c r="Q8" s="55"/>
-      <c r="R8" s="55"/>
-      <c r="S8" s="55"/>
-      <c r="T8" s="55"/>
-      <c r="U8" s="55"/>
-      <c r="V8" s="55"/>
-      <c r="W8" s="55"/>
-      <c r="X8" s="55"/>
-      <c r="Y8" s="55"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="49"/>
+      <c r="P8" s="49"/>
+      <c r="Q8" s="49"/>
+      <c r="R8" s="49"/>
+      <c r="S8" s="49"/>
+      <c r="T8" s="49"/>
+      <c r="U8" s="49"/>
+      <c r="V8" s="49"/>
+      <c r="W8" s="49"/>
+      <c r="X8" s="49"/>
+      <c r="Y8" s="49"/>
     </row>
     <row r="9" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11">
         <v>5</v>
       </c>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="62" t="s">
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="62"/>
-      <c r="G9" s="59" t="s">
+      <c r="F9" s="53"/>
+      <c r="G9" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="59"/>
-      <c r="K9" s="59"/>
-      <c r="L9" s="59"/>
-      <c r="M9" s="54" t="s">
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="51"/>
+      <c r="M9" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="55"/>
-      <c r="O9" s="55"/>
-      <c r="P9" s="55"/>
-      <c r="Q9" s="55"/>
-      <c r="R9" s="55"/>
-      <c r="S9" s="55"/>
-      <c r="T9" s="55"/>
-      <c r="U9" s="55"/>
-      <c r="V9" s="55"/>
-      <c r="W9" s="55"/>
-      <c r="X9" s="55"/>
-      <c r="Y9" s="55"/>
+      <c r="N9" s="49"/>
+      <c r="O9" s="49"/>
+      <c r="P9" s="49"/>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="49"/>
+      <c r="S9" s="49"/>
+      <c r="T9" s="49"/>
+      <c r="U9" s="49"/>
+      <c r="V9" s="49"/>
+      <c r="W9" s="49"/>
+      <c r="X9" s="49"/>
+      <c r="Y9" s="49"/>
     </row>
     <row r="10" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="11">
         <v>6</v>
       </c>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="62" t="s">
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="62"/>
-      <c r="G10" s="59" t="s">
+      <c r="F10" s="53"/>
+      <c r="G10" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59"/>
-      <c r="J10" s="59"/>
-      <c r="K10" s="59"/>
-      <c r="L10" s="59"/>
-      <c r="M10" s="54" t="s">
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="N10" s="55"/>
-      <c r="O10" s="55"/>
-      <c r="P10" s="55"/>
-      <c r="Q10" s="55"/>
-      <c r="R10" s="55"/>
-      <c r="S10" s="55"/>
-      <c r="T10" s="55"/>
-      <c r="U10" s="55"/>
-      <c r="V10" s="55"/>
-      <c r="W10" s="55"/>
-      <c r="X10" s="55"/>
-      <c r="Y10" s="55"/>
+      <c r="N10" s="49"/>
+      <c r="O10" s="49"/>
+      <c r="P10" s="49"/>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="49"/>
+      <c r="S10" s="49"/>
+      <c r="T10" s="49"/>
+      <c r="U10" s="49"/>
+      <c r="V10" s="49"/>
+      <c r="W10" s="49"/>
+      <c r="X10" s="49"/>
+      <c r="Y10" s="49"/>
     </row>
     <row r="11" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="11">
         <v>7</v>
       </c>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="62" t="s">
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="62"/>
-      <c r="G11" s="59" t="s">
+      <c r="F11" s="53"/>
+      <c r="G11" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="59"/>
-      <c r="K11" s="59"/>
-      <c r="L11" s="59"/>
-      <c r="M11" s="55" t="s">
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="55"/>
-      <c r="O11" s="55"/>
-      <c r="P11" s="55"/>
-      <c r="Q11" s="55"/>
-      <c r="R11" s="55"/>
-      <c r="S11" s="55"/>
-      <c r="T11" s="55"/>
-      <c r="U11" s="55"/>
-      <c r="V11" s="55"/>
-      <c r="W11" s="55"/>
-      <c r="X11" s="55"/>
-      <c r="Y11" s="55"/>
+      <c r="N11" s="49"/>
+      <c r="O11" s="49"/>
+      <c r="P11" s="49"/>
+      <c r="Q11" s="49"/>
+      <c r="R11" s="49"/>
+      <c r="S11" s="49"/>
+      <c r="T11" s="49"/>
+      <c r="U11" s="49"/>
+      <c r="V11" s="49"/>
+      <c r="W11" s="49"/>
+      <c r="X11" s="49"/>
+      <c r="Y11" s="49"/>
     </row>
     <row r="12" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="11">
         <v>8</v>
       </c>
-      <c r="C12" s="61" t="s">
+      <c r="C12" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="61"/>
-      <c r="E12" s="62" t="s">
+      <c r="D12" s="52"/>
+      <c r="E12" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="62"/>
-      <c r="G12" s="59" t="s">
+      <c r="F12" s="53"/>
+      <c r="G12" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="59"/>
-      <c r="K12" s="59"/>
-      <c r="L12" s="59"/>
-      <c r="M12" s="55" t="s">
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="N12" s="55"/>
-      <c r="O12" s="55"/>
-      <c r="P12" s="55"/>
-      <c r="Q12" s="55"/>
-      <c r="R12" s="55"/>
-      <c r="S12" s="55"/>
-      <c r="T12" s="55"/>
-      <c r="U12" s="55"/>
-      <c r="V12" s="55"/>
-      <c r="W12" s="55"/>
-      <c r="X12" s="55"/>
-      <c r="Y12" s="55"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="49"/>
+      <c r="P12" s="49"/>
+      <c r="Q12" s="49"/>
+      <c r="R12" s="49"/>
+      <c r="S12" s="49"/>
+      <c r="T12" s="49"/>
+      <c r="U12" s="49"/>
+      <c r="V12" s="49"/>
+      <c r="W12" s="49"/>
+      <c r="X12" s="49"/>
+      <c r="Y12" s="49"/>
     </row>
     <row r="46" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B49" s="60" t="s">
+      <c r="B49" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="60"/>
-      <c r="D49" s="60"/>
-      <c r="E49" s="60"/>
-      <c r="F49" s="60"/>
-      <c r="G49" s="60"/>
-      <c r="H49" s="60"/>
-      <c r="I49" s="60"/>
-      <c r="J49" s="60"/>
-      <c r="K49" s="60"/>
-      <c r="L49" s="60"/>
-      <c r="M49" s="60"/>
-      <c r="N49" s="60"/>
-      <c r="O49" s="60"/>
-      <c r="P49" s="60"/>
-      <c r="Q49" s="60"/>
-      <c r="R49" s="60"/>
-      <c r="S49" s="60"/>
-      <c r="T49" s="60"/>
-      <c r="U49" s="60"/>
-      <c r="V49" s="60"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="54"/>
+      <c r="K49" s="54"/>
+      <c r="L49" s="54"/>
+      <c r="M49" s="54"/>
+      <c r="N49" s="54"/>
+      <c r="O49" s="54"/>
+      <c r="P49" s="54"/>
+      <c r="Q49" s="54"/>
+      <c r="R49" s="54"/>
+      <c r="S49" s="54"/>
+      <c r="T49" s="54"/>
+      <c r="U49" s="54"/>
+      <c r="V49" s="54"/>
     </row>
     <row r="50" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B50" s="60"/>
-      <c r="C50" s="60"/>
-      <c r="D50" s="60"/>
-      <c r="E50" s="60"/>
-      <c r="F50" s="60"/>
-      <c r="G50" s="60"/>
-      <c r="H50" s="60"/>
-      <c r="I50" s="60"/>
-      <c r="J50" s="60"/>
-      <c r="K50" s="60"/>
-      <c r="L50" s="60"/>
-      <c r="M50" s="60"/>
-      <c r="N50" s="60"/>
-      <c r="O50" s="60"/>
-      <c r="P50" s="60"/>
-      <c r="Q50" s="60"/>
-      <c r="R50" s="60"/>
-      <c r="S50" s="60"/>
-      <c r="T50" s="60"/>
-      <c r="U50" s="60"/>
-      <c r="V50" s="60"/>
-      <c r="W50" s="89"/>
-      <c r="X50" s="89"/>
-      <c r="Y50" s="89"/>
+      <c r="B50" s="54"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="54"/>
+      <c r="K50" s="54"/>
+      <c r="L50" s="54"/>
+      <c r="M50" s="54"/>
+      <c r="N50" s="54"/>
+      <c r="O50" s="54"/>
+      <c r="P50" s="54"/>
+      <c r="Q50" s="54"/>
+      <c r="R50" s="54"/>
+      <c r="S50" s="54"/>
+      <c r="T50" s="54"/>
+      <c r="U50" s="54"/>
+      <c r="V50" s="54"/>
+      <c r="W50" s="8"/>
+      <c r="X50" s="8"/>
+      <c r="Y50" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
     <mergeCell ref="B49:V50"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
@@ -5017,6 +5027,9 @@
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="M10:Y10"/>
     <mergeCell ref="G11:L11"/>
+    <mergeCell ref="M9:Y9"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
     <mergeCell ref="G12:L12"/>
     <mergeCell ref="M11:Y11"/>
     <mergeCell ref="M12:Y12"/>
@@ -5027,7 +5040,6 @@
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="M9:Y9"/>
     <mergeCell ref="M4:Y4"/>
     <mergeCell ref="M5:Y5"/>
     <mergeCell ref="M6:Y6"/>
@@ -5058,20 +5070,20 @@
       </c>
     </row>
     <row r="8" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L8" s="78" t="s">
+      <c r="L8" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="M8" s="64"/>
-      <c r="N8" s="64"/>
-      <c r="O8" s="64"/>
-      <c r="P8" s="64"/>
-      <c r="Q8" s="64"/>
-      <c r="R8" s="64"/>
-      <c r="S8" s="64"/>
-      <c r="T8" s="64"/>
-      <c r="U8" s="64"/>
-      <c r="V8" s="64"/>
-      <c r="W8" s="64"/>
+      <c r="M8" s="58"/>
+      <c r="N8" s="58"/>
+      <c r="O8" s="58"/>
+      <c r="P8" s="58"/>
+      <c r="Q8" s="58"/>
+      <c r="R8" s="58"/>
+      <c r="S8" s="58"/>
+      <c r="T8" s="58"/>
+      <c r="U8" s="58"/>
+      <c r="V8" s="58"/>
+      <c r="W8" s="58"/>
     </row>
     <row r="9" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="L9" s="7"/>
@@ -5088,25 +5100,25 @@
       <c r="W9" s="7"/>
     </row>
     <row r="10" spans="1:28" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L10" s="76" t="s">
+      <c r="L10" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="M10" s="47"/>
-      <c r="N10" s="47"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="47"/>
-      <c r="Q10" s="47"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="47"/>
-      <c r="T10" s="47"/>
-      <c r="U10" s="47"/>
-      <c r="V10" s="47"/>
-      <c r="W10" s="47"/>
-      <c r="X10" s="47"/>
-      <c r="Y10" s="47"/>
-      <c r="Z10" s="47"/>
-      <c r="AA10" s="47"/>
-      <c r="AB10" s="47"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="39"/>
+      <c r="P10" s="39"/>
+      <c r="Q10" s="39"/>
+      <c r="R10" s="39"/>
+      <c r="S10" s="39"/>
+      <c r="T10" s="39"/>
+      <c r="U10" s="39"/>
+      <c r="V10" s="39"/>
+      <c r="W10" s="39"/>
+      <c r="X10" s="39"/>
+      <c r="Y10" s="39"/>
+      <c r="Z10" s="39"/>
+      <c r="AA10" s="39"/>
+      <c r="AB10" s="39"/>
     </row>
     <row r="11" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="L11" s="7"/>
@@ -5123,25 +5135,25 @@
       <c r="W11" s="7"/>
     </row>
     <row r="12" spans="1:28" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L12" s="76" t="s">
+      <c r="L12" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="M12" s="48"/>
-      <c r="N12" s="48"/>
-      <c r="O12" s="48"/>
-      <c r="P12" s="48"/>
-      <c r="Q12" s="48"/>
-      <c r="R12" s="48"/>
-      <c r="S12" s="48"/>
-      <c r="T12" s="48"/>
-      <c r="U12" s="48"/>
-      <c r="V12" s="48"/>
-      <c r="W12" s="48"/>
-      <c r="X12" s="48"/>
-      <c r="Y12" s="48"/>
-      <c r="Z12" s="48"/>
-      <c r="AA12" s="48"/>
-      <c r="AB12" s="48"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="40"/>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="40"/>
+      <c r="S12" s="40"/>
+      <c r="T12" s="40"/>
+      <c r="U12" s="40"/>
+      <c r="V12" s="40"/>
+      <c r="W12" s="40"/>
+      <c r="X12" s="40"/>
+      <c r="Y12" s="40"/>
+      <c r="Z12" s="40"/>
+      <c r="AA12" s="40"/>
+      <c r="AB12" s="40"/>
     </row>
     <row r="13" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="S13" s="12"/>
@@ -5155,35 +5167,35 @@
       <c r="B16" s="8"/>
     </row>
     <row r="17" spans="2:28" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="61" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
-      <c r="L17" s="69"/>
-      <c r="M17" s="69"/>
-      <c r="N17" s="69"/>
-      <c r="O17" s="69"/>
-      <c r="P17" s="69"/>
-      <c r="Q17" s="69"/>
-      <c r="R17" s="69"/>
-      <c r="S17" s="69"/>
-      <c r="T17" s="69"/>
-      <c r="U17" s="69"/>
-      <c r="V17" s="69"/>
-      <c r="W17" s="69"/>
-      <c r="X17" s="69"/>
-      <c r="Y17" s="69"/>
-      <c r="Z17" s="69"/>
-      <c r="AA17" s="69"/>
-      <c r="AB17" s="69"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="62"/>
+      <c r="K17" s="62"/>
+      <c r="L17" s="62"/>
+      <c r="M17" s="62"/>
+      <c r="N17" s="62"/>
+      <c r="O17" s="62"/>
+      <c r="P17" s="62"/>
+      <c r="Q17" s="62"/>
+      <c r="R17" s="62"/>
+      <c r="S17" s="62"/>
+      <c r="T17" s="62"/>
+      <c r="U17" s="62"/>
+      <c r="V17" s="62"/>
+      <c r="W17" s="62"/>
+      <c r="X17" s="62"/>
+      <c r="Y17" s="62"/>
+      <c r="Z17" s="62"/>
+      <c r="AA17" s="62"/>
+      <c r="AB17" s="62"/>
     </row>
     <row r="18" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="15"/>
@@ -5218,41 +5230,41 @@
       <c r="C20" s="10"/>
     </row>
     <row r="22" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="P22" s="65" t="s">
+      <c r="P22" s="59" t="s">
         <v>73</v>
       </c>
-      <c r="Q22" s="65"/>
-      <c r="R22" s="65"/>
-      <c r="S22" s="65"/>
-      <c r="T22" s="65"/>
-      <c r="U22" s="65"/>
-      <c r="V22" s="65"/>
-      <c r="W22" s="65"/>
-      <c r="X22" s="65"/>
-      <c r="Y22" s="65"/>
-      <c r="Z22" s="65"/>
-      <c r="AA22" s="65"/>
-      <c r="AB22" s="65"/>
+      <c r="Q22" s="59"/>
+      <c r="R22" s="59"/>
+      <c r="S22" s="59"/>
+      <c r="T22" s="59"/>
+      <c r="U22" s="59"/>
+      <c r="V22" s="59"/>
+      <c r="W22" s="59"/>
+      <c r="X22" s="59"/>
+      <c r="Y22" s="59"/>
+      <c r="Z22" s="59"/>
+      <c r="AA22" s="59"/>
+      <c r="AB22" s="59"/>
     </row>
     <row r="23" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P23" s="12"/>
     </row>
     <row r="24" spans="2:28" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P24" s="63" t="s">
+      <c r="P24" s="56" t="s">
         <v>172</v>
       </c>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="66"/>
-      <c r="S24" s="66"/>
-      <c r="T24" s="66"/>
-      <c r="U24" s="66"/>
-      <c r="V24" s="66"/>
-      <c r="W24" s="66"/>
-      <c r="X24" s="66"/>
-      <c r="Y24" s="66"/>
-      <c r="Z24" s="66"/>
-      <c r="AA24" s="66"/>
-      <c r="AB24" s="66"/>
+      <c r="Q24" s="60"/>
+      <c r="R24" s="60"/>
+      <c r="S24" s="60"/>
+      <c r="T24" s="60"/>
+      <c r="U24" s="60"/>
+      <c r="V24" s="60"/>
+      <c r="W24" s="60"/>
+      <c r="X24" s="60"/>
+      <c r="Y24" s="60"/>
+      <c r="Z24" s="60"/>
+      <c r="AA24" s="60"/>
+      <c r="AB24" s="60"/>
     </row>
     <row r="25" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P25" s="19"/>
@@ -5270,21 +5282,21 @@
       <c r="AB25" s="17"/>
     </row>
     <row r="26" spans="2:28" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P26" s="63" t="s">
+      <c r="P26" s="56" t="s">
         <v>174</v>
       </c>
-      <c r="Q26" s="63"/>
-      <c r="R26" s="63"/>
-      <c r="S26" s="63"/>
-      <c r="T26" s="63"/>
-      <c r="U26" s="63"/>
-      <c r="V26" s="63"/>
-      <c r="W26" s="63"/>
-      <c r="X26" s="63"/>
-      <c r="Y26" s="63"/>
-      <c r="Z26" s="63"/>
-      <c r="AA26" s="63"/>
-      <c r="AB26" s="63"/>
+      <c r="Q26" s="56"/>
+      <c r="R26" s="56"/>
+      <c r="S26" s="56"/>
+      <c r="T26" s="56"/>
+      <c r="U26" s="56"/>
+      <c r="V26" s="56"/>
+      <c r="W26" s="56"/>
+      <c r="X26" s="56"/>
+      <c r="Y26" s="56"/>
+      <c r="Z26" s="56"/>
+      <c r="AA26" s="56"/>
+      <c r="AB26" s="56"/>
     </row>
     <row r="27" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P27" s="17"/>
@@ -5302,21 +5314,21 @@
       <c r="AB27" s="17"/>
     </row>
     <row r="28" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="P28" s="65" t="s">
+      <c r="P28" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="Q28" s="65"/>
-      <c r="R28" s="65"/>
-      <c r="S28" s="65"/>
-      <c r="T28" s="65"/>
-      <c r="U28" s="65"/>
-      <c r="V28" s="65"/>
-      <c r="W28" s="65"/>
-      <c r="X28" s="65"/>
-      <c r="Y28" s="65"/>
-      <c r="Z28" s="65"/>
-      <c r="AA28" s="65"/>
-      <c r="AB28" s="65"/>
+      <c r="Q28" s="59"/>
+      <c r="R28" s="59"/>
+      <c r="S28" s="59"/>
+      <c r="T28" s="59"/>
+      <c r="U28" s="59"/>
+      <c r="V28" s="59"/>
+      <c r="W28" s="59"/>
+      <c r="X28" s="59"/>
+      <c r="Y28" s="59"/>
+      <c r="Z28" s="59"/>
+      <c r="AA28" s="59"/>
+      <c r="AB28" s="59"/>
     </row>
     <row r="29" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P29" s="12"/>
@@ -5362,39 +5374,38 @@
       <c r="AB35" s="12"/>
     </row>
     <row r="36" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P36" s="47" t="s">
+      <c r="P36" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="Q36" s="47"/>
-      <c r="R36" s="47"/>
-      <c r="S36" s="47"/>
-      <c r="T36" s="47"/>
-      <c r="U36" s="47"/>
-      <c r="V36" s="47"/>
-      <c r="W36" s="47"/>
-      <c r="X36" s="47"/>
-      <c r="Y36" s="47"/>
-      <c r="Z36" s="47"/>
-      <c r="AA36" s="47"/>
-      <c r="AB36" s="47"/>
+      <c r="Q36" s="39"/>
+      <c r="R36" s="39"/>
+      <c r="S36" s="39"/>
+      <c r="T36" s="39"/>
+      <c r="U36" s="39"/>
+      <c r="V36" s="39"/>
+      <c r="W36" s="39"/>
+      <c r="X36" s="39"/>
+      <c r="Y36" s="39"/>
+      <c r="Z36" s="39"/>
+      <c r="AA36" s="39"/>
+      <c r="AB36" s="39"/>
     </row>
     <row r="38" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B38" s="67" t="s">
+      <c r="B38" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="67"/>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
-      <c r="H38" s="67"/>
-      <c r="I38" s="67"/>
-      <c r="J38" s="67"/>
-      <c r="K38" s="67"/>
-      <c r="L38" s="67"/>
-      <c r="M38" s="67"/>
-      <c r="N38" s="67"/>
-      <c r="O38" s="79"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="65"/>
+      <c r="J38" s="65"/>
+      <c r="K38" s="65"/>
+      <c r="L38" s="65"/>
+      <c r="M38" s="65"/>
+      <c r="N38" s="65"/>
       <c r="P38" s="8" t="s">
         <v>57</v>
       </c>
@@ -5412,22 +5423,22 @@
       <c r="AB38" s="12"/>
     </row>
     <row r="39" spans="2:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P39" s="76" t="s">
+      <c r="P39" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="Q39" s="76"/>
-      <c r="R39" s="76"/>
-      <c r="S39" s="76"/>
-      <c r="T39" s="76"/>
-      <c r="U39" s="76"/>
-      <c r="V39" s="76"/>
-      <c r="W39" s="76"/>
-      <c r="X39" s="76"/>
-      <c r="Y39" s="76"/>
-      <c r="Z39" s="76"/>
-      <c r="AA39" s="76"/>
-      <c r="AB39" s="76"/>
-      <c r="AC39" s="86"/>
+      <c r="Q39" s="35"/>
+      <c r="R39" s="35"/>
+      <c r="S39" s="35"/>
+      <c r="T39" s="35"/>
+      <c r="U39" s="35"/>
+      <c r="V39" s="35"/>
+      <c r="W39" s="35"/>
+      <c r="X39" s="35"/>
+      <c r="Y39" s="35"/>
+      <c r="Z39" s="35"/>
+      <c r="AA39" s="35"/>
+      <c r="AB39" s="35"/>
+      <c r="AC39" s="31"/>
     </row>
     <row r="40" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P40" s="12" t="s">
@@ -5440,22 +5451,22 @@
       </c>
     </row>
     <row r="42" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="P42" s="65" t="s">
+      <c r="P42" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="Q42" s="65"/>
-      <c r="R42" s="65"/>
-      <c r="S42" s="65"/>
-      <c r="T42" s="65"/>
-      <c r="U42" s="65"/>
-      <c r="V42" s="65"/>
-      <c r="W42" s="65"/>
-      <c r="X42" s="65"/>
-      <c r="Y42" s="65"/>
-      <c r="Z42" s="65"/>
-      <c r="AA42" s="65"/>
-      <c r="AB42" s="65"/>
-      <c r="AC42" s="65"/>
+      <c r="Q42" s="59"/>
+      <c r="R42" s="59"/>
+      <c r="S42" s="59"/>
+      <c r="T42" s="59"/>
+      <c r="U42" s="59"/>
+      <c r="V42" s="59"/>
+      <c r="W42" s="59"/>
+      <c r="X42" s="59"/>
+      <c r="Y42" s="59"/>
+      <c r="Z42" s="59"/>
+      <c r="AA42" s="59"/>
+      <c r="AB42" s="59"/>
+      <c r="AC42" s="59"/>
     </row>
     <row r="43" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P43" s="12" t="s">
@@ -5468,22 +5479,22 @@
       </c>
     </row>
     <row r="45" spans="2:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P45" s="47" t="s">
+      <c r="P45" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="Q45" s="47"/>
-      <c r="R45" s="47"/>
-      <c r="S45" s="47"/>
-      <c r="T45" s="47"/>
-      <c r="U45" s="47"/>
-      <c r="V45" s="47"/>
-      <c r="W45" s="47"/>
-      <c r="X45" s="47"/>
-      <c r="Y45" s="47"/>
-      <c r="Z45" s="47"/>
-      <c r="AA45" s="47"/>
-      <c r="AB45" s="47"/>
-      <c r="AC45" s="87"/>
+      <c r="Q45" s="39"/>
+      <c r="R45" s="39"/>
+      <c r="S45" s="39"/>
+      <c r="T45" s="39"/>
+      <c r="U45" s="39"/>
+      <c r="V45" s="39"/>
+      <c r="W45" s="39"/>
+      <c r="X45" s="39"/>
+      <c r="Y45" s="39"/>
+      <c r="Z45" s="39"/>
+      <c r="AA45" s="39"/>
+      <c r="AB45" s="39"/>
+      <c r="AC45" s="32"/>
     </row>
     <row r="46" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P46" s="12" t="s">
@@ -5491,45 +5502,43 @@
       </c>
     </row>
     <row r="47" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B47" s="80" t="s">
+      <c r="B47" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="C47" s="80"/>
-      <c r="D47" s="80"/>
-      <c r="E47" s="80"/>
-      <c r="F47" s="80"/>
-      <c r="G47" s="80"/>
-      <c r="H47" s="80"/>
-      <c r="I47" s="80"/>
-      <c r="J47" s="80"/>
-      <c r="K47" s="80"/>
-      <c r="L47" s="80"/>
-      <c r="M47" s="80"/>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="66"/>
+      <c r="L47" s="66"/>
+      <c r="M47" s="66"/>
       <c r="P47" s="8" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="48" spans="2:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P48" s="76" t="s">
+      <c r="P48" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="Q48" s="76"/>
-      <c r="R48" s="76"/>
-      <c r="S48" s="76"/>
-      <c r="T48" s="76"/>
-      <c r="U48" s="76"/>
-      <c r="V48" s="76"/>
-      <c r="W48" s="76"/>
-      <c r="X48" s="76"/>
-      <c r="Y48" s="76"/>
-      <c r="Z48" s="76"/>
-      <c r="AA48" s="76"/>
-      <c r="AB48" s="76"/>
-      <c r="AC48" s="81"/>
+      <c r="Q48" s="35"/>
+      <c r="R48" s="35"/>
+      <c r="S48" s="35"/>
+      <c r="T48" s="35"/>
+      <c r="U48" s="35"/>
+      <c r="V48" s="35"/>
+      <c r="W48" s="35"/>
+      <c r="X48" s="35"/>
+      <c r="Y48" s="35"/>
+      <c r="Z48" s="35"/>
+      <c r="AA48" s="35"/>
+      <c r="AB48" s="35"/>
+      <c r="AC48" s="29"/>
     </row>
     <row r="49" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="N49" s="79"/>
-      <c r="O49" s="79"/>
       <c r="P49" s="12" t="s">
         <v>69</v>
       </c>
@@ -5540,21 +5549,21 @@
       </c>
     </row>
     <row r="51" spans="2:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P51" s="47" t="s">
+      <c r="P51" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="Q51" s="47"/>
-      <c r="R51" s="47"/>
-      <c r="S51" s="47"/>
-      <c r="T51" s="47"/>
-      <c r="U51" s="47"/>
-      <c r="V51" s="47"/>
-      <c r="W51" s="47"/>
-      <c r="X51" s="47"/>
-      <c r="Y51" s="47"/>
-      <c r="Z51" s="47"/>
-      <c r="AA51" s="47"/>
-      <c r="AB51" s="47"/>
+      <c r="Q51" s="39"/>
+      <c r="R51" s="39"/>
+      <c r="S51" s="39"/>
+      <c r="T51" s="39"/>
+      <c r="U51" s="39"/>
+      <c r="V51" s="39"/>
+      <c r="W51" s="39"/>
+      <c r="X51" s="39"/>
+      <c r="Y51" s="39"/>
+      <c r="Z51" s="39"/>
+      <c r="AA51" s="39"/>
+      <c r="AB51" s="39"/>
     </row>
     <row r="52" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P52" s="12" t="s">
@@ -5574,42 +5583,42 @@
       <c r="T55" s="12"/>
     </row>
     <row r="56" spans="2:29" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O56" s="76" t="s">
+      <c r="O56" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="P56" s="76"/>
-      <c r="Q56" s="76"/>
-      <c r="R56" s="76"/>
-      <c r="S56" s="76"/>
-      <c r="T56" s="76"/>
-      <c r="U56" s="76"/>
-      <c r="V56" s="76"/>
-      <c r="W56" s="76"/>
-      <c r="X56" s="76"/>
-      <c r="Y56" s="76"/>
-      <c r="Z56" s="76"/>
-      <c r="AA56" s="76"/>
-      <c r="AB56" s="76"/>
-      <c r="AC56" s="76"/>
+      <c r="P56" s="35"/>
+      <c r="Q56" s="35"/>
+      <c r="R56" s="35"/>
+      <c r="S56" s="35"/>
+      <c r="T56" s="35"/>
+      <c r="U56" s="35"/>
+      <c r="V56" s="35"/>
+      <c r="W56" s="35"/>
+      <c r="X56" s="35"/>
+      <c r="Y56" s="35"/>
+      <c r="Z56" s="35"/>
+      <c r="AA56" s="35"/>
+      <c r="AB56" s="35"/>
+      <c r="AC56" s="35"/>
     </row>
     <row r="58" spans="2:29" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O58" s="82" t="s">
+      <c r="O58" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="P58" s="82"/>
-      <c r="Q58" s="82"/>
-      <c r="R58" s="82"/>
-      <c r="S58" s="82"/>
-      <c r="T58" s="82"/>
-      <c r="U58" s="82"/>
-      <c r="V58" s="82"/>
-      <c r="W58" s="82"/>
-      <c r="X58" s="82"/>
-      <c r="Y58" s="82"/>
-      <c r="Z58" s="82"/>
-      <c r="AA58" s="82"/>
-      <c r="AB58" s="82"/>
-      <c r="AC58" s="82"/>
+      <c r="P58" s="67"/>
+      <c r="Q58" s="67"/>
+      <c r="R58" s="67"/>
+      <c r="S58" s="67"/>
+      <c r="T58" s="67"/>
+      <c r="U58" s="67"/>
+      <c r="V58" s="67"/>
+      <c r="W58" s="67"/>
+      <c r="X58" s="67"/>
+      <c r="Y58" s="67"/>
+      <c r="Z58" s="67"/>
+      <c r="AA58" s="67"/>
+      <c r="AB58" s="67"/>
+      <c r="AC58" s="67"/>
     </row>
     <row r="59" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
       <c r="O59" s="18"/>
@@ -5629,23 +5638,23 @@
       <c r="AC59" s="17"/>
     </row>
     <row r="60" spans="2:29" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O60" s="83" t="s">
+      <c r="O60" s="68" t="s">
         <v>175</v>
       </c>
-      <c r="P60" s="83"/>
-      <c r="Q60" s="83"/>
-      <c r="R60" s="83"/>
-      <c r="S60" s="83"/>
-      <c r="T60" s="83"/>
-      <c r="U60" s="83"/>
-      <c r="V60" s="83"/>
-      <c r="W60" s="83"/>
-      <c r="X60" s="83"/>
-      <c r="Y60" s="83"/>
-      <c r="Z60" s="83"/>
-      <c r="AA60" s="83"/>
-      <c r="AB60" s="83"/>
-      <c r="AC60" s="83"/>
+      <c r="P60" s="68"/>
+      <c r="Q60" s="68"/>
+      <c r="R60" s="68"/>
+      <c r="S60" s="68"/>
+      <c r="T60" s="68"/>
+      <c r="U60" s="68"/>
+      <c r="V60" s="68"/>
+      <c r="W60" s="68"/>
+      <c r="X60" s="68"/>
+      <c r="Y60" s="68"/>
+      <c r="Z60" s="68"/>
+      <c r="AA60" s="68"/>
+      <c r="AB60" s="68"/>
+      <c r="AC60" s="68"/>
     </row>
     <row r="62" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="O62" s="8" t="s">
@@ -5656,23 +5665,23 @@
       <c r="O63" s="8"/>
     </row>
     <row r="64" spans="2:29" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O64" s="77" t="s">
+      <c r="O64" s="63" t="s">
         <v>173</v>
       </c>
-      <c r="P64" s="63"/>
-      <c r="Q64" s="63"/>
-      <c r="R64" s="63"/>
-      <c r="S64" s="63"/>
-      <c r="T64" s="63"/>
-      <c r="U64" s="63"/>
-      <c r="V64" s="63"/>
-      <c r="W64" s="63"/>
-      <c r="X64" s="63"/>
-      <c r="Y64" s="63"/>
-      <c r="Z64" s="63"/>
-      <c r="AA64" s="63"/>
-      <c r="AB64" s="63"/>
-      <c r="AC64" s="63"/>
+      <c r="P64" s="56"/>
+      <c r="Q64" s="56"/>
+      <c r="R64" s="56"/>
+      <c r="S64" s="56"/>
+      <c r="T64" s="56"/>
+      <c r="U64" s="56"/>
+      <c r="V64" s="56"/>
+      <c r="W64" s="56"/>
+      <c r="X64" s="56"/>
+      <c r="Y64" s="56"/>
+      <c r="Z64" s="56"/>
+      <c r="AA64" s="56"/>
+      <c r="AB64" s="56"/>
+      <c r="AC64" s="56"/>
     </row>
     <row r="65" spans="15:29" ht="19.5" x14ac:dyDescent="0.25">
       <c r="O65" s="18"/>
@@ -5692,42 +5701,42 @@
       <c r="AC65" s="17"/>
     </row>
     <row r="66" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O66" s="85" t="s">
+      <c r="O66" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="P66" s="85"/>
-      <c r="Q66" s="85"/>
-      <c r="R66" s="85"/>
-      <c r="S66" s="85"/>
-      <c r="T66" s="84"/>
-      <c r="U66" s="84"/>
-      <c r="V66" s="84"/>
-      <c r="W66" s="84"/>
-      <c r="X66" s="84"/>
-      <c r="Y66" s="84"/>
-      <c r="Z66" s="84"/>
-      <c r="AA66" s="84"/>
-      <c r="AB66" s="84"/>
-      <c r="AC66" s="84"/>
+      <c r="P66" s="64"/>
+      <c r="Q66" s="64"/>
+      <c r="R66" s="64"/>
+      <c r="S66" s="64"/>
+      <c r="T66" s="30"/>
+      <c r="U66" s="30"/>
+      <c r="V66" s="30"/>
+      <c r="W66" s="30"/>
+      <c r="X66" s="30"/>
+      <c r="Y66" s="30"/>
+      <c r="Z66" s="30"/>
+      <c r="AA66" s="30"/>
+      <c r="AB66" s="30"/>
+      <c r="AC66" s="30"/>
     </row>
     <row r="67" spans="15:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O67" s="76" t="s">
+      <c r="O67" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="P67" s="47"/>
-      <c r="Q67" s="47"/>
-      <c r="R67" s="47"/>
-      <c r="S67" s="47"/>
-      <c r="T67" s="47"/>
-      <c r="U67" s="47"/>
-      <c r="V67" s="47"/>
-      <c r="W67" s="47"/>
-      <c r="X67" s="47"/>
-      <c r="Y67" s="47"/>
-      <c r="Z67" s="47"/>
-      <c r="AA67" s="47"/>
-      <c r="AB67" s="47"/>
-      <c r="AC67" s="47"/>
+      <c r="P67" s="39"/>
+      <c r="Q67" s="39"/>
+      <c r="R67" s="39"/>
+      <c r="S67" s="39"/>
+      <c r="T67" s="39"/>
+      <c r="U67" s="39"/>
+      <c r="V67" s="39"/>
+      <c r="W67" s="39"/>
+      <c r="X67" s="39"/>
+      <c r="Y67" s="39"/>
+      <c r="Z67" s="39"/>
+      <c r="AA67" s="39"/>
+      <c r="AB67" s="39"/>
+      <c r="AC67" s="39"/>
     </row>
     <row r="68" spans="15:29" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="O68" s="12" t="s">
@@ -5735,42 +5744,42 @@
       </c>
     </row>
     <row r="69" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O69" s="85" t="s">
+      <c r="O69" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="P69" s="85"/>
-      <c r="Q69" s="85"/>
-      <c r="R69" s="85"/>
-      <c r="S69" s="85"/>
-      <c r="T69" s="84"/>
-      <c r="U69" s="84"/>
-      <c r="V69" s="84"/>
-      <c r="W69" s="84"/>
-      <c r="X69" s="84"/>
-      <c r="Y69" s="84"/>
-      <c r="Z69" s="84"/>
-      <c r="AA69" s="84"/>
-      <c r="AB69" s="84"/>
-      <c r="AC69" s="84"/>
+      <c r="P69" s="64"/>
+      <c r="Q69" s="64"/>
+      <c r="R69" s="64"/>
+      <c r="S69" s="64"/>
+      <c r="T69" s="30"/>
+      <c r="U69" s="30"/>
+      <c r="V69" s="30"/>
+      <c r="W69" s="30"/>
+      <c r="X69" s="30"/>
+      <c r="Y69" s="30"/>
+      <c r="Z69" s="30"/>
+      <c r="AA69" s="30"/>
+      <c r="AB69" s="30"/>
+      <c r="AC69" s="30"/>
     </row>
     <row r="70" spans="15:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O70" s="76" t="s">
+      <c r="O70" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="P70" s="76"/>
-      <c r="Q70" s="76"/>
-      <c r="R70" s="76"/>
-      <c r="S70" s="76"/>
-      <c r="T70" s="76"/>
-      <c r="U70" s="76"/>
-      <c r="V70" s="76"/>
-      <c r="W70" s="76"/>
-      <c r="X70" s="76"/>
-      <c r="Y70" s="76"/>
-      <c r="Z70" s="76"/>
-      <c r="AA70" s="76"/>
-      <c r="AB70" s="76"/>
-      <c r="AC70" s="76"/>
+      <c r="P70" s="35"/>
+      <c r="Q70" s="35"/>
+      <c r="R70" s="35"/>
+      <c r="S70" s="35"/>
+      <c r="T70" s="35"/>
+      <c r="U70" s="35"/>
+      <c r="V70" s="35"/>
+      <c r="W70" s="35"/>
+      <c r="X70" s="35"/>
+      <c r="Y70" s="35"/>
+      <c r="Z70" s="35"/>
+      <c r="AA70" s="35"/>
+      <c r="AB70" s="35"/>
+      <c r="AC70" s="35"/>
     </row>
     <row r="71" spans="15:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="O71" s="12" t="s">
@@ -5783,19 +5792,17 @@
     <row r="78" spans="15:29" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B38:N38"/>
-    <mergeCell ref="B47:M47"/>
     <mergeCell ref="O58:AC58"/>
     <mergeCell ref="O56:AC56"/>
     <mergeCell ref="O60:AC60"/>
+    <mergeCell ref="P39:AB39"/>
+    <mergeCell ref="P45:AB45"/>
+    <mergeCell ref="P48:AB48"/>
     <mergeCell ref="O64:AC64"/>
     <mergeCell ref="O66:S66"/>
     <mergeCell ref="O67:AC67"/>
     <mergeCell ref="O69:S69"/>
     <mergeCell ref="O70:AC70"/>
-    <mergeCell ref="P39:AB39"/>
-    <mergeCell ref="P45:AB45"/>
-    <mergeCell ref="P48:AB48"/>
     <mergeCell ref="P26:AB26"/>
     <mergeCell ref="P51:AB51"/>
     <mergeCell ref="L8:W8"/>
@@ -5807,6 +5814,8 @@
     <mergeCell ref="L12:AB12"/>
     <mergeCell ref="P28:AB28"/>
     <mergeCell ref="B17:AB17"/>
+    <mergeCell ref="B38:N38"/>
+    <mergeCell ref="B47:M47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -5832,23 +5841,23 @@
     </row>
     <row r="4" spans="1:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="70" t="s">
         <v>144</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
     </row>
     <row r="5" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="L5" s="56" t="s">
+      <c r="L5" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="M5" s="56"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="56"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
     </row>
     <row r="6" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
@@ -5862,13 +5871,13 @@
     </row>
     <row r="7" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
-      <c r="L7" s="35" t="s">
+      <c r="L7" s="72" t="s">
         <v>122</v>
       </c>
-      <c r="M7" s="35"/>
-      <c r="N7" s="35"/>
-      <c r="O7" s="35"/>
-      <c r="P7" s="35"/>
+      <c r="M7" s="72"/>
+      <c r="N7" s="72"/>
+      <c r="O7" s="72"/>
+      <c r="P7" s="72"/>
     </row>
     <row r="8" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
@@ -5892,17 +5901,17 @@
     </row>
     <row r="10" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
-      <c r="L10" s="35" t="s">
+      <c r="L10" s="72" t="s">
         <v>125</v>
       </c>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="72"/>
+      <c r="P10" s="72"/>
     </row>
     <row r="11" spans="1:31" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
-      <c r="L11" s="35" t="s">
+      <c r="L11" s="72" t="s">
         <v>126</v>
       </c>
       <c r="M11" s="73"/>
@@ -5912,29 +5921,29 @@
     </row>
     <row r="12" spans="1:31" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1"/>
-      <c r="L12" s="35" t="s">
+      <c r="L12" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="35"/>
-      <c r="P12" s="35"/>
-      <c r="R12" s="72" t="s">
+      <c r="M12" s="72"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="72"/>
+      <c r="P12" s="72"/>
+      <c r="R12" s="71" t="s">
         <v>139</v>
       </c>
-      <c r="S12" s="72"/>
-      <c r="T12" s="72"/>
-      <c r="U12" s="72"/>
-      <c r="V12" s="72"/>
-      <c r="W12" s="72"/>
-      <c r="X12" s="72"/>
-      <c r="Y12" s="72"/>
-      <c r="Z12" s="72"/>
-      <c r="AA12" s="72"/>
-      <c r="AB12" s="72"/>
-      <c r="AC12" s="72"/>
-      <c r="AD12" s="88"/>
-      <c r="AE12" s="88"/>
+      <c r="S12" s="71"/>
+      <c r="T12" s="71"/>
+      <c r="U12" s="71"/>
+      <c r="V12" s="71"/>
+      <c r="W12" s="71"/>
+      <c r="X12" s="71"/>
+      <c r="Y12" s="71"/>
+      <c r="Z12" s="71"/>
+      <c r="AA12" s="71"/>
+      <c r="AB12" s="71"/>
+      <c r="AC12" s="71"/>
+      <c r="AD12" s="33"/>
+      <c r="AE12" s="33"/>
     </row>
     <row r="13" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
@@ -5965,67 +5974,67 @@
     </row>
     <row r="17" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A17" s="1"/>
-      <c r="L17" s="56" t="s">
+      <c r="L17" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="M17" s="56"/>
-      <c r="N17" s="56"/>
-      <c r="O17" s="56" t="s">
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="P17" s="56"/>
-      <c r="Q17" s="56"/>
-      <c r="R17" s="56"/>
-      <c r="S17" s="56"/>
-      <c r="T17" s="56"/>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="46"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="46"/>
     </row>
     <row r="18" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
-      <c r="L18" s="61" t="s">
+      <c r="L18" s="52" t="s">
         <v>134</v>
       </c>
-      <c r="M18" s="61"/>
-      <c r="N18" s="61"/>
-      <c r="O18" s="71" t="s">
+      <c r="M18" s="52"/>
+      <c r="N18" s="52"/>
+      <c r="O18" s="69" t="s">
         <v>132</v>
       </c>
-      <c r="P18" s="71"/>
-      <c r="Q18" s="71"/>
-      <c r="R18" s="71"/>
-      <c r="S18" s="71"/>
-      <c r="T18" s="71"/>
+      <c r="P18" s="69"/>
+      <c r="Q18" s="69"/>
+      <c r="R18" s="69"/>
+      <c r="S18" s="69"/>
+      <c r="T18" s="69"/>
     </row>
     <row r="19" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
-      <c r="L19" s="61" t="s">
+      <c r="L19" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="M19" s="61"/>
-      <c r="N19" s="61"/>
-      <c r="O19" s="71" t="s">
+      <c r="M19" s="52"/>
+      <c r="N19" s="52"/>
+      <c r="O19" s="69" t="s">
         <v>136</v>
       </c>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="71"/>
-      <c r="R19" s="71"/>
-      <c r="S19" s="71"/>
-      <c r="T19" s="71"/>
+      <c r="P19" s="69"/>
+      <c r="Q19" s="69"/>
+      <c r="R19" s="69"/>
+      <c r="S19" s="69"/>
+      <c r="T19" s="69"/>
     </row>
     <row r="20" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
-      <c r="L20" s="61" t="s">
+      <c r="L20" s="52" t="s">
         <v>137</v>
       </c>
-      <c r="M20" s="61"/>
-      <c r="N20" s="61"/>
-      <c r="O20" s="71" t="s">
+      <c r="M20" s="52"/>
+      <c r="N20" s="52"/>
+      <c r="O20" s="69" t="s">
         <v>138</v>
       </c>
-      <c r="P20" s="71"/>
-      <c r="Q20" s="71"/>
-      <c r="R20" s="71"/>
-      <c r="S20" s="71"/>
-      <c r="T20" s="71"/>
+      <c r="P20" s="69"/>
+      <c r="Q20" s="69"/>
+      <c r="R20" s="69"/>
+      <c r="S20" s="69"/>
+      <c r="T20" s="69"/>
     </row>
     <row r="21" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A21" s="1"/>
@@ -6129,32 +6138,32 @@
       </c>
     </row>
     <row r="105" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B105" s="70" t="s">
+      <c r="B105" s="74" t="s">
         <v>153</v>
       </c>
-      <c r="C105" s="70"/>
-      <c r="D105" s="70"/>
-      <c r="E105" s="70"/>
-      <c r="F105" s="70"/>
-      <c r="G105" s="70"/>
-      <c r="H105" s="70"/>
-      <c r="I105" s="70"/>
-      <c r="J105" s="70"/>
-      <c r="K105" s="70"/>
-      <c r="L105" s="70"/>
-      <c r="M105" s="70"/>
-      <c r="N105" s="70"/>
-      <c r="O105" s="70"/>
-      <c r="P105" s="70"/>
-      <c r="Q105" s="70"/>
-      <c r="R105" s="70"/>
-      <c r="S105" s="70"/>
-      <c r="T105" s="70"/>
-      <c r="U105" s="70"/>
-      <c r="V105" s="70"/>
-      <c r="W105" s="70"/>
-      <c r="X105" s="70"/>
-      <c r="Y105" s="70"/>
+      <c r="C105" s="74"/>
+      <c r="D105" s="74"/>
+      <c r="E105" s="74"/>
+      <c r="F105" s="74"/>
+      <c r="G105" s="74"/>
+      <c r="H105" s="74"/>
+      <c r="I105" s="74"/>
+      <c r="J105" s="74"/>
+      <c r="K105" s="74"/>
+      <c r="L105" s="74"/>
+      <c r="M105" s="74"/>
+      <c r="N105" s="74"/>
+      <c r="O105" s="74"/>
+      <c r="P105" s="74"/>
+      <c r="Q105" s="74"/>
+      <c r="R105" s="74"/>
+      <c r="S105" s="74"/>
+      <c r="T105" s="74"/>
+      <c r="U105" s="74"/>
+      <c r="V105" s="74"/>
+      <c r="W105" s="74"/>
+      <c r="X105" s="74"/>
+      <c r="Y105" s="74"/>
     </row>
     <row r="108" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A108" s="1" t="s">
@@ -6187,36 +6196,36 @@
       </c>
     </row>
     <row r="118" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="76" t="s">
+      <c r="B118" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="C118" s="76"/>
-      <c r="D118" s="76"/>
-      <c r="E118" s="76"/>
-      <c r="F118" s="76"/>
-      <c r="G118" s="76"/>
-      <c r="H118" s="76"/>
-      <c r="I118" s="76"/>
-      <c r="J118" s="76"/>
-      <c r="K118" s="76"/>
-      <c r="L118" s="76"/>
-      <c r="M118" s="76"/>
-      <c r="N118" s="76"/>
-      <c r="O118" s="76"/>
-      <c r="P118" s="76"/>
-      <c r="Q118" s="76"/>
-      <c r="R118" s="76"/>
-      <c r="S118" s="76"/>
-      <c r="T118" s="76"/>
-      <c r="U118" s="76"/>
-      <c r="V118" s="76"/>
-      <c r="W118" s="76"/>
-      <c r="X118" s="76"/>
-      <c r="Y118" s="76"/>
-      <c r="Z118" s="76"/>
-      <c r="AA118" s="76"/>
-      <c r="AB118" s="76"/>
-      <c r="AC118" s="76"/>
+      <c r="C118" s="35"/>
+      <c r="D118" s="35"/>
+      <c r="E118" s="35"/>
+      <c r="F118" s="35"/>
+      <c r="G118" s="35"/>
+      <c r="H118" s="35"/>
+      <c r="I118" s="35"/>
+      <c r="J118" s="35"/>
+      <c r="K118" s="35"/>
+      <c r="L118" s="35"/>
+      <c r="M118" s="35"/>
+      <c r="N118" s="35"/>
+      <c r="O118" s="35"/>
+      <c r="P118" s="35"/>
+      <c r="Q118" s="35"/>
+      <c r="R118" s="35"/>
+      <c r="S118" s="35"/>
+      <c r="T118" s="35"/>
+      <c r="U118" s="35"/>
+      <c r="V118" s="35"/>
+      <c r="W118" s="35"/>
+      <c r="X118" s="35"/>
+      <c r="Y118" s="35"/>
+      <c r="Z118" s="35"/>
+      <c r="AA118" s="35"/>
+      <c r="AB118" s="35"/>
+      <c r="AC118" s="35"/>
     </row>
     <row r="119" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B119" s="26" t="s">
@@ -6235,7 +6244,7 @@
       <c r="B122" s="20"/>
     </row>
     <row r="123" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B123" s="75" t="s">
+      <c r="B123" s="28" t="s">
         <v>219</v>
       </c>
     </row>
@@ -6310,7 +6319,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A2:W27"/>
+  <dimension ref="A2:U26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
@@ -6319,790 +6328,786 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="55" t="s">
         <v>218</v>
       </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="41" t="s">
+      <c r="C4" s="55"/>
+      <c r="D4" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="42"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="28" t="s">
+      <c r="E4" s="86"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28" t="s">
+      <c r="H4" s="55"/>
+      <c r="I4" s="55" t="s">
         <v>119</v>
       </c>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28" t="s">
+      <c r="J4" s="55"/>
+      <c r="K4" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28" t="s">
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="55"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="55" t="s">
         <v>221</v>
       </c>
-      <c r="U4" s="28"/>
+      <c r="U4" s="55"/>
     </row>
     <row r="5" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="90" t="s">
         <v>183</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="30" t="s">
+      <c r="C5" s="90"/>
+      <c r="D5" s="75" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="33" t="s">
+      <c r="E5" s="76"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="78" t="s">
         <v>92</v>
       </c>
-      <c r="H5" s="33"/>
-      <c r="I5" s="34" t="s">
+      <c r="H5" s="78"/>
+      <c r="I5" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="J5" s="34"/>
-      <c r="K5" s="35" t="s">
+      <c r="J5" s="79"/>
+      <c r="K5" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="L5" s="35"/>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="35"/>
-      <c r="T5" s="92" t="s">
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="72"/>
+      <c r="O5" s="72"/>
+      <c r="P5" s="72"/>
+      <c r="Q5" s="72"/>
+      <c r="R5" s="72"/>
+      <c r="S5" s="72"/>
+      <c r="T5" s="88" t="s">
         <v>223</v>
       </c>
-      <c r="U5" s="92"/>
+      <c r="U5" s="88"/>
     </row>
     <row r="6" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="90" t="s">
         <v>204</v>
       </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="30" t="s">
+      <c r="C6" s="90"/>
+      <c r="D6" s="75" t="s">
         <v>113</v>
       </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="36" t="s">
+      <c r="E6" s="76"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="H6" s="36"/>
-      <c r="I6" s="34" t="s">
+      <c r="H6" s="80"/>
+      <c r="I6" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="J6" s="34"/>
-      <c r="K6" s="35" t="s">
+      <c r="J6" s="79"/>
+      <c r="K6" s="72" t="s">
         <v>179</v>
       </c>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
-      <c r="S6" s="35"/>
-      <c r="T6" s="92" t="s">
+      <c r="L6" s="72"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="72"/>
+      <c r="O6" s="72"/>
+      <c r="P6" s="72"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="88" t="s">
         <v>223</v>
       </c>
-      <c r="U6" s="92"/>
+      <c r="U6" s="88"/>
     </row>
     <row r="7" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="90" t="s">
         <v>189</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="30" t="s">
+      <c r="C7" s="90"/>
+      <c r="D7" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="33" t="s">
+      <c r="E7" s="76"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="78" t="s">
         <v>92</v>
       </c>
-      <c r="H7" s="33"/>
-      <c r="I7" s="34" t="s">
+      <c r="H7" s="78"/>
+      <c r="I7" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="J7" s="34"/>
-      <c r="K7" s="35" t="s">
+      <c r="J7" s="79"/>
+      <c r="K7" s="72" t="s">
         <v>109</v>
       </c>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
-      <c r="N7" s="35"/>
-      <c r="O7" s="35"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="35"/>
-      <c r="S7" s="35"/>
-      <c r="T7" s="92" t="s">
+      <c r="L7" s="72"/>
+      <c r="M7" s="72"/>
+      <c r="N7" s="72"/>
+      <c r="O7" s="72"/>
+      <c r="P7" s="72"/>
+      <c r="Q7" s="72"/>
+      <c r="R7" s="72"/>
+      <c r="S7" s="72"/>
+      <c r="T7" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="U7" s="88"/>
+    </row>
+    <row r="8" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="90" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="90"/>
+      <c r="D8" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="76"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8" s="78"/>
+      <c r="I8" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="J8" s="79"/>
+      <c r="K8" s="72" t="s">
+        <v>109</v>
+      </c>
+      <c r="L8" s="72"/>
+      <c r="M8" s="72"/>
+      <c r="N8" s="72"/>
+      <c r="O8" s="72"/>
+      <c r="P8" s="72"/>
+      <c r="Q8" s="72"/>
+      <c r="R8" s="72"/>
+      <c r="S8" s="72"/>
+      <c r="T8" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="U8" s="88"/>
+    </row>
+    <row r="9" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="90" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" s="90"/>
+      <c r="D9" s="75" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="76"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="78"/>
+      <c r="I9" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" s="79"/>
+      <c r="K9" s="72" t="s">
+        <v>109</v>
+      </c>
+      <c r="L9" s="72"/>
+      <c r="M9" s="72"/>
+      <c r="N9" s="72"/>
+      <c r="O9" s="72"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="72"/>
+      <c r="T9" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="U9" s="88"/>
+    </row>
+    <row r="10" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="90" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="90"/>
+      <c r="D10" s="75" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="76"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="78"/>
+      <c r="I10" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="J10" s="79"/>
+      <c r="K10" s="72" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="72"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="72"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="72"/>
+      <c r="T10" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="U10" s="88"/>
+    </row>
+    <row r="11" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="90" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="90"/>
+      <c r="D11" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="76"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="78"/>
+      <c r="I11" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="J11" s="79"/>
+      <c r="K11" s="72" t="s">
+        <v>109</v>
+      </c>
+      <c r="L11" s="72"/>
+      <c r="M11" s="72"/>
+      <c r="N11" s="72"/>
+      <c r="O11" s="72"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="72"/>
+      <c r="S11" s="72"/>
+      <c r="T11" s="89" t="s">
+        <v>223</v>
+      </c>
+      <c r="U11" s="88"/>
+    </row>
+    <row r="12" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="C12" s="90"/>
+      <c r="D12" s="82" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="83"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="78"/>
+      <c r="I12" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="J12" s="79"/>
+      <c r="K12" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="L12" s="72"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="72"/>
+      <c r="P12" s="72"/>
+      <c r="Q12" s="72"/>
+      <c r="R12" s="72"/>
+      <c r="S12" s="72"/>
+      <c r="T12" s="88" t="s">
+        <v>223</v>
+      </c>
+      <c r="U12" s="88"/>
+    </row>
+    <row r="13" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="90" t="s">
+        <v>185</v>
+      </c>
+      <c r="C13" s="90"/>
+      <c r="D13" s="75" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="76"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="H13" s="78"/>
+      <c r="I13" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" s="79"/>
+      <c r="K13" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="L13" s="72"/>
+      <c r="M13" s="72"/>
+      <c r="N13" s="72"/>
+      <c r="O13" s="72"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="72"/>
+      <c r="S13" s="72"/>
+      <c r="T13" s="88" t="s">
+        <v>223</v>
+      </c>
+      <c r="U13" s="88"/>
+    </row>
+    <row r="14" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="90" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" s="90"/>
+      <c r="D14" s="75" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" s="76"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="78"/>
+      <c r="I14" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="J14" s="79"/>
+      <c r="K14" s="72" t="s">
+        <v>117</v>
+      </c>
+      <c r="L14" s="72"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="72"/>
+      <c r="O14" s="72"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="72"/>
+      <c r="T14" s="88" t="s">
+        <v>223</v>
+      </c>
+      <c r="U14" s="88"/>
+    </row>
+    <row r="15" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="90" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" s="90"/>
+      <c r="D15" s="75" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="76"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="78"/>
+      <c r="I15" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="J15" s="79"/>
+      <c r="K15" s="72" t="s">
+        <v>118</v>
+      </c>
+      <c r="L15" s="72"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="72"/>
+      <c r="O15" s="72"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="72"/>
+      <c r="T15" s="88" t="s">
+        <v>223</v>
+      </c>
+      <c r="U15" s="88"/>
+    </row>
+    <row r="16" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="90" t="s">
+        <v>188</v>
+      </c>
+      <c r="C16" s="90"/>
+      <c r="D16" s="75" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="76"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="78"/>
+      <c r="I16" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="J16" s="79"/>
+      <c r="K16" s="72" t="s">
+        <v>118</v>
+      </c>
+      <c r="L16" s="72"/>
+      <c r="M16" s="72"/>
+      <c r="N16" s="72"/>
+      <c r="O16" s="72"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72"/>
+      <c r="T16" s="88" t="s">
         <v>222</v>
       </c>
-      <c r="U7" s="92"/>
-    </row>
-    <row r="8" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="H8" s="33"/>
-      <c r="I8" s="34" t="s">
+      <c r="U16" s="88"/>
+    </row>
+    <row r="17" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B17" s="90" t="s">
+        <v>195</v>
+      </c>
+      <c r="C17" s="90"/>
+      <c r="D17" s="75" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="76"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="80" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="80"/>
+      <c r="I17" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="J8" s="34"/>
-      <c r="K8" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
-      <c r="N8" s="35"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="35"/>
-      <c r="S8" s="35"/>
-      <c r="T8" s="92" t="s">
-        <v>222</v>
-      </c>
-      <c r="U8" s="92"/>
-    </row>
-    <row r="9" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="29" t="s">
-        <v>191</v>
-      </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="33"/>
-      <c r="I9" s="34" t="s">
+      <c r="J17" s="79"/>
+      <c r="K17" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="L17" s="72"/>
+      <c r="M17" s="72"/>
+      <c r="N17" s="72"/>
+      <c r="O17" s="72"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="72"/>
+      <c r="T17" s="88" t="s">
+        <v>223</v>
+      </c>
+      <c r="U17" s="88"/>
+    </row>
+    <row r="18" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B18" s="90" t="s">
+        <v>194</v>
+      </c>
+      <c r="C18" s="90"/>
+      <c r="D18" s="75" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="76"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="80" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="80"/>
+      <c r="I18" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="J9" s="34"/>
-      <c r="K9" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="35"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="35"/>
-      <c r="S9" s="35"/>
-      <c r="T9" s="92" t="s">
-        <v>222</v>
-      </c>
-      <c r="U9" s="92"/>
-    </row>
-    <row r="10" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="H10" s="33"/>
-      <c r="I10" s="34" t="s">
+      <c r="J18" s="79"/>
+      <c r="K18" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="L18" s="72"/>
+      <c r="M18" s="72"/>
+      <c r="N18" s="72"/>
+      <c r="O18" s="72"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="72"/>
+      <c r="T18" s="88" t="s">
+        <v>223</v>
+      </c>
+      <c r="U18" s="88"/>
+    </row>
+    <row r="19" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B19" s="90" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" s="90"/>
+      <c r="D19" s="75" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" s="76"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="80" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="80"/>
+      <c r="I19" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="J10" s="34"/>
-      <c r="K10" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="92" t="s">
-        <v>222</v>
-      </c>
-      <c r="U10" s="92"/>
-    </row>
-    <row r="11" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="H11" s="33"/>
-      <c r="I11" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="J11" s="34"/>
-      <c r="K11" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="35"/>
-      <c r="O11" s="35"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="35"/>
-      <c r="T11" s="92" t="s">
-        <v>222</v>
-      </c>
-      <c r="U11" s="92"/>
-    </row>
-    <row r="12" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12" s="39"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="H12" s="33"/>
-      <c r="I12" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="J12" s="34"/>
-      <c r="K12" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="35"/>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="35"/>
-      <c r="R12" s="35"/>
-      <c r="S12" s="35"/>
-      <c r="T12" s="92" t="s">
+      <c r="J19" s="79"/>
+      <c r="K19" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="L19" s="72"/>
+      <c r="M19" s="72"/>
+      <c r="N19" s="72"/>
+      <c r="O19" s="72"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="72"/>
+      <c r="T19" s="88" t="s">
         <v>223</v>
       </c>
-      <c r="U12" s="92"/>
-    </row>
-    <row r="13" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B13" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="E13" s="31"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" s="33"/>
-      <c r="I13" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="J13" s="34"/>
-      <c r="K13" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="35"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="35"/>
-      <c r="S13" s="35"/>
-      <c r="T13" s="92" t="s">
+      <c r="U19" s="88"/>
+    </row>
+    <row r="20" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B20" s="90" t="s">
+        <v>197</v>
+      </c>
+      <c r="C20" s="90"/>
+      <c r="D20" s="75" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="76"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="80" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="80"/>
+      <c r="I20" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="81"/>
+      <c r="K20" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="L20" s="72"/>
+      <c r="M20" s="72"/>
+      <c r="N20" s="72"/>
+      <c r="O20" s="72"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="72"/>
+      <c r="T20" s="88" t="s">
         <v>223</v>
       </c>
-      <c r="U13" s="92"/>
-    </row>
-    <row r="14" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="E14" s="31"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="H14" s="33"/>
-      <c r="I14" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="J14" s="34"/>
-      <c r="K14" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
-      <c r="R14" s="35"/>
-      <c r="S14" s="35"/>
-      <c r="T14" s="92" t="s">
+      <c r="U20" s="88"/>
+    </row>
+    <row r="21" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B21" s="90" t="s">
+        <v>198</v>
+      </c>
+      <c r="C21" s="90"/>
+      <c r="D21" s="75" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="76"/>
+      <c r="F21" s="77"/>
+      <c r="G21" s="80" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" s="80"/>
+      <c r="I21" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="81"/>
+      <c r="K21" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="L21" s="72"/>
+      <c r="M21" s="72"/>
+      <c r="N21" s="72"/>
+      <c r="O21" s="72"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="72"/>
+      <c r="T21" s="88" t="s">
         <v>223</v>
       </c>
-      <c r="U14" s="92"/>
-    </row>
-    <row r="15" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" s="31"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="H15" s="33"/>
-      <c r="I15" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="J15" s="34"/>
-      <c r="K15" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
-      <c r="S15" s="35"/>
-      <c r="T15" s="92" t="s">
+      <c r="U21" s="88"/>
+    </row>
+    <row r="22" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B22" s="90" t="s">
+        <v>199</v>
+      </c>
+      <c r="C22" s="90"/>
+      <c r="D22" s="75" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="76"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="80" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="80"/>
+      <c r="I22" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="81"/>
+      <c r="K22" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="L22" s="72"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="72"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="72"/>
+      <c r="T22" s="88" t="s">
         <v>223</v>
       </c>
-      <c r="U15" s="92"/>
-    </row>
-    <row r="16" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" s="31"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="H16" s="33"/>
-      <c r="I16" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="J16" s="34"/>
-      <c r="K16" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="35"/>
-      <c r="T16" s="92" t="s">
-        <v>222</v>
-      </c>
-      <c r="U16" s="92"/>
-    </row>
-    <row r="17" spans="2:23" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B17" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="C17" s="29"/>
-      <c r="D17" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="E17" s="31"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="36" t="s">
+      <c r="U22" s="88"/>
+    </row>
+    <row r="23" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B23" s="90" t="s">
+        <v>200</v>
+      </c>
+      <c r="C23" s="90"/>
+      <c r="D23" s="75" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="76"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="H17" s="36"/>
-      <c r="I17" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="J17" s="34"/>
-      <c r="K17" s="35" t="s">
+      <c r="H23" s="80"/>
+      <c r="I23" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="81"/>
+      <c r="K23" s="72" t="s">
         <v>111</v>
       </c>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="92" t="s">
-        <v>222</v>
-      </c>
-      <c r="U17" s="92"/>
-    </row>
-    <row r="18" spans="2:23" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B18" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="E18" s="31"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="36" t="s">
+      <c r="L23" s="72"/>
+      <c r="M23" s="72"/>
+      <c r="N23" s="72"/>
+      <c r="O23" s="72"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="72"/>
+      <c r="T23" s="88" t="s">
+        <v>223</v>
+      </c>
+      <c r="U23" s="88"/>
+    </row>
+    <row r="24" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B24" s="90" t="s">
+        <v>201</v>
+      </c>
+      <c r="C24" s="90"/>
+      <c r="D24" s="75" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" s="76"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="H18" s="36"/>
-      <c r="I18" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="J18" s="34"/>
-      <c r="K18" s="35" t="s">
+      <c r="H24" s="80"/>
+      <c r="I24" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="81"/>
+      <c r="K24" s="72" t="s">
         <v>111</v>
       </c>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="35"/>
-      <c r="T18" s="92" t="s">
+      <c r="L24" s="72"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="72"/>
+      <c r="O24" s="72"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="72"/>
+      <c r="T24" s="88" t="s">
         <v>223</v>
       </c>
-      <c r="U18" s="92"/>
-    </row>
-    <row r="19" spans="2:23" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B19" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="E19" s="31"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="36" t="s">
+      <c r="U24" s="88"/>
+    </row>
+    <row r="25" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B25" s="90" t="s">
+        <v>202</v>
+      </c>
+      <c r="C25" s="90"/>
+      <c r="D25" s="75" t="s">
+        <v>108</v>
+      </c>
+      <c r="E25" s="76"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="H19" s="36"/>
-      <c r="I19" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="J19" s="34"/>
-      <c r="K19" s="35" t="s">
+      <c r="H25" s="80"/>
+      <c r="I25" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="81"/>
+      <c r="K25" s="72" t="s">
         <v>111</v>
       </c>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="35"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="35"/>
-      <c r="S19" s="35"/>
-      <c r="T19" s="92" t="s">
+      <c r="L25" s="72"/>
+      <c r="M25" s="72"/>
+      <c r="N25" s="72"/>
+      <c r="O25" s="72"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="72"/>
+      <c r="T25" s="88" t="s">
         <v>223</v>
       </c>
-      <c r="U19" s="92"/>
-    </row>
-    <row r="20" spans="2:23" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B20" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="E20" s="31"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="36" t="s">
+      <c r="U25" s="88"/>
+    </row>
+    <row r="26" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="90" t="s">
+        <v>203</v>
+      </c>
+      <c r="C26" s="90"/>
+      <c r="D26" s="75" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26" s="76"/>
+      <c r="F26" s="77"/>
+      <c r="G26" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="H20" s="36"/>
-      <c r="I20" s="37" t="s">
+      <c r="H26" s="80"/>
+      <c r="I26" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="J20" s="37"/>
-      <c r="K20" s="35" t="s">
+      <c r="J26" s="81"/>
+      <c r="K26" s="72" t="s">
         <v>111</v>
       </c>
-      <c r="L20" s="35"/>
-      <c r="M20" s="35"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="35"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="35"/>
-      <c r="R20" s="35"/>
-      <c r="S20" s="35"/>
-      <c r="T20" s="92" t="s">
+      <c r="L26" s="72"/>
+      <c r="M26" s="72"/>
+      <c r="N26" s="72"/>
+      <c r="O26" s="72"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="72"/>
+      <c r="T26" s="88" t="s">
         <v>223</v>
       </c>
-      <c r="U20" s="92"/>
-    </row>
-    <row r="21" spans="2:23" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B21" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" s="31"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="H21" s="36"/>
-      <c r="I21" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="37"/>
-      <c r="K21" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="35"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="35"/>
-      <c r="S21" s="35"/>
-      <c r="T21" s="92" t="s">
-        <v>222</v>
-      </c>
-      <c r="U21" s="92"/>
-    </row>
-    <row r="22" spans="2:23" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B22" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="E22" s="31"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="H22" s="36"/>
-      <c r="I22" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="37"/>
-      <c r="K22" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="35"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="35"/>
-      <c r="T22" s="92" t="s">
-        <v>223</v>
-      </c>
-      <c r="U22" s="92"/>
-    </row>
-    <row r="23" spans="2:23" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B23" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="E23" s="31"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="H23" s="36"/>
-      <c r="I23" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="37"/>
-      <c r="K23" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
-      <c r="R23" s="35"/>
-      <c r="S23" s="35"/>
-      <c r="T23" s="92" t="s">
-        <v>223</v>
-      </c>
-      <c r="U23" s="92"/>
-    </row>
-    <row r="24" spans="2:23" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B24" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" s="31"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="H24" s="36"/>
-      <c r="I24" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="37"/>
-      <c r="K24" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35"/>
-      <c r="Q24" s="35"/>
-      <c r="R24" s="35"/>
-      <c r="S24" s="35"/>
-      <c r="T24" s="92" t="s">
-        <v>223</v>
-      </c>
-      <c r="U24" s="92"/>
-    </row>
-    <row r="25" spans="2:23" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B25" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="C25" s="29"/>
-      <c r="D25" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="E25" s="31"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="H25" s="36"/>
-      <c r="I25" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="37"/>
-      <c r="K25" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
-      <c r="R25" s="35"/>
-      <c r="S25" s="35"/>
-      <c r="T25" s="92" t="s">
-        <v>223</v>
-      </c>
-      <c r="U25" s="92"/>
-    </row>
-    <row r="26" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="E26" s="31"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="H26" s="36"/>
-      <c r="I26" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="37"/>
-      <c r="K26" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="35"/>
-      <c r="R26" s="35"/>
-      <c r="S26" s="35"/>
-      <c r="T26" s="92" t="s">
-        <v>222</v>
-      </c>
-      <c r="U26" s="92"/>
-    </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="V27" s="91"/>
-      <c r="W27" s="91"/>
+      <c r="U26" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="138">
@@ -7135,6 +7140,10 @@
     <mergeCell ref="T8:U8"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K4:S4"/>
+    <mergeCell ref="K5:S5"/>
+    <mergeCell ref="K7:S7"/>
+    <mergeCell ref="K8:S8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="I9:J9"/>
@@ -7144,6 +7153,14 @@
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="I7:J7"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G6:H6"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="G26:H26"/>
     <mergeCell ref="I26:J26"/>
@@ -7156,10 +7173,7 @@
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="I18:J18"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="B22:C22"/>
@@ -7180,6 +7194,10 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="K26:S26"/>
     <mergeCell ref="D20:F20"/>
     <mergeCell ref="D21:F21"/>
@@ -7193,10 +7211,10 @@
     <mergeCell ref="D19:F19"/>
     <mergeCell ref="G23:H23"/>
     <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K4:S4"/>
-    <mergeCell ref="K5:S5"/>
-    <mergeCell ref="K7:S7"/>
-    <mergeCell ref="K8:S8"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:S16"/>
     <mergeCell ref="K9:S9"/>
     <mergeCell ref="K10:S10"/>
     <mergeCell ref="K11:S11"/>
@@ -7221,16 +7239,6 @@
     <mergeCell ref="K23:S23"/>
     <mergeCell ref="K17:S17"/>
     <mergeCell ref="K18:S18"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:S16"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="G15:H15"/>
@@ -7241,11 +7249,8 @@
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="I14:J14"/>
     <mergeCell ref="K14:S14"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:H6"/>
   </mergeCells>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="T5:U5">
     <cfRule type="colorScale" priority="1">
       <colorScale>
@@ -7275,7 +7280,7 @@
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A2:AB67"/>
+  <dimension ref="A2:AB66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:16" ht="26.25" x14ac:dyDescent="0.4">
@@ -7289,53 +7294,53 @@
       </c>
     </row>
     <row r="10" spans="1:16" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="P10" s="75" t="s">
+      <c r="P10" s="28" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="21" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="P21" s="75" t="s">
+      <c r="P21" s="28" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="22" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="P22" s="90" t="s">
+      <c r="P22" s="34" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="24" spans="2:28" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P24" s="76" t="s">
+      <c r="P24" s="35" t="s">
         <v>211</v>
       </c>
-      <c r="Q24" s="76"/>
-      <c r="R24" s="76"/>
-      <c r="S24" s="76"/>
-      <c r="T24" s="76"/>
-      <c r="U24" s="76"/>
-      <c r="V24" s="76"/>
-      <c r="W24" s="76"/>
-      <c r="X24" s="76"/>
-      <c r="Y24" s="76"/>
-      <c r="Z24" s="76"/>
-      <c r="AA24" s="76"/>
-      <c r="AB24" s="76"/>
+      <c r="Q24" s="35"/>
+      <c r="R24" s="35"/>
+      <c r="S24" s="35"/>
+      <c r="T24" s="35"/>
+      <c r="U24" s="35"/>
+      <c r="V24" s="35"/>
+      <c r="W24" s="35"/>
+      <c r="X24" s="35"/>
+      <c r="Y24" s="35"/>
+      <c r="Z24" s="35"/>
+      <c r="AA24" s="35"/>
+      <c r="AB24" s="35"/>
     </row>
     <row r="26" spans="2:28" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P26" s="76" t="s">
+      <c r="P26" s="35" t="s">
         <v>210</v>
       </c>
-      <c r="Q26" s="76"/>
-      <c r="R26" s="76"/>
-      <c r="S26" s="76"/>
-      <c r="T26" s="76"/>
-      <c r="U26" s="76"/>
-      <c r="V26" s="76"/>
-      <c r="W26" s="76"/>
-      <c r="X26" s="76"/>
-      <c r="Y26" s="76"/>
-      <c r="Z26" s="76"/>
-      <c r="AA26" s="76"/>
-      <c r="AB26" s="76"/>
+      <c r="Q26" s="35"/>
+      <c r="R26" s="35"/>
+      <c r="S26" s="35"/>
+      <c r="T26" s="35"/>
+      <c r="U26" s="35"/>
+      <c r="V26" s="35"/>
+      <c r="W26" s="35"/>
+      <c r="X26" s="35"/>
+      <c r="Y26" s="35"/>
+      <c r="Z26" s="35"/>
+      <c r="AA26" s="35"/>
+      <c r="AB26" s="35"/>
     </row>
     <row r="27" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7362,924 +7367,924 @@
       </c>
     </row>
     <row r="35" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="75" t="s">
+      <c r="A35" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="B35" s="76" t="s">
+      <c r="B35" s="35" t="s">
         <v>225</v>
       </c>
-      <c r="C35" s="76"/>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
-      <c r="I35" s="76"/>
-      <c r="J35" s="76"/>
-      <c r="K35" s="76"/>
-      <c r="L35" s="76"/>
-      <c r="M35" s="76"/>
-      <c r="N35" s="76"/>
-      <c r="O35" s="76"/>
-      <c r="P35" s="76"/>
-      <c r="Q35" s="76"/>
-      <c r="R35" s="76"/>
-      <c r="S35" s="76"/>
-      <c r="T35" s="76"/>
-      <c r="U35" s="76"/>
-      <c r="V35" s="76"/>
-      <c r="W35" s="76"/>
-      <c r="X35" s="76"/>
-      <c r="Y35" s="76"/>
-      <c r="Z35" s="76"/>
-      <c r="AA35" s="76"/>
-      <c r="AB35" s="76"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="35"/>
+      <c r="N35" s="35"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="35"/>
+      <c r="Q35" s="35"/>
+      <c r="R35" s="35"/>
+      <c r="S35" s="35"/>
+      <c r="T35" s="35"/>
+      <c r="U35" s="35"/>
+      <c r="V35" s="35"/>
+      <c r="W35" s="35"/>
+      <c r="X35" s="35"/>
+      <c r="Y35" s="35"/>
+      <c r="Z35" s="35"/>
+      <c r="AA35" s="35"/>
+      <c r="AB35" s="35"/>
     </row>
     <row r="36" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="76" t="s">
+      <c r="B36" s="35" t="s">
         <v>226</v>
       </c>
-      <c r="C36" s="76"/>
-      <c r="D36" s="76"/>
-      <c r="E36" s="76"/>
-      <c r="F36" s="76"/>
-      <c r="G36" s="76"/>
-      <c r="H36" s="76"/>
-      <c r="I36" s="76"/>
-      <c r="J36" s="76"/>
-      <c r="K36" s="76"/>
-      <c r="L36" s="76"/>
-      <c r="M36" s="76"/>
-      <c r="N36" s="76"/>
-      <c r="O36" s="76"/>
-      <c r="P36" s="76"/>
-      <c r="Q36" s="76"/>
-      <c r="R36" s="76"/>
-      <c r="S36" s="76"/>
-      <c r="T36" s="76"/>
-      <c r="U36" s="76"/>
-      <c r="V36" s="76"/>
-      <c r="W36" s="76"/>
-      <c r="X36" s="76"/>
-      <c r="Y36" s="76"/>
-      <c r="Z36" s="76"/>
-      <c r="AA36" s="76"/>
-      <c r="AB36" s="76"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="35"/>
+      <c r="L36" s="35"/>
+      <c r="M36" s="35"/>
+      <c r="N36" s="35"/>
+      <c r="O36" s="35"/>
+      <c r="P36" s="35"/>
+      <c r="Q36" s="35"/>
+      <c r="R36" s="35"/>
+      <c r="S36" s="35"/>
+      <c r="T36" s="35"/>
+      <c r="U36" s="35"/>
+      <c r="V36" s="35"/>
+      <c r="W36" s="35"/>
+      <c r="X36" s="35"/>
+      <c r="Y36" s="35"/>
+      <c r="Z36" s="35"/>
+      <c r="AA36" s="35"/>
+      <c r="AB36" s="35"/>
     </row>
     <row r="37" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="76" t="s">
+      <c r="B37" s="35" t="s">
         <v>227</v>
       </c>
-      <c r="C37" s="76"/>
-      <c r="D37" s="76"/>
-      <c r="E37" s="76"/>
-      <c r="F37" s="76"/>
-      <c r="G37" s="76"/>
-      <c r="H37" s="76"/>
-      <c r="I37" s="76"/>
-      <c r="J37" s="76"/>
-      <c r="K37" s="76"/>
-      <c r="L37" s="76"/>
-      <c r="M37" s="76"/>
-      <c r="N37" s="76"/>
-      <c r="O37" s="76"/>
-      <c r="P37" s="76"/>
-      <c r="Q37" s="76"/>
-      <c r="R37" s="76"/>
-      <c r="S37" s="76"/>
-      <c r="T37" s="76"/>
-      <c r="U37" s="76"/>
-      <c r="V37" s="76"/>
-      <c r="W37" s="76"/>
-      <c r="X37" s="76"/>
-      <c r="Y37" s="76"/>
-      <c r="Z37" s="76"/>
-      <c r="AA37" s="76"/>
-      <c r="AB37" s="76"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="35"/>
+      <c r="L37" s="35"/>
+      <c r="M37" s="35"/>
+      <c r="N37" s="35"/>
+      <c r="O37" s="35"/>
+      <c r="P37" s="35"/>
+      <c r="Q37" s="35"/>
+      <c r="R37" s="35"/>
+      <c r="S37" s="35"/>
+      <c r="T37" s="35"/>
+      <c r="U37" s="35"/>
+      <c r="V37" s="35"/>
+      <c r="W37" s="35"/>
+      <c r="X37" s="35"/>
+      <c r="Y37" s="35"/>
+      <c r="Z37" s="35"/>
+      <c r="AA37" s="35"/>
+      <c r="AB37" s="35"/>
     </row>
     <row r="38" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="76" t="s">
+      <c r="B38" s="35" t="s">
         <v>228</v>
       </c>
-      <c r="C38" s="76"/>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76"/>
-      <c r="F38" s="76"/>
-      <c r="G38" s="76"/>
-      <c r="H38" s="76"/>
-      <c r="I38" s="76"/>
-      <c r="J38" s="76"/>
-      <c r="K38" s="76"/>
-      <c r="L38" s="76"/>
-      <c r="M38" s="76"/>
-      <c r="N38" s="76"/>
-      <c r="O38" s="76"/>
-      <c r="P38" s="76"/>
-      <c r="Q38" s="76"/>
-      <c r="R38" s="76"/>
-      <c r="S38" s="76"/>
-      <c r="T38" s="76"/>
-      <c r="U38" s="76"/>
-      <c r="V38" s="76"/>
-      <c r="W38" s="76"/>
-      <c r="X38" s="76"/>
-      <c r="Y38" s="76"/>
-      <c r="Z38" s="76"/>
-      <c r="AA38" s="76"/>
-      <c r="AB38" s="76"/>
+      <c r="C38" s="35"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="35"/>
+      <c r="K38" s="35"/>
+      <c r="L38" s="35"/>
+      <c r="M38" s="35"/>
+      <c r="N38" s="35"/>
+      <c r="O38" s="35"/>
+      <c r="P38" s="35"/>
+      <c r="Q38" s="35"/>
+      <c r="R38" s="35"/>
+      <c r="S38" s="35"/>
+      <c r="T38" s="35"/>
+      <c r="U38" s="35"/>
+      <c r="V38" s="35"/>
+      <c r="W38" s="35"/>
+      <c r="X38" s="35"/>
+      <c r="Y38" s="35"/>
+      <c r="Z38" s="35"/>
+      <c r="AA38" s="35"/>
+      <c r="AB38" s="35"/>
     </row>
     <row r="39" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="76" t="s">
+      <c r="B39" s="35" t="s">
         <v>213</v>
       </c>
-      <c r="C39" s="76"/>
-      <c r="D39" s="76"/>
-      <c r="E39" s="76"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="76"/>
-      <c r="H39" s="76"/>
-      <c r="I39" s="76"/>
-      <c r="J39" s="76"/>
-      <c r="K39" s="76"/>
-      <c r="L39" s="76"/>
-      <c r="M39" s="76"/>
-      <c r="N39" s="76"/>
-      <c r="O39" s="76"/>
-      <c r="P39" s="76"/>
-      <c r="Q39" s="76"/>
-      <c r="R39" s="76"/>
-      <c r="S39" s="76"/>
-      <c r="T39" s="76"/>
-      <c r="U39" s="76"/>
-      <c r="V39" s="76"/>
-      <c r="W39" s="76"/>
-      <c r="X39" s="76"/>
-      <c r="Y39" s="76"/>
-      <c r="Z39" s="76"/>
-      <c r="AA39" s="76"/>
-      <c r="AB39" s="76"/>
-    </row>
-    <row r="41" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="76" t="s">
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="35"/>
+      <c r="J39" s="35"/>
+      <c r="K39" s="35"/>
+      <c r="L39" s="35"/>
+      <c r="M39" s="35"/>
+      <c r="N39" s="35"/>
+      <c r="O39" s="35"/>
+      <c r="P39" s="35"/>
+      <c r="Q39" s="35"/>
+      <c r="R39" s="35"/>
+      <c r="S39" s="35"/>
+      <c r="T39" s="35"/>
+      <c r="U39" s="35"/>
+      <c r="V39" s="35"/>
+      <c r="W39" s="35"/>
+      <c r="X39" s="35"/>
+      <c r="Y39" s="35"/>
+      <c r="Z39" s="35"/>
+      <c r="AA39" s="35"/>
+      <c r="AB39" s="35"/>
+    </row>
+    <row r="40" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="35" t="s">
         <v>229</v>
       </c>
-      <c r="C41" s="76"/>
-      <c r="D41" s="76"/>
-      <c r="E41" s="76"/>
-      <c r="F41" s="76"/>
-      <c r="G41" s="76"/>
-      <c r="H41" s="76"/>
-      <c r="I41" s="76"/>
-      <c r="J41" s="76"/>
-      <c r="K41" s="76"/>
-      <c r="L41" s="76"/>
-      <c r="M41" s="76"/>
-      <c r="N41" s="76"/>
-      <c r="O41" s="76"/>
-      <c r="P41" s="76"/>
-      <c r="Q41" s="76"/>
-      <c r="R41" s="76"/>
-      <c r="S41" s="76"/>
-      <c r="T41" s="76"/>
-      <c r="U41" s="76"/>
-      <c r="V41" s="76"/>
-      <c r="W41" s="76"/>
-      <c r="X41" s="76"/>
-      <c r="Y41" s="76"/>
-      <c r="Z41" s="76"/>
-      <c r="AA41" s="76"/>
-      <c r="AB41" s="76"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="35"/>
+      <c r="L40" s="35"/>
+      <c r="M40" s="35"/>
+      <c r="N40" s="35"/>
+      <c r="O40" s="35"/>
+      <c r="P40" s="35"/>
+      <c r="Q40" s="35"/>
+      <c r="R40" s="35"/>
+      <c r="S40" s="35"/>
+      <c r="T40" s="35"/>
+      <c r="U40" s="35"/>
+      <c r="V40" s="35"/>
+      <c r="W40" s="35"/>
+      <c r="X40" s="35"/>
+      <c r="Y40" s="35"/>
+      <c r="Z40" s="35"/>
+      <c r="AA40" s="35"/>
+      <c r="AB40" s="35"/>
+    </row>
+    <row r="41" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B41" s="35" t="s">
+        <v>230</v>
+      </c>
+      <c r="C41" s="35"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="35"/>
+      <c r="J41" s="35"/>
+      <c r="K41" s="35"/>
+      <c r="L41" s="35"/>
+      <c r="M41" s="35"/>
+      <c r="N41" s="35"/>
+      <c r="O41" s="35"/>
+      <c r="P41" s="35"/>
+      <c r="Q41" s="35"/>
+      <c r="R41" s="35"/>
+      <c r="S41" s="35"/>
+      <c r="T41" s="35"/>
+      <c r="U41" s="35"/>
+      <c r="V41" s="35"/>
+      <c r="W41" s="35"/>
+      <c r="X41" s="35"/>
+      <c r="Y41" s="35"/>
+      <c r="Z41" s="35"/>
+      <c r="AA41" s="35"/>
+      <c r="AB41" s="35"/>
     </row>
     <row r="42" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B42" s="76" t="s">
-        <v>230</v>
-      </c>
-      <c r="C42" s="76"/>
-      <c r="D42" s="76"/>
-      <c r="E42" s="76"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="76"/>
-      <c r="H42" s="76"/>
-      <c r="I42" s="76"/>
-      <c r="J42" s="76"/>
-      <c r="K42" s="76"/>
-      <c r="L42" s="76"/>
-      <c r="M42" s="76"/>
-      <c r="N42" s="76"/>
-      <c r="O42" s="76"/>
-      <c r="P42" s="76"/>
-      <c r="Q42" s="76"/>
-      <c r="R42" s="76"/>
-      <c r="S42" s="76"/>
-      <c r="T42" s="76"/>
-      <c r="U42" s="76"/>
-      <c r="V42" s="76"/>
-      <c r="W42" s="76"/>
-      <c r="X42" s="76"/>
-      <c r="Y42" s="76"/>
-      <c r="Z42" s="76"/>
-      <c r="AA42" s="76"/>
-      <c r="AB42" s="76"/>
+      <c r="B42" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="C42" s="35"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="35"/>
+      <c r="J42" s="35"/>
+      <c r="K42" s="35"/>
+      <c r="L42" s="35"/>
+      <c r="M42" s="35"/>
+      <c r="N42" s="35"/>
+      <c r="O42" s="35"/>
+      <c r="P42" s="35"/>
+      <c r="Q42" s="35"/>
+      <c r="R42" s="35"/>
+      <c r="S42" s="35"/>
+      <c r="T42" s="35"/>
+      <c r="U42" s="35"/>
+      <c r="V42" s="35"/>
+      <c r="W42" s="35"/>
+      <c r="X42" s="35"/>
+      <c r="Y42" s="35"/>
+      <c r="Z42" s="35"/>
+      <c r="AA42" s="35"/>
+      <c r="AB42" s="35"/>
     </row>
     <row r="43" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B43" s="76" t="s">
-        <v>231</v>
-      </c>
-      <c r="C43" s="76"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="76"/>
-      <c r="H43" s="76"/>
-      <c r="I43" s="76"/>
-      <c r="J43" s="76"/>
-      <c r="K43" s="76"/>
-      <c r="L43" s="76"/>
-      <c r="M43" s="76"/>
-      <c r="N43" s="76"/>
-      <c r="O43" s="76"/>
-      <c r="P43" s="76"/>
-      <c r="Q43" s="76"/>
-      <c r="R43" s="76"/>
-      <c r="S43" s="76"/>
-      <c r="T43" s="76"/>
-      <c r="U43" s="76"/>
-      <c r="V43" s="76"/>
-      <c r="W43" s="76"/>
-      <c r="X43" s="76"/>
-      <c r="Y43" s="76"/>
-      <c r="Z43" s="76"/>
-      <c r="AA43" s="76"/>
-      <c r="AB43" s="76"/>
+      <c r="B43" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="35"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="35"/>
+      <c r="J43" s="35"/>
+      <c r="K43" s="35"/>
+      <c r="L43" s="35"/>
+      <c r="M43" s="35"/>
+      <c r="N43" s="35"/>
+      <c r="O43" s="35"/>
+      <c r="P43" s="35"/>
+      <c r="Q43" s="35"/>
+      <c r="R43" s="35"/>
+      <c r="S43" s="35"/>
+      <c r="T43" s="35"/>
+      <c r="U43" s="35"/>
+      <c r="V43" s="35"/>
+      <c r="W43" s="35"/>
+      <c r="X43" s="35"/>
+      <c r="Y43" s="35"/>
+      <c r="Z43" s="35"/>
+      <c r="AA43" s="35"/>
+      <c r="AB43" s="35"/>
     </row>
     <row r="44" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B44" s="76" t="s">
-        <v>232</v>
-      </c>
-      <c r="C44" s="76"/>
-      <c r="D44" s="76"/>
-      <c r="E44" s="76"/>
-      <c r="F44" s="76"/>
-      <c r="G44" s="76"/>
-      <c r="H44" s="76"/>
-      <c r="I44" s="76"/>
-      <c r="J44" s="76"/>
-      <c r="K44" s="76"/>
-      <c r="L44" s="76"/>
-      <c r="M44" s="76"/>
-      <c r="N44" s="76"/>
-      <c r="O44" s="76"/>
-      <c r="P44" s="76"/>
-      <c r="Q44" s="76"/>
-      <c r="R44" s="76"/>
-      <c r="S44" s="76"/>
-      <c r="T44" s="76"/>
-      <c r="U44" s="76"/>
-      <c r="V44" s="76"/>
-      <c r="W44" s="76"/>
-      <c r="X44" s="76"/>
-      <c r="Y44" s="76"/>
-      <c r="Z44" s="76"/>
-      <c r="AA44" s="76"/>
-      <c r="AB44" s="76"/>
+      <c r="B44" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="C44" s="35"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="35"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="35"/>
+      <c r="H44" s="35"/>
+      <c r="I44" s="35"/>
+      <c r="J44" s="35"/>
+      <c r="K44" s="35"/>
+      <c r="L44" s="35"/>
+      <c r="M44" s="35"/>
+      <c r="N44" s="35"/>
+      <c r="O44" s="35"/>
+      <c r="P44" s="35"/>
+      <c r="Q44" s="35"/>
+      <c r="R44" s="35"/>
+      <c r="S44" s="35"/>
+      <c r="T44" s="35"/>
+      <c r="U44" s="35"/>
+      <c r="V44" s="35"/>
+      <c r="W44" s="35"/>
+      <c r="X44" s="35"/>
+      <c r="Y44" s="35"/>
+      <c r="Z44" s="35"/>
+      <c r="AA44" s="35"/>
+      <c r="AB44" s="35"/>
     </row>
     <row r="45" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B45" s="76" t="s">
-        <v>233</v>
-      </c>
-      <c r="C45" s="76"/>
-      <c r="D45" s="76"/>
-      <c r="E45" s="76"/>
-      <c r="F45" s="76"/>
-      <c r="G45" s="76"/>
-      <c r="H45" s="76"/>
-      <c r="I45" s="76"/>
-      <c r="J45" s="76"/>
-      <c r="K45" s="76"/>
-      <c r="L45" s="76"/>
-      <c r="M45" s="76"/>
-      <c r="N45" s="76"/>
-      <c r="O45" s="76"/>
-      <c r="P45" s="76"/>
-      <c r="Q45" s="76"/>
-      <c r="R45" s="76"/>
-      <c r="S45" s="76"/>
-      <c r="T45" s="76"/>
-      <c r="U45" s="76"/>
-      <c r="V45" s="76"/>
-      <c r="W45" s="76"/>
-      <c r="X45" s="76"/>
-      <c r="Y45" s="76"/>
-      <c r="Z45" s="76"/>
-      <c r="AA45" s="76"/>
-      <c r="AB45" s="76"/>
+      <c r="B45" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="C45" s="35"/>
+      <c r="D45" s="35"/>
+      <c r="E45" s="35"/>
+      <c r="F45" s="35"/>
+      <c r="G45" s="35"/>
+      <c r="H45" s="35"/>
+      <c r="I45" s="35"/>
+      <c r="J45" s="35"/>
+      <c r="K45" s="35"/>
+      <c r="L45" s="35"/>
+      <c r="M45" s="35"/>
+      <c r="N45" s="35"/>
+      <c r="O45" s="35"/>
+      <c r="P45" s="35"/>
+      <c r="Q45" s="35"/>
+      <c r="R45" s="35"/>
+      <c r="S45" s="35"/>
+      <c r="T45" s="35"/>
+      <c r="U45" s="35"/>
+      <c r="V45" s="35"/>
+      <c r="W45" s="35"/>
+      <c r="X45" s="35"/>
+      <c r="Y45" s="35"/>
+      <c r="Z45" s="35"/>
+      <c r="AA45" s="35"/>
+      <c r="AB45" s="35"/>
     </row>
     <row r="46" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B46" s="76" t="s">
-        <v>234</v>
-      </c>
-      <c r="C46" s="76"/>
-      <c r="D46" s="76"/>
-      <c r="E46" s="76"/>
-      <c r="F46" s="76"/>
-      <c r="G46" s="76"/>
-      <c r="H46" s="76"/>
-      <c r="I46" s="76"/>
-      <c r="J46" s="76"/>
-      <c r="K46" s="76"/>
-      <c r="L46" s="76"/>
-      <c r="M46" s="76"/>
-      <c r="N46" s="76"/>
-      <c r="O46" s="76"/>
-      <c r="P46" s="76"/>
-      <c r="Q46" s="76"/>
-      <c r="R46" s="76"/>
-      <c r="S46" s="76"/>
-      <c r="T46" s="76"/>
-      <c r="U46" s="76"/>
-      <c r="V46" s="76"/>
-      <c r="W46" s="76"/>
-      <c r="X46" s="76"/>
-      <c r="Y46" s="76"/>
-      <c r="Z46" s="76"/>
-      <c r="AA46" s="76"/>
-      <c r="AB46" s="76"/>
+      <c r="B46" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="C46" s="35"/>
+      <c r="D46" s="35"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="35"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="35"/>
+      <c r="J46" s="35"/>
+      <c r="K46" s="35"/>
+      <c r="L46" s="35"/>
+      <c r="M46" s="35"/>
+      <c r="N46" s="35"/>
+      <c r="O46" s="35"/>
+      <c r="P46" s="35"/>
+      <c r="Q46" s="35"/>
+      <c r="R46" s="35"/>
+      <c r="S46" s="35"/>
+      <c r="T46" s="35"/>
+      <c r="U46" s="35"/>
+      <c r="V46" s="35"/>
+      <c r="W46" s="35"/>
+      <c r="X46" s="35"/>
+      <c r="Y46" s="35"/>
+      <c r="Z46" s="35"/>
+      <c r="AA46" s="35"/>
+      <c r="AB46" s="35"/>
     </row>
     <row r="47" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B47" s="76" t="s">
-        <v>235</v>
-      </c>
-      <c r="C47" s="76"/>
-      <c r="D47" s="76"/>
-      <c r="E47" s="76"/>
-      <c r="F47" s="76"/>
-      <c r="G47" s="76"/>
-      <c r="H47" s="76"/>
-      <c r="I47" s="76"/>
-      <c r="J47" s="76"/>
-      <c r="K47" s="76"/>
-      <c r="L47" s="76"/>
-      <c r="M47" s="76"/>
-      <c r="N47" s="76"/>
-      <c r="O47" s="76"/>
-      <c r="P47" s="76"/>
-      <c r="Q47" s="76"/>
-      <c r="R47" s="76"/>
-      <c r="S47" s="76"/>
-      <c r="T47" s="76"/>
-      <c r="U47" s="76"/>
-      <c r="V47" s="76"/>
-      <c r="W47" s="76"/>
-      <c r="X47" s="76"/>
-      <c r="Y47" s="76"/>
-      <c r="Z47" s="76"/>
-      <c r="AA47" s="76"/>
-      <c r="AB47" s="76"/>
+      <c r="B47" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
+      <c r="E47" s="35"/>
+      <c r="F47" s="35"/>
+      <c r="G47" s="35"/>
+      <c r="H47" s="35"/>
+      <c r="I47" s="35"/>
+      <c r="J47" s="35"/>
+      <c r="K47" s="35"/>
+      <c r="L47" s="35"/>
+      <c r="M47" s="35"/>
+      <c r="N47" s="35"/>
+      <c r="O47" s="35"/>
+      <c r="P47" s="35"/>
+      <c r="Q47" s="35"/>
+      <c r="R47" s="35"/>
+      <c r="S47" s="35"/>
+      <c r="T47" s="35"/>
+      <c r="U47" s="35"/>
+      <c r="V47" s="35"/>
+      <c r="W47" s="35"/>
+      <c r="X47" s="35"/>
+      <c r="Y47" s="35"/>
+      <c r="Z47" s="35"/>
+      <c r="AA47" s="35"/>
+      <c r="AB47" s="35"/>
     </row>
     <row r="48" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B48" s="76" t="s">
-        <v>236</v>
-      </c>
-      <c r="C48" s="76"/>
-      <c r="D48" s="76"/>
-      <c r="E48" s="76"/>
-      <c r="F48" s="76"/>
-      <c r="G48" s="76"/>
-      <c r="H48" s="76"/>
-      <c r="I48" s="76"/>
-      <c r="J48" s="76"/>
-      <c r="K48" s="76"/>
-      <c r="L48" s="76"/>
-      <c r="M48" s="76"/>
-      <c r="N48" s="76"/>
-      <c r="O48" s="76"/>
-      <c r="P48" s="76"/>
-      <c r="Q48" s="76"/>
-      <c r="R48" s="76"/>
-      <c r="S48" s="76"/>
-      <c r="T48" s="76"/>
-      <c r="U48" s="76"/>
-      <c r="V48" s="76"/>
-      <c r="W48" s="76"/>
-      <c r="X48" s="76"/>
-      <c r="Y48" s="76"/>
-      <c r="Z48" s="76"/>
-      <c r="AA48" s="76"/>
-      <c r="AB48" s="76"/>
+      <c r="B48" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="C48" s="35"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="35"/>
+      <c r="F48" s="35"/>
+      <c r="G48" s="35"/>
+      <c r="H48" s="35"/>
+      <c r="I48" s="35"/>
+      <c r="J48" s="35"/>
+      <c r="K48" s="35"/>
+      <c r="L48" s="35"/>
+      <c r="M48" s="35"/>
+      <c r="N48" s="35"/>
+      <c r="O48" s="35"/>
+      <c r="P48" s="35"/>
+      <c r="Q48" s="35"/>
+      <c r="R48" s="35"/>
+      <c r="S48" s="35"/>
+      <c r="T48" s="35"/>
+      <c r="U48" s="35"/>
+      <c r="V48" s="35"/>
+      <c r="W48" s="35"/>
+      <c r="X48" s="35"/>
+      <c r="Y48" s="35"/>
+      <c r="Z48" s="35"/>
+      <c r="AA48" s="35"/>
+      <c r="AB48" s="35"/>
     </row>
     <row r="49" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B49" s="76" t="s">
-        <v>237</v>
-      </c>
-      <c r="C49" s="76"/>
-      <c r="D49" s="76"/>
-      <c r="E49" s="76"/>
-      <c r="F49" s="76"/>
-      <c r="G49" s="76"/>
-      <c r="H49" s="76"/>
-      <c r="I49" s="76"/>
-      <c r="J49" s="76"/>
-      <c r="K49" s="76"/>
-      <c r="L49" s="76"/>
-      <c r="M49" s="76"/>
-      <c r="N49" s="76"/>
-      <c r="O49" s="76"/>
-      <c r="P49" s="76"/>
-      <c r="Q49" s="76"/>
-      <c r="R49" s="76"/>
-      <c r="S49" s="76"/>
-      <c r="T49" s="76"/>
-      <c r="U49" s="76"/>
-      <c r="V49" s="76"/>
-      <c r="W49" s="76"/>
-      <c r="X49" s="76"/>
-      <c r="Y49" s="76"/>
-      <c r="Z49" s="76"/>
-      <c r="AA49" s="76"/>
-      <c r="AB49" s="76"/>
+      <c r="B49" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="C49" s="35"/>
+      <c r="D49" s="35"/>
+      <c r="E49" s="35"/>
+      <c r="F49" s="35"/>
+      <c r="G49" s="35"/>
+      <c r="H49" s="35"/>
+      <c r="I49" s="35"/>
+      <c r="J49" s="35"/>
+      <c r="K49" s="35"/>
+      <c r="L49" s="35"/>
+      <c r="M49" s="35"/>
+      <c r="N49" s="35"/>
+      <c r="O49" s="35"/>
+      <c r="P49" s="35"/>
+      <c r="Q49" s="35"/>
+      <c r="R49" s="35"/>
+      <c r="S49" s="35"/>
+      <c r="T49" s="35"/>
+      <c r="U49" s="35"/>
+      <c r="V49" s="35"/>
+      <c r="W49" s="35"/>
+      <c r="X49" s="35"/>
+      <c r="Y49" s="35"/>
+      <c r="Z49" s="35"/>
+      <c r="AA49" s="35"/>
+      <c r="AB49" s="35"/>
     </row>
     <row r="50" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B50" s="76" t="s">
-        <v>238</v>
-      </c>
-      <c r="C50" s="76"/>
-      <c r="D50" s="76"/>
-      <c r="E50" s="76"/>
-      <c r="F50" s="76"/>
-      <c r="G50" s="76"/>
-      <c r="H50" s="76"/>
-      <c r="I50" s="76"/>
-      <c r="J50" s="76"/>
-      <c r="K50" s="76"/>
-      <c r="L50" s="76"/>
-      <c r="M50" s="76"/>
-      <c r="N50" s="76"/>
-      <c r="O50" s="76"/>
-      <c r="P50" s="76"/>
-      <c r="Q50" s="76"/>
-      <c r="R50" s="76"/>
-      <c r="S50" s="76"/>
-      <c r="T50" s="76"/>
-      <c r="U50" s="76"/>
-      <c r="V50" s="76"/>
-      <c r="W50" s="76"/>
-      <c r="X50" s="76"/>
-      <c r="Y50" s="76"/>
-      <c r="Z50" s="76"/>
-      <c r="AA50" s="76"/>
-      <c r="AB50" s="76"/>
+      <c r="B50" s="35" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="35"/>
+      <c r="D50" s="35"/>
+      <c r="E50" s="35"/>
+      <c r="F50" s="35"/>
+      <c r="G50" s="35"/>
+      <c r="H50" s="35"/>
+      <c r="I50" s="35"/>
+      <c r="J50" s="35"/>
+      <c r="K50" s="35"/>
+      <c r="L50" s="35"/>
+      <c r="M50" s="35"/>
+      <c r="N50" s="35"/>
+      <c r="O50" s="35"/>
+      <c r="P50" s="35"/>
+      <c r="Q50" s="35"/>
+      <c r="R50" s="35"/>
+      <c r="S50" s="35"/>
+      <c r="T50" s="35"/>
+      <c r="U50" s="35"/>
+      <c r="V50" s="35"/>
+      <c r="W50" s="35"/>
+      <c r="X50" s="35"/>
+      <c r="Y50" s="35"/>
+      <c r="Z50" s="35"/>
+      <c r="AA50" s="35"/>
+      <c r="AB50" s="35"/>
     </row>
     <row r="51" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B51" s="76" t="s">
-        <v>239</v>
-      </c>
-      <c r="C51" s="76"/>
-      <c r="D51" s="76"/>
-      <c r="E51" s="76"/>
-      <c r="F51" s="76"/>
-      <c r="G51" s="76"/>
-      <c r="H51" s="76"/>
-      <c r="I51" s="76"/>
-      <c r="J51" s="76"/>
-      <c r="K51" s="76"/>
-      <c r="L51" s="76"/>
-      <c r="M51" s="76"/>
-      <c r="N51" s="76"/>
-      <c r="O51" s="76"/>
-      <c r="P51" s="76"/>
-      <c r="Q51" s="76"/>
-      <c r="R51" s="76"/>
-      <c r="S51" s="76"/>
-      <c r="T51" s="76"/>
-      <c r="U51" s="76"/>
-      <c r="V51" s="76"/>
-      <c r="W51" s="76"/>
-      <c r="X51" s="76"/>
-      <c r="Y51" s="76"/>
-      <c r="Z51" s="76"/>
-      <c r="AA51" s="76"/>
-      <c r="AB51" s="76"/>
+      <c r="B51" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="C51" s="35"/>
+      <c r="D51" s="35"/>
+      <c r="E51" s="35"/>
+      <c r="F51" s="35"/>
+      <c r="G51" s="35"/>
+      <c r="H51" s="35"/>
+      <c r="I51" s="35"/>
+      <c r="J51" s="35"/>
+      <c r="K51" s="35"/>
+      <c r="L51" s="35"/>
+      <c r="M51" s="35"/>
+      <c r="N51" s="35"/>
+      <c r="O51" s="35"/>
+      <c r="P51" s="35"/>
+      <c r="Q51" s="35"/>
+      <c r="R51" s="35"/>
+      <c r="S51" s="35"/>
+      <c r="T51" s="35"/>
+      <c r="U51" s="35"/>
+      <c r="V51" s="35"/>
+      <c r="W51" s="35"/>
+      <c r="X51" s="35"/>
+      <c r="Y51" s="35"/>
+      <c r="Z51" s="35"/>
+      <c r="AA51" s="35"/>
+      <c r="AB51" s="35"/>
     </row>
     <row r="52" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B52" s="76" t="s">
-        <v>240</v>
-      </c>
-      <c r="C52" s="76"/>
-      <c r="D52" s="76"/>
-      <c r="E52" s="76"/>
-      <c r="F52" s="76"/>
-      <c r="G52" s="76"/>
-      <c r="H52" s="76"/>
-      <c r="I52" s="76"/>
-      <c r="J52" s="76"/>
-      <c r="K52" s="76"/>
-      <c r="L52" s="76"/>
-      <c r="M52" s="76"/>
-      <c r="N52" s="76"/>
-      <c r="O52" s="76"/>
-      <c r="P52" s="76"/>
-      <c r="Q52" s="76"/>
-      <c r="R52" s="76"/>
-      <c r="S52" s="76"/>
-      <c r="T52" s="76"/>
-      <c r="U52" s="76"/>
-      <c r="V52" s="76"/>
-      <c r="W52" s="76"/>
-      <c r="X52" s="76"/>
-      <c r="Y52" s="76"/>
-      <c r="Z52" s="76"/>
-      <c r="AA52" s="76"/>
-      <c r="AB52" s="76"/>
-    </row>
-    <row r="53" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B53" s="76" t="s">
+      <c r="B52" s="35" t="s">
         <v>241</v>
       </c>
-      <c r="C53" s="76"/>
-      <c r="D53" s="76"/>
-      <c r="E53" s="76"/>
-      <c r="F53" s="76"/>
-      <c r="G53" s="76"/>
-      <c r="H53" s="76"/>
-      <c r="I53" s="76"/>
-      <c r="J53" s="76"/>
-      <c r="K53" s="76"/>
-      <c r="L53" s="76"/>
-      <c r="M53" s="76"/>
-      <c r="N53" s="76"/>
-      <c r="O53" s="76"/>
-      <c r="P53" s="76"/>
-      <c r="Q53" s="76"/>
-      <c r="R53" s="76"/>
-      <c r="S53" s="76"/>
-      <c r="T53" s="76"/>
-      <c r="U53" s="76"/>
-      <c r="V53" s="76"/>
-      <c r="W53" s="76"/>
-      <c r="X53" s="76"/>
-      <c r="Y53" s="76"/>
-      <c r="Z53" s="76"/>
-      <c r="AA53" s="76"/>
-      <c r="AB53" s="76"/>
+      <c r="C52" s="35"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="35"/>
+      <c r="F52" s="35"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="35"/>
+      <c r="I52" s="35"/>
+      <c r="J52" s="35"/>
+      <c r="K52" s="35"/>
+      <c r="L52" s="35"/>
+      <c r="M52" s="35"/>
+      <c r="N52" s="35"/>
+      <c r="O52" s="35"/>
+      <c r="P52" s="35"/>
+      <c r="Q52" s="35"/>
+      <c r="R52" s="35"/>
+      <c r="S52" s="35"/>
+      <c r="T52" s="35"/>
+      <c r="U52" s="35"/>
+      <c r="V52" s="35"/>
+      <c r="W52" s="35"/>
+      <c r="X52" s="35"/>
+      <c r="Y52" s="35"/>
+      <c r="Z52" s="35"/>
+      <c r="AA52" s="35"/>
+      <c r="AB52" s="35"/>
+    </row>
+    <row r="54" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B54" s="8" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="55" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B55" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B56" s="8" t="s">
-        <v>217</v>
-      </c>
+      <c r="B56" s="8"/>
     </row>
     <row r="57" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B57" s="8"/>
-    </row>
-    <row r="58" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A58" s="75" t="s">
+      <c r="A57" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="B58" s="76" t="s">
+      <c r="B57" s="35" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="76"/>
-      <c r="D58" s="76"/>
-      <c r="E58" s="76"/>
-      <c r="F58" s="76"/>
-      <c r="G58" s="76"/>
-      <c r="H58" s="76"/>
-      <c r="I58" s="76"/>
-      <c r="J58" s="76"/>
-      <c r="K58" s="76"/>
-      <c r="L58" s="76"/>
-      <c r="M58" s="76"/>
-      <c r="N58" s="76"/>
-      <c r="O58" s="76"/>
-      <c r="P58" s="76"/>
-      <c r="Q58" s="76"/>
-      <c r="R58" s="76"/>
-      <c r="S58" s="76"/>
-      <c r="T58" s="76"/>
-      <c r="U58" s="76"/>
-      <c r="V58" s="76"/>
-      <c r="W58" s="76"/>
-      <c r="X58" s="76"/>
-      <c r="Y58" s="76"/>
-      <c r="Z58" s="76"/>
-      <c r="AA58" s="76"/>
-      <c r="AB58" s="76"/>
+      <c r="C57" s="35"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="35"/>
+      <c r="I57" s="35"/>
+      <c r="J57" s="35"/>
+      <c r="K57" s="35"/>
+      <c r="L57" s="35"/>
+      <c r="M57" s="35"/>
+      <c r="N57" s="35"/>
+      <c r="O57" s="35"/>
+      <c r="P57" s="35"/>
+      <c r="Q57" s="35"/>
+      <c r="R57" s="35"/>
+      <c r="S57" s="35"/>
+      <c r="T57" s="35"/>
+      <c r="U57" s="35"/>
+      <c r="V57" s="35"/>
+      <c r="W57" s="35"/>
+      <c r="X57" s="35"/>
+      <c r="Y57" s="35"/>
+      <c r="Z57" s="35"/>
+      <c r="AA57" s="35"/>
+      <c r="AB57" s="35"/>
+    </row>
+    <row r="58" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B58" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="35"/>
+      <c r="I58" s="35"/>
+      <c r="J58" s="35"/>
+      <c r="K58" s="35"/>
+      <c r="L58" s="35"/>
+      <c r="M58" s="35"/>
+      <c r="N58" s="35"/>
+      <c r="O58" s="35"/>
+      <c r="P58" s="35"/>
+      <c r="Q58" s="35"/>
+      <c r="R58" s="35"/>
+      <c r="S58" s="35"/>
+      <c r="T58" s="35"/>
+      <c r="U58" s="35"/>
+      <c r="V58" s="35"/>
+      <c r="W58" s="35"/>
+      <c r="X58" s="35"/>
+      <c r="Y58" s="35"/>
+      <c r="Z58" s="35"/>
+      <c r="AA58" s="35"/>
+      <c r="AB58" s="35"/>
     </row>
     <row r="59" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B59" s="76" t="s">
-        <v>231</v>
-      </c>
-      <c r="C59" s="76"/>
-      <c r="D59" s="76"/>
-      <c r="E59" s="76"/>
-      <c r="F59" s="76"/>
-      <c r="G59" s="76"/>
-      <c r="H59" s="76"/>
-      <c r="I59" s="76"/>
-      <c r="J59" s="76"/>
-      <c r="K59" s="76"/>
-      <c r="L59" s="76"/>
-      <c r="M59" s="76"/>
-      <c r="N59" s="76"/>
-      <c r="O59" s="76"/>
-      <c r="P59" s="76"/>
-      <c r="Q59" s="76"/>
-      <c r="R59" s="76"/>
-      <c r="S59" s="76"/>
-      <c r="T59" s="76"/>
-      <c r="U59" s="76"/>
-      <c r="V59" s="76"/>
-      <c r="W59" s="76"/>
-      <c r="X59" s="76"/>
-      <c r="Y59" s="76"/>
-      <c r="Z59" s="76"/>
-      <c r="AA59" s="76"/>
-      <c r="AB59" s="76"/>
+      <c r="B59" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="C59" s="35"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="35"/>
+      <c r="I59" s="35"/>
+      <c r="J59" s="35"/>
+      <c r="K59" s="35"/>
+      <c r="L59" s="35"/>
+      <c r="M59" s="35"/>
+      <c r="N59" s="35"/>
+      <c r="O59" s="35"/>
+      <c r="P59" s="35"/>
+      <c r="Q59" s="35"/>
+      <c r="R59" s="35"/>
+      <c r="S59" s="35"/>
+      <c r="T59" s="35"/>
+      <c r="U59" s="35"/>
+      <c r="V59" s="35"/>
+      <c r="W59" s="35"/>
+      <c r="X59" s="35"/>
+      <c r="Y59" s="35"/>
+      <c r="Z59" s="35"/>
+      <c r="AA59" s="35"/>
+      <c r="AB59" s="35"/>
     </row>
     <row r="60" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B60" s="76" t="s">
-        <v>232</v>
-      </c>
-      <c r="C60" s="76"/>
-      <c r="D60" s="76"/>
-      <c r="E60" s="76"/>
-      <c r="F60" s="76"/>
-      <c r="G60" s="76"/>
-      <c r="H60" s="76"/>
-      <c r="I60" s="76"/>
-      <c r="J60" s="76"/>
-      <c r="K60" s="76"/>
-      <c r="L60" s="76"/>
-      <c r="M60" s="76"/>
-      <c r="N60" s="76"/>
-      <c r="O60" s="76"/>
-      <c r="P60" s="76"/>
-      <c r="Q60" s="76"/>
-      <c r="R60" s="76"/>
-      <c r="S60" s="76"/>
-      <c r="T60" s="76"/>
-      <c r="U60" s="76"/>
-      <c r="V60" s="76"/>
-      <c r="W60" s="76"/>
-      <c r="X60" s="76"/>
-      <c r="Y60" s="76"/>
-      <c r="Z60" s="76"/>
-      <c r="AA60" s="76"/>
-      <c r="AB60" s="76"/>
+      <c r="B60" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="C60" s="35"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="35"/>
+      <c r="F60" s="35"/>
+      <c r="G60" s="35"/>
+      <c r="H60" s="35"/>
+      <c r="I60" s="35"/>
+      <c r="J60" s="35"/>
+      <c r="K60" s="35"/>
+      <c r="L60" s="35"/>
+      <c r="M60" s="35"/>
+      <c r="N60" s="35"/>
+      <c r="O60" s="35"/>
+      <c r="P60" s="35"/>
+      <c r="Q60" s="35"/>
+      <c r="R60" s="35"/>
+      <c r="S60" s="35"/>
+      <c r="T60" s="35"/>
+      <c r="U60" s="35"/>
+      <c r="V60" s="35"/>
+      <c r="W60" s="35"/>
+      <c r="X60" s="35"/>
+      <c r="Y60" s="35"/>
+      <c r="Z60" s="35"/>
+      <c r="AA60" s="35"/>
+      <c r="AB60" s="35"/>
     </row>
     <row r="61" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B61" s="76" t="s">
-        <v>233</v>
-      </c>
-      <c r="C61" s="76"/>
-      <c r="D61" s="76"/>
-      <c r="E61" s="76"/>
-      <c r="F61" s="76"/>
-      <c r="G61" s="76"/>
-      <c r="H61" s="76"/>
-      <c r="I61" s="76"/>
-      <c r="J61" s="76"/>
-      <c r="K61" s="76"/>
-      <c r="L61" s="76"/>
-      <c r="M61" s="76"/>
-      <c r="N61" s="76"/>
-      <c r="O61" s="76"/>
-      <c r="P61" s="76"/>
-      <c r="Q61" s="76"/>
-      <c r="R61" s="76"/>
-      <c r="S61" s="76"/>
-      <c r="T61" s="76"/>
-      <c r="U61" s="76"/>
-      <c r="V61" s="76"/>
-      <c r="W61" s="76"/>
-      <c r="X61" s="76"/>
-      <c r="Y61" s="76"/>
-      <c r="Z61" s="76"/>
-      <c r="AA61" s="76"/>
-      <c r="AB61" s="76"/>
+      <c r="B61" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="C61" s="35"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="35"/>
+      <c r="F61" s="35"/>
+      <c r="G61" s="35"/>
+      <c r="H61" s="35"/>
+      <c r="I61" s="35"/>
+      <c r="J61" s="35"/>
+      <c r="K61" s="35"/>
+      <c r="L61" s="35"/>
+      <c r="M61" s="35"/>
+      <c r="N61" s="35"/>
+      <c r="O61" s="35"/>
+      <c r="P61" s="35"/>
+      <c r="Q61" s="35"/>
+      <c r="R61" s="35"/>
+      <c r="S61" s="35"/>
+      <c r="T61" s="35"/>
+      <c r="U61" s="35"/>
+      <c r="V61" s="35"/>
+      <c r="W61" s="35"/>
+      <c r="X61" s="35"/>
+      <c r="Y61" s="35"/>
+      <c r="Z61" s="35"/>
+      <c r="AA61" s="35"/>
+      <c r="AB61" s="35"/>
     </row>
     <row r="62" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B62" s="76" t="s">
-        <v>234</v>
-      </c>
-      <c r="C62" s="76"/>
-      <c r="D62" s="76"/>
-      <c r="E62" s="76"/>
-      <c r="F62" s="76"/>
-      <c r="G62" s="76"/>
-      <c r="H62" s="76"/>
-      <c r="I62" s="76"/>
-      <c r="J62" s="76"/>
-      <c r="K62" s="76"/>
-      <c r="L62" s="76"/>
-      <c r="M62" s="76"/>
-      <c r="N62" s="76"/>
-      <c r="O62" s="76"/>
-      <c r="P62" s="76"/>
-      <c r="Q62" s="76"/>
-      <c r="R62" s="76"/>
-      <c r="S62" s="76"/>
-      <c r="T62" s="76"/>
-      <c r="U62" s="76"/>
-      <c r="V62" s="76"/>
-      <c r="W62" s="76"/>
-      <c r="X62" s="76"/>
-      <c r="Y62" s="76"/>
-      <c r="Z62" s="76"/>
-      <c r="AA62" s="76"/>
-      <c r="AB62" s="76"/>
+      <c r="B62" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="C62" s="35"/>
+      <c r="D62" s="35"/>
+      <c r="E62" s="35"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="35"/>
+      <c r="I62" s="35"/>
+      <c r="J62" s="35"/>
+      <c r="K62" s="35"/>
+      <c r="L62" s="35"/>
+      <c r="M62" s="35"/>
+      <c r="N62" s="35"/>
+      <c r="O62" s="35"/>
+      <c r="P62" s="35"/>
+      <c r="Q62" s="35"/>
+      <c r="R62" s="35"/>
+      <c r="S62" s="35"/>
+      <c r="T62" s="35"/>
+      <c r="U62" s="35"/>
+      <c r="V62" s="35"/>
+      <c r="W62" s="35"/>
+      <c r="X62" s="35"/>
+      <c r="Y62" s="35"/>
+      <c r="Z62" s="35"/>
+      <c r="AA62" s="35"/>
+      <c r="AB62" s="35"/>
     </row>
     <row r="63" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B63" s="76" t="s">
-        <v>235</v>
-      </c>
-      <c r="C63" s="76"/>
-      <c r="D63" s="76"/>
-      <c r="E63" s="76"/>
-      <c r="F63" s="76"/>
-      <c r="G63" s="76"/>
-      <c r="H63" s="76"/>
-      <c r="I63" s="76"/>
-      <c r="J63" s="76"/>
-      <c r="K63" s="76"/>
-      <c r="L63" s="76"/>
-      <c r="M63" s="76"/>
-      <c r="N63" s="76"/>
-      <c r="O63" s="76"/>
-      <c r="P63" s="76"/>
-      <c r="Q63" s="76"/>
-      <c r="R63" s="76"/>
-      <c r="S63" s="76"/>
-      <c r="T63" s="76"/>
-      <c r="U63" s="76"/>
-      <c r="V63" s="76"/>
-      <c r="W63" s="76"/>
-      <c r="X63" s="76"/>
-      <c r="Y63" s="76"/>
-      <c r="Z63" s="76"/>
-      <c r="AA63" s="76"/>
-      <c r="AB63" s="76"/>
+      <c r="B63" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="C63" s="35"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="35"/>
+      <c r="I63" s="35"/>
+      <c r="J63" s="35"/>
+      <c r="K63" s="35"/>
+      <c r="L63" s="35"/>
+      <c r="M63" s="35"/>
+      <c r="N63" s="35"/>
+      <c r="O63" s="35"/>
+      <c r="P63" s="35"/>
+      <c r="Q63" s="35"/>
+      <c r="R63" s="35"/>
+      <c r="S63" s="35"/>
+      <c r="T63" s="35"/>
+      <c r="U63" s="35"/>
+      <c r="V63" s="35"/>
+      <c r="W63" s="35"/>
+      <c r="X63" s="35"/>
+      <c r="Y63" s="35"/>
+      <c r="Z63" s="35"/>
+      <c r="AA63" s="35"/>
+      <c r="AB63" s="35"/>
     </row>
     <row r="64" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B64" s="76" t="s">
-        <v>236</v>
-      </c>
-      <c r="C64" s="76"/>
-      <c r="D64" s="76"/>
-      <c r="E64" s="76"/>
-      <c r="F64" s="76"/>
-      <c r="G64" s="76"/>
-      <c r="H64" s="76"/>
-      <c r="I64" s="76"/>
-      <c r="J64" s="76"/>
-      <c r="K64" s="76"/>
-      <c r="L64" s="76"/>
-      <c r="M64" s="76"/>
-      <c r="N64" s="76"/>
-      <c r="O64" s="76"/>
-      <c r="P64" s="76"/>
-      <c r="Q64" s="76"/>
-      <c r="R64" s="76"/>
-      <c r="S64" s="76"/>
-      <c r="T64" s="76"/>
-      <c r="U64" s="76"/>
-      <c r="V64" s="76"/>
-      <c r="W64" s="76"/>
-      <c r="X64" s="76"/>
-      <c r="Y64" s="76"/>
-      <c r="Z64" s="76"/>
-      <c r="AA64" s="76"/>
-      <c r="AB64" s="76"/>
+      <c r="B64" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="C64" s="35"/>
+      <c r="D64" s="35"/>
+      <c r="E64" s="35"/>
+      <c r="F64" s="35"/>
+      <c r="G64" s="35"/>
+      <c r="H64" s="35"/>
+      <c r="I64" s="35"/>
+      <c r="J64" s="35"/>
+      <c r="K64" s="35"/>
+      <c r="L64" s="35"/>
+      <c r="M64" s="35"/>
+      <c r="N64" s="35"/>
+      <c r="O64" s="35"/>
+      <c r="P64" s="35"/>
+      <c r="Q64" s="35"/>
+      <c r="R64" s="35"/>
+      <c r="S64" s="35"/>
+      <c r="T64" s="35"/>
+      <c r="U64" s="35"/>
+      <c r="V64" s="35"/>
+      <c r="W64" s="35"/>
+      <c r="X64" s="35"/>
+      <c r="Y64" s="35"/>
+      <c r="Z64" s="35"/>
+      <c r="AA64" s="35"/>
+      <c r="AB64" s="35"/>
     </row>
     <row r="65" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B65" s="76" t="s">
-        <v>237</v>
-      </c>
-      <c r="C65" s="76"/>
-      <c r="D65" s="76"/>
-      <c r="E65" s="76"/>
-      <c r="F65" s="76"/>
-      <c r="G65" s="76"/>
-      <c r="H65" s="76"/>
-      <c r="I65" s="76"/>
-      <c r="J65" s="76"/>
-      <c r="K65" s="76"/>
-      <c r="L65" s="76"/>
-      <c r="M65" s="76"/>
-      <c r="N65" s="76"/>
-      <c r="O65" s="76"/>
-      <c r="P65" s="76"/>
-      <c r="Q65" s="76"/>
-      <c r="R65" s="76"/>
-      <c r="S65" s="76"/>
-      <c r="T65" s="76"/>
-      <c r="U65" s="76"/>
-      <c r="V65" s="76"/>
-      <c r="W65" s="76"/>
-      <c r="X65" s="76"/>
-      <c r="Y65" s="76"/>
-      <c r="Z65" s="76"/>
-      <c r="AA65" s="76"/>
-      <c r="AB65" s="76"/>
+      <c r="B65" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="C65" s="35"/>
+      <c r="D65" s="35"/>
+      <c r="E65" s="35"/>
+      <c r="F65" s="35"/>
+      <c r="G65" s="35"/>
+      <c r="H65" s="35"/>
+      <c r="I65" s="35"/>
+      <c r="J65" s="35"/>
+      <c r="K65" s="35"/>
+      <c r="L65" s="35"/>
+      <c r="M65" s="35"/>
+      <c r="N65" s="35"/>
+      <c r="O65" s="35"/>
+      <c r="P65" s="35"/>
+      <c r="Q65" s="35"/>
+      <c r="R65" s="35"/>
+      <c r="S65" s="35"/>
+      <c r="T65" s="35"/>
+      <c r="U65" s="35"/>
+      <c r="V65" s="35"/>
+      <c r="W65" s="35"/>
+      <c r="X65" s="35"/>
+      <c r="Y65" s="35"/>
+      <c r="Z65" s="35"/>
+      <c r="AA65" s="35"/>
+      <c r="AB65" s="35"/>
     </row>
     <row r="66" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B66" s="76" t="s">
-        <v>238</v>
-      </c>
-      <c r="C66" s="76"/>
-      <c r="D66" s="76"/>
-      <c r="E66" s="76"/>
-      <c r="F66" s="76"/>
-      <c r="G66" s="76"/>
-      <c r="H66" s="76"/>
-      <c r="I66" s="76"/>
-      <c r="J66" s="76"/>
-      <c r="K66" s="76"/>
-      <c r="L66" s="76"/>
-      <c r="M66" s="76"/>
-      <c r="N66" s="76"/>
-      <c r="O66" s="76"/>
-      <c r="P66" s="76"/>
-      <c r="Q66" s="76"/>
-      <c r="R66" s="76"/>
-      <c r="S66" s="76"/>
-      <c r="T66" s="76"/>
-      <c r="U66" s="76"/>
-      <c r="V66" s="76"/>
-      <c r="W66" s="76"/>
-      <c r="X66" s="76"/>
-      <c r="Y66" s="76"/>
-      <c r="Z66" s="76"/>
-      <c r="AA66" s="76"/>
-      <c r="AB66" s="76"/>
-    </row>
-    <row r="67" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B67" s="76" t="s">
+      <c r="B66" s="35" t="s">
         <v>239</v>
       </c>
-      <c r="C67" s="76"/>
-      <c r="D67" s="76"/>
-      <c r="E67" s="76"/>
-      <c r="F67" s="76"/>
-      <c r="G67" s="76"/>
-      <c r="H67" s="76"/>
-      <c r="I67" s="76"/>
-      <c r="J67" s="76"/>
-      <c r="K67" s="76"/>
-      <c r="L67" s="76"/>
-      <c r="M67" s="76"/>
-      <c r="N67" s="76"/>
-      <c r="O67" s="76"/>
-      <c r="P67" s="76"/>
-      <c r="Q67" s="76"/>
-      <c r="R67" s="76"/>
-      <c r="S67" s="76"/>
-      <c r="T67" s="76"/>
-      <c r="U67" s="76"/>
-      <c r="V67" s="76"/>
-      <c r="W67" s="76"/>
-      <c r="X67" s="76"/>
-      <c r="Y67" s="76"/>
-      <c r="Z67" s="76"/>
-      <c r="AA67" s="76"/>
-      <c r="AB67" s="76"/>
+      <c r="C66" s="35"/>
+      <c r="D66" s="35"/>
+      <c r="E66" s="35"/>
+      <c r="F66" s="35"/>
+      <c r="G66" s="35"/>
+      <c r="H66" s="35"/>
+      <c r="I66" s="35"/>
+      <c r="J66" s="35"/>
+      <c r="K66" s="35"/>
+      <c r="L66" s="35"/>
+      <c r="M66" s="35"/>
+      <c r="N66" s="35"/>
+      <c r="O66" s="35"/>
+      <c r="P66" s="35"/>
+      <c r="Q66" s="35"/>
+      <c r="R66" s="35"/>
+      <c r="S66" s="35"/>
+      <c r="T66" s="35"/>
+      <c r="U66" s="35"/>
+      <c r="V66" s="35"/>
+      <c r="W66" s="35"/>
+      <c r="X66" s="35"/>
+      <c r="Y66" s="35"/>
+      <c r="Z66" s="35"/>
+      <c r="AA66" s="35"/>
+      <c r="AB66" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="B66:AB66"/>
+    <mergeCell ref="B51:AB51"/>
+    <mergeCell ref="B52:AB52"/>
+    <mergeCell ref="B57:AB57"/>
+    <mergeCell ref="B58:AB58"/>
+    <mergeCell ref="B59:AB59"/>
+    <mergeCell ref="B60:AB60"/>
+    <mergeCell ref="B61:AB61"/>
     <mergeCell ref="B62:AB62"/>
     <mergeCell ref="B63:AB63"/>
     <mergeCell ref="B64:AB64"/>
     <mergeCell ref="B65:AB65"/>
-    <mergeCell ref="B66:AB66"/>
-    <mergeCell ref="B67:AB67"/>
-    <mergeCell ref="B52:AB52"/>
-    <mergeCell ref="B53:AB53"/>
-    <mergeCell ref="B58:AB58"/>
-    <mergeCell ref="B59:AB59"/>
-    <mergeCell ref="B60:AB60"/>
-    <mergeCell ref="B61:AB61"/>
-    <mergeCell ref="B46:AB46"/>
-    <mergeCell ref="B47:AB47"/>
-    <mergeCell ref="B48:AB48"/>
-    <mergeCell ref="B49:AB49"/>
     <mergeCell ref="B50:AB50"/>
-    <mergeCell ref="B51:AB51"/>
     <mergeCell ref="B39:AB39"/>
+    <mergeCell ref="B40:AB40"/>
     <mergeCell ref="B41:AB41"/>
     <mergeCell ref="B42:AB42"/>
     <mergeCell ref="B43:AB43"/>
     <mergeCell ref="B44:AB44"/>
     <mergeCell ref="B45:AB45"/>
+    <mergeCell ref="B46:AB46"/>
+    <mergeCell ref="B47:AB47"/>
+    <mergeCell ref="B48:AB48"/>
+    <mergeCell ref="B49:AB49"/>
+    <mergeCell ref="B38:AB38"/>
     <mergeCell ref="P24:AB24"/>
     <mergeCell ref="P26:AB26"/>
     <mergeCell ref="B35:AB35"/>
     <mergeCell ref="B36:AB36"/>
     <mergeCell ref="B37:AB37"/>
-    <mergeCell ref="B38:AB38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226ED0FD-6AFE-4068-A0C8-4116B067C007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C8ADE5-33FF-4313-BAB9-D9EEA3D45D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="244">
   <si>
     <t>SIGNOMALY</t>
   </si>
@@ -953,6 +953,1193 @@
   </si>
   <si>
     <r>
+      <t>Puzzle tìm đồ vật cũng sẽ dựa vào câu đố nhưng lần này câu đố sẽ được cấp trực tiếp tại bức tranh, không phải đi tìm như giải đố. Bức tranh có thể giống theo mẫu bên trái.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Có tổng cộng là 2 bức tranh.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Khi puzzle giải đố được kích hoạt: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Người chơi cần </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>tìm ra 2 đồ vật phù hợp nhất với câu đố. Mỗi lượt sẽ là câu đố cho 1 món đồ vật.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Cầm đồ vật chứa câu đố đầu tiên trên tay mang lại bức tranh thứ nhất thì câu đố thứ 2 sẽ mở ra ở bức tranh thứ 2. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Gameplay:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Người chơi sẽ là người tham gia vào một trò chơi sinh tồn giải đố. Người chơi sẽ bị nhốt trong một căn phòng tưởng chừng như bình thường, nhưng theo thời gian, căn phòng bắt đầu xuất hiện những "Tín hiệu (Signal)" bất thường (đồ vật biến đổi, âm thanh lạ, môi trường biến dạng). Nhiệm vụ người chơi là liên tục quan sát, thiết lập mức độ ưu tiên và phát hiện ra những tín hiệu trước khi chúng vào trạng thái báo động. Trò chơi yêu cầu cao về suy luận logic, tìm kiếm vật phẩm tương tác để khắc phục và đưa trạng thái của chúng về mức bình thường và hoàn thành trò chơi.</t>
+    </r>
+  </si>
+  <si>
+    <t>(Reference cơ chế đọc thư. Chỉ cần hiện nền đen và chữ. Có nút tắt)</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Tờ hướng dẫn</t>
+  </si>
+  <si>
+    <t>Dùng để hướng dẫn phương pháp giải đố, cách giải đố.</t>
+  </si>
+  <si>
+    <t>Tên Item</t>
+  </si>
+  <si>
+    <t>Compass</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Coins</t>
+  </si>
+  <si>
+    <t>Flower</t>
+  </si>
+  <si>
+    <t>Ball</t>
+  </si>
+  <si>
+    <t>Statue</t>
+  </si>
+  <si>
+    <t>Mirror</t>
+  </si>
+  <si>
+    <t>Lamp</t>
+  </si>
+  <si>
+    <t>Cup Champion</t>
+  </si>
+  <si>
+    <t>Cup of coffee</t>
+  </si>
+  <si>
+    <t>Table</t>
+  </si>
+  <si>
+    <t>Chair</t>
+  </si>
+  <si>
+    <t>Giấy câu đố</t>
+  </si>
+  <si>
+    <t>Vật phẩm cho câu đố</t>
+  </si>
+  <si>
+    <t>Đồ trang trí</t>
+  </si>
+  <si>
+    <t>V. SCENES</t>
+  </si>
+  <si>
+    <t>Mico (NPC)</t>
+  </si>
+  <si>
+    <t>Tranh Puzzle #1</t>
+  </si>
+  <si>
+    <t>Tranh Puzzle #2</t>
+  </si>
+  <si>
+    <t>Máy điền số</t>
+  </si>
+  <si>
+    <t>Dùng để điền mật mã tìm được</t>
+  </si>
+  <si>
+    <t>Dùng để giải đố</t>
+  </si>
+  <si>
+    <t>Interactable?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cần có Title game, các button như: New Game +, Options, Exit. Và được thiết kế layout tương tự như 2 hình mẫu. Với việc khung lựa chọn + Logo ở bên trái và illustration đại diện nằm bên phải. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Deep background: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#08090D</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">UI Surface: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#111118</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Secondary panels: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#2A2B3D</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inactive / borders: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#3D3E52</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Primary text: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#D4D4E0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Secondary text: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#6B6B7A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Signal Active: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#24FF74</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Main accent / CRT glow</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Warnings / alerts: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#F5A623</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Danger / threat (Anomaly): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#E8263C</t>
+    </r>
+  </si>
+  <si>
+    <t>COLOR PALLETE</t>
+  </si>
+  <si>
+    <t>TYPOGRAPHY</t>
+  </si>
+  <si>
+    <t>Titles · UI headers · Terminal readouts · Game Over screen</t>
+  </si>
+  <si>
+    <t>USE FOR</t>
+  </si>
+  <si>
+    <t>VT323</t>
+  </si>
+  <si>
+    <t>Share Tech Mono</t>
+  </si>
+  <si>
+    <t>HUD labels · Subtitles · Button text · Status indicators</t>
+  </si>
+  <si>
+    <t>IBM Plex Mono</t>
+  </si>
+  <si>
+    <t>Log entries · Descriptions · Tooltips · Small text</t>
+  </si>
+  <si>
+    <t>(IN PREVIEW)</t>
+  </si>
+  <si>
+    <t>Option screen: cần có overall quality (với menu thả xuống để lựa chọn), Audio (on/off), nút back để quay về.</t>
+  </si>
+  <si>
+    <t>2. SCREEN</t>
+  </si>
+  <si>
+    <t>1. MAP (BLOCKOUT)</t>
+  </si>
+  <si>
+    <t>2. PUZZLE (MAIN MECHANICS)</t>
+  </si>
+  <si>
+    <t>1. DESIGN STYLE</t>
+  </si>
+  <si>
+    <t>2.3. IN-GAME</t>
+  </si>
+  <si>
+    <t>- Với mốc A: Tinh chỉnh hex màu tường (sàn, trần) từ màu của texture dần sang màu đỏ thẩm; Saturation: +7%</t>
+  </si>
+  <si>
+    <t>- Với mốc B: Tinh chỉnh hex màu tường (sàn, trần) từ màu của texture càng dần sang màu đỏ thẩm; Saturation: +12%</t>
+  </si>
+  <si>
+    <t>- Với mốc C: Tinh chỉnh hex màu tường (sàn, trần) từ màu của texture thành màu đỏ thẩm; Saturation: +17%</t>
+  </si>
+  <si>
+    <t>2.3.1. Biến đổi môi trường</t>
+  </si>
+  <si>
+    <t>2.3.2. Biến đổi Puzzle</t>
+  </si>
+  <si>
+    <t>Model Puzzle sẽ gồm 2 biến thể (A và B), trong đó: biến thể A là object ở trạng thái bình thường, biến thể B là object ở trạng thái Anomaly.</t>
+  </si>
+  <si>
+    <t>Thiết lập model Puzzle sẽ tự động chuyển A sang B với cooldown là 15-20 giây (random), và duration là 7 giây, sau đó sẽ quay trở lại biến thể A và lặp lại.</t>
+  </si>
+  <si>
+    <t>Khi puzzle giải đố được kích hoạt và người chơi nhấn giữ phím "E" thì sẽ luôn giữ ở dạng biến thể A. Sau khi hoàn thành nhấn giữ sẽ chuyển hoàn toàn sang biến thể B (Optional)</t>
+  </si>
+  <si>
+    <r>
+      <t>Mốc thời gian chính (Timelapse):</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 15 phút</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Chia ra 3 mốc thời gian như sau: A=B=C= 5 phút.</t>
+    </r>
+  </si>
+  <si>
+    <t>2.1. Menu Screen UI</t>
+  </si>
+  <si>
+    <t>2.2. Option Screen UI</t>
+  </si>
+  <si>
+    <t>III. MODULES AND FEATURES</t>
+  </si>
+  <si>
+    <t>IV. DETAILS</t>
+  </si>
+  <si>
+    <t>1. Game Movement</t>
+  </si>
+  <si>
+    <t>VI. GAME FEATURES</t>
+  </si>
+  <si>
+    <t>2. Game Interaction</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Người chơi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>nhấn E để tương tác</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">; Người chơi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>nhấn Q để huỷ bỏ đồ vật đang cầm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> trên tay.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Người chơi sẽ tương tác với vật thể object như sau: Với</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> X là đồ vật trang trí sẽ có object tương tác được và không tương tác được</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Dựa vào Item List); </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Y: luôn cầm được</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (nó sẽ hiển thị icon chìa khoá ở top).</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Blink </t>
+  </si>
+  <si>
+    <t>Khi vừa vào game người chơi sẽ thấy màn hình đang chớp mắt (1-2 lần), từ mờ thành rõ ràng.</t>
+  </si>
+  <si>
+    <t>4. NPC</t>
+  </si>
+  <si>
+    <t>VII. Item lists</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Người chơi sẽ di chuyển bằng phím </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>"WASD"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Tốc độ khi di chuyển của người chơi sẽ nhanh vừa phải. Người chơi</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> không thể chạy, nhảy.</t>
+    </r>
+  </si>
+  <si>
+    <t>Dialogues!A1</t>
+  </si>
+  <si>
+    <t>Đối thoại với NPC để hiểu cơ chế chơi. Đoạn đối thoại có thể xem bên tab</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Khi puzzle giải đố được kích hoạt: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Người chơi cần </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>tìm ra các mảnh bằng chứng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (vật phẩm, giấy) có chứa các đoạn văn và </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>cần giải mã để ra một dãy số (không có văn bản)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Dãy số này sẽ là lời giải cho câu đố và thoả mãn "Điều kiện tổng".</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Ngoài ra sẽ hiện luôn cả #Tờ hướng dẫn, kế bên.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>#Hướng dẫn:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> "This room once belonged to someone. They have departed but they did not take everything with them. They left behind two objects. Each one is hidden behind a message. Find the right one, and only then will you understand who they truly were."</t>
+    </r>
+  </si>
+  <si>
+    <t>Phần Puzzle UI này sẽ nhìn trực diện vào máy bảo mật, và có nút back ra. Khi bấm sai thì nó sẽ hiển thị: "This is incorrect".</t>
+  </si>
+  <si>
+    <t>Phần Puzzle UI này sẽ không cần nhìn vào #tờ hướng dẫn. Mà sẽ hiển thị #hướng dẫn trực tiếp trên màn hình, và có nút back về. Nếu đưa đồ vật không phù hợp, thì sẽ không thể vào Puzzle UI mà sẽ hiển thị chữ: "This item is not correct!".</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Style: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Low-Poly</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Độ phù hợp với theme: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Các sự kiện bất thường trong phòng chính là tín hiệu mà người chơi phải nhận ra. Gameplay xoay quanh việc giải mã và xử lý tín hiệu để sinh tồn. Yếu tố thời gian và sự thay đổi liên tục khiến tín hiệu trở thành cơ chế trung tâm, không chỉ là chi tiết phụ.</t>
+    </r>
+  </si>
+  <si>
+    <t>Item List'!A1</t>
+  </si>
+  <si>
+    <t>Người hướng dẫn</t>
+  </si>
+  <si>
+    <t>VIII. DIALOGUES</t>
+  </si>
+  <si>
+    <t>Sau khi hiển thị Timelapse, nó sẽ luôn ở biến thể B. Và sau khi hoàn thành điều kiện, nó sẽ quay trở lại biến thể A.</t>
+  </si>
+  <si>
+    <t>Nút UI của E sẽ hiển thị ở vị trí của object.</t>
+  </si>
+  <si>
+    <t>INS_GUIDE</t>
+  </si>
+  <si>
+    <t>PZ_COMPASS</t>
+  </si>
+  <si>
+    <t>PZ_KEY</t>
+  </si>
+  <si>
+    <t>PZ_MACHINE</t>
+  </si>
+  <si>
+    <t>PZ_PICTURE1</t>
+  </si>
+  <si>
+    <t>PZ_PICTURE2</t>
+  </si>
+  <si>
+    <t>Y_MERCURY</t>
+  </si>
+  <si>
+    <t>Y_VENUS</t>
+  </si>
+  <si>
+    <t>Y_EARTH</t>
+  </si>
+  <si>
+    <t>Y_MARS</t>
+  </si>
+  <si>
+    <t>Y_JUPITER</t>
+  </si>
+  <si>
+    <t>X_BALL</t>
+  </si>
+  <si>
+    <t>X_FLOWER</t>
+  </si>
+  <si>
+    <t>X_COINS</t>
+  </si>
+  <si>
+    <t>X_MIRROR</t>
+  </si>
+  <si>
+    <t>X_LAMP</t>
+  </si>
+  <si>
+    <t>X_CHAMP</t>
+  </si>
+  <si>
+    <t>X_COFFEE</t>
+  </si>
+  <si>
+    <t>X_TABLE</t>
+  </si>
+  <si>
+    <t>X_CHAIR</t>
+  </si>
+  <si>
+    <t>X_STATUE</t>
+  </si>
+  <si>
+    <t>INS_MICO</t>
+  </si>
+  <si>
+    <t>"An alphabet of twenty-six. But strip away the silent consonants. How many letters hold the true voice of the language?
+Count the vowels."</t>
+  </si>
+  <si>
+    <t>1. Các loại hộp Dialouges (tham khảo)</t>
+  </si>
+  <si>
+    <t>2 loại hộp dialouges phổ biến trong game 3D.</t>
+  </si>
+  <si>
+    <t>Cần hiển thị hộp dialouges như mẫu kế bên.</t>
+  </si>
+  <si>
+    <t>Tinh chỉnh góc quay phù hợp khi bắt đầu cuộc đối thoại với NPC (Optional)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Về phương thức tương tác:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  Ở </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>lần tương tác đầu tiên</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>, người chơi</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> không thể skip, double click</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> chạy hết chữ, hay </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>thoát ra ngoài</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> vào gameplay, mà phải xem hết một đoạn đối thoại, sau đó mới được click để sang đoạn tiếp theo. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Để tiếp tục đoạn đối thoại</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>, người chơi</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> sẽ nhấn chuột trái</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Ở</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> lần tương tác thứ 2,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> người chơi sẽ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">được phép double click </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">để chạy full đoạn đối thoại và nhảy sang đoạn đối thoại tiếp theo, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>được phép thoát ra ngoài</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> khi đang đối thoại. Nút để thoát ra ngoài là </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>"ESCAPE"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Lời đối thoại</t>
+  </si>
+  <si>
+    <t>You’ll become nothing more than entertainment for Them. Hahahaha…</t>
+  </si>
+  <si>
+    <t>***Lưu ý: Mỗi đoạn được viết dưới đây thì đều là từng đoạn sẽ hiển thị ra khi người chơi click chuột sang đoạn kế.</t>
+  </si>
+  <si>
+    <t>2.1. Tương tác lần đầu: hiển thị toàn bộ cuộc trò chuyện</t>
+  </si>
+  <si>
+    <t>***Lưu ý: không thể skip, double click chạy hết chữ, hay thoát ra ngoài vào gameplay.</t>
+  </si>
+  <si>
+    <t>***Lưu ý: lần tương tác thứ 2, người chơi sẽ được phép double click để chạy full đoạn đối thoại và nhảy sang đoạn đối thoại tiếp theo, được phép thoát ra ngoài.</t>
+  </si>
+  <si>
+    <t>Item ID</t>
+  </si>
+  <si>
+    <t>Điều kiện để tương tác với vật thể: Vật thể phải luôn trong tầm nhìn của người chơi; Phạm vi của vật thể phát hiện người chơi. Trong trường hợp có 2 vật thể thì chỉ cho người chơi tương tác với vật thể gần nhất.</t>
+  </si>
+  <si>
+    <t>2.2. Tương tác lần 2 trở đi: chỉ hiển thị chỉ dẫn cần thiết</t>
+  </si>
+  <si>
+    <t>FBX?</t>
+  </si>
+  <si>
+    <t>Chưa có</t>
+  </si>
+  <si>
+    <t>Đang Render</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPC: </t>
+  </si>
+  <si>
+    <t>Heh… another one, huh? Are you really that greedy for money?</t>
+  </si>
+  <si>
+    <t>Well, everything comes at a price.</t>
+  </si>
+  <si>
+    <t>If you want the treasure, you’ll have to play the game just like the contract says.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Win, and you might walk away with that massive fortune. But lose… and we take no responsibility. </t>
+  </si>
+  <si>
+    <t>So… ready to step into hell?</t>
+  </si>
+  <si>
+    <t>Good. Here are the rules of our little game. See that door beside you, ahh the one with the… unusual requirement? That’s your way out. But to unlock it, you’ll need to fulfill two conditions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First, look at the door in front of you. </t>
+  </si>
+  <si>
+    <t>See the timer? Fifteen minutes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That’s all the time you have left to finish the game. </t>
+  </si>
+  <si>
+    <t>Meet the other condition before it hits zero, and the door will open. If not… hahaha.</t>
+  </si>
+  <si>
+    <t>Second, beyond this room lies a space filled with all sorts of objects. Your task is to find the anomalies among them.</t>
+  </si>
+  <si>
+    <t>If you suspect something’s off, stand your ground and face it directly, don’t look away. It will present you with a puzzle. Solve it, and you’ll set it free.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">But don’t get too corky. These anomalies aren’t as forgiving as I am. </t>
+  </si>
+  <si>
+    <t>Each of them has its own timer hovering overhead… and if their time runs out, it’s game over for you too. So keep your eyes sharp.</t>
+  </si>
+  <si>
+    <t>Free them all within the fifteen minutes I’ve given you, and the door will open. Walk through it, and that million-dollar prize is yours.</t>
+  </si>
+  <si>
+    <t>…assuming you can pull it off. Plenty have tried. Plenty have died. Turns out, if you want something valuable, you have to pay a matching price.</t>
+  </si>
+  <si>
+    <t>Good luck? I guess… and perhaps we’ll meet again or not, hahaha…</t>
+  </si>
+  <si>
+    <t>See that door beside you, ahh the one with the… unusual requirement? That’s your way out. But to unlock it, you’ll need to fulfill two conditions.</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Yêu cầu:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Khung đối thoại có </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>màu đen constrast cao</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, độ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>opacity cần là 60%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> để đảm bảo vẫn nhìn rõ môi trường đằng sau. Cần có tên người nói hiển thị ở góc trên đoạn đối thoại (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>tên người nói màu Trắng, brightness thấp hơn đối thoại và viết hoa chữ cái đầu)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Đoạn đối thoại </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>cần viết thường, và chỉ viết hoa chữ cái đầu sau dấu chấm (đoạn đối thoại màu trắng, với brightness cao hơn tên)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Cần có icon chuột chớp nháy để người chơi biết hết đoạn đối thoại và qua phần kế.</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">- </t>
     </r>
     <r>
@@ -1101,7 +2288,27 @@
       </rPr>
       <t xml:space="preserve">Timelapse nhỏ sẽ xuất hiện và bắt đầu tính thời gian.
 - Chỉ được kích hoạt 1 puzzle 1 lần. Khi puzzle đầu tiên hoàn thành thì có thể thực hiện puzzle thứ 2.
-***Lưu ý: </t>
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Puzzle UI cần được hiển thị: Title, mô tả câu đố. Trong đó các text được xếp middle với nhau.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">***Lưu ý: </t>
     </r>
     <r>
       <rPr>
@@ -1150,1190 +2357,6 @@
       </rPr>
       <t xml:space="preserve"> ngay lập tức.</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>Puzzle tìm đồ vật cũng sẽ dựa vào câu đố nhưng lần này câu đố sẽ được cấp trực tiếp tại bức tranh, không phải đi tìm như giải đố. Bức tranh có thể giống theo mẫu bên trái.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Có tổng cộng là 2 bức tranh.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Khi puzzle giải đố được kích hoạt: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Người chơi cần </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>tìm ra 2 đồ vật phù hợp nhất với câu đố. Mỗi lượt sẽ là câu đố cho 1 món đồ vật.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Cầm đồ vật chứa câu đố đầu tiên trên tay mang lại bức tranh thứ nhất thì câu đố thứ 2 sẽ mở ra ở bức tranh thứ 2. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Gameplay:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Người chơi sẽ là người tham gia vào một trò chơi sinh tồn giải đố. Người chơi sẽ bị nhốt trong một căn phòng tưởng chừng như bình thường, nhưng theo thời gian, căn phòng bắt đầu xuất hiện những "Tín hiệu (Signal)" bất thường (đồ vật biến đổi, âm thanh lạ, môi trường biến dạng). Nhiệm vụ người chơi là liên tục quan sát, thiết lập mức độ ưu tiên và phát hiện ra những tín hiệu trước khi chúng vào trạng thái báo động. Trò chơi yêu cầu cao về suy luận logic, tìm kiếm vật phẩm tương tác để khắc phục và đưa trạng thái của chúng về mức bình thường và hoàn thành trò chơi.</t>
-    </r>
-  </si>
-  <si>
-    <t>(Reference cơ chế đọc thư. Chỉ cần hiện nền đen và chữ. Có nút tắt)</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Tờ hướng dẫn</t>
-  </si>
-  <si>
-    <t>Dùng để hướng dẫn phương pháp giải đố, cách giải đố.</t>
-  </si>
-  <si>
-    <t>Tên Item</t>
-  </si>
-  <si>
-    <t>Compass</t>
-  </si>
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Coins</t>
-  </si>
-  <si>
-    <t>Flower</t>
-  </si>
-  <si>
-    <t>Ball</t>
-  </si>
-  <si>
-    <t>Statue</t>
-  </si>
-  <si>
-    <t>Mirror</t>
-  </si>
-  <si>
-    <t>Lamp</t>
-  </si>
-  <si>
-    <t>Cup Champion</t>
-  </si>
-  <si>
-    <t>Cup of coffee</t>
-  </si>
-  <si>
-    <t>Table</t>
-  </si>
-  <si>
-    <t>Chair</t>
-  </si>
-  <si>
-    <t>Giấy câu đố</t>
-  </si>
-  <si>
-    <t>Vật phẩm cho câu đố</t>
-  </si>
-  <si>
-    <t>Đồ trang trí</t>
-  </si>
-  <si>
-    <t>V. SCENES</t>
-  </si>
-  <si>
-    <t>Mico (NPC)</t>
-  </si>
-  <si>
-    <t>Tranh Puzzle #1</t>
-  </si>
-  <si>
-    <t>Tranh Puzzle #2</t>
-  </si>
-  <si>
-    <t>Máy điền số</t>
-  </si>
-  <si>
-    <t>Dùng để điền mật mã tìm được</t>
-  </si>
-  <si>
-    <t>Dùng để giải đố</t>
-  </si>
-  <si>
-    <t>Interactable?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cần có Title game, các button như: New Game +, Options, Exit. Và được thiết kế layout tương tự như 2 hình mẫu. Với việc khung lựa chọn + Logo ở bên trái và illustration đại diện nằm bên phải. </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Deep background: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>#08090D</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">UI Surface: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>#111118</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Secondary panels: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>#2A2B3D</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inactive / borders: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>#3D3E52</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Primary text: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>#D4D4E0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Secondary text: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>#6B6B7A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Signal Active: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>#24FF74</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Main accent / CRT glow</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Warnings / alerts: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>#F5A623</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Danger / threat (Anomaly): </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>#E8263C</t>
-    </r>
-  </si>
-  <si>
-    <t>COLOR PALLETE</t>
-  </si>
-  <si>
-    <t>TYPOGRAPHY</t>
-  </si>
-  <si>
-    <t>Titles · UI headers · Terminal readouts · Game Over screen</t>
-  </si>
-  <si>
-    <t>USE FOR</t>
-  </si>
-  <si>
-    <t>VT323</t>
-  </si>
-  <si>
-    <t>Share Tech Mono</t>
-  </si>
-  <si>
-    <t>HUD labels · Subtitles · Button text · Status indicators</t>
-  </si>
-  <si>
-    <t>IBM Plex Mono</t>
-  </si>
-  <si>
-    <t>Log entries · Descriptions · Tooltips · Small text</t>
-  </si>
-  <si>
-    <t>(IN PREVIEW)</t>
-  </si>
-  <si>
-    <t>Option screen: cần có overall quality (với menu thả xuống để lựa chọn), Audio (on/off), nút back để quay về.</t>
-  </si>
-  <si>
-    <t>2. SCREEN</t>
-  </si>
-  <si>
-    <t>1. MAP (BLOCKOUT)</t>
-  </si>
-  <si>
-    <t>2. PUZZLE (MAIN MECHANICS)</t>
-  </si>
-  <si>
-    <t>1. DESIGN STYLE</t>
-  </si>
-  <si>
-    <t>2.3. IN-GAME</t>
-  </si>
-  <si>
-    <t>- Với mốc A: Tinh chỉnh hex màu tường (sàn, trần) từ màu của texture dần sang màu đỏ thẩm; Saturation: +7%</t>
-  </si>
-  <si>
-    <t>- Với mốc B: Tinh chỉnh hex màu tường (sàn, trần) từ màu của texture càng dần sang màu đỏ thẩm; Saturation: +12%</t>
-  </si>
-  <si>
-    <t>- Với mốc C: Tinh chỉnh hex màu tường (sàn, trần) từ màu của texture thành màu đỏ thẩm; Saturation: +17%</t>
-  </si>
-  <si>
-    <t>2.3.1. Biến đổi môi trường</t>
-  </si>
-  <si>
-    <t>2.3.2. Biến đổi Puzzle</t>
-  </si>
-  <si>
-    <t>Model Puzzle sẽ gồm 2 biến thể (A và B), trong đó: biến thể A là object ở trạng thái bình thường, biến thể B là object ở trạng thái Anomaly.</t>
-  </si>
-  <si>
-    <t>Thiết lập model Puzzle sẽ tự động chuyển A sang B với cooldown là 15-20 giây (random), và duration là 7 giây, sau đó sẽ quay trở lại biến thể A và lặp lại.</t>
-  </si>
-  <si>
-    <t>Khi puzzle giải đố được kích hoạt và người chơi nhấn giữ phím "E" thì sẽ luôn giữ ở dạng biến thể A. Sau khi hoàn thành nhấn giữ sẽ chuyển hoàn toàn sang biến thể B (Optional)</t>
-  </si>
-  <si>
-    <r>
-      <t>Mốc thời gian chính (Timelapse):</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 15 phút</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Chia ra 3 mốc thời gian như sau: A=B=C= 5 phút.</t>
-    </r>
-  </si>
-  <si>
-    <t>2.1. Menu Screen UI</t>
-  </si>
-  <si>
-    <t>2.2. Option Screen UI</t>
-  </si>
-  <si>
-    <t>III. MODULES AND FEATURES</t>
-  </si>
-  <si>
-    <t>IV. DETAILS</t>
-  </si>
-  <si>
-    <t>1. Game Movement</t>
-  </si>
-  <si>
-    <t>VI. GAME FEATURES</t>
-  </si>
-  <si>
-    <t>2. Game Interaction</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Người chơi </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>nhấn E để tương tác</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">; Người chơi </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>nhấn Q để huỷ bỏ đồ vật đang cầm</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> trên tay.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Người chơi sẽ tương tác với vật thể object như sau: Với</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> X là đồ vật trang trí sẽ có object tương tác được và không tương tác được</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Dựa vào Item List); </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Y: luôn cầm được</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (nó sẽ hiển thị icon chìa khoá ở top).</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Blink </t>
-  </si>
-  <si>
-    <t>Khi vừa vào game người chơi sẽ thấy màn hình đang chớp mắt (1-2 lần), từ mờ thành rõ ràng.</t>
-  </si>
-  <si>
-    <t>4. NPC</t>
-  </si>
-  <si>
-    <t>VII. Item lists</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Người chơi sẽ di chuyển bằng phím </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>"WASD"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Tốc độ khi di chuyển của người chơi sẽ nhanh vừa phải. Người chơi</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> không thể chạy, nhảy.</t>
-    </r>
-  </si>
-  <si>
-    <t>Dialogues!A1</t>
-  </si>
-  <si>
-    <t>Đối thoại với NPC để hiểu cơ chế chơi. Đoạn đối thoại có thể xem bên tab</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Khi puzzle giải đố được kích hoạt: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Người chơi cần </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>tìm ra các mảnh bằng chứng</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (vật phẩm, giấy) có chứa các đoạn văn và </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>cần giải mã để ra một dãy số (không có văn bản)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Dãy số này sẽ là lời giải cho câu đố và thoả mãn "Điều kiện tổng".</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Ngoài ra sẽ hiện luôn cả #Tờ hướng dẫn, kế bên.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>#Hướng dẫn:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> "This room once belonged to someone. They have departed but they did not take everything with them. They left behind two objects. Each one is hidden behind a message. Find the right one, and only then will you understand who they truly were."</t>
-    </r>
-  </si>
-  <si>
-    <t>Phần Puzzle UI này sẽ nhìn trực diện vào máy bảo mật, và có nút back ra. Khi bấm sai thì nó sẽ hiển thị: "This is incorrect".</t>
-  </si>
-  <si>
-    <t>Phần Puzzle UI này sẽ không cần nhìn vào #tờ hướng dẫn. Mà sẽ hiển thị #hướng dẫn trực tiếp trên màn hình, và có nút back về. Nếu đưa đồ vật không phù hợp, thì sẽ không thể vào Puzzle UI mà sẽ hiển thị chữ: "This item is not correct!".</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Style: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Low-Poly</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Độ phù hợp với theme: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Các sự kiện bất thường trong phòng chính là tín hiệu mà người chơi phải nhận ra. Gameplay xoay quanh việc giải mã và xử lý tín hiệu để sinh tồn. Yếu tố thời gian và sự thay đổi liên tục khiến tín hiệu trở thành cơ chế trung tâm, không chỉ là chi tiết phụ.</t>
-    </r>
-  </si>
-  <si>
-    <t>Item List'!A1</t>
-  </si>
-  <si>
-    <t>Người hướng dẫn</t>
-  </si>
-  <si>
-    <t>VIII. DIALOGUES</t>
-  </si>
-  <si>
-    <t>Sau khi hiển thị Timelapse, nó sẽ luôn ở biến thể B. Và sau khi hoàn thành điều kiện, nó sẽ quay trở lại biến thể A.</t>
-  </si>
-  <si>
-    <t>Nút UI của E sẽ hiển thị ở vị trí của object.</t>
-  </si>
-  <si>
-    <t>INS_GUIDE</t>
-  </si>
-  <si>
-    <t>PZ_COMPASS</t>
-  </si>
-  <si>
-    <t>PZ_KEY</t>
-  </si>
-  <si>
-    <t>PZ_MACHINE</t>
-  </si>
-  <si>
-    <t>PZ_PICTURE1</t>
-  </si>
-  <si>
-    <t>PZ_PICTURE2</t>
-  </si>
-  <si>
-    <t>Y_MERCURY</t>
-  </si>
-  <si>
-    <t>Y_VENUS</t>
-  </si>
-  <si>
-    <t>Y_EARTH</t>
-  </si>
-  <si>
-    <t>Y_MARS</t>
-  </si>
-  <si>
-    <t>Y_JUPITER</t>
-  </si>
-  <si>
-    <t>X_BALL</t>
-  </si>
-  <si>
-    <t>X_FLOWER</t>
-  </si>
-  <si>
-    <t>X_COINS</t>
-  </si>
-  <si>
-    <t>X_MIRROR</t>
-  </si>
-  <si>
-    <t>X_LAMP</t>
-  </si>
-  <si>
-    <t>X_CHAMP</t>
-  </si>
-  <si>
-    <t>X_COFFEE</t>
-  </si>
-  <si>
-    <t>X_TABLE</t>
-  </si>
-  <si>
-    <t>X_CHAIR</t>
-  </si>
-  <si>
-    <t>X_STATUE</t>
-  </si>
-  <si>
-    <t>INS_MICO</t>
-  </si>
-  <si>
-    <t>"An alphabet of twenty-six. But strip away the silent consonants. How many letters hold the true voice of the language?
-Count the vowels."</t>
-  </si>
-  <si>
-    <t>1. Các loại hộp Dialouges (tham khảo)</t>
-  </si>
-  <si>
-    <t>2 loại hộp dialouges phổ biến trong game 3D.</t>
-  </si>
-  <si>
-    <t>Cần hiển thị hộp dialouges như mẫu kế bên.</t>
-  </si>
-  <si>
-    <t>Tinh chỉnh góc quay phù hợp khi bắt đầu cuộc đối thoại với NPC (Optional)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Về phương thức tương tác:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  Ở </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>lần tương tác đầu tiên</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, người chơi</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> không thể skip, double click</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> chạy hết chữ, hay </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>thoát ra ngoài</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> vào gameplay, mà phải xem hết một đoạn đối thoại, sau đó mới được click để sang đoạn tiếp theo. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Để tiếp tục đoạn đối thoại</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, người chơi</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> sẽ nhấn chuột trái</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Ở</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> lần tương tác thứ 2,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> người chơi sẽ </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">được phép double click </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">để chạy full đoạn đối thoại và nhảy sang đoạn đối thoại tiếp theo, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>được phép thoát ra ngoài</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> khi đang đối thoại. Nút để thoát ra ngoài là </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>"ESCAPE"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Yêu cầu:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Khung đối thoại có </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>màu đen constrast cao</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, độ </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>opacity cần là 60%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> để đảm bảo vẫn nhìn rõ môi trường đằng sau. Cần có tên người nói hiển thị ở góc trên đoạn đối thoại (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>tên người nói màu Trắng, brightness thấp hơn đối thoại và viết hoa chữ cái đầu)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. Đoạn đối thoại </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>cần viết thường, và chỉ viết hoa chữ cái đầu sau dấu chấm (đoạn đối thoại màu trắng, với brightness cao hơn tên)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>2. Lời đối thoại</t>
-  </si>
-  <si>
-    <t>You’ll become nothing more than entertainment for Them. Hahahaha…</t>
-  </si>
-  <si>
-    <t>***Lưu ý: Mỗi đoạn được viết dưới đây thì đều là từng đoạn sẽ hiển thị ra khi người chơi click chuột sang đoạn kế.</t>
-  </si>
-  <si>
-    <t>2.1. Tương tác lần đầu: hiển thị toàn bộ cuộc trò chuyện</t>
-  </si>
-  <si>
-    <t>***Lưu ý: không thể skip, double click chạy hết chữ, hay thoát ra ngoài vào gameplay.</t>
-  </si>
-  <si>
-    <t>***Lưu ý: lần tương tác thứ 2, người chơi sẽ được phép double click để chạy full đoạn đối thoại và nhảy sang đoạn đối thoại tiếp theo, được phép thoát ra ngoài.</t>
-  </si>
-  <si>
-    <t>Item ID</t>
-  </si>
-  <si>
-    <t>Điều kiện để tương tác với vật thể: Vật thể phải luôn trong tầm nhìn của người chơi; Phạm vi của vật thể phát hiện người chơi. Trong trường hợp có 2 vật thể thì chỉ cho người chơi tương tác với vật thể gần nhất.</t>
-  </si>
-  <si>
-    <t>2.2. Tương tác lần 2 trở đi: chỉ hiển thị chỉ dẫn cần thiết</t>
-  </si>
-  <si>
-    <t>FBX?</t>
-  </si>
-  <si>
-    <t>Chưa có</t>
-  </si>
-  <si>
-    <t>Đang Render</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPC: </t>
-  </si>
-  <si>
-    <t>Heh… another one, huh? Are you really that greedy for money?</t>
-  </si>
-  <si>
-    <t>Well, everything comes at a price.</t>
-  </si>
-  <si>
-    <t>If you want the treasure, you’ll have to play the game just like the contract says.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Win, and you might walk away with that massive fortune. But lose… and we take no responsibility. </t>
-  </si>
-  <si>
-    <t>So… ready to step into hell?</t>
-  </si>
-  <si>
-    <t>Good. Here are the rules of our little game. See that door beside you, ahh the one with the… unusual requirement? That’s your way out. But to unlock it, you’ll need to fulfill two conditions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First, look at the door in front of you. </t>
-  </si>
-  <si>
-    <t>See the timer? Fifteen minutes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">That’s all the time you have left to finish the game. </t>
-  </si>
-  <si>
-    <t>Meet the other condition before it hits zero, and the door will open. If not… hahaha.</t>
-  </si>
-  <si>
-    <t>Second, beyond this room lies a space filled with all sorts of objects. Your task is to find the anomalies among them.</t>
-  </si>
-  <si>
-    <t>If you suspect something’s off, stand your ground and face it directly, don’t look away. It will present you with a puzzle. Solve it, and you’ll set it free.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">But don’t get too corky. These anomalies aren’t as forgiving as I am. </t>
-  </si>
-  <si>
-    <t>Each of them has its own timer hovering overhead… and if their time runs out, it’s game over for you too. So keep your eyes sharp.</t>
-  </si>
-  <si>
-    <t>Free them all within the fifteen minutes I’ve given you, and the door will open. Walk through it, and that million-dollar prize is yours.</t>
-  </si>
-  <si>
-    <t>…assuming you can pull it off. Plenty have tried. Plenty have died. Turns out, if you want something valuable, you have to pay a matching price.</t>
-  </si>
-  <si>
-    <t>Good luck? I guess… and perhaps we’ll meet again or not, hahaha…</t>
-  </si>
-  <si>
-    <t>See that door beside you, ahh the one with the… unusual requirement? That’s your way out. But to unlock it, you’ll need to fulfill two conditions.</t>
   </si>
 </sst>
 </file>
@@ -2571,7 +2594,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2721,9 +2744,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2810,6 +2830,18 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3837,8 +3869,8 @@
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>6457</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>1301857</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4301,7 +4333,7 @@
     </row>
     <row r="12" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B12" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C12" s="42"/>
       <c r="D12" s="42"/>
@@ -4375,7 +4407,7 @@
     </row>
     <row r="16" spans="1:26" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C16" s="38"/>
       <c r="D16" s="38"/>
@@ -4476,7 +4508,7 @@
     </row>
     <row r="20" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="43"/>
@@ -4636,7 +4668,7 @@
   <sheetData>
     <row r="2" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B2" s="8"/>
     </row>
@@ -5061,12 +5093,12 @@
   <sheetData>
     <row r="2" spans="1:28" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5160,42 +5192,42 @@
     </row>
     <row r="15" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B15" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B16" s="8"/>
     </row>
-    <row r="17" spans="2:28" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="61" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
-      <c r="L17" s="62"/>
-      <c r="M17" s="62"/>
-      <c r="N17" s="62"/>
-      <c r="O17" s="62"/>
-      <c r="P17" s="62"/>
-      <c r="Q17" s="62"/>
-      <c r="R17" s="62"/>
-      <c r="S17" s="62"/>
-      <c r="T17" s="62"/>
-      <c r="U17" s="62"/>
-      <c r="V17" s="62"/>
-      <c r="W17" s="62"/>
-      <c r="X17" s="62"/>
-      <c r="Y17" s="62"/>
-      <c r="Z17" s="62"/>
-      <c r="AA17" s="62"/>
-      <c r="AB17" s="62"/>
+    <row r="17" spans="2:28" ht="138" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="93" t="s">
+        <v>243</v>
+      </c>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="61"/>
+      <c r="M17" s="61"/>
+      <c r="N17" s="61"/>
+      <c r="O17" s="61"/>
+      <c r="P17" s="61"/>
+      <c r="Q17" s="61"/>
+      <c r="R17" s="61"/>
+      <c r="S17" s="61"/>
+      <c r="T17" s="61"/>
+      <c r="U17" s="61"/>
+      <c r="V17" s="61"/>
+      <c r="W17" s="61"/>
+      <c r="X17" s="61"/>
+      <c r="Y17" s="61"/>
+      <c r="Z17" s="61"/>
+      <c r="AA17" s="61"/>
+      <c r="AB17" s="61"/>
     </row>
     <row r="18" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="15"/>
@@ -5251,7 +5283,7 @@
     </row>
     <row r="24" spans="2:28" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P24" s="56" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q24" s="60"/>
       <c r="R24" s="60"/>
@@ -5283,7 +5315,7 @@
     </row>
     <row r="26" spans="2:28" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P26" s="56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q26" s="56"/>
       <c r="R26" s="56"/>
@@ -5391,21 +5423,21 @@
       <c r="AB36" s="39"/>
     </row>
     <row r="38" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B38" s="65" t="s">
+      <c r="B38" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="65"/>
-      <c r="D38" s="65"/>
-      <c r="E38" s="65"/>
-      <c r="F38" s="65"/>
-      <c r="G38" s="65"/>
-      <c r="H38" s="65"/>
-      <c r="I38" s="65"/>
-      <c r="J38" s="65"/>
-      <c r="K38" s="65"/>
-      <c r="L38" s="65"/>
-      <c r="M38" s="65"/>
-      <c r="N38" s="65"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="64"/>
+      <c r="E38" s="64"/>
+      <c r="F38" s="64"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="64"/>
+      <c r="J38" s="64"/>
+      <c r="K38" s="64"/>
+      <c r="L38" s="64"/>
+      <c r="M38" s="64"/>
+      <c r="N38" s="64"/>
       <c r="P38" s="8" t="s">
         <v>57</v>
       </c>
@@ -5424,7 +5456,7 @@
     </row>
     <row r="39" spans="2:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P39" s="35" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q39" s="35"/>
       <c r="R39" s="35"/>
@@ -5502,20 +5534,20 @@
       </c>
     </row>
     <row r="47" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B47" s="66" t="s">
-        <v>90</v>
-      </c>
-      <c r="C47" s="66"/>
-      <c r="D47" s="66"/>
-      <c r="E47" s="66"/>
-      <c r="F47" s="66"/>
-      <c r="G47" s="66"/>
-      <c r="H47" s="66"/>
-      <c r="I47" s="66"/>
-      <c r="J47" s="66"/>
-      <c r="K47" s="66"/>
-      <c r="L47" s="66"/>
-      <c r="M47" s="66"/>
+      <c r="B47" s="65" t="s">
+        <v>89</v>
+      </c>
+      <c r="C47" s="65"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65"/>
+      <c r="I47" s="65"/>
+      <c r="J47" s="65"/>
+      <c r="K47" s="65"/>
+      <c r="L47" s="65"/>
+      <c r="M47" s="65"/>
       <c r="P47" s="8" t="s">
         <v>60</v>
       </c>
@@ -5584,7 +5616,7 @@
     </row>
     <row r="56" spans="2:29" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O56" s="35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P56" s="35"/>
       <c r="Q56" s="35"/>
@@ -5602,23 +5634,23 @@
       <c r="AC56" s="35"/>
     </row>
     <row r="58" spans="2:29" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O58" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="P58" s="67"/>
-      <c r="Q58" s="67"/>
-      <c r="R58" s="67"/>
-      <c r="S58" s="67"/>
-      <c r="T58" s="67"/>
-      <c r="U58" s="67"/>
-      <c r="V58" s="67"/>
-      <c r="W58" s="67"/>
-      <c r="X58" s="67"/>
-      <c r="Y58" s="67"/>
-      <c r="Z58" s="67"/>
-      <c r="AA58" s="67"/>
-      <c r="AB58" s="67"/>
-      <c r="AC58" s="67"/>
+      <c r="O58" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="P58" s="66"/>
+      <c r="Q58" s="66"/>
+      <c r="R58" s="66"/>
+      <c r="S58" s="66"/>
+      <c r="T58" s="66"/>
+      <c r="U58" s="66"/>
+      <c r="V58" s="66"/>
+      <c r="W58" s="66"/>
+      <c r="X58" s="66"/>
+      <c r="Y58" s="66"/>
+      <c r="Z58" s="66"/>
+      <c r="AA58" s="66"/>
+      <c r="AB58" s="66"/>
+      <c r="AC58" s="66"/>
     </row>
     <row r="59" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
       <c r="O59" s="18"/>
@@ -5638,23 +5670,23 @@
       <c r="AC59" s="17"/>
     </row>
     <row r="60" spans="2:29" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O60" s="68" t="s">
-        <v>175</v>
-      </c>
-      <c r="P60" s="68"/>
-      <c r="Q60" s="68"/>
-      <c r="R60" s="68"/>
-      <c r="S60" s="68"/>
-      <c r="T60" s="68"/>
-      <c r="U60" s="68"/>
-      <c r="V60" s="68"/>
-      <c r="W60" s="68"/>
-      <c r="X60" s="68"/>
-      <c r="Y60" s="68"/>
-      <c r="Z60" s="68"/>
-      <c r="AA60" s="68"/>
-      <c r="AB60" s="68"/>
-      <c r="AC60" s="68"/>
+      <c r="O60" s="92" t="s">
+        <v>174</v>
+      </c>
+      <c r="P60" s="67"/>
+      <c r="Q60" s="67"/>
+      <c r="R60" s="67"/>
+      <c r="S60" s="67"/>
+      <c r="T60" s="67"/>
+      <c r="U60" s="67"/>
+      <c r="V60" s="67"/>
+      <c r="W60" s="67"/>
+      <c r="X60" s="67"/>
+      <c r="Y60" s="67"/>
+      <c r="Z60" s="67"/>
+      <c r="AA60" s="67"/>
+      <c r="AB60" s="67"/>
+      <c r="AC60" s="67"/>
     </row>
     <row r="62" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="O62" s="8" t="s">
@@ -5665,8 +5697,8 @@
       <c r="O63" s="8"/>
     </row>
     <row r="64" spans="2:29" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O64" s="63" t="s">
-        <v>173</v>
+      <c r="O64" s="62" t="s">
+        <v>172</v>
       </c>
       <c r="P64" s="56"/>
       <c r="Q64" s="56"/>
@@ -5701,13 +5733,13 @@
       <c r="AC65" s="17"/>
     </row>
     <row r="66" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O66" s="64" t="s">
+      <c r="O66" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="P66" s="64"/>
-      <c r="Q66" s="64"/>
-      <c r="R66" s="64"/>
-      <c r="S66" s="64"/>
+      <c r="P66" s="63"/>
+      <c r="Q66" s="63"/>
+      <c r="R66" s="63"/>
+      <c r="S66" s="63"/>
       <c r="T66" s="30"/>
       <c r="U66" s="30"/>
       <c r="V66" s="30"/>
@@ -5744,13 +5776,13 @@
       </c>
     </row>
     <row r="69" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O69" s="64" t="s">
+      <c r="O69" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="P69" s="64"/>
-      <c r="Q69" s="64"/>
-      <c r="R69" s="64"/>
-      <c r="S69" s="64"/>
+      <c r="P69" s="63"/>
+      <c r="Q69" s="63"/>
+      <c r="R69" s="63"/>
+      <c r="S69" s="63"/>
       <c r="T69" s="30"/>
       <c r="U69" s="30"/>
       <c r="V69" s="30"/>
@@ -5833,7 +5865,7 @@
   <sheetData>
     <row r="2" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
@@ -5841,18 +5873,18 @@
     </row>
     <row r="4" spans="1:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="70" t="s">
-        <v>144</v>
-      </c>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
+      <c r="B4" s="69" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
     </row>
     <row r="5" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="L5" s="46" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M5" s="46"/>
       <c r="N5" s="46"/>
@@ -5861,109 +5893,109 @@
     </row>
     <row r="6" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
-      <c r="L6" s="73" t="s">
-        <v>121</v>
-      </c>
-      <c r="M6" s="73"/>
-      <c r="N6" s="73"/>
-      <c r="O6" s="73"/>
-      <c r="P6" s="73"/>
+      <c r="L6" s="72" t="s">
+        <v>120</v>
+      </c>
+      <c r="M6" s="72"/>
+      <c r="N6" s="72"/>
+      <c r="O6" s="72"/>
+      <c r="P6" s="72"/>
     </row>
     <row r="7" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
-      <c r="L7" s="72" t="s">
-        <v>122</v>
-      </c>
-      <c r="M7" s="72"/>
-      <c r="N7" s="72"/>
-      <c r="O7" s="72"/>
-      <c r="P7" s="72"/>
+      <c r="L7" s="71" t="s">
+        <v>121</v>
+      </c>
+      <c r="M7" s="71"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="71"/>
+      <c r="P7" s="71"/>
     </row>
     <row r="8" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
-      <c r="L8" s="73" t="s">
-        <v>123</v>
-      </c>
-      <c r="M8" s="73"/>
-      <c r="N8" s="73"/>
-      <c r="O8" s="73"/>
-      <c r="P8" s="73"/>
+      <c r="L8" s="72" t="s">
+        <v>122</v>
+      </c>
+      <c r="M8" s="72"/>
+      <c r="N8" s="72"/>
+      <c r="O8" s="72"/>
+      <c r="P8" s="72"/>
     </row>
     <row r="9" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1"/>
-      <c r="L9" s="73" t="s">
-        <v>124</v>
-      </c>
-      <c r="M9" s="73"/>
-      <c r="N9" s="73"/>
-      <c r="O9" s="73"/>
-      <c r="P9" s="73"/>
+      <c r="L9" s="72" t="s">
+        <v>123</v>
+      </c>
+      <c r="M9" s="72"/>
+      <c r="N9" s="72"/>
+      <c r="O9" s="72"/>
+      <c r="P9" s="72"/>
     </row>
     <row r="10" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
-      <c r="L10" s="72" t="s">
-        <v>125</v>
-      </c>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="72"/>
+      <c r="L10" s="71" t="s">
+        <v>124</v>
+      </c>
+      <c r="M10" s="71"/>
+      <c r="N10" s="71"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="71"/>
     </row>
     <row r="11" spans="1:31" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
-      <c r="L11" s="72" t="s">
-        <v>126</v>
-      </c>
-      <c r="M11" s="73"/>
-      <c r="N11" s="73"/>
-      <c r="O11" s="73"/>
-      <c r="P11" s="73"/>
+      <c r="L11" s="71" t="s">
+        <v>125</v>
+      </c>
+      <c r="M11" s="72"/>
+      <c r="N11" s="72"/>
+      <c r="O11" s="72"/>
+      <c r="P11" s="72"/>
     </row>
     <row r="12" spans="1:31" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1"/>
-      <c r="L12" s="72" t="s">
-        <v>127</v>
-      </c>
-      <c r="M12" s="72"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="72"/>
-      <c r="P12" s="72"/>
-      <c r="R12" s="71" t="s">
-        <v>139</v>
-      </c>
-      <c r="S12" s="71"/>
-      <c r="T12" s="71"/>
-      <c r="U12" s="71"/>
-      <c r="V12" s="71"/>
-      <c r="W12" s="71"/>
-      <c r="X12" s="71"/>
-      <c r="Y12" s="71"/>
-      <c r="Z12" s="71"/>
-      <c r="AA12" s="71"/>
-      <c r="AB12" s="71"/>
-      <c r="AC12" s="71"/>
+      <c r="L12" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="M12" s="71"/>
+      <c r="N12" s="71"/>
+      <c r="O12" s="71"/>
+      <c r="P12" s="71"/>
+      <c r="R12" s="70" t="s">
+        <v>138</v>
+      </c>
+      <c r="S12" s="70"/>
+      <c r="T12" s="70"/>
+      <c r="U12" s="70"/>
+      <c r="V12" s="70"/>
+      <c r="W12" s="70"/>
+      <c r="X12" s="70"/>
+      <c r="Y12" s="70"/>
+      <c r="Z12" s="70"/>
+      <c r="AA12" s="70"/>
+      <c r="AB12" s="70"/>
+      <c r="AC12" s="70"/>
       <c r="AD12" s="33"/>
       <c r="AE12" s="33"/>
     </row>
     <row r="13" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
-      <c r="L13" s="73" t="s">
-        <v>128</v>
-      </c>
-      <c r="M13" s="73"/>
-      <c r="N13" s="73"/>
-      <c r="O13" s="73"/>
-      <c r="P13" s="73"/>
+      <c r="L13" s="72" t="s">
+        <v>127</v>
+      </c>
+      <c r="M13" s="72"/>
+      <c r="N13" s="72"/>
+      <c r="O13" s="72"/>
+      <c r="P13" s="72"/>
     </row>
     <row r="14" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A14" s="1"/>
-      <c r="L14" s="73" t="s">
-        <v>129</v>
-      </c>
-      <c r="M14" s="73"/>
-      <c r="N14" s="73"/>
-      <c r="O14" s="73"/>
-      <c r="P14" s="73"/>
+      <c r="L14" s="72" t="s">
+        <v>128</v>
+      </c>
+      <c r="M14" s="72"/>
+      <c r="N14" s="72"/>
+      <c r="O14" s="72"/>
+      <c r="P14" s="72"/>
     </row>
     <row r="15" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
@@ -5975,12 +6007,12 @@
     <row r="17" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A17" s="1"/>
       <c r="L17" s="46" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M17" s="46"/>
       <c r="N17" s="46"/>
       <c r="O17" s="46" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P17" s="46"/>
       <c r="Q17" s="46"/>
@@ -5991,50 +6023,50 @@
     <row r="18" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
       <c r="L18" s="52" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="M18" s="52"/>
       <c r="N18" s="52"/>
-      <c r="O18" s="69" t="s">
-        <v>132</v>
-      </c>
-      <c r="P18" s="69"/>
-      <c r="Q18" s="69"/>
-      <c r="R18" s="69"/>
-      <c r="S18" s="69"/>
-      <c r="T18" s="69"/>
+      <c r="O18" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="P18" s="68"/>
+      <c r="Q18" s="68"/>
+      <c r="R18" s="68"/>
+      <c r="S18" s="68"/>
+      <c r="T18" s="68"/>
     </row>
     <row r="19" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="L19" s="52" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M19" s="52"/>
       <c r="N19" s="52"/>
-      <c r="O19" s="69" t="s">
-        <v>136</v>
-      </c>
-      <c r="P19" s="69"/>
-      <c r="Q19" s="69"/>
-      <c r="R19" s="69"/>
-      <c r="S19" s="69"/>
-      <c r="T19" s="69"/>
+      <c r="O19" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="P19" s="68"/>
+      <c r="Q19" s="68"/>
+      <c r="R19" s="68"/>
+      <c r="S19" s="68"/>
+      <c r="T19" s="68"/>
     </row>
     <row r="20" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
       <c r="L20" s="52" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M20" s="52"/>
       <c r="N20" s="52"/>
-      <c r="O20" s="69" t="s">
-        <v>138</v>
-      </c>
-      <c r="P20" s="69"/>
-      <c r="Q20" s="69"/>
-      <c r="R20" s="69"/>
-      <c r="S20" s="69"/>
-      <c r="T20" s="69"/>
+      <c r="O20" s="68" t="s">
+        <v>137</v>
+      </c>
+      <c r="P20" s="68"/>
+      <c r="Q20" s="68"/>
+      <c r="R20" s="68"/>
+      <c r="S20" s="68"/>
+      <c r="T20" s="68"/>
     </row>
     <row r="21" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A21" s="1"/>
@@ -6052,7 +6084,7 @@
     </row>
     <row r="25" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B25" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
@@ -6060,12 +6092,12 @@
     </row>
     <row r="27" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B27" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B56" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
@@ -6073,17 +6105,17 @@
     </row>
     <row r="58" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="85" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B85" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="87" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B87" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="88" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
@@ -6091,42 +6123,42 @@
     </row>
     <row r="89" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B89" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="91" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B91" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="93" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B93" s="24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="94" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B94" s="24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="95" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B95" s="24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="97" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B97" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="99" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B99" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="101" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B101" s="20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="102" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
@@ -6134,52 +6166,52 @@
     </row>
     <row r="103" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B103" s="20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="105" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B105" s="74" t="s">
-        <v>153</v>
-      </c>
-      <c r="C105" s="74"/>
-      <c r="D105" s="74"/>
-      <c r="E105" s="74"/>
-      <c r="F105" s="74"/>
-      <c r="G105" s="74"/>
-      <c r="H105" s="74"/>
-      <c r="I105" s="74"/>
-      <c r="J105" s="74"/>
-      <c r="K105" s="74"/>
-      <c r="L105" s="74"/>
-      <c r="M105" s="74"/>
-      <c r="N105" s="74"/>
-      <c r="O105" s="74"/>
-      <c r="P105" s="74"/>
-      <c r="Q105" s="74"/>
-      <c r="R105" s="74"/>
-      <c r="S105" s="74"/>
-      <c r="T105" s="74"/>
-      <c r="U105" s="74"/>
-      <c r="V105" s="74"/>
-      <c r="W105" s="74"/>
-      <c r="X105" s="74"/>
-      <c r="Y105" s="74"/>
+      <c r="B105" s="73" t="s">
+        <v>152</v>
+      </c>
+      <c r="C105" s="73"/>
+      <c r="D105" s="73"/>
+      <c r="E105" s="73"/>
+      <c r="F105" s="73"/>
+      <c r="G105" s="73"/>
+      <c r="H105" s="73"/>
+      <c r="I105" s="73"/>
+      <c r="J105" s="73"/>
+      <c r="K105" s="73"/>
+      <c r="L105" s="73"/>
+      <c r="M105" s="73"/>
+      <c r="N105" s="73"/>
+      <c r="O105" s="73"/>
+      <c r="P105" s="73"/>
+      <c r="Q105" s="73"/>
+      <c r="R105" s="73"/>
+      <c r="S105" s="73"/>
+      <c r="T105" s="73"/>
+      <c r="U105" s="73"/>
+      <c r="V105" s="73"/>
+      <c r="W105" s="73"/>
+      <c r="X105" s="73"/>
+      <c r="Y105" s="73"/>
     </row>
     <row r="108" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A108" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="110" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B110" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C110" s="8"/>
       <c r="D110" s="25"/>
     </row>
     <row r="112" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B112" s="20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="113" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
@@ -6187,17 +6219,17 @@
     </row>
     <row r="114" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B114" s="20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="116" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B116" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="118" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B118" s="35" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C118" s="35"/>
       <c r="D118" s="35"/>
@@ -6229,7 +6261,7 @@
     </row>
     <row r="119" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B119" s="26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="120" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
@@ -6237,7 +6269,7 @@
     </row>
     <row r="121" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B121" s="20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="122" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
@@ -6245,7 +6277,7 @@
     </row>
     <row r="123" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B123" s="28" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="124" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
@@ -6253,30 +6285,30 @@
     </row>
     <row r="125" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B125" s="20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="127" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B127" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="129" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B129" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="131" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B131" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="133" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B133" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L133" s="27" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M133" s="20"/>
     </row>
@@ -6324,25 +6356,28 @@
   <sheetData>
     <row r="2" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="90" t="s">
+        <v>241</v>
+      </c>
       <c r="B4" s="55" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C4" s="55"/>
-      <c r="D4" s="85" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" s="86"/>
-      <c r="F4" s="87"/>
+      <c r="D4" s="84" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="85"/>
+      <c r="F4" s="86"/>
       <c r="G4" s="55" t="s">
         <v>25</v>
       </c>
       <c r="H4" s="55"/>
       <c r="I4" s="55" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J4" s="55"/>
       <c r="K4" s="55" t="s">
@@ -6357,757 +6392,823 @@
       <c r="R4" s="55"/>
       <c r="S4" s="55"/>
       <c r="T4" s="55" t="s">
+        <v>219</v>
+      </c>
+      <c r="U4" s="55"/>
+    </row>
+    <row r="5" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="91">
+        <v>1</v>
+      </c>
+      <c r="B5" s="89" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="89"/>
+      <c r="D5" s="74" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="75"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" s="77"/>
+      <c r="I5" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="J5" s="78"/>
+      <c r="K5" s="71" t="s">
+        <v>94</v>
+      </c>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="71"/>
+      <c r="R5" s="71"/>
+      <c r="S5" s="71"/>
+      <c r="T5" s="87" t="s">
         <v>221</v>
       </c>
-      <c r="U4" s="55"/>
-    </row>
-    <row r="5" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="90" t="s">
+      <c r="U5" s="87"/>
+    </row>
+    <row r="6" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="91">
+        <v>2</v>
+      </c>
+      <c r="B6" s="89" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" s="89"/>
+      <c r="D6" s="74" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" s="75"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" s="79"/>
+      <c r="I6" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="J6" s="78"/>
+      <c r="K6" s="71" t="s">
+        <v>178</v>
+      </c>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="71"/>
+      <c r="O6" s="71"/>
+      <c r="P6" s="71"/>
+      <c r="Q6" s="71"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="87" t="s">
+        <v>221</v>
+      </c>
+      <c r="U6" s="87"/>
+    </row>
+    <row r="7" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="91">
+        <v>3</v>
+      </c>
+      <c r="B7" s="89" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" s="89"/>
+      <c r="D7" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="75"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7" s="77"/>
+      <c r="I7" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="J7" s="78"/>
+      <c r="K7" s="71" t="s">
+        <v>108</v>
+      </c>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="71"/>
+      <c r="P7" s="71"/>
+      <c r="Q7" s="71"/>
+      <c r="R7" s="71"/>
+      <c r="S7" s="71"/>
+      <c r="T7" s="88" t="s">
+        <v>221</v>
+      </c>
+      <c r="U7" s="87"/>
+    </row>
+    <row r="8" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="91">
+        <v>4</v>
+      </c>
+      <c r="B8" s="89" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" s="89"/>
+      <c r="D8" s="74" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="75"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="77"/>
+      <c r="I8" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="J8" s="78"/>
+      <c r="K8" s="71" t="s">
+        <v>108</v>
+      </c>
+      <c r="L8" s="71"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="71"/>
+      <c r="O8" s="71"/>
+      <c r="P8" s="71"/>
+      <c r="Q8" s="71"/>
+      <c r="R8" s="71"/>
+      <c r="S8" s="71"/>
+      <c r="T8" s="88" t="s">
+        <v>221</v>
+      </c>
+      <c r="U8" s="87"/>
+    </row>
+    <row r="9" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="91">
+        <v>5</v>
+      </c>
+      <c r="B9" s="89" t="s">
+        <v>190</v>
+      </c>
+      <c r="C9" s="89"/>
+      <c r="D9" s="74" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="75"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="77"/>
+      <c r="I9" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="J9" s="78"/>
+      <c r="K9" s="71" t="s">
+        <v>108</v>
+      </c>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="71"/>
+      <c r="S9" s="71"/>
+      <c r="T9" s="88" t="s">
+        <v>221</v>
+      </c>
+      <c r="U9" s="87"/>
+    </row>
+    <row r="10" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="91">
+        <v>6</v>
+      </c>
+      <c r="B10" s="89" t="s">
+        <v>191</v>
+      </c>
+      <c r="C10" s="89"/>
+      <c r="D10" s="74" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="75"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="77"/>
+      <c r="I10" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="J10" s="78"/>
+      <c r="K10" s="71" t="s">
+        <v>108</v>
+      </c>
+      <c r="L10" s="71"/>
+      <c r="M10" s="71"/>
+      <c r="N10" s="71"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="71"/>
+      <c r="S10" s="71"/>
+      <c r="T10" s="88" t="s">
+        <v>221</v>
+      </c>
+      <c r="U10" s="87"/>
+    </row>
+    <row r="11" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="91">
+        <v>7</v>
+      </c>
+      <c r="B11" s="89" t="s">
+        <v>192</v>
+      </c>
+      <c r="C11" s="89"/>
+      <c r="D11" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="75"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="77"/>
+      <c r="I11" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="J11" s="78"/>
+      <c r="K11" s="71" t="s">
+        <v>108</v>
+      </c>
+      <c r="L11" s="71"/>
+      <c r="M11" s="71"/>
+      <c r="N11" s="71"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="71"/>
+      <c r="S11" s="71"/>
+      <c r="T11" s="88" t="s">
+        <v>221</v>
+      </c>
+      <c r="U11" s="87"/>
+    </row>
+    <row r="12" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="91">
+        <v>8</v>
+      </c>
+      <c r="B12" s="89" t="s">
         <v>183</v>
       </c>
-      <c r="C5" s="90"/>
-      <c r="D5" s="75" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" s="76"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="78" t="s">
+      <c r="C12" s="89"/>
+      <c r="D12" s="81" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="82"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="77"/>
+      <c r="I12" s="78" t="s">
         <v>92</v>
       </c>
-      <c r="H5" s="78"/>
-      <c r="I5" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="J5" s="79"/>
-      <c r="K5" s="72" t="s">
-        <v>95</v>
-      </c>
-      <c r="L5" s="72"/>
-      <c r="M5" s="72"/>
-      <c r="N5" s="72"/>
-      <c r="O5" s="72"/>
-      <c r="P5" s="72"/>
-      <c r="Q5" s="72"/>
-      <c r="R5" s="72"/>
-      <c r="S5" s="72"/>
-      <c r="T5" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="U5" s="88"/>
-    </row>
-    <row r="6" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B6" s="90" t="s">
-        <v>204</v>
-      </c>
-      <c r="C6" s="90"/>
-      <c r="D6" s="75" t="s">
+      <c r="J12" s="78"/>
+      <c r="K12" s="71" t="s">
+        <v>109</v>
+      </c>
+      <c r="L12" s="71"/>
+      <c r="M12" s="71"/>
+      <c r="N12" s="71"/>
+      <c r="O12" s="71"/>
+      <c r="P12" s="71"/>
+      <c r="Q12" s="71"/>
+      <c r="R12" s="71"/>
+      <c r="S12" s="71"/>
+      <c r="T12" s="87" t="s">
+        <v>221</v>
+      </c>
+      <c r="U12" s="87"/>
+    </row>
+    <row r="13" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="91">
+        <v>9</v>
+      </c>
+      <c r="B13" s="89" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" s="89"/>
+      <c r="D13" s="74" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="75"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" s="77"/>
+      <c r="I13" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="J13" s="78"/>
+      <c r="K13" s="71" t="s">
+        <v>109</v>
+      </c>
+      <c r="L13" s="71"/>
+      <c r="M13" s="71"/>
+      <c r="N13" s="71"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="71"/>
+      <c r="T13" s="87" t="s">
+        <v>221</v>
+      </c>
+      <c r="U13" s="87"/>
+    </row>
+    <row r="14" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="91">
+        <v>10</v>
+      </c>
+      <c r="B14" s="89" t="s">
+        <v>185</v>
+      </c>
+      <c r="C14" s="89"/>
+      <c r="D14" s="74" t="s">
+        <v>115</v>
+      </c>
+      <c r="E14" s="75"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="77"/>
+      <c r="I14" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="J14" s="78"/>
+      <c r="K14" s="71" t="s">
+        <v>116</v>
+      </c>
+      <c r="L14" s="71"/>
+      <c r="M14" s="71"/>
+      <c r="N14" s="71"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="71"/>
+      <c r="S14" s="71"/>
+      <c r="T14" s="87" t="s">
+        <v>221</v>
+      </c>
+      <c r="U14" s="87"/>
+    </row>
+    <row r="15" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="91">
+        <v>11</v>
+      </c>
+      <c r="B15" s="89" t="s">
+        <v>186</v>
+      </c>
+      <c r="C15" s="89"/>
+      <c r="D15" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="E6" s="76"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="80" t="s">
+      <c r="E15" s="75"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="77" t="s">
         <v>91</v>
       </c>
-      <c r="H6" s="80"/>
-      <c r="I6" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="J6" s="79"/>
-      <c r="K6" s="72" t="s">
-        <v>179</v>
-      </c>
-      <c r="L6" s="72"/>
-      <c r="M6" s="72"/>
-      <c r="N6" s="72"/>
-      <c r="O6" s="72"/>
-      <c r="P6" s="72"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="72"/>
-      <c r="T6" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="U6" s="88"/>
-    </row>
-    <row r="7" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="90" t="s">
-        <v>189</v>
-      </c>
-      <c r="C7" s="90"/>
-      <c r="D7" s="75" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="76"/>
-      <c r="F7" s="77"/>
-      <c r="G7" s="78" t="s">
+      <c r="H15" s="77"/>
+      <c r="I15" s="78" t="s">
         <v>92</v>
       </c>
-      <c r="H7" s="78"/>
-      <c r="I7" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="J7" s="79"/>
-      <c r="K7" s="72" t="s">
-        <v>109</v>
-      </c>
-      <c r="L7" s="72"/>
-      <c r="M7" s="72"/>
-      <c r="N7" s="72"/>
-      <c r="O7" s="72"/>
-      <c r="P7" s="72"/>
-      <c r="Q7" s="72"/>
-      <c r="R7" s="72"/>
-      <c r="S7" s="72"/>
-      <c r="T7" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="U7" s="88"/>
-    </row>
-    <row r="8" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="90" t="s">
-        <v>190</v>
-      </c>
-      <c r="C8" s="90"/>
-      <c r="D8" s="75" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="76"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="78" t="s">
+      <c r="J15" s="78"/>
+      <c r="K15" s="71" t="s">
+        <v>117</v>
+      </c>
+      <c r="L15" s="71"/>
+      <c r="M15" s="71"/>
+      <c r="N15" s="71"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="71"/>
+      <c r="S15" s="71"/>
+      <c r="T15" s="87" t="s">
+        <v>221</v>
+      </c>
+      <c r="U15" s="87"/>
+    </row>
+    <row r="16" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="91">
+        <v>12</v>
+      </c>
+      <c r="B16" s="89" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16" s="89"/>
+      <c r="D16" s="74" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" s="75"/>
+      <c r="F16" s="76"/>
+      <c r="G16" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" s="77"/>
+      <c r="I16" s="78" t="s">
         <v>92</v>
       </c>
-      <c r="H8" s="78"/>
-      <c r="I8" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="J8" s="79"/>
-      <c r="K8" s="72" t="s">
-        <v>109</v>
-      </c>
-      <c r="L8" s="72"/>
-      <c r="M8" s="72"/>
-      <c r="N8" s="72"/>
-      <c r="O8" s="72"/>
-      <c r="P8" s="72"/>
-      <c r="Q8" s="72"/>
-      <c r="R8" s="72"/>
-      <c r="S8" s="72"/>
-      <c r="T8" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="U8" s="88"/>
-    </row>
-    <row r="9" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="90" t="s">
-        <v>191</v>
-      </c>
-      <c r="C9" s="90"/>
-      <c r="D9" s="75" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="76"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="78" t="s">
+      <c r="J16" s="78"/>
+      <c r="K16" s="71" t="s">
+        <v>117</v>
+      </c>
+      <c r="L16" s="71"/>
+      <c r="M16" s="71"/>
+      <c r="N16" s="71"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="71"/>
+      <c r="S16" s="71"/>
+      <c r="T16" s="87" t="s">
+        <v>220</v>
+      </c>
+      <c r="U16" s="87"/>
+    </row>
+    <row r="17" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="91">
+        <v>13</v>
+      </c>
+      <c r="B17" s="89" t="s">
+        <v>194</v>
+      </c>
+      <c r="C17" s="89"/>
+      <c r="D17" s="74" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="75"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" s="79"/>
+      <c r="I17" s="78" t="s">
         <v>92</v>
       </c>
-      <c r="H9" s="78"/>
-      <c r="I9" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="J9" s="79"/>
-      <c r="K9" s="72" t="s">
-        <v>109</v>
-      </c>
-      <c r="L9" s="72"/>
-      <c r="M9" s="72"/>
-      <c r="N9" s="72"/>
-      <c r="O9" s="72"/>
-      <c r="P9" s="72"/>
-      <c r="Q9" s="72"/>
-      <c r="R9" s="72"/>
-      <c r="S9" s="72"/>
-      <c r="T9" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="U9" s="88"/>
-    </row>
-    <row r="10" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="90" t="s">
-        <v>192</v>
-      </c>
-      <c r="C10" s="90"/>
-      <c r="D10" s="75" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="76"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="78" t="s">
+      <c r="J17" s="78"/>
+      <c r="K17" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="L17" s="71"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="71"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="71"/>
+      <c r="S17" s="71"/>
+      <c r="T17" s="87" t="s">
+        <v>221</v>
+      </c>
+      <c r="U17" s="87"/>
+    </row>
+    <row r="18" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="91">
+        <v>14</v>
+      </c>
+      <c r="B18" s="89" t="s">
+        <v>193</v>
+      </c>
+      <c r="C18" s="89"/>
+      <c r="D18" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" s="75"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="H18" s="79"/>
+      <c r="I18" s="78" t="s">
         <v>92</v>
       </c>
-      <c r="H10" s="78"/>
-      <c r="I10" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="J10" s="79"/>
-      <c r="K10" s="72" t="s">
-        <v>109</v>
-      </c>
-      <c r="L10" s="72"/>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
-      <c r="R10" s="72"/>
-      <c r="S10" s="72"/>
-      <c r="T10" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="U10" s="88"/>
-    </row>
-    <row r="11" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="90" t="s">
-        <v>193</v>
-      </c>
-      <c r="C11" s="90"/>
-      <c r="D11" s="75" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="76"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="78" t="s">
+      <c r="J18" s="78"/>
+      <c r="K18" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="L18" s="71"/>
+      <c r="M18" s="71"/>
+      <c r="N18" s="71"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="71"/>
+      <c r="S18" s="71"/>
+      <c r="T18" s="87" t="s">
+        <v>221</v>
+      </c>
+      <c r="U18" s="87"/>
+    </row>
+    <row r="19" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="91">
+        <v>15</v>
+      </c>
+      <c r="B19" s="89" t="s">
+        <v>195</v>
+      </c>
+      <c r="C19" s="89"/>
+      <c r="D19" s="74" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="75"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="H19" s="79"/>
+      <c r="I19" s="78" t="s">
         <v>92</v>
       </c>
-      <c r="H11" s="78"/>
-      <c r="I11" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="J11" s="79"/>
-      <c r="K11" s="72" t="s">
-        <v>109</v>
-      </c>
-      <c r="L11" s="72"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="72"/>
-      <c r="O11" s="72"/>
-      <c r="P11" s="72"/>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="72"/>
-      <c r="T11" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="U11" s="88"/>
-    </row>
-    <row r="12" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="C12" s="90"/>
-      <c r="D12" s="82" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12" s="83"/>
-      <c r="F12" s="84"/>
-      <c r="G12" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="H12" s="78"/>
-      <c r="I12" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="J12" s="79"/>
-      <c r="K12" s="72" t="s">
+      <c r="J19" s="78"/>
+      <c r="K19" s="71" t="s">
         <v>110</v>
       </c>
-      <c r="L12" s="72"/>
-      <c r="M12" s="72"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="72"/>
-      <c r="P12" s="72"/>
-      <c r="Q12" s="72"/>
-      <c r="R12" s="72"/>
-      <c r="S12" s="72"/>
-      <c r="T12" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="U12" s="88"/>
-    </row>
-    <row r="13" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B13" s="90" t="s">
-        <v>185</v>
-      </c>
-      <c r="C13" s="90"/>
-      <c r="D13" s="75" t="s">
-        <v>98</v>
-      </c>
-      <c r="E13" s="76"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" s="78"/>
-      <c r="I13" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="J13" s="79"/>
-      <c r="K13" s="72" t="s">
+      <c r="L19" s="71"/>
+      <c r="M19" s="71"/>
+      <c r="N19" s="71"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="71"/>
+      <c r="S19" s="71"/>
+      <c r="T19" s="87" t="s">
+        <v>221</v>
+      </c>
+      <c r="U19" s="87"/>
+    </row>
+    <row r="20" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="91">
+        <v>16</v>
+      </c>
+      <c r="B20" s="89" t="s">
+        <v>196</v>
+      </c>
+      <c r="C20" s="89"/>
+      <c r="D20" s="74" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="75"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="H20" s="79"/>
+      <c r="I20" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="80"/>
+      <c r="K20" s="71" t="s">
         <v>110</v>
       </c>
-      <c r="L13" s="72"/>
-      <c r="M13" s="72"/>
-      <c r="N13" s="72"/>
-      <c r="O13" s="72"/>
-      <c r="P13" s="72"/>
-      <c r="Q13" s="72"/>
-      <c r="R13" s="72"/>
-      <c r="S13" s="72"/>
-      <c r="T13" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="U13" s="88"/>
-    </row>
-    <row r="14" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="90" t="s">
-        <v>186</v>
-      </c>
-      <c r="C14" s="90"/>
-      <c r="D14" s="75" t="s">
-        <v>116</v>
-      </c>
-      <c r="E14" s="76"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="H14" s="78"/>
-      <c r="I14" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="J14" s="79"/>
-      <c r="K14" s="72" t="s">
-        <v>117</v>
-      </c>
-      <c r="L14" s="72"/>
-      <c r="M14" s="72"/>
-      <c r="N14" s="72"/>
-      <c r="O14" s="72"/>
-      <c r="P14" s="72"/>
-      <c r="Q14" s="72"/>
-      <c r="R14" s="72"/>
-      <c r="S14" s="72"/>
-      <c r="T14" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="U14" s="88"/>
-    </row>
-    <row r="15" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="90" t="s">
-        <v>187</v>
-      </c>
-      <c r="C15" s="90"/>
-      <c r="D15" s="75" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" s="76"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="H15" s="78"/>
-      <c r="I15" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="J15" s="79"/>
-      <c r="K15" s="72" t="s">
-        <v>118</v>
-      </c>
-      <c r="L15" s="72"/>
-      <c r="M15" s="72"/>
-      <c r="N15" s="72"/>
-      <c r="O15" s="72"/>
-      <c r="P15" s="72"/>
-      <c r="Q15" s="72"/>
-      <c r="R15" s="72"/>
-      <c r="S15" s="72"/>
-      <c r="T15" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="U15" s="88"/>
-    </row>
-    <row r="16" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="90" t="s">
-        <v>188</v>
-      </c>
-      <c r="C16" s="90"/>
-      <c r="D16" s="75" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" s="76"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="H16" s="78"/>
-      <c r="I16" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="J16" s="79"/>
-      <c r="K16" s="72" t="s">
-        <v>118</v>
-      </c>
-      <c r="L16" s="72"/>
-      <c r="M16" s="72"/>
-      <c r="N16" s="72"/>
-      <c r="O16" s="72"/>
-      <c r="P16" s="72"/>
-      <c r="Q16" s="72"/>
-      <c r="R16" s="72"/>
-      <c r="S16" s="72"/>
-      <c r="T16" s="88" t="s">
-        <v>222</v>
-      </c>
-      <c r="U16" s="88"/>
-    </row>
-    <row r="17" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B17" s="90" t="s">
-        <v>195</v>
-      </c>
-      <c r="C17" s="90"/>
-      <c r="D17" s="75" t="s">
-        <v>100</v>
-      </c>
-      <c r="E17" s="76"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="80" t="s">
-        <v>91</v>
-      </c>
-      <c r="H17" s="80"/>
-      <c r="I17" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="J17" s="79"/>
-      <c r="K17" s="72" t="s">
-        <v>111</v>
-      </c>
-      <c r="L17" s="72"/>
-      <c r="M17" s="72"/>
-      <c r="N17" s="72"/>
-      <c r="O17" s="72"/>
-      <c r="P17" s="72"/>
-      <c r="Q17" s="72"/>
-      <c r="R17" s="72"/>
-      <c r="S17" s="72"/>
-      <c r="T17" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="U17" s="88"/>
-    </row>
-    <row r="18" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B18" s="90" t="s">
-        <v>194</v>
-      </c>
-      <c r="C18" s="90"/>
-      <c r="D18" s="75" t="s">
+      <c r="L20" s="71"/>
+      <c r="M20" s="71"/>
+      <c r="N20" s="71"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="71"/>
+      <c r="S20" s="71"/>
+      <c r="T20" s="87" t="s">
+        <v>221</v>
+      </c>
+      <c r="U20" s="87"/>
+    </row>
+    <row r="21" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="91">
+        <v>17</v>
+      </c>
+      <c r="B21" s="89" t="s">
+        <v>197</v>
+      </c>
+      <c r="C21" s="89"/>
+      <c r="D21" s="74" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" s="75"/>
+      <c r="F21" s="76"/>
+      <c r="G21" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="H21" s="79"/>
+      <c r="I21" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="80"/>
+      <c r="K21" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="L21" s="71"/>
+      <c r="M21" s="71"/>
+      <c r="N21" s="71"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="71"/>
+      <c r="S21" s="71"/>
+      <c r="T21" s="87" t="s">
+        <v>221</v>
+      </c>
+      <c r="U21" s="87"/>
+    </row>
+    <row r="22" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A22" s="91">
+        <v>18</v>
+      </c>
+      <c r="B22" s="89" t="s">
+        <v>198</v>
+      </c>
+      <c r="C22" s="89"/>
+      <c r="D22" s="74" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22" s="75"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="H22" s="79"/>
+      <c r="I22" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="80"/>
+      <c r="K22" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="L22" s="71"/>
+      <c r="M22" s="71"/>
+      <c r="N22" s="71"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="71"/>
+      <c r="S22" s="71"/>
+      <c r="T22" s="87" t="s">
+        <v>221</v>
+      </c>
+      <c r="U22" s="87"/>
+    </row>
+    <row r="23" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A23" s="91">
+        <v>19</v>
+      </c>
+      <c r="B23" s="89" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" s="89"/>
+      <c r="D23" s="74" t="s">
+        <v>105</v>
+      </c>
+      <c r="E23" s="75"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="H23" s="79"/>
+      <c r="I23" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="80"/>
+      <c r="K23" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="L23" s="71"/>
+      <c r="M23" s="71"/>
+      <c r="N23" s="71"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="71"/>
+      <c r="S23" s="71"/>
+      <c r="T23" s="87" t="s">
+        <v>221</v>
+      </c>
+      <c r="U23" s="87"/>
+    </row>
+    <row r="24" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="91">
+        <v>20</v>
+      </c>
+      <c r="B24" s="89" t="s">
+        <v>200</v>
+      </c>
+      <c r="C24" s="89"/>
+      <c r="D24" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" s="75"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="79"/>
+      <c r="I24" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="80"/>
+      <c r="K24" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="L24" s="71"/>
+      <c r="M24" s="71"/>
+      <c r="N24" s="71"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="71"/>
+      <c r="S24" s="71"/>
+      <c r="T24" s="87" t="s">
+        <v>221</v>
+      </c>
+      <c r="U24" s="87"/>
+    </row>
+    <row r="25" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="91">
+        <v>21</v>
+      </c>
+      <c r="B25" s="89" t="s">
+        <v>201</v>
+      </c>
+      <c r="C25" s="89"/>
+      <c r="D25" s="74" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="75"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="H25" s="79"/>
+      <c r="I25" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="80"/>
+      <c r="K25" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="L25" s="71"/>
+      <c r="M25" s="71"/>
+      <c r="N25" s="71"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="71"/>
+      <c r="S25" s="71"/>
+      <c r="T25" s="87" t="s">
+        <v>221</v>
+      </c>
+      <c r="U25" s="87"/>
+    </row>
+    <row r="26" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="91">
+        <v>22</v>
+      </c>
+      <c r="B26" s="89" t="s">
+        <v>202</v>
+      </c>
+      <c r="C26" s="89"/>
+      <c r="D26" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="E18" s="76"/>
-      <c r="F18" s="77"/>
-      <c r="G18" s="80" t="s">
-        <v>91</v>
-      </c>
-      <c r="H18" s="80"/>
-      <c r="I18" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="J18" s="79"/>
-      <c r="K18" s="72" t="s">
-        <v>111</v>
-      </c>
-      <c r="L18" s="72"/>
-      <c r="M18" s="72"/>
-      <c r="N18" s="72"/>
-      <c r="O18" s="72"/>
-      <c r="P18" s="72"/>
-      <c r="Q18" s="72"/>
-      <c r="R18" s="72"/>
-      <c r="S18" s="72"/>
-      <c r="T18" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="U18" s="88"/>
-    </row>
-    <row r="19" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B19" s="90" t="s">
-        <v>196</v>
-      </c>
-      <c r="C19" s="90"/>
-      <c r="D19" s="75" t="s">
-        <v>99</v>
-      </c>
-      <c r="E19" s="76"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="80" t="s">
-        <v>91</v>
-      </c>
-      <c r="H19" s="80"/>
-      <c r="I19" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="J19" s="79"/>
-      <c r="K19" s="72" t="s">
-        <v>111</v>
-      </c>
-      <c r="L19" s="72"/>
-      <c r="M19" s="72"/>
-      <c r="N19" s="72"/>
-      <c r="O19" s="72"/>
-      <c r="P19" s="72"/>
-      <c r="Q19" s="72"/>
-      <c r="R19" s="72"/>
-      <c r="S19" s="72"/>
-      <c r="T19" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="U19" s="88"/>
-    </row>
-    <row r="20" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B20" s="90" t="s">
-        <v>197</v>
-      </c>
-      <c r="C20" s="90"/>
-      <c r="D20" s="75" t="s">
-        <v>103</v>
-      </c>
-      <c r="E20" s="76"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="80" t="s">
-        <v>91</v>
-      </c>
-      <c r="H20" s="80"/>
-      <c r="I20" s="81" t="s">
+      <c r="E26" s="75"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="H26" s="79"/>
+      <c r="I26" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="J20" s="81"/>
-      <c r="K20" s="72" t="s">
-        <v>111</v>
-      </c>
-      <c r="L20" s="72"/>
-      <c r="M20" s="72"/>
-      <c r="N20" s="72"/>
-      <c r="O20" s="72"/>
-      <c r="P20" s="72"/>
-      <c r="Q20" s="72"/>
-      <c r="R20" s="72"/>
-      <c r="S20" s="72"/>
-      <c r="T20" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="U20" s="88"/>
-    </row>
-    <row r="21" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B21" s="90" t="s">
-        <v>198</v>
-      </c>
-      <c r="C21" s="90"/>
-      <c r="D21" s="75" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" s="76"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="80" t="s">
-        <v>91</v>
-      </c>
-      <c r="H21" s="80"/>
-      <c r="I21" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="81"/>
-      <c r="K21" s="72" t="s">
-        <v>111</v>
-      </c>
-      <c r="L21" s="72"/>
-      <c r="M21" s="72"/>
-      <c r="N21" s="72"/>
-      <c r="O21" s="72"/>
-      <c r="P21" s="72"/>
-      <c r="Q21" s="72"/>
-      <c r="R21" s="72"/>
-      <c r="S21" s="72"/>
-      <c r="T21" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="U21" s="88"/>
-    </row>
-    <row r="22" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B22" s="90" t="s">
-        <v>199</v>
-      </c>
-      <c r="C22" s="90"/>
-      <c r="D22" s="75" t="s">
-        <v>105</v>
-      </c>
-      <c r="E22" s="76"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="80" t="s">
-        <v>91</v>
-      </c>
-      <c r="H22" s="80"/>
-      <c r="I22" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="81"/>
-      <c r="K22" s="72" t="s">
-        <v>111</v>
-      </c>
-      <c r="L22" s="72"/>
-      <c r="M22" s="72"/>
-      <c r="N22" s="72"/>
-      <c r="O22" s="72"/>
-      <c r="P22" s="72"/>
-      <c r="Q22" s="72"/>
-      <c r="R22" s="72"/>
-      <c r="S22" s="72"/>
-      <c r="T22" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="U22" s="88"/>
-    </row>
-    <row r="23" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B23" s="90" t="s">
-        <v>200</v>
-      </c>
-      <c r="C23" s="90"/>
-      <c r="D23" s="75" t="s">
-        <v>106</v>
-      </c>
-      <c r="E23" s="76"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="80" t="s">
-        <v>91</v>
-      </c>
-      <c r="H23" s="80"/>
-      <c r="I23" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="81"/>
-      <c r="K23" s="72" t="s">
-        <v>111</v>
-      </c>
-      <c r="L23" s="72"/>
-      <c r="M23" s="72"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="72"/>
-      <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
-      <c r="R23" s="72"/>
-      <c r="S23" s="72"/>
-      <c r="T23" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="U23" s="88"/>
-    </row>
-    <row r="24" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B24" s="90" t="s">
-        <v>201</v>
-      </c>
-      <c r="C24" s="90"/>
-      <c r="D24" s="75" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" s="76"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="80" t="s">
-        <v>91</v>
-      </c>
-      <c r="H24" s="80"/>
-      <c r="I24" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="81"/>
-      <c r="K24" s="72" t="s">
-        <v>111</v>
-      </c>
-      <c r="L24" s="72"/>
-      <c r="M24" s="72"/>
-      <c r="N24" s="72"/>
-      <c r="O24" s="72"/>
-      <c r="P24" s="72"/>
-      <c r="Q24" s="72"/>
-      <c r="R24" s="72"/>
-      <c r="S24" s="72"/>
-      <c r="T24" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="U24" s="88"/>
-    </row>
-    <row r="25" spans="2:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B25" s="90" t="s">
-        <v>202</v>
-      </c>
-      <c r="C25" s="90"/>
-      <c r="D25" s="75" t="s">
-        <v>108</v>
-      </c>
-      <c r="E25" s="76"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="80" t="s">
-        <v>91</v>
-      </c>
-      <c r="H25" s="80"/>
-      <c r="I25" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="81"/>
-      <c r="K25" s="72" t="s">
-        <v>111</v>
-      </c>
-      <c r="L25" s="72"/>
-      <c r="M25" s="72"/>
-      <c r="N25" s="72"/>
-      <c r="O25" s="72"/>
-      <c r="P25" s="72"/>
-      <c r="Q25" s="72"/>
-      <c r="R25" s="72"/>
-      <c r="S25" s="72"/>
-      <c r="T25" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="U25" s="88"/>
-    </row>
-    <row r="26" spans="2:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="90" t="s">
-        <v>203</v>
-      </c>
-      <c r="C26" s="90"/>
-      <c r="D26" s="75" t="s">
-        <v>102</v>
-      </c>
-      <c r="E26" s="76"/>
-      <c r="F26" s="77"/>
-      <c r="G26" s="80" t="s">
-        <v>91</v>
-      </c>
-      <c r="H26" s="80"/>
-      <c r="I26" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="81"/>
-      <c r="K26" s="72" t="s">
-        <v>111</v>
-      </c>
-      <c r="L26" s="72"/>
-      <c r="M26" s="72"/>
-      <c r="N26" s="72"/>
-      <c r="O26" s="72"/>
-      <c r="P26" s="72"/>
-      <c r="Q26" s="72"/>
-      <c r="R26" s="72"/>
-      <c r="S26" s="72"/>
-      <c r="T26" s="88" t="s">
-        <v>223</v>
-      </c>
-      <c r="U26" s="88"/>
+      <c r="J26" s="80"/>
+      <c r="K26" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="L26" s="71"/>
+      <c r="M26" s="71"/>
+      <c r="N26" s="71"/>
+      <c r="O26" s="71"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="71"/>
+      <c r="S26" s="71"/>
+      <c r="T26" s="87" t="s">
+        <v>221</v>
+      </c>
+      <c r="U26" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="138">
@@ -7285,32 +7386,32 @@
   <sheetData>
     <row r="2" spans="1:16" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P10" s="28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P21" s="28" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P22" s="34" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="24" spans="2:28" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P24" s="35" t="s">
-        <v>211</v>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="24" spans="2:28" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P24" s="92" t="s">
+        <v>242</v>
       </c>
       <c r="Q24" s="35"/>
       <c r="R24" s="35"/>
@@ -7326,8 +7427,8 @@
       <c r="AB24" s="35"/>
     </row>
     <row r="26" spans="2:28" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P26" s="35" t="s">
-        <v>210</v>
+      <c r="P26" s="92" t="s">
+        <v>209</v>
       </c>
       <c r="Q26" s="35"/>
       <c r="R26" s="35"/>
@@ -7345,7 +7446,7 @@
     <row r="27" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7353,25 +7454,25 @@
     </row>
     <row r="31" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="33" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B33" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="35" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="28" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B35" s="35" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C35" s="35"/>
       <c r="D35" s="35"/>
@@ -7402,7 +7503,7 @@
     </row>
     <row r="36" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="35" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C36" s="35"/>
       <c r="D36" s="35"/>
@@ -7433,7 +7534,7 @@
     </row>
     <row r="37" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="35" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C37" s="35"/>
       <c r="D37" s="35"/>
@@ -7464,7 +7565,7 @@
     </row>
     <row r="38" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
@@ -7495,7 +7596,7 @@
     </row>
     <row r="39" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="35" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C39" s="35"/>
       <c r="D39" s="35"/>
@@ -7526,7 +7627,7 @@
     </row>
     <row r="40" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="35" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C40" s="35"/>
       <c r="D40" s="35"/>
@@ -7557,7 +7658,7 @@
     </row>
     <row r="41" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B41" s="35" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C41" s="35"/>
       <c r="D41" s="35"/>
@@ -7588,7 +7689,7 @@
     </row>
     <row r="42" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B42" s="35" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C42" s="35"/>
       <c r="D42" s="35"/>
@@ -7619,7 +7720,7 @@
     </row>
     <row r="43" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B43" s="35" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C43" s="35"/>
       <c r="D43" s="35"/>
@@ -7650,7 +7751,7 @@
     </row>
     <row r="44" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B44" s="35" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C44" s="35"/>
       <c r="D44" s="35"/>
@@ -7681,7 +7782,7 @@
     </row>
     <row r="45" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B45" s="35" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C45" s="35"/>
       <c r="D45" s="35"/>
@@ -7712,7 +7813,7 @@
     </row>
     <row r="46" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B46" s="35" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C46" s="35"/>
       <c r="D46" s="35"/>
@@ -7743,7 +7844,7 @@
     </row>
     <row r="47" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B47" s="35" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C47" s="35"/>
       <c r="D47" s="35"/>
@@ -7774,7 +7875,7 @@
     </row>
     <row r="48" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B48" s="35" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C48" s="35"/>
       <c r="D48" s="35"/>
@@ -7805,7 +7906,7 @@
     </row>
     <row r="49" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B49" s="35" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C49" s="35"/>
       <c r="D49" s="35"/>
@@ -7836,7 +7937,7 @@
     </row>
     <row r="50" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B50" s="35" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C50" s="35"/>
       <c r="D50" s="35"/>
@@ -7867,7 +7968,7 @@
     </row>
     <row r="51" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B51" s="35" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C51" s="35"/>
       <c r="D51" s="35"/>
@@ -7898,7 +7999,7 @@
     </row>
     <row r="52" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B52" s="35" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C52" s="35"/>
       <c r="D52" s="35"/>
@@ -7929,12 +8030,12 @@
     </row>
     <row r="54" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B54" s="8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="55" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B55" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="56" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
@@ -7942,10 +8043,10 @@
     </row>
     <row r="57" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A57" s="28" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B57" s="35" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C57" s="35"/>
       <c r="D57" s="35"/>
@@ -7976,7 +8077,7 @@
     </row>
     <row r="58" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B58" s="35" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C58" s="35"/>
       <c r="D58" s="35"/>
@@ -8007,7 +8108,7 @@
     </row>
     <row r="59" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B59" s="35" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C59" s="35"/>
       <c r="D59" s="35"/>
@@ -8038,7 +8139,7 @@
     </row>
     <row r="60" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B60" s="35" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C60" s="35"/>
       <c r="D60" s="35"/>
@@ -8069,7 +8170,7 @@
     </row>
     <row r="61" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B61" s="35" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C61" s="35"/>
       <c r="D61" s="35"/>
@@ -8100,7 +8201,7 @@
     </row>
     <row r="62" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B62" s="35" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C62" s="35"/>
       <c r="D62" s="35"/>
@@ -8131,7 +8232,7 @@
     </row>
     <row r="63" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B63" s="35" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C63" s="35"/>
       <c r="D63" s="35"/>
@@ -8162,7 +8263,7 @@
     </row>
     <row r="64" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B64" s="35" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C64" s="35"/>
       <c r="D64" s="35"/>
@@ -8193,7 +8294,7 @@
     </row>
     <row r="65" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B65" s="35" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C65" s="35"/>
       <c r="D65" s="35"/>
@@ -8224,7 +8325,7 @@
     </row>
     <row r="66" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B66" s="35" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C66" s="35"/>
       <c r="D66" s="35"/>

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C8ADE5-33FF-4313-BAB9-D9EEA3D45D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35CFDA9-1782-468E-A848-257FC462E672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="UI &amp; Scene Set Up" sheetId="3" r:id="rId4"/>
     <sheet name="Item List" sheetId="4" r:id="rId5"/>
     <sheet name="Dialogues" sheetId="5" r:id="rId6"/>
+    <sheet name="Sound &amp; Music" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="296">
   <si>
     <t>SIGNOMALY</t>
   </si>
@@ -1496,9 +1497,6 @@
     <t>4. NPC</t>
   </si>
   <si>
-    <t>VII. Item lists</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Người chơi sẽ di chuyển bằng phím </t>
     </r>
@@ -1754,6 +1752,114 @@
     <t>Tinh chỉnh góc quay phù hợp khi bắt đầu cuộc đối thoại với NPC (Optional)</t>
   </si>
   <si>
+    <t>2. Lời đối thoại</t>
+  </si>
+  <si>
+    <t>You’ll become nothing more than entertainment for Them. Hahahaha…</t>
+  </si>
+  <si>
+    <t>***Lưu ý: Mỗi đoạn được viết dưới đây thì đều là từng đoạn sẽ hiển thị ra khi người chơi click chuột sang đoạn kế.</t>
+  </si>
+  <si>
+    <t>2.1. Tương tác lần đầu: hiển thị toàn bộ cuộc trò chuyện</t>
+  </si>
+  <si>
+    <t>***Lưu ý: không thể skip, double click chạy hết chữ, hay thoát ra ngoài vào gameplay.</t>
+  </si>
+  <si>
+    <t>***Lưu ý: lần tương tác thứ 2, người chơi sẽ được phép double click để chạy full đoạn đối thoại và nhảy sang đoạn đối thoại tiếp theo, được phép thoát ra ngoài.</t>
+  </si>
+  <si>
+    <t>Item ID</t>
+  </si>
+  <si>
+    <t>Điều kiện để tương tác với vật thể: Vật thể phải luôn trong tầm nhìn của người chơi; Phạm vi của vật thể phát hiện người chơi. Trong trường hợp có 2 vật thể thì chỉ cho người chơi tương tác với vật thể gần nhất.</t>
+  </si>
+  <si>
+    <t>2.2. Tương tác lần 2 trở đi: chỉ hiển thị chỉ dẫn cần thiết</t>
+  </si>
+  <si>
+    <t>FBX?</t>
+  </si>
+  <si>
+    <t>Chưa có</t>
+  </si>
+  <si>
+    <t>Đang Render</t>
+  </si>
+  <si>
+    <t>Heh… another one, huh? Are you really that greedy for money?</t>
+  </si>
+  <si>
+    <t>Well, everything comes at a price.</t>
+  </si>
+  <si>
+    <t>If you want the treasure, you’ll have to play the game just like the contract says.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Win, and you might walk away with that massive fortune. But lose… and we take no responsibility. </t>
+  </si>
+  <si>
+    <t>So… ready to step into hell?</t>
+  </si>
+  <si>
+    <t>Good. Here are the rules of our little game. See that door beside you, ahh the one with the… unusual requirement? That’s your way out. But to unlock it, you’ll need to fulfill two conditions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First, look at the door in front of you. </t>
+  </si>
+  <si>
+    <t>See the timer? Fifteen minutes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That’s all the time you have left to finish the game. </t>
+  </si>
+  <si>
+    <t>Meet the other condition before it hits zero, and the door will open. If not… hahaha.</t>
+  </si>
+  <si>
+    <t>Second, beyond this room lies a space filled with all sorts of objects. Your task is to find the anomalies among them.</t>
+  </si>
+  <si>
+    <t>If you suspect something’s off, stand your ground and face it directly, don’t look away. It will present you with a puzzle. Solve it, and you’ll set it free.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">But don’t get too corky. These anomalies aren’t as forgiving as I am. </t>
+  </si>
+  <si>
+    <t>Each of them has its own timer hovering overhead… and if their time runs out, it’s game over for you too. So keep your eyes sharp.</t>
+  </si>
+  <si>
+    <t>Free them all within the fifteen minutes I’ve given you, and the door will open. Walk through it, and that million-dollar prize is yours.</t>
+  </si>
+  <si>
+    <t>…assuming you can pull it off. Plenty have tried. Plenty have died. Turns out, if you want something valuable, you have to pay a matching price.</t>
+  </si>
+  <si>
+    <t>Good luck? I guess… and perhaps we’ll meet again or not, hahaha…</t>
+  </si>
+  <si>
+    <t>See that door beside you, ahh the one with the… unusual requirement? That’s your way out. But to unlock it, you’ll need to fulfill two conditions.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thời gian cho phép của puzzle giải đố (Timelapse nhỏ): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>7 phút.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Mico: </t>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
@@ -1800,7 +1906,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> không thể skip, double click</t>
+      <t xml:space="preserve"> không thể skip, không thể double click</t>
     </r>
     <r>
       <rPr>
@@ -1828,7 +1934,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> vào gameplay, mà phải xem hết một đoạn đối thoại, sau đó mới được click để sang đoạn tiếp theo. </t>
+      <t xml:space="preserve"> vào gameplay, mà phải xem hết một đoạn đối thoại, sau đó mới được click để sang đoạn tiếp theo. Để tiếp tục đoạn đối thoại, người chơi</t>
     </r>
     <r>
       <rPr>
@@ -1838,16 +1944,16 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>Để tiếp tục đoạn đối thoại</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>, người chơi</t>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>sẽ nhấn chuột trái. Ở</t>
     </r>
     <r>
       <rPr>
@@ -1857,16 +1963,16 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> sẽ nhấn chuột trái</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Ở</t>
+      <t xml:space="preserve"> lần tương tác thứ 2,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> người chơi sẽ </t>
     </r>
     <r>
       <rPr>
@@ -1876,16 +1982,16 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> lần tương tác thứ 2,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> người chơi sẽ </t>
+      <t xml:space="preserve">được phép double click </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">để chạy full đoạn đối thoại và nhảy sang đoạn đối thoại tiếp theo, </t>
     </r>
     <r>
       <rPr>
@@ -1895,16 +2001,16 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">được phép double click </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">để chạy full đoạn đối thoại và nhảy sang đoạn đối thoại tiếp theo, </t>
+      <t>được phép thoát ra ngoài</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> khi đang đối thoại. Nút để thoát ra ngoài là </t>
     </r>
     <r>
       <rPr>
@@ -1914,16 +2020,37 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>được phép thoát ra ngoài</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> khi đang đối thoại. Nút để thoát ra ngoài là </t>
+      <t>"ESCAPE"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Yêu cầu:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Khung đối thoại có </t>
     </r>
     <r>
       <rPr>
@@ -1933,115 +2060,98 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>"ESCAPE"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>2. Lời đối thoại</t>
-  </si>
-  <si>
-    <t>You’ll become nothing more than entertainment for Them. Hahahaha…</t>
-  </si>
-  <si>
-    <t>***Lưu ý: Mỗi đoạn được viết dưới đây thì đều là từng đoạn sẽ hiển thị ra khi người chơi click chuột sang đoạn kế.</t>
-  </si>
-  <si>
-    <t>2.1. Tương tác lần đầu: hiển thị toàn bộ cuộc trò chuyện</t>
-  </si>
-  <si>
-    <t>***Lưu ý: không thể skip, double click chạy hết chữ, hay thoát ra ngoài vào gameplay.</t>
-  </si>
-  <si>
-    <t>***Lưu ý: lần tương tác thứ 2, người chơi sẽ được phép double click để chạy full đoạn đối thoại và nhảy sang đoạn đối thoại tiếp theo, được phép thoát ra ngoài.</t>
-  </si>
-  <si>
-    <t>Item ID</t>
-  </si>
-  <si>
-    <t>Điều kiện để tương tác với vật thể: Vật thể phải luôn trong tầm nhìn của người chơi; Phạm vi của vật thể phát hiện người chơi. Trong trường hợp có 2 vật thể thì chỉ cho người chơi tương tác với vật thể gần nhất.</t>
-  </si>
-  <si>
-    <t>2.2. Tương tác lần 2 trở đi: chỉ hiển thị chỉ dẫn cần thiết</t>
-  </si>
-  <si>
-    <t>FBX?</t>
-  </si>
-  <si>
-    <t>Chưa có</t>
-  </si>
-  <si>
-    <t>Đang Render</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPC: </t>
-  </si>
-  <si>
-    <t>Heh… another one, huh? Are you really that greedy for money?</t>
-  </si>
-  <si>
-    <t>Well, everything comes at a price.</t>
-  </si>
-  <si>
-    <t>If you want the treasure, you’ll have to play the game just like the contract says.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Win, and you might walk away with that massive fortune. But lose… and we take no responsibility. </t>
-  </si>
-  <si>
-    <t>So… ready to step into hell?</t>
-  </si>
-  <si>
-    <t>Good. Here are the rules of our little game. See that door beside you, ahh the one with the… unusual requirement? That’s your way out. But to unlock it, you’ll need to fulfill two conditions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First, look at the door in front of you. </t>
-  </si>
-  <si>
-    <t>See the timer? Fifteen minutes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">That’s all the time you have left to finish the game. </t>
-  </si>
-  <si>
-    <t>Meet the other condition before it hits zero, and the door will open. If not… hahaha.</t>
-  </si>
-  <si>
-    <t>Second, beyond this room lies a space filled with all sorts of objects. Your task is to find the anomalies among them.</t>
-  </si>
-  <si>
-    <t>If you suspect something’s off, stand your ground and face it directly, don’t look away. It will present you with a puzzle. Solve it, and you’ll set it free.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">But don’t get too corky. These anomalies aren’t as forgiving as I am. </t>
-  </si>
-  <si>
-    <t>Each of them has its own timer hovering overhead… and if their time runs out, it’s game over for you too. So keep your eyes sharp.</t>
-  </si>
-  <si>
-    <t>Free them all within the fifteen minutes I’ve given you, and the door will open. Walk through it, and that million-dollar prize is yours.</t>
-  </si>
-  <si>
-    <t>…assuming you can pull it off. Plenty have tried. Plenty have died. Turns out, if you want something valuable, you have to pay a matching price.</t>
-  </si>
-  <si>
-    <t>Good luck? I guess… and perhaps we’ll meet again or not, hahaha…</t>
-  </si>
-  <si>
-    <t>See that door beside you, ahh the one with the… unusual requirement? That’s your way out. But to unlock it, you’ll need to fulfill two conditions.</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
+      <t>màu đen constrast cao</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, độ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>opacity cần là 60%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> để đảm bảo vẫn nhìn rõ môi trường đằng sau. Cần có tên người nói hiển thị ở góc trên đoạn đối thoại (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>tên người nói màu Trắng, brightness thấp hơn đối thoại và viết hoa chữ cái đầu)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Đoạn đối thoại </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>cần viết thường, và chỉ viết hoa chữ cái đầu sau dấu chấm (đoạn đối thoại màu trắng, với brightness cao hơn tên)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Cần có </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>icon chuột chớp nháy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> để người chơi biết hết đoạn đối thoại và qua phần kế.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
     <r>
       <rPr>
         <u/>
@@ -2050,16 +2160,16 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>Yêu cầu:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Khung đối thoại có </t>
+      <t>Puzzle:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> là những câu đố xuyên suốt trong game, có số lượng tối đa là </t>
     </r>
     <r>
       <rPr>
@@ -2069,16 +2179,16 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>màu đen constrast cao</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, độ </t>
+      <t>2 loại puzzles (giải đố/ tìm đồ vật)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Người chơi cần giải được các câu đố để hoàn thành </t>
     </r>
     <r>
       <rPr>
@@ -2088,16 +2198,36 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>opacity cần là 60%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> để đảm bảo vẫn nhìn rõ môi trường đằng sau. Cần có tên người nói hiển thị ở góc trên đoạn đối thoại (</t>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> "Điều kiện tổng".
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Thời gian 2 loại puzzle sẽ có sự biến đổi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> sẽ khoảng </t>
     </r>
     <r>
       <rPr>
@@ -2107,16 +2237,16 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>tên người nói màu Trắng, brightness thấp hơn đối thoại và viết hoa chữ cái đầu)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. Đoạn đối thoại </t>
+      <t>15-30 giây</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> và chúng sẽ không xảy ra đồng thời với nhau. Ngoài ra sau khi biến đổi nó sẽ giữ nguyên trạng thái trong khoảng </t>
     </r>
     <r>
       <rPr>
@@ -2126,79 +2256,16 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>cần viết thường, và chỉ viết hoa chữ cái đầu sau dấu chấm (đoạn đối thoại màu trắng, với brightness cao hơn tên)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Cần có icon chuột chớp nháy để người chơi biết hết đoạn đối thoại và qua phần kế.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">- </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Puzzle:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> là những câu đố xuyên suốt trong game, có số lượng tối đa là </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2 loại puzzles (giải đố/ tìm đồ vật)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. Người chơi cần giải được các câu đố để hoàn thành </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> "Điều kiện tổng".
-- Cả 2 loại puzzle đều sẽ có sự biến đổi cứ khoảng 15-20 giây và chúng sẽ không xảy ra đồng thời với nhau. Ngoài ra sau khi biến đổi nó sẽ giữ nguyên trạng thái trong khoảng 7 giây rồi quay về trạng thái cũ.
+      <t>3 giây</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> rồi quay về trạng thái cũ.
 - </t>
     </r>
     <r>
@@ -2357,15 +2424,180 @@
       </rPr>
       <t xml:space="preserve"> ngay lập tức.</t>
     </r>
+  </si>
+  <si>
+    <t>IX. Soundfx</t>
+  </si>
+  <si>
+    <t>SoundID</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Human</t>
+  </si>
+  <si>
+    <t>H_Footstep</t>
+  </si>
+  <si>
+    <t>Khi người chơi di chuyển</t>
+  </si>
+  <si>
+    <t>Sync theo tốc độ người chơi</t>
+  </si>
+  <si>
+    <t>Object</t>
+  </si>
+  <si>
+    <t>Khi puzzle biến đổi</t>
+  </si>
+  <si>
+    <t>Condition</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>3-5s</t>
+  </si>
+  <si>
+    <t>3s</t>
+  </si>
+  <si>
+    <t>E_Puzzle</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>Khi người chơi tương tác</t>
+  </si>
+  <si>
+    <t>2s</t>
+  </si>
+  <si>
+    <t>Duration (s)</t>
+  </si>
+  <si>
+    <t>Number of Times</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loop </t>
+  </si>
+  <si>
+    <t>Xảy ra khi gười chơi tương tác Object X, Y</t>
+  </si>
+  <si>
+    <t>3-4s</t>
+  </si>
+  <si>
+    <t>Khi người chơi thả object</t>
+  </si>
+  <si>
+    <t>Xảy ra khi người chơi thả Object X, Y</t>
+  </si>
+  <si>
+    <t>O_ObjectInter</t>
+  </si>
+  <si>
+    <t>O_ObjectDrop</t>
+  </si>
+  <si>
+    <t>O_Paper</t>
+  </si>
+  <si>
+    <t>Người chơi mở xem nội dung</t>
+  </si>
+  <si>
+    <t>Người chơi xem các tài liêu, document sẽ trigger</t>
+  </si>
+  <si>
+    <t>Applied for</t>
+  </si>
+  <si>
+    <t>Main Character</t>
+  </si>
+  <si>
+    <t>PZ_PICTURE1; PZ_PICTURE2</t>
+  </si>
+  <si>
+    <t>1.  ITEMS</t>
+  </si>
+  <si>
+    <t>VII. 3D ASSETS</t>
+  </si>
+  <si>
+    <t>2. CONSTRUCTION</t>
+  </si>
+  <si>
+    <t>C_Wall</t>
+  </si>
+  <si>
+    <t>C_Floor</t>
+  </si>
+  <si>
+    <t>C_Door</t>
+  </si>
+  <si>
+    <t>Tường</t>
+  </si>
+  <si>
+    <t>Sàn</t>
+  </si>
+  <si>
+    <t>Cửa</t>
+  </si>
+  <si>
+    <t>All the X/Y/PZ_Objects (Except X_Statue)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All the Y/INS_Objects </t>
+  </si>
+  <si>
+    <t>O_Mico</t>
+  </si>
+  <si>
+    <t>Các đoạn đối thoại bằng chữ với MICO sẽ có âm thanh phím</t>
+  </si>
+  <si>
+    <t>Không trực tiếp phát ra tại Puzzle (= âm thanh xung quanh)</t>
+  </si>
+  <si>
+    <t>E_Time</t>
+  </si>
+  <si>
+    <t>Always on</t>
+  </si>
+  <si>
+    <t>1-3s</t>
+  </si>
+  <si>
+    <t>40px (Main Title); 56px (GameOver);  32px (Timer, Mã Code)</t>
+  </si>
+  <si>
+    <t>22px (Menu, tên section); 16px (Panel header HUD); 13px (Status)</t>
+  </si>
+  <si>
+    <t>12px (Log text, mô tả); 11px (Timestamp,Log); 9px (Label, tag)</t>
+  </si>
+  <si>
+    <t>FONT SIZE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="15"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2509,7 +2741,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2528,8 +2760,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -2589,259 +2827,378 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3222,8 +3579,8 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>604610</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>238125</xdr:rowOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>457200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3404,13 +3761,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>9524</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>10477</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3465,13 +3822,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>134937</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>102753</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3525,15 +3882,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>590549</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>238125</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>321056</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>435357</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>29202</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3556,8 +3913,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="590549" y="1123950"/>
-          <a:ext cx="5826507" cy="6715125"/>
+          <a:off x="76200" y="1095375"/>
+          <a:ext cx="6455157" cy="7439652"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3614,13 +3971,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>9526</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>133946</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3675,13 +4032,13 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>131564</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3862,15 +4219,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
+      <xdr:colOff>429577</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>1301857</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>15982</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3900,8 +4257,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2800350" y="3686175"/>
-          <a:ext cx="5629275" cy="3816457"/>
+          <a:off x="2867977" y="3867150"/>
+          <a:ext cx="5685473" cy="3854557"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4247,29 +4604,29 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:26" ht="46.5" x14ac:dyDescent="0.7">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="36"/>
-      <c r="S1" s="36"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
     </row>
     <row r="3" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
@@ -4293,104 +4650,104 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="42" t="s">
-        <v>175</v>
-      </c>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
+      <c r="B12" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
     </row>
     <row r="13" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="41"/>
-      <c r="O13" s="41"/>
-      <c r="P13" s="41"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="41"/>
-      <c r="S13" s="41"/>
-      <c r="T13" s="41"/>
-      <c r="U13" s="41"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="45"/>
+      <c r="M13" s="45"/>
+      <c r="N13" s="45"/>
+      <c r="O13" s="45"/>
+      <c r="P13" s="45"/>
+      <c r="Q13" s="45"/>
+      <c r="R13" s="45"/>
+      <c r="S13" s="45"/>
+      <c r="T13" s="45"/>
+      <c r="U13" s="45"/>
     </row>
     <row r="14" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="37"/>
-      <c r="L14" s="37"/>
-      <c r="M14" s="37"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="37"/>
-      <c r="S14" s="37"/>
-      <c r="T14" s="37"/>
-      <c r="U14" s="37"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="42"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="42"/>
+      <c r="R14" s="42"/>
+      <c r="S14" s="42"/>
+      <c r="T14" s="42"/>
+      <c r="U14" s="42"/>
     </row>
     <row r="15" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
@@ -4406,28 +4763,28 @@
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:26" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="38"/>
-      <c r="P16" s="38"/>
-      <c r="Q16" s="38"/>
-      <c r="R16" s="38"/>
-      <c r="S16" s="38"/>
-      <c r="T16" s="38"/>
-      <c r="U16" s="38"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="40"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="40"/>
+      <c r="R16" s="40"/>
+      <c r="S16" s="40"/>
+      <c r="T16" s="40"/>
+      <c r="U16" s="40"/>
       <c r="V16" s="6"/>
       <c r="W16" s="6"/>
       <c r="X16" s="6"/>
@@ -4435,100 +4792,100 @@
       <c r="Z16" s="6"/>
     </row>
     <row r="17" spans="1:21" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="38"/>
-      <c r="P17" s="38"/>
-      <c r="Q17" s="38"/>
-      <c r="R17" s="38"/>
-      <c r="S17" s="38"/>
-      <c r="T17" s="38"/>
-      <c r="U17" s="38"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="40"/>
+      <c r="P17" s="40"/>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="40"/>
+      <c r="S17" s="40"/>
+      <c r="T17" s="40"/>
+      <c r="U17" s="40"/>
     </row>
     <row r="18" spans="1:21" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="37" t="s">
+      <c r="B18" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="37"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="37"/>
-      <c r="S18" s="37"/>
-      <c r="T18" s="37"/>
-      <c r="U18" s="37"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="42"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="42"/>
+      <c r="R18" s="42"/>
+      <c r="S18" s="42"/>
+      <c r="T18" s="42"/>
+      <c r="U18" s="42"/>
     </row>
     <row r="19" spans="1:21" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="40"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="40"/>
-      <c r="P19" s="40"/>
-      <c r="Q19" s="40"/>
-      <c r="R19" s="40"/>
-      <c r="S19" s="40"/>
-      <c r="T19" s="40"/>
-      <c r="U19" s="40"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="44"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="44"/>
+      <c r="P19" s="44"/>
+      <c r="Q19" s="44"/>
+      <c r="R19" s="44"/>
+      <c r="S19" s="44"/>
+      <c r="T19" s="44"/>
+      <c r="U19" s="44"/>
     </row>
     <row r="20" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="43"/>
-      <c r="P20" s="43"/>
-      <c r="Q20" s="43"/>
-      <c r="R20" s="43"/>
-      <c r="S20" s="43"/>
-      <c r="T20" s="43"/>
-      <c r="U20" s="43"/>
+      <c r="B20" s="37" t="s">
+        <v>175</v>
+      </c>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="37"/>
+      <c r="M20" s="37"/>
+      <c r="N20" s="37"/>
+      <c r="O20" s="37"/>
+      <c r="P20" s="37"/>
+      <c r="Q20" s="37"/>
+      <c r="R20" s="37"/>
+      <c r="S20" s="37"/>
+      <c r="T20" s="37"/>
+      <c r="U20" s="37"/>
     </row>
     <row r="22" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
@@ -4641,11 +4998,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B20:U20"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B16:U16"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="B18:U18"/>
     <mergeCell ref="B17:U17"/>
@@ -4653,6 +5005,11 @@
     <mergeCell ref="B14:U14"/>
     <mergeCell ref="B13:U13"/>
     <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B20:U20"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B16:U16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4676,50 +5033,50 @@
       <c r="B4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55" t="s">
+      <c r="D4" s="48"/>
+      <c r="E4" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="55"/>
-      <c r="G4" s="46" t="s">
+      <c r="F4" s="48"/>
+      <c r="G4" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="46" t="s">
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="46"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="46"/>
-      <c r="S4" s="46"/>
-      <c r="T4" s="46"/>
-      <c r="U4" s="46"/>
-      <c r="V4" s="46"/>
-      <c r="W4" s="46"/>
-      <c r="X4" s="46"/>
-      <c r="Y4" s="46"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="52"/>
+      <c r="P4" s="52"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="52"/>
+      <c r="V4" s="52"/>
+      <c r="W4" s="52"/>
+      <c r="X4" s="52"/>
+      <c r="Y4" s="52"/>
     </row>
     <row r="5" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11">
         <v>1</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="53" t="s">
+      <c r="D5" s="49"/>
+      <c r="E5" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="53"/>
+      <c r="F5" s="50"/>
       <c r="G5" s="51" t="s">
         <v>30</v>
       </c>
@@ -4728,32 +5085,32 @@
       <c r="J5" s="51"/>
       <c r="K5" s="51"/>
       <c r="L5" s="51"/>
-      <c r="M5" s="47" t="s">
+      <c r="M5" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="N5" s="47"/>
-      <c r="O5" s="47"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="47"/>
-      <c r="R5" s="47"/>
-      <c r="S5" s="47"/>
-      <c r="T5" s="47"/>
-      <c r="U5" s="47"/>
-      <c r="V5" s="47"/>
-      <c r="W5" s="47"/>
-      <c r="X5" s="47"/>
-      <c r="Y5" s="47"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
+      <c r="S5" s="55"/>
+      <c r="T5" s="55"/>
+      <c r="U5" s="55"/>
+      <c r="V5" s="55"/>
+      <c r="W5" s="55"/>
+      <c r="X5" s="55"/>
+      <c r="Y5" s="55"/>
     </row>
     <row r="6" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11">
         <v>2</v>
       </c>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="53" t="s">
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="53"/>
+      <c r="F6" s="50"/>
       <c r="G6" s="51" t="s">
         <v>31</v>
       </c>
@@ -4762,32 +5119,32 @@
       <c r="J6" s="51"/>
       <c r="K6" s="51"/>
       <c r="L6" s="51"/>
-      <c r="M6" s="48" t="s">
+      <c r="M6" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="47"/>
-      <c r="Q6" s="47"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47"/>
-      <c r="T6" s="47"/>
-      <c r="U6" s="47"/>
-      <c r="V6" s="47"/>
-      <c r="W6" s="47"/>
-      <c r="X6" s="47"/>
-      <c r="Y6" s="47"/>
+      <c r="N6" s="55"/>
+      <c r="O6" s="55"/>
+      <c r="P6" s="55"/>
+      <c r="Q6" s="55"/>
+      <c r="R6" s="55"/>
+      <c r="S6" s="55"/>
+      <c r="T6" s="55"/>
+      <c r="U6" s="55"/>
+      <c r="V6" s="55"/>
+      <c r="W6" s="55"/>
+      <c r="X6" s="55"/>
+      <c r="Y6" s="55"/>
     </row>
     <row r="7" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11">
         <v>3</v>
       </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="53" t="s">
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="53"/>
+      <c r="F7" s="50"/>
       <c r="G7" s="51" t="s">
         <v>46</v>
       </c>
@@ -4796,34 +5153,34 @@
       <c r="J7" s="51"/>
       <c r="K7" s="51"/>
       <c r="L7" s="51"/>
-      <c r="M7" s="49" t="s">
+      <c r="M7" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="49"/>
-      <c r="R7" s="49"/>
-      <c r="S7" s="49"/>
-      <c r="T7" s="49"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="49"/>
-      <c r="W7" s="49"/>
-      <c r="X7" s="49"/>
-      <c r="Y7" s="49"/>
+      <c r="N7" s="54"/>
+      <c r="O7" s="54"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="54"/>
+      <c r="T7" s="54"/>
+      <c r="U7" s="54"/>
+      <c r="V7" s="54"/>
+      <c r="W7" s="54"/>
+      <c r="X7" s="54"/>
+      <c r="Y7" s="54"/>
     </row>
     <row r="8" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11">
         <v>4</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="52"/>
-      <c r="E8" s="53" t="s">
+      <c r="D8" s="49"/>
+      <c r="E8" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="53"/>
+      <c r="F8" s="50"/>
       <c r="G8" s="51" t="s">
         <v>32</v>
       </c>
@@ -4832,32 +5189,32 @@
       <c r="J8" s="51"/>
       <c r="K8" s="51"/>
       <c r="L8" s="51"/>
-      <c r="M8" s="50" t="s">
+      <c r="M8" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="N8" s="49"/>
-      <c r="O8" s="49"/>
-      <c r="P8" s="49"/>
-      <c r="Q8" s="49"/>
-      <c r="R8" s="49"/>
-      <c r="S8" s="49"/>
-      <c r="T8" s="49"/>
-      <c r="U8" s="49"/>
-      <c r="V8" s="49"/>
-      <c r="W8" s="49"/>
-      <c r="X8" s="49"/>
-      <c r="Y8" s="49"/>
+      <c r="N8" s="54"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="54"/>
+      <c r="Q8" s="54"/>
+      <c r="R8" s="54"/>
+      <c r="S8" s="54"/>
+      <c r="T8" s="54"/>
+      <c r="U8" s="54"/>
+      <c r="V8" s="54"/>
+      <c r="W8" s="54"/>
+      <c r="X8" s="54"/>
+      <c r="Y8" s="54"/>
     </row>
     <row r="9" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11">
         <v>5</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="53" t="s">
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="53"/>
+      <c r="F9" s="50"/>
       <c r="G9" s="51" t="s">
         <v>33</v>
       </c>
@@ -4866,32 +5223,32 @@
       <c r="J9" s="51"/>
       <c r="K9" s="51"/>
       <c r="L9" s="51"/>
-      <c r="M9" s="50" t="s">
+      <c r="M9" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="49"/>
-      <c r="O9" s="49"/>
-      <c r="P9" s="49"/>
-      <c r="Q9" s="49"/>
-      <c r="R9" s="49"/>
-      <c r="S9" s="49"/>
-      <c r="T9" s="49"/>
-      <c r="U9" s="49"/>
-      <c r="V9" s="49"/>
-      <c r="W9" s="49"/>
-      <c r="X9" s="49"/>
-      <c r="Y9" s="49"/>
+      <c r="N9" s="54"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="54"/>
+      <c r="Q9" s="54"/>
+      <c r="R9" s="54"/>
+      <c r="S9" s="54"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="54"/>
+      <c r="V9" s="54"/>
+      <c r="W9" s="54"/>
+      <c r="X9" s="54"/>
+      <c r="Y9" s="54"/>
     </row>
     <row r="10" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="11">
         <v>6</v>
       </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="53" t="s">
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="53"/>
+      <c r="F10" s="50"/>
       <c r="G10" s="51" t="s">
         <v>34</v>
       </c>
@@ -4900,32 +5257,32 @@
       <c r="J10" s="51"/>
       <c r="K10" s="51"/>
       <c r="L10" s="51"/>
-      <c r="M10" s="50" t="s">
+      <c r="M10" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="N10" s="49"/>
-      <c r="O10" s="49"/>
-      <c r="P10" s="49"/>
-      <c r="Q10" s="49"/>
-      <c r="R10" s="49"/>
-      <c r="S10" s="49"/>
-      <c r="T10" s="49"/>
-      <c r="U10" s="49"/>
-      <c r="V10" s="49"/>
-      <c r="W10" s="49"/>
-      <c r="X10" s="49"/>
-      <c r="Y10" s="49"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="54"/>
+      <c r="R10" s="54"/>
+      <c r="S10" s="54"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="54"/>
+      <c r="V10" s="54"/>
+      <c r="W10" s="54"/>
+      <c r="X10" s="54"/>
+      <c r="Y10" s="54"/>
     </row>
     <row r="11" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="11">
         <v>7</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="53" t="s">
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="53"/>
+      <c r="F11" s="50"/>
       <c r="G11" s="51" t="s">
         <v>37</v>
       </c>
@@ -4934,34 +5291,34 @@
       <c r="J11" s="51"/>
       <c r="K11" s="51"/>
       <c r="L11" s="51"/>
-      <c r="M11" s="49" t="s">
+      <c r="M11" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="49"/>
-      <c r="O11" s="49"/>
-      <c r="P11" s="49"/>
-      <c r="Q11" s="49"/>
-      <c r="R11" s="49"/>
-      <c r="S11" s="49"/>
-      <c r="T11" s="49"/>
-      <c r="U11" s="49"/>
-      <c r="V11" s="49"/>
-      <c r="W11" s="49"/>
-      <c r="X11" s="49"/>
-      <c r="Y11" s="49"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="54"/>
+      <c r="S11" s="54"/>
+      <c r="T11" s="54"/>
+      <c r="U11" s="54"/>
+      <c r="V11" s="54"/>
+      <c r="W11" s="54"/>
+      <c r="X11" s="54"/>
+      <c r="Y11" s="54"/>
     </row>
     <row r="12" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="11">
         <v>8</v>
       </c>
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="52"/>
-      <c r="E12" s="53" t="s">
+      <c r="D12" s="49"/>
+      <c r="E12" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="53"/>
+      <c r="F12" s="50"/>
       <c r="G12" s="51" t="s">
         <v>35</v>
       </c>
@@ -4970,76 +5327,97 @@
       <c r="J12" s="51"/>
       <c r="K12" s="51"/>
       <c r="L12" s="51"/>
-      <c r="M12" s="49" t="s">
+      <c r="M12" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="N12" s="49"/>
-      <c r="O12" s="49"/>
-      <c r="P12" s="49"/>
-      <c r="Q12" s="49"/>
-      <c r="R12" s="49"/>
-      <c r="S12" s="49"/>
-      <c r="T12" s="49"/>
-      <c r="U12" s="49"/>
-      <c r="V12" s="49"/>
-      <c r="W12" s="49"/>
-      <c r="X12" s="49"/>
-      <c r="Y12" s="49"/>
+      <c r="N12" s="54"/>
+      <c r="O12" s="54"/>
+      <c r="P12" s="54"/>
+      <c r="Q12" s="54"/>
+      <c r="R12" s="54"/>
+      <c r="S12" s="54"/>
+      <c r="T12" s="54"/>
+      <c r="U12" s="54"/>
+      <c r="V12" s="54"/>
+      <c r="W12" s="54"/>
+      <c r="X12" s="54"/>
+      <c r="Y12" s="54"/>
     </row>
     <row r="46" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B49" s="54" t="s">
+      <c r="B49" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="54"/>
-      <c r="D49" s="54"/>
-      <c r="E49" s="54"/>
-      <c r="F49" s="54"/>
-      <c r="G49" s="54"/>
-      <c r="H49" s="54"/>
-      <c r="I49" s="54"/>
-      <c r="J49" s="54"/>
-      <c r="K49" s="54"/>
-      <c r="L49" s="54"/>
-      <c r="M49" s="54"/>
-      <c r="N49" s="54"/>
-      <c r="O49" s="54"/>
-      <c r="P49" s="54"/>
-      <c r="Q49" s="54"/>
-      <c r="R49" s="54"/>
-      <c r="S49" s="54"/>
-      <c r="T49" s="54"/>
-      <c r="U49" s="54"/>
-      <c r="V49" s="54"/>
+      <c r="C49" s="47"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="47"/>
+      <c r="G49" s="47"/>
+      <c r="H49" s="47"/>
+      <c r="I49" s="47"/>
+      <c r="J49" s="47"/>
+      <c r="K49" s="47"/>
+      <c r="L49" s="47"/>
+      <c r="M49" s="47"/>
+      <c r="N49" s="47"/>
+      <c r="O49" s="47"/>
+      <c r="P49" s="47"/>
+      <c r="Q49" s="47"/>
+      <c r="R49" s="47"/>
+      <c r="S49" s="47"/>
+      <c r="T49" s="47"/>
+      <c r="U49" s="47"/>
+      <c r="V49" s="47"/>
     </row>
     <row r="50" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B50" s="54"/>
-      <c r="C50" s="54"/>
-      <c r="D50" s="54"/>
-      <c r="E50" s="54"/>
-      <c r="F50" s="54"/>
-      <c r="G50" s="54"/>
-      <c r="H50" s="54"/>
-      <c r="I50" s="54"/>
-      <c r="J50" s="54"/>
-      <c r="K50" s="54"/>
-      <c r="L50" s="54"/>
-      <c r="M50" s="54"/>
-      <c r="N50" s="54"/>
-      <c r="O50" s="54"/>
-      <c r="P50" s="54"/>
-      <c r="Q50" s="54"/>
-      <c r="R50" s="54"/>
-      <c r="S50" s="54"/>
-      <c r="T50" s="54"/>
-      <c r="U50" s="54"/>
-      <c r="V50" s="54"/>
+      <c r="B50" s="47"/>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="47"/>
+      <c r="G50" s="47"/>
+      <c r="H50" s="47"/>
+      <c r="I50" s="47"/>
+      <c r="J50" s="47"/>
+      <c r="K50" s="47"/>
+      <c r="L50" s="47"/>
+      <c r="M50" s="47"/>
+      <c r="N50" s="47"/>
+      <c r="O50" s="47"/>
+      <c r="P50" s="47"/>
+      <c r="Q50" s="47"/>
+      <c r="R50" s="47"/>
+      <c r="S50" s="47"/>
+      <c r="T50" s="47"/>
+      <c r="U50" s="47"/>
+      <c r="V50" s="47"/>
       <c r="W50" s="8"/>
       <c r="X50" s="8"/>
       <c r="Y50" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="M4:Y4"/>
+    <mergeCell ref="M5:Y5"/>
+    <mergeCell ref="M6:Y6"/>
+    <mergeCell ref="M7:Y7"/>
+    <mergeCell ref="M8:Y8"/>
+    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="M11:Y11"/>
+    <mergeCell ref="M12:Y12"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="M10:Y10"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="M9:Y9"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
     <mergeCell ref="B49:V50"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
@@ -5056,27 +5434,6 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="M10:Y10"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="M9:Y9"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="M11:Y11"/>
-    <mergeCell ref="M12:Y12"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="M4:Y4"/>
-    <mergeCell ref="M5:Y5"/>
-    <mergeCell ref="M6:Y6"/>
-    <mergeCell ref="M7:Y7"/>
-    <mergeCell ref="M8:Y8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5088,7 +5445,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A2:AC78"/>
+  <dimension ref="A2:AC80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:28" ht="26.25" x14ac:dyDescent="0.4">
@@ -5102,20 +5459,20 @@
       </c>
     </row>
     <row r="8" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L8" s="57" t="s">
+      <c r="L8" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="M8" s="58"/>
-      <c r="N8" s="58"/>
-      <c r="O8" s="58"/>
-      <c r="P8" s="58"/>
-      <c r="Q8" s="58"/>
-      <c r="R8" s="58"/>
-      <c r="S8" s="58"/>
-      <c r="T8" s="58"/>
-      <c r="U8" s="58"/>
-      <c r="V8" s="58"/>
-      <c r="W8" s="58"/>
+      <c r="M8" s="65"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="65"/>
+      <c r="Q8" s="65"/>
+      <c r="R8" s="65"/>
+      <c r="S8" s="65"/>
+      <c r="T8" s="65"/>
+      <c r="U8" s="65"/>
+      <c r="V8" s="65"/>
+      <c r="W8" s="65"/>
     </row>
     <row r="9" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="L9" s="7"/>
@@ -5132,25 +5489,25 @@
       <c r="W9" s="7"/>
     </row>
     <row r="10" spans="1:28" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L10" s="35" t="s">
+      <c r="L10" s="58" t="s">
         <v>63</v>
       </c>
-      <c r="M10" s="39"/>
-      <c r="N10" s="39"/>
-      <c r="O10" s="39"/>
-      <c r="P10" s="39"/>
-      <c r="Q10" s="39"/>
-      <c r="R10" s="39"/>
-      <c r="S10" s="39"/>
-      <c r="T10" s="39"/>
-      <c r="U10" s="39"/>
-      <c r="V10" s="39"/>
-      <c r="W10" s="39"/>
-      <c r="X10" s="39"/>
-      <c r="Y10" s="39"/>
-      <c r="Z10" s="39"/>
-      <c r="AA10" s="39"/>
-      <c r="AB10" s="39"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="43"/>
+      <c r="X10" s="43"/>
+      <c r="Y10" s="43"/>
+      <c r="Z10" s="43"/>
+      <c r="AA10" s="43"/>
+      <c r="AB10" s="43"/>
     </row>
     <row r="11" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="L11" s="7"/>
@@ -5167,25 +5524,25 @@
       <c r="W11" s="7"/>
     </row>
     <row r="12" spans="1:28" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L12" s="35" t="s">
+      <c r="L12" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="M12" s="40"/>
-      <c r="N12" s="40"/>
-      <c r="O12" s="40"/>
-      <c r="P12" s="40"/>
-      <c r="Q12" s="40"/>
-      <c r="R12" s="40"/>
-      <c r="S12" s="40"/>
-      <c r="T12" s="40"/>
-      <c r="U12" s="40"/>
-      <c r="V12" s="40"/>
-      <c r="W12" s="40"/>
-      <c r="X12" s="40"/>
-      <c r="Y12" s="40"/>
-      <c r="Z12" s="40"/>
-      <c r="AA12" s="40"/>
-      <c r="AB12" s="40"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
+      <c r="T12" s="44"/>
+      <c r="U12" s="44"/>
+      <c r="V12" s="44"/>
+      <c r="W12" s="44"/>
+      <c r="X12" s="44"/>
+      <c r="Y12" s="44"/>
+      <c r="Z12" s="44"/>
+      <c r="AA12" s="44"/>
+      <c r="AB12" s="44"/>
     </row>
     <row r="13" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="S13" s="12"/>
@@ -5198,38 +5555,39 @@
     <row r="16" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B16" s="8"/>
     </row>
-    <row r="17" spans="2:28" ht="138" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="93" t="s">
-        <v>243</v>
-      </c>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="61"/>
-      <c r="K17" s="61"/>
-      <c r="L17" s="61"/>
-      <c r="M17" s="61"/>
-      <c r="N17" s="61"/>
-      <c r="O17" s="61"/>
-      <c r="P17" s="61"/>
-      <c r="Q17" s="61"/>
-      <c r="R17" s="61"/>
-      <c r="S17" s="61"/>
-      <c r="T17" s="61"/>
-      <c r="U17" s="61"/>
-      <c r="V17" s="61"/>
-      <c r="W17" s="61"/>
-      <c r="X17" s="61"/>
-      <c r="Y17" s="61"/>
-      <c r="Z17" s="61"/>
-      <c r="AA17" s="61"/>
-      <c r="AB17" s="61"/>
-    </row>
-    <row r="18" spans="2:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:29" ht="138" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="95" t="s">
+        <v>242</v>
+      </c>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="95"/>
+      <c r="K17" s="95"/>
+      <c r="L17" s="95"/>
+      <c r="M17" s="95"/>
+      <c r="N17" s="95"/>
+      <c r="O17" s="95"/>
+      <c r="P17" s="95"/>
+      <c r="Q17" s="95"/>
+      <c r="R17" s="95"/>
+      <c r="S17" s="95"/>
+      <c r="T17" s="95"/>
+      <c r="U17" s="95"/>
+      <c r="V17" s="95"/>
+      <c r="W17" s="95"/>
+      <c r="X17" s="95"/>
+      <c r="Y17" s="95"/>
+      <c r="Z17" s="95"/>
+      <c r="AA17" s="95"/>
+      <c r="AB17" s="95"/>
+      <c r="AC17" s="95"/>
+    </row>
+    <row r="18" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="15"/>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
@@ -5255,50 +5613,50 @@
       <c r="X18" s="16"/>
       <c r="Y18" s="16"/>
     </row>
-    <row r="20" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
         <v>41</v>
       </c>
       <c r="C20" s="10"/>
     </row>
-    <row r="22" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="P22" s="59" t="s">
+    <row r="22" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="P22" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="Q22" s="59"/>
-      <c r="R22" s="59"/>
-      <c r="S22" s="59"/>
-      <c r="T22" s="59"/>
-      <c r="U22" s="59"/>
-      <c r="V22" s="59"/>
-      <c r="W22" s="59"/>
-      <c r="X22" s="59"/>
-      <c r="Y22" s="59"/>
-      <c r="Z22" s="59"/>
-      <c r="AA22" s="59"/>
-      <c r="AB22" s="59"/>
-    </row>
-    <row r="23" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="Q22" s="66"/>
+      <c r="R22" s="66"/>
+      <c r="S22" s="66"/>
+      <c r="T22" s="66"/>
+      <c r="U22" s="66"/>
+      <c r="V22" s="66"/>
+      <c r="W22" s="66"/>
+      <c r="X22" s="66"/>
+      <c r="Y22" s="66"/>
+      <c r="Z22" s="66"/>
+      <c r="AA22" s="66"/>
+      <c r="AB22" s="66"/>
+    </row>
+    <row r="23" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P23" s="12"/>
     </row>
-    <row r="24" spans="2:28" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P24" s="56" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q24" s="60"/>
-      <c r="R24" s="60"/>
-      <c r="S24" s="60"/>
-      <c r="T24" s="60"/>
-      <c r="U24" s="60"/>
-      <c r="V24" s="60"/>
-      <c r="W24" s="60"/>
-      <c r="X24" s="60"/>
-      <c r="Y24" s="60"/>
-      <c r="Z24" s="60"/>
-      <c r="AA24" s="60"/>
-      <c r="AB24" s="60"/>
-    </row>
-    <row r="25" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:29" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P24" s="62" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="67"/>
+      <c r="S24" s="67"/>
+      <c r="T24" s="67"/>
+      <c r="U24" s="67"/>
+      <c r="V24" s="67"/>
+      <c r="W24" s="67"/>
+      <c r="X24" s="67"/>
+      <c r="Y24" s="67"/>
+      <c r="Z24" s="67"/>
+      <c r="AA24" s="67"/>
+      <c r="AB24" s="67"/>
+    </row>
+    <row r="25" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P25" s="19"/>
       <c r="Q25" s="17"/>
       <c r="R25" s="17"/>
@@ -5313,24 +5671,24 @@
       <c r="AA25" s="17"/>
       <c r="AB25" s="17"/>
     </row>
-    <row r="26" spans="2:28" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P26" s="56" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q26" s="56"/>
-      <c r="R26" s="56"/>
-      <c r="S26" s="56"/>
-      <c r="T26" s="56"/>
-      <c r="U26" s="56"/>
-      <c r="V26" s="56"/>
-      <c r="W26" s="56"/>
-      <c r="X26" s="56"/>
-      <c r="Y26" s="56"/>
-      <c r="Z26" s="56"/>
-      <c r="AA26" s="56"/>
-      <c r="AB26" s="56"/>
-    </row>
-    <row r="27" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:29" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P26" s="62" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q26" s="62"/>
+      <c r="R26" s="62"/>
+      <c r="S26" s="62"/>
+      <c r="T26" s="62"/>
+      <c r="U26" s="62"/>
+      <c r="V26" s="62"/>
+      <c r="W26" s="62"/>
+      <c r="X26" s="62"/>
+      <c r="Y26" s="62"/>
+      <c r="Z26" s="62"/>
+      <c r="AA26" s="62"/>
+      <c r="AB26" s="62"/>
+    </row>
+    <row r="27" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P27" s="17"/>
       <c r="Q27" s="17"/>
       <c r="R27" s="17"/>
@@ -5345,37 +5703,37 @@
       <c r="AA27" s="17"/>
       <c r="AB27" s="17"/>
     </row>
-    <row r="28" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="P28" s="59" t="s">
+    <row r="28" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="P28" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="Q28" s="59"/>
-      <c r="R28" s="59"/>
-      <c r="S28" s="59"/>
-      <c r="T28" s="59"/>
-      <c r="U28" s="59"/>
-      <c r="V28" s="59"/>
-      <c r="W28" s="59"/>
-      <c r="X28" s="59"/>
-      <c r="Y28" s="59"/>
-      <c r="Z28" s="59"/>
-      <c r="AA28" s="59"/>
-      <c r="AB28" s="59"/>
-    </row>
-    <row r="29" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="Q28" s="66"/>
+      <c r="R28" s="66"/>
+      <c r="S28" s="66"/>
+      <c r="T28" s="66"/>
+      <c r="U28" s="66"/>
+      <c r="V28" s="66"/>
+      <c r="W28" s="66"/>
+      <c r="X28" s="66"/>
+      <c r="Y28" s="66"/>
+      <c r="Z28" s="66"/>
+      <c r="AA28" s="66"/>
+      <c r="AB28" s="66"/>
+    </row>
+    <row r="29" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P29" s="12"/>
     </row>
-    <row r="30" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P30" s="12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P31" s="12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P32" s="12"/>
     </row>
     <row r="33" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
@@ -5406,38 +5764,38 @@
       <c r="AB35" s="12"/>
     </row>
     <row r="36" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P36" s="39" t="s">
+      <c r="P36" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="Q36" s="39"/>
-      <c r="R36" s="39"/>
-      <c r="S36" s="39"/>
-      <c r="T36" s="39"/>
-      <c r="U36" s="39"/>
-      <c r="V36" s="39"/>
-      <c r="W36" s="39"/>
-      <c r="X36" s="39"/>
-      <c r="Y36" s="39"/>
-      <c r="Z36" s="39"/>
-      <c r="AA36" s="39"/>
-      <c r="AB36" s="39"/>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="43"/>
+      <c r="S36" s="43"/>
+      <c r="T36" s="43"/>
+      <c r="U36" s="43"/>
+      <c r="V36" s="43"/>
+      <c r="W36" s="43"/>
+      <c r="X36" s="43"/>
+      <c r="Y36" s="43"/>
+      <c r="Z36" s="43"/>
+      <c r="AA36" s="43"/>
+      <c r="AB36" s="43"/>
     </row>
     <row r="38" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B38" s="64" t="s">
+      <c r="B38" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="64"/>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
-      <c r="F38" s="64"/>
-      <c r="G38" s="64"/>
-      <c r="H38" s="64"/>
-      <c r="I38" s="64"/>
-      <c r="J38" s="64"/>
-      <c r="K38" s="64"/>
-      <c r="L38" s="64"/>
-      <c r="M38" s="64"/>
-      <c r="N38" s="64"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="68"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="68"/>
+      <c r="H38" s="68"/>
+      <c r="I38" s="68"/>
+      <c r="J38" s="68"/>
+      <c r="K38" s="68"/>
+      <c r="L38" s="68"/>
+      <c r="M38" s="68"/>
+      <c r="N38" s="68"/>
       <c r="P38" s="8" t="s">
         <v>57</v>
       </c>
@@ -5455,22 +5813,22 @@
       <c r="AB38" s="12"/>
     </row>
     <row r="39" spans="2:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P39" s="35" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q39" s="35"/>
-      <c r="R39" s="35"/>
-      <c r="S39" s="35"/>
-      <c r="T39" s="35"/>
-      <c r="U39" s="35"/>
-      <c r="V39" s="35"/>
-      <c r="W39" s="35"/>
-      <c r="X39" s="35"/>
-      <c r="Y39" s="35"/>
-      <c r="Z39" s="35"/>
-      <c r="AA39" s="35"/>
-      <c r="AB39" s="35"/>
-      <c r="AC39" s="31"/>
+      <c r="P39" s="58" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q39" s="58"/>
+      <c r="R39" s="58"/>
+      <c r="S39" s="58"/>
+      <c r="T39" s="58"/>
+      <c r="U39" s="58"/>
+      <c r="V39" s="58"/>
+      <c r="W39" s="58"/>
+      <c r="X39" s="58"/>
+      <c r="Y39" s="58"/>
+      <c r="Z39" s="58"/>
+      <c r="AA39" s="58"/>
+      <c r="AB39" s="58"/>
+      <c r="AC39" s="29"/>
     </row>
     <row r="40" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P40" s="12" t="s">
@@ -5483,22 +5841,22 @@
       </c>
     </row>
     <row r="42" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="P42" s="59" t="s">
+      <c r="P42" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="Q42" s="59"/>
-      <c r="R42" s="59"/>
-      <c r="S42" s="59"/>
-      <c r="T42" s="59"/>
-      <c r="U42" s="59"/>
-      <c r="V42" s="59"/>
-      <c r="W42" s="59"/>
-      <c r="X42" s="59"/>
-      <c r="Y42" s="59"/>
-      <c r="Z42" s="59"/>
-      <c r="AA42" s="59"/>
-      <c r="AB42" s="59"/>
-      <c r="AC42" s="59"/>
+      <c r="Q42" s="66"/>
+      <c r="R42" s="66"/>
+      <c r="S42" s="66"/>
+      <c r="T42" s="66"/>
+      <c r="U42" s="66"/>
+      <c r="V42" s="66"/>
+      <c r="W42" s="66"/>
+      <c r="X42" s="66"/>
+      <c r="Y42" s="66"/>
+      <c r="Z42" s="66"/>
+      <c r="AA42" s="66"/>
+      <c r="AB42" s="66"/>
+      <c r="AC42" s="66"/>
     </row>
     <row r="43" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P43" s="12" t="s">
@@ -5511,22 +5869,22 @@
       </c>
     </row>
     <row r="45" spans="2:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P45" s="39" t="s">
+      <c r="P45" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="Q45" s="39"/>
-      <c r="R45" s="39"/>
-      <c r="S45" s="39"/>
-      <c r="T45" s="39"/>
-      <c r="U45" s="39"/>
-      <c r="V45" s="39"/>
-      <c r="W45" s="39"/>
-      <c r="X45" s="39"/>
-      <c r="Y45" s="39"/>
-      <c r="Z45" s="39"/>
-      <c r="AA45" s="39"/>
-      <c r="AB45" s="39"/>
-      <c r="AC45" s="32"/>
+      <c r="Q45" s="43"/>
+      <c r="R45" s="43"/>
+      <c r="S45" s="43"/>
+      <c r="T45" s="43"/>
+      <c r="U45" s="43"/>
+      <c r="V45" s="43"/>
+      <c r="W45" s="43"/>
+      <c r="X45" s="43"/>
+      <c r="Y45" s="43"/>
+      <c r="Z45" s="43"/>
+      <c r="AA45" s="43"/>
+      <c r="AB45" s="43"/>
+      <c r="AC45" s="30"/>
     </row>
     <row r="46" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P46" s="12" t="s">
@@ -5534,41 +5892,41 @@
       </c>
     </row>
     <row r="47" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B47" s="65" t="s">
+      <c r="B47" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="C47" s="65"/>
-      <c r="D47" s="65"/>
-      <c r="E47" s="65"/>
-      <c r="F47" s="65"/>
-      <c r="G47" s="65"/>
-      <c r="H47" s="65"/>
-      <c r="I47" s="65"/>
-      <c r="J47" s="65"/>
-      <c r="K47" s="65"/>
-      <c r="L47" s="65"/>
-      <c r="M47" s="65"/>
+      <c r="C47" s="69"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="69"/>
+      <c r="H47" s="69"/>
+      <c r="I47" s="69"/>
+      <c r="J47" s="69"/>
+      <c r="K47" s="69"/>
+      <c r="L47" s="69"/>
+      <c r="M47" s="69"/>
       <c r="P47" s="8" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="48" spans="2:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P48" s="35" t="s">
+      <c r="P48" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="Q48" s="35"/>
-      <c r="R48" s="35"/>
-      <c r="S48" s="35"/>
-      <c r="T48" s="35"/>
-      <c r="U48" s="35"/>
-      <c r="V48" s="35"/>
-      <c r="W48" s="35"/>
-      <c r="X48" s="35"/>
-      <c r="Y48" s="35"/>
-      <c r="Z48" s="35"/>
-      <c r="AA48" s="35"/>
-      <c r="AB48" s="35"/>
-      <c r="AC48" s="29"/>
+      <c r="Q48" s="58"/>
+      <c r="R48" s="58"/>
+      <c r="S48" s="58"/>
+      <c r="T48" s="58"/>
+      <c r="U48" s="58"/>
+      <c r="V48" s="58"/>
+      <c r="W48" s="58"/>
+      <c r="X48" s="58"/>
+      <c r="Y48" s="58"/>
+      <c r="Z48" s="58"/>
+      <c r="AA48" s="58"/>
+      <c r="AB48" s="58"/>
+      <c r="AC48" s="27"/>
     </row>
     <row r="49" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P49" s="12" t="s">
@@ -5581,21 +5939,21 @@
       </c>
     </row>
     <row r="51" spans="2:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P51" s="39" t="s">
+      <c r="P51" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="Q51" s="39"/>
-      <c r="R51" s="39"/>
-      <c r="S51" s="39"/>
-      <c r="T51" s="39"/>
-      <c r="U51" s="39"/>
-      <c r="V51" s="39"/>
-      <c r="W51" s="39"/>
-      <c r="X51" s="39"/>
-      <c r="Y51" s="39"/>
-      <c r="Z51" s="39"/>
-      <c r="AA51" s="39"/>
-      <c r="AB51" s="39"/>
+      <c r="Q51" s="43"/>
+      <c r="R51" s="43"/>
+      <c r="S51" s="43"/>
+      <c r="T51" s="43"/>
+      <c r="U51" s="43"/>
+      <c r="V51" s="43"/>
+      <c r="W51" s="43"/>
+      <c r="X51" s="43"/>
+      <c r="Y51" s="43"/>
+      <c r="Z51" s="43"/>
+      <c r="AA51" s="43"/>
+      <c r="AB51" s="43"/>
     </row>
     <row r="52" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P52" s="12" t="s">
@@ -5615,42 +5973,42 @@
       <c r="T55" s="12"/>
     </row>
     <row r="56" spans="2:29" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O56" s="35" t="s">
+      <c r="O56" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="P56" s="35"/>
-      <c r="Q56" s="35"/>
-      <c r="R56" s="35"/>
-      <c r="S56" s="35"/>
-      <c r="T56" s="35"/>
-      <c r="U56" s="35"/>
-      <c r="V56" s="35"/>
-      <c r="W56" s="35"/>
-      <c r="X56" s="35"/>
-      <c r="Y56" s="35"/>
-      <c r="Z56" s="35"/>
-      <c r="AA56" s="35"/>
-      <c r="AB56" s="35"/>
-      <c r="AC56" s="35"/>
+      <c r="P56" s="58"/>
+      <c r="Q56" s="58"/>
+      <c r="R56" s="58"/>
+      <c r="S56" s="58"/>
+      <c r="T56" s="58"/>
+      <c r="U56" s="58"/>
+      <c r="V56" s="58"/>
+      <c r="W56" s="58"/>
+      <c r="X56" s="58"/>
+      <c r="Y56" s="58"/>
+      <c r="Z56" s="58"/>
+      <c r="AA56" s="58"/>
+      <c r="AB56" s="58"/>
+      <c r="AC56" s="58"/>
     </row>
     <row r="58" spans="2:29" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O58" s="66" t="s">
+      <c r="O58" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="P58" s="66"/>
-      <c r="Q58" s="66"/>
-      <c r="R58" s="66"/>
-      <c r="S58" s="66"/>
-      <c r="T58" s="66"/>
-      <c r="U58" s="66"/>
-      <c r="V58" s="66"/>
-      <c r="W58" s="66"/>
-      <c r="X58" s="66"/>
-      <c r="Y58" s="66"/>
-      <c r="Z58" s="66"/>
-      <c r="AA58" s="66"/>
-      <c r="AB58" s="66"/>
-      <c r="AC58" s="66"/>
+      <c r="P58" s="57"/>
+      <c r="Q58" s="57"/>
+      <c r="R58" s="57"/>
+      <c r="S58" s="57"/>
+      <c r="T58" s="57"/>
+      <c r="U58" s="57"/>
+      <c r="V58" s="57"/>
+      <c r="W58" s="57"/>
+      <c r="X58" s="57"/>
+      <c r="Y58" s="57"/>
+      <c r="Z58" s="57"/>
+      <c r="AA58" s="57"/>
+      <c r="AB58" s="57"/>
+      <c r="AC58" s="57"/>
     </row>
     <row r="59" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
       <c r="O59" s="18"/>
@@ -5670,171 +6028,198 @@
       <c r="AC59" s="17"/>
     </row>
     <row r="60" spans="2:29" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O60" s="92" t="s">
-        <v>174</v>
-      </c>
-      <c r="P60" s="67"/>
-      <c r="Q60" s="67"/>
-      <c r="R60" s="67"/>
-      <c r="S60" s="67"/>
-      <c r="T60" s="67"/>
-      <c r="U60" s="67"/>
-      <c r="V60" s="67"/>
-      <c r="W60" s="67"/>
-      <c r="X60" s="67"/>
-      <c r="Y60" s="67"/>
-      <c r="Z60" s="67"/>
-      <c r="AA60" s="67"/>
-      <c r="AB60" s="67"/>
-      <c r="AC60" s="67"/>
-    </row>
-    <row r="62" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="O62" s="8" t="s">
+      <c r="O60" s="59" t="s">
+        <v>173</v>
+      </c>
+      <c r="P60" s="60"/>
+      <c r="Q60" s="60"/>
+      <c r="R60" s="60"/>
+      <c r="S60" s="60"/>
+      <c r="T60" s="60"/>
+      <c r="U60" s="60"/>
+      <c r="V60" s="60"/>
+      <c r="W60" s="60"/>
+      <c r="X60" s="60"/>
+      <c r="Y60" s="60"/>
+      <c r="Z60" s="60"/>
+      <c r="AA60" s="60"/>
+      <c r="AB60" s="60"/>
+      <c r="AC60" s="60"/>
+    </row>
+    <row r="61" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O61" s="36"/>
+      <c r="P61" s="34"/>
+      <c r="Q61" s="34"/>
+      <c r="R61" s="34"/>
+      <c r="S61" s="34"/>
+      <c r="T61" s="34"/>
+      <c r="U61" s="34"/>
+      <c r="V61" s="34"/>
+      <c r="W61" s="34"/>
+      <c r="X61" s="34"/>
+      <c r="Y61" s="34"/>
+      <c r="Z61" s="34"/>
+      <c r="AA61" s="34"/>
+      <c r="AB61" s="34"/>
+      <c r="AC61" s="34"/>
+    </row>
+    <row r="62" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O62" s="94" t="s">
+        <v>238</v>
+      </c>
+      <c r="P62" s="66"/>
+      <c r="Q62" s="66"/>
+      <c r="R62" s="66"/>
+      <c r="S62" s="66"/>
+      <c r="T62" s="66"/>
+      <c r="U62" s="66"/>
+      <c r="V62" s="66"/>
+      <c r="W62" s="66"/>
+      <c r="X62" s="66"/>
+      <c r="Y62" s="66"/>
+      <c r="Z62" s="66"/>
+      <c r="AA62" s="66"/>
+      <c r="AB62" s="34"/>
+      <c r="AC62" s="34"/>
+    </row>
+    <row r="64" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="O64" s="8" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="63" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="O63" s="8"/>
-    </row>
-    <row r="64" spans="2:29" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O64" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="P64" s="56"/>
-      <c r="Q64" s="56"/>
-      <c r="R64" s="56"/>
-      <c r="S64" s="56"/>
-      <c r="T64" s="56"/>
-      <c r="U64" s="56"/>
-      <c r="V64" s="56"/>
-      <c r="W64" s="56"/>
-      <c r="X64" s="56"/>
-      <c r="Y64" s="56"/>
-      <c r="Z64" s="56"/>
-      <c r="AA64" s="56"/>
-      <c r="AB64" s="56"/>
-      <c r="AC64" s="56"/>
-    </row>
-    <row r="65" spans="15:29" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="O65" s="18"/>
-      <c r="P65" s="17"/>
-      <c r="Q65" s="17"/>
-      <c r="R65" s="17"/>
-      <c r="S65" s="17"/>
-      <c r="T65" s="17"/>
-      <c r="U65" s="17"/>
-      <c r="V65" s="17"/>
-      <c r="W65" s="17"/>
-      <c r="X65" s="17"/>
-      <c r="Y65" s="17"/>
-      <c r="Z65" s="17"/>
-      <c r="AA65" s="17"/>
-      <c r="AB65" s="17"/>
-      <c r="AC65" s="17"/>
-    </row>
-    <row r="66" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O66" s="63" t="s">
+    <row r="65" spans="15:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="O65" s="8"/>
+    </row>
+    <row r="66" spans="15:29" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O66" s="61" t="s">
+        <v>171</v>
+      </c>
+      <c r="P66" s="62"/>
+      <c r="Q66" s="62"/>
+      <c r="R66" s="62"/>
+      <c r="S66" s="62"/>
+      <c r="T66" s="62"/>
+      <c r="U66" s="62"/>
+      <c r="V66" s="62"/>
+      <c r="W66" s="62"/>
+      <c r="X66" s="62"/>
+      <c r="Y66" s="62"/>
+      <c r="Z66" s="62"/>
+      <c r="AA66" s="62"/>
+      <c r="AB66" s="62"/>
+      <c r="AC66" s="62"/>
+    </row>
+    <row r="67" spans="15:29" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="O67" s="18"/>
+      <c r="P67" s="17"/>
+      <c r="Q67" s="17"/>
+      <c r="R67" s="17"/>
+      <c r="S67" s="17"/>
+      <c r="T67" s="17"/>
+      <c r="U67" s="17"/>
+      <c r="V67" s="17"/>
+      <c r="W67" s="17"/>
+      <c r="X67" s="17"/>
+      <c r="Y67" s="17"/>
+      <c r="Z67" s="17"/>
+      <c r="AA67" s="17"/>
+      <c r="AB67" s="17"/>
+      <c r="AC67" s="17"/>
+    </row>
+    <row r="68" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O68" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="P66" s="63"/>
-      <c r="Q66" s="63"/>
-      <c r="R66" s="63"/>
-      <c r="S66" s="63"/>
-      <c r="T66" s="30"/>
-      <c r="U66" s="30"/>
-      <c r="V66" s="30"/>
-      <c r="W66" s="30"/>
-      <c r="X66" s="30"/>
-      <c r="Y66" s="30"/>
-      <c r="Z66" s="30"/>
-      <c r="AA66" s="30"/>
-      <c r="AB66" s="30"/>
-      <c r="AC66" s="30"/>
-    </row>
-    <row r="67" spans="15:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O67" s="35" t="s">
+      <c r="P68" s="63"/>
+      <c r="Q68" s="63"/>
+      <c r="R68" s="63"/>
+      <c r="S68" s="63"/>
+      <c r="T68" s="28"/>
+      <c r="U68" s="28"/>
+      <c r="V68" s="28"/>
+      <c r="W68" s="28"/>
+      <c r="X68" s="28"/>
+      <c r="Y68" s="28"/>
+      <c r="Z68" s="28"/>
+      <c r="AA68" s="28"/>
+      <c r="AB68" s="28"/>
+      <c r="AC68" s="28"/>
+    </row>
+    <row r="69" spans="15:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O69" s="58" t="s">
         <v>76</v>
       </c>
-      <c r="P67" s="39"/>
-      <c r="Q67" s="39"/>
-      <c r="R67" s="39"/>
-      <c r="S67" s="39"/>
-      <c r="T67" s="39"/>
-      <c r="U67" s="39"/>
-      <c r="V67" s="39"/>
-      <c r="W67" s="39"/>
-      <c r="X67" s="39"/>
-      <c r="Y67" s="39"/>
-      <c r="Z67" s="39"/>
-      <c r="AA67" s="39"/>
-      <c r="AB67" s="39"/>
-      <c r="AC67" s="39"/>
-    </row>
-    <row r="68" spans="15:29" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O68" s="12" t="s">
+      <c r="P69" s="43"/>
+      <c r="Q69" s="43"/>
+      <c r="R69" s="43"/>
+      <c r="S69" s="43"/>
+      <c r="T69" s="43"/>
+      <c r="U69" s="43"/>
+      <c r="V69" s="43"/>
+      <c r="W69" s="43"/>
+      <c r="X69" s="43"/>
+      <c r="Y69" s="43"/>
+      <c r="Z69" s="43"/>
+      <c r="AA69" s="43"/>
+      <c r="AB69" s="43"/>
+      <c r="AC69" s="43"/>
+    </row>
+    <row r="70" spans="15:29" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O70" s="12" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="69" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O69" s="63" t="s">
+    <row r="71" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O71" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="P69" s="63"/>
-      <c r="Q69" s="63"/>
-      <c r="R69" s="63"/>
-      <c r="S69" s="63"/>
-      <c r="T69" s="30"/>
-      <c r="U69" s="30"/>
-      <c r="V69" s="30"/>
-      <c r="W69" s="30"/>
-      <c r="X69" s="30"/>
-      <c r="Y69" s="30"/>
-      <c r="Z69" s="30"/>
-      <c r="AA69" s="30"/>
-      <c r="AB69" s="30"/>
-      <c r="AC69" s="30"/>
-    </row>
-    <row r="70" spans="15:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O70" s="35" t="s">
+      <c r="P71" s="63"/>
+      <c r="Q71" s="63"/>
+      <c r="R71" s="63"/>
+      <c r="S71" s="63"/>
+      <c r="T71" s="28"/>
+      <c r="U71" s="28"/>
+      <c r="V71" s="28"/>
+      <c r="W71" s="28"/>
+      <c r="X71" s="28"/>
+      <c r="Y71" s="28"/>
+      <c r="Z71" s="28"/>
+      <c r="AA71" s="28"/>
+      <c r="AB71" s="28"/>
+      <c r="AC71" s="28"/>
+    </row>
+    <row r="72" spans="15:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O72" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="P70" s="35"/>
-      <c r="Q70" s="35"/>
-      <c r="R70" s="35"/>
-      <c r="S70" s="35"/>
-      <c r="T70" s="35"/>
-      <c r="U70" s="35"/>
-      <c r="V70" s="35"/>
-      <c r="W70" s="35"/>
-      <c r="X70" s="35"/>
-      <c r="Y70" s="35"/>
-      <c r="Z70" s="35"/>
-      <c r="AA70" s="35"/>
-      <c r="AB70" s="35"/>
-      <c r="AC70" s="35"/>
-    </row>
-    <row r="71" spans="15:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="O71" s="12" t="s">
+      <c r="P72" s="58"/>
+      <c r="Q72" s="58"/>
+      <c r="R72" s="58"/>
+      <c r="S72" s="58"/>
+      <c r="T72" s="58"/>
+      <c r="U72" s="58"/>
+      <c r="V72" s="58"/>
+      <c r="W72" s="58"/>
+      <c r="X72" s="58"/>
+      <c r="Y72" s="58"/>
+      <c r="Z72" s="58"/>
+      <c r="AA72" s="58"/>
+      <c r="AB72" s="58"/>
+      <c r="AC72" s="58"/>
+    </row>
+    <row r="73" spans="15:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="O73" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="72" spans="15:29" ht="42" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="15:29" ht="40.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="15:29" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="15:29" ht="42" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="15:29" ht="40.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="15:29" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="O58:AC58"/>
-    <mergeCell ref="O56:AC56"/>
-    <mergeCell ref="O60:AC60"/>
-    <mergeCell ref="P39:AB39"/>
-    <mergeCell ref="P45:AB45"/>
-    <mergeCell ref="P48:AB48"/>
-    <mergeCell ref="O64:AC64"/>
-    <mergeCell ref="O66:S66"/>
-    <mergeCell ref="O67:AC67"/>
-    <mergeCell ref="O69:S69"/>
-    <mergeCell ref="O70:AC70"/>
+  <mergeCells count="25">
+    <mergeCell ref="O62:AA62"/>
+    <mergeCell ref="B17:AC17"/>
     <mergeCell ref="P26:AB26"/>
     <mergeCell ref="P51:AB51"/>
     <mergeCell ref="L8:W8"/>
@@ -5845,9 +6230,19 @@
     <mergeCell ref="L10:AB10"/>
     <mergeCell ref="L12:AB12"/>
     <mergeCell ref="P28:AB28"/>
-    <mergeCell ref="B17:AB17"/>
     <mergeCell ref="B38:N38"/>
     <mergeCell ref="B47:M47"/>
+    <mergeCell ref="O66:AC66"/>
+    <mergeCell ref="O68:S68"/>
+    <mergeCell ref="O69:AC69"/>
+    <mergeCell ref="O71:S71"/>
+    <mergeCell ref="O72:AC72"/>
+    <mergeCell ref="O58:AC58"/>
+    <mergeCell ref="O56:AC56"/>
+    <mergeCell ref="O60:AC60"/>
+    <mergeCell ref="P39:AB39"/>
+    <mergeCell ref="P45:AB45"/>
+    <mergeCell ref="P48:AB48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -5860,7 +6255,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A2:AE133"/>
+  <dimension ref="A2:AE135"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
@@ -5873,450 +6268,532 @@
     </row>
     <row r="4" spans="1:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="70" t="s">
         <v>143</v>
       </c>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
     </row>
     <row r="5" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="L5" s="46" t="s">
+      <c r="L5" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="52"/>
+      <c r="O5" s="52"/>
+      <c r="P5" s="52"/>
     </row>
     <row r="6" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
-      <c r="L6" s="72" t="s">
+      <c r="L6" s="73" t="s">
         <v>120</v>
       </c>
-      <c r="M6" s="72"/>
-      <c r="N6" s="72"/>
-      <c r="O6" s="72"/>
-      <c r="P6" s="72"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="73"/>
+      <c r="O6" s="73"/>
+      <c r="P6" s="73"/>
     </row>
     <row r="7" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
-      <c r="L7" s="71" t="s">
+      <c r="L7" s="72" t="s">
         <v>121</v>
       </c>
-      <c r="M7" s="71"/>
-      <c r="N7" s="71"/>
-      <c r="O7" s="71"/>
-      <c r="P7" s="71"/>
+      <c r="M7" s="72"/>
+      <c r="N7" s="72"/>
+      <c r="O7" s="72"/>
+      <c r="P7" s="72"/>
     </row>
     <row r="8" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
-      <c r="L8" s="72" t="s">
+      <c r="L8" s="73" t="s">
         <v>122</v>
       </c>
-      <c r="M8" s="72"/>
-      <c r="N8" s="72"/>
-      <c r="O8" s="72"/>
-      <c r="P8" s="72"/>
+      <c r="M8" s="73"/>
+      <c r="N8" s="73"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="73"/>
     </row>
     <row r="9" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1"/>
-      <c r="L9" s="72" t="s">
+      <c r="L9" s="73" t="s">
         <v>123</v>
       </c>
-      <c r="M9" s="72"/>
-      <c r="N9" s="72"/>
-      <c r="O9" s="72"/>
-      <c r="P9" s="72"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="73"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="73"/>
     </row>
     <row r="10" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
-      <c r="L10" s="71" t="s">
+      <c r="L10" s="72" t="s">
         <v>124</v>
       </c>
-      <c r="M10" s="71"/>
-      <c r="N10" s="71"/>
-      <c r="O10" s="71"/>
-      <c r="P10" s="71"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="72"/>
+      <c r="P10" s="72"/>
     </row>
     <row r="11" spans="1:31" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
-      <c r="L11" s="71" t="s">
+      <c r="L11" s="72" t="s">
         <v>125</v>
       </c>
-      <c r="M11" s="72"/>
-      <c r="N11" s="72"/>
-      <c r="O11" s="72"/>
-      <c r="P11" s="72"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="73"/>
+      <c r="O11" s="73"/>
+      <c r="P11" s="73"/>
     </row>
     <row r="12" spans="1:31" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1"/>
-      <c r="L12" s="71" t="s">
+      <c r="L12" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="M12" s="71"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="71"/>
-      <c r="P12" s="71"/>
-      <c r="R12" s="70" t="s">
+      <c r="M12" s="72"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="72"/>
+      <c r="P12" s="72"/>
+      <c r="R12" s="71" t="s">
         <v>138</v>
       </c>
-      <c r="S12" s="70"/>
-      <c r="T12" s="70"/>
-      <c r="U12" s="70"/>
-      <c r="V12" s="70"/>
-      <c r="W12" s="70"/>
-      <c r="X12" s="70"/>
-      <c r="Y12" s="70"/>
-      <c r="Z12" s="70"/>
-      <c r="AA12" s="70"/>
-      <c r="AB12" s="70"/>
-      <c r="AC12" s="70"/>
-      <c r="AD12" s="33"/>
-      <c r="AE12" s="33"/>
+      <c r="S12" s="71"/>
+      <c r="T12" s="71"/>
+      <c r="U12" s="71"/>
+      <c r="V12" s="71"/>
+      <c r="W12" s="71"/>
+      <c r="X12" s="71"/>
+      <c r="Y12" s="71"/>
+      <c r="Z12" s="71"/>
+      <c r="AA12" s="71"/>
+      <c r="AB12" s="71"/>
+      <c r="AC12" s="71"/>
+      <c r="AD12" s="31"/>
+      <c r="AE12" s="31"/>
     </row>
     <row r="13" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
-      <c r="L13" s="72" t="s">
+      <c r="L13" s="73" t="s">
         <v>127</v>
       </c>
-      <c r="M13" s="72"/>
-      <c r="N13" s="72"/>
-      <c r="O13" s="72"/>
-      <c r="P13" s="72"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="73"/>
+      <c r="O13" s="73"/>
+      <c r="P13" s="73"/>
     </row>
     <row r="14" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A14" s="1"/>
-      <c r="L14" s="72" t="s">
+      <c r="L14" s="73" t="s">
         <v>128</v>
       </c>
-      <c r="M14" s="72"/>
-      <c r="N14" s="72"/>
-      <c r="O14" s="72"/>
-      <c r="P14" s="72"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="73"/>
+      <c r="O14" s="73"/>
+      <c r="P14" s="73"/>
     </row>
     <row r="15" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="21"/>
     </row>
     <row r="16" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
-    </row>
-    <row r="17" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="L16" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="M16" s="52"/>
+      <c r="N16" s="52"/>
+      <c r="O16" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="P16" s="52"/>
+      <c r="Q16" s="52"/>
+      <c r="R16" s="52"/>
+      <c r="S16" s="52"/>
+      <c r="T16" s="52"/>
+    </row>
+    <row r="17" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A17" s="1"/>
-      <c r="L17" s="46" t="s">
+      <c r="L17" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="M17" s="49"/>
+      <c r="N17" s="49"/>
+      <c r="O17" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="P17" s="75"/>
+      <c r="Q17" s="75"/>
+      <c r="R17" s="75"/>
+      <c r="S17" s="75"/>
+      <c r="T17" s="75"/>
+    </row>
+    <row r="18" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A18" s="1"/>
+      <c r="L18" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="M18" s="49"/>
+      <c r="N18" s="49"/>
+      <c r="O18" s="75" t="s">
+        <v>135</v>
+      </c>
+      <c r="P18" s="75"/>
+      <c r="Q18" s="75"/>
+      <c r="R18" s="75"/>
+      <c r="S18" s="75"/>
+      <c r="T18" s="75"/>
+    </row>
+    <row r="19" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A19" s="1"/>
+      <c r="L19" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="M19" s="49"/>
+      <c r="N19" s="49"/>
+      <c r="O19" s="75" t="s">
+        <v>137</v>
+      </c>
+      <c r="P19" s="75"/>
+      <c r="Q19" s="75"/>
+      <c r="R19" s="75"/>
+      <c r="S19" s="75"/>
+      <c r="T19" s="75"/>
+    </row>
+    <row r="20" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A21" s="1"/>
+      <c r="L21" s="52" t="s">
         <v>130</v>
       </c>
-      <c r="M17" s="46"/>
-      <c r="N17" s="46"/>
-      <c r="O17" s="46" t="s">
-        <v>132</v>
-      </c>
-      <c r="P17" s="46"/>
-      <c r="Q17" s="46"/>
-      <c r="R17" s="46"/>
-      <c r="S17" s="46"/>
-      <c r="T17" s="46"/>
-    </row>
-    <row r="18" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A18" s="1"/>
-      <c r="L18" s="52" t="s">
+      <c r="M21" s="52"/>
+      <c r="N21" s="52"/>
+      <c r="O21" s="52" t="s">
+        <v>295</v>
+      </c>
+      <c r="P21" s="52"/>
+      <c r="Q21" s="52"/>
+      <c r="R21" s="52"/>
+      <c r="S21" s="52"/>
+      <c r="T21" s="52"/>
+      <c r="U21" s="52"/>
+      <c r="V21" s="52"/>
+      <c r="W21" s="52"/>
+    </row>
+    <row r="22" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A22" s="1"/>
+      <c r="L22" s="49" t="s">
         <v>133</v>
       </c>
-      <c r="M18" s="52"/>
-      <c r="N18" s="52"/>
-      <c r="O18" s="68" t="s">
-        <v>131</v>
-      </c>
-      <c r="P18" s="68"/>
-      <c r="Q18" s="68"/>
-      <c r="R18" s="68"/>
-      <c r="S18" s="68"/>
-      <c r="T18" s="68"/>
-    </row>
-    <row r="19" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A19" s="1"/>
-      <c r="L19" s="52" t="s">
+      <c r="M22" s="49"/>
+      <c r="N22" s="49"/>
+      <c r="O22" s="121" t="s">
+        <v>292</v>
+      </c>
+      <c r="P22" s="121"/>
+      <c r="Q22" s="121"/>
+      <c r="R22" s="121"/>
+      <c r="S22" s="121"/>
+      <c r="T22" s="121"/>
+      <c r="U22" s="121"/>
+      <c r="V22" s="121"/>
+      <c r="W22" s="121"/>
+    </row>
+    <row r="23" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A23" s="1"/>
+      <c r="L23" s="49" t="s">
         <v>134</v>
       </c>
-      <c r="M19" s="52"/>
-      <c r="N19" s="52"/>
-      <c r="O19" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="P19" s="68"/>
-      <c r="Q19" s="68"/>
-      <c r="R19" s="68"/>
-      <c r="S19" s="68"/>
-      <c r="T19" s="68"/>
-    </row>
-    <row r="20" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A20" s="1"/>
-      <c r="L20" s="52" t="s">
+      <c r="M23" s="49"/>
+      <c r="N23" s="49"/>
+      <c r="O23" s="121" t="s">
+        <v>293</v>
+      </c>
+      <c r="P23" s="121"/>
+      <c r="Q23" s="121"/>
+      <c r="R23" s="121"/>
+      <c r="S23" s="121"/>
+      <c r="T23" s="121"/>
+      <c r="U23" s="121"/>
+      <c r="V23" s="121"/>
+      <c r="W23" s="121"/>
+    </row>
+    <row r="24" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A24" s="1"/>
+      <c r="L24" s="49" t="s">
         <v>136</v>
       </c>
-      <c r="M20" s="52"/>
-      <c r="N20" s="52"/>
-      <c r="O20" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="P20" s="68"/>
-      <c r="Q20" s="68"/>
-      <c r="R20" s="68"/>
-      <c r="S20" s="68"/>
-      <c r="T20" s="68"/>
-    </row>
-    <row r="21" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A21" s="1"/>
-    </row>
-    <row r="22" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A22" s="1"/>
-    </row>
-    <row r="23" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A23" s="1"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-    </row>
-    <row r="25" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B25" s="8" t="s">
+      <c r="M24" s="49"/>
+      <c r="N24" s="49"/>
+      <c r="O24" s="121" t="s">
+        <v>294</v>
+      </c>
+      <c r="P24" s="121"/>
+      <c r="Q24" s="121"/>
+      <c r="R24" s="121"/>
+      <c r="S24" s="121"/>
+      <c r="T24" s="121"/>
+      <c r="U24" s="121"/>
+      <c r="V24" s="121"/>
+      <c r="W24" s="121"/>
+    </row>
+    <row r="25" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A25" s="1"/>
+    </row>
+    <row r="26" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A26" s="1"/>
+    </row>
+    <row r="27" spans="1:23" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B27" s="8" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B26" s="8"/>
-    </row>
-    <row r="27" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B27" s="8" t="s">
+    <row r="28" spans="1:23" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B28" s="8"/>
+    </row>
+    <row r="29" spans="1:23" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B29" s="8" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B56" s="20" t="s">
+    <row r="58" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B58" s="20" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="57" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B57" s="20"/>
-    </row>
-    <row r="58" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B58" s="8" t="s">
+    <row r="59" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B59" s="20"/>
+    </row>
+    <row r="60" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B60" s="8" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="85" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B85" s="20" t="s">
+    <row r="87" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B87" s="20" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="87" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B87" s="8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="88" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B88" s="8"/>
     </row>
     <row r="89" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B89" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B90" s="8"/>
+    </row>
+    <row r="91" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B91" s="8" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="91" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B91" s="20" t="s">
+    <row r="93" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B93" s="20" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="93" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B93" s="24" t="s">
+    <row r="95" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B95" s="22" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="94" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B94" s="24" t="s">
+    <row r="96" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B96" s="22" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="95" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B95" s="24" t="s">
+    <row r="97" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B97" s="22" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B97" s="8" t="s">
+    <row r="99" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B99" s="8" t="s">
         <v>149</v>
-      </c>
-    </row>
-    <row r="99" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B99" s="20" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="101" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B101" s="20" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="102" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B102" s="20"/>
+        <v>150</v>
+      </c>
     </row>
     <row r="103" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B103" s="20" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="105" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B105" s="73" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B104" s="20"/>
+    </row>
+    <row r="105" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B105" s="20" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B107" s="74" t="s">
         <v>152</v>
       </c>
-      <c r="C105" s="73"/>
-      <c r="D105" s="73"/>
-      <c r="E105" s="73"/>
-      <c r="F105" s="73"/>
-      <c r="G105" s="73"/>
-      <c r="H105" s="73"/>
-      <c r="I105" s="73"/>
-      <c r="J105" s="73"/>
-      <c r="K105" s="73"/>
-      <c r="L105" s="73"/>
-      <c r="M105" s="73"/>
-      <c r="N105" s="73"/>
-      <c r="O105" s="73"/>
-      <c r="P105" s="73"/>
-      <c r="Q105" s="73"/>
-      <c r="R105" s="73"/>
-      <c r="S105" s="73"/>
-      <c r="T105" s="73"/>
-      <c r="U105" s="73"/>
-      <c r="V105" s="73"/>
-      <c r="W105" s="73"/>
-      <c r="X105" s="73"/>
-      <c r="Y105" s="73"/>
-    </row>
-    <row r="108" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A108" s="1" t="s">
+      <c r="C107" s="74"/>
+      <c r="D107" s="74"/>
+      <c r="E107" s="74"/>
+      <c r="F107" s="74"/>
+      <c r="G107" s="74"/>
+      <c r="H107" s="74"/>
+      <c r="I107" s="74"/>
+      <c r="J107" s="74"/>
+      <c r="K107" s="74"/>
+      <c r="L107" s="74"/>
+      <c r="M107" s="74"/>
+      <c r="N107" s="74"/>
+      <c r="O107" s="74"/>
+      <c r="P107" s="74"/>
+      <c r="Q107" s="74"/>
+      <c r="R107" s="74"/>
+      <c r="S107" s="74"/>
+      <c r="T107" s="74"/>
+      <c r="U107" s="74"/>
+      <c r="V107" s="74"/>
+      <c r="W107" s="74"/>
+      <c r="X107" s="74"/>
+      <c r="Y107" s="74"/>
+    </row>
+    <row r="110" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A110" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B110" s="8" t="s">
+    <row r="112" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B112" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="C110" s="8"/>
-      <c r="D110" s="25"/>
-    </row>
-    <row r="112" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B112" s="20" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="113" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B113" s="20"/>
+      <c r="C112" s="8"/>
+      <c r="D112" s="23"/>
     </row>
     <row r="114" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B114" s="20" t="s">
-        <v>168</v>
-      </c>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="115" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B115" s="20"/>
     </row>
     <row r="116" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B116" s="8" t="s">
+      <c r="B116" s="20" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="118" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B118" s="8" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="118" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="35" t="s">
+    <row r="120" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B120" s="58" t="s">
         <v>162</v>
       </c>
-      <c r="C118" s="35"/>
-      <c r="D118" s="35"/>
-      <c r="E118" s="35"/>
-      <c r="F118" s="35"/>
-      <c r="G118" s="35"/>
-      <c r="H118" s="35"/>
-      <c r="I118" s="35"/>
-      <c r="J118" s="35"/>
-      <c r="K118" s="35"/>
-      <c r="L118" s="35"/>
-      <c r="M118" s="35"/>
-      <c r="N118" s="35"/>
-      <c r="O118" s="35"/>
-      <c r="P118" s="35"/>
-      <c r="Q118" s="35"/>
-      <c r="R118" s="35"/>
-      <c r="S118" s="35"/>
-      <c r="T118" s="35"/>
-      <c r="U118" s="35"/>
-      <c r="V118" s="35"/>
-      <c r="W118" s="35"/>
-      <c r="X118" s="35"/>
-      <c r="Y118" s="35"/>
-      <c r="Z118" s="35"/>
-      <c r="AA118" s="35"/>
-      <c r="AB118" s="35"/>
-      <c r="AC118" s="35"/>
-    </row>
-    <row r="119" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B119" s="26" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="120" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B120" s="26"/>
+      <c r="C120" s="58"/>
+      <c r="D120" s="58"/>
+      <c r="E120" s="58"/>
+      <c r="F120" s="58"/>
+      <c r="G120" s="58"/>
+      <c r="H120" s="58"/>
+      <c r="I120" s="58"/>
+      <c r="J120" s="58"/>
+      <c r="K120" s="58"/>
+      <c r="L120" s="58"/>
+      <c r="M120" s="58"/>
+      <c r="N120" s="58"/>
+      <c r="O120" s="58"/>
+      <c r="P120" s="58"/>
+      <c r="Q120" s="58"/>
+      <c r="R120" s="58"/>
+      <c r="S120" s="58"/>
+      <c r="T120" s="58"/>
+      <c r="U120" s="58"/>
+      <c r="V120" s="58"/>
+      <c r="W120" s="58"/>
+      <c r="X120" s="58"/>
+      <c r="Y120" s="58"/>
+      <c r="Z120" s="58"/>
+      <c r="AA120" s="58"/>
+      <c r="AB120" s="58"/>
+      <c r="AC120" s="58"/>
     </row>
     <row r="121" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B121" s="20" t="s">
+      <c r="B121" s="24" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="122" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B122" s="24"/>
+    </row>
+    <row r="123" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B123" s="20" t="s">
         <v>161</v>
-      </c>
-    </row>
-    <row r="122" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B122" s="20"/>
-    </row>
-    <row r="123" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B123" s="28" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="124" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B124" s="20"/>
     </row>
     <row r="125" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B125" s="20" t="s">
-        <v>181</v>
-      </c>
+      <c r="B125" s="26" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="126" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B126" s="20"/>
     </row>
     <row r="127" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B127" s="8" t="s">
+      <c r="B127" s="20" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="129" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B129" s="8" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="129" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B129" s="20" t="s">
+    <row r="131" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B131" s="20" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="131" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B131" s="8" t="s">
+    <row r="133" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B133" s="8" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="133" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B133" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="L133" s="27" t="s">
+    <row r="135" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B135" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="M133" s="20"/>
+      <c r="L135" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="M135" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="30">
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O21:W21"/>
+    <mergeCell ref="O22:W22"/>
+    <mergeCell ref="O23:W23"/>
+    <mergeCell ref="O24:W24"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="O19:T19"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="R12:AC12"/>
-    <mergeCell ref="B118:AC118"/>
+    <mergeCell ref="B120:AC120"/>
     <mergeCell ref="L11:P11"/>
     <mergeCell ref="L12:P12"/>
     <mergeCell ref="L13:P13"/>
@@ -6327,19 +6804,13 @@
     <mergeCell ref="L8:P8"/>
     <mergeCell ref="L9:P9"/>
     <mergeCell ref="L10:P10"/>
-    <mergeCell ref="B105:Y105"/>
-    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="B107:Y107"/>
     <mergeCell ref="O17:T17"/>
-    <mergeCell ref="O19:T19"/>
-    <mergeCell ref="O20:T20"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O16:T16"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="L133" location="Dialogues!A1" display="Dialogues!A1" xr:uid="{5724AB96-1B0F-4DFD-A35F-382AC93CCD96}"/>
-    <hyperlink ref="B119" location="'Item List'!A1" display="'Item List'!A1" xr:uid="{961E795F-F85E-4E2A-BAED-F63C80C609A5}"/>
+    <hyperlink ref="L135" location="Dialogues!A1" display="Dialogues!A1" xr:uid="{5724AB96-1B0F-4DFD-A35F-382AC93CCD96}"/>
+    <hyperlink ref="B121" location="'Item List'!A1" display="'Item List'!A1" xr:uid="{961E795F-F85E-4E2A-BAED-F63C80C609A5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -6351,1008 +6822,1098 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A2:U26"/>
+  <dimension ref="A2:T36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="90" t="s">
-        <v>241</v>
-      </c>
-      <c r="B4" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="C4" s="55"/>
-      <c r="D4" s="84" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="1"/>
+    </row>
+    <row r="4" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="1"/>
+      <c r="B4" s="8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" s="48"/>
+      <c r="D6" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="85"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="55" t="s">
+      <c r="E6" s="79"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55" t="s">
+      <c r="H6" s="48"/>
+      <c r="I6" s="48" t="s">
         <v>118</v>
       </c>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55" t="s">
+      <c r="J6" s="48"/>
+      <c r="K6" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="55"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="55" t="s">
+      <c r="L6" s="79"/>
+      <c r="M6" s="79"/>
+      <c r="N6" s="79"/>
+      <c r="O6" s="79"/>
+      <c r="P6" s="79"/>
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="48" t="s">
+        <v>217</v>
+      </c>
+      <c r="T6" s="48"/>
+    </row>
+    <row r="7" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="35">
+        <v>1</v>
+      </c>
+      <c r="B7" s="83" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" s="83"/>
+      <c r="D7" s="84" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="85"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7" s="81"/>
+      <c r="I7" s="82" t="s">
+        <v>92</v>
+      </c>
+      <c r="J7" s="82"/>
+      <c r="K7" s="92" t="s">
+        <v>94</v>
+      </c>
+      <c r="L7" s="93"/>
+      <c r="M7" s="93"/>
+      <c r="N7" s="93"/>
+      <c r="O7" s="93"/>
+      <c r="P7" s="93"/>
+      <c r="Q7" s="93"/>
+      <c r="R7" s="93"/>
+      <c r="S7" s="76" t="s">
         <v>219</v>
       </c>
-      <c r="U4" s="55"/>
-    </row>
-    <row r="5" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="91">
+      <c r="T7" s="76"/>
+    </row>
+    <row r="8" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="35">
+        <v>2</v>
+      </c>
+      <c r="B8" s="83" t="s">
+        <v>202</v>
+      </c>
+      <c r="C8" s="83"/>
+      <c r="D8" s="84" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="85"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="87" t="s">
+        <v>90</v>
+      </c>
+      <c r="H8" s="87"/>
+      <c r="I8" s="82" t="s">
+        <v>92</v>
+      </c>
+      <c r="J8" s="82"/>
+      <c r="K8" s="92" t="s">
+        <v>177</v>
+      </c>
+      <c r="L8" s="93"/>
+      <c r="M8" s="93"/>
+      <c r="N8" s="93"/>
+      <c r="O8" s="93"/>
+      <c r="P8" s="93"/>
+      <c r="Q8" s="93"/>
+      <c r="R8" s="93"/>
+      <c r="S8" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="T8" s="76"/>
+    </row>
+    <row r="9" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="35">
+        <v>3</v>
+      </c>
+      <c r="B9" s="83" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="83"/>
+      <c r="D9" s="84" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="85"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="81"/>
+      <c r="I9" s="82" t="s">
+        <v>92</v>
+      </c>
+      <c r="J9" s="82"/>
+      <c r="K9" s="92" t="s">
+        <v>108</v>
+      </c>
+      <c r="L9" s="93"/>
+      <c r="M9" s="93"/>
+      <c r="N9" s="93"/>
+      <c r="O9" s="93"/>
+      <c r="P9" s="93"/>
+      <c r="Q9" s="93"/>
+      <c r="R9" s="93"/>
+      <c r="S9" s="77" t="s">
+        <v>219</v>
+      </c>
+      <c r="T9" s="76"/>
+    </row>
+    <row r="10" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="35">
+        <v>4</v>
+      </c>
+      <c r="B10" s="83" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" s="83"/>
+      <c r="D10" s="84" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="85"/>
+      <c r="F10" s="86"/>
+      <c r="G10" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="81"/>
+      <c r="I10" s="82" t="s">
+        <v>92</v>
+      </c>
+      <c r="J10" s="82"/>
+      <c r="K10" s="92" t="s">
+        <v>108</v>
+      </c>
+      <c r="L10" s="93"/>
+      <c r="M10" s="93"/>
+      <c r="N10" s="93"/>
+      <c r="O10" s="93"/>
+      <c r="P10" s="93"/>
+      <c r="Q10" s="93"/>
+      <c r="R10" s="93"/>
+      <c r="S10" s="77" t="s">
+        <v>219</v>
+      </c>
+      <c r="T10" s="76"/>
+    </row>
+    <row r="11" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="35">
+        <v>5</v>
+      </c>
+      <c r="B11" s="83" t="s">
+        <v>189</v>
+      </c>
+      <c r="C11" s="83"/>
+      <c r="D11" s="84" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="85"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="81"/>
+      <c r="I11" s="82" t="s">
+        <v>92</v>
+      </c>
+      <c r="J11" s="82"/>
+      <c r="K11" s="92" t="s">
+        <v>108</v>
+      </c>
+      <c r="L11" s="93"/>
+      <c r="M11" s="93"/>
+      <c r="N11" s="93"/>
+      <c r="O11" s="93"/>
+      <c r="P11" s="93"/>
+      <c r="Q11" s="93"/>
+      <c r="R11" s="93"/>
+      <c r="S11" s="77" t="s">
+        <v>219</v>
+      </c>
+      <c r="T11" s="76"/>
+    </row>
+    <row r="12" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="35">
+        <v>6</v>
+      </c>
+      <c r="B12" s="83" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="83"/>
+      <c r="D12" s="84" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="85"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="81"/>
+      <c r="I12" s="82" t="s">
+        <v>92</v>
+      </c>
+      <c r="J12" s="82"/>
+      <c r="K12" s="92" t="s">
+        <v>108</v>
+      </c>
+      <c r="L12" s="93"/>
+      <c r="M12" s="93"/>
+      <c r="N12" s="93"/>
+      <c r="O12" s="93"/>
+      <c r="P12" s="93"/>
+      <c r="Q12" s="93"/>
+      <c r="R12" s="93"/>
+      <c r="S12" s="77" t="s">
+        <v>219</v>
+      </c>
+      <c r="T12" s="76"/>
+    </row>
+    <row r="13" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="35">
+        <v>7</v>
+      </c>
+      <c r="B13" s="83" t="s">
+        <v>191</v>
+      </c>
+      <c r="C13" s="83"/>
+      <c r="D13" s="84" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="85"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" s="81"/>
+      <c r="I13" s="82" t="s">
+        <v>92</v>
+      </c>
+      <c r="J13" s="82"/>
+      <c r="K13" s="92" t="s">
+        <v>108</v>
+      </c>
+      <c r="L13" s="93"/>
+      <c r="M13" s="93"/>
+      <c r="N13" s="93"/>
+      <c r="O13" s="93"/>
+      <c r="P13" s="93"/>
+      <c r="Q13" s="93"/>
+      <c r="R13" s="93"/>
+      <c r="S13" s="77" t="s">
+        <v>219</v>
+      </c>
+      <c r="T13" s="76"/>
+    </row>
+    <row r="14" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="35">
+        <v>8</v>
+      </c>
+      <c r="B14" s="83" t="s">
+        <v>182</v>
+      </c>
+      <c r="C14" s="83"/>
+      <c r="D14" s="89" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="90"/>
+      <c r="F14" s="91"/>
+      <c r="G14" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="81"/>
+      <c r="I14" s="82" t="s">
+        <v>92</v>
+      </c>
+      <c r="J14" s="82"/>
+      <c r="K14" s="92" t="s">
+        <v>109</v>
+      </c>
+      <c r="L14" s="93"/>
+      <c r="M14" s="93"/>
+      <c r="N14" s="93"/>
+      <c r="O14" s="93"/>
+      <c r="P14" s="93"/>
+      <c r="Q14" s="93"/>
+      <c r="R14" s="93"/>
+      <c r="S14" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="T14" s="76"/>
+    </row>
+    <row r="15" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="35">
+        <v>9</v>
+      </c>
+      <c r="B15" s="83" t="s">
+        <v>183</v>
+      </c>
+      <c r="C15" s="83"/>
+      <c r="D15" s="84" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="85"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15" s="81"/>
+      <c r="I15" s="82" t="s">
+        <v>92</v>
+      </c>
+      <c r="J15" s="82"/>
+      <c r="K15" s="92" t="s">
+        <v>109</v>
+      </c>
+      <c r="L15" s="93"/>
+      <c r="M15" s="93"/>
+      <c r="N15" s="93"/>
+      <c r="O15" s="93"/>
+      <c r="P15" s="93"/>
+      <c r="Q15" s="93"/>
+      <c r="R15" s="93"/>
+      <c r="S15" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="T15" s="76"/>
+    </row>
+    <row r="16" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="35">
+        <v>10</v>
+      </c>
+      <c r="B16" s="83" t="s">
+        <v>184</v>
+      </c>
+      <c r="C16" s="83"/>
+      <c r="D16" s="84" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="85"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" s="81"/>
+      <c r="I16" s="82" t="s">
+        <v>92</v>
+      </c>
+      <c r="J16" s="82"/>
+      <c r="K16" s="92" t="s">
+        <v>116</v>
+      </c>
+      <c r="L16" s="93"/>
+      <c r="M16" s="93"/>
+      <c r="N16" s="93"/>
+      <c r="O16" s="93"/>
+      <c r="P16" s="93"/>
+      <c r="Q16" s="93"/>
+      <c r="R16" s="93"/>
+      <c r="S16" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="T16" s="76"/>
+    </row>
+    <row r="17" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="35">
+        <v>11</v>
+      </c>
+      <c r="B17" s="83" t="s">
+        <v>185</v>
+      </c>
+      <c r="C17" s="83"/>
+      <c r="D17" s="84" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="85"/>
+      <c r="F17" s="86"/>
+      <c r="G17" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="81"/>
+      <c r="I17" s="82" t="s">
+        <v>92</v>
+      </c>
+      <c r="J17" s="82"/>
+      <c r="K17" s="92" t="s">
+        <v>117</v>
+      </c>
+      <c r="L17" s="93"/>
+      <c r="M17" s="93"/>
+      <c r="N17" s="93"/>
+      <c r="O17" s="93"/>
+      <c r="P17" s="93"/>
+      <c r="Q17" s="93"/>
+      <c r="R17" s="93"/>
+      <c r="S17" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="T17" s="76"/>
+    </row>
+    <row r="18" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="35">
+        <v>12</v>
+      </c>
+      <c r="B18" s="83" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" s="83"/>
+      <c r="D18" s="84" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" s="85"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="81"/>
+      <c r="I18" s="82" t="s">
+        <v>92</v>
+      </c>
+      <c r="J18" s="82"/>
+      <c r="K18" s="92" t="s">
+        <v>117</v>
+      </c>
+      <c r="L18" s="93"/>
+      <c r="M18" s="93"/>
+      <c r="N18" s="93"/>
+      <c r="O18" s="93"/>
+      <c r="P18" s="93"/>
+      <c r="Q18" s="93"/>
+      <c r="R18" s="93"/>
+      <c r="S18" s="99" t="s">
+        <v>219</v>
+      </c>
+      <c r="T18" s="76"/>
+    </row>
+    <row r="19" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="35">
+        <v>13</v>
+      </c>
+      <c r="B19" s="83" t="s">
+        <v>192</v>
+      </c>
+      <c r="C19" s="83"/>
+      <c r="D19" s="84" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" s="85"/>
+      <c r="F19" s="86"/>
+      <c r="G19" s="87" t="s">
+        <v>90</v>
+      </c>
+      <c r="H19" s="87"/>
+      <c r="I19" s="82" t="s">
+        <v>92</v>
+      </c>
+      <c r="J19" s="82"/>
+      <c r="K19" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19" s="93"/>
+      <c r="M19" s="93"/>
+      <c r="N19" s="93"/>
+      <c r="O19" s="93"/>
+      <c r="P19" s="93"/>
+      <c r="Q19" s="93"/>
+      <c r="R19" s="93"/>
+      <c r="S19" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="T19" s="76"/>
+    </row>
+    <row r="20" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="35">
+        <v>14</v>
+      </c>
+      <c r="B20" s="83" t="s">
+        <v>194</v>
+      </c>
+      <c r="C20" s="83"/>
+      <c r="D20" s="84" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="85"/>
+      <c r="F20" s="86"/>
+      <c r="G20" s="87" t="s">
+        <v>90</v>
+      </c>
+      <c r="H20" s="87"/>
+      <c r="I20" s="82" t="s">
+        <v>92</v>
+      </c>
+      <c r="J20" s="82"/>
+      <c r="K20" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="L20" s="93"/>
+      <c r="M20" s="93"/>
+      <c r="N20" s="93"/>
+      <c r="O20" s="93"/>
+      <c r="P20" s="93"/>
+      <c r="Q20" s="93"/>
+      <c r="R20" s="93"/>
+      <c r="S20" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="T20" s="76"/>
+    </row>
+    <row r="21" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="35">
+        <v>15</v>
+      </c>
+      <c r="B21" s="83" t="s">
+        <v>195</v>
+      </c>
+      <c r="C21" s="83"/>
+      <c r="D21" s="84" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="85"/>
+      <c r="F21" s="86"/>
+      <c r="G21" s="87" t="s">
+        <v>90</v>
+      </c>
+      <c r="H21" s="87"/>
+      <c r="I21" s="88" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="88"/>
+      <c r="K21" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="L21" s="93"/>
+      <c r="M21" s="93"/>
+      <c r="N21" s="93"/>
+      <c r="O21" s="93"/>
+      <c r="P21" s="93"/>
+      <c r="Q21" s="93"/>
+      <c r="R21" s="93"/>
+      <c r="S21" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="T21" s="76"/>
+    </row>
+    <row r="22" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="35">
+        <v>16</v>
+      </c>
+      <c r="B22" s="83" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" s="83"/>
+      <c r="D22" s="84" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" s="85"/>
+      <c r="F22" s="86"/>
+      <c r="G22" s="87" t="s">
+        <v>90</v>
+      </c>
+      <c r="H22" s="87"/>
+      <c r="I22" s="88" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="88"/>
+      <c r="K22" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="L22" s="93"/>
+      <c r="M22" s="93"/>
+      <c r="N22" s="93"/>
+      <c r="O22" s="93"/>
+      <c r="P22" s="93"/>
+      <c r="Q22" s="93"/>
+      <c r="R22" s="93"/>
+      <c r="S22" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="T22" s="76"/>
+    </row>
+    <row r="23" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="35">
+        <v>17</v>
+      </c>
+      <c r="B23" s="83" t="s">
+        <v>197</v>
+      </c>
+      <c r="C23" s="83"/>
+      <c r="D23" s="84" t="s">
+        <v>104</v>
+      </c>
+      <c r="E23" s="85"/>
+      <c r="F23" s="86"/>
+      <c r="G23" s="87" t="s">
+        <v>90</v>
+      </c>
+      <c r="H23" s="87"/>
+      <c r="I23" s="88" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="88"/>
+      <c r="K23" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="L23" s="93"/>
+      <c r="M23" s="93"/>
+      <c r="N23" s="93"/>
+      <c r="O23" s="93"/>
+      <c r="P23" s="93"/>
+      <c r="Q23" s="93"/>
+      <c r="R23" s="93"/>
+      <c r="S23" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="T23" s="76"/>
+    </row>
+    <row r="24" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="35">
+        <v>18</v>
+      </c>
+      <c r="B24" s="83" t="s">
+        <v>198</v>
+      </c>
+      <c r="C24" s="83"/>
+      <c r="D24" s="84" t="s">
+        <v>105</v>
+      </c>
+      <c r="E24" s="85"/>
+      <c r="F24" s="86"/>
+      <c r="G24" s="87" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="87"/>
+      <c r="I24" s="88" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="88"/>
+      <c r="K24" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="L24" s="93"/>
+      <c r="M24" s="93"/>
+      <c r="N24" s="93"/>
+      <c r="O24" s="93"/>
+      <c r="P24" s="93"/>
+      <c r="Q24" s="93"/>
+      <c r="R24" s="93"/>
+      <c r="S24" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="T24" s="76"/>
+    </row>
+    <row r="25" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="35">
+        <v>19</v>
+      </c>
+      <c r="B25" s="83" t="s">
+        <v>199</v>
+      </c>
+      <c r="C25" s="83"/>
+      <c r="D25" s="84" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="85"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="87" t="s">
+        <v>90</v>
+      </c>
+      <c r="H25" s="87"/>
+      <c r="I25" s="88" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="88"/>
+      <c r="K25" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="L25" s="93"/>
+      <c r="M25" s="93"/>
+      <c r="N25" s="93"/>
+      <c r="O25" s="93"/>
+      <c r="P25" s="93"/>
+      <c r="Q25" s="93"/>
+      <c r="R25" s="93"/>
+      <c r="S25" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="T25" s="76"/>
+    </row>
+    <row r="26" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="35">
+        <v>20</v>
+      </c>
+      <c r="B26" s="83" t="s">
+        <v>200</v>
+      </c>
+      <c r="C26" s="83"/>
+      <c r="D26" s="84" t="s">
+        <v>107</v>
+      </c>
+      <c r="E26" s="85"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="87" t="s">
+        <v>90</v>
+      </c>
+      <c r="H26" s="87"/>
+      <c r="I26" s="88" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="88"/>
+      <c r="K26" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="L26" s="93"/>
+      <c r="M26" s="93"/>
+      <c r="N26" s="93"/>
+      <c r="O26" s="93"/>
+      <c r="P26" s="93"/>
+      <c r="Q26" s="93"/>
+      <c r="R26" s="93"/>
+      <c r="S26" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="T26" s="76"/>
+    </row>
+    <row r="27" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="35">
+        <v>21</v>
+      </c>
+      <c r="B27" s="83" t="s">
+        <v>201</v>
+      </c>
+      <c r="C27" s="83"/>
+      <c r="D27" s="84" t="s">
+        <v>101</v>
+      </c>
+      <c r="E27" s="85"/>
+      <c r="F27" s="86"/>
+      <c r="G27" s="87" t="s">
+        <v>90</v>
+      </c>
+      <c r="H27" s="87"/>
+      <c r="I27" s="88" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="88"/>
+      <c r="K27" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="L27" s="93"/>
+      <c r="M27" s="93"/>
+      <c r="N27" s="93"/>
+      <c r="O27" s="93"/>
+      <c r="P27" s="93"/>
+      <c r="Q27" s="93"/>
+      <c r="R27" s="93"/>
+      <c r="S27" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="T27" s="76"/>
+    </row>
+    <row r="28" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="110">
+        <v>13</v>
+      </c>
+      <c r="B28" s="111" t="s">
+        <v>193</v>
+      </c>
+      <c r="C28" s="111"/>
+      <c r="D28" s="112" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" s="113"/>
+      <c r="F28" s="114"/>
+      <c r="G28" s="115" t="s">
+        <v>90</v>
+      </c>
+      <c r="H28" s="115"/>
+      <c r="I28" s="116" t="s">
+        <v>92</v>
+      </c>
+      <c r="J28" s="116"/>
+      <c r="K28" s="122" t="s">
+        <v>110</v>
+      </c>
+      <c r="L28" s="123"/>
+      <c r="M28" s="123"/>
+      <c r="N28" s="123"/>
+      <c r="O28" s="123"/>
+      <c r="P28" s="123"/>
+      <c r="Q28" s="123"/>
+      <c r="R28" s="123"/>
+      <c r="S28" s="117" t="s">
+        <v>218</v>
+      </c>
+      <c r="T28" s="117"/>
+    </row>
+    <row r="31" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B31" s="8" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B32" s="8"/>
+    </row>
+    <row r="33" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="C33" s="48"/>
+      <c r="D33" s="78" t="s">
+        <v>95</v>
+      </c>
+      <c r="E33" s="79"/>
+      <c r="F33" s="80"/>
+      <c r="G33" s="48" t="s">
+        <v>217</v>
+      </c>
+      <c r="H33" s="48"/>
+    </row>
+    <row r="34" spans="1:8" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A34" s="11">
         <v>1</v>
       </c>
-      <c r="B5" s="89" t="s">
-        <v>182</v>
-      </c>
-      <c r="C5" s="89"/>
-      <c r="D5" s="74" t="s">
-        <v>93</v>
-      </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="H5" s="77"/>
-      <c r="I5" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="J5" s="78"/>
-      <c r="K5" s="71" t="s">
-        <v>94</v>
-      </c>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
-      <c r="P5" s="71"/>
-      <c r="Q5" s="71"/>
-      <c r="R5" s="71"/>
-      <c r="S5" s="71"/>
-      <c r="T5" s="87" t="s">
-        <v>221</v>
-      </c>
-      <c r="U5" s="87"/>
-    </row>
-    <row r="6" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="91">
+      <c r="B34" s="97" t="s">
+        <v>278</v>
+      </c>
+      <c r="C34" s="97"/>
+      <c r="D34" s="84" t="s">
+        <v>281</v>
+      </c>
+      <c r="E34" s="85"/>
+      <c r="F34" s="86"/>
+      <c r="G34" s="76" t="s">
+        <v>218</v>
+      </c>
+      <c r="H34" s="76"/>
+    </row>
+    <row r="35" spans="1:8" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A35" s="11">
         <v>2</v>
       </c>
-      <c r="B6" s="89" t="s">
-        <v>203</v>
-      </c>
-      <c r="C6" s="89"/>
-      <c r="D6" s="74" t="s">
-        <v>112</v>
-      </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="H6" s="79"/>
-      <c r="I6" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="J6" s="78"/>
-      <c r="K6" s="71" t="s">
-        <v>178</v>
-      </c>
-      <c r="L6" s="71"/>
-      <c r="M6" s="71"/>
-      <c r="N6" s="71"/>
-      <c r="O6" s="71"/>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="71"/>
-      <c r="T6" s="87" t="s">
-        <v>221</v>
-      </c>
-      <c r="U6" s="87"/>
-    </row>
-    <row r="7" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="91">
+      <c r="B35" s="97" t="s">
+        <v>279</v>
+      </c>
+      <c r="C35" s="97"/>
+      <c r="D35" s="84" t="s">
+        <v>282</v>
+      </c>
+      <c r="E35" s="85"/>
+      <c r="F35" s="86"/>
+      <c r="G35" s="76" t="s">
+        <v>218</v>
+      </c>
+      <c r="H35" s="76"/>
+    </row>
+    <row r="36" spans="1:8" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A36" s="11">
         <v>3</v>
       </c>
-      <c r="B7" s="89" t="s">
-        <v>188</v>
-      </c>
-      <c r="C7" s="89"/>
-      <c r="D7" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="75"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="H7" s="77"/>
-      <c r="I7" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="J7" s="78"/>
-      <c r="K7" s="71" t="s">
-        <v>108</v>
-      </c>
-      <c r="L7" s="71"/>
-      <c r="M7" s="71"/>
-      <c r="N7" s="71"/>
-      <c r="O7" s="71"/>
-      <c r="P7" s="71"/>
-      <c r="Q7" s="71"/>
-      <c r="R7" s="71"/>
-      <c r="S7" s="71"/>
-      <c r="T7" s="88" t="s">
-        <v>221</v>
-      </c>
-      <c r="U7" s="87"/>
-    </row>
-    <row r="8" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="91">
-        <v>4</v>
-      </c>
-      <c r="B8" s="89" t="s">
-        <v>189</v>
-      </c>
-      <c r="C8" s="89"/>
-      <c r="D8" s="74" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="75"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="H8" s="77"/>
-      <c r="I8" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="J8" s="78"/>
-      <c r="K8" s="71" t="s">
-        <v>108</v>
-      </c>
-      <c r="L8" s="71"/>
-      <c r="M8" s="71"/>
-      <c r="N8" s="71"/>
-      <c r="O8" s="71"/>
-      <c r="P8" s="71"/>
-      <c r="Q8" s="71"/>
-      <c r="R8" s="71"/>
-      <c r="S8" s="71"/>
-      <c r="T8" s="88" t="s">
-        <v>221</v>
-      </c>
-      <c r="U8" s="87"/>
-    </row>
-    <row r="9" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="91">
-        <v>5</v>
-      </c>
-      <c r="B9" s="89" t="s">
-        <v>190</v>
-      </c>
-      <c r="C9" s="89"/>
-      <c r="D9" s="74" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="75"/>
-      <c r="F9" s="76"/>
-      <c r="G9" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="H9" s="77"/>
-      <c r="I9" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="J9" s="78"/>
-      <c r="K9" s="71" t="s">
-        <v>108</v>
-      </c>
-      <c r="L9" s="71"/>
-      <c r="M9" s="71"/>
-      <c r="N9" s="71"/>
-      <c r="O9" s="71"/>
-      <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
-      <c r="R9" s="71"/>
-      <c r="S9" s="71"/>
-      <c r="T9" s="88" t="s">
-        <v>221</v>
-      </c>
-      <c r="U9" s="87"/>
-    </row>
-    <row r="10" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="91">
-        <v>6</v>
-      </c>
-      <c r="B10" s="89" t="s">
-        <v>191</v>
-      </c>
-      <c r="C10" s="89"/>
-      <c r="D10" s="74" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="75"/>
-      <c r="F10" s="76"/>
-      <c r="G10" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="H10" s="77"/>
-      <c r="I10" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="J10" s="78"/>
-      <c r="K10" s="71" t="s">
-        <v>108</v>
-      </c>
-      <c r="L10" s="71"/>
-      <c r="M10" s="71"/>
-      <c r="N10" s="71"/>
-      <c r="O10" s="71"/>
-      <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
-      <c r="R10" s="71"/>
-      <c r="S10" s="71"/>
-      <c r="T10" s="88" t="s">
-        <v>221</v>
-      </c>
-      <c r="U10" s="87"/>
-    </row>
-    <row r="11" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="91">
-        <v>7</v>
-      </c>
-      <c r="B11" s="89" t="s">
-        <v>192</v>
-      </c>
-      <c r="C11" s="89"/>
-      <c r="D11" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="75"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="H11" s="77"/>
-      <c r="I11" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="J11" s="78"/>
-      <c r="K11" s="71" t="s">
-        <v>108</v>
-      </c>
-      <c r="L11" s="71"/>
-      <c r="M11" s="71"/>
-      <c r="N11" s="71"/>
-      <c r="O11" s="71"/>
-      <c r="P11" s="71"/>
-      <c r="Q11" s="71"/>
-      <c r="R11" s="71"/>
-      <c r="S11" s="71"/>
-      <c r="T11" s="88" t="s">
-        <v>221</v>
-      </c>
-      <c r="U11" s="87"/>
-    </row>
-    <row r="12" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="91">
-        <v>8</v>
-      </c>
-      <c r="B12" s="89" t="s">
-        <v>183</v>
-      </c>
-      <c r="C12" s="89"/>
-      <c r="D12" s="81" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12" s="82"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" s="77"/>
-      <c r="I12" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="J12" s="78"/>
-      <c r="K12" s="71" t="s">
-        <v>109</v>
-      </c>
-      <c r="L12" s="71"/>
-      <c r="M12" s="71"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="71"/>
-      <c r="P12" s="71"/>
-      <c r="Q12" s="71"/>
-      <c r="R12" s="71"/>
-      <c r="S12" s="71"/>
-      <c r="T12" s="87" t="s">
-        <v>221</v>
-      </c>
-      <c r="U12" s="87"/>
-    </row>
-    <row r="13" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="91">
-        <v>9</v>
-      </c>
-      <c r="B13" s="89" t="s">
-        <v>184</v>
-      </c>
-      <c r="C13" s="89"/>
-      <c r="D13" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" s="75"/>
-      <c r="F13" s="76"/>
-      <c r="G13" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="H13" s="77"/>
-      <c r="I13" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="J13" s="78"/>
-      <c r="K13" s="71" t="s">
-        <v>109</v>
-      </c>
-      <c r="L13" s="71"/>
-      <c r="M13" s="71"/>
-      <c r="N13" s="71"/>
-      <c r="O13" s="71"/>
-      <c r="P13" s="71"/>
-      <c r="Q13" s="71"/>
-      <c r="R13" s="71"/>
-      <c r="S13" s="71"/>
-      <c r="T13" s="87" t="s">
-        <v>221</v>
-      </c>
-      <c r="U13" s="87"/>
-    </row>
-    <row r="14" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="91">
-        <v>10</v>
-      </c>
-      <c r="B14" s="89" t="s">
-        <v>185</v>
-      </c>
-      <c r="C14" s="89"/>
-      <c r="D14" s="74" t="s">
-        <v>115</v>
-      </c>
-      <c r="E14" s="75"/>
-      <c r="F14" s="76"/>
-      <c r="G14" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="H14" s="77"/>
-      <c r="I14" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="J14" s="78"/>
-      <c r="K14" s="71" t="s">
-        <v>116</v>
-      </c>
-      <c r="L14" s="71"/>
-      <c r="M14" s="71"/>
-      <c r="N14" s="71"/>
-      <c r="O14" s="71"/>
-      <c r="P14" s="71"/>
-      <c r="Q14" s="71"/>
-      <c r="R14" s="71"/>
-      <c r="S14" s="71"/>
-      <c r="T14" s="87" t="s">
-        <v>221</v>
-      </c>
-      <c r="U14" s="87"/>
-    </row>
-    <row r="15" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="91">
-        <v>11</v>
-      </c>
-      <c r="B15" s="89" t="s">
-        <v>186</v>
-      </c>
-      <c r="C15" s="89"/>
-      <c r="D15" s="74" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="75"/>
-      <c r="F15" s="76"/>
-      <c r="G15" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="H15" s="77"/>
-      <c r="I15" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="J15" s="78"/>
-      <c r="K15" s="71" t="s">
-        <v>117</v>
-      </c>
-      <c r="L15" s="71"/>
-      <c r="M15" s="71"/>
-      <c r="N15" s="71"/>
-      <c r="O15" s="71"/>
-      <c r="P15" s="71"/>
-      <c r="Q15" s="71"/>
-      <c r="R15" s="71"/>
-      <c r="S15" s="71"/>
-      <c r="T15" s="87" t="s">
-        <v>221</v>
-      </c>
-      <c r="U15" s="87"/>
-    </row>
-    <row r="16" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="91">
-        <v>12</v>
-      </c>
-      <c r="B16" s="89" t="s">
-        <v>187</v>
-      </c>
-      <c r="C16" s="89"/>
-      <c r="D16" s="74" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" s="75"/>
-      <c r="F16" s="76"/>
-      <c r="G16" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="H16" s="77"/>
-      <c r="I16" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="J16" s="78"/>
-      <c r="K16" s="71" t="s">
-        <v>117</v>
-      </c>
-      <c r="L16" s="71"/>
-      <c r="M16" s="71"/>
-      <c r="N16" s="71"/>
-      <c r="O16" s="71"/>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="71"/>
-      <c r="R16" s="71"/>
-      <c r="S16" s="71"/>
-      <c r="T16" s="87" t="s">
-        <v>220</v>
-      </c>
-      <c r="U16" s="87"/>
-    </row>
-    <row r="17" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A17" s="91">
-        <v>13</v>
-      </c>
-      <c r="B17" s="89" t="s">
-        <v>194</v>
-      </c>
-      <c r="C17" s="89"/>
-      <c r="D17" s="74" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="75"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="H17" s="79"/>
-      <c r="I17" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="J17" s="78"/>
-      <c r="K17" s="71" t="s">
-        <v>110</v>
-      </c>
-      <c r="L17" s="71"/>
-      <c r="M17" s="71"/>
-      <c r="N17" s="71"/>
-      <c r="O17" s="71"/>
-      <c r="P17" s="71"/>
-      <c r="Q17" s="71"/>
-      <c r="R17" s="71"/>
-      <c r="S17" s="71"/>
-      <c r="T17" s="87" t="s">
-        <v>221</v>
-      </c>
-      <c r="U17" s="87"/>
-    </row>
-    <row r="18" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="91">
-        <v>14</v>
-      </c>
-      <c r="B18" s="89" t="s">
-        <v>193</v>
-      </c>
-      <c r="C18" s="89"/>
-      <c r="D18" s="74" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" s="75"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="H18" s="79"/>
-      <c r="I18" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="J18" s="78"/>
-      <c r="K18" s="71" t="s">
-        <v>110</v>
-      </c>
-      <c r="L18" s="71"/>
-      <c r="M18" s="71"/>
-      <c r="N18" s="71"/>
-      <c r="O18" s="71"/>
-      <c r="P18" s="71"/>
-      <c r="Q18" s="71"/>
-      <c r="R18" s="71"/>
-      <c r="S18" s="71"/>
-      <c r="T18" s="87" t="s">
-        <v>221</v>
-      </c>
-      <c r="U18" s="87"/>
-    </row>
-    <row r="19" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="91">
-        <v>15</v>
-      </c>
-      <c r="B19" s="89" t="s">
-        <v>195</v>
-      </c>
-      <c r="C19" s="89"/>
-      <c r="D19" s="74" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" s="75"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="H19" s="79"/>
-      <c r="I19" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="J19" s="78"/>
-      <c r="K19" s="71" t="s">
-        <v>110</v>
-      </c>
-      <c r="L19" s="71"/>
-      <c r="M19" s="71"/>
-      <c r="N19" s="71"/>
-      <c r="O19" s="71"/>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="71"/>
-      <c r="R19" s="71"/>
-      <c r="S19" s="71"/>
-      <c r="T19" s="87" t="s">
-        <v>221</v>
-      </c>
-      <c r="U19" s="87"/>
-    </row>
-    <row r="20" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="91">
-        <v>16</v>
-      </c>
-      <c r="B20" s="89" t="s">
-        <v>196</v>
-      </c>
-      <c r="C20" s="89"/>
-      <c r="D20" s="74" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" s="75"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="H20" s="79"/>
-      <c r="I20" s="80" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" s="80"/>
-      <c r="K20" s="71" t="s">
-        <v>110</v>
-      </c>
-      <c r="L20" s="71"/>
-      <c r="M20" s="71"/>
-      <c r="N20" s="71"/>
-      <c r="O20" s="71"/>
-      <c r="P20" s="71"/>
-      <c r="Q20" s="71"/>
-      <c r="R20" s="71"/>
-      <c r="S20" s="71"/>
-      <c r="T20" s="87" t="s">
-        <v>221</v>
-      </c>
-      <c r="U20" s="87"/>
-    </row>
-    <row r="21" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="91">
-        <v>17</v>
-      </c>
-      <c r="B21" s="89" t="s">
-        <v>197</v>
-      </c>
-      <c r="C21" s="89"/>
-      <c r="D21" s="74" t="s">
-        <v>103</v>
-      </c>
-      <c r="E21" s="75"/>
-      <c r="F21" s="76"/>
-      <c r="G21" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="H21" s="79"/>
-      <c r="I21" s="80" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="80"/>
-      <c r="K21" s="71" t="s">
-        <v>110</v>
-      </c>
-      <c r="L21" s="71"/>
-      <c r="M21" s="71"/>
-      <c r="N21" s="71"/>
-      <c r="O21" s="71"/>
-      <c r="P21" s="71"/>
-      <c r="Q21" s="71"/>
-      <c r="R21" s="71"/>
-      <c r="S21" s="71"/>
-      <c r="T21" s="87" t="s">
-        <v>221</v>
-      </c>
-      <c r="U21" s="87"/>
-    </row>
-    <row r="22" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="91">
-        <v>18</v>
-      </c>
-      <c r="B22" s="89" t="s">
-        <v>198</v>
-      </c>
-      <c r="C22" s="89"/>
-      <c r="D22" s="74" t="s">
-        <v>104</v>
-      </c>
-      <c r="E22" s="75"/>
-      <c r="F22" s="76"/>
-      <c r="G22" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="H22" s="79"/>
-      <c r="I22" s="80" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="80"/>
-      <c r="K22" s="71" t="s">
-        <v>110</v>
-      </c>
-      <c r="L22" s="71"/>
-      <c r="M22" s="71"/>
-      <c r="N22" s="71"/>
-      <c r="O22" s="71"/>
-      <c r="P22" s="71"/>
-      <c r="Q22" s="71"/>
-      <c r="R22" s="71"/>
-      <c r="S22" s="71"/>
-      <c r="T22" s="87" t="s">
-        <v>221</v>
-      </c>
-      <c r="U22" s="87"/>
-    </row>
-    <row r="23" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="91">
-        <v>19</v>
-      </c>
-      <c r="B23" s="89" t="s">
-        <v>199</v>
-      </c>
-      <c r="C23" s="89"/>
-      <c r="D23" s="74" t="s">
-        <v>105</v>
-      </c>
-      <c r="E23" s="75"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="H23" s="79"/>
-      <c r="I23" s="80" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="80"/>
-      <c r="K23" s="71" t="s">
-        <v>110</v>
-      </c>
-      <c r="L23" s="71"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="71"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="71"/>
-      <c r="Q23" s="71"/>
-      <c r="R23" s="71"/>
-      <c r="S23" s="71"/>
-      <c r="T23" s="87" t="s">
-        <v>221</v>
-      </c>
-      <c r="U23" s="87"/>
-    </row>
-    <row r="24" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A24" s="91">
-        <v>20</v>
-      </c>
-      <c r="B24" s="89" t="s">
-        <v>200</v>
-      </c>
-      <c r="C24" s="89"/>
-      <c r="D24" s="74" t="s">
-        <v>106</v>
-      </c>
-      <c r="E24" s="75"/>
-      <c r="F24" s="76"/>
-      <c r="G24" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="H24" s="79"/>
-      <c r="I24" s="80" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="80"/>
-      <c r="K24" s="71" t="s">
-        <v>110</v>
-      </c>
-      <c r="L24" s="71"/>
-      <c r="M24" s="71"/>
-      <c r="N24" s="71"/>
-      <c r="O24" s="71"/>
-      <c r="P24" s="71"/>
-      <c r="Q24" s="71"/>
-      <c r="R24" s="71"/>
-      <c r="S24" s="71"/>
-      <c r="T24" s="87" t="s">
-        <v>221</v>
-      </c>
-      <c r="U24" s="87"/>
-    </row>
-    <row r="25" spans="1:21" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A25" s="91">
-        <v>21</v>
-      </c>
-      <c r="B25" s="89" t="s">
-        <v>201</v>
-      </c>
-      <c r="C25" s="89"/>
-      <c r="D25" s="74" t="s">
-        <v>107</v>
-      </c>
-      <c r="E25" s="75"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="H25" s="79"/>
-      <c r="I25" s="80" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="80"/>
-      <c r="K25" s="71" t="s">
-        <v>110</v>
-      </c>
-      <c r="L25" s="71"/>
-      <c r="M25" s="71"/>
-      <c r="N25" s="71"/>
-      <c r="O25" s="71"/>
-      <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
-      <c r="R25" s="71"/>
-      <c r="S25" s="71"/>
-      <c r="T25" s="87" t="s">
-        <v>221</v>
-      </c>
-      <c r="U25" s="87"/>
-    </row>
-    <row r="26" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="91">
-        <v>22</v>
-      </c>
-      <c r="B26" s="89" t="s">
-        <v>202</v>
-      </c>
-      <c r="C26" s="89"/>
-      <c r="D26" s="74" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26" s="75"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="H26" s="79"/>
-      <c r="I26" s="80" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="80"/>
-      <c r="K26" s="71" t="s">
-        <v>110</v>
-      </c>
-      <c r="L26" s="71"/>
-      <c r="M26" s="71"/>
-      <c r="N26" s="71"/>
-      <c r="O26" s="71"/>
-      <c r="P26" s="71"/>
-      <c r="Q26" s="71"/>
-      <c r="R26" s="71"/>
-      <c r="S26" s="71"/>
-      <c r="T26" s="87" t="s">
-        <v>221</v>
-      </c>
-      <c r="U26" s="87"/>
+      <c r="B36" s="97" t="s">
+        <v>280</v>
+      </c>
+      <c r="C36" s="97"/>
+      <c r="D36" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="E36" s="85"/>
+      <c r="F36" s="86"/>
+      <c r="G36" s="77" t="s">
+        <v>218</v>
+      </c>
+      <c r="H36" s="76"/>
     </row>
   </sheetData>
-  <mergeCells count="138">
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="T24:U24"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="T26:U26"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="G8:H8"/>
+  <mergeCells count="150">
+    <mergeCell ref="K6:R6"/>
+    <mergeCell ref="K7:R7"/>
+    <mergeCell ref="K8:R8"/>
+    <mergeCell ref="K9:R9"/>
+    <mergeCell ref="K10:R10"/>
+    <mergeCell ref="K11:R11"/>
+    <mergeCell ref="K12:R12"/>
+    <mergeCell ref="K13:R13"/>
+    <mergeCell ref="K14:R14"/>
+    <mergeCell ref="K15:R15"/>
+    <mergeCell ref="K16:R16"/>
+    <mergeCell ref="K17:R17"/>
+    <mergeCell ref="K18:R18"/>
+    <mergeCell ref="K19:R19"/>
+    <mergeCell ref="K20:R20"/>
+    <mergeCell ref="K21:R21"/>
+    <mergeCell ref="K22:R22"/>
+    <mergeCell ref="K23:R23"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
     <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K4:S4"/>
-    <mergeCell ref="K5:S5"/>
-    <mergeCell ref="K7:S7"/>
-    <mergeCell ref="K8:S8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:H6"/>
     <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
     <mergeCell ref="G26:H26"/>
     <mergeCell ref="I26:J26"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="D18:F18"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K24:R24"/>
+    <mergeCell ref="K25:R25"/>
+    <mergeCell ref="K26:R26"/>
+    <mergeCell ref="K27:R27"/>
+    <mergeCell ref="K28:R28"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D13:F13"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="G22:H22"/>
     <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="K26:S26"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:S16"/>
-    <mergeCell ref="K9:S9"/>
-    <mergeCell ref="K10:S10"/>
-    <mergeCell ref="K11:S11"/>
-    <mergeCell ref="K12:S12"/>
-    <mergeCell ref="K13:S13"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="G6:H6"/>
     <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:S6"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:S25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:S24"/>
-    <mergeCell ref="K19:S19"/>
-    <mergeCell ref="K20:S20"/>
-    <mergeCell ref="K21:S21"/>
-    <mergeCell ref="K22:S22"/>
-    <mergeCell ref="K23:S23"/>
-    <mergeCell ref="K17:S17"/>
-    <mergeCell ref="K18:S18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:S15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:S14"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="S10:T10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="S16:T16"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="S28:T28"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="S27:T27"/>
   </mergeCells>
-  <phoneticPr fontId="17" type="noConversion"/>
-  <conditionalFormatting sqref="T5:U5">
+  <phoneticPr fontId="18" type="noConversion"/>
+  <conditionalFormatting sqref="S7:T7">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G34:H34">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -7365,10 +7926,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:J26" xr:uid="{EBCDB7CB-9B76-4496-A9FD-E13B8548471C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I7:J28" xr:uid="{EBCDB7CB-9B76-4496-A9FD-E13B8548471C}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T5:U26" xr:uid="{1261FD57-5C4E-4608-A621-9535D2C1ADDD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S7:T28 G34:H36" xr:uid="{1261FD57-5C4E-4608-A621-9535D2C1ADDD}">
       <formula1>"Sẵn sàng, Đang Render, Chưa có"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7386,67 +7947,67 @@
   <sheetData>
     <row r="2" spans="1:16" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P10" s="26" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="P10" s="28" t="s">
+    <row r="21" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P21" s="26" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="21" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="P21" s="28" t="s">
+    <row r="22" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="P22" s="32" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="22" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="P22" s="34" t="s">
-        <v>208</v>
-      </c>
-    </row>
     <row r="24" spans="2:28" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P24" s="92" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q24" s="35"/>
-      <c r="R24" s="35"/>
-      <c r="S24" s="35"/>
-      <c r="T24" s="35"/>
-      <c r="U24" s="35"/>
-      <c r="V24" s="35"/>
-      <c r="W24" s="35"/>
-      <c r="X24" s="35"/>
-      <c r="Y24" s="35"/>
-      <c r="Z24" s="35"/>
-      <c r="AA24" s="35"/>
-      <c r="AB24" s="35"/>
+      <c r="P24" s="96" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q24" s="58"/>
+      <c r="R24" s="58"/>
+      <c r="S24" s="58"/>
+      <c r="T24" s="58"/>
+      <c r="U24" s="58"/>
+      <c r="V24" s="58"/>
+      <c r="W24" s="58"/>
+      <c r="X24" s="58"/>
+      <c r="Y24" s="58"/>
+      <c r="Z24" s="58"/>
+      <c r="AA24" s="58"/>
+      <c r="AB24" s="58"/>
     </row>
     <row r="26" spans="2:28" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P26" s="92" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q26" s="35"/>
-      <c r="R26" s="35"/>
-      <c r="S26" s="35"/>
-      <c r="T26" s="35"/>
-      <c r="U26" s="35"/>
-      <c r="V26" s="35"/>
-      <c r="W26" s="35"/>
-      <c r="X26" s="35"/>
-      <c r="Y26" s="35"/>
-      <c r="Z26" s="35"/>
-      <c r="AA26" s="35"/>
-      <c r="AB26" s="35"/>
+      <c r="P26" s="96" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q26" s="58"/>
+      <c r="R26" s="58"/>
+      <c r="S26" s="58"/>
+      <c r="T26" s="58"/>
+      <c r="U26" s="58"/>
+      <c r="V26" s="58"/>
+      <c r="W26" s="58"/>
+      <c r="X26" s="58"/>
+      <c r="Y26" s="58"/>
+      <c r="Z26" s="58"/>
+      <c r="AA26" s="58"/>
+      <c r="AB26" s="58"/>
     </row>
     <row r="27" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="30" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7454,908 +8015,926 @@
     </row>
     <row r="31" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B33" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="35" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="28" t="s">
+      <c r="A35" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="B35" s="58" t="s">
+        <v>220</v>
+      </c>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
+      <c r="L35" s="58"/>
+      <c r="M35" s="58"/>
+      <c r="N35" s="58"/>
+      <c r="O35" s="58"/>
+      <c r="P35" s="58"/>
+      <c r="Q35" s="58"/>
+      <c r="R35" s="58"/>
+      <c r="S35" s="58"/>
+      <c r="T35" s="58"/>
+      <c r="U35" s="58"/>
+      <c r="V35" s="58"/>
+      <c r="W35" s="58"/>
+      <c r="X35" s="58"/>
+      <c r="Y35" s="58"/>
+      <c r="Z35" s="58"/>
+      <c r="AA35" s="58"/>
+      <c r="AB35" s="58"/>
+    </row>
+    <row r="36" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="58" t="s">
+        <v>221</v>
+      </c>
+      <c r="C36" s="58"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="58"/>
+      <c r="I36" s="58"/>
+      <c r="J36" s="58"/>
+      <c r="K36" s="58"/>
+      <c r="L36" s="58"/>
+      <c r="M36" s="58"/>
+      <c r="N36" s="58"/>
+      <c r="O36" s="58"/>
+      <c r="P36" s="58"/>
+      <c r="Q36" s="58"/>
+      <c r="R36" s="58"/>
+      <c r="S36" s="58"/>
+      <c r="T36" s="58"/>
+      <c r="U36" s="58"/>
+      <c r="V36" s="58"/>
+      <c r="W36" s="58"/>
+      <c r="X36" s="58"/>
+      <c r="Y36" s="58"/>
+      <c r="Z36" s="58"/>
+      <c r="AA36" s="58"/>
+      <c r="AB36" s="58"/>
+    </row>
+    <row r="37" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="58" t="s">
         <v>222</v>
       </c>
-      <c r="B35" s="35" t="s">
+      <c r="C37" s="58"/>
+      <c r="D37" s="58"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="58"/>
+      <c r="H37" s="58"/>
+      <c r="I37" s="58"/>
+      <c r="J37" s="58"/>
+      <c r="K37" s="58"/>
+      <c r="L37" s="58"/>
+      <c r="M37" s="58"/>
+      <c r="N37" s="58"/>
+      <c r="O37" s="58"/>
+      <c r="P37" s="58"/>
+      <c r="Q37" s="58"/>
+      <c r="R37" s="58"/>
+      <c r="S37" s="58"/>
+      <c r="T37" s="58"/>
+      <c r="U37" s="58"/>
+      <c r="V37" s="58"/>
+      <c r="W37" s="58"/>
+      <c r="X37" s="58"/>
+      <c r="Y37" s="58"/>
+      <c r="Z37" s="58"/>
+      <c r="AA37" s="58"/>
+      <c r="AB37" s="58"/>
+    </row>
+    <row r="38" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="58" t="s">
         <v>223</v>
       </c>
-      <c r="C35" s="35"/>
-      <c r="D35" s="35"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="35"/>
-      <c r="H35" s="35"/>
-      <c r="I35" s="35"/>
-      <c r="J35" s="35"/>
-      <c r="K35" s="35"/>
-      <c r="L35" s="35"/>
-      <c r="M35" s="35"/>
-      <c r="N35" s="35"/>
-      <c r="O35" s="35"/>
-      <c r="P35" s="35"/>
-      <c r="Q35" s="35"/>
-      <c r="R35" s="35"/>
-      <c r="S35" s="35"/>
-      <c r="T35" s="35"/>
-      <c r="U35" s="35"/>
-      <c r="V35" s="35"/>
-      <c r="W35" s="35"/>
-      <c r="X35" s="35"/>
-      <c r="Y35" s="35"/>
-      <c r="Z35" s="35"/>
-      <c r="AA35" s="35"/>
-      <c r="AB35" s="35"/>
-    </row>
-    <row r="36" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="35" t="s">
+      <c r="C38" s="58"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
+      <c r="H38" s="58"/>
+      <c r="I38" s="58"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="58"/>
+      <c r="L38" s="58"/>
+      <c r="M38" s="58"/>
+      <c r="N38" s="58"/>
+      <c r="O38" s="58"/>
+      <c r="P38" s="58"/>
+      <c r="Q38" s="58"/>
+      <c r="R38" s="58"/>
+      <c r="S38" s="58"/>
+      <c r="T38" s="58"/>
+      <c r="U38" s="58"/>
+      <c r="V38" s="58"/>
+      <c r="W38" s="58"/>
+      <c r="X38" s="58"/>
+      <c r="Y38" s="58"/>
+      <c r="Z38" s="58"/>
+      <c r="AA38" s="58"/>
+      <c r="AB38" s="58"/>
+    </row>
+    <row r="39" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="58" t="s">
+        <v>209</v>
+      </c>
+      <c r="C39" s="58"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="58"/>
+      <c r="H39" s="58"/>
+      <c r="I39" s="58"/>
+      <c r="J39" s="58"/>
+      <c r="K39" s="58"/>
+      <c r="L39" s="58"/>
+      <c r="M39" s="58"/>
+      <c r="N39" s="58"/>
+      <c r="O39" s="58"/>
+      <c r="P39" s="58"/>
+      <c r="Q39" s="58"/>
+      <c r="R39" s="58"/>
+      <c r="S39" s="58"/>
+      <c r="T39" s="58"/>
+      <c r="U39" s="58"/>
+      <c r="V39" s="58"/>
+      <c r="W39" s="58"/>
+      <c r="X39" s="58"/>
+      <c r="Y39" s="58"/>
+      <c r="Z39" s="58"/>
+      <c r="AA39" s="58"/>
+      <c r="AB39" s="58"/>
+    </row>
+    <row r="40" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="C36" s="35"/>
-      <c r="D36" s="35"/>
-      <c r="E36" s="35"/>
-      <c r="F36" s="35"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="35"/>
-      <c r="J36" s="35"/>
-      <c r="K36" s="35"/>
-      <c r="L36" s="35"/>
-      <c r="M36" s="35"/>
-      <c r="N36" s="35"/>
-      <c r="O36" s="35"/>
-      <c r="P36" s="35"/>
-      <c r="Q36" s="35"/>
-      <c r="R36" s="35"/>
-      <c r="S36" s="35"/>
-      <c r="T36" s="35"/>
-      <c r="U36" s="35"/>
-      <c r="V36" s="35"/>
-      <c r="W36" s="35"/>
-      <c r="X36" s="35"/>
-      <c r="Y36" s="35"/>
-      <c r="Z36" s="35"/>
-      <c r="AA36" s="35"/>
-      <c r="AB36" s="35"/>
-    </row>
-    <row r="37" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="35" t="s">
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="58"/>
+      <c r="H40" s="58"/>
+      <c r="I40" s="58"/>
+      <c r="J40" s="58"/>
+      <c r="K40" s="58"/>
+      <c r="L40" s="58"/>
+      <c r="M40" s="58"/>
+      <c r="N40" s="58"/>
+      <c r="O40" s="58"/>
+      <c r="P40" s="58"/>
+      <c r="Q40" s="58"/>
+      <c r="R40" s="58"/>
+      <c r="S40" s="58"/>
+      <c r="T40" s="58"/>
+      <c r="U40" s="58"/>
+      <c r="V40" s="58"/>
+      <c r="W40" s="58"/>
+      <c r="X40" s="58"/>
+      <c r="Y40" s="58"/>
+      <c r="Z40" s="58"/>
+      <c r="AA40" s="58"/>
+      <c r="AB40" s="58"/>
+    </row>
+    <row r="41" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B41" s="58" t="s">
         <v>225</v>
       </c>
-      <c r="C37" s="35"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="35"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="35"/>
-      <c r="J37" s="35"/>
-      <c r="K37" s="35"/>
-      <c r="L37" s="35"/>
-      <c r="M37" s="35"/>
-      <c r="N37" s="35"/>
-      <c r="O37" s="35"/>
-      <c r="P37" s="35"/>
-      <c r="Q37" s="35"/>
-      <c r="R37" s="35"/>
-      <c r="S37" s="35"/>
-      <c r="T37" s="35"/>
-      <c r="U37" s="35"/>
-      <c r="V37" s="35"/>
-      <c r="W37" s="35"/>
-      <c r="X37" s="35"/>
-      <c r="Y37" s="35"/>
-      <c r="Z37" s="35"/>
-      <c r="AA37" s="35"/>
-      <c r="AB37" s="35"/>
-    </row>
-    <row r="38" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="35" t="s">
+      <c r="C41" s="58"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="58"/>
+      <c r="H41" s="58"/>
+      <c r="I41" s="58"/>
+      <c r="J41" s="58"/>
+      <c r="K41" s="58"/>
+      <c r="L41" s="58"/>
+      <c r="M41" s="58"/>
+      <c r="N41" s="58"/>
+      <c r="O41" s="58"/>
+      <c r="P41" s="58"/>
+      <c r="Q41" s="58"/>
+      <c r="R41" s="58"/>
+      <c r="S41" s="58"/>
+      <c r="T41" s="58"/>
+      <c r="U41" s="58"/>
+      <c r="V41" s="58"/>
+      <c r="W41" s="58"/>
+      <c r="X41" s="58"/>
+      <c r="Y41" s="58"/>
+      <c r="Z41" s="58"/>
+      <c r="AA41" s="58"/>
+      <c r="AB41" s="58"/>
+    </row>
+    <row r="42" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B42" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="35"/>
-      <c r="J38" s="35"/>
-      <c r="K38" s="35"/>
-      <c r="L38" s="35"/>
-      <c r="M38" s="35"/>
-      <c r="N38" s="35"/>
-      <c r="O38" s="35"/>
-      <c r="P38" s="35"/>
-      <c r="Q38" s="35"/>
-      <c r="R38" s="35"/>
-      <c r="S38" s="35"/>
-      <c r="T38" s="35"/>
-      <c r="U38" s="35"/>
-      <c r="V38" s="35"/>
-      <c r="W38" s="35"/>
-      <c r="X38" s="35"/>
-      <c r="Y38" s="35"/>
-      <c r="Z38" s="35"/>
-      <c r="AA38" s="35"/>
-      <c r="AB38" s="35"/>
-    </row>
-    <row r="39" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="35" t="s">
-        <v>211</v>
-      </c>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35"/>
-      <c r="G39" s="35"/>
-      <c r="H39" s="35"/>
-      <c r="I39" s="35"/>
-      <c r="J39" s="35"/>
-      <c r="K39" s="35"/>
-      <c r="L39" s="35"/>
-      <c r="M39" s="35"/>
-      <c r="N39" s="35"/>
-      <c r="O39" s="35"/>
-      <c r="P39" s="35"/>
-      <c r="Q39" s="35"/>
-      <c r="R39" s="35"/>
-      <c r="S39" s="35"/>
-      <c r="T39" s="35"/>
-      <c r="U39" s="35"/>
-      <c r="V39" s="35"/>
-      <c r="W39" s="35"/>
-      <c r="X39" s="35"/>
-      <c r="Y39" s="35"/>
-      <c r="Z39" s="35"/>
-      <c r="AA39" s="35"/>
-      <c r="AB39" s="35"/>
-    </row>
-    <row r="40" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="35" t="s">
+      <c r="C42" s="58"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="58"/>
+      <c r="H42" s="58"/>
+      <c r="I42" s="58"/>
+      <c r="J42" s="58"/>
+      <c r="K42" s="58"/>
+      <c r="L42" s="58"/>
+      <c r="M42" s="58"/>
+      <c r="N42" s="58"/>
+      <c r="O42" s="58"/>
+      <c r="P42" s="58"/>
+      <c r="Q42" s="58"/>
+      <c r="R42" s="58"/>
+      <c r="S42" s="58"/>
+      <c r="T42" s="58"/>
+      <c r="U42" s="58"/>
+      <c r="V42" s="58"/>
+      <c r="W42" s="58"/>
+      <c r="X42" s="58"/>
+      <c r="Y42" s="58"/>
+      <c r="Z42" s="58"/>
+      <c r="AA42" s="58"/>
+      <c r="AB42" s="58"/>
+    </row>
+    <row r="43" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B43" s="58" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="35"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="35"/>
-      <c r="J40" s="35"/>
-      <c r="K40" s="35"/>
-      <c r="L40" s="35"/>
-      <c r="M40" s="35"/>
-      <c r="N40" s="35"/>
-      <c r="O40" s="35"/>
-      <c r="P40" s="35"/>
-      <c r="Q40" s="35"/>
-      <c r="R40" s="35"/>
-      <c r="S40" s="35"/>
-      <c r="T40" s="35"/>
-      <c r="U40" s="35"/>
-      <c r="V40" s="35"/>
-      <c r="W40" s="35"/>
-      <c r="X40" s="35"/>
-      <c r="Y40" s="35"/>
-      <c r="Z40" s="35"/>
-      <c r="AA40" s="35"/>
-      <c r="AB40" s="35"/>
-    </row>
-    <row r="41" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B41" s="35" t="s">
+      <c r="C43" s="58"/>
+      <c r="D43" s="58"/>
+      <c r="E43" s="58"/>
+      <c r="F43" s="58"/>
+      <c r="G43" s="58"/>
+      <c r="H43" s="58"/>
+      <c r="I43" s="58"/>
+      <c r="J43" s="58"/>
+      <c r="K43" s="58"/>
+      <c r="L43" s="58"/>
+      <c r="M43" s="58"/>
+      <c r="N43" s="58"/>
+      <c r="O43" s="58"/>
+      <c r="P43" s="58"/>
+      <c r="Q43" s="58"/>
+      <c r="R43" s="58"/>
+      <c r="S43" s="58"/>
+      <c r="T43" s="58"/>
+      <c r="U43" s="58"/>
+      <c r="V43" s="58"/>
+      <c r="W43" s="58"/>
+      <c r="X43" s="58"/>
+      <c r="Y43" s="58"/>
+      <c r="Z43" s="58"/>
+      <c r="AA43" s="58"/>
+      <c r="AB43" s="58"/>
+    </row>
+    <row r="44" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B44" s="58" t="s">
         <v>228</v>
       </c>
-      <c r="C41" s="35"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="35"/>
-      <c r="H41" s="35"/>
-      <c r="I41" s="35"/>
-      <c r="J41" s="35"/>
-      <c r="K41" s="35"/>
-      <c r="L41" s="35"/>
-      <c r="M41" s="35"/>
-      <c r="N41" s="35"/>
-      <c r="O41" s="35"/>
-      <c r="P41" s="35"/>
-      <c r="Q41" s="35"/>
-      <c r="R41" s="35"/>
-      <c r="S41" s="35"/>
-      <c r="T41" s="35"/>
-      <c r="U41" s="35"/>
-      <c r="V41" s="35"/>
-      <c r="W41" s="35"/>
-      <c r="X41" s="35"/>
-      <c r="Y41" s="35"/>
-      <c r="Z41" s="35"/>
-      <c r="AA41" s="35"/>
-      <c r="AB41" s="35"/>
-    </row>
-    <row r="42" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B42" s="35" t="s">
+      <c r="C44" s="58"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="58"/>
+      <c r="H44" s="58"/>
+      <c r="I44" s="58"/>
+      <c r="J44" s="58"/>
+      <c r="K44" s="58"/>
+      <c r="L44" s="58"/>
+      <c r="M44" s="58"/>
+      <c r="N44" s="58"/>
+      <c r="O44" s="58"/>
+      <c r="P44" s="58"/>
+      <c r="Q44" s="58"/>
+      <c r="R44" s="58"/>
+      <c r="S44" s="58"/>
+      <c r="T44" s="58"/>
+      <c r="U44" s="58"/>
+      <c r="V44" s="58"/>
+      <c r="W44" s="58"/>
+      <c r="X44" s="58"/>
+      <c r="Y44" s="58"/>
+      <c r="Z44" s="58"/>
+      <c r="AA44" s="58"/>
+      <c r="AB44" s="58"/>
+    </row>
+    <row r="45" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B45" s="58" t="s">
         <v>229</v>
       </c>
-      <c r="C42" s="35"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="35"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="35"/>
-      <c r="I42" s="35"/>
-      <c r="J42" s="35"/>
-      <c r="K42" s="35"/>
-      <c r="L42" s="35"/>
-      <c r="M42" s="35"/>
-      <c r="N42" s="35"/>
-      <c r="O42" s="35"/>
-      <c r="P42" s="35"/>
-      <c r="Q42" s="35"/>
-      <c r="R42" s="35"/>
-      <c r="S42" s="35"/>
-      <c r="T42" s="35"/>
-      <c r="U42" s="35"/>
-      <c r="V42" s="35"/>
-      <c r="W42" s="35"/>
-      <c r="X42" s="35"/>
-      <c r="Y42" s="35"/>
-      <c r="Z42" s="35"/>
-      <c r="AA42" s="35"/>
-      <c r="AB42" s="35"/>
-    </row>
-    <row r="43" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B43" s="35" t="s">
+      <c r="C45" s="58"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="58"/>
+      <c r="H45" s="58"/>
+      <c r="I45" s="58"/>
+      <c r="J45" s="58"/>
+      <c r="K45" s="58"/>
+      <c r="L45" s="58"/>
+      <c r="M45" s="58"/>
+      <c r="N45" s="58"/>
+      <c r="O45" s="58"/>
+      <c r="P45" s="58"/>
+      <c r="Q45" s="58"/>
+      <c r="R45" s="58"/>
+      <c r="S45" s="58"/>
+      <c r="T45" s="58"/>
+      <c r="U45" s="58"/>
+      <c r="V45" s="58"/>
+      <c r="W45" s="58"/>
+      <c r="X45" s="58"/>
+      <c r="Y45" s="58"/>
+      <c r="Z45" s="58"/>
+      <c r="AA45" s="58"/>
+      <c r="AB45" s="58"/>
+    </row>
+    <row r="46" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B46" s="58" t="s">
         <v>230</v>
       </c>
-      <c r="C43" s="35"/>
-      <c r="D43" s="35"/>
-      <c r="E43" s="35"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="35"/>
-      <c r="H43" s="35"/>
-      <c r="I43" s="35"/>
-      <c r="J43" s="35"/>
-      <c r="K43" s="35"/>
-      <c r="L43" s="35"/>
-      <c r="M43" s="35"/>
-      <c r="N43" s="35"/>
-      <c r="O43" s="35"/>
-      <c r="P43" s="35"/>
-      <c r="Q43" s="35"/>
-      <c r="R43" s="35"/>
-      <c r="S43" s="35"/>
-      <c r="T43" s="35"/>
-      <c r="U43" s="35"/>
-      <c r="V43" s="35"/>
-      <c r="W43" s="35"/>
-      <c r="X43" s="35"/>
-      <c r="Y43" s="35"/>
-      <c r="Z43" s="35"/>
-      <c r="AA43" s="35"/>
-      <c r="AB43" s="35"/>
-    </row>
-    <row r="44" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B44" s="35" t="s">
+      <c r="C46" s="58"/>
+      <c r="D46" s="58"/>
+      <c r="E46" s="58"/>
+      <c r="F46" s="58"/>
+      <c r="G46" s="58"/>
+      <c r="H46" s="58"/>
+      <c r="I46" s="58"/>
+      <c r="J46" s="58"/>
+      <c r="K46" s="58"/>
+      <c r="L46" s="58"/>
+      <c r="M46" s="58"/>
+      <c r="N46" s="58"/>
+      <c r="O46" s="58"/>
+      <c r="P46" s="58"/>
+      <c r="Q46" s="58"/>
+      <c r="R46" s="58"/>
+      <c r="S46" s="58"/>
+      <c r="T46" s="58"/>
+      <c r="U46" s="58"/>
+      <c r="V46" s="58"/>
+      <c r="W46" s="58"/>
+      <c r="X46" s="58"/>
+      <c r="Y46" s="58"/>
+      <c r="Z46" s="58"/>
+      <c r="AA46" s="58"/>
+      <c r="AB46" s="58"/>
+    </row>
+    <row r="47" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B47" s="58" t="s">
         <v>231</v>
       </c>
-      <c r="C44" s="35"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="35"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="35"/>
-      <c r="I44" s="35"/>
-      <c r="J44" s="35"/>
-      <c r="K44" s="35"/>
-      <c r="L44" s="35"/>
-      <c r="M44" s="35"/>
-      <c r="N44" s="35"/>
-      <c r="O44" s="35"/>
-      <c r="P44" s="35"/>
-      <c r="Q44" s="35"/>
-      <c r="R44" s="35"/>
-      <c r="S44" s="35"/>
-      <c r="T44" s="35"/>
-      <c r="U44" s="35"/>
-      <c r="V44" s="35"/>
-      <c r="W44" s="35"/>
-      <c r="X44" s="35"/>
-      <c r="Y44" s="35"/>
-      <c r="Z44" s="35"/>
-      <c r="AA44" s="35"/>
-      <c r="AB44" s="35"/>
-    </row>
-    <row r="45" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B45" s="35" t="s">
+      <c r="C47" s="58"/>
+      <c r="D47" s="58"/>
+      <c r="E47" s="58"/>
+      <c r="F47" s="58"/>
+      <c r="G47" s="58"/>
+      <c r="H47" s="58"/>
+      <c r="I47" s="58"/>
+      <c r="J47" s="58"/>
+      <c r="K47" s="58"/>
+      <c r="L47" s="58"/>
+      <c r="M47" s="58"/>
+      <c r="N47" s="58"/>
+      <c r="O47" s="58"/>
+      <c r="P47" s="58"/>
+      <c r="Q47" s="58"/>
+      <c r="R47" s="58"/>
+      <c r="S47" s="58"/>
+      <c r="T47" s="58"/>
+      <c r="U47" s="58"/>
+      <c r="V47" s="58"/>
+      <c r="W47" s="58"/>
+      <c r="X47" s="58"/>
+      <c r="Y47" s="58"/>
+      <c r="Z47" s="58"/>
+      <c r="AA47" s="58"/>
+      <c r="AB47" s="58"/>
+    </row>
+    <row r="48" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B48" s="58" t="s">
         <v>232</v>
       </c>
-      <c r="C45" s="35"/>
-      <c r="D45" s="35"/>
-      <c r="E45" s="35"/>
-      <c r="F45" s="35"/>
-      <c r="G45" s="35"/>
-      <c r="H45" s="35"/>
-      <c r="I45" s="35"/>
-      <c r="J45" s="35"/>
-      <c r="K45" s="35"/>
-      <c r="L45" s="35"/>
-      <c r="M45" s="35"/>
-      <c r="N45" s="35"/>
-      <c r="O45" s="35"/>
-      <c r="P45" s="35"/>
-      <c r="Q45" s="35"/>
-      <c r="R45" s="35"/>
-      <c r="S45" s="35"/>
-      <c r="T45" s="35"/>
-      <c r="U45" s="35"/>
-      <c r="V45" s="35"/>
-      <c r="W45" s="35"/>
-      <c r="X45" s="35"/>
-      <c r="Y45" s="35"/>
-      <c r="Z45" s="35"/>
-      <c r="AA45" s="35"/>
-      <c r="AB45" s="35"/>
-    </row>
-    <row r="46" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B46" s="35" t="s">
+      <c r="C48" s="58"/>
+      <c r="D48" s="58"/>
+      <c r="E48" s="58"/>
+      <c r="F48" s="58"/>
+      <c r="G48" s="58"/>
+      <c r="H48" s="58"/>
+      <c r="I48" s="58"/>
+      <c r="J48" s="58"/>
+      <c r="K48" s="58"/>
+      <c r="L48" s="58"/>
+      <c r="M48" s="58"/>
+      <c r="N48" s="58"/>
+      <c r="O48" s="58"/>
+      <c r="P48" s="58"/>
+      <c r="Q48" s="58"/>
+      <c r="R48" s="58"/>
+      <c r="S48" s="58"/>
+      <c r="T48" s="58"/>
+      <c r="U48" s="58"/>
+      <c r="V48" s="58"/>
+      <c r="W48" s="58"/>
+      <c r="X48" s="58"/>
+      <c r="Y48" s="58"/>
+      <c r="Z48" s="58"/>
+      <c r="AA48" s="58"/>
+      <c r="AB48" s="58"/>
+    </row>
+    <row r="49" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B49" s="58" t="s">
         <v>233</v>
       </c>
-      <c r="C46" s="35"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="35"/>
-      <c r="J46" s="35"/>
-      <c r="K46" s="35"/>
-      <c r="L46" s="35"/>
-      <c r="M46" s="35"/>
-      <c r="N46" s="35"/>
-      <c r="O46" s="35"/>
-      <c r="P46" s="35"/>
-      <c r="Q46" s="35"/>
-      <c r="R46" s="35"/>
-      <c r="S46" s="35"/>
-      <c r="T46" s="35"/>
-      <c r="U46" s="35"/>
-      <c r="V46" s="35"/>
-      <c r="W46" s="35"/>
-      <c r="X46" s="35"/>
-      <c r="Y46" s="35"/>
-      <c r="Z46" s="35"/>
-      <c r="AA46" s="35"/>
-      <c r="AB46" s="35"/>
-    </row>
-    <row r="47" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B47" s="35" t="s">
+      <c r="C49" s="58"/>
+      <c r="D49" s="58"/>
+      <c r="E49" s="58"/>
+      <c r="F49" s="58"/>
+      <c r="G49" s="58"/>
+      <c r="H49" s="58"/>
+      <c r="I49" s="58"/>
+      <c r="J49" s="58"/>
+      <c r="K49" s="58"/>
+      <c r="L49" s="58"/>
+      <c r="M49" s="58"/>
+      <c r="N49" s="58"/>
+      <c r="O49" s="58"/>
+      <c r="P49" s="58"/>
+      <c r="Q49" s="58"/>
+      <c r="R49" s="58"/>
+      <c r="S49" s="58"/>
+      <c r="T49" s="58"/>
+      <c r="U49" s="58"/>
+      <c r="V49" s="58"/>
+      <c r="W49" s="58"/>
+      <c r="X49" s="58"/>
+      <c r="Y49" s="58"/>
+      <c r="Z49" s="58"/>
+      <c r="AA49" s="58"/>
+      <c r="AB49" s="58"/>
+    </row>
+    <row r="50" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B50" s="58" t="s">
         <v>234</v>
       </c>
-      <c r="C47" s="35"/>
-      <c r="D47" s="35"/>
-      <c r="E47" s="35"/>
-      <c r="F47" s="35"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="35"/>
-      <c r="I47" s="35"/>
-      <c r="J47" s="35"/>
-      <c r="K47" s="35"/>
-      <c r="L47" s="35"/>
-      <c r="M47" s="35"/>
-      <c r="N47" s="35"/>
-      <c r="O47" s="35"/>
-      <c r="P47" s="35"/>
-      <c r="Q47" s="35"/>
-      <c r="R47" s="35"/>
-      <c r="S47" s="35"/>
-      <c r="T47" s="35"/>
-      <c r="U47" s="35"/>
-      <c r="V47" s="35"/>
-      <c r="W47" s="35"/>
-      <c r="X47" s="35"/>
-      <c r="Y47" s="35"/>
-      <c r="Z47" s="35"/>
-      <c r="AA47" s="35"/>
-      <c r="AB47" s="35"/>
-    </row>
-    <row r="48" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B48" s="35" t="s">
+      <c r="C50" s="58"/>
+      <c r="D50" s="58"/>
+      <c r="E50" s="58"/>
+      <c r="F50" s="58"/>
+      <c r="G50" s="58"/>
+      <c r="H50" s="58"/>
+      <c r="I50" s="58"/>
+      <c r="J50" s="58"/>
+      <c r="K50" s="58"/>
+      <c r="L50" s="58"/>
+      <c r="M50" s="58"/>
+      <c r="N50" s="58"/>
+      <c r="O50" s="58"/>
+      <c r="P50" s="58"/>
+      <c r="Q50" s="58"/>
+      <c r="R50" s="58"/>
+      <c r="S50" s="58"/>
+      <c r="T50" s="58"/>
+      <c r="U50" s="58"/>
+      <c r="V50" s="58"/>
+      <c r="W50" s="58"/>
+      <c r="X50" s="58"/>
+      <c r="Y50" s="58"/>
+      <c r="Z50" s="58"/>
+      <c r="AA50" s="58"/>
+      <c r="AB50" s="58"/>
+    </row>
+    <row r="51" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B51" s="58" t="s">
         <v>235</v>
       </c>
-      <c r="C48" s="35"/>
-      <c r="D48" s="35"/>
-      <c r="E48" s="35"/>
-      <c r="F48" s="35"/>
-      <c r="G48" s="35"/>
-      <c r="H48" s="35"/>
-      <c r="I48" s="35"/>
-      <c r="J48" s="35"/>
-      <c r="K48" s="35"/>
-      <c r="L48" s="35"/>
-      <c r="M48" s="35"/>
-      <c r="N48" s="35"/>
-      <c r="O48" s="35"/>
-      <c r="P48" s="35"/>
-      <c r="Q48" s="35"/>
-      <c r="R48" s="35"/>
-      <c r="S48" s="35"/>
-      <c r="T48" s="35"/>
-      <c r="U48" s="35"/>
-      <c r="V48" s="35"/>
-      <c r="W48" s="35"/>
-      <c r="X48" s="35"/>
-      <c r="Y48" s="35"/>
-      <c r="Z48" s="35"/>
-      <c r="AA48" s="35"/>
-      <c r="AB48" s="35"/>
-    </row>
-    <row r="49" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B49" s="35" t="s">
+      <c r="C51" s="58"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="58"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="58"/>
+      <c r="H51" s="58"/>
+      <c r="I51" s="58"/>
+      <c r="J51" s="58"/>
+      <c r="K51" s="58"/>
+      <c r="L51" s="58"/>
+      <c r="M51" s="58"/>
+      <c r="N51" s="58"/>
+      <c r="O51" s="58"/>
+      <c r="P51" s="58"/>
+      <c r="Q51" s="58"/>
+      <c r="R51" s="58"/>
+      <c r="S51" s="58"/>
+      <c r="T51" s="58"/>
+      <c r="U51" s="58"/>
+      <c r="V51" s="58"/>
+      <c r="W51" s="58"/>
+      <c r="X51" s="58"/>
+      <c r="Y51" s="58"/>
+      <c r="Z51" s="58"/>
+      <c r="AA51" s="58"/>
+      <c r="AB51" s="58"/>
+    </row>
+    <row r="52" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B52" s="58" t="s">
         <v>236</v>
       </c>
-      <c r="C49" s="35"/>
-      <c r="D49" s="35"/>
-      <c r="E49" s="35"/>
-      <c r="F49" s="35"/>
-      <c r="G49" s="35"/>
-      <c r="H49" s="35"/>
-      <c r="I49" s="35"/>
-      <c r="J49" s="35"/>
-      <c r="K49" s="35"/>
-      <c r="L49" s="35"/>
-      <c r="M49" s="35"/>
-      <c r="N49" s="35"/>
-      <c r="O49" s="35"/>
-      <c r="P49" s="35"/>
-      <c r="Q49" s="35"/>
-      <c r="R49" s="35"/>
-      <c r="S49" s="35"/>
-      <c r="T49" s="35"/>
-      <c r="U49" s="35"/>
-      <c r="V49" s="35"/>
-      <c r="W49" s="35"/>
-      <c r="X49" s="35"/>
-      <c r="Y49" s="35"/>
-      <c r="Z49" s="35"/>
-      <c r="AA49" s="35"/>
-      <c r="AB49" s="35"/>
-    </row>
-    <row r="50" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B50" s="35" t="s">
-        <v>237</v>
-      </c>
-      <c r="C50" s="35"/>
-      <c r="D50" s="35"/>
-      <c r="E50" s="35"/>
-      <c r="F50" s="35"/>
-      <c r="G50" s="35"/>
-      <c r="H50" s="35"/>
-      <c r="I50" s="35"/>
-      <c r="J50" s="35"/>
-      <c r="K50" s="35"/>
-      <c r="L50" s="35"/>
-      <c r="M50" s="35"/>
-      <c r="N50" s="35"/>
-      <c r="O50" s="35"/>
-      <c r="P50" s="35"/>
-      <c r="Q50" s="35"/>
-      <c r="R50" s="35"/>
-      <c r="S50" s="35"/>
-      <c r="T50" s="35"/>
-      <c r="U50" s="35"/>
-      <c r="V50" s="35"/>
-      <c r="W50" s="35"/>
-      <c r="X50" s="35"/>
-      <c r="Y50" s="35"/>
-      <c r="Z50" s="35"/>
-      <c r="AA50" s="35"/>
-      <c r="AB50" s="35"/>
-    </row>
-    <row r="51" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B51" s="35" t="s">
-        <v>238</v>
-      </c>
-      <c r="C51" s="35"/>
-      <c r="D51" s="35"/>
-      <c r="E51" s="35"/>
-      <c r="F51" s="35"/>
-      <c r="G51" s="35"/>
-      <c r="H51" s="35"/>
-      <c r="I51" s="35"/>
-      <c r="J51" s="35"/>
-      <c r="K51" s="35"/>
-      <c r="L51" s="35"/>
-      <c r="M51" s="35"/>
-      <c r="N51" s="35"/>
-      <c r="O51" s="35"/>
-      <c r="P51" s="35"/>
-      <c r="Q51" s="35"/>
-      <c r="R51" s="35"/>
-      <c r="S51" s="35"/>
-      <c r="T51" s="35"/>
-      <c r="U51" s="35"/>
-      <c r="V51" s="35"/>
-      <c r="W51" s="35"/>
-      <c r="X51" s="35"/>
-      <c r="Y51" s="35"/>
-      <c r="Z51" s="35"/>
-      <c r="AA51" s="35"/>
-      <c r="AB51" s="35"/>
-    </row>
-    <row r="52" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B52" s="35" t="s">
-        <v>239</v>
-      </c>
-      <c r="C52" s="35"/>
-      <c r="D52" s="35"/>
-      <c r="E52" s="35"/>
-      <c r="F52" s="35"/>
-      <c r="G52" s="35"/>
-      <c r="H52" s="35"/>
-      <c r="I52" s="35"/>
-      <c r="J52" s="35"/>
-      <c r="K52" s="35"/>
-      <c r="L52" s="35"/>
-      <c r="M52" s="35"/>
-      <c r="N52" s="35"/>
-      <c r="O52" s="35"/>
-      <c r="P52" s="35"/>
-      <c r="Q52" s="35"/>
-      <c r="R52" s="35"/>
-      <c r="S52" s="35"/>
-      <c r="T52" s="35"/>
-      <c r="U52" s="35"/>
-      <c r="V52" s="35"/>
-      <c r="W52" s="35"/>
-      <c r="X52" s="35"/>
-      <c r="Y52" s="35"/>
-      <c r="Z52" s="35"/>
-      <c r="AA52" s="35"/>
-      <c r="AB52" s="35"/>
+      <c r="C52" s="58"/>
+      <c r="D52" s="58"/>
+      <c r="E52" s="58"/>
+      <c r="F52" s="58"/>
+      <c r="G52" s="58"/>
+      <c r="H52" s="58"/>
+      <c r="I52" s="58"/>
+      <c r="J52" s="58"/>
+      <c r="K52" s="58"/>
+      <c r="L52" s="58"/>
+      <c r="M52" s="58"/>
+      <c r="N52" s="58"/>
+      <c r="O52" s="58"/>
+      <c r="P52" s="58"/>
+      <c r="Q52" s="58"/>
+      <c r="R52" s="58"/>
+      <c r="S52" s="58"/>
+      <c r="T52" s="58"/>
+      <c r="U52" s="58"/>
+      <c r="V52" s="58"/>
+      <c r="W52" s="58"/>
+      <c r="X52" s="58"/>
+      <c r="Y52" s="58"/>
+      <c r="Z52" s="58"/>
+      <c r="AA52" s="58"/>
+      <c r="AB52" s="58"/>
     </row>
     <row r="54" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B54" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="55" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B55" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="56" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B56" s="8"/>
     </row>
     <row r="57" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A57" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="B57" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="C57" s="35"/>
-      <c r="D57" s="35"/>
-      <c r="E57" s="35"/>
-      <c r="F57" s="35"/>
-      <c r="G57" s="35"/>
-      <c r="H57" s="35"/>
-      <c r="I57" s="35"/>
-      <c r="J57" s="35"/>
-      <c r="K57" s="35"/>
-      <c r="L57" s="35"/>
-      <c r="M57" s="35"/>
-      <c r="N57" s="35"/>
-      <c r="O57" s="35"/>
-      <c r="P57" s="35"/>
-      <c r="Q57" s="35"/>
-      <c r="R57" s="35"/>
-      <c r="S57" s="35"/>
-      <c r="T57" s="35"/>
-      <c r="U57" s="35"/>
-      <c r="V57" s="35"/>
-      <c r="W57" s="35"/>
-      <c r="X57" s="35"/>
-      <c r="Y57" s="35"/>
-      <c r="Z57" s="35"/>
-      <c r="AA57" s="35"/>
-      <c r="AB57" s="35"/>
+      <c r="A57" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="B57" s="58" t="s">
+        <v>237</v>
+      </c>
+      <c r="C57" s="58"/>
+      <c r="D57" s="58"/>
+      <c r="E57" s="58"/>
+      <c r="F57" s="58"/>
+      <c r="G57" s="58"/>
+      <c r="H57" s="58"/>
+      <c r="I57" s="58"/>
+      <c r="J57" s="58"/>
+      <c r="K57" s="58"/>
+      <c r="L57" s="58"/>
+      <c r="M57" s="58"/>
+      <c r="N57" s="58"/>
+      <c r="O57" s="58"/>
+      <c r="P57" s="58"/>
+      <c r="Q57" s="58"/>
+      <c r="R57" s="58"/>
+      <c r="S57" s="58"/>
+      <c r="T57" s="58"/>
+      <c r="U57" s="58"/>
+      <c r="V57" s="58"/>
+      <c r="W57" s="58"/>
+      <c r="X57" s="58"/>
+      <c r="Y57" s="58"/>
+      <c r="Z57" s="58"/>
+      <c r="AA57" s="58"/>
+      <c r="AB57" s="58"/>
     </row>
     <row r="58" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B58" s="35" t="s">
+      <c r="B58" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="C58" s="58"/>
+      <c r="D58" s="58"/>
+      <c r="E58" s="58"/>
+      <c r="F58" s="58"/>
+      <c r="G58" s="58"/>
+      <c r="H58" s="58"/>
+      <c r="I58" s="58"/>
+      <c r="J58" s="58"/>
+      <c r="K58" s="58"/>
+      <c r="L58" s="58"/>
+      <c r="M58" s="58"/>
+      <c r="N58" s="58"/>
+      <c r="O58" s="58"/>
+      <c r="P58" s="58"/>
+      <c r="Q58" s="58"/>
+      <c r="R58" s="58"/>
+      <c r="S58" s="58"/>
+      <c r="T58" s="58"/>
+      <c r="U58" s="58"/>
+      <c r="V58" s="58"/>
+      <c r="W58" s="58"/>
+      <c r="X58" s="58"/>
+      <c r="Y58" s="58"/>
+      <c r="Z58" s="58"/>
+      <c r="AA58" s="58"/>
+      <c r="AB58" s="58"/>
+    </row>
+    <row r="59" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B59" s="58" t="s">
+        <v>227</v>
+      </c>
+      <c r="C59" s="58"/>
+      <c r="D59" s="58"/>
+      <c r="E59" s="58"/>
+      <c r="F59" s="58"/>
+      <c r="G59" s="58"/>
+      <c r="H59" s="58"/>
+      <c r="I59" s="58"/>
+      <c r="J59" s="58"/>
+      <c r="K59" s="58"/>
+      <c r="L59" s="58"/>
+      <c r="M59" s="58"/>
+      <c r="N59" s="58"/>
+      <c r="O59" s="58"/>
+      <c r="P59" s="58"/>
+      <c r="Q59" s="58"/>
+      <c r="R59" s="58"/>
+      <c r="S59" s="58"/>
+      <c r="T59" s="58"/>
+      <c r="U59" s="58"/>
+      <c r="V59" s="58"/>
+      <c r="W59" s="58"/>
+      <c r="X59" s="58"/>
+      <c r="Y59" s="58"/>
+      <c r="Z59" s="58"/>
+      <c r="AA59" s="58"/>
+      <c r="AB59" s="58"/>
+    </row>
+    <row r="60" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B60" s="58" t="s">
+        <v>228</v>
+      </c>
+      <c r="C60" s="58"/>
+      <c r="D60" s="58"/>
+      <c r="E60" s="58"/>
+      <c r="F60" s="58"/>
+      <c r="G60" s="58"/>
+      <c r="H60" s="58"/>
+      <c r="I60" s="58"/>
+      <c r="J60" s="58"/>
+      <c r="K60" s="58"/>
+      <c r="L60" s="58"/>
+      <c r="M60" s="58"/>
+      <c r="N60" s="58"/>
+      <c r="O60" s="58"/>
+      <c r="P60" s="58"/>
+      <c r="Q60" s="58"/>
+      <c r="R60" s="58"/>
+      <c r="S60" s="58"/>
+      <c r="T60" s="58"/>
+      <c r="U60" s="58"/>
+      <c r="V60" s="58"/>
+      <c r="W60" s="58"/>
+      <c r="X60" s="58"/>
+      <c r="Y60" s="58"/>
+      <c r="Z60" s="58"/>
+      <c r="AA60" s="58"/>
+      <c r="AB60" s="58"/>
+    </row>
+    <row r="61" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B61" s="58" t="s">
         <v>229</v>
       </c>
-      <c r="C58" s="35"/>
-      <c r="D58" s="35"/>
-      <c r="E58" s="35"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="35"/>
-      <c r="H58" s="35"/>
-      <c r="I58" s="35"/>
-      <c r="J58" s="35"/>
-      <c r="K58" s="35"/>
-      <c r="L58" s="35"/>
-      <c r="M58" s="35"/>
-      <c r="N58" s="35"/>
-      <c r="O58" s="35"/>
-      <c r="P58" s="35"/>
-      <c r="Q58" s="35"/>
-      <c r="R58" s="35"/>
-      <c r="S58" s="35"/>
-      <c r="T58" s="35"/>
-      <c r="U58" s="35"/>
-      <c r="V58" s="35"/>
-      <c r="W58" s="35"/>
-      <c r="X58" s="35"/>
-      <c r="Y58" s="35"/>
-      <c r="Z58" s="35"/>
-      <c r="AA58" s="35"/>
-      <c r="AB58" s="35"/>
-    </row>
-    <row r="59" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B59" s="35" t="s">
+      <c r="C61" s="58"/>
+      <c r="D61" s="58"/>
+      <c r="E61" s="58"/>
+      <c r="F61" s="58"/>
+      <c r="G61" s="58"/>
+      <c r="H61" s="58"/>
+      <c r="I61" s="58"/>
+      <c r="J61" s="58"/>
+      <c r="K61" s="58"/>
+      <c r="L61" s="58"/>
+      <c r="M61" s="58"/>
+      <c r="N61" s="58"/>
+      <c r="O61" s="58"/>
+      <c r="P61" s="58"/>
+      <c r="Q61" s="58"/>
+      <c r="R61" s="58"/>
+      <c r="S61" s="58"/>
+      <c r="T61" s="58"/>
+      <c r="U61" s="58"/>
+      <c r="V61" s="58"/>
+      <c r="W61" s="58"/>
+      <c r="X61" s="58"/>
+      <c r="Y61" s="58"/>
+      <c r="Z61" s="58"/>
+      <c r="AA61" s="58"/>
+      <c r="AB61" s="58"/>
+    </row>
+    <row r="62" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B62" s="58" t="s">
         <v>230</v>
       </c>
-      <c r="C59" s="35"/>
-      <c r="D59" s="35"/>
-      <c r="E59" s="35"/>
-      <c r="F59" s="35"/>
-      <c r="G59" s="35"/>
-      <c r="H59" s="35"/>
-      <c r="I59" s="35"/>
-      <c r="J59" s="35"/>
-      <c r="K59" s="35"/>
-      <c r="L59" s="35"/>
-      <c r="M59" s="35"/>
-      <c r="N59" s="35"/>
-      <c r="O59" s="35"/>
-      <c r="P59" s="35"/>
-      <c r="Q59" s="35"/>
-      <c r="R59" s="35"/>
-      <c r="S59" s="35"/>
-      <c r="T59" s="35"/>
-      <c r="U59" s="35"/>
-      <c r="V59" s="35"/>
-      <c r="W59" s="35"/>
-      <c r="X59" s="35"/>
-      <c r="Y59" s="35"/>
-      <c r="Z59" s="35"/>
-      <c r="AA59" s="35"/>
-      <c r="AB59" s="35"/>
-    </row>
-    <row r="60" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B60" s="35" t="s">
+      <c r="C62" s="58"/>
+      <c r="D62" s="58"/>
+      <c r="E62" s="58"/>
+      <c r="F62" s="58"/>
+      <c r="G62" s="58"/>
+      <c r="H62" s="58"/>
+      <c r="I62" s="58"/>
+      <c r="J62" s="58"/>
+      <c r="K62" s="58"/>
+      <c r="L62" s="58"/>
+      <c r="M62" s="58"/>
+      <c r="N62" s="58"/>
+      <c r="O62" s="58"/>
+      <c r="P62" s="58"/>
+      <c r="Q62" s="58"/>
+      <c r="R62" s="58"/>
+      <c r="S62" s="58"/>
+      <c r="T62" s="58"/>
+      <c r="U62" s="58"/>
+      <c r="V62" s="58"/>
+      <c r="W62" s="58"/>
+      <c r="X62" s="58"/>
+      <c r="Y62" s="58"/>
+      <c r="Z62" s="58"/>
+      <c r="AA62" s="58"/>
+      <c r="AB62" s="58"/>
+    </row>
+    <row r="63" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B63" s="58" t="s">
         <v>231</v>
       </c>
-      <c r="C60" s="35"/>
-      <c r="D60" s="35"/>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="35"/>
-      <c r="H60" s="35"/>
-      <c r="I60" s="35"/>
-      <c r="J60" s="35"/>
-      <c r="K60" s="35"/>
-      <c r="L60" s="35"/>
-      <c r="M60" s="35"/>
-      <c r="N60" s="35"/>
-      <c r="O60" s="35"/>
-      <c r="P60" s="35"/>
-      <c r="Q60" s="35"/>
-      <c r="R60" s="35"/>
-      <c r="S60" s="35"/>
-      <c r="T60" s="35"/>
-      <c r="U60" s="35"/>
-      <c r="V60" s="35"/>
-      <c r="W60" s="35"/>
-      <c r="X60" s="35"/>
-      <c r="Y60" s="35"/>
-      <c r="Z60" s="35"/>
-      <c r="AA60" s="35"/>
-      <c r="AB60" s="35"/>
-    </row>
-    <row r="61" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B61" s="35" t="s">
+      <c r="C63" s="58"/>
+      <c r="D63" s="58"/>
+      <c r="E63" s="58"/>
+      <c r="F63" s="58"/>
+      <c r="G63" s="58"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="58"/>
+      <c r="K63" s="58"/>
+      <c r="L63" s="58"/>
+      <c r="M63" s="58"/>
+      <c r="N63" s="58"/>
+      <c r="O63" s="58"/>
+      <c r="P63" s="58"/>
+      <c r="Q63" s="58"/>
+      <c r="R63" s="58"/>
+      <c r="S63" s="58"/>
+      <c r="T63" s="58"/>
+      <c r="U63" s="58"/>
+      <c r="V63" s="58"/>
+      <c r="W63" s="58"/>
+      <c r="X63" s="58"/>
+      <c r="Y63" s="58"/>
+      <c r="Z63" s="58"/>
+      <c r="AA63" s="58"/>
+      <c r="AB63" s="58"/>
+    </row>
+    <row r="64" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B64" s="58" t="s">
         <v>232</v>
       </c>
-      <c r="C61" s="35"/>
-      <c r="D61" s="35"/>
-      <c r="E61" s="35"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
-      <c r="H61" s="35"/>
-      <c r="I61" s="35"/>
-      <c r="J61" s="35"/>
-      <c r="K61" s="35"/>
-      <c r="L61" s="35"/>
-      <c r="M61" s="35"/>
-      <c r="N61" s="35"/>
-      <c r="O61" s="35"/>
-      <c r="P61" s="35"/>
-      <c r="Q61" s="35"/>
-      <c r="R61" s="35"/>
-      <c r="S61" s="35"/>
-      <c r="T61" s="35"/>
-      <c r="U61" s="35"/>
-      <c r="V61" s="35"/>
-      <c r="W61" s="35"/>
-      <c r="X61" s="35"/>
-      <c r="Y61" s="35"/>
-      <c r="Z61" s="35"/>
-      <c r="AA61" s="35"/>
-      <c r="AB61" s="35"/>
-    </row>
-    <row r="62" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B62" s="35" t="s">
+      <c r="C64" s="58"/>
+      <c r="D64" s="58"/>
+      <c r="E64" s="58"/>
+      <c r="F64" s="58"/>
+      <c r="G64" s="58"/>
+      <c r="H64" s="58"/>
+      <c r="I64" s="58"/>
+      <c r="J64" s="58"/>
+      <c r="K64" s="58"/>
+      <c r="L64" s="58"/>
+      <c r="M64" s="58"/>
+      <c r="N64" s="58"/>
+      <c r="O64" s="58"/>
+      <c r="P64" s="58"/>
+      <c r="Q64" s="58"/>
+      <c r="R64" s="58"/>
+      <c r="S64" s="58"/>
+      <c r="T64" s="58"/>
+      <c r="U64" s="58"/>
+      <c r="V64" s="58"/>
+      <c r="W64" s="58"/>
+      <c r="X64" s="58"/>
+      <c r="Y64" s="58"/>
+      <c r="Z64" s="58"/>
+      <c r="AA64" s="58"/>
+      <c r="AB64" s="58"/>
+    </row>
+    <row r="65" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B65" s="58" t="s">
         <v>233</v>
       </c>
-      <c r="C62" s="35"/>
-      <c r="D62" s="35"/>
-      <c r="E62" s="35"/>
-      <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="35"/>
-      <c r="I62" s="35"/>
-      <c r="J62" s="35"/>
-      <c r="K62" s="35"/>
-      <c r="L62" s="35"/>
-      <c r="M62" s="35"/>
-      <c r="N62" s="35"/>
-      <c r="O62" s="35"/>
-      <c r="P62" s="35"/>
-      <c r="Q62" s="35"/>
-      <c r="R62" s="35"/>
-      <c r="S62" s="35"/>
-      <c r="T62" s="35"/>
-      <c r="U62" s="35"/>
-      <c r="V62" s="35"/>
-      <c r="W62" s="35"/>
-      <c r="X62" s="35"/>
-      <c r="Y62" s="35"/>
-      <c r="Z62" s="35"/>
-      <c r="AA62" s="35"/>
-      <c r="AB62" s="35"/>
-    </row>
-    <row r="63" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B63" s="35" t="s">
+      <c r="C65" s="58"/>
+      <c r="D65" s="58"/>
+      <c r="E65" s="58"/>
+      <c r="F65" s="58"/>
+      <c r="G65" s="58"/>
+      <c r="H65" s="58"/>
+      <c r="I65" s="58"/>
+      <c r="J65" s="58"/>
+      <c r="K65" s="58"/>
+      <c r="L65" s="58"/>
+      <c r="M65" s="58"/>
+      <c r="N65" s="58"/>
+      <c r="O65" s="58"/>
+      <c r="P65" s="58"/>
+      <c r="Q65" s="58"/>
+      <c r="R65" s="58"/>
+      <c r="S65" s="58"/>
+      <c r="T65" s="58"/>
+      <c r="U65" s="58"/>
+      <c r="V65" s="58"/>
+      <c r="W65" s="58"/>
+      <c r="X65" s="58"/>
+      <c r="Y65" s="58"/>
+      <c r="Z65" s="58"/>
+      <c r="AA65" s="58"/>
+      <c r="AB65" s="58"/>
+    </row>
+    <row r="66" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B66" s="58" t="s">
         <v>234</v>
       </c>
-      <c r="C63" s="35"/>
-      <c r="D63" s="35"/>
-      <c r="E63" s="35"/>
-      <c r="F63" s="35"/>
-      <c r="G63" s="35"/>
-      <c r="H63" s="35"/>
-      <c r="I63" s="35"/>
-      <c r="J63" s="35"/>
-      <c r="K63" s="35"/>
-      <c r="L63" s="35"/>
-      <c r="M63" s="35"/>
-      <c r="N63" s="35"/>
-      <c r="O63" s="35"/>
-      <c r="P63" s="35"/>
-      <c r="Q63" s="35"/>
-      <c r="R63" s="35"/>
-      <c r="S63" s="35"/>
-      <c r="T63" s="35"/>
-      <c r="U63" s="35"/>
-      <c r="V63" s="35"/>
-      <c r="W63" s="35"/>
-      <c r="X63" s="35"/>
-      <c r="Y63" s="35"/>
-      <c r="Z63" s="35"/>
-      <c r="AA63" s="35"/>
-      <c r="AB63" s="35"/>
-    </row>
-    <row r="64" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B64" s="35" t="s">
-        <v>235</v>
-      </c>
-      <c r="C64" s="35"/>
-      <c r="D64" s="35"/>
-      <c r="E64" s="35"/>
-      <c r="F64" s="35"/>
-      <c r="G64" s="35"/>
-      <c r="H64" s="35"/>
-      <c r="I64" s="35"/>
-      <c r="J64" s="35"/>
-      <c r="K64" s="35"/>
-      <c r="L64" s="35"/>
-      <c r="M64" s="35"/>
-      <c r="N64" s="35"/>
-      <c r="O64" s="35"/>
-      <c r="P64" s="35"/>
-      <c r="Q64" s="35"/>
-      <c r="R64" s="35"/>
-      <c r="S64" s="35"/>
-      <c r="T64" s="35"/>
-      <c r="U64" s="35"/>
-      <c r="V64" s="35"/>
-      <c r="W64" s="35"/>
-      <c r="X64" s="35"/>
-      <c r="Y64" s="35"/>
-      <c r="Z64" s="35"/>
-      <c r="AA64" s="35"/>
-      <c r="AB64" s="35"/>
-    </row>
-    <row r="65" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B65" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="C65" s="35"/>
-      <c r="D65" s="35"/>
-      <c r="E65" s="35"/>
-      <c r="F65" s="35"/>
-      <c r="G65" s="35"/>
-      <c r="H65" s="35"/>
-      <c r="I65" s="35"/>
-      <c r="J65" s="35"/>
-      <c r="K65" s="35"/>
-      <c r="L65" s="35"/>
-      <c r="M65" s="35"/>
-      <c r="N65" s="35"/>
-      <c r="O65" s="35"/>
-      <c r="P65" s="35"/>
-      <c r="Q65" s="35"/>
-      <c r="R65" s="35"/>
-      <c r="S65" s="35"/>
-      <c r="T65" s="35"/>
-      <c r="U65" s="35"/>
-      <c r="V65" s="35"/>
-      <c r="W65" s="35"/>
-      <c r="X65" s="35"/>
-      <c r="Y65" s="35"/>
-      <c r="Z65" s="35"/>
-      <c r="AA65" s="35"/>
-      <c r="AB65" s="35"/>
-    </row>
-    <row r="66" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B66" s="35" t="s">
-        <v>237</v>
-      </c>
-      <c r="C66" s="35"/>
-      <c r="D66" s="35"/>
-      <c r="E66" s="35"/>
-      <c r="F66" s="35"/>
-      <c r="G66" s="35"/>
-      <c r="H66" s="35"/>
-      <c r="I66" s="35"/>
-      <c r="J66" s="35"/>
-      <c r="K66" s="35"/>
-      <c r="L66" s="35"/>
-      <c r="M66" s="35"/>
-      <c r="N66" s="35"/>
-      <c r="O66" s="35"/>
-      <c r="P66" s="35"/>
-      <c r="Q66" s="35"/>
-      <c r="R66" s="35"/>
-      <c r="S66" s="35"/>
-      <c r="T66" s="35"/>
-      <c r="U66" s="35"/>
-      <c r="V66" s="35"/>
-      <c r="W66" s="35"/>
-      <c r="X66" s="35"/>
-      <c r="Y66" s="35"/>
-      <c r="Z66" s="35"/>
-      <c r="AA66" s="35"/>
-      <c r="AB66" s="35"/>
+      <c r="C66" s="58"/>
+      <c r="D66" s="58"/>
+      <c r="E66" s="58"/>
+      <c r="F66" s="58"/>
+      <c r="G66" s="58"/>
+      <c r="H66" s="58"/>
+      <c r="I66" s="58"/>
+      <c r="J66" s="58"/>
+      <c r="K66" s="58"/>
+      <c r="L66" s="58"/>
+      <c r="M66" s="58"/>
+      <c r="N66" s="58"/>
+      <c r="O66" s="58"/>
+      <c r="P66" s="58"/>
+      <c r="Q66" s="58"/>
+      <c r="R66" s="58"/>
+      <c r="S66" s="58"/>
+      <c r="T66" s="58"/>
+      <c r="U66" s="58"/>
+      <c r="V66" s="58"/>
+      <c r="W66" s="58"/>
+      <c r="X66" s="58"/>
+      <c r="Y66" s="58"/>
+      <c r="Z66" s="58"/>
+      <c r="AA66" s="58"/>
+      <c r="AB66" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="B38:AB38"/>
+    <mergeCell ref="P24:AB24"/>
+    <mergeCell ref="P26:AB26"/>
+    <mergeCell ref="B35:AB35"/>
+    <mergeCell ref="B36:AB36"/>
+    <mergeCell ref="B37:AB37"/>
+    <mergeCell ref="B50:AB50"/>
+    <mergeCell ref="B39:AB39"/>
+    <mergeCell ref="B40:AB40"/>
+    <mergeCell ref="B41:AB41"/>
+    <mergeCell ref="B42:AB42"/>
+    <mergeCell ref="B43:AB43"/>
+    <mergeCell ref="B44:AB44"/>
+    <mergeCell ref="B45:AB45"/>
+    <mergeCell ref="B46:AB46"/>
+    <mergeCell ref="B47:AB47"/>
+    <mergeCell ref="B48:AB48"/>
+    <mergeCell ref="B49:AB49"/>
     <mergeCell ref="B66:AB66"/>
     <mergeCell ref="B51:AB51"/>
     <mergeCell ref="B52:AB52"/>
@@ -8368,26 +8947,499 @@
     <mergeCell ref="B63:AB63"/>
     <mergeCell ref="B64:AB64"/>
     <mergeCell ref="B65:AB65"/>
-    <mergeCell ref="B50:AB50"/>
-    <mergeCell ref="B39:AB39"/>
-    <mergeCell ref="B40:AB40"/>
-    <mergeCell ref="B41:AB41"/>
-    <mergeCell ref="B42:AB42"/>
-    <mergeCell ref="B43:AB43"/>
-    <mergeCell ref="B44:AB44"/>
-    <mergeCell ref="B45:AB45"/>
-    <mergeCell ref="B46:AB46"/>
-    <mergeCell ref="B47:AB47"/>
-    <mergeCell ref="B48:AB48"/>
-    <mergeCell ref="B49:AB49"/>
-    <mergeCell ref="B38:AB38"/>
-    <mergeCell ref="P24:AB24"/>
-    <mergeCell ref="P26:AB26"/>
-    <mergeCell ref="B35:AB35"/>
-    <mergeCell ref="B36:AB36"/>
-    <mergeCell ref="B37:AB37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{081FC855-AA6A-4393-A6AD-5E989EEC8033}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+  </sheetPr>
+  <dimension ref="A2:AC27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="10.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:29" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="48" t="s">
+        <v>244</v>
+      </c>
+      <c r="C4" s="48"/>
+      <c r="D4" s="78" t="s">
+        <v>245</v>
+      </c>
+      <c r="E4" s="79"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="48" t="s">
+        <v>272</v>
+      </c>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="78" t="s">
+        <v>252</v>
+      </c>
+      <c r="N4" s="79"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="48" t="s">
+        <v>260</v>
+      </c>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48" t="s">
+        <v>261</v>
+      </c>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48" t="s">
+        <v>253</v>
+      </c>
+      <c r="W4" s="48"/>
+      <c r="X4" s="48"/>
+      <c r="Y4" s="48"/>
+      <c r="Z4" s="48"/>
+      <c r="AA4" s="48"/>
+      <c r="AB4" s="48"/>
+      <c r="AC4" s="48"/>
+    </row>
+    <row r="5" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11">
+        <v>1</v>
+      </c>
+      <c r="B5" s="98" t="s">
+        <v>247</v>
+      </c>
+      <c r="C5" s="98"/>
+      <c r="D5" s="84" t="s">
+        <v>246</v>
+      </c>
+      <c r="E5" s="85"/>
+      <c r="F5" s="86"/>
+      <c r="G5" s="118" t="s">
+        <v>273</v>
+      </c>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="119"/>
+      <c r="K5" s="119"/>
+      <c r="L5" s="120"/>
+      <c r="M5" s="107" t="s">
+        <v>248</v>
+      </c>
+      <c r="N5" s="108"/>
+      <c r="O5" s="108"/>
+      <c r="P5" s="109"/>
+      <c r="Q5" s="105" t="s">
+        <v>254</v>
+      </c>
+      <c r="R5" s="105"/>
+      <c r="S5" s="106" t="s">
+        <v>262</v>
+      </c>
+      <c r="T5" s="103"/>
+      <c r="U5" s="104"/>
+      <c r="V5" s="101" t="s">
+        <v>249</v>
+      </c>
+      <c r="W5" s="101"/>
+      <c r="X5" s="101"/>
+      <c r="Y5" s="101"/>
+      <c r="Z5" s="101"/>
+      <c r="AA5" s="101"/>
+      <c r="AB5" s="101"/>
+      <c r="AC5" s="101"/>
+    </row>
+    <row r="6" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
+        <v>2</v>
+      </c>
+      <c r="B6" s="98" t="s">
+        <v>256</v>
+      </c>
+      <c r="C6" s="98"/>
+      <c r="D6" s="84" t="s">
+        <v>257</v>
+      </c>
+      <c r="E6" s="85"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="118" t="s">
+        <v>274</v>
+      </c>
+      <c r="H6" s="119"/>
+      <c r="I6" s="119"/>
+      <c r="J6" s="119"/>
+      <c r="K6" s="119"/>
+      <c r="L6" s="120"/>
+      <c r="M6" s="107" t="s">
+        <v>251</v>
+      </c>
+      <c r="N6" s="108"/>
+      <c r="O6" s="108"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="99" t="s">
+        <v>255</v>
+      </c>
+      <c r="R6" s="99"/>
+      <c r="S6" s="106">
+        <v>1</v>
+      </c>
+      <c r="T6" s="103"/>
+      <c r="U6" s="104"/>
+      <c r="V6" s="101" t="s">
+        <v>288</v>
+      </c>
+      <c r="W6" s="101"/>
+      <c r="X6" s="101"/>
+      <c r="Y6" s="101"/>
+      <c r="Z6" s="101"/>
+      <c r="AA6" s="101"/>
+      <c r="AB6" s="101"/>
+      <c r="AC6" s="101"/>
+    </row>
+    <row r="7" spans="1:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="11">
+        <v>3</v>
+      </c>
+      <c r="B7" s="98" t="s">
+        <v>289</v>
+      </c>
+      <c r="C7" s="98"/>
+      <c r="D7" s="84" t="s">
+        <v>257</v>
+      </c>
+      <c r="E7" s="85"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="118" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="119"/>
+      <c r="I7" s="119"/>
+      <c r="J7" s="119"/>
+      <c r="K7" s="119"/>
+      <c r="L7" s="120"/>
+      <c r="M7" s="107" t="s">
+        <v>290</v>
+      </c>
+      <c r="N7" s="108"/>
+      <c r="O7" s="108"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="99" t="s">
+        <v>291</v>
+      </c>
+      <c r="R7" s="99"/>
+      <c r="S7" s="106" t="s">
+        <v>262</v>
+      </c>
+      <c r="T7" s="103"/>
+      <c r="U7" s="104"/>
+      <c r="V7" s="101" t="s">
+        <v>288</v>
+      </c>
+      <c r="W7" s="101"/>
+      <c r="X7" s="101"/>
+      <c r="Y7" s="101"/>
+      <c r="Z7" s="101"/>
+      <c r="AA7" s="101"/>
+      <c r="AB7" s="101"/>
+      <c r="AC7" s="101"/>
+    </row>
+    <row r="8" spans="1:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="11">
+        <v>3</v>
+      </c>
+      <c r="B8" s="98" t="s">
+        <v>267</v>
+      </c>
+      <c r="C8" s="98"/>
+      <c r="D8" s="84" t="s">
+        <v>250</v>
+      </c>
+      <c r="E8" s="85"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="118" t="s">
+        <v>284</v>
+      </c>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="119"/>
+      <c r="K8" s="119"/>
+      <c r="L8" s="120"/>
+      <c r="M8" s="107" t="s">
+        <v>258</v>
+      </c>
+      <c r="N8" s="108"/>
+      <c r="O8" s="108"/>
+      <c r="P8" s="109"/>
+      <c r="Q8" s="99" t="s">
+        <v>259</v>
+      </c>
+      <c r="R8" s="99"/>
+      <c r="S8" s="102">
+        <v>1</v>
+      </c>
+      <c r="T8" s="103"/>
+      <c r="U8" s="104"/>
+      <c r="V8" s="101" t="s">
+        <v>263</v>
+      </c>
+      <c r="W8" s="101"/>
+      <c r="X8" s="101"/>
+      <c r="Y8" s="101"/>
+      <c r="Z8" s="101"/>
+      <c r="AA8" s="101"/>
+      <c r="AB8" s="101"/>
+      <c r="AC8" s="101"/>
+    </row>
+    <row r="9" spans="1:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="11">
+        <v>4</v>
+      </c>
+      <c r="B9" s="98" t="s">
+        <v>268</v>
+      </c>
+      <c r="C9" s="98"/>
+      <c r="D9" s="84" t="s">
+        <v>250</v>
+      </c>
+      <c r="E9" s="85"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="118" t="s">
+        <v>284</v>
+      </c>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="119"/>
+      <c r="K9" s="119"/>
+      <c r="L9" s="120"/>
+      <c r="M9" s="107" t="s">
+        <v>265</v>
+      </c>
+      <c r="N9" s="108"/>
+      <c r="O9" s="108"/>
+      <c r="P9" s="109"/>
+      <c r="Q9" s="99" t="s">
+        <v>264</v>
+      </c>
+      <c r="R9" s="99"/>
+      <c r="S9" s="102">
+        <v>1</v>
+      </c>
+      <c r="T9" s="103"/>
+      <c r="U9" s="104"/>
+      <c r="V9" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="W9" s="101"/>
+      <c r="X9" s="101"/>
+      <c r="Y9" s="101"/>
+      <c r="Z9" s="101"/>
+      <c r="AA9" s="101"/>
+      <c r="AB9" s="101"/>
+      <c r="AC9" s="101"/>
+    </row>
+    <row r="10" spans="1:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="11">
+        <v>5</v>
+      </c>
+      <c r="B10" s="98" t="s">
+        <v>269</v>
+      </c>
+      <c r="C10" s="98"/>
+      <c r="D10" s="84" t="s">
+        <v>250</v>
+      </c>
+      <c r="E10" s="85"/>
+      <c r="F10" s="86"/>
+      <c r="G10" s="118" t="s">
+        <v>285</v>
+      </c>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="119"/>
+      <c r="L10" s="120"/>
+      <c r="M10" s="107" t="s">
+        <v>270</v>
+      </c>
+      <c r="N10" s="108"/>
+      <c r="O10" s="108"/>
+      <c r="P10" s="109"/>
+      <c r="Q10" s="99" t="s">
+        <v>259</v>
+      </c>
+      <c r="R10" s="99"/>
+      <c r="S10" s="102">
+        <v>1</v>
+      </c>
+      <c r="T10" s="103"/>
+      <c r="U10" s="104"/>
+      <c r="V10" s="101" t="s">
+        <v>271</v>
+      </c>
+      <c r="W10" s="101"/>
+      <c r="X10" s="101"/>
+      <c r="Y10" s="101"/>
+      <c r="Z10" s="101"/>
+      <c r="AA10" s="101"/>
+      <c r="AB10" s="101"/>
+      <c r="AC10" s="101"/>
+    </row>
+    <row r="11" spans="1:29" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="11">
+        <v>6</v>
+      </c>
+      <c r="B11" s="98" t="s">
+        <v>286</v>
+      </c>
+      <c r="C11" s="98"/>
+      <c r="D11" s="84" t="s">
+        <v>250</v>
+      </c>
+      <c r="E11" s="85"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="118" t="s">
+        <v>202</v>
+      </c>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="119"/>
+      <c r="K11" s="119"/>
+      <c r="L11" s="120"/>
+      <c r="M11" s="107" t="s">
+        <v>258</v>
+      </c>
+      <c r="N11" s="108"/>
+      <c r="O11" s="108"/>
+      <c r="P11" s="109"/>
+      <c r="Q11" s="99" t="s">
+        <v>259</v>
+      </c>
+      <c r="R11" s="99"/>
+      <c r="S11" s="99" t="s">
+        <v>262</v>
+      </c>
+      <c r="T11" s="76"/>
+      <c r="U11" s="76"/>
+      <c r="V11" s="101" t="s">
+        <v>287</v>
+      </c>
+      <c r="W11" s="101"/>
+      <c r="X11" s="101"/>
+      <c r="Y11" s="101"/>
+      <c r="Z11" s="101"/>
+      <c r="AA11" s="101"/>
+      <c r="AB11" s="101"/>
+      <c r="AC11" s="101"/>
+    </row>
+    <row r="17" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E27" s="100"/>
+      <c r="F27" s="100"/>
+      <c r="G27" s="100"/>
+      <c r="H27" s="100"/>
+      <c r="I27" s="100"/>
+      <c r="J27" s="100"/>
+    </row>
+  </sheetData>
+  <mergeCells count="56">
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="S7:U7"/>
+    <mergeCell ref="V7:AC7"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:L7"/>
+    <mergeCell ref="M7:P7"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="G4:L4"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="G9:L9"/>
+    <mergeCell ref="V11:AC11"/>
+    <mergeCell ref="V4:AC4"/>
+    <mergeCell ref="V5:AC5"/>
+    <mergeCell ref="V6:AC6"/>
+    <mergeCell ref="V8:AC8"/>
+    <mergeCell ref="V9:AC9"/>
+    <mergeCell ref="V10:AC10"/>
+    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="S5:U5"/>
+    <mergeCell ref="S6:U6"/>
+    <mergeCell ref="S8:U8"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="S10:U10"/>
+    <mergeCell ref="S11:U11"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="M8:P8"/>
+    <mergeCell ref="M9:P9"/>
+    <mergeCell ref="M10:P10"/>
+    <mergeCell ref="M11:P11"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="M6:P6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="M4:P4"/>
+  </mergeCells>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <conditionalFormatting sqref="M5:M11">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:F7 D8:F11" xr:uid="{7BF058DC-62D2-424D-894E-A6AE051A4A89}">
+      <formula1>"Human, Environment, Object, Effect"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35CFDA9-1782-468E-A848-257FC462E672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEC33BC-7AD9-4953-B5BD-A82720129D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="300">
   <si>
     <t>SIGNOMALY</t>
   </si>
@@ -2583,15 +2583,33 @@
   </si>
   <si>
     <t>FONT SIZE</t>
+  </si>
+  <si>
+    <t>IX. Music</t>
+  </si>
+  <si>
+    <t>Phát trực tiếp tại đồng hồ</t>
+  </si>
+  <si>
+    <t>C_Clock</t>
+  </si>
+  <si>
+    <t>Khung đồng hồ điện</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="15"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2861,344 +2879,343 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4604,29 +4621,29 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:26" ht="46.5" x14ac:dyDescent="0.7">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
     </row>
     <row r="3" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
@@ -4650,104 +4667,104 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="44" t="s">
         <v>174</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
     </row>
     <row r="13" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="45"/>
-      <c r="M13" s="45"/>
-      <c r="N13" s="45"/>
-      <c r="O13" s="45"/>
-      <c r="P13" s="45"/>
-      <c r="Q13" s="45"/>
-      <c r="R13" s="45"/>
-      <c r="S13" s="45"/>
-      <c r="T13" s="45"/>
-      <c r="U13" s="45"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="43"/>
+      <c r="M13" s="43"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="43"/>
     </row>
     <row r="14" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="42"/>
-      <c r="M14" s="42"/>
-      <c r="N14" s="42"/>
-      <c r="O14" s="42"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="42"/>
-      <c r="U14" s="42"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="39"/>
+      <c r="Q14" s="39"/>
+      <c r="R14" s="39"/>
+      <c r="S14" s="39"/>
+      <c r="T14" s="39"/>
+      <c r="U14" s="39"/>
     </row>
     <row r="15" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
@@ -4816,76 +4833,76 @@
       <c r="U17" s="40"/>
     </row>
     <row r="18" spans="1:21" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="42"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="42"/>
-      <c r="R18" s="42"/>
-      <c r="S18" s="42"/>
-      <c r="T18" s="42"/>
-      <c r="U18" s="42"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="39"/>
+      <c r="O18" s="39"/>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="39"/>
+      <c r="R18" s="39"/>
+      <c r="S18" s="39"/>
+      <c r="T18" s="39"/>
+      <c r="U18" s="39"/>
     </row>
     <row r="19" spans="1:21" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="44"/>
-      <c r="O19" s="44"/>
-      <c r="P19" s="44"/>
-      <c r="Q19" s="44"/>
-      <c r="R19" s="44"/>
-      <c r="S19" s="44"/>
-      <c r="T19" s="44"/>
-      <c r="U19" s="44"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="42"/>
+      <c r="P19" s="42"/>
+      <c r="Q19" s="42"/>
+      <c r="R19" s="42"/>
+      <c r="S19" s="42"/>
+      <c r="T19" s="42"/>
+      <c r="U19" s="42"/>
     </row>
     <row r="20" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="45" t="s">
         <v>175</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="37"/>
-      <c r="L20" s="37"/>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="37"/>
-      <c r="P20" s="37"/>
-      <c r="Q20" s="37"/>
-      <c r="R20" s="37"/>
-      <c r="S20" s="37"/>
-      <c r="T20" s="37"/>
-      <c r="U20" s="37"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="45"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="45"/>
+      <c r="O20" s="45"/>
+      <c r="P20" s="45"/>
+      <c r="Q20" s="45"/>
+      <c r="R20" s="45"/>
+      <c r="S20" s="45"/>
+      <c r="T20" s="45"/>
+      <c r="U20" s="45"/>
     </row>
     <row r="22" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
@@ -4998,6 +5015,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B20:U20"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B16:U16"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="B18:U18"/>
     <mergeCell ref="B17:U17"/>
@@ -5005,11 +5027,6 @@
     <mergeCell ref="B14:U14"/>
     <mergeCell ref="B13:U13"/>
     <mergeCell ref="B12:J12"/>
-    <mergeCell ref="B20:U20"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B16:U16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5033,391 +5050,370 @@
       <c r="B4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="48" t="s">
+      <c r="C4" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48" t="s">
+      <c r="D4" s="57"/>
+      <c r="E4" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="48"/>
-      <c r="G4" s="52" t="s">
+      <c r="F4" s="57"/>
+      <c r="G4" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52" t="s">
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="52"/>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="52"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="52"/>
-      <c r="U4" s="52"/>
-      <c r="V4" s="52"/>
-      <c r="W4" s="52"/>
-      <c r="X4" s="52"/>
-      <c r="Y4" s="52"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="W4" s="48"/>
+      <c r="X4" s="48"/>
+      <c r="Y4" s="48"/>
     </row>
     <row r="5" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11">
         <v>1</v>
       </c>
-      <c r="C5" s="49" t="s">
+      <c r="C5" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="50" t="s">
+      <c r="D5" s="54"/>
+      <c r="E5" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="50"/>
-      <c r="G5" s="51" t="s">
+      <c r="F5" s="55"/>
+      <c r="G5" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="55" t="s">
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="N5" s="55"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="55"/>
-      <c r="T5" s="55"/>
-      <c r="U5" s="55"/>
-      <c r="V5" s="55"/>
-      <c r="W5" s="55"/>
-      <c r="X5" s="55"/>
-      <c r="Y5" s="55"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
+      <c r="W5" s="49"/>
+      <c r="X5" s="49"/>
+      <c r="Y5" s="49"/>
     </row>
     <row r="6" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11">
         <v>2</v>
       </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="50" t="s">
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="50"/>
-      <c r="G6" s="51" t="s">
+      <c r="F6" s="55"/>
+      <c r="G6" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="56" t="s">
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="N6" s="55"/>
-      <c r="O6" s="55"/>
-      <c r="P6" s="55"/>
-      <c r="Q6" s="55"/>
-      <c r="R6" s="55"/>
-      <c r="S6" s="55"/>
-      <c r="T6" s="55"/>
-      <c r="U6" s="55"/>
-      <c r="V6" s="55"/>
-      <c r="W6" s="55"/>
-      <c r="X6" s="55"/>
-      <c r="Y6" s="55"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="49"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
+      <c r="R6" s="49"/>
+      <c r="S6" s="49"/>
+      <c r="T6" s="49"/>
+      <c r="U6" s="49"/>
+      <c r="V6" s="49"/>
+      <c r="W6" s="49"/>
+      <c r="X6" s="49"/>
+      <c r="Y6" s="49"/>
     </row>
     <row r="7" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11">
         <v>3</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="50" t="s">
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="50"/>
-      <c r="G7" s="51" t="s">
+      <c r="F7" s="55"/>
+      <c r="G7" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="54" t="s">
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="53"/>
+      <c r="L7" s="53"/>
+      <c r="M7" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="54"/>
-      <c r="O7" s="54"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
-      <c r="R7" s="54"/>
-      <c r="S7" s="54"/>
-      <c r="T7" s="54"/>
-      <c r="U7" s="54"/>
-      <c r="V7" s="54"/>
-      <c r="W7" s="54"/>
-      <c r="X7" s="54"/>
-      <c r="Y7" s="54"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="51"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="51"/>
+      <c r="R7" s="51"/>
+      <c r="S7" s="51"/>
+      <c r="T7" s="51"/>
+      <c r="U7" s="51"/>
+      <c r="V7" s="51"/>
+      <c r="W7" s="51"/>
+      <c r="X7" s="51"/>
+      <c r="Y7" s="51"/>
     </row>
     <row r="8" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11">
         <v>4</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="49"/>
-      <c r="E8" s="50" t="s">
+      <c r="D8" s="54"/>
+      <c r="E8" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="50"/>
-      <c r="G8" s="51" t="s">
+      <c r="F8" s="55"/>
+      <c r="G8" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="53" t="s">
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="N8" s="54"/>
-      <c r="O8" s="54"/>
-      <c r="P8" s="54"/>
-      <c r="Q8" s="54"/>
-      <c r="R8" s="54"/>
-      <c r="S8" s="54"/>
-      <c r="T8" s="54"/>
-      <c r="U8" s="54"/>
-      <c r="V8" s="54"/>
-      <c r="W8" s="54"/>
-      <c r="X8" s="54"/>
-      <c r="Y8" s="54"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="51"/>
+      <c r="P8" s="51"/>
+      <c r="Q8" s="51"/>
+      <c r="R8" s="51"/>
+      <c r="S8" s="51"/>
+      <c r="T8" s="51"/>
+      <c r="U8" s="51"/>
+      <c r="V8" s="51"/>
+      <c r="W8" s="51"/>
+      <c r="X8" s="51"/>
+      <c r="Y8" s="51"/>
     </row>
     <row r="9" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11">
         <v>5</v>
       </c>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="50" t="s">
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="50"/>
-      <c r="G9" s="51" t="s">
+      <c r="F9" s="55"/>
+      <c r="G9" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="53" t="s">
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="53"/>
+      <c r="K9" s="53"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="54"/>
-      <c r="O9" s="54"/>
-      <c r="P9" s="54"/>
-      <c r="Q9" s="54"/>
-      <c r="R9" s="54"/>
-      <c r="S9" s="54"/>
-      <c r="T9" s="54"/>
-      <c r="U9" s="54"/>
-      <c r="V9" s="54"/>
-      <c r="W9" s="54"/>
-      <c r="X9" s="54"/>
-      <c r="Y9" s="54"/>
+      <c r="N9" s="51"/>
+      <c r="O9" s="51"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="51"/>
+      <c r="R9" s="51"/>
+      <c r="S9" s="51"/>
+      <c r="T9" s="51"/>
+      <c r="U9" s="51"/>
+      <c r="V9" s="51"/>
+      <c r="W9" s="51"/>
+      <c r="X9" s="51"/>
+      <c r="Y9" s="51"/>
     </row>
     <row r="10" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="11">
         <v>6</v>
       </c>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="50" t="s">
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="50"/>
-      <c r="G10" s="51" t="s">
+      <c r="F10" s="55"/>
+      <c r="G10" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
-      <c r="K10" s="51"/>
-      <c r="L10" s="51"/>
-      <c r="M10" s="53" t="s">
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="N10" s="54"/>
-      <c r="O10" s="54"/>
-      <c r="P10" s="54"/>
-      <c r="Q10" s="54"/>
-      <c r="R10" s="54"/>
-      <c r="S10" s="54"/>
-      <c r="T10" s="54"/>
-      <c r="U10" s="54"/>
-      <c r="V10" s="54"/>
-      <c r="W10" s="54"/>
-      <c r="X10" s="54"/>
-      <c r="Y10" s="54"/>
+      <c r="N10" s="51"/>
+      <c r="O10" s="51"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="51"/>
+      <c r="R10" s="51"/>
+      <c r="S10" s="51"/>
+      <c r="T10" s="51"/>
+      <c r="U10" s="51"/>
+      <c r="V10" s="51"/>
+      <c r="W10" s="51"/>
+      <c r="X10" s="51"/>
+      <c r="Y10" s="51"/>
     </row>
     <row r="11" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="11">
         <v>7</v>
       </c>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="50" t="s">
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="50"/>
-      <c r="G11" s="51" t="s">
+      <c r="F11" s="55"/>
+      <c r="G11" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="54" t="s">
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="54"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="54"/>
-      <c r="R11" s="54"/>
-      <c r="S11" s="54"/>
-      <c r="T11" s="54"/>
-      <c r="U11" s="54"/>
-      <c r="V11" s="54"/>
-      <c r="W11" s="54"/>
-      <c r="X11" s="54"/>
-      <c r="Y11" s="54"/>
+      <c r="N11" s="51"/>
+      <c r="O11" s="51"/>
+      <c r="P11" s="51"/>
+      <c r="Q11" s="51"/>
+      <c r="R11" s="51"/>
+      <c r="S11" s="51"/>
+      <c r="T11" s="51"/>
+      <c r="U11" s="51"/>
+      <c r="V11" s="51"/>
+      <c r="W11" s="51"/>
+      <c r="X11" s="51"/>
+      <c r="Y11" s="51"/>
     </row>
     <row r="12" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="11">
         <v>8</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="49"/>
-      <c r="E12" s="50" t="s">
+      <c r="D12" s="54"/>
+      <c r="E12" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="50"/>
-      <c r="G12" s="51" t="s">
+      <c r="F12" s="55"/>
+      <c r="G12" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="51"/>
-      <c r="M12" s="54" t="s">
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="N12" s="54"/>
-      <c r="O12" s="54"/>
-      <c r="P12" s="54"/>
-      <c r="Q12" s="54"/>
-      <c r="R12" s="54"/>
-      <c r="S12" s="54"/>
-      <c r="T12" s="54"/>
-      <c r="U12" s="54"/>
-      <c r="V12" s="54"/>
-      <c r="W12" s="54"/>
-      <c r="X12" s="54"/>
-      <c r="Y12" s="54"/>
+      <c r="N12" s="51"/>
+      <c r="O12" s="51"/>
+      <c r="P12" s="51"/>
+      <c r="Q12" s="51"/>
+      <c r="R12" s="51"/>
+      <c r="S12" s="51"/>
+      <c r="T12" s="51"/>
+      <c r="U12" s="51"/>
+      <c r="V12" s="51"/>
+      <c r="W12" s="51"/>
+      <c r="X12" s="51"/>
+      <c r="Y12" s="51"/>
     </row>
     <row r="46" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B49" s="47" t="s">
+      <c r="B49" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="47"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="47"/>
-      <c r="I49" s="47"/>
-      <c r="J49" s="47"/>
-      <c r="K49" s="47"/>
-      <c r="L49" s="47"/>
-      <c r="M49" s="47"/>
-      <c r="N49" s="47"/>
-      <c r="O49" s="47"/>
-      <c r="P49" s="47"/>
-      <c r="Q49" s="47"/>
-      <c r="R49" s="47"/>
-      <c r="S49" s="47"/>
-      <c r="T49" s="47"/>
-      <c r="U49" s="47"/>
-      <c r="V49" s="47"/>
+      <c r="C49" s="56"/>
+      <c r="D49" s="56"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="56"/>
+      <c r="J49" s="56"/>
+      <c r="K49" s="56"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="56"/>
+      <c r="N49" s="56"/>
+      <c r="O49" s="56"/>
+      <c r="P49" s="56"/>
+      <c r="Q49" s="56"/>
+      <c r="R49" s="56"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="56"/>
+      <c r="U49" s="56"/>
+      <c r="V49" s="56"/>
     </row>
     <row r="50" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B50" s="47"/>
-      <c r="C50" s="47"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="47"/>
-      <c r="G50" s="47"/>
-      <c r="H50" s="47"/>
-      <c r="I50" s="47"/>
-      <c r="J50" s="47"/>
-      <c r="K50" s="47"/>
-      <c r="L50" s="47"/>
-      <c r="M50" s="47"/>
-      <c r="N50" s="47"/>
-      <c r="O50" s="47"/>
-      <c r="P50" s="47"/>
-      <c r="Q50" s="47"/>
-      <c r="R50" s="47"/>
-      <c r="S50" s="47"/>
-      <c r="T50" s="47"/>
-      <c r="U50" s="47"/>
-      <c r="V50" s="47"/>
+      <c r="B50" s="56"/>
+      <c r="C50" s="56"/>
+      <c r="D50" s="56"/>
+      <c r="E50" s="56"/>
+      <c r="F50" s="56"/>
+      <c r="G50" s="56"/>
+      <c r="H50" s="56"/>
+      <c r="I50" s="56"/>
+      <c r="J50" s="56"/>
+      <c r="K50" s="56"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="56"/>
+      <c r="N50" s="56"/>
+      <c r="O50" s="56"/>
+      <c r="P50" s="56"/>
+      <c r="Q50" s="56"/>
+      <c r="R50" s="56"/>
+      <c r="S50" s="56"/>
+      <c r="T50" s="56"/>
+      <c r="U50" s="56"/>
+      <c r="V50" s="56"/>
       <c r="W50" s="8"/>
       <c r="X50" s="8"/>
       <c r="Y50" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="M4:Y4"/>
-    <mergeCell ref="M5:Y5"/>
-    <mergeCell ref="M6:Y6"/>
-    <mergeCell ref="M7:Y7"/>
-    <mergeCell ref="M8:Y8"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="M11:Y11"/>
-    <mergeCell ref="M12:Y12"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="M10:Y10"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="M9:Y9"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
     <mergeCell ref="B49:V50"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
@@ -5434,6 +5430,27 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="M10:Y10"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="M9:Y9"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="M11:Y11"/>
+    <mergeCell ref="M12:Y12"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="M4:Y4"/>
+    <mergeCell ref="M5:Y5"/>
+    <mergeCell ref="M6:Y6"/>
+    <mergeCell ref="M7:Y7"/>
+    <mergeCell ref="M8:Y8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5459,20 +5476,20 @@
       </c>
     </row>
     <row r="8" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L8" s="64" t="s">
+      <c r="L8" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="M8" s="65"/>
-      <c r="N8" s="65"/>
-      <c r="O8" s="65"/>
-      <c r="P8" s="65"/>
-      <c r="Q8" s="65"/>
-      <c r="R8" s="65"/>
-      <c r="S8" s="65"/>
-      <c r="T8" s="65"/>
-      <c r="U8" s="65"/>
-      <c r="V8" s="65"/>
-      <c r="W8" s="65"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="63"/>
+      <c r="O8" s="63"/>
+      <c r="P8" s="63"/>
+      <c r="Q8" s="63"/>
+      <c r="R8" s="63"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="63"/>
+      <c r="U8" s="63"/>
+      <c r="V8" s="63"/>
+      <c r="W8" s="63"/>
     </row>
     <row r="9" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="L9" s="7"/>
@@ -5489,25 +5506,25 @@
       <c r="W9" s="7"/>
     </row>
     <row r="10" spans="1:28" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L10" s="58" t="s">
+      <c r="L10" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="M10" s="43"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="43"/>
-      <c r="P10" s="43"/>
-      <c r="Q10" s="43"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="43"/>
-      <c r="V10" s="43"/>
-      <c r="W10" s="43"/>
-      <c r="X10" s="43"/>
-      <c r="Y10" s="43"/>
-      <c r="Z10" s="43"/>
-      <c r="AA10" s="43"/>
-      <c r="AB10" s="43"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="41"/>
+      <c r="R10" s="41"/>
+      <c r="S10" s="41"/>
+      <c r="T10" s="41"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="41"/>
+      <c r="W10" s="41"/>
+      <c r="X10" s="41"/>
+      <c r="Y10" s="41"/>
+      <c r="Z10" s="41"/>
+      <c r="AA10" s="41"/>
+      <c r="AB10" s="41"/>
     </row>
     <row r="11" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="L11" s="7"/>
@@ -5524,25 +5541,25 @@
       <c r="W11" s="7"/>
     </row>
     <row r="12" spans="1:28" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L12" s="58" t="s">
+      <c r="L12" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="M12" s="44"/>
-      <c r="N12" s="44"/>
-      <c r="O12" s="44"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="44"/>
-      <c r="R12" s="44"/>
-      <c r="S12" s="44"/>
-      <c r="T12" s="44"/>
-      <c r="U12" s="44"/>
-      <c r="V12" s="44"/>
-      <c r="W12" s="44"/>
-      <c r="X12" s="44"/>
-      <c r="Y12" s="44"/>
-      <c r="Z12" s="44"/>
-      <c r="AA12" s="44"/>
-      <c r="AB12" s="44"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="42"/>
+      <c r="S12" s="42"/>
+      <c r="T12" s="42"/>
+      <c r="U12" s="42"/>
+      <c r="V12" s="42"/>
+      <c r="W12" s="42"/>
+      <c r="X12" s="42"/>
+      <c r="Y12" s="42"/>
+      <c r="Z12" s="42"/>
+      <c r="AA12" s="42"/>
+      <c r="AB12" s="42"/>
     </row>
     <row r="13" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="S13" s="12"/>
@@ -5556,36 +5573,36 @@
       <c r="B16" s="8"/>
     </row>
     <row r="17" spans="2:29" ht="138" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="95" t="s">
+      <c r="B17" s="60" t="s">
         <v>242</v>
       </c>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="95"/>
-      <c r="K17" s="95"/>
-      <c r="L17" s="95"/>
-      <c r="M17" s="95"/>
-      <c r="N17" s="95"/>
-      <c r="O17" s="95"/>
-      <c r="P17" s="95"/>
-      <c r="Q17" s="95"/>
-      <c r="R17" s="95"/>
-      <c r="S17" s="95"/>
-      <c r="T17" s="95"/>
-      <c r="U17" s="95"/>
-      <c r="V17" s="95"/>
-      <c r="W17" s="95"/>
-      <c r="X17" s="95"/>
-      <c r="Y17" s="95"/>
-      <c r="Z17" s="95"/>
-      <c r="AA17" s="95"/>
-      <c r="AB17" s="95"/>
-      <c r="AC17" s="95"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="60"/>
+      <c r="L17" s="60"/>
+      <c r="M17" s="60"/>
+      <c r="N17" s="60"/>
+      <c r="O17" s="60"/>
+      <c r="P17" s="60"/>
+      <c r="Q17" s="60"/>
+      <c r="R17" s="60"/>
+      <c r="S17" s="60"/>
+      <c r="T17" s="60"/>
+      <c r="U17" s="60"/>
+      <c r="V17" s="60"/>
+      <c r="W17" s="60"/>
+      <c r="X17" s="60"/>
+      <c r="Y17" s="60"/>
+      <c r="Z17" s="60"/>
+      <c r="AA17" s="60"/>
+      <c r="AB17" s="60"/>
+      <c r="AC17" s="60"/>
     </row>
     <row r="18" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="15"/>
@@ -5620,41 +5637,41 @@
       <c r="C20" s="10"/>
     </row>
     <row r="22" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="P22" s="66" t="s">
+      <c r="P22" s="59" t="s">
         <v>73</v>
       </c>
-      <c r="Q22" s="66"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="66"/>
-      <c r="U22" s="66"/>
-      <c r="V22" s="66"/>
-      <c r="W22" s="66"/>
-      <c r="X22" s="66"/>
-      <c r="Y22" s="66"/>
-      <c r="Z22" s="66"/>
-      <c r="AA22" s="66"/>
-      <c r="AB22" s="66"/>
+      <c r="Q22" s="59"/>
+      <c r="R22" s="59"/>
+      <c r="S22" s="59"/>
+      <c r="T22" s="59"/>
+      <c r="U22" s="59"/>
+      <c r="V22" s="59"/>
+      <c r="W22" s="59"/>
+      <c r="X22" s="59"/>
+      <c r="Y22" s="59"/>
+      <c r="Z22" s="59"/>
+      <c r="AA22" s="59"/>
+      <c r="AB22" s="59"/>
     </row>
     <row r="23" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P23" s="12"/>
     </row>
     <row r="24" spans="2:29" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P24" s="62" t="s">
+      <c r="P24" s="61" t="s">
         <v>170</v>
       </c>
-      <c r="Q24" s="67"/>
-      <c r="R24" s="67"/>
-      <c r="S24" s="67"/>
-      <c r="T24" s="67"/>
-      <c r="U24" s="67"/>
-      <c r="V24" s="67"/>
-      <c r="W24" s="67"/>
-      <c r="X24" s="67"/>
-      <c r="Y24" s="67"/>
-      <c r="Z24" s="67"/>
-      <c r="AA24" s="67"/>
-      <c r="AB24" s="67"/>
+      <c r="Q24" s="64"/>
+      <c r="R24" s="64"/>
+      <c r="S24" s="64"/>
+      <c r="T24" s="64"/>
+      <c r="U24" s="64"/>
+      <c r="V24" s="64"/>
+      <c r="W24" s="64"/>
+      <c r="X24" s="64"/>
+      <c r="Y24" s="64"/>
+      <c r="Z24" s="64"/>
+      <c r="AA24" s="64"/>
+      <c r="AB24" s="64"/>
     </row>
     <row r="25" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P25" s="19"/>
@@ -5672,21 +5689,21 @@
       <c r="AB25" s="17"/>
     </row>
     <row r="26" spans="2:29" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P26" s="62" t="s">
+      <c r="P26" s="61" t="s">
         <v>172</v>
       </c>
-      <c r="Q26" s="62"/>
-      <c r="R26" s="62"/>
-      <c r="S26" s="62"/>
-      <c r="T26" s="62"/>
-      <c r="U26" s="62"/>
-      <c r="V26" s="62"/>
-      <c r="W26" s="62"/>
-      <c r="X26" s="62"/>
-      <c r="Y26" s="62"/>
-      <c r="Z26" s="62"/>
-      <c r="AA26" s="62"/>
-      <c r="AB26" s="62"/>
+      <c r="Q26" s="61"/>
+      <c r="R26" s="61"/>
+      <c r="S26" s="61"/>
+      <c r="T26" s="61"/>
+      <c r="U26" s="61"/>
+      <c r="V26" s="61"/>
+      <c r="W26" s="61"/>
+      <c r="X26" s="61"/>
+      <c r="Y26" s="61"/>
+      <c r="Z26" s="61"/>
+      <c r="AA26" s="61"/>
+      <c r="AB26" s="61"/>
     </row>
     <row r="27" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P27" s="17"/>
@@ -5704,21 +5721,21 @@
       <c r="AB27" s="17"/>
     </row>
     <row r="28" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="P28" s="66" t="s">
+      <c r="P28" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="Q28" s="66"/>
-      <c r="R28" s="66"/>
-      <c r="S28" s="66"/>
-      <c r="T28" s="66"/>
-      <c r="U28" s="66"/>
-      <c r="V28" s="66"/>
-      <c r="W28" s="66"/>
-      <c r="X28" s="66"/>
-      <c r="Y28" s="66"/>
-      <c r="Z28" s="66"/>
-      <c r="AA28" s="66"/>
-      <c r="AB28" s="66"/>
+      <c r="Q28" s="59"/>
+      <c r="R28" s="59"/>
+      <c r="S28" s="59"/>
+      <c r="T28" s="59"/>
+      <c r="U28" s="59"/>
+      <c r="V28" s="59"/>
+      <c r="W28" s="59"/>
+      <c r="X28" s="59"/>
+      <c r="Y28" s="59"/>
+      <c r="Z28" s="59"/>
+      <c r="AA28" s="59"/>
+      <c r="AB28" s="59"/>
     </row>
     <row r="29" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P29" s="12"/>
@@ -5764,38 +5781,38 @@
       <c r="AB35" s="12"/>
     </row>
     <row r="36" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P36" s="43" t="s">
+      <c r="P36" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="Q36" s="43"/>
-      <c r="R36" s="43"/>
-      <c r="S36" s="43"/>
-      <c r="T36" s="43"/>
-      <c r="U36" s="43"/>
-      <c r="V36" s="43"/>
-      <c r="W36" s="43"/>
-      <c r="X36" s="43"/>
-      <c r="Y36" s="43"/>
-      <c r="Z36" s="43"/>
-      <c r="AA36" s="43"/>
-      <c r="AB36" s="43"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="41"/>
+      <c r="S36" s="41"/>
+      <c r="T36" s="41"/>
+      <c r="U36" s="41"/>
+      <c r="V36" s="41"/>
+      <c r="W36" s="41"/>
+      <c r="X36" s="41"/>
+      <c r="Y36" s="41"/>
+      <c r="Z36" s="41"/>
+      <c r="AA36" s="41"/>
+      <c r="AB36" s="41"/>
     </row>
     <row r="38" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B38" s="68" t="s">
+      <c r="B38" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="68"/>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="68"/>
-      <c r="H38" s="68"/>
-      <c r="I38" s="68"/>
-      <c r="J38" s="68"/>
-      <c r="K38" s="68"/>
-      <c r="L38" s="68"/>
-      <c r="M38" s="68"/>
-      <c r="N38" s="68"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="66"/>
+      <c r="E38" s="66"/>
+      <c r="F38" s="66"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="66"/>
+      <c r="J38" s="66"/>
+      <c r="K38" s="66"/>
+      <c r="L38" s="66"/>
+      <c r="M38" s="66"/>
+      <c r="N38" s="66"/>
       <c r="P38" s="8" t="s">
         <v>57</v>
       </c>
@@ -5813,21 +5830,21 @@
       <c r="AB38" s="12"/>
     </row>
     <row r="39" spans="2:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P39" s="58" t="s">
+      <c r="P39" s="65" t="s">
         <v>203</v>
       </c>
-      <c r="Q39" s="58"/>
-      <c r="R39" s="58"/>
-      <c r="S39" s="58"/>
-      <c r="T39" s="58"/>
-      <c r="U39" s="58"/>
-      <c r="V39" s="58"/>
-      <c r="W39" s="58"/>
-      <c r="X39" s="58"/>
-      <c r="Y39" s="58"/>
-      <c r="Z39" s="58"/>
-      <c r="AA39" s="58"/>
-      <c r="AB39" s="58"/>
+      <c r="Q39" s="65"/>
+      <c r="R39" s="65"/>
+      <c r="S39" s="65"/>
+      <c r="T39" s="65"/>
+      <c r="U39" s="65"/>
+      <c r="V39" s="65"/>
+      <c r="W39" s="65"/>
+      <c r="X39" s="65"/>
+      <c r="Y39" s="65"/>
+      <c r="Z39" s="65"/>
+      <c r="AA39" s="65"/>
+      <c r="AB39" s="65"/>
       <c r="AC39" s="29"/>
     </row>
     <row r="40" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
@@ -5841,22 +5858,22 @@
       </c>
     </row>
     <row r="42" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="P42" s="66" t="s">
+      <c r="P42" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="Q42" s="66"/>
-      <c r="R42" s="66"/>
-      <c r="S42" s="66"/>
-      <c r="T42" s="66"/>
-      <c r="U42" s="66"/>
-      <c r="V42" s="66"/>
-      <c r="W42" s="66"/>
-      <c r="X42" s="66"/>
-      <c r="Y42" s="66"/>
-      <c r="Z42" s="66"/>
-      <c r="AA42" s="66"/>
-      <c r="AB42" s="66"/>
-      <c r="AC42" s="66"/>
+      <c r="Q42" s="59"/>
+      <c r="R42" s="59"/>
+      <c r="S42" s="59"/>
+      <c r="T42" s="59"/>
+      <c r="U42" s="59"/>
+      <c r="V42" s="59"/>
+      <c r="W42" s="59"/>
+      <c r="X42" s="59"/>
+      <c r="Y42" s="59"/>
+      <c r="Z42" s="59"/>
+      <c r="AA42" s="59"/>
+      <c r="AB42" s="59"/>
+      <c r="AC42" s="59"/>
     </row>
     <row r="43" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P43" s="12" t="s">
@@ -5869,21 +5886,21 @@
       </c>
     </row>
     <row r="45" spans="2:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P45" s="43" t="s">
+      <c r="P45" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="Q45" s="43"/>
-      <c r="R45" s="43"/>
-      <c r="S45" s="43"/>
-      <c r="T45" s="43"/>
-      <c r="U45" s="43"/>
-      <c r="V45" s="43"/>
-      <c r="W45" s="43"/>
-      <c r="X45" s="43"/>
-      <c r="Y45" s="43"/>
-      <c r="Z45" s="43"/>
-      <c r="AA45" s="43"/>
-      <c r="AB45" s="43"/>
+      <c r="Q45" s="41"/>
+      <c r="R45" s="41"/>
+      <c r="S45" s="41"/>
+      <c r="T45" s="41"/>
+      <c r="U45" s="41"/>
+      <c r="V45" s="41"/>
+      <c r="W45" s="41"/>
+      <c r="X45" s="41"/>
+      <c r="Y45" s="41"/>
+      <c r="Z45" s="41"/>
+      <c r="AA45" s="41"/>
+      <c r="AB45" s="41"/>
       <c r="AC45" s="30"/>
     </row>
     <row r="46" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
@@ -5892,40 +5909,40 @@
       </c>
     </row>
     <row r="47" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B47" s="69" t="s">
+      <c r="B47" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="C47" s="69"/>
-      <c r="D47" s="69"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="69"/>
-      <c r="G47" s="69"/>
-      <c r="H47" s="69"/>
-      <c r="I47" s="69"/>
-      <c r="J47" s="69"/>
-      <c r="K47" s="69"/>
-      <c r="L47" s="69"/>
-      <c r="M47" s="69"/>
+      <c r="C47" s="67"/>
+      <c r="D47" s="67"/>
+      <c r="E47" s="67"/>
+      <c r="F47" s="67"/>
+      <c r="G47" s="67"/>
+      <c r="H47" s="67"/>
+      <c r="I47" s="67"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="67"/>
+      <c r="L47" s="67"/>
+      <c r="M47" s="67"/>
       <c r="P47" s="8" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="48" spans="2:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P48" s="58" t="s">
+      <c r="P48" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="Q48" s="58"/>
-      <c r="R48" s="58"/>
-      <c r="S48" s="58"/>
-      <c r="T48" s="58"/>
-      <c r="U48" s="58"/>
-      <c r="V48" s="58"/>
-      <c r="W48" s="58"/>
-      <c r="X48" s="58"/>
-      <c r="Y48" s="58"/>
-      <c r="Z48" s="58"/>
-      <c r="AA48" s="58"/>
-      <c r="AB48" s="58"/>
+      <c r="Q48" s="65"/>
+      <c r="R48" s="65"/>
+      <c r="S48" s="65"/>
+      <c r="T48" s="65"/>
+      <c r="U48" s="65"/>
+      <c r="V48" s="65"/>
+      <c r="W48" s="65"/>
+      <c r="X48" s="65"/>
+      <c r="Y48" s="65"/>
+      <c r="Z48" s="65"/>
+      <c r="AA48" s="65"/>
+      <c r="AB48" s="65"/>
       <c r="AC48" s="27"/>
     </row>
     <row r="49" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
@@ -5939,21 +5956,21 @@
       </c>
     </row>
     <row r="51" spans="2:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P51" s="43" t="s">
+      <c r="P51" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="Q51" s="43"/>
-      <c r="R51" s="43"/>
-      <c r="S51" s="43"/>
-      <c r="T51" s="43"/>
-      <c r="U51" s="43"/>
-      <c r="V51" s="43"/>
-      <c r="W51" s="43"/>
-      <c r="X51" s="43"/>
-      <c r="Y51" s="43"/>
-      <c r="Z51" s="43"/>
-      <c r="AA51" s="43"/>
-      <c r="AB51" s="43"/>
+      <c r="Q51" s="41"/>
+      <c r="R51" s="41"/>
+      <c r="S51" s="41"/>
+      <c r="T51" s="41"/>
+      <c r="U51" s="41"/>
+      <c r="V51" s="41"/>
+      <c r="W51" s="41"/>
+      <c r="X51" s="41"/>
+      <c r="Y51" s="41"/>
+      <c r="Z51" s="41"/>
+      <c r="AA51" s="41"/>
+      <c r="AB51" s="41"/>
     </row>
     <row r="52" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P52" s="12" t="s">
@@ -5973,42 +5990,42 @@
       <c r="T55" s="12"/>
     </row>
     <row r="56" spans="2:29" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O56" s="58" t="s">
+      <c r="O56" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="P56" s="58"/>
-      <c r="Q56" s="58"/>
-      <c r="R56" s="58"/>
-      <c r="S56" s="58"/>
-      <c r="T56" s="58"/>
-      <c r="U56" s="58"/>
-      <c r="V56" s="58"/>
-      <c r="W56" s="58"/>
-      <c r="X56" s="58"/>
-      <c r="Y56" s="58"/>
-      <c r="Z56" s="58"/>
-      <c r="AA56" s="58"/>
-      <c r="AB56" s="58"/>
-      <c r="AC56" s="58"/>
+      <c r="P56" s="65"/>
+      <c r="Q56" s="65"/>
+      <c r="R56" s="65"/>
+      <c r="S56" s="65"/>
+      <c r="T56" s="65"/>
+      <c r="U56" s="65"/>
+      <c r="V56" s="65"/>
+      <c r="W56" s="65"/>
+      <c r="X56" s="65"/>
+      <c r="Y56" s="65"/>
+      <c r="Z56" s="65"/>
+      <c r="AA56" s="65"/>
+      <c r="AB56" s="65"/>
+      <c r="AC56" s="65"/>
     </row>
     <row r="58" spans="2:29" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O58" s="57" t="s">
+      <c r="O58" s="70" t="s">
         <v>87</v>
       </c>
-      <c r="P58" s="57"/>
-      <c r="Q58" s="57"/>
-      <c r="R58" s="57"/>
-      <c r="S58" s="57"/>
-      <c r="T58" s="57"/>
-      <c r="U58" s="57"/>
-      <c r="V58" s="57"/>
-      <c r="W58" s="57"/>
-      <c r="X58" s="57"/>
-      <c r="Y58" s="57"/>
-      <c r="Z58" s="57"/>
-      <c r="AA58" s="57"/>
-      <c r="AB58" s="57"/>
-      <c r="AC58" s="57"/>
+      <c r="P58" s="70"/>
+      <c r="Q58" s="70"/>
+      <c r="R58" s="70"/>
+      <c r="S58" s="70"/>
+      <c r="T58" s="70"/>
+      <c r="U58" s="70"/>
+      <c r="V58" s="70"/>
+      <c r="W58" s="70"/>
+      <c r="X58" s="70"/>
+      <c r="Y58" s="70"/>
+      <c r="Z58" s="70"/>
+      <c r="AA58" s="70"/>
+      <c r="AB58" s="70"/>
+      <c r="AC58" s="70"/>
     </row>
     <row r="59" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
       <c r="O59" s="18"/>
@@ -6028,23 +6045,23 @@
       <c r="AC59" s="17"/>
     </row>
     <row r="60" spans="2:29" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O60" s="59" t="s">
+      <c r="O60" s="71" t="s">
         <v>173</v>
       </c>
-      <c r="P60" s="60"/>
-      <c r="Q60" s="60"/>
-      <c r="R60" s="60"/>
-      <c r="S60" s="60"/>
-      <c r="T60" s="60"/>
-      <c r="U60" s="60"/>
-      <c r="V60" s="60"/>
-      <c r="W60" s="60"/>
-      <c r="X60" s="60"/>
-      <c r="Y60" s="60"/>
-      <c r="Z60" s="60"/>
-      <c r="AA60" s="60"/>
-      <c r="AB60" s="60"/>
-      <c r="AC60" s="60"/>
+      <c r="P60" s="72"/>
+      <c r="Q60" s="72"/>
+      <c r="R60" s="72"/>
+      <c r="S60" s="72"/>
+      <c r="T60" s="72"/>
+      <c r="U60" s="72"/>
+      <c r="V60" s="72"/>
+      <c r="W60" s="72"/>
+      <c r="X60" s="72"/>
+      <c r="Y60" s="72"/>
+      <c r="Z60" s="72"/>
+      <c r="AA60" s="72"/>
+      <c r="AB60" s="72"/>
+      <c r="AC60" s="72"/>
     </row>
     <row r="61" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O61" s="36"/>
@@ -6064,21 +6081,21 @@
       <c r="AC61" s="34"/>
     </row>
     <row r="62" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O62" s="94" t="s">
+      <c r="O62" s="58" t="s">
         <v>238</v>
       </c>
-      <c r="P62" s="66"/>
-      <c r="Q62" s="66"/>
-      <c r="R62" s="66"/>
-      <c r="S62" s="66"/>
-      <c r="T62" s="66"/>
-      <c r="U62" s="66"/>
-      <c r="V62" s="66"/>
-      <c r="W62" s="66"/>
-      <c r="X62" s="66"/>
-      <c r="Y62" s="66"/>
-      <c r="Z62" s="66"/>
-      <c r="AA62" s="66"/>
+      <c r="P62" s="59"/>
+      <c r="Q62" s="59"/>
+      <c r="R62" s="59"/>
+      <c r="S62" s="59"/>
+      <c r="T62" s="59"/>
+      <c r="U62" s="59"/>
+      <c r="V62" s="59"/>
+      <c r="W62" s="59"/>
+      <c r="X62" s="59"/>
+      <c r="Y62" s="59"/>
+      <c r="Z62" s="59"/>
+      <c r="AA62" s="59"/>
       <c r="AB62" s="34"/>
       <c r="AC62" s="34"/>
     </row>
@@ -6091,23 +6108,23 @@
       <c r="O65" s="8"/>
     </row>
     <row r="66" spans="15:29" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O66" s="61" t="s">
+      <c r="O66" s="68" t="s">
         <v>171</v>
       </c>
-      <c r="P66" s="62"/>
-      <c r="Q66" s="62"/>
-      <c r="R66" s="62"/>
-      <c r="S66" s="62"/>
-      <c r="T66" s="62"/>
-      <c r="U66" s="62"/>
-      <c r="V66" s="62"/>
-      <c r="W66" s="62"/>
-      <c r="X66" s="62"/>
-      <c r="Y66" s="62"/>
-      <c r="Z66" s="62"/>
-      <c r="AA66" s="62"/>
-      <c r="AB66" s="62"/>
-      <c r="AC66" s="62"/>
+      <c r="P66" s="61"/>
+      <c r="Q66" s="61"/>
+      <c r="R66" s="61"/>
+      <c r="S66" s="61"/>
+      <c r="T66" s="61"/>
+      <c r="U66" s="61"/>
+      <c r="V66" s="61"/>
+      <c r="W66" s="61"/>
+      <c r="X66" s="61"/>
+      <c r="Y66" s="61"/>
+      <c r="Z66" s="61"/>
+      <c r="AA66" s="61"/>
+      <c r="AB66" s="61"/>
+      <c r="AC66" s="61"/>
     </row>
     <row r="67" spans="15:29" ht="19.5" x14ac:dyDescent="0.25">
       <c r="O67" s="18"/>
@@ -6127,13 +6144,13 @@
       <c r="AC67" s="17"/>
     </row>
     <row r="68" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O68" s="63" t="s">
+      <c r="O68" s="69" t="s">
         <v>75</v>
       </c>
-      <c r="P68" s="63"/>
-      <c r="Q68" s="63"/>
-      <c r="R68" s="63"/>
-      <c r="S68" s="63"/>
+      <c r="P68" s="69"/>
+      <c r="Q68" s="69"/>
+      <c r="R68" s="69"/>
+      <c r="S68" s="69"/>
       <c r="T68" s="28"/>
       <c r="U68" s="28"/>
       <c r="V68" s="28"/>
@@ -6146,23 +6163,23 @@
       <c r="AC68" s="28"/>
     </row>
     <row r="69" spans="15:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O69" s="58" t="s">
+      <c r="O69" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="P69" s="43"/>
-      <c r="Q69" s="43"/>
-      <c r="R69" s="43"/>
-      <c r="S69" s="43"/>
-      <c r="T69" s="43"/>
-      <c r="U69" s="43"/>
-      <c r="V69" s="43"/>
-      <c r="W69" s="43"/>
-      <c r="X69" s="43"/>
-      <c r="Y69" s="43"/>
-      <c r="Z69" s="43"/>
-      <c r="AA69" s="43"/>
-      <c r="AB69" s="43"/>
-      <c r="AC69" s="43"/>
+      <c r="P69" s="41"/>
+      <c r="Q69" s="41"/>
+      <c r="R69" s="41"/>
+      <c r="S69" s="41"/>
+      <c r="T69" s="41"/>
+      <c r="U69" s="41"/>
+      <c r="V69" s="41"/>
+      <c r="W69" s="41"/>
+      <c r="X69" s="41"/>
+      <c r="Y69" s="41"/>
+      <c r="Z69" s="41"/>
+      <c r="AA69" s="41"/>
+      <c r="AB69" s="41"/>
+      <c r="AC69" s="41"/>
     </row>
     <row r="70" spans="15:29" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="O70" s="12" t="s">
@@ -6170,13 +6187,13 @@
       </c>
     </row>
     <row r="71" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O71" s="63" t="s">
+      <c r="O71" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="P71" s="63"/>
-      <c r="Q71" s="63"/>
-      <c r="R71" s="63"/>
-      <c r="S71" s="63"/>
+      <c r="P71" s="69"/>
+      <c r="Q71" s="69"/>
+      <c r="R71" s="69"/>
+      <c r="S71" s="69"/>
       <c r="T71" s="28"/>
       <c r="U71" s="28"/>
       <c r="V71" s="28"/>
@@ -6189,23 +6206,23 @@
       <c r="AC71" s="28"/>
     </row>
     <row r="72" spans="15:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O72" s="58" t="s">
+      <c r="O72" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="P72" s="58"/>
-      <c r="Q72" s="58"/>
-      <c r="R72" s="58"/>
-      <c r="S72" s="58"/>
-      <c r="T72" s="58"/>
-      <c r="U72" s="58"/>
-      <c r="V72" s="58"/>
-      <c r="W72" s="58"/>
-      <c r="X72" s="58"/>
-      <c r="Y72" s="58"/>
-      <c r="Z72" s="58"/>
-      <c r="AA72" s="58"/>
-      <c r="AB72" s="58"/>
-      <c r="AC72" s="58"/>
+      <c r="P72" s="65"/>
+      <c r="Q72" s="65"/>
+      <c r="R72" s="65"/>
+      <c r="S72" s="65"/>
+      <c r="T72" s="65"/>
+      <c r="U72" s="65"/>
+      <c r="V72" s="65"/>
+      <c r="W72" s="65"/>
+      <c r="X72" s="65"/>
+      <c r="Y72" s="65"/>
+      <c r="Z72" s="65"/>
+      <c r="AA72" s="65"/>
+      <c r="AB72" s="65"/>
+      <c r="AC72" s="65"/>
     </row>
     <row r="73" spans="15:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="O73" s="12" t="s">
@@ -6218,6 +6235,15 @@
     <row r="80" spans="15:29" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="O60:AC60"/>
+    <mergeCell ref="P39:AB39"/>
+    <mergeCell ref="P45:AB45"/>
+    <mergeCell ref="P48:AB48"/>
+    <mergeCell ref="O66:AC66"/>
+    <mergeCell ref="O68:S68"/>
+    <mergeCell ref="O69:AC69"/>
+    <mergeCell ref="O71:S71"/>
+    <mergeCell ref="O72:AC72"/>
     <mergeCell ref="O62:AA62"/>
     <mergeCell ref="B17:AC17"/>
     <mergeCell ref="P26:AB26"/>
@@ -6232,17 +6258,8 @@
     <mergeCell ref="P28:AB28"/>
     <mergeCell ref="B38:N38"/>
     <mergeCell ref="B47:M47"/>
-    <mergeCell ref="O66:AC66"/>
-    <mergeCell ref="O68:S68"/>
-    <mergeCell ref="O69:AC69"/>
-    <mergeCell ref="O71:S71"/>
-    <mergeCell ref="O72:AC72"/>
     <mergeCell ref="O58:AC58"/>
     <mergeCell ref="O56:AC56"/>
-    <mergeCell ref="O60:AC60"/>
-    <mergeCell ref="P39:AB39"/>
-    <mergeCell ref="P45:AB45"/>
-    <mergeCell ref="P48:AB48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -6268,129 +6285,129 @@
     </row>
     <row r="4" spans="1:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="75" t="s">
         <v>143</v>
       </c>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
     </row>
     <row r="5" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="L5" s="52" t="s">
+      <c r="L5" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
-      <c r="P5" s="52"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
     </row>
     <row r="6" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
-      <c r="L6" s="73" t="s">
+      <c r="L6" s="78" t="s">
         <v>120</v>
       </c>
-      <c r="M6" s="73"/>
-      <c r="N6" s="73"/>
-      <c r="O6" s="73"/>
-      <c r="P6" s="73"/>
+      <c r="M6" s="78"/>
+      <c r="N6" s="78"/>
+      <c r="O6" s="78"/>
+      <c r="P6" s="78"/>
     </row>
     <row r="7" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
-      <c r="L7" s="72" t="s">
+      <c r="L7" s="77" t="s">
         <v>121</v>
       </c>
-      <c r="M7" s="72"/>
-      <c r="N7" s="72"/>
-      <c r="O7" s="72"/>
-      <c r="P7" s="72"/>
+      <c r="M7" s="77"/>
+      <c r="N7" s="77"/>
+      <c r="O7" s="77"/>
+      <c r="P7" s="77"/>
     </row>
     <row r="8" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
-      <c r="L8" s="73" t="s">
+      <c r="L8" s="78" t="s">
         <v>122</v>
       </c>
-      <c r="M8" s="73"/>
-      <c r="N8" s="73"/>
-      <c r="O8" s="73"/>
-      <c r="P8" s="73"/>
+      <c r="M8" s="78"/>
+      <c r="N8" s="78"/>
+      <c r="O8" s="78"/>
+      <c r="P8" s="78"/>
     </row>
     <row r="9" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1"/>
-      <c r="L9" s="73" t="s">
+      <c r="L9" s="78" t="s">
         <v>123</v>
       </c>
-      <c r="M9" s="73"/>
-      <c r="N9" s="73"/>
-      <c r="O9" s="73"/>
-      <c r="P9" s="73"/>
+      <c r="M9" s="78"/>
+      <c r="N9" s="78"/>
+      <c r="O9" s="78"/>
+      <c r="P9" s="78"/>
     </row>
     <row r="10" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
-      <c r="L10" s="72" t="s">
+      <c r="L10" s="77" t="s">
         <v>124</v>
       </c>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="72"/>
+      <c r="M10" s="77"/>
+      <c r="N10" s="77"/>
+      <c r="O10" s="77"/>
+      <c r="P10" s="77"/>
     </row>
     <row r="11" spans="1:31" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
-      <c r="L11" s="72" t="s">
+      <c r="L11" s="77" t="s">
         <v>125</v>
       </c>
-      <c r="M11" s="73"/>
-      <c r="N11" s="73"/>
-      <c r="O11" s="73"/>
-      <c r="P11" s="73"/>
+      <c r="M11" s="78"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="78"/>
+      <c r="P11" s="78"/>
     </row>
     <row r="12" spans="1:31" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1"/>
-      <c r="L12" s="72" t="s">
+      <c r="L12" s="77" t="s">
         <v>126</v>
       </c>
-      <c r="M12" s="72"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="72"/>
-      <c r="P12" s="72"/>
-      <c r="R12" s="71" t="s">
+      <c r="M12" s="77"/>
+      <c r="N12" s="77"/>
+      <c r="O12" s="77"/>
+      <c r="P12" s="77"/>
+      <c r="R12" s="76" t="s">
         <v>138</v>
       </c>
-      <c r="S12" s="71"/>
-      <c r="T12" s="71"/>
-      <c r="U12" s="71"/>
-      <c r="V12" s="71"/>
-      <c r="W12" s="71"/>
-      <c r="X12" s="71"/>
-      <c r="Y12" s="71"/>
-      <c r="Z12" s="71"/>
-      <c r="AA12" s="71"/>
-      <c r="AB12" s="71"/>
-      <c r="AC12" s="71"/>
+      <c r="S12" s="76"/>
+      <c r="T12" s="76"/>
+      <c r="U12" s="76"/>
+      <c r="V12" s="76"/>
+      <c r="W12" s="76"/>
+      <c r="X12" s="76"/>
+      <c r="Y12" s="76"/>
+      <c r="Z12" s="76"/>
+      <c r="AA12" s="76"/>
+      <c r="AB12" s="76"/>
+      <c r="AC12" s="76"/>
       <c r="AD12" s="31"/>
       <c r="AE12" s="31"/>
     </row>
     <row r="13" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
-      <c r="L13" s="73" t="s">
+      <c r="L13" s="78" t="s">
         <v>127</v>
       </c>
-      <c r="M13" s="73"/>
-      <c r="N13" s="73"/>
-      <c r="O13" s="73"/>
-      <c r="P13" s="73"/>
+      <c r="M13" s="78"/>
+      <c r="N13" s="78"/>
+      <c r="O13" s="78"/>
+      <c r="P13" s="78"/>
     </row>
     <row r="14" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A14" s="1"/>
-      <c r="L14" s="73" t="s">
+      <c r="L14" s="78" t="s">
         <v>128</v>
       </c>
-      <c r="M14" s="73"/>
-      <c r="N14" s="73"/>
-      <c r="O14" s="73"/>
-      <c r="P14" s="73"/>
+      <c r="M14" s="78"/>
+      <c r="N14" s="78"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="78"/>
     </row>
     <row r="15" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
@@ -6398,146 +6415,146 @@
     </row>
     <row r="16" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
-      <c r="L16" s="52" t="s">
+      <c r="L16" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="M16" s="52"/>
-      <c r="N16" s="52"/>
-      <c r="O16" s="52" t="s">
+      <c r="M16" s="48"/>
+      <c r="N16" s="48"/>
+      <c r="O16" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="P16" s="52"/>
-      <c r="Q16" s="52"/>
-      <c r="R16" s="52"/>
-      <c r="S16" s="52"/>
-      <c r="T16" s="52"/>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="48"/>
+      <c r="R16" s="48"/>
+      <c r="S16" s="48"/>
+      <c r="T16" s="48"/>
     </row>
     <row r="17" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A17" s="1"/>
-      <c r="L17" s="49" t="s">
+      <c r="L17" s="54" t="s">
         <v>133</v>
       </c>
-      <c r="M17" s="49"/>
-      <c r="N17" s="49"/>
-      <c r="O17" s="75" t="s">
+      <c r="M17" s="54"/>
+      <c r="N17" s="54"/>
+      <c r="O17" s="74" t="s">
         <v>131</v>
       </c>
-      <c r="P17" s="75"/>
-      <c r="Q17" s="75"/>
-      <c r="R17" s="75"/>
-      <c r="S17" s="75"/>
-      <c r="T17" s="75"/>
+      <c r="P17" s="74"/>
+      <c r="Q17" s="74"/>
+      <c r="R17" s="74"/>
+      <c r="S17" s="74"/>
+      <c r="T17" s="74"/>
     </row>
     <row r="18" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
-      <c r="L18" s="49" t="s">
+      <c r="L18" s="54" t="s">
         <v>134</v>
       </c>
-      <c r="M18" s="49"/>
-      <c r="N18" s="49"/>
-      <c r="O18" s="75" t="s">
+      <c r="M18" s="54"/>
+      <c r="N18" s="54"/>
+      <c r="O18" s="74" t="s">
         <v>135</v>
       </c>
-      <c r="P18" s="75"/>
-      <c r="Q18" s="75"/>
-      <c r="R18" s="75"/>
-      <c r="S18" s="75"/>
-      <c r="T18" s="75"/>
+      <c r="P18" s="74"/>
+      <c r="Q18" s="74"/>
+      <c r="R18" s="74"/>
+      <c r="S18" s="74"/>
+      <c r="T18" s="74"/>
     </row>
     <row r="19" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
-      <c r="L19" s="49" t="s">
+      <c r="L19" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="M19" s="49"/>
-      <c r="N19" s="49"/>
-      <c r="O19" s="75" t="s">
+      <c r="M19" s="54"/>
+      <c r="N19" s="54"/>
+      <c r="O19" s="74" t="s">
         <v>137</v>
       </c>
-      <c r="P19" s="75"/>
-      <c r="Q19" s="75"/>
-      <c r="R19" s="75"/>
-      <c r="S19" s="75"/>
-      <c r="T19" s="75"/>
+      <c r="P19" s="74"/>
+      <c r="Q19" s="74"/>
+      <c r="R19" s="74"/>
+      <c r="S19" s="74"/>
+      <c r="T19" s="74"/>
     </row>
     <row r="20" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
     </row>
     <row r="21" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A21" s="1"/>
-      <c r="L21" s="52" t="s">
+      <c r="L21" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="M21" s="52"/>
-      <c r="N21" s="52"/>
-      <c r="O21" s="52" t="s">
+      <c r="M21" s="48"/>
+      <c r="N21" s="48"/>
+      <c r="O21" s="48" t="s">
         <v>295</v>
       </c>
-      <c r="P21" s="52"/>
-      <c r="Q21" s="52"/>
-      <c r="R21" s="52"/>
-      <c r="S21" s="52"/>
-      <c r="T21" s="52"/>
-      <c r="U21" s="52"/>
-      <c r="V21" s="52"/>
-      <c r="W21" s="52"/>
+      <c r="P21" s="48"/>
+      <c r="Q21" s="48"/>
+      <c r="R21" s="48"/>
+      <c r="S21" s="48"/>
+      <c r="T21" s="48"/>
+      <c r="U21" s="48"/>
+      <c r="V21" s="48"/>
+      <c r="W21" s="48"/>
     </row>
     <row r="22" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A22" s="1"/>
-      <c r="L22" s="49" t="s">
+      <c r="L22" s="54" t="s">
         <v>133</v>
       </c>
-      <c r="M22" s="49"/>
-      <c r="N22" s="49"/>
-      <c r="O22" s="121" t="s">
+      <c r="M22" s="54"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="73" t="s">
         <v>292</v>
       </c>
-      <c r="P22" s="121"/>
-      <c r="Q22" s="121"/>
-      <c r="R22" s="121"/>
-      <c r="S22" s="121"/>
-      <c r="T22" s="121"/>
-      <c r="U22" s="121"/>
-      <c r="V22" s="121"/>
-      <c r="W22" s="121"/>
+      <c r="P22" s="73"/>
+      <c r="Q22" s="73"/>
+      <c r="R22" s="73"/>
+      <c r="S22" s="73"/>
+      <c r="T22" s="73"/>
+      <c r="U22" s="73"/>
+      <c r="V22" s="73"/>
+      <c r="W22" s="73"/>
     </row>
     <row r="23" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A23" s="1"/>
-      <c r="L23" s="49" t="s">
+      <c r="L23" s="54" t="s">
         <v>134</v>
       </c>
-      <c r="M23" s="49"/>
-      <c r="N23" s="49"/>
-      <c r="O23" s="121" t="s">
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="73" t="s">
         <v>293</v>
       </c>
-      <c r="P23" s="121"/>
-      <c r="Q23" s="121"/>
-      <c r="R23" s="121"/>
-      <c r="S23" s="121"/>
-      <c r="T23" s="121"/>
-      <c r="U23" s="121"/>
-      <c r="V23" s="121"/>
-      <c r="W23" s="121"/>
+      <c r="P23" s="73"/>
+      <c r="Q23" s="73"/>
+      <c r="R23" s="73"/>
+      <c r="S23" s="73"/>
+      <c r="T23" s="73"/>
+      <c r="U23" s="73"/>
+      <c r="V23" s="73"/>
+      <c r="W23" s="73"/>
     </row>
     <row r="24" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A24" s="1"/>
-      <c r="L24" s="49" t="s">
+      <c r="L24" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="M24" s="49"/>
-      <c r="N24" s="49"/>
-      <c r="O24" s="121" t="s">
+      <c r="M24" s="54"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="73" t="s">
         <v>294</v>
       </c>
-      <c r="P24" s="121"/>
-      <c r="Q24" s="121"/>
-      <c r="R24" s="121"/>
-      <c r="S24" s="121"/>
-      <c r="T24" s="121"/>
-      <c r="U24" s="121"/>
-      <c r="V24" s="121"/>
-      <c r="W24" s="121"/>
+      <c r="P24" s="73"/>
+      <c r="Q24" s="73"/>
+      <c r="R24" s="73"/>
+      <c r="S24" s="73"/>
+      <c r="T24" s="73"/>
+      <c r="U24" s="73"/>
+      <c r="V24" s="73"/>
+      <c r="W24" s="73"/>
     </row>
     <row r="25" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
@@ -6633,32 +6650,32 @@
       </c>
     </row>
     <row r="107" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B107" s="74" t="s">
+      <c r="B107" s="79" t="s">
         <v>152</v>
       </c>
-      <c r="C107" s="74"/>
-      <c r="D107" s="74"/>
-      <c r="E107" s="74"/>
-      <c r="F107" s="74"/>
-      <c r="G107" s="74"/>
-      <c r="H107" s="74"/>
-      <c r="I107" s="74"/>
-      <c r="J107" s="74"/>
-      <c r="K107" s="74"/>
-      <c r="L107" s="74"/>
-      <c r="M107" s="74"/>
-      <c r="N107" s="74"/>
-      <c r="O107" s="74"/>
-      <c r="P107" s="74"/>
-      <c r="Q107" s="74"/>
-      <c r="R107" s="74"/>
-      <c r="S107" s="74"/>
-      <c r="T107" s="74"/>
-      <c r="U107" s="74"/>
-      <c r="V107" s="74"/>
-      <c r="W107" s="74"/>
-      <c r="X107" s="74"/>
-      <c r="Y107" s="74"/>
+      <c r="C107" s="79"/>
+      <c r="D107" s="79"/>
+      <c r="E107" s="79"/>
+      <c r="F107" s="79"/>
+      <c r="G107" s="79"/>
+      <c r="H107" s="79"/>
+      <c r="I107" s="79"/>
+      <c r="J107" s="79"/>
+      <c r="K107" s="79"/>
+      <c r="L107" s="79"/>
+      <c r="M107" s="79"/>
+      <c r="N107" s="79"/>
+      <c r="O107" s="79"/>
+      <c r="P107" s="79"/>
+      <c r="Q107" s="79"/>
+      <c r="R107" s="79"/>
+      <c r="S107" s="79"/>
+      <c r="T107" s="79"/>
+      <c r="U107" s="79"/>
+      <c r="V107" s="79"/>
+      <c r="W107" s="79"/>
+      <c r="X107" s="79"/>
+      <c r="Y107" s="79"/>
     </row>
     <row r="110" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A110" s="1" t="s">
@@ -6691,36 +6708,36 @@
       </c>
     </row>
     <row r="120" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="58" t="s">
+      <c r="B120" s="65" t="s">
         <v>162</v>
       </c>
-      <c r="C120" s="58"/>
-      <c r="D120" s="58"/>
-      <c r="E120" s="58"/>
-      <c r="F120" s="58"/>
-      <c r="G120" s="58"/>
-      <c r="H120" s="58"/>
-      <c r="I120" s="58"/>
-      <c r="J120" s="58"/>
-      <c r="K120" s="58"/>
-      <c r="L120" s="58"/>
-      <c r="M120" s="58"/>
-      <c r="N120" s="58"/>
-      <c r="O120" s="58"/>
-      <c r="P120" s="58"/>
-      <c r="Q120" s="58"/>
-      <c r="R120" s="58"/>
-      <c r="S120" s="58"/>
-      <c r="T120" s="58"/>
-      <c r="U120" s="58"/>
-      <c r="V120" s="58"/>
-      <c r="W120" s="58"/>
-      <c r="X120" s="58"/>
-      <c r="Y120" s="58"/>
-      <c r="Z120" s="58"/>
-      <c r="AA120" s="58"/>
-      <c r="AB120" s="58"/>
-      <c r="AC120" s="58"/>
+      <c r="C120" s="65"/>
+      <c r="D120" s="65"/>
+      <c r="E120" s="65"/>
+      <c r="F120" s="65"/>
+      <c r="G120" s="65"/>
+      <c r="H120" s="65"/>
+      <c r="I120" s="65"/>
+      <c r="J120" s="65"/>
+      <c r="K120" s="65"/>
+      <c r="L120" s="65"/>
+      <c r="M120" s="65"/>
+      <c r="N120" s="65"/>
+      <c r="O120" s="65"/>
+      <c r="P120" s="65"/>
+      <c r="Q120" s="65"/>
+      <c r="R120" s="65"/>
+      <c r="S120" s="65"/>
+      <c r="T120" s="65"/>
+      <c r="U120" s="65"/>
+      <c r="V120" s="65"/>
+      <c r="W120" s="65"/>
+      <c r="X120" s="65"/>
+      <c r="Y120" s="65"/>
+      <c r="Z120" s="65"/>
+      <c r="AA120" s="65"/>
+      <c r="AB120" s="65"/>
+      <c r="AC120" s="65"/>
     </row>
     <row r="121" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B121" s="24" t="s">
@@ -6777,20 +6794,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="O21:W21"/>
-    <mergeCell ref="O22:W22"/>
-    <mergeCell ref="O23:W23"/>
-    <mergeCell ref="O24:W24"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O18:T18"/>
-    <mergeCell ref="O19:T19"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="R12:AC12"/>
     <mergeCell ref="B120:AC120"/>
@@ -6807,6 +6810,20 @@
     <mergeCell ref="B107:Y107"/>
     <mergeCell ref="O17:T17"/>
     <mergeCell ref="O16:T16"/>
+    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="O19:T19"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="O21:W21"/>
+    <mergeCell ref="O22:W22"/>
+    <mergeCell ref="O23:W23"/>
+    <mergeCell ref="O24:W24"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L135" location="Dialogues!A1" display="Dialogues!A1" xr:uid="{5724AB96-1B0F-4DFD-A35F-382AC93CCD96}"/>
@@ -6822,7 +6839,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A2:T36"/>
+  <dimension ref="A2:T37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
@@ -6843,829 +6860,829 @@
       <c r="A6" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="48"/>
-      <c r="D6" s="78" t="s">
+      <c r="C6" s="57"/>
+      <c r="D6" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="48" t="s">
+      <c r="E6" s="81"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48" t="s">
+      <c r="H6" s="57"/>
+      <c r="I6" s="57" t="s">
         <v>118</v>
       </c>
-      <c r="J6" s="48"/>
-      <c r="K6" s="78" t="s">
+      <c r="J6" s="57"/>
+      <c r="K6" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="L6" s="79"/>
-      <c r="M6" s="79"/>
-      <c r="N6" s="79"/>
-      <c r="O6" s="79"/>
-      <c r="P6" s="79"/>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="48" t="s">
+      <c r="L6" s="81"/>
+      <c r="M6" s="81"/>
+      <c r="N6" s="81"/>
+      <c r="O6" s="81"/>
+      <c r="P6" s="81"/>
+      <c r="Q6" s="81"/>
+      <c r="R6" s="81"/>
+      <c r="S6" s="57" t="s">
         <v>217</v>
       </c>
-      <c r="T6" s="48"/>
+      <c r="T6" s="57"/>
     </row>
     <row r="7" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>1</v>
       </c>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="91" t="s">
         <v>181</v>
       </c>
-      <c r="C7" s="83"/>
-      <c r="D7" s="84" t="s">
+      <c r="C7" s="91"/>
+      <c r="D7" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="85"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="81" t="s">
+      <c r="E7" s="86"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="H7" s="81"/>
-      <c r="I7" s="82" t="s">
+      <c r="H7" s="92"/>
+      <c r="I7" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="J7" s="82"/>
-      <c r="K7" s="92" t="s">
+      <c r="J7" s="93"/>
+      <c r="K7" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="L7" s="93"/>
-      <c r="M7" s="93"/>
-      <c r="N7" s="93"/>
-      <c r="O7" s="93"/>
-      <c r="P7" s="93"/>
-      <c r="Q7" s="93"/>
-      <c r="R7" s="93"/>
-      <c r="S7" s="76" t="s">
+      <c r="L7" s="83"/>
+      <c r="M7" s="83"/>
+      <c r="N7" s="83"/>
+      <c r="O7" s="83"/>
+      <c r="P7" s="83"/>
+      <c r="Q7" s="83"/>
+      <c r="R7" s="83"/>
+      <c r="S7" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="T7" s="76"/>
+      <c r="T7" s="88"/>
     </row>
     <row r="8" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2</v>
       </c>
-      <c r="B8" s="83" t="s">
+      <c r="B8" s="91" t="s">
         <v>202</v>
       </c>
-      <c r="C8" s="83"/>
-      <c r="D8" s="84" t="s">
+      <c r="C8" s="91"/>
+      <c r="D8" s="85" t="s">
         <v>112</v>
       </c>
-      <c r="E8" s="85"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="87" t="s">
+      <c r="E8" s="86"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="94" t="s">
         <v>90</v>
       </c>
-      <c r="H8" s="87"/>
-      <c r="I8" s="82" t="s">
+      <c r="H8" s="94"/>
+      <c r="I8" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="J8" s="82"/>
-      <c r="K8" s="92" t="s">
+      <c r="J8" s="93"/>
+      <c r="K8" s="82" t="s">
         <v>177</v>
       </c>
-      <c r="L8" s="93"/>
-      <c r="M8" s="93"/>
-      <c r="N8" s="93"/>
-      <c r="O8" s="93"/>
-      <c r="P8" s="93"/>
-      <c r="Q8" s="93"/>
-      <c r="R8" s="93"/>
-      <c r="S8" s="76" t="s">
+      <c r="L8" s="83"/>
+      <c r="M8" s="83"/>
+      <c r="N8" s="83"/>
+      <c r="O8" s="83"/>
+      <c r="P8" s="83"/>
+      <c r="Q8" s="83"/>
+      <c r="R8" s="83"/>
+      <c r="S8" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="T8" s="76"/>
+      <c r="T8" s="88"/>
     </row>
     <row r="9" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>3</v>
       </c>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="91" t="s">
         <v>187</v>
       </c>
-      <c r="C9" s="83"/>
-      <c r="D9" s="84" t="s">
+      <c r="C9" s="91"/>
+      <c r="D9" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="85"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="81" t="s">
+      <c r="E9" s="86"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="H9" s="81"/>
-      <c r="I9" s="82" t="s">
+      <c r="H9" s="92"/>
+      <c r="I9" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="J9" s="82"/>
-      <c r="K9" s="92" t="s">
+      <c r="J9" s="93"/>
+      <c r="K9" s="82" t="s">
         <v>108</v>
       </c>
-      <c r="L9" s="93"/>
-      <c r="M9" s="93"/>
-      <c r="N9" s="93"/>
-      <c r="O9" s="93"/>
-      <c r="P9" s="93"/>
-      <c r="Q9" s="93"/>
-      <c r="R9" s="93"/>
-      <c r="S9" s="77" t="s">
+      <c r="L9" s="83"/>
+      <c r="M9" s="83"/>
+      <c r="N9" s="83"/>
+      <c r="O9" s="83"/>
+      <c r="P9" s="83"/>
+      <c r="Q9" s="83"/>
+      <c r="R9" s="83"/>
+      <c r="S9" s="89" t="s">
         <v>219</v>
       </c>
-      <c r="T9" s="76"/>
+      <c r="T9" s="88"/>
     </row>
     <row r="10" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>4</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="91" t="s">
         <v>188</v>
       </c>
-      <c r="C10" s="83"/>
-      <c r="D10" s="84" t="s">
+      <c r="C10" s="91"/>
+      <c r="D10" s="85" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="85"/>
-      <c r="F10" s="86"/>
-      <c r="G10" s="81" t="s">
+      <c r="E10" s="86"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="81"/>
-      <c r="I10" s="82" t="s">
+      <c r="H10" s="92"/>
+      <c r="I10" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="J10" s="82"/>
-      <c r="K10" s="92" t="s">
+      <c r="J10" s="93"/>
+      <c r="K10" s="82" t="s">
         <v>108</v>
       </c>
-      <c r="L10" s="93"/>
-      <c r="M10" s="93"/>
-      <c r="N10" s="93"/>
-      <c r="O10" s="93"/>
-      <c r="P10" s="93"/>
-      <c r="Q10" s="93"/>
-      <c r="R10" s="93"/>
-      <c r="S10" s="77" t="s">
+      <c r="L10" s="83"/>
+      <c r="M10" s="83"/>
+      <c r="N10" s="83"/>
+      <c r="O10" s="83"/>
+      <c r="P10" s="83"/>
+      <c r="Q10" s="83"/>
+      <c r="R10" s="83"/>
+      <c r="S10" s="89" t="s">
         <v>219</v>
       </c>
-      <c r="T10" s="76"/>
+      <c r="T10" s="88"/>
     </row>
     <row r="11" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>5</v>
       </c>
-      <c r="B11" s="83" t="s">
+      <c r="B11" s="91" t="s">
         <v>189</v>
       </c>
-      <c r="C11" s="83"/>
-      <c r="D11" s="84" t="s">
+      <c r="C11" s="91"/>
+      <c r="D11" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="85"/>
-      <c r="F11" s="86"/>
-      <c r="G11" s="81" t="s">
+      <c r="E11" s="86"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="H11" s="81"/>
-      <c r="I11" s="82" t="s">
+      <c r="H11" s="92"/>
+      <c r="I11" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="J11" s="82"/>
-      <c r="K11" s="92" t="s">
+      <c r="J11" s="93"/>
+      <c r="K11" s="82" t="s">
         <v>108</v>
       </c>
-      <c r="L11" s="93"/>
-      <c r="M11" s="93"/>
-      <c r="N11" s="93"/>
-      <c r="O11" s="93"/>
-      <c r="P11" s="93"/>
-      <c r="Q11" s="93"/>
-      <c r="R11" s="93"/>
-      <c r="S11" s="77" t="s">
+      <c r="L11" s="83"/>
+      <c r="M11" s="83"/>
+      <c r="N11" s="83"/>
+      <c r="O11" s="83"/>
+      <c r="P11" s="83"/>
+      <c r="Q11" s="83"/>
+      <c r="R11" s="83"/>
+      <c r="S11" s="89" t="s">
         <v>219</v>
       </c>
-      <c r="T11" s="76"/>
+      <c r="T11" s="88"/>
     </row>
     <row r="12" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>6</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="91" t="s">
         <v>190</v>
       </c>
-      <c r="C12" s="83"/>
-      <c r="D12" s="84" t="s">
+      <c r="C12" s="91"/>
+      <c r="D12" s="85" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="85"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="81" t="s">
+      <c r="E12" s="86"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="H12" s="81"/>
-      <c r="I12" s="82" t="s">
+      <c r="H12" s="92"/>
+      <c r="I12" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="J12" s="82"/>
-      <c r="K12" s="92" t="s">
+      <c r="J12" s="93"/>
+      <c r="K12" s="82" t="s">
         <v>108</v>
       </c>
-      <c r="L12" s="93"/>
-      <c r="M12" s="93"/>
-      <c r="N12" s="93"/>
-      <c r="O12" s="93"/>
-      <c r="P12" s="93"/>
-      <c r="Q12" s="93"/>
-      <c r="R12" s="93"/>
-      <c r="S12" s="77" t="s">
+      <c r="L12" s="83"/>
+      <c r="M12" s="83"/>
+      <c r="N12" s="83"/>
+      <c r="O12" s="83"/>
+      <c r="P12" s="83"/>
+      <c r="Q12" s="83"/>
+      <c r="R12" s="83"/>
+      <c r="S12" s="89" t="s">
         <v>219</v>
       </c>
-      <c r="T12" s="76"/>
+      <c r="T12" s="88"/>
     </row>
     <row r="13" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>7</v>
       </c>
-      <c r="B13" s="83" t="s">
+      <c r="B13" s="91" t="s">
         <v>191</v>
       </c>
-      <c r="C13" s="83"/>
-      <c r="D13" s="84" t="s">
+      <c r="C13" s="91"/>
+      <c r="D13" s="85" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="85"/>
-      <c r="F13" s="86"/>
-      <c r="G13" s="81" t="s">
+      <c r="E13" s="86"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="H13" s="81"/>
-      <c r="I13" s="82" t="s">
+      <c r="H13" s="92"/>
+      <c r="I13" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="J13" s="82"/>
-      <c r="K13" s="92" t="s">
+      <c r="J13" s="93"/>
+      <c r="K13" s="82" t="s">
         <v>108</v>
       </c>
-      <c r="L13" s="93"/>
-      <c r="M13" s="93"/>
-      <c r="N13" s="93"/>
-      <c r="O13" s="93"/>
-      <c r="P13" s="93"/>
-      <c r="Q13" s="93"/>
-      <c r="R13" s="93"/>
-      <c r="S13" s="77" t="s">
+      <c r="L13" s="83"/>
+      <c r="M13" s="83"/>
+      <c r="N13" s="83"/>
+      <c r="O13" s="83"/>
+      <c r="P13" s="83"/>
+      <c r="Q13" s="83"/>
+      <c r="R13" s="83"/>
+      <c r="S13" s="89" t="s">
         <v>219</v>
       </c>
-      <c r="T13" s="76"/>
+      <c r="T13" s="88"/>
     </row>
     <row r="14" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>8</v>
       </c>
-      <c r="B14" s="83" t="s">
+      <c r="B14" s="91" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="83"/>
-      <c r="D14" s="89" t="s">
+      <c r="C14" s="91"/>
+      <c r="D14" s="96" t="s">
         <v>96</v>
       </c>
-      <c r="E14" s="90"/>
-      <c r="F14" s="91"/>
-      <c r="G14" s="81" t="s">
+      <c r="E14" s="97"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="H14" s="81"/>
-      <c r="I14" s="82" t="s">
+      <c r="H14" s="92"/>
+      <c r="I14" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="J14" s="82"/>
-      <c r="K14" s="92" t="s">
+      <c r="J14" s="93"/>
+      <c r="K14" s="82" t="s">
         <v>109</v>
       </c>
-      <c r="L14" s="93"/>
-      <c r="M14" s="93"/>
-      <c r="N14" s="93"/>
-      <c r="O14" s="93"/>
-      <c r="P14" s="93"/>
-      <c r="Q14" s="93"/>
-      <c r="R14" s="93"/>
-      <c r="S14" s="76" t="s">
+      <c r="L14" s="83"/>
+      <c r="M14" s="83"/>
+      <c r="N14" s="83"/>
+      <c r="O14" s="83"/>
+      <c r="P14" s="83"/>
+      <c r="Q14" s="83"/>
+      <c r="R14" s="83"/>
+      <c r="S14" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="T14" s="76"/>
+      <c r="T14" s="88"/>
     </row>
     <row r="15" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="35">
         <v>9</v>
       </c>
-      <c r="B15" s="83" t="s">
+      <c r="B15" s="91" t="s">
         <v>183</v>
       </c>
-      <c r="C15" s="83"/>
-      <c r="D15" s="84" t="s">
+      <c r="C15" s="91"/>
+      <c r="D15" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="E15" s="85"/>
-      <c r="F15" s="86"/>
-      <c r="G15" s="81" t="s">
+      <c r="E15" s="86"/>
+      <c r="F15" s="87"/>
+      <c r="G15" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="H15" s="81"/>
-      <c r="I15" s="82" t="s">
+      <c r="H15" s="92"/>
+      <c r="I15" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="J15" s="82"/>
-      <c r="K15" s="92" t="s">
+      <c r="J15" s="93"/>
+      <c r="K15" s="82" t="s">
         <v>109</v>
       </c>
-      <c r="L15" s="93"/>
-      <c r="M15" s="93"/>
-      <c r="N15" s="93"/>
-      <c r="O15" s="93"/>
-      <c r="P15" s="93"/>
-      <c r="Q15" s="93"/>
-      <c r="R15" s="93"/>
-      <c r="S15" s="76" t="s">
+      <c r="L15" s="83"/>
+      <c r="M15" s="83"/>
+      <c r="N15" s="83"/>
+      <c r="O15" s="83"/>
+      <c r="P15" s="83"/>
+      <c r="Q15" s="83"/>
+      <c r="R15" s="83"/>
+      <c r="S15" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="T15" s="76"/>
+      <c r="T15" s="88"/>
     </row>
     <row r="16" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>10</v>
       </c>
-      <c r="B16" s="83" t="s">
+      <c r="B16" s="91" t="s">
         <v>184</v>
       </c>
-      <c r="C16" s="83"/>
-      <c r="D16" s="84" t="s">
+      <c r="C16" s="91"/>
+      <c r="D16" s="85" t="s">
         <v>115</v>
       </c>
-      <c r="E16" s="85"/>
-      <c r="F16" s="86"/>
-      <c r="G16" s="81" t="s">
+      <c r="E16" s="86"/>
+      <c r="F16" s="87"/>
+      <c r="G16" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="H16" s="81"/>
-      <c r="I16" s="82" t="s">
+      <c r="H16" s="92"/>
+      <c r="I16" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="J16" s="82"/>
-      <c r="K16" s="92" t="s">
+      <c r="J16" s="93"/>
+      <c r="K16" s="82" t="s">
         <v>116</v>
       </c>
-      <c r="L16" s="93"/>
-      <c r="M16" s="93"/>
-      <c r="N16" s="93"/>
-      <c r="O16" s="93"/>
-      <c r="P16" s="93"/>
-      <c r="Q16" s="93"/>
-      <c r="R16" s="93"/>
-      <c r="S16" s="76" t="s">
+      <c r="L16" s="83"/>
+      <c r="M16" s="83"/>
+      <c r="N16" s="83"/>
+      <c r="O16" s="83"/>
+      <c r="P16" s="83"/>
+      <c r="Q16" s="83"/>
+      <c r="R16" s="83"/>
+      <c r="S16" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="T16" s="76"/>
+      <c r="T16" s="88"/>
     </row>
     <row r="17" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>11</v>
       </c>
-      <c r="B17" s="83" t="s">
+      <c r="B17" s="91" t="s">
         <v>185</v>
       </c>
-      <c r="C17" s="83"/>
-      <c r="D17" s="84" t="s">
+      <c r="C17" s="91"/>
+      <c r="D17" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="E17" s="85"/>
-      <c r="F17" s="86"/>
-      <c r="G17" s="81" t="s">
+      <c r="E17" s="86"/>
+      <c r="F17" s="87"/>
+      <c r="G17" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="H17" s="81"/>
-      <c r="I17" s="82" t="s">
+      <c r="H17" s="92"/>
+      <c r="I17" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="J17" s="82"/>
-      <c r="K17" s="92" t="s">
+      <c r="J17" s="93"/>
+      <c r="K17" s="82" t="s">
         <v>117</v>
       </c>
-      <c r="L17" s="93"/>
-      <c r="M17" s="93"/>
-      <c r="N17" s="93"/>
-      <c r="O17" s="93"/>
-      <c r="P17" s="93"/>
-      <c r="Q17" s="93"/>
-      <c r="R17" s="93"/>
-      <c r="S17" s="76" t="s">
+      <c r="L17" s="83"/>
+      <c r="M17" s="83"/>
+      <c r="N17" s="83"/>
+      <c r="O17" s="83"/>
+      <c r="P17" s="83"/>
+      <c r="Q17" s="83"/>
+      <c r="R17" s="83"/>
+      <c r="S17" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="T17" s="76"/>
+      <c r="T17" s="88"/>
     </row>
     <row r="18" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>12</v>
       </c>
-      <c r="B18" s="83" t="s">
+      <c r="B18" s="91" t="s">
         <v>186</v>
       </c>
-      <c r="C18" s="83"/>
-      <c r="D18" s="84" t="s">
+      <c r="C18" s="91"/>
+      <c r="D18" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="E18" s="85"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="81" t="s">
+      <c r="E18" s="86"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="H18" s="81"/>
-      <c r="I18" s="82" t="s">
+      <c r="H18" s="92"/>
+      <c r="I18" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="J18" s="82"/>
-      <c r="K18" s="92" t="s">
+      <c r="J18" s="93"/>
+      <c r="K18" s="82" t="s">
         <v>117</v>
       </c>
-      <c r="L18" s="93"/>
-      <c r="M18" s="93"/>
-      <c r="N18" s="93"/>
-      <c r="O18" s="93"/>
-      <c r="P18" s="93"/>
-      <c r="Q18" s="93"/>
-      <c r="R18" s="93"/>
-      <c r="S18" s="99" t="s">
+      <c r="L18" s="83"/>
+      <c r="M18" s="83"/>
+      <c r="N18" s="83"/>
+      <c r="O18" s="83"/>
+      <c r="P18" s="83"/>
+      <c r="Q18" s="83"/>
+      <c r="R18" s="83"/>
+      <c r="S18" s="107" t="s">
         <v>219</v>
       </c>
-      <c r="T18" s="76"/>
+      <c r="T18" s="88"/>
     </row>
     <row r="19" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
         <v>13</v>
       </c>
-      <c r="B19" s="83" t="s">
+      <c r="B19" s="91" t="s">
         <v>192</v>
       </c>
-      <c r="C19" s="83"/>
-      <c r="D19" s="84" t="s">
+      <c r="C19" s="91"/>
+      <c r="D19" s="85" t="s">
         <v>100</v>
       </c>
-      <c r="E19" s="85"/>
-      <c r="F19" s="86"/>
-      <c r="G19" s="87" t="s">
+      <c r="E19" s="86"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="94" t="s">
         <v>90</v>
       </c>
-      <c r="H19" s="87"/>
-      <c r="I19" s="82" t="s">
+      <c r="H19" s="94"/>
+      <c r="I19" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="J19" s="82"/>
-      <c r="K19" s="92" t="s">
+      <c r="J19" s="93"/>
+      <c r="K19" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="L19" s="93"/>
-      <c r="M19" s="93"/>
-      <c r="N19" s="93"/>
-      <c r="O19" s="93"/>
-      <c r="P19" s="93"/>
-      <c r="Q19" s="93"/>
-      <c r="R19" s="93"/>
-      <c r="S19" s="76" t="s">
+      <c r="L19" s="83"/>
+      <c r="M19" s="83"/>
+      <c r="N19" s="83"/>
+      <c r="O19" s="83"/>
+      <c r="P19" s="83"/>
+      <c r="Q19" s="83"/>
+      <c r="R19" s="83"/>
+      <c r="S19" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="T19" s="76"/>
+      <c r="T19" s="88"/>
     </row>
     <row r="20" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>14</v>
       </c>
-      <c r="B20" s="83" t="s">
+      <c r="B20" s="91" t="s">
         <v>194</v>
       </c>
-      <c r="C20" s="83"/>
-      <c r="D20" s="84" t="s">
+      <c r="C20" s="91"/>
+      <c r="D20" s="85" t="s">
         <v>98</v>
       </c>
-      <c r="E20" s="85"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="87" t="s">
+      <c r="E20" s="86"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="94" t="s">
         <v>90</v>
       </c>
-      <c r="H20" s="87"/>
-      <c r="I20" s="82" t="s">
+      <c r="H20" s="94"/>
+      <c r="I20" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="J20" s="82"/>
-      <c r="K20" s="92" t="s">
+      <c r="J20" s="93"/>
+      <c r="K20" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="L20" s="93"/>
-      <c r="M20" s="93"/>
-      <c r="N20" s="93"/>
-      <c r="O20" s="93"/>
-      <c r="P20" s="93"/>
-      <c r="Q20" s="93"/>
-      <c r="R20" s="93"/>
-      <c r="S20" s="76" t="s">
+      <c r="L20" s="83"/>
+      <c r="M20" s="83"/>
+      <c r="N20" s="83"/>
+      <c r="O20" s="83"/>
+      <c r="P20" s="83"/>
+      <c r="Q20" s="83"/>
+      <c r="R20" s="83"/>
+      <c r="S20" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="T20" s="76"/>
+      <c r="T20" s="88"/>
     </row>
     <row r="21" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="35">
         <v>15</v>
       </c>
-      <c r="B21" s="83" t="s">
+      <c r="B21" s="91" t="s">
         <v>195</v>
       </c>
-      <c r="C21" s="83"/>
-      <c r="D21" s="84" t="s">
+      <c r="C21" s="91"/>
+      <c r="D21" s="85" t="s">
         <v>102</v>
       </c>
-      <c r="E21" s="85"/>
-      <c r="F21" s="86"/>
-      <c r="G21" s="87" t="s">
+      <c r="E21" s="86"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="94" t="s">
         <v>90</v>
       </c>
-      <c r="H21" s="87"/>
-      <c r="I21" s="88" t="s">
+      <c r="H21" s="94"/>
+      <c r="I21" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="J21" s="88"/>
-      <c r="K21" s="92" t="s">
+      <c r="J21" s="95"/>
+      <c r="K21" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="L21" s="93"/>
-      <c r="M21" s="93"/>
-      <c r="N21" s="93"/>
-      <c r="O21" s="93"/>
-      <c r="P21" s="93"/>
-      <c r="Q21" s="93"/>
-      <c r="R21" s="93"/>
-      <c r="S21" s="76" t="s">
+      <c r="L21" s="83"/>
+      <c r="M21" s="83"/>
+      <c r="N21" s="83"/>
+      <c r="O21" s="83"/>
+      <c r="P21" s="83"/>
+      <c r="Q21" s="83"/>
+      <c r="R21" s="83"/>
+      <c r="S21" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="T21" s="76"/>
+      <c r="T21" s="88"/>
     </row>
     <row r="22" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>16</v>
       </c>
-      <c r="B22" s="83" t="s">
+      <c r="B22" s="91" t="s">
         <v>196</v>
       </c>
-      <c r="C22" s="83"/>
-      <c r="D22" s="84" t="s">
+      <c r="C22" s="91"/>
+      <c r="D22" s="85" t="s">
         <v>103</v>
       </c>
-      <c r="E22" s="85"/>
-      <c r="F22" s="86"/>
-      <c r="G22" s="87" t="s">
+      <c r="E22" s="86"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="94" t="s">
         <v>90</v>
       </c>
-      <c r="H22" s="87"/>
-      <c r="I22" s="88" t="s">
+      <c r="H22" s="94"/>
+      <c r="I22" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="J22" s="88"/>
-      <c r="K22" s="92" t="s">
+      <c r="J22" s="95"/>
+      <c r="K22" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="L22" s="93"/>
-      <c r="M22" s="93"/>
-      <c r="N22" s="93"/>
-      <c r="O22" s="93"/>
-      <c r="P22" s="93"/>
-      <c r="Q22" s="93"/>
-      <c r="R22" s="93"/>
-      <c r="S22" s="76" t="s">
+      <c r="L22" s="83"/>
+      <c r="M22" s="83"/>
+      <c r="N22" s="83"/>
+      <c r="O22" s="83"/>
+      <c r="P22" s="83"/>
+      <c r="Q22" s="83"/>
+      <c r="R22" s="83"/>
+      <c r="S22" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="T22" s="76"/>
+      <c r="T22" s="88"/>
     </row>
     <row r="23" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>17</v>
       </c>
-      <c r="B23" s="83" t="s">
+      <c r="B23" s="91" t="s">
         <v>197</v>
       </c>
-      <c r="C23" s="83"/>
-      <c r="D23" s="84" t="s">
+      <c r="C23" s="91"/>
+      <c r="D23" s="85" t="s">
         <v>104</v>
       </c>
-      <c r="E23" s="85"/>
-      <c r="F23" s="86"/>
-      <c r="G23" s="87" t="s">
+      <c r="E23" s="86"/>
+      <c r="F23" s="87"/>
+      <c r="G23" s="94" t="s">
         <v>90</v>
       </c>
-      <c r="H23" s="87"/>
-      <c r="I23" s="88" t="s">
+      <c r="H23" s="94"/>
+      <c r="I23" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="J23" s="88"/>
-      <c r="K23" s="92" t="s">
+      <c r="J23" s="95"/>
+      <c r="K23" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="L23" s="93"/>
-      <c r="M23" s="93"/>
-      <c r="N23" s="93"/>
-      <c r="O23" s="93"/>
-      <c r="P23" s="93"/>
-      <c r="Q23" s="93"/>
-      <c r="R23" s="93"/>
-      <c r="S23" s="76" t="s">
+      <c r="L23" s="83"/>
+      <c r="M23" s="83"/>
+      <c r="N23" s="83"/>
+      <c r="O23" s="83"/>
+      <c r="P23" s="83"/>
+      <c r="Q23" s="83"/>
+      <c r="R23" s="83"/>
+      <c r="S23" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="T23" s="76"/>
+      <c r="T23" s="88"/>
     </row>
     <row r="24" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>18</v>
       </c>
-      <c r="B24" s="83" t="s">
+      <c r="B24" s="91" t="s">
         <v>198</v>
       </c>
-      <c r="C24" s="83"/>
-      <c r="D24" s="84" t="s">
+      <c r="C24" s="91"/>
+      <c r="D24" s="85" t="s">
         <v>105</v>
       </c>
-      <c r="E24" s="85"/>
-      <c r="F24" s="86"/>
-      <c r="G24" s="87" t="s">
+      <c r="E24" s="86"/>
+      <c r="F24" s="87"/>
+      <c r="G24" s="94" t="s">
         <v>90</v>
       </c>
-      <c r="H24" s="87"/>
-      <c r="I24" s="88" t="s">
+      <c r="H24" s="94"/>
+      <c r="I24" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="J24" s="88"/>
-      <c r="K24" s="92" t="s">
+      <c r="J24" s="95"/>
+      <c r="K24" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="L24" s="93"/>
-      <c r="M24" s="93"/>
-      <c r="N24" s="93"/>
-      <c r="O24" s="93"/>
-      <c r="P24" s="93"/>
-      <c r="Q24" s="93"/>
-      <c r="R24" s="93"/>
-      <c r="S24" s="76" t="s">
+      <c r="L24" s="83"/>
+      <c r="M24" s="83"/>
+      <c r="N24" s="83"/>
+      <c r="O24" s="83"/>
+      <c r="P24" s="83"/>
+      <c r="Q24" s="83"/>
+      <c r="R24" s="83"/>
+      <c r="S24" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="T24" s="76"/>
+      <c r="T24" s="88"/>
     </row>
     <row r="25" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>19</v>
       </c>
-      <c r="B25" s="83" t="s">
+      <c r="B25" s="91" t="s">
         <v>199</v>
       </c>
-      <c r="C25" s="83"/>
-      <c r="D25" s="84" t="s">
+      <c r="C25" s="91"/>
+      <c r="D25" s="85" t="s">
         <v>106</v>
       </c>
-      <c r="E25" s="85"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="87" t="s">
+      <c r="E25" s="86"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="94" t="s">
         <v>90</v>
       </c>
-      <c r="H25" s="87"/>
-      <c r="I25" s="88" t="s">
+      <c r="H25" s="94"/>
+      <c r="I25" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="J25" s="88"/>
-      <c r="K25" s="92" t="s">
+      <c r="J25" s="95"/>
+      <c r="K25" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="L25" s="93"/>
-      <c r="M25" s="93"/>
-      <c r="N25" s="93"/>
-      <c r="O25" s="93"/>
-      <c r="P25" s="93"/>
-      <c r="Q25" s="93"/>
-      <c r="R25" s="93"/>
-      <c r="S25" s="76" t="s">
+      <c r="L25" s="83"/>
+      <c r="M25" s="83"/>
+      <c r="N25" s="83"/>
+      <c r="O25" s="83"/>
+      <c r="P25" s="83"/>
+      <c r="Q25" s="83"/>
+      <c r="R25" s="83"/>
+      <c r="S25" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="T25" s="76"/>
+      <c r="T25" s="88"/>
     </row>
     <row r="26" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>20</v>
       </c>
-      <c r="B26" s="83" t="s">
+      <c r="B26" s="91" t="s">
         <v>200</v>
       </c>
-      <c r="C26" s="83"/>
-      <c r="D26" s="84" t="s">
+      <c r="C26" s="91"/>
+      <c r="D26" s="85" t="s">
         <v>107</v>
       </c>
-      <c r="E26" s="85"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="87" t="s">
+      <c r="E26" s="86"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="94" t="s">
         <v>90</v>
       </c>
-      <c r="H26" s="87"/>
-      <c r="I26" s="88" t="s">
+      <c r="H26" s="94"/>
+      <c r="I26" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="J26" s="88"/>
-      <c r="K26" s="92" t="s">
+      <c r="J26" s="95"/>
+      <c r="K26" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="L26" s="93"/>
-      <c r="M26" s="93"/>
-      <c r="N26" s="93"/>
-      <c r="O26" s="93"/>
-      <c r="P26" s="93"/>
-      <c r="Q26" s="93"/>
-      <c r="R26" s="93"/>
-      <c r="S26" s="76" t="s">
+      <c r="L26" s="83"/>
+      <c r="M26" s="83"/>
+      <c r="N26" s="83"/>
+      <c r="O26" s="83"/>
+      <c r="P26" s="83"/>
+      <c r="Q26" s="83"/>
+      <c r="R26" s="83"/>
+      <c r="S26" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="T26" s="76"/>
+      <c r="T26" s="88"/>
     </row>
     <row r="27" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>21</v>
       </c>
-      <c r="B27" s="83" t="s">
+      <c r="B27" s="91" t="s">
         <v>201</v>
       </c>
-      <c r="C27" s="83"/>
-      <c r="D27" s="84" t="s">
+      <c r="C27" s="91"/>
+      <c r="D27" s="85" t="s">
         <v>101</v>
       </c>
-      <c r="E27" s="85"/>
-      <c r="F27" s="86"/>
-      <c r="G27" s="87" t="s">
+      <c r="E27" s="86"/>
+      <c r="F27" s="87"/>
+      <c r="G27" s="94" t="s">
         <v>90</v>
       </c>
-      <c r="H27" s="87"/>
-      <c r="I27" s="88" t="s">
+      <c r="H27" s="94"/>
+      <c r="I27" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="J27" s="88"/>
-      <c r="K27" s="92" t="s">
+      <c r="J27" s="95"/>
+      <c r="K27" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="L27" s="93"/>
-      <c r="M27" s="93"/>
-      <c r="N27" s="93"/>
-      <c r="O27" s="93"/>
-      <c r="P27" s="93"/>
-      <c r="Q27" s="93"/>
-      <c r="R27" s="93"/>
-      <c r="S27" s="76" t="s">
+      <c r="L27" s="83"/>
+      <c r="M27" s="83"/>
+      <c r="N27" s="83"/>
+      <c r="O27" s="83"/>
+      <c r="P27" s="83"/>
+      <c r="Q27" s="83"/>
+      <c r="R27" s="83"/>
+      <c r="S27" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="T27" s="76"/>
+      <c r="T27" s="88"/>
     </row>
     <row r="28" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="110">
+      <c r="A28" s="37">
         <v>13</v>
       </c>
-      <c r="B28" s="111" t="s">
+      <c r="B28" s="104" t="s">
         <v>193</v>
       </c>
-      <c r="C28" s="111"/>
-      <c r="D28" s="112" t="s">
+      <c r="C28" s="104"/>
+      <c r="D28" s="99" t="s">
         <v>99</v>
       </c>
-      <c r="E28" s="113"/>
-      <c r="F28" s="114"/>
-      <c r="G28" s="115" t="s">
+      <c r="E28" s="100"/>
+      <c r="F28" s="101"/>
+      <c r="G28" s="105" t="s">
         <v>90</v>
       </c>
-      <c r="H28" s="115"/>
-      <c r="I28" s="116" t="s">
+      <c r="H28" s="105"/>
+      <c r="I28" s="106" t="s">
         <v>92</v>
       </c>
-      <c r="J28" s="116"/>
-      <c r="K28" s="122" t="s">
+      <c r="J28" s="106"/>
+      <c r="K28" s="102" t="s">
         <v>110</v>
       </c>
-      <c r="L28" s="123"/>
-      <c r="M28" s="123"/>
-      <c r="N28" s="123"/>
-      <c r="O28" s="123"/>
-      <c r="P28" s="123"/>
-      <c r="Q28" s="123"/>
-      <c r="R28" s="123"/>
-      <c r="S28" s="117" t="s">
+      <c r="L28" s="103"/>
+      <c r="M28" s="103"/>
+      <c r="N28" s="103"/>
+      <c r="O28" s="103"/>
+      <c r="P28" s="103"/>
+      <c r="Q28" s="103"/>
+      <c r="R28" s="103"/>
+      <c r="S28" s="108" t="s">
         <v>218</v>
       </c>
-      <c r="T28" s="117"/>
+      <c r="T28" s="108"/>
     </row>
     <row r="31" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
@@ -7679,138 +7696,153 @@
       <c r="A33" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B33" s="48" t="s">
+      <c r="B33" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="C33" s="48"/>
-      <c r="D33" s="78" t="s">
+      <c r="C33" s="57"/>
+      <c r="D33" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="E33" s="79"/>
-      <c r="F33" s="80"/>
-      <c r="G33" s="48" t="s">
+      <c r="E33" s="81"/>
+      <c r="F33" s="90"/>
+      <c r="G33" s="57" t="s">
         <v>217</v>
       </c>
-      <c r="H33" s="48"/>
+      <c r="H33" s="57"/>
     </row>
     <row r="34" spans="1:8" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A34" s="11">
         <v>1</v>
       </c>
-      <c r="B34" s="97" t="s">
+      <c r="B34" s="84" t="s">
         <v>278</v>
       </c>
-      <c r="C34" s="97"/>
-      <c r="D34" s="84" t="s">
+      <c r="C34" s="84"/>
+      <c r="D34" s="85" t="s">
         <v>281</v>
       </c>
-      <c r="E34" s="85"/>
-      <c r="F34" s="86"/>
-      <c r="G34" s="76" t="s">
+      <c r="E34" s="86"/>
+      <c r="F34" s="87"/>
+      <c r="G34" s="88" t="s">
         <v>218</v>
       </c>
-      <c r="H34" s="76"/>
+      <c r="H34" s="88"/>
     </row>
     <row r="35" spans="1:8" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A35" s="11">
         <v>2</v>
       </c>
-      <c r="B35" s="97" t="s">
+      <c r="B35" s="84" t="s">
         <v>279</v>
       </c>
-      <c r="C35" s="97"/>
-      <c r="D35" s="84" t="s">
+      <c r="C35" s="84"/>
+      <c r="D35" s="85" t="s">
         <v>282</v>
       </c>
-      <c r="E35" s="85"/>
-      <c r="F35" s="86"/>
-      <c r="G35" s="76" t="s">
+      <c r="E35" s="86"/>
+      <c r="F35" s="87"/>
+      <c r="G35" s="88" t="s">
         <v>218</v>
       </c>
-      <c r="H35" s="76"/>
+      <c r="H35" s="88"/>
     </row>
     <row r="36" spans="1:8" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A36" s="11">
         <v>3</v>
       </c>
-      <c r="B36" s="97" t="s">
+      <c r="B36" s="84" t="s">
         <v>280</v>
       </c>
-      <c r="C36" s="97"/>
-      <c r="D36" s="84" t="s">
+      <c r="C36" s="84"/>
+      <c r="D36" s="85" t="s">
         <v>283</v>
       </c>
-      <c r="E36" s="85"/>
-      <c r="F36" s="86"/>
-      <c r="G36" s="77" t="s">
+      <c r="E36" s="86"/>
+      <c r="F36" s="87"/>
+      <c r="G36" s="89" t="s">
         <v>218</v>
       </c>
-      <c r="H36" s="76"/>
+      <c r="H36" s="88"/>
+    </row>
+    <row r="37" spans="1:8" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A37" s="11">
+        <v>4</v>
+      </c>
+      <c r="B37" s="84" t="s">
+        <v>298</v>
+      </c>
+      <c r="C37" s="84"/>
+      <c r="D37" s="85" t="s">
+        <v>299</v>
+      </c>
+      <c r="E37" s="86"/>
+      <c r="F37" s="87"/>
+      <c r="G37" s="89" t="s">
+        <v>218</v>
+      </c>
+      <c r="H37" s="88"/>
     </row>
   </sheetData>
-  <mergeCells count="150">
-    <mergeCell ref="K6:R6"/>
-    <mergeCell ref="K7:R7"/>
-    <mergeCell ref="K8:R8"/>
-    <mergeCell ref="K9:R9"/>
-    <mergeCell ref="K10:R10"/>
-    <mergeCell ref="K11:R11"/>
-    <mergeCell ref="K12:R12"/>
-    <mergeCell ref="K13:R13"/>
-    <mergeCell ref="K14:R14"/>
-    <mergeCell ref="K15:R15"/>
-    <mergeCell ref="K16:R16"/>
-    <mergeCell ref="K17:R17"/>
-    <mergeCell ref="K18:R18"/>
-    <mergeCell ref="K19:R19"/>
-    <mergeCell ref="K20:R20"/>
-    <mergeCell ref="K21:R21"/>
-    <mergeCell ref="K22:R22"/>
-    <mergeCell ref="K23:R23"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
+  <mergeCells count="153">
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="S16:T16"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="S28:T28"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="S10:T10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="K24:R24"/>
     <mergeCell ref="K25:R25"/>
     <mergeCell ref="K26:R26"/>
@@ -7835,74 +7867,80 @@
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="G12:H12"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
     <mergeCell ref="D11:F11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="S8:T8"/>
-    <mergeCell ref="S9:T9"/>
-    <mergeCell ref="S10:T10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="S14:T14"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="S16:T16"/>
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="S28:T28"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="S22:T22"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="K15:R15"/>
+    <mergeCell ref="K16:R16"/>
+    <mergeCell ref="K17:R17"/>
+    <mergeCell ref="K18:R18"/>
+    <mergeCell ref="K19:R19"/>
+    <mergeCell ref="K20:R20"/>
+    <mergeCell ref="K21:R21"/>
+    <mergeCell ref="K22:R22"/>
+    <mergeCell ref="K23:R23"/>
+    <mergeCell ref="K6:R6"/>
+    <mergeCell ref="K7:R7"/>
+    <mergeCell ref="K8:R8"/>
+    <mergeCell ref="K9:R9"/>
+    <mergeCell ref="K10:R10"/>
+    <mergeCell ref="K11:R11"/>
+    <mergeCell ref="K12:R12"/>
+    <mergeCell ref="K13:R13"/>
+    <mergeCell ref="K14:R14"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="S7:T7">
-    <cfRule type="colorScale" priority="2">
+  <phoneticPr fontId="19" type="noConversion"/>
+  <conditionalFormatting sqref="G34:H34">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7913,8 +7951,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G34:H34">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="S7:T7">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7929,7 +7967,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I7:J28" xr:uid="{EBCDB7CB-9B76-4496-A9FD-E13B8548471C}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S7:T28 G34:H36" xr:uid="{1261FD57-5C4E-4608-A621-9535D2C1ADDD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S7:T28 G34:H37" xr:uid="{1261FD57-5C4E-4608-A621-9535D2C1ADDD}">
       <formula1>"Sẵn sàng, Đang Render, Chưa có"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7971,38 +8009,38 @@
       </c>
     </row>
     <row r="24" spans="2:28" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P24" s="96" t="s">
+      <c r="P24" s="109" t="s">
         <v>241</v>
       </c>
-      <c r="Q24" s="58"/>
-      <c r="R24" s="58"/>
-      <c r="S24" s="58"/>
-      <c r="T24" s="58"/>
-      <c r="U24" s="58"/>
-      <c r="V24" s="58"/>
-      <c r="W24" s="58"/>
-      <c r="X24" s="58"/>
-      <c r="Y24" s="58"/>
-      <c r="Z24" s="58"/>
-      <c r="AA24" s="58"/>
-      <c r="AB24" s="58"/>
+      <c r="Q24" s="65"/>
+      <c r="R24" s="65"/>
+      <c r="S24" s="65"/>
+      <c r="T24" s="65"/>
+      <c r="U24" s="65"/>
+      <c r="V24" s="65"/>
+      <c r="W24" s="65"/>
+      <c r="X24" s="65"/>
+      <c r="Y24" s="65"/>
+      <c r="Z24" s="65"/>
+      <c r="AA24" s="65"/>
+      <c r="AB24" s="65"/>
     </row>
     <row r="26" spans="2:28" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P26" s="96" t="s">
+      <c r="P26" s="109" t="s">
         <v>240</v>
       </c>
-      <c r="Q26" s="58"/>
-      <c r="R26" s="58"/>
-      <c r="S26" s="58"/>
-      <c r="T26" s="58"/>
-      <c r="U26" s="58"/>
-      <c r="V26" s="58"/>
-      <c r="W26" s="58"/>
-      <c r="X26" s="58"/>
-      <c r="Y26" s="58"/>
-      <c r="Z26" s="58"/>
-      <c r="AA26" s="58"/>
-      <c r="AB26" s="58"/>
+      <c r="Q26" s="65"/>
+      <c r="R26" s="65"/>
+      <c r="S26" s="65"/>
+      <c r="T26" s="65"/>
+      <c r="U26" s="65"/>
+      <c r="V26" s="65"/>
+      <c r="W26" s="65"/>
+      <c r="X26" s="65"/>
+      <c r="Y26" s="65"/>
+      <c r="Z26" s="65"/>
+      <c r="AA26" s="65"/>
+      <c r="AB26" s="65"/>
     </row>
     <row r="27" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8032,562 +8070,562 @@
       <c r="A35" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="B35" s="58" t="s">
+      <c r="B35" s="65" t="s">
         <v>220</v>
       </c>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
-      <c r="L35" s="58"/>
-      <c r="M35" s="58"/>
-      <c r="N35" s="58"/>
-      <c r="O35" s="58"/>
-      <c r="P35" s="58"/>
-      <c r="Q35" s="58"/>
-      <c r="R35" s="58"/>
-      <c r="S35" s="58"/>
-      <c r="T35" s="58"/>
-      <c r="U35" s="58"/>
-      <c r="V35" s="58"/>
-      <c r="W35" s="58"/>
-      <c r="X35" s="58"/>
-      <c r="Y35" s="58"/>
-      <c r="Z35" s="58"/>
-      <c r="AA35" s="58"/>
-      <c r="AB35" s="58"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
+      <c r="I35" s="65"/>
+      <c r="J35" s="65"/>
+      <c r="K35" s="65"/>
+      <c r="L35" s="65"/>
+      <c r="M35" s="65"/>
+      <c r="N35" s="65"/>
+      <c r="O35" s="65"/>
+      <c r="P35" s="65"/>
+      <c r="Q35" s="65"/>
+      <c r="R35" s="65"/>
+      <c r="S35" s="65"/>
+      <c r="T35" s="65"/>
+      <c r="U35" s="65"/>
+      <c r="V35" s="65"/>
+      <c r="W35" s="65"/>
+      <c r="X35" s="65"/>
+      <c r="Y35" s="65"/>
+      <c r="Z35" s="65"/>
+      <c r="AA35" s="65"/>
+      <c r="AB35" s="65"/>
     </row>
     <row r="36" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="58" t="s">
+      <c r="B36" s="65" t="s">
         <v>221</v>
       </c>
-      <c r="C36" s="58"/>
-      <c r="D36" s="58"/>
-      <c r="E36" s="58"/>
-      <c r="F36" s="58"/>
-      <c r="G36" s="58"/>
-      <c r="H36" s="58"/>
-      <c r="I36" s="58"/>
-      <c r="J36" s="58"/>
-      <c r="K36" s="58"/>
-      <c r="L36" s="58"/>
-      <c r="M36" s="58"/>
-      <c r="N36" s="58"/>
-      <c r="O36" s="58"/>
-      <c r="P36" s="58"/>
-      <c r="Q36" s="58"/>
-      <c r="R36" s="58"/>
-      <c r="S36" s="58"/>
-      <c r="T36" s="58"/>
-      <c r="U36" s="58"/>
-      <c r="V36" s="58"/>
-      <c r="W36" s="58"/>
-      <c r="X36" s="58"/>
-      <c r="Y36" s="58"/>
-      <c r="Z36" s="58"/>
-      <c r="AA36" s="58"/>
-      <c r="AB36" s="58"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="65"/>
+      <c r="H36" s="65"/>
+      <c r="I36" s="65"/>
+      <c r="J36" s="65"/>
+      <c r="K36" s="65"/>
+      <c r="L36" s="65"/>
+      <c r="M36" s="65"/>
+      <c r="N36" s="65"/>
+      <c r="O36" s="65"/>
+      <c r="P36" s="65"/>
+      <c r="Q36" s="65"/>
+      <c r="R36" s="65"/>
+      <c r="S36" s="65"/>
+      <c r="T36" s="65"/>
+      <c r="U36" s="65"/>
+      <c r="V36" s="65"/>
+      <c r="W36" s="65"/>
+      <c r="X36" s="65"/>
+      <c r="Y36" s="65"/>
+      <c r="Z36" s="65"/>
+      <c r="AA36" s="65"/>
+      <c r="AB36" s="65"/>
     </row>
     <row r="37" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="58" t="s">
+      <c r="B37" s="65" t="s">
         <v>222</v>
       </c>
-      <c r="C37" s="58"/>
-      <c r="D37" s="58"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="58"/>
-      <c r="H37" s="58"/>
-      <c r="I37" s="58"/>
-      <c r="J37" s="58"/>
-      <c r="K37" s="58"/>
-      <c r="L37" s="58"/>
-      <c r="M37" s="58"/>
-      <c r="N37" s="58"/>
-      <c r="O37" s="58"/>
-      <c r="P37" s="58"/>
-      <c r="Q37" s="58"/>
-      <c r="R37" s="58"/>
-      <c r="S37" s="58"/>
-      <c r="T37" s="58"/>
-      <c r="U37" s="58"/>
-      <c r="V37" s="58"/>
-      <c r="W37" s="58"/>
-      <c r="X37" s="58"/>
-      <c r="Y37" s="58"/>
-      <c r="Z37" s="58"/>
-      <c r="AA37" s="58"/>
-      <c r="AB37" s="58"/>
+      <c r="C37" s="65"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="65"/>
+      <c r="J37" s="65"/>
+      <c r="K37" s="65"/>
+      <c r="L37" s="65"/>
+      <c r="M37" s="65"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="65"/>
+      <c r="P37" s="65"/>
+      <c r="Q37" s="65"/>
+      <c r="R37" s="65"/>
+      <c r="S37" s="65"/>
+      <c r="T37" s="65"/>
+      <c r="U37" s="65"/>
+      <c r="V37" s="65"/>
+      <c r="W37" s="65"/>
+      <c r="X37" s="65"/>
+      <c r="Y37" s="65"/>
+      <c r="Z37" s="65"/>
+      <c r="AA37" s="65"/>
+      <c r="AB37" s="65"/>
     </row>
     <row r="38" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="58" t="s">
+      <c r="B38" s="65" t="s">
         <v>223</v>
       </c>
-      <c r="C38" s="58"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="58"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="58"/>
-      <c r="K38" s="58"/>
-      <c r="L38" s="58"/>
-      <c r="M38" s="58"/>
-      <c r="N38" s="58"/>
-      <c r="O38" s="58"/>
-      <c r="P38" s="58"/>
-      <c r="Q38" s="58"/>
-      <c r="R38" s="58"/>
-      <c r="S38" s="58"/>
-      <c r="T38" s="58"/>
-      <c r="U38" s="58"/>
-      <c r="V38" s="58"/>
-      <c r="W38" s="58"/>
-      <c r="X38" s="58"/>
-      <c r="Y38" s="58"/>
-      <c r="Z38" s="58"/>
-      <c r="AA38" s="58"/>
-      <c r="AB38" s="58"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="65"/>
+      <c r="J38" s="65"/>
+      <c r="K38" s="65"/>
+      <c r="L38" s="65"/>
+      <c r="M38" s="65"/>
+      <c r="N38" s="65"/>
+      <c r="O38" s="65"/>
+      <c r="P38" s="65"/>
+      <c r="Q38" s="65"/>
+      <c r="R38" s="65"/>
+      <c r="S38" s="65"/>
+      <c r="T38" s="65"/>
+      <c r="U38" s="65"/>
+      <c r="V38" s="65"/>
+      <c r="W38" s="65"/>
+      <c r="X38" s="65"/>
+      <c r="Y38" s="65"/>
+      <c r="Z38" s="65"/>
+      <c r="AA38" s="65"/>
+      <c r="AB38" s="65"/>
     </row>
     <row r="39" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="58" t="s">
+      <c r="B39" s="65" t="s">
         <v>209</v>
       </c>
-      <c r="C39" s="58"/>
-      <c r="D39" s="58"/>
-      <c r="E39" s="58"/>
-      <c r="F39" s="58"/>
-      <c r="G39" s="58"/>
-      <c r="H39" s="58"/>
-      <c r="I39" s="58"/>
-      <c r="J39" s="58"/>
-      <c r="K39" s="58"/>
-      <c r="L39" s="58"/>
-      <c r="M39" s="58"/>
-      <c r="N39" s="58"/>
-      <c r="O39" s="58"/>
-      <c r="P39" s="58"/>
-      <c r="Q39" s="58"/>
-      <c r="R39" s="58"/>
-      <c r="S39" s="58"/>
-      <c r="T39" s="58"/>
-      <c r="U39" s="58"/>
-      <c r="V39" s="58"/>
-      <c r="W39" s="58"/>
-      <c r="X39" s="58"/>
-      <c r="Y39" s="58"/>
-      <c r="Z39" s="58"/>
-      <c r="AA39" s="58"/>
-      <c r="AB39" s="58"/>
+      <c r="C39" s="65"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="65"/>
+      <c r="F39" s="65"/>
+      <c r="G39" s="65"/>
+      <c r="H39" s="65"/>
+      <c r="I39" s="65"/>
+      <c r="J39" s="65"/>
+      <c r="K39" s="65"/>
+      <c r="L39" s="65"/>
+      <c r="M39" s="65"/>
+      <c r="N39" s="65"/>
+      <c r="O39" s="65"/>
+      <c r="P39" s="65"/>
+      <c r="Q39" s="65"/>
+      <c r="R39" s="65"/>
+      <c r="S39" s="65"/>
+      <c r="T39" s="65"/>
+      <c r="U39" s="65"/>
+      <c r="V39" s="65"/>
+      <c r="W39" s="65"/>
+      <c r="X39" s="65"/>
+      <c r="Y39" s="65"/>
+      <c r="Z39" s="65"/>
+      <c r="AA39" s="65"/>
+      <c r="AB39" s="65"/>
     </row>
     <row r="40" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="58" t="s">
+      <c r="B40" s="65" t="s">
         <v>224</v>
       </c>
-      <c r="C40" s="58"/>
-      <c r="D40" s="58"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="58"/>
-      <c r="I40" s="58"/>
-      <c r="J40" s="58"/>
-      <c r="K40" s="58"/>
-      <c r="L40" s="58"/>
-      <c r="M40" s="58"/>
-      <c r="N40" s="58"/>
-      <c r="O40" s="58"/>
-      <c r="P40" s="58"/>
-      <c r="Q40" s="58"/>
-      <c r="R40" s="58"/>
-      <c r="S40" s="58"/>
-      <c r="T40" s="58"/>
-      <c r="U40" s="58"/>
-      <c r="V40" s="58"/>
-      <c r="W40" s="58"/>
-      <c r="X40" s="58"/>
-      <c r="Y40" s="58"/>
-      <c r="Z40" s="58"/>
-      <c r="AA40" s="58"/>
-      <c r="AB40" s="58"/>
+      <c r="C40" s="65"/>
+      <c r="D40" s="65"/>
+      <c r="E40" s="65"/>
+      <c r="F40" s="65"/>
+      <c r="G40" s="65"/>
+      <c r="H40" s="65"/>
+      <c r="I40" s="65"/>
+      <c r="J40" s="65"/>
+      <c r="K40" s="65"/>
+      <c r="L40" s="65"/>
+      <c r="M40" s="65"/>
+      <c r="N40" s="65"/>
+      <c r="O40" s="65"/>
+      <c r="P40" s="65"/>
+      <c r="Q40" s="65"/>
+      <c r="R40" s="65"/>
+      <c r="S40" s="65"/>
+      <c r="T40" s="65"/>
+      <c r="U40" s="65"/>
+      <c r="V40" s="65"/>
+      <c r="W40" s="65"/>
+      <c r="X40" s="65"/>
+      <c r="Y40" s="65"/>
+      <c r="Z40" s="65"/>
+      <c r="AA40" s="65"/>
+      <c r="AB40" s="65"/>
     </row>
     <row r="41" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B41" s="58" t="s">
+      <c r="B41" s="65" t="s">
         <v>225</v>
       </c>
-      <c r="C41" s="58"/>
-      <c r="D41" s="58"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="58"/>
-      <c r="N41" s="58"/>
-      <c r="O41" s="58"/>
-      <c r="P41" s="58"/>
-      <c r="Q41" s="58"/>
-      <c r="R41" s="58"/>
-      <c r="S41" s="58"/>
-      <c r="T41" s="58"/>
-      <c r="U41" s="58"/>
-      <c r="V41" s="58"/>
-      <c r="W41" s="58"/>
-      <c r="X41" s="58"/>
-      <c r="Y41" s="58"/>
-      <c r="Z41" s="58"/>
-      <c r="AA41" s="58"/>
-      <c r="AB41" s="58"/>
+      <c r="C41" s="65"/>
+      <c r="D41" s="65"/>
+      <c r="E41" s="65"/>
+      <c r="F41" s="65"/>
+      <c r="G41" s="65"/>
+      <c r="H41" s="65"/>
+      <c r="I41" s="65"/>
+      <c r="J41" s="65"/>
+      <c r="K41" s="65"/>
+      <c r="L41" s="65"/>
+      <c r="M41" s="65"/>
+      <c r="N41" s="65"/>
+      <c r="O41" s="65"/>
+      <c r="P41" s="65"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="65"/>
+      <c r="S41" s="65"/>
+      <c r="T41" s="65"/>
+      <c r="U41" s="65"/>
+      <c r="V41" s="65"/>
+      <c r="W41" s="65"/>
+      <c r="X41" s="65"/>
+      <c r="Y41" s="65"/>
+      <c r="Z41" s="65"/>
+      <c r="AA41" s="65"/>
+      <c r="AB41" s="65"/>
     </row>
     <row r="42" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B42" s="58" t="s">
+      <c r="B42" s="65" t="s">
         <v>226</v>
       </c>
-      <c r="C42" s="58"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="58"/>
-      <c r="I42" s="58"/>
-      <c r="J42" s="58"/>
-      <c r="K42" s="58"/>
-      <c r="L42" s="58"/>
-      <c r="M42" s="58"/>
-      <c r="N42" s="58"/>
-      <c r="O42" s="58"/>
-      <c r="P42" s="58"/>
-      <c r="Q42" s="58"/>
-      <c r="R42" s="58"/>
-      <c r="S42" s="58"/>
-      <c r="T42" s="58"/>
-      <c r="U42" s="58"/>
-      <c r="V42" s="58"/>
-      <c r="W42" s="58"/>
-      <c r="X42" s="58"/>
-      <c r="Y42" s="58"/>
-      <c r="Z42" s="58"/>
-      <c r="AA42" s="58"/>
-      <c r="AB42" s="58"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="65"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="65"/>
+      <c r="K42" s="65"/>
+      <c r="L42" s="65"/>
+      <c r="M42" s="65"/>
+      <c r="N42" s="65"/>
+      <c r="O42" s="65"/>
+      <c r="P42" s="65"/>
+      <c r="Q42" s="65"/>
+      <c r="R42" s="65"/>
+      <c r="S42" s="65"/>
+      <c r="T42" s="65"/>
+      <c r="U42" s="65"/>
+      <c r="V42" s="65"/>
+      <c r="W42" s="65"/>
+      <c r="X42" s="65"/>
+      <c r="Y42" s="65"/>
+      <c r="Z42" s="65"/>
+      <c r="AA42" s="65"/>
+      <c r="AB42" s="65"/>
     </row>
     <row r="43" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B43" s="58" t="s">
+      <c r="B43" s="65" t="s">
         <v>227</v>
       </c>
-      <c r="C43" s="58"/>
-      <c r="D43" s="58"/>
-      <c r="E43" s="58"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="58"/>
-      <c r="I43" s="58"/>
-      <c r="J43" s="58"/>
-      <c r="K43" s="58"/>
-      <c r="L43" s="58"/>
-      <c r="M43" s="58"/>
-      <c r="N43" s="58"/>
-      <c r="O43" s="58"/>
-      <c r="P43" s="58"/>
-      <c r="Q43" s="58"/>
-      <c r="R43" s="58"/>
-      <c r="S43" s="58"/>
-      <c r="T43" s="58"/>
-      <c r="U43" s="58"/>
-      <c r="V43" s="58"/>
-      <c r="W43" s="58"/>
-      <c r="X43" s="58"/>
-      <c r="Y43" s="58"/>
-      <c r="Z43" s="58"/>
-      <c r="AA43" s="58"/>
-      <c r="AB43" s="58"/>
+      <c r="C43" s="65"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="65"/>
+      <c r="J43" s="65"/>
+      <c r="K43" s="65"/>
+      <c r="L43" s="65"/>
+      <c r="M43" s="65"/>
+      <c r="N43" s="65"/>
+      <c r="O43" s="65"/>
+      <c r="P43" s="65"/>
+      <c r="Q43" s="65"/>
+      <c r="R43" s="65"/>
+      <c r="S43" s="65"/>
+      <c r="T43" s="65"/>
+      <c r="U43" s="65"/>
+      <c r="V43" s="65"/>
+      <c r="W43" s="65"/>
+      <c r="X43" s="65"/>
+      <c r="Y43" s="65"/>
+      <c r="Z43" s="65"/>
+      <c r="AA43" s="65"/>
+      <c r="AB43" s="65"/>
     </row>
     <row r="44" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B44" s="58" t="s">
+      <c r="B44" s="65" t="s">
         <v>228</v>
       </c>
-      <c r="C44" s="58"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="58"/>
-      <c r="I44" s="58"/>
-      <c r="J44" s="58"/>
-      <c r="K44" s="58"/>
-      <c r="L44" s="58"/>
-      <c r="M44" s="58"/>
-      <c r="N44" s="58"/>
-      <c r="O44" s="58"/>
-      <c r="P44" s="58"/>
-      <c r="Q44" s="58"/>
-      <c r="R44" s="58"/>
-      <c r="S44" s="58"/>
-      <c r="T44" s="58"/>
-      <c r="U44" s="58"/>
-      <c r="V44" s="58"/>
-      <c r="W44" s="58"/>
-      <c r="X44" s="58"/>
-      <c r="Y44" s="58"/>
-      <c r="Z44" s="58"/>
-      <c r="AA44" s="58"/>
-      <c r="AB44" s="58"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="65"/>
+      <c r="F44" s="65"/>
+      <c r="G44" s="65"/>
+      <c r="H44" s="65"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="65"/>
+      <c r="K44" s="65"/>
+      <c r="L44" s="65"/>
+      <c r="M44" s="65"/>
+      <c r="N44" s="65"/>
+      <c r="O44" s="65"/>
+      <c r="P44" s="65"/>
+      <c r="Q44" s="65"/>
+      <c r="R44" s="65"/>
+      <c r="S44" s="65"/>
+      <c r="T44" s="65"/>
+      <c r="U44" s="65"/>
+      <c r="V44" s="65"/>
+      <c r="W44" s="65"/>
+      <c r="X44" s="65"/>
+      <c r="Y44" s="65"/>
+      <c r="Z44" s="65"/>
+      <c r="AA44" s="65"/>
+      <c r="AB44" s="65"/>
     </row>
     <row r="45" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B45" s="58" t="s">
+      <c r="B45" s="65" t="s">
         <v>229</v>
       </c>
-      <c r="C45" s="58"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="58"/>
-      <c r="I45" s="58"/>
-      <c r="J45" s="58"/>
-      <c r="K45" s="58"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="58"/>
-      <c r="N45" s="58"/>
-      <c r="O45" s="58"/>
-      <c r="P45" s="58"/>
-      <c r="Q45" s="58"/>
-      <c r="R45" s="58"/>
-      <c r="S45" s="58"/>
-      <c r="T45" s="58"/>
-      <c r="U45" s="58"/>
-      <c r="V45" s="58"/>
-      <c r="W45" s="58"/>
-      <c r="X45" s="58"/>
-      <c r="Y45" s="58"/>
-      <c r="Z45" s="58"/>
-      <c r="AA45" s="58"/>
-      <c r="AB45" s="58"/>
+      <c r="C45" s="65"/>
+      <c r="D45" s="65"/>
+      <c r="E45" s="65"/>
+      <c r="F45" s="65"/>
+      <c r="G45" s="65"/>
+      <c r="H45" s="65"/>
+      <c r="I45" s="65"/>
+      <c r="J45" s="65"/>
+      <c r="K45" s="65"/>
+      <c r="L45" s="65"/>
+      <c r="M45" s="65"/>
+      <c r="N45" s="65"/>
+      <c r="O45" s="65"/>
+      <c r="P45" s="65"/>
+      <c r="Q45" s="65"/>
+      <c r="R45" s="65"/>
+      <c r="S45" s="65"/>
+      <c r="T45" s="65"/>
+      <c r="U45" s="65"/>
+      <c r="V45" s="65"/>
+      <c r="W45" s="65"/>
+      <c r="X45" s="65"/>
+      <c r="Y45" s="65"/>
+      <c r="Z45" s="65"/>
+      <c r="AA45" s="65"/>
+      <c r="AB45" s="65"/>
     </row>
     <row r="46" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B46" s="58" t="s">
+      <c r="B46" s="65" t="s">
         <v>230</v>
       </c>
-      <c r="C46" s="58"/>
-      <c r="D46" s="58"/>
-      <c r="E46" s="58"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="58"/>
-      <c r="H46" s="58"/>
-      <c r="I46" s="58"/>
-      <c r="J46" s="58"/>
-      <c r="K46" s="58"/>
-      <c r="L46" s="58"/>
-      <c r="M46" s="58"/>
-      <c r="N46" s="58"/>
-      <c r="O46" s="58"/>
-      <c r="P46" s="58"/>
-      <c r="Q46" s="58"/>
-      <c r="R46" s="58"/>
-      <c r="S46" s="58"/>
-      <c r="T46" s="58"/>
-      <c r="U46" s="58"/>
-      <c r="V46" s="58"/>
-      <c r="W46" s="58"/>
-      <c r="X46" s="58"/>
-      <c r="Y46" s="58"/>
-      <c r="Z46" s="58"/>
-      <c r="AA46" s="58"/>
-      <c r="AB46" s="58"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="65"/>
+      <c r="E46" s="65"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="65"/>
+      <c r="H46" s="65"/>
+      <c r="I46" s="65"/>
+      <c r="J46" s="65"/>
+      <c r="K46" s="65"/>
+      <c r="L46" s="65"/>
+      <c r="M46" s="65"/>
+      <c r="N46" s="65"/>
+      <c r="O46" s="65"/>
+      <c r="P46" s="65"/>
+      <c r="Q46" s="65"/>
+      <c r="R46" s="65"/>
+      <c r="S46" s="65"/>
+      <c r="T46" s="65"/>
+      <c r="U46" s="65"/>
+      <c r="V46" s="65"/>
+      <c r="W46" s="65"/>
+      <c r="X46" s="65"/>
+      <c r="Y46" s="65"/>
+      <c r="Z46" s="65"/>
+      <c r="AA46" s="65"/>
+      <c r="AB46" s="65"/>
     </row>
     <row r="47" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B47" s="58" t="s">
+      <c r="B47" s="65" t="s">
         <v>231</v>
       </c>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="58"/>
-      <c r="J47" s="58"/>
-      <c r="K47" s="58"/>
-      <c r="L47" s="58"/>
-      <c r="M47" s="58"/>
-      <c r="N47" s="58"/>
-      <c r="O47" s="58"/>
-      <c r="P47" s="58"/>
-      <c r="Q47" s="58"/>
-      <c r="R47" s="58"/>
-      <c r="S47" s="58"/>
-      <c r="T47" s="58"/>
-      <c r="U47" s="58"/>
-      <c r="V47" s="58"/>
-      <c r="W47" s="58"/>
-      <c r="X47" s="58"/>
-      <c r="Y47" s="58"/>
-      <c r="Z47" s="58"/>
-      <c r="AA47" s="58"/>
-      <c r="AB47" s="58"/>
+      <c r="C47" s="65"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65"/>
+      <c r="I47" s="65"/>
+      <c r="J47" s="65"/>
+      <c r="K47" s="65"/>
+      <c r="L47" s="65"/>
+      <c r="M47" s="65"/>
+      <c r="N47" s="65"/>
+      <c r="O47" s="65"/>
+      <c r="P47" s="65"/>
+      <c r="Q47" s="65"/>
+      <c r="R47" s="65"/>
+      <c r="S47" s="65"/>
+      <c r="T47" s="65"/>
+      <c r="U47" s="65"/>
+      <c r="V47" s="65"/>
+      <c r="W47" s="65"/>
+      <c r="X47" s="65"/>
+      <c r="Y47" s="65"/>
+      <c r="Z47" s="65"/>
+      <c r="AA47" s="65"/>
+      <c r="AB47" s="65"/>
     </row>
     <row r="48" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B48" s="58" t="s">
+      <c r="B48" s="65" t="s">
         <v>232</v>
       </c>
-      <c r="C48" s="58"/>
-      <c r="D48" s="58"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="58"/>
-      <c r="H48" s="58"/>
-      <c r="I48" s="58"/>
-      <c r="J48" s="58"/>
-      <c r="K48" s="58"/>
-      <c r="L48" s="58"/>
-      <c r="M48" s="58"/>
-      <c r="N48" s="58"/>
-      <c r="O48" s="58"/>
-      <c r="P48" s="58"/>
-      <c r="Q48" s="58"/>
-      <c r="R48" s="58"/>
-      <c r="S48" s="58"/>
-      <c r="T48" s="58"/>
-      <c r="U48" s="58"/>
-      <c r="V48" s="58"/>
-      <c r="W48" s="58"/>
-      <c r="X48" s="58"/>
-      <c r="Y48" s="58"/>
-      <c r="Z48" s="58"/>
-      <c r="AA48" s="58"/>
-      <c r="AB48" s="58"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="65"/>
+      <c r="F48" s="65"/>
+      <c r="G48" s="65"/>
+      <c r="H48" s="65"/>
+      <c r="I48" s="65"/>
+      <c r="J48" s="65"/>
+      <c r="K48" s="65"/>
+      <c r="L48" s="65"/>
+      <c r="M48" s="65"/>
+      <c r="N48" s="65"/>
+      <c r="O48" s="65"/>
+      <c r="P48" s="65"/>
+      <c r="Q48" s="65"/>
+      <c r="R48" s="65"/>
+      <c r="S48" s="65"/>
+      <c r="T48" s="65"/>
+      <c r="U48" s="65"/>
+      <c r="V48" s="65"/>
+      <c r="W48" s="65"/>
+      <c r="X48" s="65"/>
+      <c r="Y48" s="65"/>
+      <c r="Z48" s="65"/>
+      <c r="AA48" s="65"/>
+      <c r="AB48" s="65"/>
     </row>
     <row r="49" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B49" s="58" t="s">
+      <c r="B49" s="65" t="s">
         <v>233</v>
       </c>
-      <c r="C49" s="58"/>
-      <c r="D49" s="58"/>
-      <c r="E49" s="58"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="58"/>
-      <c r="H49" s="58"/>
-      <c r="I49" s="58"/>
-      <c r="J49" s="58"/>
-      <c r="K49" s="58"/>
-      <c r="L49" s="58"/>
-      <c r="M49" s="58"/>
-      <c r="N49" s="58"/>
-      <c r="O49" s="58"/>
-      <c r="P49" s="58"/>
-      <c r="Q49" s="58"/>
-      <c r="R49" s="58"/>
-      <c r="S49" s="58"/>
-      <c r="T49" s="58"/>
-      <c r="U49" s="58"/>
-      <c r="V49" s="58"/>
-      <c r="W49" s="58"/>
-      <c r="X49" s="58"/>
-      <c r="Y49" s="58"/>
-      <c r="Z49" s="58"/>
-      <c r="AA49" s="58"/>
-      <c r="AB49" s="58"/>
+      <c r="C49" s="65"/>
+      <c r="D49" s="65"/>
+      <c r="E49" s="65"/>
+      <c r="F49" s="65"/>
+      <c r="G49" s="65"/>
+      <c r="H49" s="65"/>
+      <c r="I49" s="65"/>
+      <c r="J49" s="65"/>
+      <c r="K49" s="65"/>
+      <c r="L49" s="65"/>
+      <c r="M49" s="65"/>
+      <c r="N49" s="65"/>
+      <c r="O49" s="65"/>
+      <c r="P49" s="65"/>
+      <c r="Q49" s="65"/>
+      <c r="R49" s="65"/>
+      <c r="S49" s="65"/>
+      <c r="T49" s="65"/>
+      <c r="U49" s="65"/>
+      <c r="V49" s="65"/>
+      <c r="W49" s="65"/>
+      <c r="X49" s="65"/>
+      <c r="Y49" s="65"/>
+      <c r="Z49" s="65"/>
+      <c r="AA49" s="65"/>
+      <c r="AB49" s="65"/>
     </row>
     <row r="50" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B50" s="58" t="s">
+      <c r="B50" s="65" t="s">
         <v>234</v>
       </c>
-      <c r="C50" s="58"/>
-      <c r="D50" s="58"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="58"/>
-      <c r="H50" s="58"/>
-      <c r="I50" s="58"/>
-      <c r="J50" s="58"/>
-      <c r="K50" s="58"/>
-      <c r="L50" s="58"/>
-      <c r="M50" s="58"/>
-      <c r="N50" s="58"/>
-      <c r="O50" s="58"/>
-      <c r="P50" s="58"/>
-      <c r="Q50" s="58"/>
-      <c r="R50" s="58"/>
-      <c r="S50" s="58"/>
-      <c r="T50" s="58"/>
-      <c r="U50" s="58"/>
-      <c r="V50" s="58"/>
-      <c r="W50" s="58"/>
-      <c r="X50" s="58"/>
-      <c r="Y50" s="58"/>
-      <c r="Z50" s="58"/>
-      <c r="AA50" s="58"/>
-      <c r="AB50" s="58"/>
+      <c r="C50" s="65"/>
+      <c r="D50" s="65"/>
+      <c r="E50" s="65"/>
+      <c r="F50" s="65"/>
+      <c r="G50" s="65"/>
+      <c r="H50" s="65"/>
+      <c r="I50" s="65"/>
+      <c r="J50" s="65"/>
+      <c r="K50" s="65"/>
+      <c r="L50" s="65"/>
+      <c r="M50" s="65"/>
+      <c r="N50" s="65"/>
+      <c r="O50" s="65"/>
+      <c r="P50" s="65"/>
+      <c r="Q50" s="65"/>
+      <c r="R50" s="65"/>
+      <c r="S50" s="65"/>
+      <c r="T50" s="65"/>
+      <c r="U50" s="65"/>
+      <c r="V50" s="65"/>
+      <c r="W50" s="65"/>
+      <c r="X50" s="65"/>
+      <c r="Y50" s="65"/>
+      <c r="Z50" s="65"/>
+      <c r="AA50" s="65"/>
+      <c r="AB50" s="65"/>
     </row>
     <row r="51" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B51" s="58" t="s">
+      <c r="B51" s="65" t="s">
         <v>235</v>
       </c>
-      <c r="C51" s="58"/>
-      <c r="D51" s="58"/>
-      <c r="E51" s="58"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="58"/>
-      <c r="H51" s="58"/>
-      <c r="I51" s="58"/>
-      <c r="J51" s="58"/>
-      <c r="K51" s="58"/>
-      <c r="L51" s="58"/>
-      <c r="M51" s="58"/>
-      <c r="N51" s="58"/>
-      <c r="O51" s="58"/>
-      <c r="P51" s="58"/>
-      <c r="Q51" s="58"/>
-      <c r="R51" s="58"/>
-      <c r="S51" s="58"/>
-      <c r="T51" s="58"/>
-      <c r="U51" s="58"/>
-      <c r="V51" s="58"/>
-      <c r="W51" s="58"/>
-      <c r="X51" s="58"/>
-      <c r="Y51" s="58"/>
-      <c r="Z51" s="58"/>
-      <c r="AA51" s="58"/>
-      <c r="AB51" s="58"/>
+      <c r="C51" s="65"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="65"/>
+      <c r="K51" s="65"/>
+      <c r="L51" s="65"/>
+      <c r="M51" s="65"/>
+      <c r="N51" s="65"/>
+      <c r="O51" s="65"/>
+      <c r="P51" s="65"/>
+      <c r="Q51" s="65"/>
+      <c r="R51" s="65"/>
+      <c r="S51" s="65"/>
+      <c r="T51" s="65"/>
+      <c r="U51" s="65"/>
+      <c r="V51" s="65"/>
+      <c r="W51" s="65"/>
+      <c r="X51" s="65"/>
+      <c r="Y51" s="65"/>
+      <c r="Z51" s="65"/>
+      <c r="AA51" s="65"/>
+      <c r="AB51" s="65"/>
     </row>
     <row r="52" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B52" s="58" t="s">
+      <c r="B52" s="65" t="s">
         <v>236</v>
       </c>
-      <c r="C52" s="58"/>
-      <c r="D52" s="58"/>
-      <c r="E52" s="58"/>
-      <c r="F52" s="58"/>
-      <c r="G52" s="58"/>
-      <c r="H52" s="58"/>
-      <c r="I52" s="58"/>
-      <c r="J52" s="58"/>
-      <c r="K52" s="58"/>
-      <c r="L52" s="58"/>
-      <c r="M52" s="58"/>
-      <c r="N52" s="58"/>
-      <c r="O52" s="58"/>
-      <c r="P52" s="58"/>
-      <c r="Q52" s="58"/>
-      <c r="R52" s="58"/>
-      <c r="S52" s="58"/>
-      <c r="T52" s="58"/>
-      <c r="U52" s="58"/>
-      <c r="V52" s="58"/>
-      <c r="W52" s="58"/>
-      <c r="X52" s="58"/>
-      <c r="Y52" s="58"/>
-      <c r="Z52" s="58"/>
-      <c r="AA52" s="58"/>
-      <c r="AB52" s="58"/>
+      <c r="C52" s="65"/>
+      <c r="D52" s="65"/>
+      <c r="E52" s="65"/>
+      <c r="F52" s="65"/>
+      <c r="G52" s="65"/>
+      <c r="H52" s="65"/>
+      <c r="I52" s="65"/>
+      <c r="J52" s="65"/>
+      <c r="K52" s="65"/>
+      <c r="L52" s="65"/>
+      <c r="M52" s="65"/>
+      <c r="N52" s="65"/>
+      <c r="O52" s="65"/>
+      <c r="P52" s="65"/>
+      <c r="Q52" s="65"/>
+      <c r="R52" s="65"/>
+      <c r="S52" s="65"/>
+      <c r="T52" s="65"/>
+      <c r="U52" s="65"/>
+      <c r="V52" s="65"/>
+      <c r="W52" s="65"/>
+      <c r="X52" s="65"/>
+      <c r="Y52" s="65"/>
+      <c r="Z52" s="65"/>
+      <c r="AA52" s="65"/>
+      <c r="AB52" s="65"/>
     </row>
     <row r="54" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B54" s="8" t="s">
@@ -8606,323 +8644,329 @@
       <c r="A57" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="B57" s="58" t="s">
+      <c r="B57" s="65" t="s">
         <v>237</v>
       </c>
-      <c r="C57" s="58"/>
-      <c r="D57" s="58"/>
-      <c r="E57" s="58"/>
-      <c r="F57" s="58"/>
-      <c r="G57" s="58"/>
-      <c r="H57" s="58"/>
-      <c r="I57" s="58"/>
-      <c r="J57" s="58"/>
-      <c r="K57" s="58"/>
-      <c r="L57" s="58"/>
-      <c r="M57" s="58"/>
-      <c r="N57" s="58"/>
-      <c r="O57" s="58"/>
-      <c r="P57" s="58"/>
-      <c r="Q57" s="58"/>
-      <c r="R57" s="58"/>
-      <c r="S57" s="58"/>
-      <c r="T57" s="58"/>
-      <c r="U57" s="58"/>
-      <c r="V57" s="58"/>
-      <c r="W57" s="58"/>
-      <c r="X57" s="58"/>
-      <c r="Y57" s="58"/>
-      <c r="Z57" s="58"/>
-      <c r="AA57" s="58"/>
-      <c r="AB57" s="58"/>
+      <c r="C57" s="65"/>
+      <c r="D57" s="65"/>
+      <c r="E57" s="65"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
+      <c r="H57" s="65"/>
+      <c r="I57" s="65"/>
+      <c r="J57" s="65"/>
+      <c r="K57" s="65"/>
+      <c r="L57" s="65"/>
+      <c r="M57" s="65"/>
+      <c r="N57" s="65"/>
+      <c r="O57" s="65"/>
+      <c r="P57" s="65"/>
+      <c r="Q57" s="65"/>
+      <c r="R57" s="65"/>
+      <c r="S57" s="65"/>
+      <c r="T57" s="65"/>
+      <c r="U57" s="65"/>
+      <c r="V57" s="65"/>
+      <c r="W57" s="65"/>
+      <c r="X57" s="65"/>
+      <c r="Y57" s="65"/>
+      <c r="Z57" s="65"/>
+      <c r="AA57" s="65"/>
+      <c r="AB57" s="65"/>
     </row>
     <row r="58" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B58" s="58" t="s">
+      <c r="B58" s="65" t="s">
         <v>226</v>
       </c>
-      <c r="C58" s="58"/>
-      <c r="D58" s="58"/>
-      <c r="E58" s="58"/>
-      <c r="F58" s="58"/>
-      <c r="G58" s="58"/>
-      <c r="H58" s="58"/>
-      <c r="I58" s="58"/>
-      <c r="J58" s="58"/>
-      <c r="K58" s="58"/>
-      <c r="L58" s="58"/>
-      <c r="M58" s="58"/>
-      <c r="N58" s="58"/>
-      <c r="O58" s="58"/>
-      <c r="P58" s="58"/>
-      <c r="Q58" s="58"/>
-      <c r="R58" s="58"/>
-      <c r="S58" s="58"/>
-      <c r="T58" s="58"/>
-      <c r="U58" s="58"/>
-      <c r="V58" s="58"/>
-      <c r="W58" s="58"/>
-      <c r="X58" s="58"/>
-      <c r="Y58" s="58"/>
-      <c r="Z58" s="58"/>
-      <c r="AA58" s="58"/>
-      <c r="AB58" s="58"/>
+      <c r="C58" s="65"/>
+      <c r="D58" s="65"/>
+      <c r="E58" s="65"/>
+      <c r="F58" s="65"/>
+      <c r="G58" s="65"/>
+      <c r="H58" s="65"/>
+      <c r="I58" s="65"/>
+      <c r="J58" s="65"/>
+      <c r="K58" s="65"/>
+      <c r="L58" s="65"/>
+      <c r="M58" s="65"/>
+      <c r="N58" s="65"/>
+      <c r="O58" s="65"/>
+      <c r="P58" s="65"/>
+      <c r="Q58" s="65"/>
+      <c r="R58" s="65"/>
+      <c r="S58" s="65"/>
+      <c r="T58" s="65"/>
+      <c r="U58" s="65"/>
+      <c r="V58" s="65"/>
+      <c r="W58" s="65"/>
+      <c r="X58" s="65"/>
+      <c r="Y58" s="65"/>
+      <c r="Z58" s="65"/>
+      <c r="AA58" s="65"/>
+      <c r="AB58" s="65"/>
     </row>
     <row r="59" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B59" s="58" t="s">
+      <c r="B59" s="65" t="s">
         <v>227</v>
       </c>
-      <c r="C59" s="58"/>
-      <c r="D59" s="58"/>
-      <c r="E59" s="58"/>
-      <c r="F59" s="58"/>
-      <c r="G59" s="58"/>
-      <c r="H59" s="58"/>
-      <c r="I59" s="58"/>
-      <c r="J59" s="58"/>
-      <c r="K59" s="58"/>
-      <c r="L59" s="58"/>
-      <c r="M59" s="58"/>
-      <c r="N59" s="58"/>
-      <c r="O59" s="58"/>
-      <c r="P59" s="58"/>
-      <c r="Q59" s="58"/>
-      <c r="R59" s="58"/>
-      <c r="S59" s="58"/>
-      <c r="T59" s="58"/>
-      <c r="U59" s="58"/>
-      <c r="V59" s="58"/>
-      <c r="W59" s="58"/>
-      <c r="X59" s="58"/>
-      <c r="Y59" s="58"/>
-      <c r="Z59" s="58"/>
-      <c r="AA59" s="58"/>
-      <c r="AB59" s="58"/>
+      <c r="C59" s="65"/>
+      <c r="D59" s="65"/>
+      <c r="E59" s="65"/>
+      <c r="F59" s="65"/>
+      <c r="G59" s="65"/>
+      <c r="H59" s="65"/>
+      <c r="I59" s="65"/>
+      <c r="J59" s="65"/>
+      <c r="K59" s="65"/>
+      <c r="L59" s="65"/>
+      <c r="M59" s="65"/>
+      <c r="N59" s="65"/>
+      <c r="O59" s="65"/>
+      <c r="P59" s="65"/>
+      <c r="Q59" s="65"/>
+      <c r="R59" s="65"/>
+      <c r="S59" s="65"/>
+      <c r="T59" s="65"/>
+      <c r="U59" s="65"/>
+      <c r="V59" s="65"/>
+      <c r="W59" s="65"/>
+      <c r="X59" s="65"/>
+      <c r="Y59" s="65"/>
+      <c r="Z59" s="65"/>
+      <c r="AA59" s="65"/>
+      <c r="AB59" s="65"/>
     </row>
     <row r="60" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B60" s="58" t="s">
+      <c r="B60" s="65" t="s">
         <v>228</v>
       </c>
-      <c r="C60" s="58"/>
-      <c r="D60" s="58"/>
-      <c r="E60" s="58"/>
-      <c r="F60" s="58"/>
-      <c r="G60" s="58"/>
-      <c r="H60" s="58"/>
-      <c r="I60" s="58"/>
-      <c r="J60" s="58"/>
-      <c r="K60" s="58"/>
-      <c r="L60" s="58"/>
-      <c r="M60" s="58"/>
-      <c r="N60" s="58"/>
-      <c r="O60" s="58"/>
-      <c r="P60" s="58"/>
-      <c r="Q60" s="58"/>
-      <c r="R60" s="58"/>
-      <c r="S60" s="58"/>
-      <c r="T60" s="58"/>
-      <c r="U60" s="58"/>
-      <c r="V60" s="58"/>
-      <c r="W60" s="58"/>
-      <c r="X60" s="58"/>
-      <c r="Y60" s="58"/>
-      <c r="Z60" s="58"/>
-      <c r="AA60" s="58"/>
-      <c r="AB60" s="58"/>
+      <c r="C60" s="65"/>
+      <c r="D60" s="65"/>
+      <c r="E60" s="65"/>
+      <c r="F60" s="65"/>
+      <c r="G60" s="65"/>
+      <c r="H60" s="65"/>
+      <c r="I60" s="65"/>
+      <c r="J60" s="65"/>
+      <c r="K60" s="65"/>
+      <c r="L60" s="65"/>
+      <c r="M60" s="65"/>
+      <c r="N60" s="65"/>
+      <c r="O60" s="65"/>
+      <c r="P60" s="65"/>
+      <c r="Q60" s="65"/>
+      <c r="R60" s="65"/>
+      <c r="S60" s="65"/>
+      <c r="T60" s="65"/>
+      <c r="U60" s="65"/>
+      <c r="V60" s="65"/>
+      <c r="W60" s="65"/>
+      <c r="X60" s="65"/>
+      <c r="Y60" s="65"/>
+      <c r="Z60" s="65"/>
+      <c r="AA60" s="65"/>
+      <c r="AB60" s="65"/>
     </row>
     <row r="61" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B61" s="58" t="s">
+      <c r="B61" s="65" t="s">
         <v>229</v>
       </c>
-      <c r="C61" s="58"/>
-      <c r="D61" s="58"/>
-      <c r="E61" s="58"/>
-      <c r="F61" s="58"/>
-      <c r="G61" s="58"/>
-      <c r="H61" s="58"/>
-      <c r="I61" s="58"/>
-      <c r="J61" s="58"/>
-      <c r="K61" s="58"/>
-      <c r="L61" s="58"/>
-      <c r="M61" s="58"/>
-      <c r="N61" s="58"/>
-      <c r="O61" s="58"/>
-      <c r="P61" s="58"/>
-      <c r="Q61" s="58"/>
-      <c r="R61" s="58"/>
-      <c r="S61" s="58"/>
-      <c r="T61" s="58"/>
-      <c r="U61" s="58"/>
-      <c r="V61" s="58"/>
-      <c r="W61" s="58"/>
-      <c r="X61" s="58"/>
-      <c r="Y61" s="58"/>
-      <c r="Z61" s="58"/>
-      <c r="AA61" s="58"/>
-      <c r="AB61" s="58"/>
+      <c r="C61" s="65"/>
+      <c r="D61" s="65"/>
+      <c r="E61" s="65"/>
+      <c r="F61" s="65"/>
+      <c r="G61" s="65"/>
+      <c r="H61" s="65"/>
+      <c r="I61" s="65"/>
+      <c r="J61" s="65"/>
+      <c r="K61" s="65"/>
+      <c r="L61" s="65"/>
+      <c r="M61" s="65"/>
+      <c r="N61" s="65"/>
+      <c r="O61" s="65"/>
+      <c r="P61" s="65"/>
+      <c r="Q61" s="65"/>
+      <c r="R61" s="65"/>
+      <c r="S61" s="65"/>
+      <c r="T61" s="65"/>
+      <c r="U61" s="65"/>
+      <c r="V61" s="65"/>
+      <c r="W61" s="65"/>
+      <c r="X61" s="65"/>
+      <c r="Y61" s="65"/>
+      <c r="Z61" s="65"/>
+      <c r="AA61" s="65"/>
+      <c r="AB61" s="65"/>
     </row>
     <row r="62" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B62" s="58" t="s">
+      <c r="B62" s="65" t="s">
         <v>230</v>
       </c>
-      <c r="C62" s="58"/>
-      <c r="D62" s="58"/>
-      <c r="E62" s="58"/>
-      <c r="F62" s="58"/>
-      <c r="G62" s="58"/>
-      <c r="H62" s="58"/>
-      <c r="I62" s="58"/>
-      <c r="J62" s="58"/>
-      <c r="K62" s="58"/>
-      <c r="L62" s="58"/>
-      <c r="M62" s="58"/>
-      <c r="N62" s="58"/>
-      <c r="O62" s="58"/>
-      <c r="P62" s="58"/>
-      <c r="Q62" s="58"/>
-      <c r="R62" s="58"/>
-      <c r="S62" s="58"/>
-      <c r="T62" s="58"/>
-      <c r="U62" s="58"/>
-      <c r="V62" s="58"/>
-      <c r="W62" s="58"/>
-      <c r="X62" s="58"/>
-      <c r="Y62" s="58"/>
-      <c r="Z62" s="58"/>
-      <c r="AA62" s="58"/>
-      <c r="AB62" s="58"/>
+      <c r="C62" s="65"/>
+      <c r="D62" s="65"/>
+      <c r="E62" s="65"/>
+      <c r="F62" s="65"/>
+      <c r="G62" s="65"/>
+      <c r="H62" s="65"/>
+      <c r="I62" s="65"/>
+      <c r="J62" s="65"/>
+      <c r="K62" s="65"/>
+      <c r="L62" s="65"/>
+      <c r="M62" s="65"/>
+      <c r="N62" s="65"/>
+      <c r="O62" s="65"/>
+      <c r="P62" s="65"/>
+      <c r="Q62" s="65"/>
+      <c r="R62" s="65"/>
+      <c r="S62" s="65"/>
+      <c r="T62" s="65"/>
+      <c r="U62" s="65"/>
+      <c r="V62" s="65"/>
+      <c r="W62" s="65"/>
+      <c r="X62" s="65"/>
+      <c r="Y62" s="65"/>
+      <c r="Z62" s="65"/>
+      <c r="AA62" s="65"/>
+      <c r="AB62" s="65"/>
     </row>
     <row r="63" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B63" s="58" t="s">
+      <c r="B63" s="65" t="s">
         <v>231</v>
       </c>
-      <c r="C63" s="58"/>
-      <c r="D63" s="58"/>
-      <c r="E63" s="58"/>
-      <c r="F63" s="58"/>
-      <c r="G63" s="58"/>
-      <c r="H63" s="58"/>
-      <c r="I63" s="58"/>
-      <c r="J63" s="58"/>
-      <c r="K63" s="58"/>
-      <c r="L63" s="58"/>
-      <c r="M63" s="58"/>
-      <c r="N63" s="58"/>
-      <c r="O63" s="58"/>
-      <c r="P63" s="58"/>
-      <c r="Q63" s="58"/>
-      <c r="R63" s="58"/>
-      <c r="S63" s="58"/>
-      <c r="T63" s="58"/>
-      <c r="U63" s="58"/>
-      <c r="V63" s="58"/>
-      <c r="W63" s="58"/>
-      <c r="X63" s="58"/>
-      <c r="Y63" s="58"/>
-      <c r="Z63" s="58"/>
-      <c r="AA63" s="58"/>
-      <c r="AB63" s="58"/>
+      <c r="C63" s="65"/>
+      <c r="D63" s="65"/>
+      <c r="E63" s="65"/>
+      <c r="F63" s="65"/>
+      <c r="G63" s="65"/>
+      <c r="H63" s="65"/>
+      <c r="I63" s="65"/>
+      <c r="J63" s="65"/>
+      <c r="K63" s="65"/>
+      <c r="L63" s="65"/>
+      <c r="M63" s="65"/>
+      <c r="N63" s="65"/>
+      <c r="O63" s="65"/>
+      <c r="P63" s="65"/>
+      <c r="Q63" s="65"/>
+      <c r="R63" s="65"/>
+      <c r="S63" s="65"/>
+      <c r="T63" s="65"/>
+      <c r="U63" s="65"/>
+      <c r="V63" s="65"/>
+      <c r="W63" s="65"/>
+      <c r="X63" s="65"/>
+      <c r="Y63" s="65"/>
+      <c r="Z63" s="65"/>
+      <c r="AA63" s="65"/>
+      <c r="AB63" s="65"/>
     </row>
     <row r="64" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B64" s="58" t="s">
+      <c r="B64" s="65" t="s">
         <v>232</v>
       </c>
-      <c r="C64" s="58"/>
-      <c r="D64" s="58"/>
-      <c r="E64" s="58"/>
-      <c r="F64" s="58"/>
-      <c r="G64" s="58"/>
-      <c r="H64" s="58"/>
-      <c r="I64" s="58"/>
-      <c r="J64" s="58"/>
-      <c r="K64" s="58"/>
-      <c r="L64" s="58"/>
-      <c r="M64" s="58"/>
-      <c r="N64" s="58"/>
-      <c r="O64" s="58"/>
-      <c r="P64" s="58"/>
-      <c r="Q64" s="58"/>
-      <c r="R64" s="58"/>
-      <c r="S64" s="58"/>
-      <c r="T64" s="58"/>
-      <c r="U64" s="58"/>
-      <c r="V64" s="58"/>
-      <c r="W64" s="58"/>
-      <c r="X64" s="58"/>
-      <c r="Y64" s="58"/>
-      <c r="Z64" s="58"/>
-      <c r="AA64" s="58"/>
-      <c r="AB64" s="58"/>
+      <c r="C64" s="65"/>
+      <c r="D64" s="65"/>
+      <c r="E64" s="65"/>
+      <c r="F64" s="65"/>
+      <c r="G64" s="65"/>
+      <c r="H64" s="65"/>
+      <c r="I64" s="65"/>
+      <c r="J64" s="65"/>
+      <c r="K64" s="65"/>
+      <c r="L64" s="65"/>
+      <c r="M64" s="65"/>
+      <c r="N64" s="65"/>
+      <c r="O64" s="65"/>
+      <c r="P64" s="65"/>
+      <c r="Q64" s="65"/>
+      <c r="R64" s="65"/>
+      <c r="S64" s="65"/>
+      <c r="T64" s="65"/>
+      <c r="U64" s="65"/>
+      <c r="V64" s="65"/>
+      <c r="W64" s="65"/>
+      <c r="X64" s="65"/>
+      <c r="Y64" s="65"/>
+      <c r="Z64" s="65"/>
+      <c r="AA64" s="65"/>
+      <c r="AB64" s="65"/>
     </row>
     <row r="65" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B65" s="58" t="s">
+      <c r="B65" s="65" t="s">
         <v>233</v>
       </c>
-      <c r="C65" s="58"/>
-      <c r="D65" s="58"/>
-      <c r="E65" s="58"/>
-      <c r="F65" s="58"/>
-      <c r="G65" s="58"/>
-      <c r="H65" s="58"/>
-      <c r="I65" s="58"/>
-      <c r="J65" s="58"/>
-      <c r="K65" s="58"/>
-      <c r="L65" s="58"/>
-      <c r="M65" s="58"/>
-      <c r="N65" s="58"/>
-      <c r="O65" s="58"/>
-      <c r="P65" s="58"/>
-      <c r="Q65" s="58"/>
-      <c r="R65" s="58"/>
-      <c r="S65" s="58"/>
-      <c r="T65" s="58"/>
-      <c r="U65" s="58"/>
-      <c r="V65" s="58"/>
-      <c r="W65" s="58"/>
-      <c r="X65" s="58"/>
-      <c r="Y65" s="58"/>
-      <c r="Z65" s="58"/>
-      <c r="AA65" s="58"/>
-      <c r="AB65" s="58"/>
+      <c r="C65" s="65"/>
+      <c r="D65" s="65"/>
+      <c r="E65" s="65"/>
+      <c r="F65" s="65"/>
+      <c r="G65" s="65"/>
+      <c r="H65" s="65"/>
+      <c r="I65" s="65"/>
+      <c r="J65" s="65"/>
+      <c r="K65" s="65"/>
+      <c r="L65" s="65"/>
+      <c r="M65" s="65"/>
+      <c r="N65" s="65"/>
+      <c r="O65" s="65"/>
+      <c r="P65" s="65"/>
+      <c r="Q65" s="65"/>
+      <c r="R65" s="65"/>
+      <c r="S65" s="65"/>
+      <c r="T65" s="65"/>
+      <c r="U65" s="65"/>
+      <c r="V65" s="65"/>
+      <c r="W65" s="65"/>
+      <c r="X65" s="65"/>
+      <c r="Y65" s="65"/>
+      <c r="Z65" s="65"/>
+      <c r="AA65" s="65"/>
+      <c r="AB65" s="65"/>
     </row>
     <row r="66" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B66" s="58" t="s">
+      <c r="B66" s="65" t="s">
         <v>234</v>
       </c>
-      <c r="C66" s="58"/>
-      <c r="D66" s="58"/>
-      <c r="E66" s="58"/>
-      <c r="F66" s="58"/>
-      <c r="G66" s="58"/>
-      <c r="H66" s="58"/>
-      <c r="I66" s="58"/>
-      <c r="J66" s="58"/>
-      <c r="K66" s="58"/>
-      <c r="L66" s="58"/>
-      <c r="M66" s="58"/>
-      <c r="N66" s="58"/>
-      <c r="O66" s="58"/>
-      <c r="P66" s="58"/>
-      <c r="Q66" s="58"/>
-      <c r="R66" s="58"/>
-      <c r="S66" s="58"/>
-      <c r="T66" s="58"/>
-      <c r="U66" s="58"/>
-      <c r="V66" s="58"/>
-      <c r="W66" s="58"/>
-      <c r="X66" s="58"/>
-      <c r="Y66" s="58"/>
-      <c r="Z66" s="58"/>
-      <c r="AA66" s="58"/>
-      <c r="AB66" s="58"/>
+      <c r="C66" s="65"/>
+      <c r="D66" s="65"/>
+      <c r="E66" s="65"/>
+      <c r="F66" s="65"/>
+      <c r="G66" s="65"/>
+      <c r="H66" s="65"/>
+      <c r="I66" s="65"/>
+      <c r="J66" s="65"/>
+      <c r="K66" s="65"/>
+      <c r="L66" s="65"/>
+      <c r="M66" s="65"/>
+      <c r="N66" s="65"/>
+      <c r="O66" s="65"/>
+      <c r="P66" s="65"/>
+      <c r="Q66" s="65"/>
+      <c r="R66" s="65"/>
+      <c r="S66" s="65"/>
+      <c r="T66" s="65"/>
+      <c r="U66" s="65"/>
+      <c r="V66" s="65"/>
+      <c r="W66" s="65"/>
+      <c r="X66" s="65"/>
+      <c r="Y66" s="65"/>
+      <c r="Z66" s="65"/>
+      <c r="AA66" s="65"/>
+      <c r="AB66" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B38:AB38"/>
-    <mergeCell ref="P24:AB24"/>
-    <mergeCell ref="P26:AB26"/>
-    <mergeCell ref="B35:AB35"/>
-    <mergeCell ref="B36:AB36"/>
-    <mergeCell ref="B37:AB37"/>
+    <mergeCell ref="B66:AB66"/>
+    <mergeCell ref="B51:AB51"/>
+    <mergeCell ref="B52:AB52"/>
+    <mergeCell ref="B57:AB57"/>
+    <mergeCell ref="B58:AB58"/>
+    <mergeCell ref="B59:AB59"/>
+    <mergeCell ref="B60:AB60"/>
+    <mergeCell ref="B61:AB61"/>
+    <mergeCell ref="B62:AB62"/>
+    <mergeCell ref="B63:AB63"/>
+    <mergeCell ref="B64:AB64"/>
+    <mergeCell ref="B65:AB65"/>
     <mergeCell ref="B50:AB50"/>
     <mergeCell ref="B39:AB39"/>
     <mergeCell ref="B40:AB40"/>
@@ -8935,18 +8979,12 @@
     <mergeCell ref="B47:AB47"/>
     <mergeCell ref="B48:AB48"/>
     <mergeCell ref="B49:AB49"/>
-    <mergeCell ref="B66:AB66"/>
-    <mergeCell ref="B51:AB51"/>
-    <mergeCell ref="B52:AB52"/>
-    <mergeCell ref="B57:AB57"/>
-    <mergeCell ref="B58:AB58"/>
-    <mergeCell ref="B59:AB59"/>
-    <mergeCell ref="B60:AB60"/>
-    <mergeCell ref="B61:AB61"/>
-    <mergeCell ref="B62:AB62"/>
-    <mergeCell ref="B63:AB63"/>
-    <mergeCell ref="B64:AB64"/>
-    <mergeCell ref="B65:AB65"/>
+    <mergeCell ref="B38:AB38"/>
+    <mergeCell ref="P24:AB24"/>
+    <mergeCell ref="P26:AB26"/>
+    <mergeCell ref="B35:AB35"/>
+    <mergeCell ref="B36:AB36"/>
+    <mergeCell ref="B37:AB37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -8958,7 +8996,7 @@
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A2:AC27"/>
+  <dimension ref="A2:AC26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.28515625" customWidth="1"/>
@@ -8973,433 +9011,404 @@
       <c r="A4" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="57" t="s">
         <v>244</v>
       </c>
-      <c r="C4" s="48"/>
-      <c r="D4" s="78" t="s">
+      <c r="C4" s="57"/>
+      <c r="D4" s="80" t="s">
         <v>245</v>
       </c>
-      <c r="E4" s="79"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="48" t="s">
+      <c r="E4" s="81"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="57" t="s">
         <v>272</v>
       </c>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="48"/>
-      <c r="M4" s="78" t="s">
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="80" t="s">
         <v>252</v>
       </c>
-      <c r="N4" s="79"/>
-      <c r="O4" s="79"/>
-      <c r="P4" s="80"/>
-      <c r="Q4" s="48" t="s">
+      <c r="N4" s="81"/>
+      <c r="O4" s="81"/>
+      <c r="P4" s="90"/>
+      <c r="Q4" s="57" t="s">
         <v>260</v>
       </c>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48" t="s">
+      <c r="R4" s="57"/>
+      <c r="S4" s="57" t="s">
         <v>261</v>
       </c>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48" t="s">
+      <c r="T4" s="57"/>
+      <c r="U4" s="57"/>
+      <c r="V4" s="57" t="s">
         <v>253</v>
       </c>
-      <c r="W4" s="48"/>
-      <c r="X4" s="48"/>
-      <c r="Y4" s="48"/>
-      <c r="Z4" s="48"/>
-      <c r="AA4" s="48"/>
-      <c r="AB4" s="48"/>
-      <c r="AC4" s="48"/>
+      <c r="W4" s="57"/>
+      <c r="X4" s="57"/>
+      <c r="Y4" s="57"/>
+      <c r="Z4" s="57"/>
+      <c r="AA4" s="57"/>
+      <c r="AB4" s="57"/>
+      <c r="AC4" s="57"/>
     </row>
     <row r="5" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>1</v>
       </c>
-      <c r="B5" s="98" t="s">
+      <c r="B5" s="113" t="s">
         <v>247</v>
       </c>
-      <c r="C5" s="98"/>
-      <c r="D5" s="84" t="s">
+      <c r="C5" s="113"/>
+      <c r="D5" s="85" t="s">
         <v>246</v>
       </c>
-      <c r="E5" s="85"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="118" t="s">
+      <c r="E5" s="86"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="114" t="s">
         <v>273</v>
       </c>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
-      <c r="J5" s="119"/>
-      <c r="K5" s="119"/>
-      <c r="L5" s="120"/>
-      <c r="M5" s="107" t="s">
+      <c r="H5" s="115"/>
+      <c r="I5" s="115"/>
+      <c r="J5" s="115"/>
+      <c r="K5" s="115"/>
+      <c r="L5" s="116"/>
+      <c r="M5" s="117" t="s">
         <v>248</v>
       </c>
-      <c r="N5" s="108"/>
-      <c r="O5" s="108"/>
-      <c r="P5" s="109"/>
-      <c r="Q5" s="105" t="s">
+      <c r="N5" s="118"/>
+      <c r="O5" s="118"/>
+      <c r="P5" s="119"/>
+      <c r="Q5" s="121" t="s">
         <v>254</v>
       </c>
-      <c r="R5" s="105"/>
-      <c r="S5" s="106" t="s">
+      <c r="R5" s="121"/>
+      <c r="S5" s="110" t="s">
         <v>262</v>
       </c>
-      <c r="T5" s="103"/>
-      <c r="U5" s="104"/>
-      <c r="V5" s="101" t="s">
+      <c r="T5" s="111"/>
+      <c r="U5" s="112"/>
+      <c r="V5" s="73" t="s">
         <v>249</v>
       </c>
-      <c r="W5" s="101"/>
-      <c r="X5" s="101"/>
-      <c r="Y5" s="101"/>
-      <c r="Z5" s="101"/>
-      <c r="AA5" s="101"/>
-      <c r="AB5" s="101"/>
-      <c r="AC5" s="101"/>
+      <c r="W5" s="73"/>
+      <c r="X5" s="73"/>
+      <c r="Y5" s="73"/>
+      <c r="Z5" s="73"/>
+      <c r="AA5" s="73"/>
+      <c r="AB5" s="73"/>
+      <c r="AC5" s="73"/>
     </row>
     <row r="6" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>2</v>
       </c>
-      <c r="B6" s="98" t="s">
+      <c r="B6" s="113" t="s">
         <v>256</v>
       </c>
-      <c r="C6" s="98"/>
-      <c r="D6" s="84" t="s">
+      <c r="C6" s="113"/>
+      <c r="D6" s="85" t="s">
         <v>257</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="118" t="s">
+      <c r="E6" s="86"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="114" t="s">
         <v>274</v>
       </c>
-      <c r="H6" s="119"/>
-      <c r="I6" s="119"/>
-      <c r="J6" s="119"/>
-      <c r="K6" s="119"/>
-      <c r="L6" s="120"/>
-      <c r="M6" s="107" t="s">
+      <c r="H6" s="115"/>
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="116"/>
+      <c r="M6" s="117" t="s">
         <v>251</v>
       </c>
-      <c r="N6" s="108"/>
-      <c r="O6" s="108"/>
-      <c r="P6" s="109"/>
-      <c r="Q6" s="99" t="s">
+      <c r="N6" s="118"/>
+      <c r="O6" s="118"/>
+      <c r="P6" s="119"/>
+      <c r="Q6" s="107" t="s">
         <v>255</v>
       </c>
-      <c r="R6" s="99"/>
-      <c r="S6" s="106">
+      <c r="R6" s="107"/>
+      <c r="S6" s="110">
         <v>1</v>
       </c>
-      <c r="T6" s="103"/>
-      <c r="U6" s="104"/>
-      <c r="V6" s="101" t="s">
+      <c r="T6" s="111"/>
+      <c r="U6" s="112"/>
+      <c r="V6" s="73" t="s">
         <v>288</v>
       </c>
-      <c r="W6" s="101"/>
-      <c r="X6" s="101"/>
-      <c r="Y6" s="101"/>
-      <c r="Z6" s="101"/>
-      <c r="AA6" s="101"/>
-      <c r="AB6" s="101"/>
-      <c r="AC6" s="101"/>
+      <c r="W6" s="73"/>
+      <c r="X6" s="73"/>
+      <c r="Y6" s="73"/>
+      <c r="Z6" s="73"/>
+      <c r="AA6" s="73"/>
+      <c r="AB6" s="73"/>
+      <c r="AC6" s="73"/>
     </row>
     <row r="7" spans="1:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>3</v>
       </c>
-      <c r="B7" s="98" t="s">
+      <c r="B7" s="113" t="s">
         <v>289</v>
       </c>
-      <c r="C7" s="98"/>
-      <c r="D7" s="84" t="s">
+      <c r="C7" s="113"/>
+      <c r="D7" s="85" t="s">
         <v>257</v>
       </c>
-      <c r="E7" s="85"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="118" t="s">
+      <c r="E7" s="86"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="119"/>
-      <c r="I7" s="119"/>
-      <c r="J7" s="119"/>
-      <c r="K7" s="119"/>
-      <c r="L7" s="120"/>
-      <c r="M7" s="107" t="s">
+      <c r="H7" s="115"/>
+      <c r="I7" s="115"/>
+      <c r="J7" s="115"/>
+      <c r="K7" s="115"/>
+      <c r="L7" s="116"/>
+      <c r="M7" s="117" t="s">
         <v>290</v>
       </c>
-      <c r="N7" s="108"/>
-      <c r="O7" s="108"/>
-      <c r="P7" s="109"/>
-      <c r="Q7" s="99" t="s">
+      <c r="N7" s="118"/>
+      <c r="O7" s="118"/>
+      <c r="P7" s="119"/>
+      <c r="Q7" s="107" t="s">
         <v>291</v>
       </c>
-      <c r="R7" s="99"/>
-      <c r="S7" s="106" t="s">
+      <c r="R7" s="107"/>
+      <c r="S7" s="110" t="s">
         <v>262</v>
       </c>
-      <c r="T7" s="103"/>
-      <c r="U7" s="104"/>
-      <c r="V7" s="101" t="s">
-        <v>288</v>
-      </c>
-      <c r="W7" s="101"/>
-      <c r="X7" s="101"/>
-      <c r="Y7" s="101"/>
-      <c r="Z7" s="101"/>
-      <c r="AA7" s="101"/>
-      <c r="AB7" s="101"/>
-      <c r="AC7" s="101"/>
+      <c r="T7" s="111"/>
+      <c r="U7" s="112"/>
+      <c r="V7" s="122" t="s">
+        <v>297</v>
+      </c>
+      <c r="W7" s="73"/>
+      <c r="X7" s="73"/>
+      <c r="Y7" s="73"/>
+      <c r="Z7" s="73"/>
+      <c r="AA7" s="73"/>
+      <c r="AB7" s="73"/>
+      <c r="AC7" s="73"/>
     </row>
     <row r="8" spans="1:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>3</v>
       </c>
-      <c r="B8" s="98" t="s">
+      <c r="B8" s="113" t="s">
         <v>267</v>
       </c>
-      <c r="C8" s="98"/>
-      <c r="D8" s="84" t="s">
+      <c r="C8" s="113"/>
+      <c r="D8" s="85" t="s">
         <v>250</v>
       </c>
-      <c r="E8" s="85"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="118" t="s">
+      <c r="E8" s="86"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="114" t="s">
         <v>284</v>
       </c>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="119"/>
-      <c r="K8" s="119"/>
-      <c r="L8" s="120"/>
-      <c r="M8" s="107" t="s">
+      <c r="H8" s="115"/>
+      <c r="I8" s="115"/>
+      <c r="J8" s="115"/>
+      <c r="K8" s="115"/>
+      <c r="L8" s="116"/>
+      <c r="M8" s="117" t="s">
         <v>258</v>
       </c>
-      <c r="N8" s="108"/>
-      <c r="O8" s="108"/>
-      <c r="P8" s="109"/>
-      <c r="Q8" s="99" t="s">
+      <c r="N8" s="118"/>
+      <c r="O8" s="118"/>
+      <c r="P8" s="119"/>
+      <c r="Q8" s="107" t="s">
         <v>259</v>
       </c>
-      <c r="R8" s="99"/>
-      <c r="S8" s="102">
+      <c r="R8" s="107"/>
+      <c r="S8" s="120">
         <v>1</v>
       </c>
-      <c r="T8" s="103"/>
-      <c r="U8" s="104"/>
-      <c r="V8" s="101" t="s">
+      <c r="T8" s="111"/>
+      <c r="U8" s="112"/>
+      <c r="V8" s="73" t="s">
         <v>263</v>
       </c>
-      <c r="W8" s="101"/>
-      <c r="X8" s="101"/>
-      <c r="Y8" s="101"/>
-      <c r="Z8" s="101"/>
-      <c r="AA8" s="101"/>
-      <c r="AB8" s="101"/>
-      <c r="AC8" s="101"/>
+      <c r="W8" s="73"/>
+      <c r="X8" s="73"/>
+      <c r="Y8" s="73"/>
+      <c r="Z8" s="73"/>
+      <c r="AA8" s="73"/>
+      <c r="AB8" s="73"/>
+      <c r="AC8" s="73"/>
     </row>
     <row r="9" spans="1:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>4</v>
       </c>
-      <c r="B9" s="98" t="s">
+      <c r="B9" s="113" t="s">
         <v>268</v>
       </c>
-      <c r="C9" s="98"/>
-      <c r="D9" s="84" t="s">
+      <c r="C9" s="113"/>
+      <c r="D9" s="85" t="s">
         <v>250</v>
       </c>
-      <c r="E9" s="85"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="118" t="s">
+      <c r="E9" s="86"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="114" t="s">
         <v>284</v>
       </c>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="119"/>
-      <c r="K9" s="119"/>
-      <c r="L9" s="120"/>
-      <c r="M9" s="107" t="s">
+      <c r="H9" s="115"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="115"/>
+      <c r="K9" s="115"/>
+      <c r="L9" s="116"/>
+      <c r="M9" s="117" t="s">
         <v>265</v>
       </c>
-      <c r="N9" s="108"/>
-      <c r="O9" s="108"/>
-      <c r="P9" s="109"/>
-      <c r="Q9" s="99" t="s">
+      <c r="N9" s="118"/>
+      <c r="O9" s="118"/>
+      <c r="P9" s="119"/>
+      <c r="Q9" s="107" t="s">
         <v>264</v>
       </c>
-      <c r="R9" s="99"/>
-      <c r="S9" s="102">
+      <c r="R9" s="107"/>
+      <c r="S9" s="120">
         <v>1</v>
       </c>
-      <c r="T9" s="103"/>
-      <c r="U9" s="104"/>
-      <c r="V9" s="101" t="s">
+      <c r="T9" s="111"/>
+      <c r="U9" s="112"/>
+      <c r="V9" s="73" t="s">
         <v>266</v>
       </c>
-      <c r="W9" s="101"/>
-      <c r="X9" s="101"/>
-      <c r="Y9" s="101"/>
-      <c r="Z9" s="101"/>
-      <c r="AA9" s="101"/>
-      <c r="AB9" s="101"/>
-      <c r="AC9" s="101"/>
+      <c r="W9" s="73"/>
+      <c r="X9" s="73"/>
+      <c r="Y9" s="73"/>
+      <c r="Z9" s="73"/>
+      <c r="AA9" s="73"/>
+      <c r="AB9" s="73"/>
+      <c r="AC9" s="73"/>
     </row>
     <row r="10" spans="1:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>5</v>
       </c>
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="113" t="s">
         <v>269</v>
       </c>
-      <c r="C10" s="98"/>
-      <c r="D10" s="84" t="s">
+      <c r="C10" s="113"/>
+      <c r="D10" s="85" t="s">
         <v>250</v>
       </c>
-      <c r="E10" s="85"/>
-      <c r="F10" s="86"/>
-      <c r="G10" s="118" t="s">
+      <c r="E10" s="86"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="114" t="s">
         <v>285</v>
       </c>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="119"/>
-      <c r="K10" s="119"/>
-      <c r="L10" s="120"/>
-      <c r="M10" s="107" t="s">
+      <c r="H10" s="115"/>
+      <c r="I10" s="115"/>
+      <c r="J10" s="115"/>
+      <c r="K10" s="115"/>
+      <c r="L10" s="116"/>
+      <c r="M10" s="117" t="s">
         <v>270</v>
       </c>
-      <c r="N10" s="108"/>
-      <c r="O10" s="108"/>
-      <c r="P10" s="109"/>
-      <c r="Q10" s="99" t="s">
+      <c r="N10" s="118"/>
+      <c r="O10" s="118"/>
+      <c r="P10" s="119"/>
+      <c r="Q10" s="107" t="s">
         <v>259</v>
       </c>
-      <c r="R10" s="99"/>
-      <c r="S10" s="102">
+      <c r="R10" s="107"/>
+      <c r="S10" s="120">
         <v>1</v>
       </c>
-      <c r="T10" s="103"/>
-      <c r="U10" s="104"/>
-      <c r="V10" s="101" t="s">
+      <c r="T10" s="111"/>
+      <c r="U10" s="112"/>
+      <c r="V10" s="73" t="s">
         <v>271</v>
       </c>
-      <c r="W10" s="101"/>
-      <c r="X10" s="101"/>
-      <c r="Y10" s="101"/>
-      <c r="Z10" s="101"/>
-      <c r="AA10" s="101"/>
-      <c r="AB10" s="101"/>
-      <c r="AC10" s="101"/>
+      <c r="W10" s="73"/>
+      <c r="X10" s="73"/>
+      <c r="Y10" s="73"/>
+      <c r="Z10" s="73"/>
+      <c r="AA10" s="73"/>
+      <c r="AB10" s="73"/>
+      <c r="AC10" s="73"/>
     </row>
     <row r="11" spans="1:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>6</v>
       </c>
-      <c r="B11" s="98" t="s">
+      <c r="B11" s="113" t="s">
         <v>286</v>
       </c>
-      <c r="C11" s="98"/>
-      <c r="D11" s="84" t="s">
+      <c r="C11" s="113"/>
+      <c r="D11" s="85" t="s">
         <v>250</v>
       </c>
-      <c r="E11" s="85"/>
-      <c r="F11" s="86"/>
-      <c r="G11" s="118" t="s">
+      <c r="E11" s="86"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="114" t="s">
         <v>202</v>
       </c>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="119"/>
-      <c r="K11" s="119"/>
-      <c r="L11" s="120"/>
-      <c r="M11" s="107" t="s">
+      <c r="H11" s="115"/>
+      <c r="I11" s="115"/>
+      <c r="J11" s="115"/>
+      <c r="K11" s="115"/>
+      <c r="L11" s="116"/>
+      <c r="M11" s="117" t="s">
         <v>258</v>
       </c>
-      <c r="N11" s="108"/>
-      <c r="O11" s="108"/>
-      <c r="P11" s="109"/>
-      <c r="Q11" s="99" t="s">
+      <c r="N11" s="118"/>
+      <c r="O11" s="118"/>
+      <c r="P11" s="119"/>
+      <c r="Q11" s="107" t="s">
         <v>259</v>
       </c>
-      <c r="R11" s="99"/>
-      <c r="S11" s="99" t="s">
+      <c r="R11" s="107"/>
+      <c r="S11" s="107" t="s">
         <v>262</v>
       </c>
-      <c r="T11" s="76"/>
-      <c r="U11" s="76"/>
-      <c r="V11" s="101" t="s">
+      <c r="T11" s="88"/>
+      <c r="U11" s="88"/>
+      <c r="V11" s="73" t="s">
         <v>287</v>
       </c>
-      <c r="W11" s="101"/>
-      <c r="X11" s="101"/>
-      <c r="Y11" s="101"/>
-      <c r="Z11" s="101"/>
-      <c r="AA11" s="101"/>
-      <c r="AB11" s="101"/>
-      <c r="AC11" s="101"/>
-    </row>
-    <row r="17" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="5:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E27" s="100"/>
-      <c r="F27" s="100"/>
-      <c r="G27" s="100"/>
-      <c r="H27" s="100"/>
-      <c r="I27" s="100"/>
-      <c r="J27" s="100"/>
-    </row>
+      <c r="W11" s="73"/>
+      <c r="X11" s="73"/>
+      <c r="Y11" s="73"/>
+      <c r="Z11" s="73"/>
+      <c r="AA11" s="73"/>
+      <c r="AB11" s="73"/>
+      <c r="AC11" s="73"/>
+    </row>
+    <row r="14" spans="1:29" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="S7:U7"/>
-    <mergeCell ref="V7:AC7"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:L7"/>
-    <mergeCell ref="M7:P7"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="G4:L4"/>
-    <mergeCell ref="G5:L5"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="G9:L9"/>
-    <mergeCell ref="V11:AC11"/>
-    <mergeCell ref="V4:AC4"/>
-    <mergeCell ref="V5:AC5"/>
-    <mergeCell ref="V6:AC6"/>
-    <mergeCell ref="V8:AC8"/>
-    <mergeCell ref="V9:AC9"/>
-    <mergeCell ref="V10:AC10"/>
-    <mergeCell ref="S4:U4"/>
-    <mergeCell ref="S5:U5"/>
-    <mergeCell ref="S6:U6"/>
-    <mergeCell ref="S8:U8"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="S10:U10"/>
-    <mergeCell ref="S11:U11"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="M6:P6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="M5:P5"/>
     <mergeCell ref="M8:P8"/>
     <mergeCell ref="M9:P9"/>
     <mergeCell ref="M10:P10"/>
@@ -9412,17 +9421,43 @@
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D8:F8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="M6:P6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="M5:P5"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="S10:U10"/>
+    <mergeCell ref="S11:U11"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="S5:U5"/>
+    <mergeCell ref="S6:U6"/>
+    <mergeCell ref="S8:U8"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="V11:AC11"/>
+    <mergeCell ref="V4:AC4"/>
+    <mergeCell ref="V5:AC5"/>
+    <mergeCell ref="V6:AC6"/>
+    <mergeCell ref="V8:AC8"/>
+    <mergeCell ref="V9:AC9"/>
+    <mergeCell ref="V10:AC10"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="G4:L4"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="G9:L9"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="S7:U7"/>
+    <mergeCell ref="V7:AC7"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:L7"/>
+    <mergeCell ref="M7:P7"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="M5:M11">
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -9436,7 +9471,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:F7 D8:F11" xr:uid="{7BF058DC-62D2-424D-894E-A6AE051A4A89}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:F11" xr:uid="{7BF058DC-62D2-424D-894E-A6AE051A4A89}">
       <formula1>"Human, Environment, Object, Effect"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEC33BC-7AD9-4953-B5BD-A82720129D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6628F8E3-6474-4C2A-BF99-A22F22B12B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -1622,9 +1622,6 @@
     </r>
   </si>
   <si>
-    <t>Phần Puzzle UI này sẽ nhìn trực diện vào máy bảo mật, và có nút back ra. Khi bấm sai thì nó sẽ hiển thị: "This is incorrect".</t>
-  </si>
-  <si>
     <t>Phần Puzzle UI này sẽ không cần nhìn vào #tờ hướng dẫn. Mà sẽ hiển thị #hướng dẫn trực tiếp trên màn hình, và có nút back về. Nếu đưa đồ vật không phù hợp, thì sẽ không thể vào Puzzle UI mà sẽ hiển thị chữ: "This item is not correct!".</t>
   </si>
   <si>
@@ -1767,9 +1764,6 @@
     <t>***Lưu ý: không thể skip, double click chạy hết chữ, hay thoát ra ngoài vào gameplay.</t>
   </si>
   <si>
-    <t>***Lưu ý: lần tương tác thứ 2, người chơi sẽ được phép double click để chạy full đoạn đối thoại và nhảy sang đoạn đối thoại tiếp theo, được phép thoát ra ngoài.</t>
-  </si>
-  <si>
     <t>Item ID</t>
   </si>
   <si>
@@ -2147,6 +2141,180 @@
       </rPr>
       <t xml:space="preserve"> để người chơi biết hết đoạn đối thoại và qua phần kế.</t>
     </r>
+  </si>
+  <si>
+    <t>IX. Soundfx</t>
+  </si>
+  <si>
+    <t>SoundID</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Human</t>
+  </si>
+  <si>
+    <t>H_Footstep</t>
+  </si>
+  <si>
+    <t>Khi người chơi di chuyển</t>
+  </si>
+  <si>
+    <t>Sync theo tốc độ người chơi</t>
+  </si>
+  <si>
+    <t>Object</t>
+  </si>
+  <si>
+    <t>Khi puzzle biến đổi</t>
+  </si>
+  <si>
+    <t>Condition</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>3-5s</t>
+  </si>
+  <si>
+    <t>3s</t>
+  </si>
+  <si>
+    <t>E_Puzzle</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>Khi người chơi tương tác</t>
+  </si>
+  <si>
+    <t>2s</t>
+  </si>
+  <si>
+    <t>Duration (s)</t>
+  </si>
+  <si>
+    <t>Number of Times</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loop </t>
+  </si>
+  <si>
+    <t>Xảy ra khi gười chơi tương tác Object X, Y</t>
+  </si>
+  <si>
+    <t>3-4s</t>
+  </si>
+  <si>
+    <t>Khi người chơi thả object</t>
+  </si>
+  <si>
+    <t>Xảy ra khi người chơi thả Object X, Y</t>
+  </si>
+  <si>
+    <t>O_ObjectInter</t>
+  </si>
+  <si>
+    <t>O_ObjectDrop</t>
+  </si>
+  <si>
+    <t>O_Paper</t>
+  </si>
+  <si>
+    <t>Người chơi mở xem nội dung</t>
+  </si>
+  <si>
+    <t>Người chơi xem các tài liêu, document sẽ trigger</t>
+  </si>
+  <si>
+    <t>Applied for</t>
+  </si>
+  <si>
+    <t>Main Character</t>
+  </si>
+  <si>
+    <t>PZ_PICTURE1; PZ_PICTURE2</t>
+  </si>
+  <si>
+    <t>1.  ITEMS</t>
+  </si>
+  <si>
+    <t>VII. 3D ASSETS</t>
+  </si>
+  <si>
+    <t>2. CONSTRUCTION</t>
+  </si>
+  <si>
+    <t>C_Wall</t>
+  </si>
+  <si>
+    <t>C_Floor</t>
+  </si>
+  <si>
+    <t>C_Door</t>
+  </si>
+  <si>
+    <t>Tường</t>
+  </si>
+  <si>
+    <t>Sàn</t>
+  </si>
+  <si>
+    <t>Cửa</t>
+  </si>
+  <si>
+    <t>All the X/Y/PZ_Objects (Except X_Statue)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All the Y/INS_Objects </t>
+  </si>
+  <si>
+    <t>O_Mico</t>
+  </si>
+  <si>
+    <t>Các đoạn đối thoại bằng chữ với MICO sẽ có âm thanh phím</t>
+  </si>
+  <si>
+    <t>Không trực tiếp phát ra tại Puzzle (= âm thanh xung quanh)</t>
+  </si>
+  <si>
+    <t>E_Time</t>
+  </si>
+  <si>
+    <t>Always on</t>
+  </si>
+  <si>
+    <t>1-3s</t>
+  </si>
+  <si>
+    <t>40px (Main Title); 56px (GameOver);  32px (Timer, Mã Code)</t>
+  </si>
+  <si>
+    <t>22px (Menu, tên section); 16px (Panel header HUD); 13px (Status)</t>
+  </si>
+  <si>
+    <t>12px (Log text, mô tả); 11px (Timestamp,Log); 9px (Label, tag)</t>
+  </si>
+  <si>
+    <t>FONT SIZE</t>
+  </si>
+  <si>
+    <t>IX. Music</t>
+  </si>
+  <si>
+    <t>Phát trực tiếp tại đồng hồ</t>
+  </si>
+  <si>
+    <t>C_Clock</t>
+  </si>
+  <si>
+    <t>Khung đồng hồ điện</t>
+  </si>
+  <si>
+    <t>***Lưu ý: Từ lần tương tác thứ 2, người chơi sẽ được phép double click để chạy full đoạn đối thoại và nhảy sang đoạn đối thoại tiếp theo, được phép thoát ra ngoài.</t>
   </si>
   <si>
     <r>
@@ -2354,6 +2522,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">Timelapse nhỏ sẽ xuất hiện và bắt đầu tính thời gian.
+- Khi vừa vào game sẽ cho phép toàn bộ puzzle biến đổi. 
 - Chỉ được kích hoạt 1 puzzle 1 lần. Khi puzzle đầu tiên hoàn thành thì có thể thực hiện puzzle thứ 2.
 - </t>
     </r>
@@ -2426,175 +2595,7 @@
     </r>
   </si>
   <si>
-    <t>IX. Soundfx</t>
-  </si>
-  <si>
-    <t>SoundID</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Human</t>
-  </si>
-  <si>
-    <t>H_Footstep</t>
-  </si>
-  <si>
-    <t>Khi người chơi di chuyển</t>
-  </si>
-  <si>
-    <t>Sync theo tốc độ người chơi</t>
-  </si>
-  <si>
-    <t>Object</t>
-  </si>
-  <si>
-    <t>Khi puzzle biến đổi</t>
-  </si>
-  <si>
-    <t>Condition</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>3-5s</t>
-  </si>
-  <si>
-    <t>3s</t>
-  </si>
-  <si>
-    <t>E_Puzzle</t>
-  </si>
-  <si>
-    <t>Effect</t>
-  </si>
-  <si>
-    <t>Khi người chơi tương tác</t>
-  </si>
-  <si>
-    <t>2s</t>
-  </si>
-  <si>
-    <t>Duration (s)</t>
-  </si>
-  <si>
-    <t>Number of Times</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loop </t>
-  </si>
-  <si>
-    <t>Xảy ra khi gười chơi tương tác Object X, Y</t>
-  </si>
-  <si>
-    <t>3-4s</t>
-  </si>
-  <si>
-    <t>Khi người chơi thả object</t>
-  </si>
-  <si>
-    <t>Xảy ra khi người chơi thả Object X, Y</t>
-  </si>
-  <si>
-    <t>O_ObjectInter</t>
-  </si>
-  <si>
-    <t>O_ObjectDrop</t>
-  </si>
-  <si>
-    <t>O_Paper</t>
-  </si>
-  <si>
-    <t>Người chơi mở xem nội dung</t>
-  </si>
-  <si>
-    <t>Người chơi xem các tài liêu, document sẽ trigger</t>
-  </si>
-  <si>
-    <t>Applied for</t>
-  </si>
-  <si>
-    <t>Main Character</t>
-  </si>
-  <si>
-    <t>PZ_PICTURE1; PZ_PICTURE2</t>
-  </si>
-  <si>
-    <t>1.  ITEMS</t>
-  </si>
-  <si>
-    <t>VII. 3D ASSETS</t>
-  </si>
-  <si>
-    <t>2. CONSTRUCTION</t>
-  </si>
-  <si>
-    <t>C_Wall</t>
-  </si>
-  <si>
-    <t>C_Floor</t>
-  </si>
-  <si>
-    <t>C_Door</t>
-  </si>
-  <si>
-    <t>Tường</t>
-  </si>
-  <si>
-    <t>Sàn</t>
-  </si>
-  <si>
-    <t>Cửa</t>
-  </si>
-  <si>
-    <t>All the X/Y/PZ_Objects (Except X_Statue)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All the Y/INS_Objects </t>
-  </si>
-  <si>
-    <t>O_Mico</t>
-  </si>
-  <si>
-    <t>Các đoạn đối thoại bằng chữ với MICO sẽ có âm thanh phím</t>
-  </si>
-  <si>
-    <t>Không trực tiếp phát ra tại Puzzle (= âm thanh xung quanh)</t>
-  </si>
-  <si>
-    <t>E_Time</t>
-  </si>
-  <si>
-    <t>Always on</t>
-  </si>
-  <si>
-    <t>1-3s</t>
-  </si>
-  <si>
-    <t>40px (Main Title); 56px (GameOver);  32px (Timer, Mã Code)</t>
-  </si>
-  <si>
-    <t>22px (Menu, tên section); 16px (Panel header HUD); 13px (Status)</t>
-  </si>
-  <si>
-    <t>12px (Log text, mô tả); 11px (Timestamp,Log); 9px (Label, tag)</t>
-  </si>
-  <si>
-    <t>FONT SIZE</t>
-  </si>
-  <si>
-    <t>IX. Music</t>
-  </si>
-  <si>
-    <t>Phát trực tiếp tại đồng hồ</t>
-  </si>
-  <si>
-    <t>C_Clock</t>
-  </si>
-  <si>
-    <t>Khung đồng hồ điện</t>
+    <t>Phần Puzzle UI này sẽ nhìn trực diện vào máy bảo mật, và có nút back ra. Khi bấm sai thì nó sẽ hiển thị: "This is incorrect". UI sẽ như sau: khi người chơi tương tác, camera sẽ zoom vào máy bảo mật và align bên trái, còn nơi nhập mã code sẽ là UI hiển thị phần nhập bên phải.</t>
   </si>
 </sst>
 </file>
@@ -2881,7 +2882,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3216,6 +3217,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3352,8 +3359,8 @@
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>54949</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>102967</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>160117</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3413,8 +3420,8 @@
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>12580</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>129024</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>186174</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4707,7 +4714,7 @@
     </row>
     <row r="12" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B12" s="44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C12" s="44"/>
       <c r="D12" s="44"/>
@@ -4882,7 +4889,7 @@
     </row>
     <row r="20" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="45" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C20" s="45"/>
       <c r="D20" s="45"/>
@@ -5572,9 +5579,9 @@
     <row r="16" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B16" s="8"/>
     </row>
-    <row r="17" spans="2:29" ht="138" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="60" t="s">
-        <v>242</v>
+    <row r="17" spans="2:29" ht="157.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="123" t="s">
+        <v>298</v>
       </c>
       <c r="C17" s="60"/>
       <c r="D17" s="60"/>
@@ -5688,9 +5695,9 @@
       <c r="AA25" s="17"/>
       <c r="AB25" s="17"/>
     </row>
-    <row r="26" spans="2:29" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P26" s="61" t="s">
-        <v>172</v>
+    <row r="26" spans="2:29" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P26" s="124" t="s">
+        <v>299</v>
       </c>
       <c r="Q26" s="61"/>
       <c r="R26" s="61"/>
@@ -5831,7 +5838,7 @@
     </row>
     <row r="39" spans="2:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P39" s="65" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q39" s="65"/>
       <c r="R39" s="65"/>
@@ -6046,7 +6053,7 @@
     </row>
     <row r="60" spans="2:29" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O60" s="71" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P60" s="72"/>
       <c r="Q60" s="72"/>
@@ -6082,7 +6089,7 @@
     </row>
     <row r="62" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O62" s="58" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="P62" s="59"/>
       <c r="Q62" s="59"/>
@@ -6488,7 +6495,7 @@
       <c r="M21" s="48"/>
       <c r="N21" s="48"/>
       <c r="O21" s="48" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="P21" s="48"/>
       <c r="Q21" s="48"/>
@@ -6507,7 +6514,7 @@
       <c r="M22" s="54"/>
       <c r="N22" s="54"/>
       <c r="O22" s="73" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="P22" s="73"/>
       <c r="Q22" s="73"/>
@@ -6526,7 +6533,7 @@
       <c r="M23" s="54"/>
       <c r="N23" s="54"/>
       <c r="O23" s="73" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="P23" s="73"/>
       <c r="Q23" s="73"/>
@@ -6545,7 +6552,7 @@
       <c r="M24" s="54"/>
       <c r="N24" s="54"/>
       <c r="O24" s="73" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="P24" s="73"/>
       <c r="Q24" s="73"/>
@@ -6646,7 +6653,7 @@
     </row>
     <row r="105" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B105" s="20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="107" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
@@ -6741,7 +6748,7 @@
     </row>
     <row r="121" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B121" s="24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="122" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
@@ -6757,7 +6764,7 @@
     </row>
     <row r="125" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B125" s="26" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="126" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
@@ -6765,7 +6772,7 @@
     </row>
     <row r="127" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B127" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="129" spans="2:13" ht="19.5" x14ac:dyDescent="0.3">
@@ -6844,7 +6851,7 @@
   <sheetData>
     <row r="2" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6853,7 +6860,7 @@
     <row r="4" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="B4" s="8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
@@ -6861,7 +6868,7 @@
         <v>15</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C6" s="57"/>
       <c r="D6" s="80" t="s">
@@ -6888,7 +6895,7 @@
       <c r="Q6" s="81"/>
       <c r="R6" s="81"/>
       <c r="S6" s="57" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="T6" s="57"/>
     </row>
@@ -6897,7 +6904,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="91" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C7" s="91"/>
       <c r="D7" s="85" t="s">
@@ -6924,7 +6931,7 @@
       <c r="Q7" s="83"/>
       <c r="R7" s="83"/>
       <c r="S7" s="88" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T7" s="88"/>
     </row>
@@ -6933,7 +6940,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="91" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C8" s="91"/>
       <c r="D8" s="85" t="s">
@@ -6950,7 +6957,7 @@
       </c>
       <c r="J8" s="93"/>
       <c r="K8" s="82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L8" s="83"/>
       <c r="M8" s="83"/>
@@ -6960,7 +6967,7 @@
       <c r="Q8" s="83"/>
       <c r="R8" s="83"/>
       <c r="S8" s="88" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T8" s="88"/>
     </row>
@@ -6969,7 +6976,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="91" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C9" s="91"/>
       <c r="D9" s="85" t="s">
@@ -6996,7 +7003,7 @@
       <c r="Q9" s="83"/>
       <c r="R9" s="83"/>
       <c r="S9" s="89" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T9" s="88"/>
     </row>
@@ -7005,7 +7012,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="91" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C10" s="91"/>
       <c r="D10" s="85" t="s">
@@ -7032,7 +7039,7 @@
       <c r="Q10" s="83"/>
       <c r="R10" s="83"/>
       <c r="S10" s="89" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T10" s="88"/>
     </row>
@@ -7041,7 +7048,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="91" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C11" s="91"/>
       <c r="D11" s="85" t="s">
@@ -7068,7 +7075,7 @@
       <c r="Q11" s="83"/>
       <c r="R11" s="83"/>
       <c r="S11" s="89" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T11" s="88"/>
     </row>
@@ -7077,7 +7084,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="91" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C12" s="91"/>
       <c r="D12" s="85" t="s">
@@ -7104,7 +7111,7 @@
       <c r="Q12" s="83"/>
       <c r="R12" s="83"/>
       <c r="S12" s="89" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T12" s="88"/>
     </row>
@@ -7113,7 +7120,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="91" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C13" s="91"/>
       <c r="D13" s="85" t="s">
@@ -7140,7 +7147,7 @@
       <c r="Q13" s="83"/>
       <c r="R13" s="83"/>
       <c r="S13" s="89" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T13" s="88"/>
     </row>
@@ -7149,7 +7156,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="91" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C14" s="91"/>
       <c r="D14" s="96" t="s">
@@ -7176,7 +7183,7 @@
       <c r="Q14" s="83"/>
       <c r="R14" s="83"/>
       <c r="S14" s="88" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T14" s="88"/>
     </row>
@@ -7185,7 +7192,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="91" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C15" s="91"/>
       <c r="D15" s="85" t="s">
@@ -7212,7 +7219,7 @@
       <c r="Q15" s="83"/>
       <c r="R15" s="83"/>
       <c r="S15" s="88" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T15" s="88"/>
     </row>
@@ -7221,7 +7228,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="91" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C16" s="91"/>
       <c r="D16" s="85" t="s">
@@ -7248,7 +7255,7 @@
       <c r="Q16" s="83"/>
       <c r="R16" s="83"/>
       <c r="S16" s="88" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T16" s="88"/>
     </row>
@@ -7257,7 +7264,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="91" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C17" s="91"/>
       <c r="D17" s="85" t="s">
@@ -7284,7 +7291,7 @@
       <c r="Q17" s="83"/>
       <c r="R17" s="83"/>
       <c r="S17" s="88" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T17" s="88"/>
     </row>
@@ -7293,7 +7300,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="91" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C18" s="91"/>
       <c r="D18" s="85" t="s">
@@ -7320,7 +7327,7 @@
       <c r="Q18" s="83"/>
       <c r="R18" s="83"/>
       <c r="S18" s="107" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T18" s="88"/>
     </row>
@@ -7329,7 +7336,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="91" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C19" s="91"/>
       <c r="D19" s="85" t="s">
@@ -7356,7 +7363,7 @@
       <c r="Q19" s="83"/>
       <c r="R19" s="83"/>
       <c r="S19" s="88" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T19" s="88"/>
     </row>
@@ -7365,7 +7372,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="91" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C20" s="91"/>
       <c r="D20" s="85" t="s">
@@ -7392,7 +7399,7 @@
       <c r="Q20" s="83"/>
       <c r="R20" s="83"/>
       <c r="S20" s="88" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T20" s="88"/>
     </row>
@@ -7401,7 +7408,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C21" s="91"/>
       <c r="D21" s="85" t="s">
@@ -7428,7 +7435,7 @@
       <c r="Q21" s="83"/>
       <c r="R21" s="83"/>
       <c r="S21" s="88" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T21" s="88"/>
     </row>
@@ -7437,7 +7444,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="91" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C22" s="91"/>
       <c r="D22" s="85" t="s">
@@ -7464,7 +7471,7 @@
       <c r="Q22" s="83"/>
       <c r="R22" s="83"/>
       <c r="S22" s="88" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T22" s="88"/>
     </row>
@@ -7473,7 +7480,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="91" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C23" s="91"/>
       <c r="D23" s="85" t="s">
@@ -7500,7 +7507,7 @@
       <c r="Q23" s="83"/>
       <c r="R23" s="83"/>
       <c r="S23" s="88" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T23" s="88"/>
     </row>
@@ -7509,7 +7516,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="91" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C24" s="91"/>
       <c r="D24" s="85" t="s">
@@ -7536,7 +7543,7 @@
       <c r="Q24" s="83"/>
       <c r="R24" s="83"/>
       <c r="S24" s="88" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T24" s="88"/>
     </row>
@@ -7545,7 +7552,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="91" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C25" s="91"/>
       <c r="D25" s="85" t="s">
@@ -7572,7 +7579,7 @@
       <c r="Q25" s="83"/>
       <c r="R25" s="83"/>
       <c r="S25" s="88" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T25" s="88"/>
     </row>
@@ -7581,7 +7588,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="91" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="91"/>
       <c r="D26" s="85" t="s">
@@ -7608,7 +7615,7 @@
       <c r="Q26" s="83"/>
       <c r="R26" s="83"/>
       <c r="S26" s="88" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T26" s="88"/>
     </row>
@@ -7617,7 +7624,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="91" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C27" s="91"/>
       <c r="D27" s="85" t="s">
@@ -7644,7 +7651,7 @@
       <c r="Q27" s="83"/>
       <c r="R27" s="83"/>
       <c r="S27" s="88" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="T27" s="88"/>
     </row>
@@ -7653,7 +7660,7 @@
         <v>13</v>
       </c>
       <c r="B28" s="104" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C28" s="104"/>
       <c r="D28" s="99" t="s">
@@ -7680,13 +7687,13 @@
       <c r="Q28" s="103"/>
       <c r="R28" s="103"/>
       <c r="S28" s="108" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="T28" s="108"/>
     </row>
     <row r="31" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
@@ -7697,7 +7704,7 @@
         <v>15</v>
       </c>
       <c r="B33" s="57" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C33" s="57"/>
       <c r="D33" s="80" t="s">
@@ -7706,7 +7713,7 @@
       <c r="E33" s="81"/>
       <c r="F33" s="90"/>
       <c r="G33" s="57" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H33" s="57"/>
     </row>
@@ -7715,16 +7722,16 @@
         <v>1</v>
       </c>
       <c r="B34" s="84" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C34" s="84"/>
       <c r="D34" s="85" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E34" s="86"/>
       <c r="F34" s="87"/>
       <c r="G34" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H34" s="88"/>
     </row>
@@ -7733,16 +7740,16 @@
         <v>2</v>
       </c>
       <c r="B35" s="84" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C35" s="84"/>
       <c r="D35" s="85" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E35" s="86"/>
       <c r="F35" s="87"/>
       <c r="G35" s="88" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H35" s="88"/>
     </row>
@@ -7751,16 +7758,16 @@
         <v>3</v>
       </c>
       <c r="B36" s="84" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C36" s="84"/>
       <c r="D36" s="85" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E36" s="86"/>
       <c r="F36" s="87"/>
       <c r="G36" s="89" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H36" s="88"/>
     </row>
@@ -7769,16 +7776,16 @@
         <v>4</v>
       </c>
       <c r="B37" s="84" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C37" s="84"/>
       <c r="D37" s="85" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E37" s="86"/>
       <c r="F37" s="87"/>
       <c r="G37" s="89" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H37" s="88"/>
     </row>
@@ -7985,32 +7992,32 @@
   <sheetData>
     <row r="2" spans="1:16" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P10" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P21" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="22" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P22" s="32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="24" spans="2:28" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P24" s="109" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="Q24" s="65"/>
       <c r="R24" s="65"/>
@@ -8027,7 +8034,7 @@
     </row>
     <row r="26" spans="2:28" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P26" s="109" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="Q26" s="65"/>
       <c r="R26" s="65"/>
@@ -8045,7 +8052,7 @@
     <row r="27" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8053,25 +8060,25 @@
     </row>
     <row r="31" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="2:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="33" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B33" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B35" s="65" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C35" s="65"/>
       <c r="D35" s="65"/>
@@ -8102,7 +8109,7 @@
     </row>
     <row r="36" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="65" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C36" s="65"/>
       <c r="D36" s="65"/>
@@ -8133,7 +8140,7 @@
     </row>
     <row r="37" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="65" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C37" s="65"/>
       <c r="D37" s="65"/>
@@ -8164,7 +8171,7 @@
     </row>
     <row r="38" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="65" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C38" s="65"/>
       <c r="D38" s="65"/>
@@ -8195,7 +8202,7 @@
     </row>
     <row r="39" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="65" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C39" s="65"/>
       <c r="D39" s="65"/>
@@ -8226,7 +8233,7 @@
     </row>
     <row r="40" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="65" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C40" s="65"/>
       <c r="D40" s="65"/>
@@ -8257,7 +8264,7 @@
     </row>
     <row r="41" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B41" s="65" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C41" s="65"/>
       <c r="D41" s="65"/>
@@ -8288,7 +8295,7 @@
     </row>
     <row r="42" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B42" s="65" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C42" s="65"/>
       <c r="D42" s="65"/>
@@ -8319,7 +8326,7 @@
     </row>
     <row r="43" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B43" s="65" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C43" s="65"/>
       <c r="D43" s="65"/>
@@ -8350,7 +8357,7 @@
     </row>
     <row r="44" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B44" s="65" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C44" s="65"/>
       <c r="D44" s="65"/>
@@ -8381,7 +8388,7 @@
     </row>
     <row r="45" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B45" s="65" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C45" s="65"/>
       <c r="D45" s="65"/>
@@ -8412,7 +8419,7 @@
     </row>
     <row r="46" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B46" s="65" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C46" s="65"/>
       <c r="D46" s="65"/>
@@ -8443,7 +8450,7 @@
     </row>
     <row r="47" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B47" s="65" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C47" s="65"/>
       <c r="D47" s="65"/>
@@ -8474,7 +8481,7 @@
     </row>
     <row r="48" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B48" s="65" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C48" s="65"/>
       <c r="D48" s="65"/>
@@ -8505,7 +8512,7 @@
     </row>
     <row r="49" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B49" s="65" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C49" s="65"/>
       <c r="D49" s="65"/>
@@ -8536,7 +8543,7 @@
     </row>
     <row r="50" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B50" s="65" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C50" s="65"/>
       <c r="D50" s="65"/>
@@ -8567,7 +8574,7 @@
     </row>
     <row r="51" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B51" s="65" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C51" s="65"/>
       <c r="D51" s="65"/>
@@ -8598,7 +8605,7 @@
     </row>
     <row r="52" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B52" s="65" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C52" s="65"/>
       <c r="D52" s="65"/>
@@ -8629,12 +8636,12 @@
     </row>
     <row r="54" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B54" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="55" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B55" s="8" t="s">
-        <v>213</v>
+        <v>297</v>
       </c>
     </row>
     <row r="56" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
@@ -8642,10 +8649,10 @@
     </row>
     <row r="57" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B57" s="65" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C57" s="65"/>
       <c r="D57" s="65"/>
@@ -8676,7 +8683,7 @@
     </row>
     <row r="58" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B58" s="65" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C58" s="65"/>
       <c r="D58" s="65"/>
@@ -8707,7 +8714,7 @@
     </row>
     <row r="59" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B59" s="65" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C59" s="65"/>
       <c r="D59" s="65"/>
@@ -8738,7 +8745,7 @@
     </row>
     <row r="60" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B60" s="65" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C60" s="65"/>
       <c r="D60" s="65"/>
@@ -8769,7 +8776,7 @@
     </row>
     <row r="61" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B61" s="65" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C61" s="65"/>
       <c r="D61" s="65"/>
@@ -8800,7 +8807,7 @@
     </row>
     <row r="62" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B62" s="65" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C62" s="65"/>
       <c r="D62" s="65"/>
@@ -8831,7 +8838,7 @@
     </row>
     <row r="63" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B63" s="65" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C63" s="65"/>
       <c r="D63" s="65"/>
@@ -8862,7 +8869,7 @@
     </row>
     <row r="64" spans="1:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B64" s="65" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C64" s="65"/>
       <c r="D64" s="65"/>
@@ -8893,7 +8900,7 @@
     </row>
     <row r="65" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B65" s="65" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C65" s="65"/>
       <c r="D65" s="65"/>
@@ -8924,7 +8931,7 @@
     </row>
     <row r="66" spans="2:28" ht="19.5" x14ac:dyDescent="0.25">
       <c r="B66" s="65" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C66" s="65"/>
       <c r="D66" s="65"/>
@@ -9004,7 +9011,7 @@
   <sheetData>
     <row r="2" spans="1:29" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -9012,16 +9019,16 @@
         <v>15</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C4" s="57"/>
       <c r="D4" s="80" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E4" s="81"/>
       <c r="F4" s="90"/>
       <c r="G4" s="57" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H4" s="57"/>
       <c r="I4" s="57"/>
@@ -9029,22 +9036,22 @@
       <c r="K4" s="57"/>
       <c r="L4" s="57"/>
       <c r="M4" s="80" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="N4" s="81"/>
       <c r="O4" s="81"/>
       <c r="P4" s="90"/>
       <c r="Q4" s="57" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="R4" s="57"/>
       <c r="S4" s="57" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="T4" s="57"/>
       <c r="U4" s="57"/>
       <c r="V4" s="57" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="W4" s="57"/>
       <c r="X4" s="57"/>
@@ -9059,16 +9066,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="113" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C5" s="113"/>
       <c r="D5" s="85" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E5" s="86"/>
       <c r="F5" s="87"/>
       <c r="G5" s="114" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H5" s="115"/>
       <c r="I5" s="115"/>
@@ -9076,22 +9083,22 @@
       <c r="K5" s="115"/>
       <c r="L5" s="116"/>
       <c r="M5" s="117" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N5" s="118"/>
       <c r="O5" s="118"/>
       <c r="P5" s="119"/>
       <c r="Q5" s="121" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="R5" s="121"/>
       <c r="S5" s="110" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="T5" s="111"/>
       <c r="U5" s="112"/>
       <c r="V5" s="73" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="W5" s="73"/>
       <c r="X5" s="73"/>
@@ -9106,16 +9113,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="113" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C6" s="113"/>
       <c r="D6" s="85" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E6" s="86"/>
       <c r="F6" s="87"/>
       <c r="G6" s="114" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H6" s="115"/>
       <c r="I6" s="115"/>
@@ -9123,13 +9130,13 @@
       <c r="K6" s="115"/>
       <c r="L6" s="116"/>
       <c r="M6" s="117" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N6" s="118"/>
       <c r="O6" s="118"/>
       <c r="P6" s="119"/>
       <c r="Q6" s="107" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="R6" s="107"/>
       <c r="S6" s="110">
@@ -9138,7 +9145,7 @@
       <c r="T6" s="111"/>
       <c r="U6" s="112"/>
       <c r="V6" s="73" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="W6" s="73"/>
       <c r="X6" s="73"/>
@@ -9153,11 +9160,11 @@
         <v>3</v>
       </c>
       <c r="B7" s="113" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C7" s="113"/>
       <c r="D7" s="85" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E7" s="86"/>
       <c r="F7" s="87"/>
@@ -9170,22 +9177,22 @@
       <c r="K7" s="115"/>
       <c r="L7" s="116"/>
       <c r="M7" s="117" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="N7" s="118"/>
       <c r="O7" s="118"/>
       <c r="P7" s="119"/>
       <c r="Q7" s="107" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="R7" s="107"/>
       <c r="S7" s="110" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="T7" s="111"/>
       <c r="U7" s="112"/>
       <c r="V7" s="122" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="W7" s="73"/>
       <c r="X7" s="73"/>
@@ -9200,16 +9207,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="113" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C8" s="113"/>
       <c r="D8" s="85" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E8" s="86"/>
       <c r="F8" s="87"/>
       <c r="G8" s="114" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H8" s="115"/>
       <c r="I8" s="115"/>
@@ -9217,13 +9224,13 @@
       <c r="K8" s="115"/>
       <c r="L8" s="116"/>
       <c r="M8" s="117" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N8" s="118"/>
       <c r="O8" s="118"/>
       <c r="P8" s="119"/>
       <c r="Q8" s="107" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="R8" s="107"/>
       <c r="S8" s="120">
@@ -9232,7 +9239,7 @@
       <c r="T8" s="111"/>
       <c r="U8" s="112"/>
       <c r="V8" s="73" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="W8" s="73"/>
       <c r="X8" s="73"/>
@@ -9247,16 +9254,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="113" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C9" s="113"/>
       <c r="D9" s="85" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E9" s="86"/>
       <c r="F9" s="87"/>
       <c r="G9" s="114" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H9" s="115"/>
       <c r="I9" s="115"/>
@@ -9264,13 +9271,13 @@
       <c r="K9" s="115"/>
       <c r="L9" s="116"/>
       <c r="M9" s="117" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="N9" s="118"/>
       <c r="O9" s="118"/>
       <c r="P9" s="119"/>
       <c r="Q9" s="107" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="R9" s="107"/>
       <c r="S9" s="120">
@@ -9279,7 +9286,7 @@
       <c r="T9" s="111"/>
       <c r="U9" s="112"/>
       <c r="V9" s="73" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="W9" s="73"/>
       <c r="X9" s="73"/>
@@ -9294,16 +9301,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="113" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C10" s="113"/>
       <c r="D10" s="85" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E10" s="86"/>
       <c r="F10" s="87"/>
       <c r="G10" s="114" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H10" s="115"/>
       <c r="I10" s="115"/>
@@ -9311,13 +9318,13 @@
       <c r="K10" s="115"/>
       <c r="L10" s="116"/>
       <c r="M10" s="117" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="N10" s="118"/>
       <c r="O10" s="118"/>
       <c r="P10" s="119"/>
       <c r="Q10" s="107" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="R10" s="107"/>
       <c r="S10" s="120">
@@ -9326,7 +9333,7 @@
       <c r="T10" s="111"/>
       <c r="U10" s="112"/>
       <c r="V10" s="73" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="W10" s="73"/>
       <c r="X10" s="73"/>
@@ -9341,16 +9348,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="113" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C11" s="113"/>
       <c r="D11" s="85" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E11" s="86"/>
       <c r="F11" s="87"/>
       <c r="G11" s="114" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H11" s="115"/>
       <c r="I11" s="115"/>
@@ -9358,22 +9365,22 @@
       <c r="K11" s="115"/>
       <c r="L11" s="116"/>
       <c r="M11" s="117" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N11" s="118"/>
       <c r="O11" s="118"/>
       <c r="P11" s="119"/>
       <c r="Q11" s="107" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="R11" s="107"/>
       <c r="S11" s="107" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="T11" s="88"/>
       <c r="U11" s="88"/>
       <c r="V11" s="73" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="W11" s="73"/>
       <c r="X11" s="73"/>
@@ -9385,7 +9392,7 @@
     </row>
     <row r="14" spans="1:29" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6628F8E3-6474-4C2A-BF99-A22F22B12B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0462BC2-052C-4C37-97AA-E2CD02D286CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="306">
   <si>
     <t>SIGNOMALY</t>
   </si>
@@ -2596,6 +2596,24 @@
   </si>
   <si>
     <t>Phần Puzzle UI này sẽ nhìn trực diện vào máy bảo mật, và có nút back ra. Khi bấm sai thì nó sẽ hiển thị: "This is incorrect". UI sẽ như sau: khi người chơi tương tác, camera sẽ zoom vào máy bảo mật và align bên trái, còn nơi nhập mã code sẽ là UI hiển thị phần nhập bên phải.</t>
+  </si>
+  <si>
+    <t>1. X_Object: Chủ yếu là trang trí</t>
+  </si>
+  <si>
+    <t>2. PZ_Object: Liên quan đến mechanic game</t>
+  </si>
+  <si>
+    <t>3. C_Object: Liên quan đến thiết kế level game</t>
+  </si>
+  <si>
+    <t>4. A_PZ/X_Object: Anomaly</t>
+  </si>
+  <si>
+    <t>3. FILE NAME ASSETS</t>
+  </si>
+  <si>
+    <t>5. Number_C: Variables of 1 single object</t>
   </si>
 </sst>
 </file>
@@ -2882,7 +2900,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3224,6 +3242,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3695,7 +3726,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="573881" y="12944475"/>
+          <a:off x="573881" y="13611225"/>
           <a:ext cx="3983858" cy="2247900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6846,7 +6877,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A2:T37"/>
+  <dimension ref="A2:T45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
@@ -7187,14 +7218,14 @@
       </c>
       <c r="T14" s="88"/>
     </row>
-    <row r="15" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A15" s="35">
         <v>9</v>
       </c>
-      <c r="B15" s="91" t="s">
+      <c r="B15" s="125" t="s">
         <v>182</v>
       </c>
-      <c r="C15" s="91"/>
+      <c r="C15" s="126"/>
       <c r="D15" s="85" t="s">
         <v>97</v>
       </c>
@@ -7721,10 +7752,10 @@
       <c r="A34" s="11">
         <v>1</v>
       </c>
-      <c r="B34" s="84" t="s">
+      <c r="B34" s="127" t="s">
         <v>275</v>
       </c>
-      <c r="C34" s="84"/>
+      <c r="C34" s="128"/>
       <c r="D34" s="85" t="s">
         <v>278</v>
       </c>
@@ -7749,7 +7780,7 @@
       <c r="E35" s="86"/>
       <c r="F35" s="87"/>
       <c r="G35" s="88" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H35" s="88"/>
     </row>
@@ -7767,7 +7798,7 @@
       <c r="E36" s="86"/>
       <c r="F36" s="87"/>
       <c r="G36" s="89" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H36" s="88"/>
     </row>
@@ -7788,6 +7819,36 @@
         <v>216</v>
       </c>
       <c r="H37" s="88"/>
+    </row>
+    <row r="39" spans="1:8" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B39" s="8" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B41" s="129" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B42" s="129" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B43" s="129" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B44" s="129" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B45" s="129" t="s">
+        <v>305</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="153">

--- a/Signomaly/GDD/Signomaly.xlsx
+++ b/Signomaly/GDD/Signomaly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity_GameMaking\0. Projects\170426_LD_GameJam59\LD59_Signomaly\Signomaly\GDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0462BC2-052C-4C37-97AA-E2CD02D286CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA87CD5F-DCEF-4E0F-ABD1-E27A3FEECE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{93CE968A-0C34-467A-AF09-AD4AE7C1ADD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Gameplay_Overview" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="304">
   <si>
     <t>SIGNOMALY</t>
   </si>
@@ -1333,15 +1333,6 @@
     <t>2.3. IN-GAME</t>
   </si>
   <si>
-    <t>- Với mốc A: Tinh chỉnh hex màu tường (sàn, trần) từ màu của texture dần sang màu đỏ thẩm; Saturation: +7%</t>
-  </si>
-  <si>
-    <t>- Với mốc B: Tinh chỉnh hex màu tường (sàn, trần) từ màu của texture càng dần sang màu đỏ thẩm; Saturation: +12%</t>
-  </si>
-  <si>
-    <t>- Với mốc C: Tinh chỉnh hex màu tường (sàn, trần) từ màu của texture thành màu đỏ thẩm; Saturation: +17%</t>
-  </si>
-  <si>
     <t>2.3.1. Biến đổi môi trường</t>
   </si>
   <si>
@@ -1355,30 +1346,6 @@
   </si>
   <si>
     <t>Khi puzzle giải đố được kích hoạt và người chơi nhấn giữ phím "E" thì sẽ luôn giữ ở dạng biến thể A. Sau khi hoàn thành nhấn giữ sẽ chuyển hoàn toàn sang biến thể B (Optional)</t>
-  </si>
-  <si>
-    <r>
-      <t>Mốc thời gian chính (Timelapse):</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 15 phút</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>. Chia ra 3 mốc thời gian như sau: A=B=C= 5 phút.</t>
-    </r>
   </si>
   <si>
     <t>2.1. Menu Screen UI</t>
@@ -2614,6 +2581,33 @@
   </si>
   <si>
     <t>5. Number_C: Variables of 1 single object</t>
+  </si>
+  <si>
+    <r>
+      <t>Mốc thời gian chính (Timelapse):</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 15 phút</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Chia ra 2 mốc thời gian như sau: A=B= 15/2.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sẽ biến đổi model (tường, sàn) bình thường A sang model Anomaly B.</t>
   </si>
 </sst>
 </file>
@@ -2900,7 +2894,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2945,7 +2939,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -4659,29 +4652,29 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:26" ht="46.5" x14ac:dyDescent="0.7">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
     </row>
     <row r="3" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
@@ -4705,104 +4698,104 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="44" t="s">
-        <v>173</v>
-      </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
+      <c r="B12" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
     </row>
     <row r="13" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="43"/>
-      <c r="T13" s="43"/>
-      <c r="U13" s="43"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
+      <c r="R13" s="42"/>
+      <c r="S13" s="42"/>
+      <c r="T13" s="42"/>
+      <c r="U13" s="42"/>
     </row>
     <row r="14" spans="1:26" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="39"/>
-      <c r="P14" s="39"/>
-      <c r="Q14" s="39"/>
-      <c r="R14" s="39"/>
-      <c r="S14" s="39"/>
-      <c r="T14" s="39"/>
-      <c r="U14" s="39"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="38"/>
+      <c r="P14" s="38"/>
+      <c r="Q14" s="38"/>
+      <c r="R14" s="38"/>
+      <c r="S14" s="38"/>
+      <c r="T14" s="38"/>
+      <c r="U14" s="38"/>
     </row>
     <row r="15" spans="1:26" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
@@ -4818,28 +4811,28 @@
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:26" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="40"/>
-      <c r="R16" s="40"/>
-      <c r="S16" s="40"/>
-      <c r="T16" s="40"/>
-      <c r="U16" s="40"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="39"/>
+      <c r="R16" s="39"/>
+      <c r="S16" s="39"/>
+      <c r="T16" s="39"/>
+      <c r="U16" s="39"/>
       <c r="V16" s="6"/>
       <c r="W16" s="6"/>
       <c r="X16" s="6"/>
@@ -4847,100 +4840,100 @@
       <c r="Z16" s="6"/>
     </row>
     <row r="17" spans="1:21" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="40"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="40"/>
-      <c r="M17" s="40"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="40"/>
-      <c r="P17" s="40"/>
-      <c r="Q17" s="40"/>
-      <c r="R17" s="40"/>
-      <c r="S17" s="40"/>
-      <c r="T17" s="40"/>
-      <c r="U17" s="40"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="39"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="39"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="39"/>
+      <c r="R17" s="39"/>
+      <c r="S17" s="39"/>
+      <c r="T17" s="39"/>
+      <c r="U17" s="39"/>
     </row>
     <row r="18" spans="1:21" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="39"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="39"/>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="39"/>
-      <c r="R18" s="39"/>
-      <c r="S18" s="39"/>
-      <c r="T18" s="39"/>
-      <c r="U18" s="39"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="38"/>
+      <c r="R18" s="38"/>
+      <c r="S18" s="38"/>
+      <c r="T18" s="38"/>
+      <c r="U18" s="38"/>
     </row>
     <row r="19" spans="1:21" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="42"/>
-      <c r="S19" s="42"/>
-      <c r="T19" s="42"/>
-      <c r="U19" s="42"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="41"/>
+      <c r="P19" s="41"/>
+      <c r="Q19" s="41"/>
+      <c r="R19" s="41"/>
+      <c r="S19" s="41"/>
+      <c r="T19" s="41"/>
+      <c r="U19" s="41"/>
     </row>
     <row r="20" spans="1:21" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="45" t="s">
-        <v>174</v>
-      </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="45"/>
-      <c r="M20" s="45"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="45"/>
-      <c r="P20" s="45"/>
-      <c r="Q20" s="45"/>
-      <c r="R20" s="45"/>
-      <c r="S20" s="45"/>
-      <c r="T20" s="45"/>
-      <c r="U20" s="45"/>
+      <c r="B20" s="44" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="44"/>
+      <c r="M20" s="44"/>
+      <c r="N20" s="44"/>
+      <c r="O20" s="44"/>
+      <c r="P20" s="44"/>
+      <c r="Q20" s="44"/>
+      <c r="R20" s="44"/>
+      <c r="S20" s="44"/>
+      <c r="T20" s="44"/>
+      <c r="U20" s="44"/>
     </row>
     <row r="22" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
@@ -5080,7 +5073,7 @@
   <sheetData>
     <row r="2" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B2" s="8"/>
     </row>
@@ -5088,364 +5081,364 @@
       <c r="B4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57" t="s">
+      <c r="D4" s="56"/>
+      <c r="E4" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="57"/>
-      <c r="G4" s="48" t="s">
+      <c r="F4" s="56"/>
+      <c r="G4" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="48"/>
-      <c r="M4" s="48" t="s">
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="W4" s="48"/>
-      <c r="X4" s="48"/>
-      <c r="Y4" s="48"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="47"/>
+      <c r="T4" s="47"/>
+      <c r="U4" s="47"/>
+      <c r="V4" s="47"/>
+      <c r="W4" s="47"/>
+      <c r="X4" s="47"/>
+      <c r="Y4" s="47"/>
     </row>
     <row r="5" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11">
         <v>1</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="54"/>
-      <c r="E5" s="55" t="s">
+      <c r="D5" s="53"/>
+      <c r="E5" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="55"/>
-      <c r="G5" s="53" t="s">
+      <c r="F5" s="54"/>
+      <c r="G5" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="49" t="s">
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
-      <c r="W5" s="49"/>
-      <c r="X5" s="49"/>
-      <c r="Y5" s="49"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="48"/>
+      <c r="S5" s="48"/>
+      <c r="T5" s="48"/>
+      <c r="U5" s="48"/>
+      <c r="V5" s="48"/>
+      <c r="W5" s="48"/>
+      <c r="X5" s="48"/>
+      <c r="Y5" s="48"/>
     </row>
     <row r="6" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11">
         <v>2</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="55" t="s">
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="55"/>
-      <c r="G6" s="53" t="s">
+      <c r="F6" s="54"/>
+      <c r="G6" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="50" t="s">
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="N6" s="49"/>
-      <c r="O6" s="49"/>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49"/>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
-      <c r="V6" s="49"/>
-      <c r="W6" s="49"/>
-      <c r="X6" s="49"/>
-      <c r="Y6" s="49"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="48"/>
+      <c r="U6" s="48"/>
+      <c r="V6" s="48"/>
+      <c r="W6" s="48"/>
+      <c r="X6" s="48"/>
+      <c r="Y6" s="48"/>
     </row>
     <row r="7" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11">
         <v>3</v>
       </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="55" t="s">
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="55"/>
-      <c r="G7" s="53" t="s">
+      <c r="F7" s="54"/>
+      <c r="G7" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="51" t="s">
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="51"/>
-      <c r="T7" s="51"/>
-      <c r="U7" s="51"/>
-      <c r="V7" s="51"/>
-      <c r="W7" s="51"/>
-      <c r="X7" s="51"/>
-      <c r="Y7" s="51"/>
+      <c r="N7" s="50"/>
+      <c r="O7" s="50"/>
+      <c r="P7" s="50"/>
+      <c r="Q7" s="50"/>
+      <c r="R7" s="50"/>
+      <c r="S7" s="50"/>
+      <c r="T7" s="50"/>
+      <c r="U7" s="50"/>
+      <c r="V7" s="50"/>
+      <c r="W7" s="50"/>
+      <c r="X7" s="50"/>
+      <c r="Y7" s="50"/>
     </row>
     <row r="8" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11">
         <v>4</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="54"/>
-      <c r="E8" s="55" t="s">
+      <c r="D8" s="53"/>
+      <c r="E8" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="55"/>
-      <c r="G8" s="53" t="s">
+      <c r="F8" s="54"/>
+      <c r="G8" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="52" t="s">
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="N8" s="51"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="51"/>
-      <c r="R8" s="51"/>
-      <c r="S8" s="51"/>
-      <c r="T8" s="51"/>
-      <c r="U8" s="51"/>
-      <c r="V8" s="51"/>
-      <c r="W8" s="51"/>
-      <c r="X8" s="51"/>
-      <c r="Y8" s="51"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="50"/>
+      <c r="P8" s="50"/>
+      <c r="Q8" s="50"/>
+      <c r="R8" s="50"/>
+      <c r="S8" s="50"/>
+      <c r="T8" s="50"/>
+      <c r="U8" s="50"/>
+      <c r="V8" s="50"/>
+      <c r="W8" s="50"/>
+      <c r="X8" s="50"/>
+      <c r="Y8" s="50"/>
     </row>
     <row r="9" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11">
         <v>5</v>
       </c>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="55" t="s">
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="55"/>
-      <c r="G9" s="53" t="s">
+      <c r="F9" s="54"/>
+      <c r="G9" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="52" t="s">
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
+      <c r="K9" s="52"/>
+      <c r="L9" s="52"/>
+      <c r="M9" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="51"/>
-      <c r="O9" s="51"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="51"/>
-      <c r="R9" s="51"/>
-      <c r="S9" s="51"/>
-      <c r="T9" s="51"/>
-      <c r="U9" s="51"/>
-      <c r="V9" s="51"/>
-      <c r="W9" s="51"/>
-      <c r="X9" s="51"/>
-      <c r="Y9" s="51"/>
+      <c r="N9" s="50"/>
+      <c r="O9" s="50"/>
+      <c r="P9" s="50"/>
+      <c r="Q9" s="50"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="50"/>
+      <c r="T9" s="50"/>
+      <c r="U9" s="50"/>
+      <c r="V9" s="50"/>
+      <c r="W9" s="50"/>
+      <c r="X9" s="50"/>
+      <c r="Y9" s="50"/>
     </row>
     <row r="10" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="11">
         <v>6</v>
       </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="55" t="s">
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="55"/>
-      <c r="G10" s="53" t="s">
+      <c r="F10" s="54"/>
+      <c r="G10" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="52" t="s">
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="52"/>
+      <c r="M10" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="N10" s="51"/>
-      <c r="O10" s="51"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="51"/>
-      <c r="R10" s="51"/>
-      <c r="S10" s="51"/>
-      <c r="T10" s="51"/>
-      <c r="U10" s="51"/>
-      <c r="V10" s="51"/>
-      <c r="W10" s="51"/>
-      <c r="X10" s="51"/>
-      <c r="Y10" s="51"/>
+      <c r="N10" s="50"/>
+      <c r="O10" s="50"/>
+      <c r="P10" s="50"/>
+      <c r="Q10" s="50"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="50"/>
+      <c r="T10" s="50"/>
+      <c r="U10" s="50"/>
+      <c r="V10" s="50"/>
+      <c r="W10" s="50"/>
+      <c r="X10" s="50"/>
+      <c r="Y10" s="50"/>
     </row>
     <row r="11" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="11">
         <v>7</v>
       </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="55" t="s">
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="55"/>
-      <c r="G11" s="53" t="s">
+      <c r="F11" s="54"/>
+      <c r="G11" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="53"/>
-      <c r="M11" s="51" t="s">
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="51"/>
-      <c r="O11" s="51"/>
-      <c r="P11" s="51"/>
-      <c r="Q11" s="51"/>
-      <c r="R11" s="51"/>
-      <c r="S11" s="51"/>
-      <c r="T11" s="51"/>
-      <c r="U11" s="51"/>
-      <c r="V11" s="51"/>
-      <c r="W11" s="51"/>
-      <c r="X11" s="51"/>
-      <c r="Y11" s="51"/>
+      <c r="N11" s="50"/>
+      <c r="O11" s="50"/>
+      <c r="P11" s="50"/>
+      <c r="Q11" s="50"/>
+      <c r="R11" s="50"/>
+      <c r="S11" s="50"/>
+      <c r="T11" s="50"/>
+      <c r="U11" s="50"/>
+      <c r="V11" s="50"/>
+      <c r="W11" s="50"/>
+      <c r="X11" s="50"/>
+      <c r="Y11" s="50"/>
     </row>
     <row r="12" spans="1:25" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="11">
         <v>8</v>
       </c>
-      <c r="C12" s="54" t="s">
+      <c r="C12" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="54"/>
-      <c r="E12" s="55" t="s">
+      <c r="D12" s="53"/>
+      <c r="E12" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="55"/>
-      <c r="G12" s="53" t="s">
+      <c r="F12" s="54"/>
+      <c r="G12" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="51" t="s">
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="52"/>
+      <c r="L12" s="52"/>
+      <c r="M12" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="N12" s="51"/>
-      <c r="O12" s="51"/>
-      <c r="P12" s="51"/>
-      <c r="Q12" s="51"/>
-      <c r="R12" s="51"/>
-      <c r="S12" s="51"/>
-      <c r="T12" s="51"/>
-      <c r="U12" s="51"/>
-      <c r="V12" s="51"/>
-      <c r="W12" s="51"/>
-      <c r="X12" s="51"/>
-      <c r="Y12" s="51"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="50"/>
+      <c r="W12" s="50"/>
+      <c r="X12" s="50"/>
+      <c r="Y12" s="50"/>
     </row>
     <row r="46" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B49" s="56" t="s">
+      <c r="B49" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="56"/>
-      <c r="D49" s="56"/>
-      <c r="E49" s="56"/>
-      <c r="F49" s="56"/>
-      <c r="G49" s="56"/>
-      <c r="H49" s="56"/>
-      <c r="I49" s="56"/>
-      <c r="J49" s="56"/>
-      <c r="K49" s="56"/>
-      <c r="L49" s="56"/>
-      <c r="M49" s="56"/>
-      <c r="N49" s="56"/>
-      <c r="O49" s="56"/>
-      <c r="P49" s="56"/>
-      <c r="Q49" s="56"/>
-      <c r="R49" s="56"/>
-      <c r="S49" s="56"/>
-      <c r="T49" s="56"/>
-      <c r="U49" s="56"/>
-      <c r="V49" s="56"/>
+      <c r="C49" s="55"/>
+      <c r="D49" s="55"/>
+      <c r="E49" s="55"/>
+      <c r="F49" s="55"/>
+      <c r="G49" s="55"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="55"/>
+      <c r="J49" s="55"/>
+      <c r="K49" s="55"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="55"/>
+      <c r="N49" s="55"/>
+      <c r="O49" s="55"/>
+      <c r="P49" s="55"/>
+      <c r="Q49" s="55"/>
+      <c r="R49" s="55"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="55"/>
+      <c r="U49" s="55"/>
+      <c r="V49" s="55"/>
     </row>
     <row r="50" spans="2:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B50" s="56"/>
-      <c r="C50" s="56"/>
-      <c r="D50" s="56"/>
-      <c r="E50" s="56"/>
-      <c r="F50" s="56"/>
-      <c r="G50" s="56"/>
-      <c r="H50" s="56"/>
-      <c r="I50" s="56"/>
-      <c r="J50" s="56"/>
-      <c r="K50" s="56"/>
-      <c r="L50" s="56"/>
-      <c r="M50" s="56"/>
-      <c r="N50" s="56"/>
-      <c r="O50" s="56"/>
-      <c r="P50" s="56"/>
-      <c r="Q50" s="56"/>
-      <c r="R50" s="56"/>
-      <c r="S50" s="56"/>
-      <c r="T50" s="56"/>
-      <c r="U50" s="56"/>
-      <c r="V50" s="56"/>
+      <c r="B50" s="55"/>
+      <c r="C50" s="55"/>
+      <c r="D50" s="55"/>
+      <c r="E50" s="55"/>
+      <c r="F50" s="55"/>
+      <c r="G50" s="55"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="55"/>
+      <c r="J50" s="55"/>
+      <c r="K50" s="55"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="55"/>
+      <c r="N50" s="55"/>
+      <c r="O50" s="55"/>
+      <c r="P50" s="55"/>
+      <c r="Q50" s="55"/>
+      <c r="R50" s="55"/>
+      <c r="S50" s="55"/>
+      <c r="T50" s="55"/>
+      <c r="U50" s="55"/>
+      <c r="V50" s="55"/>
       <c r="W50" s="8"/>
       <c r="X50" s="8"/>
       <c r="Y50" s="8"/>
@@ -5505,7 +5498,7 @@
   <sheetData>
     <row r="2" spans="1:28" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
@@ -5514,20 +5507,20 @@
       </c>
     </row>
     <row r="8" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L8" s="62" t="s">
+      <c r="L8" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="M8" s="63"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="63"/>
-      <c r="P8" s="63"/>
-      <c r="Q8" s="63"/>
-      <c r="R8" s="63"/>
-      <c r="S8" s="63"/>
-      <c r="T8" s="63"/>
-      <c r="U8" s="63"/>
-      <c r="V8" s="63"/>
-      <c r="W8" s="63"/>
+      <c r="M8" s="62"/>
+      <c r="N8" s="62"/>
+      <c r="O8" s="62"/>
+      <c r="P8" s="62"/>
+      <c r="Q8" s="62"/>
+      <c r="R8" s="62"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="62"/>
+      <c r="U8" s="62"/>
+      <c r="V8" s="62"/>
+      <c r="W8" s="62"/>
     </row>
     <row r="9" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="L9" s="7"/>
@@ -5544,25 +5537,25 @@
       <c r="W9" s="7"/>
     </row>
     <row r="10" spans="1:28" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L10" s="65" t="s">
+      <c r="L10" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="41"/>
-      <c r="R10" s="41"/>
-      <c r="S10" s="41"/>
-      <c r="T10" s="41"/>
-      <c r="U10" s="41"/>
-      <c r="V10" s="41"/>
-      <c r="W10" s="41"/>
-      <c r="X10" s="41"/>
-      <c r="Y10" s="41"/>
-      <c r="Z10" s="41"/>
-      <c r="AA10" s="41"/>
-      <c r="AB10" s="41"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
+      <c r="P10" s="40"/>
+      <c r="Q10" s="40"/>
+      <c r="R10" s="40"/>
+      <c r="S10" s="40"/>
+      <c r="T10" s="40"/>
+      <c r="U10" s="40"/>
+      <c r="V10" s="40"/>
+      <c r="W10" s="40"/>
+      <c r="X10" s="40"/>
+      <c r="Y10" s="40"/>
+      <c r="Z10" s="40"/>
+      <c r="AA10" s="40"/>
+      <c r="AB10" s="40"/>
     </row>
     <row r="11" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="L11" s="7"/>
@@ -5579,25 +5572,25 @@
       <c r="W11" s="7"/>
     </row>
     <row r="12" spans="1:28" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L12" s="65" t="s">
+      <c r="L12" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="M12" s="42"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="42"/>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="42"/>
-      <c r="S12" s="42"/>
-      <c r="T12" s="42"/>
-      <c r="U12" s="42"/>
-      <c r="V12" s="42"/>
-      <c r="W12" s="42"/>
-      <c r="X12" s="42"/>
-      <c r="Y12" s="42"/>
-      <c r="Z12" s="42"/>
-      <c r="AA12" s="42"/>
-      <c r="AB12" s="42"/>
+      <c r="M12" s="41"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="41"/>
+      <c r="P12" s="41"/>
+      <c r="Q12" s="41"/>
+      <c r="R12" s="41"/>
+      <c r="S12" s="41"/>
+      <c r="T12" s="41"/>
+      <c r="U12" s="41"/>
+      <c r="V12" s="41"/>
+      <c r="W12" s="41"/>
+      <c r="X12" s="41"/>
+      <c r="Y12" s="41"/>
+      <c r="Z12" s="41"/>
+      <c r="AA12" s="41"/>
+      <c r="AB12" s="41"/>
     </row>
     <row r="13" spans="1:28" ht="19.5" x14ac:dyDescent="0.3">
       <c r="S13" s="12"/>
@@ -5611,36 +5604,36 @@
       <c r="B16" s="8"/>
     </row>
     <row r="17" spans="2:29" ht="157.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="123" t="s">
-        <v>298</v>
-      </c>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="60"/>
-      <c r="L17" s="60"/>
-      <c r="M17" s="60"/>
-      <c r="N17" s="60"/>
-      <c r="O17" s="60"/>
-      <c r="P17" s="60"/>
-      <c r="Q17" s="60"/>
-      <c r="R17" s="60"/>
-      <c r="S17" s="60"/>
-      <c r="T17" s="60"/>
-      <c r="U17" s="60"/>
-      <c r="V17" s="60"/>
-      <c r="W17" s="60"/>
-      <c r="X17" s="60"/>
-      <c r="Y17" s="60"/>
-      <c r="Z17" s="60"/>
-      <c r="AA17" s="60"/>
-      <c r="AB17" s="60"/>
-      <c r="AC17" s="60"/>
+      <c r="B17" s="122" t="s">
+        <v>294</v>
+      </c>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="59"/>
+      <c r="K17" s="59"/>
+      <c r="L17" s="59"/>
+      <c r="M17" s="59"/>
+      <c r="N17" s="59"/>
+      <c r="O17" s="59"/>
+      <c r="P17" s="59"/>
+      <c r="Q17" s="59"/>
+      <c r="R17" s="59"/>
+      <c r="S17" s="59"/>
+      <c r="T17" s="59"/>
+      <c r="U17" s="59"/>
+      <c r="V17" s="59"/>
+      <c r="W17" s="59"/>
+      <c r="X17" s="59"/>
+      <c r="Y17" s="59"/>
+      <c r="Z17" s="59"/>
+      <c r="AA17" s="59"/>
+      <c r="AB17" s="59"/>
+      <c r="AC17" s="59"/>
     </row>
     <row r="18" spans="2:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="15"/>
@@ -5675,41 +5668,41 @@
       <c r="C20" s="10"/>
     </row>
     <row r="22" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="P22" s="59" t="s">
+      <c r="P22" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="Q22" s="59"/>
-      <c r="R22" s="59"/>
-      <c r="S22" s="59"/>
-      <c r="T22" s="59"/>
-      <c r="U22" s="59"/>
-      <c r="V22" s="59"/>
-      <c r="W22" s="59"/>
-      <c r="X22" s="59"/>
-      <c r="Y22" s="59"/>
-      <c r="Z22" s="59"/>
-      <c r="AA22" s="59"/>
-      <c r="AB22" s="59"/>
+      <c r="Q22" s="58"/>
+      <c r="R22" s="58"/>
+      <c r="S22" s="58"/>
+      <c r="T22" s="58"/>
+      <c r="U22" s="58"/>
+      <c r="V22" s="58"/>
+      <c r="W22" s="58"/>
+      <c r="X22" s="58"/>
+      <c r="Y22" s="58"/>
+      <c r="Z22" s="58"/>
+      <c r="AA22" s="58"/>
+      <c r="AB22" s="58"/>
     </row>
     <row r="23" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P23" s="12"/>
     </row>
     <row r="24" spans="2:29" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P24" s="61" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q24" s="64"/>
-      <c r="R24" s="64"/>
-      <c r="S24" s="64"/>
-      <c r="T24" s="64"/>
-      <c r="U24" s="64"/>
-      <c r="V24" s="64"/>
-      <c r="W24" s="64"/>
-      <c r="X24" s="64"/>
-      <c r="Y24" s="64"/>
-      <c r="Z24" s="64"/>
-      <c r="AA24" s="64"/>
-      <c r="AB24" s="64"/>
+      <c r="P24" s="60" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q24" s="63"/>
+      <c r="R24" s="63"/>
+      <c r="S24" s="63"/>
+      <c r="T24" s="63"/>
+      <c r="U24" s="63"/>
+      <c r="V24" s="63"/>
+      <c r="W24" s="63"/>
+      <c r="X24" s="63"/>
+      <c r="Y24" s="63"/>
+      <c r="Z24" s="63"/>
+      <c r="AA24" s="63"/>
+      <c r="AB24" s="63"/>
     </row>
     <row r="25" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P25" s="19"/>
@@ -5727,21 +5720,21 @@
       <c r="AB25" s="17"/>
     </row>
     <row r="26" spans="2:29" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P26" s="124" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q26" s="61"/>
-      <c r="R26" s="61"/>
-      <c r="S26" s="61"/>
-      <c r="T26" s="61"/>
-      <c r="U26" s="61"/>
-      <c r="V26" s="61"/>
-      <c r="W26" s="61"/>
-      <c r="X26" s="61"/>
-      <c r="Y26" s="61"/>
-      <c r="Z26" s="61"/>
-      <c r="AA26" s="61"/>
-      <c r="AB26" s="61"/>
+      <c r="P26" s="123" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q26" s="60"/>
+      <c r="R26" s="60"/>
+      <c r="S26" s="60"/>
+      <c r="T26" s="60"/>
+      <c r="U26" s="60"/>
+      <c r="V26" s="60"/>
+      <c r="W26" s="60"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="60"/>
+      <c r="Z26" s="60"/>
+      <c r="AA26" s="60"/>
+      <c r="AB26" s="60"/>
     </row>
     <row r="27" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="P27" s="17"/>
@@ -5759,21 +5752,21 @@
       <c r="AB27" s="17"/>
     </row>
     <row r="28" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="P28" s="59" t="s">
+      <c r="P28" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="Q28" s="59"/>
-      <c r="R28" s="59"/>
-      <c r="S28" s="59"/>
-      <c r="T28" s="59"/>
-      <c r="U28" s="59"/>
-      <c r="V28" s="59"/>
-      <c r="W28" s="59"/>
-      <c r="X28" s="59"/>
-      <c r="Y28" s="59"/>
-      <c r="Z28" s="59"/>
-      <c r="AA28" s="59"/>
-      <c r="AB28" s="59"/>
+      <c r="Q28" s="58"/>
+      <c r="R28" s="58"/>
+      <c r="S28" s="58"/>
+      <c r="T28" s="58"/>
+      <c r="U28" s="58"/>
+      <c r="V28" s="58"/>
+      <c r="W28" s="58"/>
+      <c r="X28" s="58"/>
+      <c r="Y28" s="58"/>
+      <c r="Z28" s="58"/>
+      <c r="AA28" s="58"/>
+      <c r="AB28" s="58"/>
     </row>
     <row r="29" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P29" s="12"/>
@@ -5819,38 +5812,38 @@
       <c r="AB35" s="12"/>
     </row>
     <row r="36" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P36" s="41" t="s">
+      <c r="P36" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="41"/>
-      <c r="S36" s="41"/>
-      <c r="T36" s="41"/>
-      <c r="U36" s="41"/>
-      <c r="V36" s="41"/>
-      <c r="W36" s="41"/>
-      <c r="X36" s="41"/>
-      <c r="Y36" s="41"/>
-      <c r="Z36" s="41"/>
-      <c r="AA36" s="41"/>
-      <c r="AB36" s="41"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="40"/>
+      <c r="S36" s="40"/>
+      <c r="T36" s="40"/>
+      <c r="U36" s="40"/>
+      <c r="V36" s="40"/>
+      <c r="W36" s="40"/>
+      <c r="X36" s="40"/>
+      <c r="Y36" s="40"/>
+      <c r="Z36" s="40"/>
+      <c r="AA36" s="40"/>
+      <c r="AB36" s="40"/>
     </row>
     <row r="38" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B38" s="66" t="s">
+      <c r="B38" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="66"/>
-      <c r="D38" s="66"/>
-      <c r="E38" s="66"/>
-      <c r="F38" s="66"/>
-      <c r="G38" s="66"/>
-      <c r="H38" s="66"/>
-      <c r="I38" s="66"/>
-      <c r="J38" s="66"/>
-      <c r="K38" s="66"/>
-      <c r="L38" s="66"/>
-      <c r="M38" s="66"/>
-      <c r="N38" s="66"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="65"/>
+      <c r="J38" s="65"/>
+      <c r="K38" s="65"/>
+      <c r="L38" s="65"/>
+      <c r="M38" s="65"/>
+      <c r="N38" s="65"/>
       <c r="P38" s="8" t="s">
         <v>57</v>
       </c>
@@ -5868,22 +5861,22 @@
       <c r="AB38" s="12"/>
     </row>
     <row r="39" spans="2:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P39" s="65" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q39" s="65"/>
-      <c r="R39" s="65"/>
-      <c r="S39" s="65"/>
-      <c r="T39" s="65"/>
-      <c r="U39" s="65"/>
-      <c r="V39" s="65"/>
-      <c r="W39" s="65"/>
-      <c r="X39" s="65"/>
-      <c r="Y39" s="65"/>
-      <c r="Z39" s="65"/>
-      <c r="AA39" s="65"/>
-      <c r="AB39" s="65"/>
-      <c r="AC39" s="29"/>
+      <c r="P39" s="64" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q39" s="64"/>
+      <c r="R39" s="64"/>
+      <c r="S39" s="64"/>
+      <c r="T39" s="64"/>
+      <c r="U39" s="64"/>
+      <c r="V39" s="64"/>
+      <c r="W39" s="64"/>
+      <c r="X39" s="64"/>
+      <c r="Y39" s="64"/>
+      <c r="Z39" s="64"/>
+      <c r="AA39" s="64"/>
+      <c r="AB39" s="64"/>
+      <c r="AC39" s="28"/>
     </row>
     <row r="40" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P40" s="12" t="s">
@@ -5896,22 +5889,22 @@
       </c>
     </row>
     <row r="42" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="P42" s="59" t="s">
+      <c r="P42" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="Q42" s="59"/>
-      <c r="R42" s="59"/>
-      <c r="S42" s="59"/>
-      <c r="T42" s="59"/>
-      <c r="U42" s="59"/>
-      <c r="V42" s="59"/>
-      <c r="W42" s="59"/>
-      <c r="X42" s="59"/>
-      <c r="Y42" s="59"/>
-      <c r="Z42" s="59"/>
-      <c r="AA42" s="59"/>
-      <c r="AB42" s="59"/>
-      <c r="AC42" s="59"/>
+      <c r="Q42" s="58"/>
+      <c r="R42" s="58"/>
+      <c r="S42" s="58"/>
+      <c r="T42" s="58"/>
+      <c r="U42" s="58"/>
+      <c r="V42" s="58"/>
+      <c r="W42" s="58"/>
+      <c r="X42" s="58"/>
+      <c r="Y42" s="58"/>
+      <c r="Z42" s="58"/>
+      <c r="AA42" s="58"/>
+      <c r="AB42" s="58"/>
+      <c r="AC42" s="58"/>
     </row>
     <row r="43" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P43" s="12" t="s">
@@ -5924,22 +5917,22 @@
       </c>
     </row>
     <row r="45" spans="2:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P45" s="41" t="s">
+      <c r="P45" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="Q45" s="41"/>
-      <c r="R45" s="41"/>
-      <c r="S45" s="41"/>
-      <c r="T45" s="41"/>
-      <c r="U45" s="41"/>
-      <c r="V45" s="41"/>
-      <c r="W45" s="41"/>
-      <c r="X45" s="41"/>
-      <c r="Y45" s="41"/>
-      <c r="Z45" s="41"/>
-      <c r="AA45" s="41"/>
-      <c r="AB45" s="41"/>
-      <c r="AC45" s="30"/>
+      <c r="Q45" s="40"/>
+      <c r="R45" s="40"/>
+      <c r="S45" s="40"/>
+      <c r="T45" s="40"/>
+      <c r="U45" s="40"/>
+      <c r="V45" s="40"/>
+      <c r="W45" s="40"/>
+      <c r="X45" s="40"/>
+      <c r="Y45" s="40"/>
+      <c r="Z45" s="40"/>
+      <c r="AA45" s="40"/>
+      <c r="AB45" s="40"/>
+      <c r="AC45" s="29"/>
     </row>
     <row r="46" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P46" s="12" t="s">
@@ -5947,41 +5940,41 @@
       </c>
     </row>
     <row r="47" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B47" s="67" t="s">
+      <c r="B47" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="C47" s="67"/>
-      <c r="D47" s="67"/>
-      <c r="E47" s="67"/>
-      <c r="F47" s="67"/>
-      <c r="G47" s="67"/>
-      <c r="H47" s="67"/>
-      <c r="I47" s="67"/>
-      <c r="J47" s="67"/>
-      <c r="K47" s="67"/>
-      <c r="L47" s="67"/>
-      <c r="M47" s="67"/>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="66"/>
+      <c r="L47" s="66"/>
+      <c r="M47" s="66"/>
       <c r="P47" s="8" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="48" spans="2:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P48" s="65" t="s">
+      <c r="P48" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="Q48" s="65"/>
-      <c r="R48" s="65"/>
-      <c r="S48" s="65"/>
-      <c r="T48" s="65"/>
-      <c r="U48" s="65"/>
-      <c r="V48" s="65"/>
-      <c r="W48" s="65"/>
-      <c r="X48" s="65"/>
-      <c r="Y48" s="65"/>
-      <c r="Z48" s="65"/>
-      <c r="AA48" s="65"/>
-      <c r="AB48" s="65"/>
-      <c r="AC48" s="27"/>
+      <c r="Q48" s="64"/>
+      <c r="R48" s="64"/>
+      <c r="S48" s="64"/>
+      <c r="T48" s="64"/>
+      <c r="U48" s="64"/>
+      <c r="V48" s="64"/>
+      <c r="W48" s="64"/>
+      <c r="X48" s="64"/>
+      <c r="Y48" s="64"/>
+      <c r="Z48" s="64"/>
+      <c r="AA48" s="64"/>
+      <c r="AB48" s="64"/>
+      <c r="AC48" s="26"/>
     </row>
     <row r="49" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P49" s="12" t="s">
@@ -5994,21 +5987,21 @@
       </c>
     </row>
     <row r="51" spans="2:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P51" s="41" t="s">
+      <c r="P51" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="Q51" s="41"/>
-      <c r="R51" s="41"/>
-      <c r="S51" s="41"/>
-      <c r="T51" s="41"/>
-      <c r="U51" s="41"/>
-      <c r="V51" s="41"/>
-      <c r="W51" s="41"/>
-      <c r="X51" s="41"/>
-      <c r="Y51" s="41"/>
-      <c r="Z51" s="41"/>
-      <c r="AA51" s="41"/>
-      <c r="AB51" s="41"/>
+      <c r="Q51" s="40"/>
+      <c r="R51" s="40"/>
+      <c r="S51" s="40"/>
+      <c r="T51" s="40"/>
+      <c r="U51" s="40"/>
+      <c r="V51" s="40"/>
+      <c r="W51" s="40"/>
+      <c r="X51" s="40"/>
+      <c r="Y51" s="40"/>
+      <c r="Z51" s="40"/>
+      <c r="AA51" s="40"/>
+      <c r="AB51" s="40"/>
     </row>
     <row r="52" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="P52" s="12" t="s">
@@ -6028,42 +6021,42 @@
       <c r="T55" s="12"/>
     </row>
     <row r="56" spans="2:29" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O56" s="65" t="s">
+      <c r="O56" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="P56" s="65"/>
-      <c r="Q56" s="65"/>
-      <c r="R56" s="65"/>
-      <c r="S56" s="65"/>
-      <c r="T56" s="65"/>
-      <c r="U56" s="65"/>
-      <c r="V56" s="65"/>
-      <c r="W56" s="65"/>
-      <c r="X56" s="65"/>
-      <c r="Y56" s="65"/>
-      <c r="Z56" s="65"/>
-      <c r="AA56" s="65"/>
-      <c r="AB56" s="65"/>
-      <c r="AC56" s="65"/>
+      <c r="P56" s="64"/>
+      <c r="Q56" s="64"/>
+      <c r="R56" s="64"/>
+      <c r="S56" s="64"/>
+      <c r="T56" s="64"/>
+      <c r="U56" s="64"/>
+      <c r="V56" s="64"/>
+      <c r="W56" s="64"/>
+      <c r="X56" s="64"/>
+      <c r="Y56" s="64"/>
+      <c r="Z56" s="64"/>
+      <c r="AA56" s="64"/>
+      <c r="AB56" s="64"/>
+      <c r="AC56" s="64"/>
     </row>
     <row r="58" spans="2:29" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O58" s="70" t="s">
+      <c r="O58" s="69" t="s">
         <v>87</v>
       </c>
-      <c r="P58" s="70"/>
-      <c r="Q58" s="70"/>
-      <c r="R58" s="70"/>
-      <c r="S58" s="70"/>
-      <c r="T58" s="70"/>
-      <c r="U58" s="70"/>
-      <c r="V58" s="70"/>
-      <c r="W58" s="70"/>
-      <c r="X58" s="70"/>
-      <c r="Y58" s="70"/>
-      <c r="Z58" s="70"/>
-      <c r="AA58" s="70"/>
-      <c r="AB58" s="70"/>
-      <c r="AC58" s="70"/>
+      <c r="P58" s="69"/>
+      <c r="Q58" s="69"/>
+      <c r="R58" s="69"/>
+      <c r="S58" s="69"/>
+      <c r="T58" s="69"/>
+      <c r="U58" s="69"/>
+      <c r="V58" s="69"/>
+      <c r="W58" s="69"/>
+      <c r="X58" s="69"/>
+      <c r="Y58" s="69"/>
+      <c r="Z58" s="69"/>
+      <c r="AA58" s="69"/>
+      <c r="AB58" s="69"/>
+      <c r="AC58" s="69"/>
     </row>
     <row r="59" spans="2:29" ht="19.5" x14ac:dyDescent="0.25">
       <c r="O59" s="18"/>
@@ -6083,59 +6076,59 @@
       <c r="AC59" s="17"/>
     </row>
     <row r="60" spans="2:29" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O60" s="71" t="s">
-        <v>172</v>
-      </c>
-      <c r="P60" s="72"/>
-      <c r="Q60" s="72"/>
-      <c r="R60" s="72"/>
-      <c r="S60" s="72"/>
-      <c r="T60" s="72"/>
-      <c r="U60" s="72"/>
-      <c r="V60" s="72"/>
-      <c r="W60" s="72"/>
-      <c r="X60" s="72"/>
-      <c r="Y60" s="72"/>
-      <c r="Z60" s="72"/>
-      <c r="AA60" s="72"/>
-      <c r="AB60" s="72"/>
-      <c r="AC60" s="72"/>
+      <c r="O60" s="70" t="s">
+        <v>168</v>
+      </c>
+      <c r="P60" s="71"/>
+      <c r="Q60" s="71"/>
+      <c r="R60" s="71"/>
+      <c r="S60" s="71"/>
+      <c r="T60" s="71"/>
+      <c r="U60" s="71"/>
+      <c r="V60" s="71"/>
+      <c r="W60" s="71"/>
+      <c r="X60" s="71"/>
+      <c r="Y60" s="71"/>
+      <c r="Z60" s="71"/>
+      <c r="AA60" s="71"/>
+      <c r="AB60" s="71"/>
+      <c r="AC60" s="71"/>
     </row>
     <row r="61" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O61" s="36"/>
-      <c r="P61" s="34"/>
-      <c r="Q61" s="34"/>
-      <c r="R61" s="34"/>
-      <c r="S61" s="34"/>
-      <c r="T61" s="34"/>
-      <c r="U61" s="34"/>
-      <c r="V61" s="34"/>
-      <c r="W61" s="34"/>
-      <c r="X61" s="34"/>
-      <c r="Y61" s="34"/>
-      <c r="Z61" s="34"/>
-      <c r="AA61" s="34"/>
-      <c r="AB61" s="34"/>
-      <c r="AC61" s="34"/>
+      <c r="O61" s="35"/>
+      <c r="P61" s="33"/>
+      <c r="Q61" s="33"/>
+      <c r="R61" s="33"/>
+      <c r="S61" s="33"/>
+      <c r="T61" s="33"/>
+      <c r="U61" s="33"/>
+      <c r="V61" s="33"/>
+      <c r="W61" s="33"/>
+      <c r="X61" s="33"/>
+      <c r="Y61" s="33"/>
+      <c r="Z61" s="33"/>
+      <c r="AA61" s="33"/>
+      <c r="AB61" s="33"/>
+      <c r="AC61" s="33"/>
     </row>
     <row r="62" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O62" s="58" t="s">
-        <v>236</v>
-      </c>
-      <c r="P62" s="59"/>
-      <c r="Q62" s="59"/>
-      <c r="R62" s="59"/>
-      <c r="S62" s="59"/>
-      <c r="T62" s="59"/>
-      <c r="U62" s="59"/>
-      <c r="V62" s="59"/>
-      <c r="W62" s="59"/>
-      <c r="X62" s="59"/>
-      <c r="Y62" s="59"/>
-      <c r="Z62" s="59"/>
-      <c r="AA62" s="59"/>
-      <c r="AB62" s="34"/>
-      <c r="AC62" s="34"/>
+      <c r="O62" s="57" t="s">
+        <v>232</v>
+      </c>
+      <c r="P62" s="58"/>
+      <c r="Q62" s="58"/>
+      <c r="R62" s="58"/>
+      <c r="S62" s="58"/>
+      <c r="T62" s="58"/>
+      <c r="U62" s="58"/>
+      <c r="V62" s="58"/>
+      <c r="W62" s="58"/>
+      <c r="X62" s="58"/>
+      <c r="Y62" s="58"/>
+      <c r="Z62" s="58"/>
+      <c r="AA62" s="58"/>
+      <c r="AB62" s="33"/>
+      <c r="AC62" s="33"/>
     </row>
     <row r="64" spans="2:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="O64" s="8" t="s">
@@ -6146,23 +6139,23 @@
       <c r="O65" s="8"/>
     </row>
     <row r="66" spans="15:29" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O66" s="68" t="s">
-        <v>171</v>
-      </c>
-      <c r="P66" s="61"/>
-      <c r="Q66" s="61"/>
-      <c r="R66" s="61"/>
-      <c r="S66" s="61"/>
-      <c r="T66" s="61"/>
-      <c r="U66" s="61"/>
-      <c r="V66" s="61"/>
-      <c r="W66" s="61"/>
-      <c r="X66" s="61"/>
-      <c r="Y66" s="61"/>
-      <c r="Z66" s="61"/>
-      <c r="AA66" s="61"/>
-      <c r="AB66" s="61"/>
-      <c r="AC66" s="61"/>
+      <c r="O66" s="67" t="s">
+        <v>167</v>
+      </c>
+      <c r="P66" s="60"/>
+      <c r="Q66" s="60"/>
+      <c r="R66" s="60"/>
+      <c r="S66" s="60"/>
+      <c r="T66" s="60"/>
+      <c r="U66" s="60"/>
+      <c r="V66" s="60"/>
+      <c r="W66" s="60"/>
+      <c r="X66" s="60"/>
+      <c r="Y66" s="60"/>
+      <c r="Z66" s="60"/>
+      <c r="AA66" s="60"/>
+      <c r="AB66" s="60"/>
+      <c r="AC66" s="60"/>
     </row>
     <row r="67" spans="15:29" ht="19.5" x14ac:dyDescent="0.25">
       <c r="O67" s="18"/>
@@ -6182,42 +6175,42 @@
       <c r="AC67" s="17"/>
     </row>
     <row r="68" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O68" s="69" t="s">
+      <c r="O68" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="P68" s="69"/>
-      <c r="Q68" s="69"/>
-      <c r="R68" s="69"/>
-      <c r="S68" s="69"/>
-      <c r="T68" s="28"/>
-      <c r="U68" s="28"/>
-      <c r="V68" s="28"/>
-      <c r="W68" s="28"/>
-      <c r="X68" s="28"/>
-      <c r="Y68" s="28"/>
-      <c r="Z68" s="28"/>
-      <c r="AA68" s="28"/>
-      <c r="AB68" s="28"/>
-      <c r="AC68" s="28"/>
+      <c r="P68" s="68"/>
+      <c r="Q68" s="68"/>
+      <c r="R68" s="68"/>
+      <c r="S68" s="68"/>
+      <c r="T68" s="27"/>
+      <c r="U68" s="27"/>
+      <c r="V68" s="27"/>
+      <c r="W68" s="27"/>
+      <c r="X68" s="27"/>
+      <c r="Y68" s="27"/>
+      <c r="Z68" s="27"/>
+      <c r="AA68" s="27"/>
+      <c r="AB68" s="27"/>
+      <c r="AC68" s="27"/>
     </row>
     <row r="69" spans="15:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O69" s="65" t="s">
+      <c r="O69" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="P69" s="41"/>
-      <c r="Q69" s="41"/>
-      <c r="R69" s="41"/>
-      <c r="S69" s="41"/>
-      <c r="T69" s="41"/>
-      <c r="U69" s="41"/>
-      <c r="V69" s="41"/>
-      <c r="W69" s="41"/>
-      <c r="X69" s="41"/>
-      <c r="Y69" s="41"/>
-      <c r="Z69" s="41"/>
-      <c r="AA69" s="41"/>
-      <c r="AB69" s="41"/>
-      <c r="AC69" s="41"/>
+      <c r="P69" s="40"/>
+      <c r="Q69" s="40"/>
+      <c r="R69" s="40"/>
+      <c r="S69" s="40"/>
+      <c r="T69" s="40"/>
+      <c r="U69" s="40"/>
+      <c r="V69" s="40"/>
+      <c r="W69" s="40"/>
+      <c r="X69" s="40"/>
+      <c r="Y69" s="40"/>
+      <c r="Z69" s="40"/>
+      <c r="AA69" s="40"/>
+      <c r="AB69" s="40"/>
+      <c r="AC69" s="40"/>
     </row>
     <row r="70" spans="15:29" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="O70" s="12" t="s">
@@ -6225,42 +6218,42 @@
       </c>
     </row>
     <row r="71" spans="15:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O71" s="69" t="s">
+      <c r="O71" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="P71" s="69"/>
-      <c r="Q71" s="69"/>
-      <c r="R71" s="69"/>
-      <c r="S71" s="69"/>
-      <c r="T71" s="28"/>
-      <c r="U71" s="28"/>
-      <c r="V71" s="28"/>
-      <c r="W71" s="28"/>
-      <c r="X71" s="28"/>
-      <c r="Y71" s="28"/>
-      <c r="Z71" s="28"/>
-      <c r="AA71" s="28"/>
-      <c r="AB71" s="28"/>
-      <c r="AC71" s="28"/>
+      <c r="P71" s="68"/>
+      <c r="Q71" s="68"/>
+      <c r="R71" s="68"/>
+      <c r="S71" s="68"/>
+      <c r="T71" s="27"/>
+      <c r="U71" s="27"/>
+      <c r="V71" s="27"/>
+      <c r="W71" s="27"/>
+      <c r="X71" s="27"/>
+      <c r="Y71" s="27"/>
+      <c r="Z71" s="27"/>
+      <c r="AA71" s="27"/>
+      <c r="AB71" s="27"/>
+      <c r="AC71" s="27"/>
     </row>
     <row r="72" spans="15:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O72" s="65" t="s">
+      <c r="O72" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="P72" s="65"/>
-      <c r="Q72" s="65"/>
-      <c r="R72" s="65"/>
-      <c r="S72" s="65"/>
-      <c r="T72" s="65"/>
-      <c r="U72" s="65"/>
-      <c r="V72" s="65"/>
-      <c r="W72" s="65"/>
-      <c r="X72" s="65"/>
-      <c r="Y72" s="65"/>
-      <c r="Z72" s="65"/>
-      <c r="AA72" s="65"/>
-      <c r="AB72" s="65"/>
-      <c r="AC72" s="65"/>
+      <c r="P72" s="64"/>
+      <c r="Q72" s="64"/>
+      <c r="R72" s="64"/>
+      <c r="S72" s="64"/>
+      <c r="T72" s="64"/>
+      <c r="U72" s="64"/>
+      <c r="V72" s="64"/>
+      <c r="W72" s="64"/>
+      <c r="X72" s="64"/>
+      <c r="Y72" s="64"/>
+      <c r="Z72" s="64"/>
+      <c r="AA72" s="64"/>
+      <c r="AB72" s="64"/>
+      <c r="AC72" s="64"/>
     </row>
     <row r="73" spans="15:29" ht="19.5" x14ac:dyDescent="0.3">
       <c r="O73" s="12" t="s">
@@ -6310,7 +6303,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A2:AE135"/>
+  <dimension ref="A2:AE132"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
@@ -6323,129 +6316,129 @@
     </row>
     <row r="4" spans="1:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
-      <c r="B4" s="75" t="s">
+      <c r="B4" s="74" t="s">
         <v>143</v>
       </c>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
     </row>
     <row r="5" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="L5" s="48" t="s">
+      <c r="L5" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
     </row>
     <row r="6" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
-      <c r="L6" s="78" t="s">
+      <c r="L6" s="77" t="s">
         <v>120</v>
       </c>
-      <c r="M6" s="78"/>
-      <c r="N6" s="78"/>
-      <c r="O6" s="78"/>
-      <c r="P6" s="78"/>
+      <c r="M6" s="77"/>
+      <c r="N6" s="77"/>
+      <c r="O6" s="77"/>
+      <c r="P6" s="77"/>
     </row>
     <row r="7" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
-      <c r="L7" s="77" t="s">
+      <c r="L7" s="76" t="s">
         <v>121</v>
       </c>
-      <c r="M7" s="77"/>
-      <c r="N7" s="77"/>
-      <c r="O7" s="77"/>
-      <c r="P7" s="77"/>
+      <c r="M7" s="76"/>
+      <c r="N7" s="76"/>
+      <c r="O7" s="76"/>
+      <c r="P7" s="76"/>
     </row>
     <row r="8" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
-      <c r="L8" s="78" t="s">
+      <c r="L8" s="77" t="s">
         <v>122</v>
       </c>
-      <c r="M8" s="78"/>
-      <c r="N8" s="78"/>
-      <c r="O8" s="78"/>
-      <c r="P8" s="78"/>
+      <c r="M8" s="77"/>
+      <c r="N8" s="77"/>
+      <c r="O8" s="77"/>
+      <c r="P8" s="77"/>
     </row>
     <row r="9" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1"/>
-      <c r="L9" s="78" t="s">
+      <c r="L9" s="77" t="s">
         <v>123</v>
       </c>
-      <c r="M9" s="78"/>
-      <c r="N9" s="78"/>
-      <c r="O9" s="78"/>
-      <c r="P9" s="78"/>
+      <c r="M9" s="77"/>
+      <c r="N9" s="77"/>
+      <c r="O9" s="77"/>
+      <c r="P9" s="77"/>
     </row>
     <row r="10" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
-      <c r="L10" s="77" t="s">
+      <c r="L10" s="76" t="s">
         <v>124</v>
       </c>
-      <c r="M10" s="77"/>
-      <c r="N10" s="77"/>
-      <c r="O10" s="77"/>
-      <c r="P10" s="77"/>
+      <c r="M10" s="76"/>
+      <c r="N10" s="76"/>
+      <c r="O10" s="76"/>
+      <c r="P10" s="76"/>
     </row>
     <row r="11" spans="1:31" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
-      <c r="L11" s="77" t="s">
+      <c r="L11" s="76" t="s">
         <v>125</v>
       </c>
-      <c r="M11" s="78"/>
-      <c r="N11" s="78"/>
-      <c r="O11" s="78"/>
-      <c r="P11" s="78"/>
+      <c r="M11" s="77"/>
+      <c r="N11" s="77"/>
+      <c r="O11" s="77"/>
+      <c r="P11" s="77"/>
     </row>
     <row r="12" spans="1:31" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1"/>
-      <c r="L12" s="77" t="s">
+      <c r="L12" s="76" t="s">
         <v>126</v>
       </c>
-      <c r="M12" s="77"/>
-      <c r="N12" s="77"/>
-      <c r="O12" s="77"/>
-      <c r="P12" s="77"/>
-      <c r="R12" s="76" t="s">
+      <c r="M12" s="76"/>
+      <c r="N12" s="76"/>
+      <c r="O12" s="76"/>
+      <c r="P12" s="76"/>
+      <c r="R12" s="75" t="s">
         <v>138</v>
       </c>
-      <c r="S12" s="76"/>
-      <c r="T12" s="76"/>
-      <c r="U12" s="76"/>
-      <c r="V12" s="76"/>
-      <c r="W12" s="76"/>
-      <c r="X12" s="76"/>
-      <c r="Y12" s="76"/>
-      <c r="Z12" s="76"/>
-      <c r="AA12" s="76"/>
-      <c r="AB12" s="76"/>
-      <c r="AC12" s="76"/>
-      <c r="AD12" s="31"/>
-      <c r="AE12" s="31"/>
+      <c r="S12" s="75"/>
+      <c r="T12" s="75"/>
+      <c r="U12" s="75"/>
+      <c r="V12" s="75"/>
+      <c r="W12" s="75"/>
+      <c r="X12" s="75"/>
+      <c r="Y12" s="75"/>
+      <c r="Z12" s="75"/>
+      <c r="AA12" s="75"/>
+      <c r="AB12" s="75"/>
+      <c r="AC12" s="75"/>
+      <c r="AD12" s="30"/>
+      <c r="AE12" s="30"/>
     </row>
     <row r="13" spans="1:31" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
-      <c r="L13" s="78" t="s">
+      <c r="L13" s="77" t="s">
         <v>127</v>
       </c>
-      <c r="M13" s="78"/>
-      <c r="N13" s="78"/>
-      <c r="O13" s="78"/>
-      <c r="P13" s="78"/>
+      <c r="M13" s="77"/>
+      <c r="N13" s="77"/>
+      <c r="O13" s="77"/>
+      <c r="P13" s="77"/>
     </row>
     <row r="14" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A14" s="1"/>
-      <c r="L14" s="78" t="s">
+      <c r="L14" s="77" t="s">
         <v>128</v>
       </c>
-      <c r="M14" s="78"/>
-      <c r="N14" s="78"/>
-      <c r="O14" s="78"/>
-      <c r="P14" s="78"/>
+      <c r="M14" s="77"/>
+      <c r="N14" s="77"/>
+      <c r="O14" s="77"/>
+      <c r="P14" s="77"/>
     </row>
     <row r="15" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
@@ -6453,146 +6446,146 @@
     </row>
     <row r="16" spans="1:31" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
-      <c r="L16" s="48" t="s">
+      <c r="L16" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="M16" s="48"/>
-      <c r="N16" s="48"/>
-      <c r="O16" s="48" t="s">
+      <c r="M16" s="47"/>
+      <c r="N16" s="47"/>
+      <c r="O16" s="47" t="s">
         <v>132</v>
       </c>
-      <c r="P16" s="48"/>
-      <c r="Q16" s="48"/>
-      <c r="R16" s="48"/>
-      <c r="S16" s="48"/>
-      <c r="T16" s="48"/>
+      <c r="P16" s="47"/>
+      <c r="Q16" s="47"/>
+      <c r="R16" s="47"/>
+      <c r="S16" s="47"/>
+      <c r="T16" s="47"/>
     </row>
     <row r="17" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A17" s="1"/>
-      <c r="L17" s="54" t="s">
+      <c r="L17" s="53" t="s">
         <v>133</v>
       </c>
-      <c r="M17" s="54"/>
-      <c r="N17" s="54"/>
-      <c r="O17" s="74" t="s">
+      <c r="M17" s="53"/>
+      <c r="N17" s="53"/>
+      <c r="O17" s="73" t="s">
         <v>131</v>
       </c>
-      <c r="P17" s="74"/>
-      <c r="Q17" s="74"/>
-      <c r="R17" s="74"/>
-      <c r="S17" s="74"/>
-      <c r="T17" s="74"/>
+      <c r="P17" s="73"/>
+      <c r="Q17" s="73"/>
+      <c r="R17" s="73"/>
+      <c r="S17" s="73"/>
+      <c r="T17" s="73"/>
     </row>
     <row r="18" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
-      <c r="L18" s="54" t="s">
+      <c r="L18" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="M18" s="54"/>
-      <c r="N18" s="54"/>
-      <c r="O18" s="74" t="s">
+      <c r="M18" s="53"/>
+      <c r="N18" s="53"/>
+      <c r="O18" s="73" t="s">
         <v>135</v>
       </c>
-      <c r="P18" s="74"/>
-      <c r="Q18" s="74"/>
-      <c r="R18" s="74"/>
-      <c r="S18" s="74"/>
-      <c r="T18" s="74"/>
+      <c r="P18" s="73"/>
+      <c r="Q18" s="73"/>
+      <c r="R18" s="73"/>
+      <c r="S18" s="73"/>
+      <c r="T18" s="73"/>
     </row>
     <row r="19" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
-      <c r="L19" s="54" t="s">
+      <c r="L19" s="53" t="s">
         <v>136</v>
       </c>
-      <c r="M19" s="54"/>
-      <c r="N19" s="54"/>
-      <c r="O19" s="74" t="s">
+      <c r="M19" s="53"/>
+      <c r="N19" s="53"/>
+      <c r="O19" s="73" t="s">
         <v>137</v>
       </c>
-      <c r="P19" s="74"/>
-      <c r="Q19" s="74"/>
-      <c r="R19" s="74"/>
-      <c r="S19" s="74"/>
-      <c r="T19" s="74"/>
+      <c r="P19" s="73"/>
+      <c r="Q19" s="73"/>
+      <c r="R19" s="73"/>
+      <c r="S19" s="73"/>
+      <c r="T19" s="73"/>
     </row>
     <row r="20" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
     </row>
     <row r="21" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A21" s="1"/>
-      <c r="L21" s="48" t="s">
+      <c r="L21" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="M21" s="48"/>
-      <c r="N21" s="48"/>
-      <c r="O21" s="48" t="s">
-        <v>292</v>
-      </c>
-      <c r="P21" s="48"/>
-      <c r="Q21" s="48"/>
-      <c r="R21" s="48"/>
-      <c r="S21" s="48"/>
-      <c r="T21" s="48"/>
-      <c r="U21" s="48"/>
-      <c r="V21" s="48"/>
-      <c r="W21" s="48"/>
+      <c r="M21" s="47"/>
+      <c r="N21" s="47"/>
+      <c r="O21" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="P21" s="47"/>
+      <c r="Q21" s="47"/>
+      <c r="R21" s="47"/>
+      <c r="S21" s="47"/>
+      <c r="T21" s="47"/>
+      <c r="U21" s="47"/>
+      <c r="V21" s="47"/>
+      <c r="W21" s="47"/>
     </row>
     <row r="22" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A22" s="1"/>
-      <c r="L22" s="54" t="s">
+      <c r="L22" s="53" t="s">
         <v>133</v>
       </c>
-      <c r="M22" s="54"/>
-      <c r="N22" s="54"/>
-      <c r="O22" s="73" t="s">
-        <v>289</v>
-      </c>
-      <c r="P22" s="73"/>
-      <c r="Q22" s="73"/>
-      <c r="R22" s="73"/>
-      <c r="S22" s="73"/>
-      <c r="T22" s="73"/>
-      <c r="U22" s="73"/>
-      <c r="V22" s="73"/>
-      <c r="W22" s="73"/>
+      <c r="M22" s="53"/>
+      <c r="N22" s="53"/>
+      <c r="O22" s="72" t="s">
+        <v>285</v>
+      </c>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="72"/>
+      <c r="T22" s="72"/>
+      <c r="U22" s="72"/>
+      <c r="V22" s="72"/>
+      <c r="W22" s="72"/>
     </row>
     <row r="23" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A23" s="1"/>
-      <c r="L23" s="54" t="s">
+      <c r="L23" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="M23" s="54"/>
-      <c r="N23" s="54"/>
-      <c r="O23" s="73" t="s">
-        <v>290</v>
-      </c>
-      <c r="P23" s="73"/>
-      <c r="Q23" s="73"/>
-      <c r="R23" s="73"/>
-      <c r="S23" s="73"/>
-      <c r="T23" s="73"/>
-      <c r="U23" s="73"/>
-      <c r="V23" s="73"/>
-      <c r="W23" s="73"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="72" t="s">
+        <v>286</v>
+      </c>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="72"/>
+      <c r="T23" s="72"/>
+      <c r="U23" s="72"/>
+      <c r="V23" s="72"/>
+      <c r="W23" s="72"/>
     </row>
     <row r="24" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A24" s="1"/>
-      <c r="L24" s="54" t="s">
+      <c r="L24" s="53" t="s">
         <v>136</v>
       </c>
-      <c r="M24" s="54"/>
-      <c r="N24" s="54"/>
-      <c r="O24" s="73" t="s">
-        <v>291</v>
-      </c>
-      <c r="P24" s="73"/>
-      <c r="Q24" s="73"/>
-      <c r="R24" s="73"/>
-      <c r="S24" s="73"/>
-      <c r="T24" s="73"/>
-      <c r="U24" s="73"/>
-      <c r="V24" s="73"/>
-      <c r="W24" s="73"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="53"/>
+      <c r="O24" s="72" t="s">
+        <v>287</v>
+      </c>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="72"/>
+      <c r="T24" s="72"/>
+      <c r="U24" s="72"/>
+      <c r="V24" s="72"/>
+      <c r="W24" s="72"/>
     </row>
     <row r="25" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
@@ -6610,7 +6603,7 @@
     </row>
     <row r="29" spans="1:23" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B29" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
@@ -6623,7 +6616,7 @@
     </row>
     <row r="60" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B60" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="87" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
@@ -6641,200 +6634,190 @@
     </row>
     <row r="91" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B91" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B93" s="128" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B94" s="128" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B96" s="8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B98" s="20" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B100" s="20" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="93" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B93" s="20" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="95" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B95" s="22" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B96" s="22" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="97" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B97" s="22" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="99" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B99" s="8" t="s">
+    <row r="101" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B101" s="20"/>
+    </row>
+    <row r="102" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B102" s="20" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B104" s="78" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="101" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B101" s="20" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="103" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B103" s="20" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="104" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B104" s="20"/>
-    </row>
-    <row r="105" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="B105" s="20" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="107" spans="1:25" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B107" s="79" t="s">
-        <v>152</v>
-      </c>
-      <c r="C107" s="79"/>
-      <c r="D107" s="79"/>
-      <c r="E107" s="79"/>
-      <c r="F107" s="79"/>
-      <c r="G107" s="79"/>
-      <c r="H107" s="79"/>
-      <c r="I107" s="79"/>
-      <c r="J107" s="79"/>
-      <c r="K107" s="79"/>
-      <c r="L107" s="79"/>
-      <c r="M107" s="79"/>
-      <c r="N107" s="79"/>
-      <c r="O107" s="79"/>
-      <c r="P107" s="79"/>
-      <c r="Q107" s="79"/>
-      <c r="R107" s="79"/>
-      <c r="S107" s="79"/>
-      <c r="T107" s="79"/>
-      <c r="U107" s="79"/>
-      <c r="V107" s="79"/>
-      <c r="W107" s="79"/>
-      <c r="X107" s="79"/>
-      <c r="Y107" s="79"/>
-    </row>
-    <row r="110" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A110" s="1" t="s">
+      <c r="C104" s="78"/>
+      <c r="D104" s="78"/>
+      <c r="E104" s="78"/>
+      <c r="F104" s="78"/>
+      <c r="G104" s="78"/>
+      <c r="H104" s="78"/>
+      <c r="I104" s="78"/>
+      <c r="J104" s="78"/>
+      <c r="K104" s="78"/>
+      <c r="L104" s="78"/>
+      <c r="M104" s="78"/>
+      <c r="N104" s="78"/>
+      <c r="O104" s="78"/>
+      <c r="P104" s="78"/>
+      <c r="Q104" s="78"/>
+      <c r="R104" s="78"/>
+      <c r="S104" s="78"/>
+      <c r="T104" s="78"/>
+      <c r="U104" s="78"/>
+      <c r="V104" s="78"/>
+      <c r="W104" s="78"/>
+      <c r="X104" s="78"/>
+      <c r="Y104" s="78"/>
+    </row>
+    <row r="107" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A107" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B109" s="8" t="s">
+    